--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-04.xlsx
@@ -391,7 +391,7 @@
     <t>Newells</t>
   </si>
   <si>
-    <t>2026-05-02 01:38:18</t>
+    <t>2026-05-02 04:08:47</t>
   </si>
 </sst>
 </file>
@@ -1217,13 +1217,13 @@
         <v>9.6</v>
       </c>
       <c r="AH3">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI3">
         <v>65</v>
       </c>
       <c r="AJ3">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AK3">
         <v>17</v>
@@ -1232,10 +1232,10 @@
         <v>32</v>
       </c>
       <c r="AM3">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AN3">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AO3">
         <v>55</v>
@@ -1250,7 +1250,7 @@
         <v>36</v>
       </c>
       <c r="AS3">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AT3">
         <v>9.6</v>
@@ -1292,7 +1292,7 @@
         <v>7.8</v>
       </c>
       <c r="BG3">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="BH3" t="s">
         <v>125</v>
@@ -1694,7 +1694,7 @@
         <v>3.25</v>
       </c>
       <c r="K6">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="L6">
         <v>0</v>
@@ -1748,7 +1748,7 @@
         <v>11</v>
       </c>
       <c r="AC6">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AD6">
         <v>12.5</v>
@@ -1817,7 +1817,7 @@
         <v>12</v>
       </c>
       <c r="AZ6">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BA6">
         <v>28</v>
@@ -1832,7 +1832,7 @@
         <v>29</v>
       </c>
       <c r="BE6">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BF6">
         <v>24</v>
@@ -2774,7 +2774,7 @@
         <v>1.6</v>
       </c>
       <c r="G12">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="H12">
         <v>5.5</v>
@@ -3362,7 +3362,7 @@
         <v>1.97</v>
       </c>
       <c r="U15">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="V15">
         <v>0</v>
@@ -3619,13 +3619,13 @@
         <v>13</v>
       </c>
       <c r="AT16">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AU16">
         <v>10.5</v>
       </c>
       <c r="AV16">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AW16">
         <v>14</v>
@@ -3684,7 +3684,7 @@
         <v>2.36</v>
       </c>
       <c r="G17">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="H17">
         <v>3.5</v>
@@ -3711,7 +3711,7 @@
         <v>1.68</v>
       </c>
       <c r="P17">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="Q17">
         <v>3</v>
@@ -3732,7 +3732,7 @@
         <v>1.33</v>
       </c>
       <c r="W17">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="X17">
         <v>8</v>
@@ -4045,22 +4045,22 @@
         <v>122</v>
       </c>
       <c r="F19">
-        <v>1.27</v>
+        <v>1.91</v>
       </c>
       <c r="G19">
         <v>2.62</v>
       </c>
       <c r="H19">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="I19">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J19">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="K19">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="L19">
         <v>0</v>
@@ -4075,10 +4075,10 @@
         <v>0</v>
       </c>
       <c r="P19">
-        <v>1.6</v>
+        <v>1.94</v>
       </c>
       <c r="Q19">
-        <v>1.94</v>
+        <v>1.65</v>
       </c>
       <c r="R19">
         <v>0</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-04.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="130">
   <si>
     <t>League</t>
   </si>
@@ -214,15 +214,18 @@
     <t>Polish Ekstraklasa</t>
   </si>
   <si>
+    <t>Israeli Premier League</t>
+  </si>
+  <si>
     <t>Norwegian Eliteserien</t>
   </si>
   <si>
-    <t>Israeli Premier League</t>
-  </si>
-  <si>
     <t>Danish Superliga</t>
   </si>
   <si>
+    <t>Portuguese Primeira Liga</t>
+  </si>
+  <si>
     <t>Argentinian Primera Division</t>
   </si>
   <si>
@@ -259,6 +262,9 @@
     <t>16:00:00</t>
   </si>
   <si>
+    <t>16:15:00</t>
+  </si>
+  <si>
     <t>17:00:00</t>
   </si>
   <si>
@@ -289,15 +295,15 @@
     <t>Radomiak Radom</t>
   </si>
   <si>
+    <t>Maccabi Netanya</t>
+  </si>
+  <si>
+    <t>Bnei Sakhnin</t>
+  </si>
+  <si>
     <t>Bodo Glimt</t>
   </si>
   <si>
-    <t>Bnei Sakhnin</t>
-  </si>
-  <si>
-    <t>Maccabi Netanya</t>
-  </si>
-  <si>
     <t>Al Ittihad (EGY)</t>
   </si>
   <si>
@@ -316,6 +322,9 @@
     <t>Everton</t>
   </si>
   <si>
+    <t>Sporting Lisbon</t>
+  </si>
+  <si>
     <t>Gimnasia Mendoza</t>
   </si>
   <si>
@@ -349,15 +358,15 @@
     <t>Lechia Gdansk</t>
   </si>
   <si>
+    <t>Hapoel Jerusalem</t>
+  </si>
+  <si>
+    <t>Maccabi Bnei Raina</t>
+  </si>
+  <si>
     <t>Molde</t>
   </si>
   <si>
-    <t>Maccabi Bnei Raina</t>
-  </si>
-  <si>
-    <t>Hapoel Jerusalem</t>
-  </si>
-  <si>
     <t>Petrojet</t>
   </si>
   <si>
@@ -376,6 +385,9 @@
     <t>Man City</t>
   </si>
   <si>
+    <t>Guimaraes</t>
+  </si>
+  <si>
     <t>Defensa y Justicia</t>
   </si>
   <si>
@@ -391,7 +403,7 @@
     <t>Newells</t>
   </si>
   <si>
-    <t>2026-05-02 04:08:47</t>
+    <t>2026-05-02 06:39:15</t>
   </si>
 </sst>
 </file>
@@ -749,7 +761,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BH21"/>
+  <dimension ref="A1:BH22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:60">
@@ -939,16 +951,16 @@
         <v>60</v>
       </c>
       <c r="B2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="F2">
         <v>2.88</v>
@@ -981,10 +993,10 @@
         <v>0</v>
       </c>
       <c r="P2">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="Q2">
-        <v>2.66</v>
+        <v>1.01</v>
       </c>
       <c r="R2">
         <v>0</v>
@@ -1113,7 +1125,7 @@
         <v>0</v>
       </c>
       <c r="BH2" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="3" spans="1:60">
@@ -1121,19 +1133,19 @@
         <v>61</v>
       </c>
       <c r="B3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E3" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="F3">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="G3">
         <v>1.74</v>
@@ -1202,7 +1214,7 @@
         <v>10.5</v>
       </c>
       <c r="AC3">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD3">
         <v>21</v>
@@ -1217,7 +1229,7 @@
         <v>9.6</v>
       </c>
       <c r="AH3">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI3">
         <v>65</v>
@@ -1250,7 +1262,7 @@
         <v>36</v>
       </c>
       <c r="AS3">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="AT3">
         <v>9.6</v>
@@ -1262,7 +1274,7 @@
         <v>18.5</v>
       </c>
       <c r="AW3">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AX3">
         <v>10.5</v>
@@ -1286,16 +1298,16 @@
         <v>27</v>
       </c>
       <c r="BE3">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BF3">
         <v>7.8</v>
       </c>
       <c r="BG3">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="BH3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="4" spans="1:60">
@@ -1303,16 +1315,16 @@
         <v>62</v>
       </c>
       <c r="B4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D4" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E4" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="F4">
         <v>1.38</v>
@@ -1321,13 +1333,13 @@
         <v>1.62</v>
       </c>
       <c r="H4">
-        <v>2.68</v>
+        <v>1.04</v>
       </c>
       <c r="I4">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="J4">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="K4">
         <v>950</v>
@@ -1345,10 +1357,10 @@
         <v>0</v>
       </c>
       <c r="P4">
-        <v>2.1</v>
+        <v>1.25</v>
       </c>
       <c r="Q4">
-        <v>1.54</v>
+        <v>1.01</v>
       </c>
       <c r="R4">
         <v>0</v>
@@ -1477,7 +1489,7 @@
         <v>0</v>
       </c>
       <c r="BH4" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="5" spans="1:60">
@@ -1485,16 +1497,16 @@
         <v>63</v>
       </c>
       <c r="B5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E5" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="F5">
         <v>2.26</v>
@@ -1659,7 +1671,7 @@
         <v>0</v>
       </c>
       <c r="BH5" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="6" spans="1:60">
@@ -1667,16 +1679,16 @@
         <v>64</v>
       </c>
       <c r="B6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D6" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E6" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="F6">
         <v>3.1</v>
@@ -1826,7 +1838,7 @@
         <v>27</v>
       </c>
       <c r="BC6">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="BD6">
         <v>29</v>
@@ -1841,7 +1853,7 @@
         <v>25</v>
       </c>
       <c r="BH6" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7" spans="1:60">
@@ -1849,34 +1861,34 @@
         <v>65</v>
       </c>
       <c r="B7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D7" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E7" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="F7">
-        <v>2.06</v>
+        <v>1.19</v>
       </c>
       <c r="G7">
-        <v>2.76</v>
+        <v>1000</v>
       </c>
       <c r="H7">
-        <v>2.74</v>
+        <v>1.19</v>
       </c>
       <c r="I7">
-        <v>4</v>
+        <v>1000</v>
       </c>
       <c r="J7">
-        <v>2.56</v>
+        <v>1.01</v>
       </c>
       <c r="K7">
-        <v>6.8</v>
+        <v>85</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -1891,10 +1903,10 @@
         <v>0</v>
       </c>
       <c r="P7">
-        <v>2.02</v>
+        <v>1.25</v>
       </c>
       <c r="Q7">
-        <v>1.57</v>
+        <v>1.01</v>
       </c>
       <c r="R7">
         <v>0</v>
@@ -2023,7 +2035,7 @@
         <v>0</v>
       </c>
       <c r="BH7" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="8" spans="1:60">
@@ -2031,34 +2043,34 @@
         <v>66</v>
       </c>
       <c r="B8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D8" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E8" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="F8">
-        <v>1.31</v>
+        <v>1.69</v>
       </c>
       <c r="G8">
-        <v>1.51</v>
+        <v>2.16</v>
       </c>
       <c r="H8">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I8">
-        <v>25</v>
+        <v>4.5</v>
       </c>
       <c r="J8">
-        <v>5.1</v>
+        <v>3.15</v>
       </c>
       <c r="K8">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="L8">
         <v>0</v>
@@ -2073,10 +2085,10 @@
         <v>0</v>
       </c>
       <c r="P8">
-        <v>3.1</v>
+        <v>2.14</v>
       </c>
       <c r="Q8">
-        <v>1.28</v>
+        <v>1.64</v>
       </c>
       <c r="R8">
         <v>0</v>
@@ -2205,42 +2217,42 @@
         <v>0</v>
       </c>
       <c r="BH8" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="9" spans="1:60">
       <c r="A9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D9" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E9" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="F9">
-        <v>1.98</v>
+        <v>1.18</v>
       </c>
       <c r="G9">
-        <v>2.68</v>
+        <v>2.92</v>
       </c>
       <c r="H9">
-        <v>2.88</v>
+        <v>1.18</v>
       </c>
       <c r="I9">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="J9">
-        <v>2.5</v>
+        <v>1.01</v>
       </c>
       <c r="K9">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="L9">
         <v>0</v>
@@ -2255,10 +2267,10 @@
         <v>0</v>
       </c>
       <c r="P9">
-        <v>1.58</v>
+        <v>1.24</v>
       </c>
       <c r="Q9">
-        <v>1.98</v>
+        <v>1.01</v>
       </c>
       <c r="R9">
         <v>0</v>
@@ -2387,7 +2399,7 @@
         <v>0</v>
       </c>
       <c r="BH9" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="10" spans="1:60">
@@ -2395,34 +2407,34 @@
         <v>67</v>
       </c>
       <c r="B10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D10" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E10" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="F10">
-        <v>1.69</v>
+        <v>1.32</v>
       </c>
       <c r="G10">
-        <v>2.16</v>
+        <v>1000</v>
       </c>
       <c r="H10">
-        <v>3.1</v>
+        <v>1.04</v>
       </c>
       <c r="I10">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="J10">
-        <v>3.15</v>
+        <v>1.03</v>
       </c>
       <c r="K10">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -2437,10 +2449,10 @@
         <v>0</v>
       </c>
       <c r="P10">
-        <v>1.89</v>
+        <v>1.25</v>
       </c>
       <c r="Q10">
-        <v>1.64</v>
+        <v>1.01</v>
       </c>
       <c r="R10">
         <v>0</v>
@@ -2569,7 +2581,7 @@
         <v>0</v>
       </c>
       <c r="BH10" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="11" spans="1:60">
@@ -2577,34 +2589,34 @@
         <v>60</v>
       </c>
       <c r="B11" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D11" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E11" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="F11">
-        <v>2.12</v>
+        <v>1.04</v>
       </c>
       <c r="G11">
-        <v>2.9</v>
+        <v>1000</v>
       </c>
       <c r="H11">
-        <v>3.2</v>
+        <v>1.04</v>
       </c>
       <c r="I11">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="J11">
-        <v>2.18</v>
+        <v>1.01</v>
       </c>
       <c r="K11">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -2619,10 +2631,10 @@
         <v>0</v>
       </c>
       <c r="P11">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="Q11">
-        <v>2.34</v>
+        <v>1.01</v>
       </c>
       <c r="R11">
         <v>0</v>
@@ -2751,7 +2763,7 @@
         <v>0</v>
       </c>
       <c r="BH11" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="12" spans="1:60">
@@ -2759,16 +2771,16 @@
         <v>68</v>
       </c>
       <c r="B12" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C12" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D12" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E12" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="F12">
         <v>1.6</v>
@@ -2933,7 +2945,7 @@
         <v>0</v>
       </c>
       <c r="BH12" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="13" spans="1:60">
@@ -2941,16 +2953,16 @@
         <v>60</v>
       </c>
       <c r="B13" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D13" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E13" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="F13">
         <v>1.63</v>
@@ -2959,7 +2971,7 @@
         <v>2.06</v>
       </c>
       <c r="H13">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="I13">
         <v>1000</v>
@@ -2968,7 +2980,7 @@
         <v>1.94</v>
       </c>
       <c r="K13">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -3115,7 +3127,7 @@
         <v>0</v>
       </c>
       <c r="BH13" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14" spans="1:60">
@@ -3123,16 +3135,16 @@
         <v>63</v>
       </c>
       <c r="B14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C14" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D14" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E14" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="F14">
         <v>1.86</v>
@@ -3297,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="BH14" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="15" spans="1:60">
@@ -3305,25 +3317,25 @@
         <v>64</v>
       </c>
       <c r="B15" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D15" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E15" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F15">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="G15">
         <v>1.68</v>
       </c>
       <c r="H15">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="I15">
         <v>6.2</v>
@@ -3374,10 +3386,10 @@
         <v>16</v>
       </c>
       <c r="Y15">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Z15">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AA15">
         <v>1000</v>
@@ -3392,7 +3404,7 @@
         <v>23</v>
       </c>
       <c r="AE15">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AF15">
         <v>9.6</v>
@@ -3401,31 +3413,31 @@
         <v>10</v>
       </c>
       <c r="AH15">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI15">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AJ15">
+        <v>16.5</v>
+      </c>
+      <c r="AK15">
         <v>18</v>
       </c>
-      <c r="AK15">
-        <v>19</v>
-      </c>
       <c r="AL15">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AM15">
         <v>150</v>
       </c>
       <c r="AN15">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AO15">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AP15">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AQ15">
         <v>17</v>
@@ -3434,7 +3446,7 @@
         <v>25</v>
       </c>
       <c r="AS15">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AT15">
         <v>7.6</v>
@@ -3443,10 +3455,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AV15">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AW15">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="AX15">
         <v>9</v>
@@ -3461,25 +3473,25 @@
         <v>13.5</v>
       </c>
       <c r="BB15">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BC15">
         <v>16</v>
       </c>
       <c r="BD15">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="BE15">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BF15">
         <v>9.199999999999999</v>
       </c>
       <c r="BG15">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BH15" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="16" spans="1:60">
@@ -3487,16 +3499,16 @@
         <v>61</v>
       </c>
       <c r="B16" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C16" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D16" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E16" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="F16">
         <v>7</v>
@@ -3505,10 +3517,10 @@
         <v>7.2</v>
       </c>
       <c r="H16">
+        <v>1.49</v>
+      </c>
+      <c r="I16">
         <v>1.5</v>
-      </c>
-      <c r="I16">
-        <v>1.51</v>
       </c>
       <c r="J16">
         <v>5.1</v>
@@ -3571,7 +3583,7 @@
         <v>11.5</v>
       </c>
       <c r="AD16">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AE16">
         <v>15</v>
@@ -3583,10 +3595,10 @@
         <v>25</v>
       </c>
       <c r="AH16">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI16">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AJ16">
         <v>200</v>
@@ -3619,7 +3631,7 @@
         <v>13</v>
       </c>
       <c r="AT16">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AU16">
         <v>10.5</v>
@@ -3628,10 +3640,10 @@
         <v>9.4</v>
       </c>
       <c r="AW16">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AX16">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AY16">
         <v>22</v>
@@ -3640,7 +3652,7 @@
         <v>20</v>
       </c>
       <c r="BA16">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BB16">
         <v>46</v>
@@ -3649,19 +3661,19 @@
         <v>55</v>
       </c>
       <c r="BD16">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BE16">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BF16">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BG16">
         <v>6</v>
       </c>
       <c r="BH16" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="17" spans="1:60">
@@ -3669,181 +3681,181 @@
         <v>69</v>
       </c>
       <c r="B17" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C17" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D17" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E17" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F17">
-        <v>2.36</v>
+        <v>1.27</v>
       </c>
       <c r="G17">
-        <v>2.56</v>
+        <v>1.31</v>
       </c>
       <c r="H17">
-        <v>3.5</v>
+        <v>10</v>
       </c>
       <c r="I17">
-        <v>4.1</v>
+        <v>22</v>
       </c>
       <c r="J17">
-        <v>2.9</v>
+        <v>6</v>
       </c>
       <c r="K17">
-        <v>3.2</v>
+        <v>9</v>
       </c>
       <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <v>1.25</v>
+      </c>
+      <c r="Q17">
         <v>1.01</v>
       </c>
-      <c r="M17">
-        <v>1.15</v>
-      </c>
-      <c r="N17">
-        <v>2.28</v>
-      </c>
-      <c r="O17">
-        <v>1.68</v>
-      </c>
-      <c r="P17">
-        <v>1.42</v>
-      </c>
-      <c r="Q17">
-        <v>3</v>
-      </c>
       <c r="R17">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="S17">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="T17">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U17">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="V17">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W17">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="X17">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Y17">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="Z17">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="AA17">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="AB17">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="AC17">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AD17">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AE17">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="AF17">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AG17">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="AH17">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AI17">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="AJ17">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="AK17">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="AL17">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="AM17">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="AN17">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="AO17">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="AP17">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AQ17">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AR17">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AS17">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AT17">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AU17">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="AV17">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AW17">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AX17">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AY17">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AZ17">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BA17">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="BB17">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="BC17">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="BD17">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="BE17">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="BF17">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BG17">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="BH17" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="18" spans="1:60">
@@ -3851,181 +3863,181 @@
         <v>70</v>
       </c>
       <c r="B18" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C18" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D18" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E18" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="F18">
-        <v>1.34</v>
+        <v>2.36</v>
       </c>
       <c r="G18">
+        <v>2.56</v>
+      </c>
+      <c r="H18">
+        <v>3.5</v>
+      </c>
+      <c r="I18">
+        <v>4.1</v>
+      </c>
+      <c r="J18">
+        <v>2.9</v>
+      </c>
+      <c r="K18">
+        <v>3.2</v>
+      </c>
+      <c r="L18">
+        <v>1.01</v>
+      </c>
+      <c r="M18">
+        <v>1.15</v>
+      </c>
+      <c r="N18">
+        <v>2.28</v>
+      </c>
+      <c r="O18">
+        <v>1.68</v>
+      </c>
+      <c r="P18">
+        <v>1.42</v>
+      </c>
+      <c r="Q18">
+        <v>3</v>
+      </c>
+      <c r="R18">
+        <v>1.14</v>
+      </c>
+      <c r="S18">
+        <v>6.8</v>
+      </c>
+      <c r="T18">
+        <v>2.2</v>
+      </c>
+      <c r="U18">
         <v>1.62</v>
       </c>
-      <c r="H18">
-        <v>2.6</v>
-      </c>
-      <c r="I18">
-        <v>1000</v>
-      </c>
-      <c r="J18">
-        <v>2.6</v>
-      </c>
-      <c r="K18">
-        <v>1000</v>
-      </c>
-      <c r="L18">
-        <v>0</v>
-      </c>
-      <c r="M18">
-        <v>0</v>
-      </c>
-      <c r="N18">
-        <v>0</v>
-      </c>
-      <c r="O18">
-        <v>0</v>
-      </c>
-      <c r="P18">
-        <v>1.9</v>
-      </c>
-      <c r="Q18">
-        <v>1.63</v>
-      </c>
-      <c r="R18">
-        <v>0</v>
-      </c>
-      <c r="S18">
-        <v>0</v>
-      </c>
-      <c r="T18">
-        <v>0</v>
-      </c>
-      <c r="U18">
-        <v>0</v>
-      </c>
       <c r="V18">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AG18">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AH18">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AI18">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AJ18">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AK18">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AL18">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AM18">
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="AN18">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AO18">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AP18">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AQ18">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AR18">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AS18">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AT18">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AU18">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AV18">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AW18">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AX18">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AY18">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AZ18">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BA18">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BB18">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BC18">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BD18">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BE18">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BF18">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BG18">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BH18" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="19" spans="1:60">
@@ -4033,34 +4045,34 @@
         <v>71</v>
       </c>
       <c r="B19" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C19" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D19" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E19" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="F19">
-        <v>1.91</v>
+        <v>1.34</v>
       </c>
       <c r="G19">
-        <v>2.62</v>
+        <v>1.62</v>
       </c>
       <c r="H19">
-        <v>2.9</v>
+        <v>2.68</v>
       </c>
       <c r="I19">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="J19">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="K19">
-        <v>7.6</v>
+        <v>85</v>
       </c>
       <c r="L19">
         <v>0</v>
@@ -4075,10 +4087,10 @@
         <v>0</v>
       </c>
       <c r="P19">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="Q19">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="R19">
         <v>0</v>
@@ -4207,7 +4219,7 @@
         <v>0</v>
       </c>
       <c r="BH19" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="20" spans="1:60">
@@ -4215,34 +4227,34 @@
         <v>72</v>
       </c>
       <c r="B20" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C20" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D20" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E20" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F20">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="G20">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="K20">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="L20">
         <v>0</v>
@@ -4257,10 +4269,10 @@
         <v>0</v>
       </c>
       <c r="P20">
-        <v>1.05</v>
+        <v>1.94</v>
       </c>
       <c r="Q20">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="R20">
         <v>0</v>
@@ -4389,189 +4401,371 @@
         <v>0</v>
       </c>
       <c r="BH20" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="21" spans="1:60">
       <c r="A21" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B21" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C21" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E21" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21">
+        <v>1.05</v>
+      </c>
+      <c r="Q21">
+        <v>1.01</v>
+      </c>
+      <c r="R21">
+        <v>0</v>
+      </c>
+      <c r="S21">
+        <v>0</v>
+      </c>
+      <c r="T21">
+        <v>0</v>
+      </c>
+      <c r="U21">
+        <v>0</v>
+      </c>
+      <c r="V21">
+        <v>0</v>
+      </c>
+      <c r="W21">
+        <v>0</v>
+      </c>
+      <c r="X21">
+        <v>0</v>
+      </c>
+      <c r="Y21">
+        <v>0</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+      <c r="AA21">
+        <v>0</v>
+      </c>
+      <c r="AB21">
+        <v>0</v>
+      </c>
+      <c r="AC21">
+        <v>0</v>
+      </c>
+      <c r="AD21">
+        <v>0</v>
+      </c>
+      <c r="AE21">
+        <v>0</v>
+      </c>
+      <c r="AF21">
+        <v>0</v>
+      </c>
+      <c r="AG21">
+        <v>0</v>
+      </c>
+      <c r="AH21">
+        <v>0</v>
+      </c>
+      <c r="AI21">
+        <v>0</v>
+      </c>
+      <c r="AJ21">
+        <v>0</v>
+      </c>
+      <c r="AK21">
+        <v>0</v>
+      </c>
+      <c r="AL21">
+        <v>0</v>
+      </c>
+      <c r="AM21">
+        <v>0</v>
+      </c>
+      <c r="AN21">
+        <v>0</v>
+      </c>
+      <c r="AO21">
+        <v>0</v>
+      </c>
+      <c r="AP21">
+        <v>0</v>
+      </c>
+      <c r="AQ21">
+        <v>0</v>
+      </c>
+      <c r="AR21">
+        <v>0</v>
+      </c>
+      <c r="AS21">
+        <v>0</v>
+      </c>
+      <c r="AT21">
+        <v>0</v>
+      </c>
+      <c r="AU21">
+        <v>0</v>
+      </c>
+      <c r="AV21">
+        <v>0</v>
+      </c>
+      <c r="AW21">
+        <v>0</v>
+      </c>
+      <c r="AX21">
+        <v>0</v>
+      </c>
+      <c r="AY21">
+        <v>0</v>
+      </c>
+      <c r="AZ21">
+        <v>0</v>
+      </c>
+      <c r="BA21">
+        <v>0</v>
+      </c>
+      <c r="BB21">
+        <v>0</v>
+      </c>
+      <c r="BC21">
+        <v>0</v>
+      </c>
+      <c r="BD21">
+        <v>0</v>
+      </c>
+      <c r="BE21">
+        <v>0</v>
+      </c>
+      <c r="BF21">
+        <v>0</v>
+      </c>
+      <c r="BG21">
+        <v>0</v>
+      </c>
+      <c r="BH21" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="22" spans="1:60">
+      <c r="A22" t="s">
+        <v>70</v>
+      </c>
+      <c r="B22" t="s">
+        <v>74</v>
+      </c>
+      <c r="C22" t="s">
+        <v>86</v>
+      </c>
+      <c r="D22" t="s">
+        <v>107</v>
+      </c>
+      <c r="E22" t="s">
+        <v>128</v>
+      </c>
+      <c r="F22">
         <v>1.61</v>
       </c>
-      <c r="G21">
+      <c r="G22">
         <v>1.75</v>
       </c>
-      <c r="H21">
+      <c r="H22">
         <v>5.1</v>
       </c>
-      <c r="I21">
+      <c r="I22">
         <v>9.6</v>
       </c>
-      <c r="J21">
+      <c r="J22">
         <v>3.2</v>
       </c>
-      <c r="K21">
+      <c r="K22">
         <v>4.5</v>
       </c>
-      <c r="L21">
+      <c r="L22">
         <v>1.01</v>
       </c>
-      <c r="M21">
+      <c r="M22">
         <v>1.01</v>
       </c>
-      <c r="N21">
+      <c r="N22">
         <v>1.01</v>
       </c>
-      <c r="O21">
+      <c r="O22">
         <v>1.02</v>
       </c>
-      <c r="P21">
+      <c r="P22">
         <v>1.25</v>
       </c>
-      <c r="Q21">
+      <c r="Q22">
         <v>1.44</v>
       </c>
-      <c r="R21">
+      <c r="R22">
         <v>1.18</v>
       </c>
-      <c r="S21">
+      <c r="S22">
         <v>3.6</v>
       </c>
-      <c r="T21">
+      <c r="T22">
         <v>1.01</v>
       </c>
-      <c r="U21">
+      <c r="U22">
         <v>1.01</v>
       </c>
-      <c r="V21">
+      <c r="V22">
         <v>1.13</v>
       </c>
-      <c r="W21">
+      <c r="W22">
         <v>2.32</v>
       </c>
-      <c r="X21">
+      <c r="X22">
         <v>1000</v>
       </c>
-      <c r="Y21">
+      <c r="Y22">
         <v>1000</v>
       </c>
-      <c r="Z21">
+      <c r="Z22">
         <v>1000</v>
       </c>
-      <c r="AA21">
+      <c r="AA22">
         <v>1000</v>
       </c>
-      <c r="AB21">
+      <c r="AB22">
         <v>1000</v>
       </c>
-      <c r="AC21">
+      <c r="AC22">
         <v>1000</v>
       </c>
-      <c r="AD21">
+      <c r="AD22">
         <v>1000</v>
       </c>
-      <c r="AE21">
+      <c r="AE22">
         <v>1000</v>
       </c>
-      <c r="AF21">
+      <c r="AF22">
         <v>1000</v>
       </c>
-      <c r="AG21">
+      <c r="AG22">
         <v>1000</v>
       </c>
-      <c r="AH21">
+      <c r="AH22">
         <v>1000</v>
       </c>
-      <c r="AI21">
+      <c r="AI22">
         <v>1000</v>
       </c>
-      <c r="AJ21">
+      <c r="AJ22">
         <v>1000</v>
       </c>
-      <c r="AK21">
+      <c r="AK22">
         <v>1000</v>
       </c>
-      <c r="AL21">
+      <c r="AL22">
         <v>1000</v>
       </c>
-      <c r="AM21">
+      <c r="AM22">
         <v>1000</v>
       </c>
-      <c r="AN21">
+      <c r="AN22">
         <v>1000</v>
       </c>
-      <c r="AO21">
+      <c r="AO22">
         <v>1000</v>
       </c>
-      <c r="AP21">
+      <c r="AP22">
         <v>1.01</v>
       </c>
-      <c r="AQ21">
+      <c r="AQ22">
         <v>1.01</v>
       </c>
-      <c r="AR21">
+      <c r="AR22">
         <v>1.01</v>
       </c>
-      <c r="AS21">
+      <c r="AS22">
         <v>1.01</v>
       </c>
-      <c r="AT21">
+      <c r="AT22">
         <v>1.01</v>
       </c>
-      <c r="AU21">
+      <c r="AU22">
         <v>1.01</v>
       </c>
-      <c r="AV21">
+      <c r="AV22">
         <v>1.01</v>
       </c>
-      <c r="AW21">
+      <c r="AW22">
         <v>1.01</v>
       </c>
-      <c r="AX21">
+      <c r="AX22">
         <v>1.01</v>
       </c>
-      <c r="AY21">
+      <c r="AY22">
         <v>1.01</v>
       </c>
-      <c r="AZ21">
+      <c r="AZ22">
         <v>1.01</v>
       </c>
-      <c r="BA21">
+      <c r="BA22">
         <v>1.01</v>
       </c>
-      <c r="BB21">
+      <c r="BB22">
         <v>1.01</v>
       </c>
-      <c r="BC21">
+      <c r="BC22">
         <v>1.01</v>
       </c>
-      <c r="BD21">
+      <c r="BD22">
         <v>1.01</v>
       </c>
-      <c r="BE21">
+      <c r="BE22">
         <v>1.01</v>
       </c>
-      <c r="BF21">
+      <c r="BF22">
         <v>1.01</v>
       </c>
-      <c r="BG21">
+      <c r="BG22">
         <v>1.01</v>
       </c>
-      <c r="BH21" t="s">
-        <v>125</v>
+      <c r="BH22" t="s">
+        <v>129</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-04.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="126">
   <si>
     <t>League</t>
   </si>
@@ -214,18 +214,15 @@
     <t>Polish Ekstraklasa</t>
   </si>
   <si>
+    <t>Norwegian Eliteserien</t>
+  </si>
+  <si>
     <t>Israeli Premier League</t>
   </si>
   <si>
-    <t>Norwegian Eliteserien</t>
-  </si>
-  <si>
     <t>Danish Superliga</t>
   </si>
   <si>
-    <t>Portuguese Primeira Liga</t>
-  </si>
-  <si>
     <t>Argentinian Primera Division</t>
   </si>
   <si>
@@ -262,9 +259,6 @@
     <t>16:00:00</t>
   </si>
   <si>
-    <t>16:15:00</t>
-  </si>
-  <si>
     <t>17:00:00</t>
   </si>
   <si>
@@ -295,15 +289,15 @@
     <t>Radomiak Radom</t>
   </si>
   <si>
+    <t>Bodo Glimt</t>
+  </si>
+  <si>
+    <t>Bnei Sakhnin</t>
+  </si>
+  <si>
     <t>Maccabi Netanya</t>
   </si>
   <si>
-    <t>Bnei Sakhnin</t>
-  </si>
-  <si>
-    <t>Bodo Glimt</t>
-  </si>
-  <si>
     <t>Al Ittihad (EGY)</t>
   </si>
   <si>
@@ -322,9 +316,6 @@
     <t>Everton</t>
   </si>
   <si>
-    <t>Sporting Lisbon</t>
-  </si>
-  <si>
     <t>Gimnasia Mendoza</t>
   </si>
   <si>
@@ -358,15 +349,15 @@
     <t>Lechia Gdansk</t>
   </si>
   <si>
+    <t>Molde</t>
+  </si>
+  <si>
+    <t>Maccabi Bnei Raina</t>
+  </si>
+  <si>
     <t>Hapoel Jerusalem</t>
   </si>
   <si>
-    <t>Maccabi Bnei Raina</t>
-  </si>
-  <si>
-    <t>Molde</t>
-  </si>
-  <si>
     <t>Petrojet</t>
   </si>
   <si>
@@ -385,9 +376,6 @@
     <t>Man City</t>
   </si>
   <si>
-    <t>Guimaraes</t>
-  </si>
-  <si>
     <t>Defensa y Justicia</t>
   </si>
   <si>
@@ -403,7 +391,7 @@
     <t>Newells</t>
   </si>
   <si>
-    <t>2026-05-02 06:39:15</t>
+    <t>2026-05-02 09:09:49</t>
   </si>
 </sst>
 </file>
@@ -761,7 +749,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BH22"/>
+  <dimension ref="A1:BH21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:60">
@@ -951,16 +939,16 @@
         <v>60</v>
       </c>
       <c r="B2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C2" t="s">
         <v>74</v>
       </c>
-      <c r="C2" t="s">
-        <v>75</v>
-      </c>
       <c r="D2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="F2">
         <v>2.88</v>
@@ -972,10 +960,10 @@
         <v>2.4</v>
       </c>
       <c r="I2">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="J2">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="K2">
         <v>4.3</v>
@@ -993,10 +981,10 @@
         <v>0</v>
       </c>
       <c r="P2">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="Q2">
-        <v>1.01</v>
+        <v>2.62</v>
       </c>
       <c r="R2">
         <v>0</v>
@@ -1125,7 +1113,7 @@
         <v>0</v>
       </c>
       <c r="BH2" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="3" spans="1:60">
@@ -1133,28 +1121,28 @@
         <v>61</v>
       </c>
       <c r="B3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C3" t="s">
         <v>74</v>
       </c>
-      <c r="C3" t="s">
-        <v>75</v>
-      </c>
       <c r="D3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E3" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F3">
         <v>1.72</v>
       </c>
       <c r="G3">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="H3">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="I3">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="J3">
         <v>4.2</v>
@@ -1169,7 +1157,7 @@
         <v>1.05</v>
       </c>
       <c r="N3">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="O3">
         <v>1.24</v>
@@ -1190,7 +1178,7 @@
         <v>1.75</v>
       </c>
       <c r="U3">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V3">
         <v>0</v>
@@ -1220,7 +1208,7 @@
         <v>21</v>
       </c>
       <c r="AE3">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF3">
         <v>11.5</v>
@@ -1262,7 +1250,7 @@
         <v>36</v>
       </c>
       <c r="AS3">
-        <v>40</v>
+        <v>18.5</v>
       </c>
       <c r="AT3">
         <v>9.6</v>
@@ -1274,7 +1262,7 @@
         <v>18.5</v>
       </c>
       <c r="AW3">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AX3">
         <v>10.5</v>
@@ -1286,7 +1274,7 @@
         <v>16.5</v>
       </c>
       <c r="BA3">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BB3">
         <v>16</v>
@@ -1298,16 +1286,16 @@
         <v>27</v>
       </c>
       <c r="BE3">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="BF3">
         <v>7.8</v>
       </c>
       <c r="BG3">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="BH3" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="4" spans="1:60">
@@ -1315,31 +1303,31 @@
         <v>62</v>
       </c>
       <c r="B4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E4" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F4">
         <v>1.38</v>
       </c>
       <c r="G4">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="H4">
-        <v>1.04</v>
+        <v>2.72</v>
       </c>
       <c r="I4">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="J4">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="K4">
         <v>950</v>
@@ -1357,10 +1345,10 @@
         <v>0</v>
       </c>
       <c r="P4">
-        <v>1.25</v>
+        <v>2.08</v>
       </c>
       <c r="Q4">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="R4">
         <v>0</v>
@@ -1489,7 +1477,7 @@
         <v>0</v>
       </c>
       <c r="BH4" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="5" spans="1:60">
@@ -1497,19 +1485,19 @@
         <v>63</v>
       </c>
       <c r="B5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E5" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="F5">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="G5">
         <v>3.05</v>
@@ -1524,7 +1512,7 @@
         <v>2.9</v>
       </c>
       <c r="K5">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="L5">
         <v>0</v>
@@ -1671,7 +1659,7 @@
         <v>0</v>
       </c>
       <c r="BH5" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="6" spans="1:60">
@@ -1679,16 +1667,16 @@
         <v>64</v>
       </c>
       <c r="B6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D6" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E6" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="F6">
         <v>3.1</v>
@@ -1697,7 +1685,7 @@
         <v>3.15</v>
       </c>
       <c r="H6">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="I6">
         <v>2.68</v>
@@ -1808,7 +1796,7 @@
         <v>14.5</v>
       </c>
       <c r="AS6">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AT6">
         <v>10</v>
@@ -1847,13 +1835,13 @@
         <v>11.5</v>
       </c>
       <c r="BF6">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BG6">
         <v>25</v>
       </c>
       <c r="BH6" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7" spans="1:60">
@@ -1861,34 +1849,34 @@
         <v>65</v>
       </c>
       <c r="B7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D7" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F7">
-        <v>1.19</v>
+        <v>2.16</v>
       </c>
       <c r="G7">
-        <v>1000</v>
+        <v>2.76</v>
       </c>
       <c r="H7">
-        <v>1.19</v>
+        <v>2.74</v>
       </c>
       <c r="I7">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="J7">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="K7">
-        <v>85</v>
+        <v>5.9</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -1903,10 +1891,10 @@
         <v>0</v>
       </c>
       <c r="P7">
-        <v>1.25</v>
+        <v>2.02</v>
       </c>
       <c r="Q7">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="R7">
         <v>0</v>
@@ -2035,7 +2023,7 @@
         <v>0</v>
       </c>
       <c r="BH7" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="8" spans="1:60">
@@ -2043,52 +2031,52 @@
         <v>66</v>
       </c>
       <c r="B8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D8" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E8" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="F8">
-        <v>1.69</v>
+        <v>1.34</v>
       </c>
       <c r="G8">
-        <v>2.16</v>
+        <v>1.51</v>
       </c>
       <c r="H8">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="I8">
-        <v>4.5</v>
+        <v>17.5</v>
       </c>
       <c r="J8">
+        <v>5.1</v>
+      </c>
+      <c r="K8">
+        <v>1000</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
         <v>3.15</v>
       </c>
-      <c r="K8">
-        <v>12</v>
-      </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-      <c r="N8">
-        <v>0</v>
-      </c>
-      <c r="O8">
-        <v>0</v>
-      </c>
-      <c r="P8">
-        <v>2.14</v>
-      </c>
       <c r="Q8">
-        <v>1.64</v>
+        <v>1.27</v>
       </c>
       <c r="R8">
         <v>0</v>
@@ -2217,42 +2205,42 @@
         <v>0</v>
       </c>
       <c r="BH8" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="9" spans="1:60">
       <c r="A9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D9" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E9" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="F9">
-        <v>1.18</v>
+        <v>1.98</v>
       </c>
       <c r="G9">
-        <v>2.92</v>
+        <v>2.68</v>
       </c>
       <c r="H9">
-        <v>1.18</v>
+        <v>2.88</v>
       </c>
       <c r="I9">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="J9">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="K9">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="L9">
         <v>0</v>
@@ -2267,10 +2255,10 @@
         <v>0</v>
       </c>
       <c r="P9">
-        <v>1.24</v>
+        <v>1.58</v>
       </c>
       <c r="Q9">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="R9">
         <v>0</v>
@@ -2399,7 +2387,7 @@
         <v>0</v>
       </c>
       <c r="BH9" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="10" spans="1:60">
@@ -2407,34 +2395,34 @@
         <v>67</v>
       </c>
       <c r="B10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D10" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E10" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="F10">
-        <v>1.32</v>
+        <v>1.69</v>
       </c>
       <c r="G10">
-        <v>1000</v>
+        <v>2.16</v>
       </c>
       <c r="H10">
-        <v>1.04</v>
+        <v>3.1</v>
       </c>
       <c r="I10">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="J10">
-        <v>1.03</v>
+        <v>3.15</v>
       </c>
       <c r="K10">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -2449,10 +2437,10 @@
         <v>0</v>
       </c>
       <c r="P10">
-        <v>1.25</v>
+        <v>2.14</v>
       </c>
       <c r="Q10">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="R10">
         <v>0</v>
@@ -2581,7 +2569,7 @@
         <v>0</v>
       </c>
       <c r="BH10" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="11" spans="1:60">
@@ -2589,34 +2577,34 @@
         <v>60</v>
       </c>
       <c r="B11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D11" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E11" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="F11">
-        <v>1.04</v>
+        <v>2.12</v>
       </c>
       <c r="G11">
-        <v>1000</v>
+        <v>2.9</v>
       </c>
       <c r="H11">
-        <v>1.04</v>
+        <v>3.2</v>
       </c>
       <c r="I11">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="J11">
-        <v>1.01</v>
+        <v>2.62</v>
       </c>
       <c r="K11">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -2631,10 +2619,10 @@
         <v>0</v>
       </c>
       <c r="P11">
-        <v>1.25</v>
+        <v>1.51</v>
       </c>
       <c r="Q11">
-        <v>1.01</v>
+        <v>2.36</v>
       </c>
       <c r="R11">
         <v>0</v>
@@ -2763,7 +2751,7 @@
         <v>0</v>
       </c>
       <c r="BH11" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="12" spans="1:60">
@@ -2771,16 +2759,16 @@
         <v>68</v>
       </c>
       <c r="B12" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C12" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D12" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E12" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F12">
         <v>1.6</v>
@@ -2945,7 +2933,7 @@
         <v>0</v>
       </c>
       <c r="BH12" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="13" spans="1:60">
@@ -2953,16 +2941,16 @@
         <v>60</v>
       </c>
       <c r="B13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C13" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D13" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E13" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="F13">
         <v>1.63</v>
@@ -2974,10 +2962,10 @@
         <v>1.98</v>
       </c>
       <c r="I13">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="J13">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="K13">
         <v>85</v>
@@ -3127,7 +3115,7 @@
         <v>0</v>
       </c>
       <c r="BH13" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14" spans="1:60">
@@ -3135,19 +3123,19 @@
         <v>63</v>
       </c>
       <c r="B14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C14" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D14" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E14" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="F14">
-        <v>1.86</v>
+        <v>1.97</v>
       </c>
       <c r="G14">
         <v>2.38</v>
@@ -3162,7 +3150,7 @@
         <v>3.25</v>
       </c>
       <c r="K14">
-        <v>6.6</v>
+        <v>5.5</v>
       </c>
       <c r="L14">
         <v>0</v>
@@ -3309,7 +3297,7 @@
         <v>0</v>
       </c>
       <c r="BH14" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="15" spans="1:60">
@@ -3317,25 +3305,25 @@
         <v>64</v>
       </c>
       <c r="B15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C15" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D15" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E15" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F15">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="G15">
         <v>1.68</v>
       </c>
       <c r="H15">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="I15">
         <v>6.2</v>
@@ -3365,7 +3353,7 @@
         <v>1.94</v>
       </c>
       <c r="R15">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="S15">
         <v>3.45</v>
@@ -3416,7 +3404,7 @@
         <v>24</v>
       </c>
       <c r="AI15">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AJ15">
         <v>16.5</v>
@@ -3446,7 +3434,7 @@
         <v>25</v>
       </c>
       <c r="AS15">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AT15">
         <v>7.6</v>
@@ -3458,7 +3446,7 @@
         <v>20</v>
       </c>
       <c r="AW15">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AX15">
         <v>9</v>
@@ -3470,7 +3458,7 @@
         <v>21</v>
       </c>
       <c r="BA15">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BB15">
         <v>14.5</v>
@@ -3479,7 +3467,7 @@
         <v>16</v>
       </c>
       <c r="BD15">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="BE15">
         <v>14</v>
@@ -3488,10 +3476,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BG15">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BH15" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="16" spans="1:60">
@@ -3499,31 +3487,31 @@
         <v>61</v>
       </c>
       <c r="B16" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C16" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D16" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E16" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="F16">
+        <v>6.8</v>
+      </c>
+      <c r="G16">
         <v>7</v>
       </c>
-      <c r="G16">
-        <v>7.2</v>
-      </c>
       <c r="H16">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="I16">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="J16">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="K16">
         <v>5.3</v>
@@ -3625,7 +3613,7 @@
         <v>9</v>
       </c>
       <c r="AR16">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AS16">
         <v>13</v>
@@ -3664,16 +3652,16 @@
         <v>55</v>
       </c>
       <c r="BE16">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BF16">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BG16">
         <v>6</v>
       </c>
       <c r="BH16" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="17" spans="1:60">
@@ -3681,181 +3669,181 @@
         <v>69</v>
       </c>
       <c r="B17" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C17" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D17" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E17" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="F17">
-        <v>1.27</v>
+        <v>2.36</v>
       </c>
       <c r="G17">
-        <v>1.31</v>
+        <v>2.56</v>
       </c>
       <c r="H17">
-        <v>10</v>
+        <v>3.5</v>
       </c>
       <c r="I17">
-        <v>22</v>
+        <v>4.1</v>
       </c>
       <c r="J17">
-        <v>6</v>
+        <v>2.9</v>
       </c>
       <c r="K17">
-        <v>9</v>
+        <v>3.2</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M17">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="P17">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="Q17">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AH17">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AI17">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AK17">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AL17">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AM17">
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="AN17">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AO17">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AP17">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AQ17">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AR17">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AS17">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AT17">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AU17">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AV17">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AW17">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AX17">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AY17">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AZ17">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="BA17">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BB17">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BC17">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BD17">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BE17">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BF17">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BG17">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BH17" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="18" spans="1:60">
@@ -3863,181 +3851,181 @@
         <v>70</v>
       </c>
       <c r="B18" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C18" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D18" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E18" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F18">
-        <v>2.36</v>
+        <v>1.34</v>
       </c>
       <c r="G18">
-        <v>2.56</v>
+        <v>1.62</v>
       </c>
       <c r="H18">
-        <v>3.5</v>
+        <v>2.68</v>
       </c>
       <c r="I18">
-        <v>4.1</v>
+        <v>100</v>
       </c>
       <c r="J18">
-        <v>2.9</v>
+        <v>2.68</v>
       </c>
       <c r="K18">
-        <v>3.2</v>
+        <v>85</v>
       </c>
       <c r="L18">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M18">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="N18">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O18">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="P18">
-        <v>1.42</v>
+        <v>1.91</v>
       </c>
       <c r="Q18">
-        <v>3</v>
+        <v>1.63</v>
       </c>
       <c r="R18">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="S18">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="T18">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U18">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="V18">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W18">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="X18">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Y18">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="Z18">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="AA18">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="AB18">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="AC18">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AD18">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AE18">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="AF18">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AG18">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="AH18">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AI18">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="AJ18">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="AK18">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="AL18">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="AM18">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="AN18">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="AO18">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="AP18">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AQ18">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AR18">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AS18">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AT18">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AU18">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="AV18">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AW18">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AX18">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AY18">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AZ18">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BA18">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="BB18">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="BC18">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="BD18">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="BE18">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="BF18">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BG18">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="BH18" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="19" spans="1:60">
@@ -4045,181 +4033,181 @@
         <v>71</v>
       </c>
       <c r="B19" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C19" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D19" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E19" t="s">
+        <v>122</v>
+      </c>
+      <c r="F19">
+        <v>1.91</v>
+      </c>
+      <c r="G19">
+        <v>2.64</v>
+      </c>
+      <c r="H19">
+        <v>2.84</v>
+      </c>
+      <c r="I19">
+        <v>4.5</v>
+      </c>
+      <c r="J19">
+        <v>3.05</v>
+      </c>
+      <c r="K19">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <v>1.94</v>
+      </c>
+      <c r="Q19">
+        <v>1.66</v>
+      </c>
+      <c r="R19">
+        <v>0</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="T19">
+        <v>0</v>
+      </c>
+      <c r="U19">
+        <v>0</v>
+      </c>
+      <c r="V19">
+        <v>0</v>
+      </c>
+      <c r="W19">
+        <v>0</v>
+      </c>
+      <c r="X19">
+        <v>0</v>
+      </c>
+      <c r="Y19">
+        <v>0</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+      <c r="AA19">
+        <v>0</v>
+      </c>
+      <c r="AB19">
+        <v>0</v>
+      </c>
+      <c r="AC19">
+        <v>0</v>
+      </c>
+      <c r="AD19">
+        <v>0</v>
+      </c>
+      <c r="AE19">
+        <v>0</v>
+      </c>
+      <c r="AF19">
+        <v>0</v>
+      </c>
+      <c r="AG19">
+        <v>0</v>
+      </c>
+      <c r="AH19">
+        <v>0</v>
+      </c>
+      <c r="AI19">
+        <v>0</v>
+      </c>
+      <c r="AJ19">
+        <v>0</v>
+      </c>
+      <c r="AK19">
+        <v>0</v>
+      </c>
+      <c r="AL19">
+        <v>0</v>
+      </c>
+      <c r="AM19">
+        <v>0</v>
+      </c>
+      <c r="AN19">
+        <v>0</v>
+      </c>
+      <c r="AO19">
+        <v>0</v>
+      </c>
+      <c r="AP19">
+        <v>0</v>
+      </c>
+      <c r="AQ19">
+        <v>0</v>
+      </c>
+      <c r="AR19">
+        <v>0</v>
+      </c>
+      <c r="AS19">
+        <v>0</v>
+      </c>
+      <c r="AT19">
+        <v>0</v>
+      </c>
+      <c r="AU19">
+        <v>0</v>
+      </c>
+      <c r="AV19">
+        <v>0</v>
+      </c>
+      <c r="AW19">
+        <v>0</v>
+      </c>
+      <c r="AX19">
+        <v>0</v>
+      </c>
+      <c r="AY19">
+        <v>0</v>
+      </c>
+      <c r="AZ19">
+        <v>0</v>
+      </c>
+      <c r="BA19">
+        <v>0</v>
+      </c>
+      <c r="BB19">
+        <v>0</v>
+      </c>
+      <c r="BC19">
+        <v>0</v>
+      </c>
+      <c r="BD19">
+        <v>0</v>
+      </c>
+      <c r="BE19">
+        <v>0</v>
+      </c>
+      <c r="BF19">
+        <v>0</v>
+      </c>
+      <c r="BG19">
+        <v>0</v>
+      </c>
+      <c r="BH19" t="s">
         <v>125</v>
-      </c>
-      <c r="F19">
-        <v>1.34</v>
-      </c>
-      <c r="G19">
-        <v>1.62</v>
-      </c>
-      <c r="H19">
-        <v>2.68</v>
-      </c>
-      <c r="I19">
-        <v>1000</v>
-      </c>
-      <c r="J19">
-        <v>2.6</v>
-      </c>
-      <c r="K19">
-        <v>85</v>
-      </c>
-      <c r="L19">
-        <v>0</v>
-      </c>
-      <c r="M19">
-        <v>0</v>
-      </c>
-      <c r="N19">
-        <v>0</v>
-      </c>
-      <c r="O19">
-        <v>0</v>
-      </c>
-      <c r="P19">
-        <v>1.9</v>
-      </c>
-      <c r="Q19">
-        <v>1.63</v>
-      </c>
-      <c r="R19">
-        <v>0</v>
-      </c>
-      <c r="S19">
-        <v>0</v>
-      </c>
-      <c r="T19">
-        <v>0</v>
-      </c>
-      <c r="U19">
-        <v>0</v>
-      </c>
-      <c r="V19">
-        <v>0</v>
-      </c>
-      <c r="W19">
-        <v>0</v>
-      </c>
-      <c r="X19">
-        <v>0</v>
-      </c>
-      <c r="Y19">
-        <v>0</v>
-      </c>
-      <c r="Z19">
-        <v>0</v>
-      </c>
-      <c r="AA19">
-        <v>0</v>
-      </c>
-      <c r="AB19">
-        <v>0</v>
-      </c>
-      <c r="AC19">
-        <v>0</v>
-      </c>
-      <c r="AD19">
-        <v>0</v>
-      </c>
-      <c r="AE19">
-        <v>0</v>
-      </c>
-      <c r="AF19">
-        <v>0</v>
-      </c>
-      <c r="AG19">
-        <v>0</v>
-      </c>
-      <c r="AH19">
-        <v>0</v>
-      </c>
-      <c r="AI19">
-        <v>0</v>
-      </c>
-      <c r="AJ19">
-        <v>0</v>
-      </c>
-      <c r="AK19">
-        <v>0</v>
-      </c>
-      <c r="AL19">
-        <v>0</v>
-      </c>
-      <c r="AM19">
-        <v>0</v>
-      </c>
-      <c r="AN19">
-        <v>0</v>
-      </c>
-      <c r="AO19">
-        <v>0</v>
-      </c>
-      <c r="AP19">
-        <v>0</v>
-      </c>
-      <c r="AQ19">
-        <v>0</v>
-      </c>
-      <c r="AR19">
-        <v>0</v>
-      </c>
-      <c r="AS19">
-        <v>0</v>
-      </c>
-      <c r="AT19">
-        <v>0</v>
-      </c>
-      <c r="AU19">
-        <v>0</v>
-      </c>
-      <c r="AV19">
-        <v>0</v>
-      </c>
-      <c r="AW19">
-        <v>0</v>
-      </c>
-      <c r="AX19">
-        <v>0</v>
-      </c>
-      <c r="AY19">
-        <v>0</v>
-      </c>
-      <c r="AZ19">
-        <v>0</v>
-      </c>
-      <c r="BA19">
-        <v>0</v>
-      </c>
-      <c r="BB19">
-        <v>0</v>
-      </c>
-      <c r="BC19">
-        <v>0</v>
-      </c>
-      <c r="BD19">
-        <v>0</v>
-      </c>
-      <c r="BE19">
-        <v>0</v>
-      </c>
-      <c r="BF19">
-        <v>0</v>
-      </c>
-      <c r="BG19">
-        <v>0</v>
-      </c>
-      <c r="BH19" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="20" spans="1:60">
@@ -4227,34 +4215,34 @@
         <v>72</v>
       </c>
       <c r="B20" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C20" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D20" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E20" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="F20">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="G20">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="H20">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="I20">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="J20">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="K20">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="L20">
         <v>0</v>
@@ -4269,10 +4257,10 @@
         <v>0</v>
       </c>
       <c r="P20">
-        <v>1.94</v>
+        <v>1.05</v>
       </c>
       <c r="Q20">
-        <v>1.65</v>
+        <v>1.01</v>
       </c>
       <c r="R20">
         <v>0</v>
@@ -4401,371 +4389,189 @@
         <v>0</v>
       </c>
       <c r="BH20" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="21" spans="1:60">
       <c r="A21" t="s">
+        <v>69</v>
+      </c>
+      <c r="B21" t="s">
         <v>73</v>
       </c>
-      <c r="B21" t="s">
-        <v>74</v>
-      </c>
       <c r="C21" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D21" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E21" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="F21">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="J21">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="K21">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="L21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="P21">
-        <v>1.05</v>
+        <v>1.25</v>
       </c>
       <c r="Q21">
+        <v>1.44</v>
+      </c>
+      <c r="R21">
+        <v>1.18</v>
+      </c>
+      <c r="S21">
+        <v>3.6</v>
+      </c>
+      <c r="T21">
         <v>1.01</v>
       </c>
-      <c r="R21">
-        <v>0</v>
-      </c>
-      <c r="S21">
-        <v>0</v>
-      </c>
-      <c r="T21">
-        <v>0</v>
-      </c>
       <c r="U21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH21" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="22" spans="1:60">
-      <c r="A22" t="s">
-        <v>70</v>
-      </c>
-      <c r="B22" t="s">
-        <v>74</v>
-      </c>
-      <c r="C22" t="s">
-        <v>86</v>
-      </c>
-      <c r="D22" t="s">
-        <v>107</v>
-      </c>
-      <c r="E22" t="s">
-        <v>128</v>
-      </c>
-      <c r="F22">
-        <v>1.61</v>
-      </c>
-      <c r="G22">
-        <v>1.75</v>
-      </c>
-      <c r="H22">
-        <v>5.1</v>
-      </c>
-      <c r="I22">
-        <v>9.6</v>
-      </c>
-      <c r="J22">
-        <v>3.2</v>
-      </c>
-      <c r="K22">
-        <v>4.5</v>
-      </c>
-      <c r="L22">
-        <v>1.01</v>
-      </c>
-      <c r="M22">
-        <v>1.01</v>
-      </c>
-      <c r="N22">
-        <v>1.01</v>
-      </c>
-      <c r="O22">
-        <v>1.02</v>
-      </c>
-      <c r="P22">
-        <v>1.25</v>
-      </c>
-      <c r="Q22">
-        <v>1.44</v>
-      </c>
-      <c r="R22">
-        <v>1.18</v>
-      </c>
-      <c r="S22">
-        <v>3.6</v>
-      </c>
-      <c r="T22">
-        <v>1.01</v>
-      </c>
-      <c r="U22">
-        <v>1.01</v>
-      </c>
-      <c r="V22">
-        <v>1.13</v>
-      </c>
-      <c r="W22">
-        <v>2.32</v>
-      </c>
-      <c r="X22">
-        <v>1000</v>
-      </c>
-      <c r="Y22">
-        <v>1000</v>
-      </c>
-      <c r="Z22">
-        <v>1000</v>
-      </c>
-      <c r="AA22">
-        <v>1000</v>
-      </c>
-      <c r="AB22">
-        <v>1000</v>
-      </c>
-      <c r="AC22">
-        <v>1000</v>
-      </c>
-      <c r="AD22">
-        <v>1000</v>
-      </c>
-      <c r="AE22">
-        <v>1000</v>
-      </c>
-      <c r="AF22">
-        <v>1000</v>
-      </c>
-      <c r="AG22">
-        <v>1000</v>
-      </c>
-      <c r="AH22">
-        <v>1000</v>
-      </c>
-      <c r="AI22">
-        <v>1000</v>
-      </c>
-      <c r="AJ22">
-        <v>1000</v>
-      </c>
-      <c r="AK22">
-        <v>1000</v>
-      </c>
-      <c r="AL22">
-        <v>1000</v>
-      </c>
-      <c r="AM22">
-        <v>1000</v>
-      </c>
-      <c r="AN22">
-        <v>1000</v>
-      </c>
-      <c r="AO22">
-        <v>1000</v>
-      </c>
-      <c r="AP22">
-        <v>1.01</v>
-      </c>
-      <c r="AQ22">
-        <v>1.01</v>
-      </c>
-      <c r="AR22">
-        <v>1.01</v>
-      </c>
-      <c r="AS22">
-        <v>1.01</v>
-      </c>
-      <c r="AT22">
-        <v>1.01</v>
-      </c>
-      <c r="AU22">
-        <v>1.01</v>
-      </c>
-      <c r="AV22">
-        <v>1.01</v>
-      </c>
-      <c r="AW22">
-        <v>1.01</v>
-      </c>
-      <c r="AX22">
-        <v>1.01</v>
-      </c>
-      <c r="AY22">
-        <v>1.01</v>
-      </c>
-      <c r="AZ22">
-        <v>1.01</v>
-      </c>
-      <c r="BA22">
-        <v>1.01</v>
-      </c>
-      <c r="BB22">
-        <v>1.01</v>
-      </c>
-      <c r="BC22">
-        <v>1.01</v>
-      </c>
-      <c r="BD22">
-        <v>1.01</v>
-      </c>
-      <c r="BE22">
-        <v>1.01</v>
-      </c>
-      <c r="BF22">
-        <v>1.01</v>
-      </c>
-      <c r="BG22">
-        <v>1.01</v>
-      </c>
-      <c r="BH22" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-04.xlsx
@@ -391,7 +391,7 @@
     <t>Newells</t>
   </si>
   <si>
-    <t>2026-05-02 09:09:49</t>
+    <t>2026-05-02 11:40:22</t>
   </si>
 </sst>
 </file>
@@ -951,13 +951,13 @@
         <v>105</v>
       </c>
       <c r="F2">
-        <v>2.88</v>
+        <v>3.15</v>
       </c>
       <c r="G2">
         <v>4.3</v>
       </c>
       <c r="H2">
-        <v>2.4</v>
+        <v>2.58</v>
       </c>
       <c r="I2">
         <v>3.4</v>
@@ -966,19 +966,19 @@
         <v>2.1</v>
       </c>
       <c r="K2">
-        <v>4.3</v>
+        <v>3.4</v>
       </c>
       <c r="L2">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P2">
         <v>1.33</v>
@@ -987,130 +987,130 @@
         <v>2.62</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP2">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AQ2">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AR2">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AS2">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AT2">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AU2">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AV2">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AW2">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AX2">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AY2">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AZ2">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BA2">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BB2">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BC2">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BD2">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BE2">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BF2">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG2">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BH2" t="s">
         <v>125</v>
@@ -1139,7 +1139,7 @@
         <v>1.73</v>
       </c>
       <c r="H3">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="I3">
         <v>5.4</v>
@@ -1148,10 +1148,10 @@
         <v>4.2</v>
       </c>
       <c r="K3">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L3">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M3">
         <v>1.05</v>
@@ -1181,19 +1181,19 @@
         <v>2.28</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="X3">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Y3">
         <v>22</v>
       </c>
       <c r="Z3">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AA3">
         <v>130</v>
@@ -1202,40 +1202,40 @@
         <v>10.5</v>
       </c>
       <c r="AC3">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AD3">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE3">
         <v>60</v>
       </c>
       <c r="AF3">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG3">
         <v>9.6</v>
       </c>
       <c r="AH3">
+        <v>18</v>
+      </c>
+      <c r="AI3">
+        <v>60</v>
+      </c>
+      <c r="AJ3">
         <v>17.5</v>
       </c>
-      <c r="AI3">
-        <v>65</v>
-      </c>
-      <c r="AJ3">
-        <v>18.5</v>
-      </c>
       <c r="AK3">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL3">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AM3">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AN3">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AO3">
         <v>55</v>
@@ -1244,25 +1244,25 @@
         <v>17.5</v>
       </c>
       <c r="AQ3">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AR3">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AS3">
-        <v>18.5</v>
+        <v>40</v>
       </c>
       <c r="AT3">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU3">
         <v>9</v>
       </c>
       <c r="AV3">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AW3">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AX3">
         <v>10.5</v>
@@ -1271,13 +1271,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ3">
+        <v>17</v>
+      </c>
+      <c r="BA3">
+        <v>50</v>
+      </c>
+      <c r="BB3">
         <v>16.5</v>
-      </c>
-      <c r="BA3">
-        <v>48</v>
-      </c>
-      <c r="BB3">
-        <v>16</v>
       </c>
       <c r="BC3">
         <v>15.5</v>
@@ -1286,13 +1286,13 @@
         <v>27</v>
       </c>
       <c r="BE3">
+        <v>70</v>
+      </c>
+      <c r="BF3">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BG3">
         <v>50</v>
-      </c>
-      <c r="BF3">
-        <v>7.8</v>
-      </c>
-      <c r="BG3">
-        <v>30</v>
       </c>
       <c r="BH3" t="s">
         <v>125</v>
@@ -1688,10 +1688,10 @@
         <v>2.64</v>
       </c>
       <c r="I6">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="J6">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K6">
         <v>3.35</v>
@@ -1796,7 +1796,7 @@
         <v>14.5</v>
       </c>
       <c r="AS6">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AT6">
         <v>10</v>
@@ -3317,7 +3317,7 @@
         <v>118</v>
       </c>
       <c r="F15">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="G15">
         <v>1.68</v>
@@ -3329,10 +3329,10 @@
         <v>6.2</v>
       </c>
       <c r="J15">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K15">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L15">
         <v>0</v>
@@ -3389,7 +3389,7 @@
         <v>9.6</v>
       </c>
       <c r="AD15">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE15">
         <v>1000</v>
@@ -3404,7 +3404,7 @@
         <v>24</v>
       </c>
       <c r="AI15">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AJ15">
         <v>16.5</v>
@@ -3422,7 +3422,7 @@
         <v>10</v>
       </c>
       <c r="AO15">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AP15">
         <v>14</v>
@@ -3434,7 +3434,7 @@
         <v>25</v>
       </c>
       <c r="AS15">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AT15">
         <v>7.6</v>
@@ -3446,7 +3446,7 @@
         <v>20</v>
       </c>
       <c r="AW15">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AX15">
         <v>9</v>
@@ -3458,7 +3458,7 @@
         <v>21</v>
       </c>
       <c r="BA15">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BB15">
         <v>14.5</v>
@@ -3470,13 +3470,13 @@
         <v>23</v>
       </c>
       <c r="BE15">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BF15">
         <v>9.199999999999999</v>
       </c>
       <c r="BG15">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BH15" t="s">
         <v>125</v>
@@ -3508,10 +3508,10 @@
         <v>1.5</v>
       </c>
       <c r="I16">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="J16">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="K16">
         <v>5.3</v>
@@ -3535,7 +3535,7 @@
         <v>1.67</v>
       </c>
       <c r="R16">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="S16">
         <v>2.72</v>
@@ -3544,7 +3544,7 @@
         <v>1.84</v>
       </c>
       <c r="U16">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V16">
         <v>0</v>
@@ -3571,10 +3571,10 @@
         <v>11.5</v>
       </c>
       <c r="AD16">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AE16">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AF16">
         <v>60</v>
@@ -3625,7 +3625,7 @@
         <v>10.5</v>
       </c>
       <c r="AV16">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW16">
         <v>13.5</v>
@@ -3649,16 +3649,16 @@
         <v>55</v>
       </c>
       <c r="BD16">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BE16">
         <v>65</v>
       </c>
       <c r="BF16">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BG16">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BH16" t="s">
         <v>125</v>
@@ -3693,7 +3693,7 @@
         <v>4.1</v>
       </c>
       <c r="J17">
-        <v>2.9</v>
+        <v>2.78</v>
       </c>
       <c r="K17">
         <v>3.2</v>
@@ -3705,19 +3705,19 @@
         <v>1.15</v>
       </c>
       <c r="N17">
-        <v>2.28</v>
+        <v>2.1</v>
       </c>
       <c r="O17">
         <v>1.68</v>
       </c>
       <c r="P17">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="Q17">
         <v>3</v>
       </c>
       <c r="R17">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="S17">
         <v>6.8</v>
@@ -4045,7 +4045,7 @@
         <v>122</v>
       </c>
       <c r="F19">
-        <v>1.91</v>
+        <v>1.55</v>
       </c>
       <c r="G19">
         <v>2.64</v>
@@ -4060,7 +4060,7 @@
         <v>3.05</v>
       </c>
       <c r="K19">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="L19">
         <v>0</v>
@@ -4078,7 +4078,7 @@
         <v>1.94</v>
       </c>
       <c r="Q19">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="R19">
         <v>0</v>
@@ -4257,7 +4257,7 @@
         <v>0</v>
       </c>
       <c r="P20">
-        <v>1.05</v>
+        <v>1.78</v>
       </c>
       <c r="Q20">
         <v>1.01</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-04.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="148">
   <si>
     <t>League</t>
   </si>
@@ -205,24 +205,30 @@
     <t>Finnish Veikkausliiga</t>
   </si>
   <si>
+    <t>Irish Division 1</t>
+  </si>
+  <si>
+    <t>Irish Premier Division</t>
+  </si>
+  <si>
+    <t>Italian Serie A</t>
+  </si>
+  <si>
     <t>Austrian Bundesliga</t>
   </si>
   <si>
-    <t>Italian Serie A</t>
+    <t>Danish Superliga</t>
+  </si>
+  <si>
+    <t>Israeli Premier League</t>
+  </si>
+  <si>
+    <t>Norwegian Eliteserien</t>
   </si>
   <si>
     <t>Polish Ekstraklasa</t>
   </si>
   <si>
-    <t>Norwegian Eliteserien</t>
-  </si>
-  <si>
-    <t>Israeli Premier League</t>
-  </si>
-  <si>
-    <t>Danish Superliga</t>
-  </si>
-  <si>
     <t>Argentinian Primera Division</t>
   </si>
   <si>
@@ -280,33 +286,63 @@
     <t>HJK Helsinki</t>
   </si>
   <si>
+    <t>Finn Harps</t>
+  </si>
+  <si>
+    <t>Treaty United</t>
+  </si>
+  <si>
+    <t>Cobh Ramblers</t>
+  </si>
+  <si>
+    <t>Longford</t>
+  </si>
+  <si>
+    <t>Kerry FC</t>
+  </si>
+  <si>
+    <t>Derry City</t>
+  </si>
+  <si>
+    <t>Waterford</t>
+  </si>
+  <si>
+    <t>Sligo Rovers</t>
+  </si>
+  <si>
+    <t>Bohemians</t>
+  </si>
+  <si>
+    <t>Shamrock Rovers</t>
+  </si>
+  <si>
+    <t>US Cremonese</t>
+  </si>
+  <si>
     <t>SCR Altach</t>
   </si>
   <si>
-    <t>US Cremonese</t>
+    <t>Midtjylland</t>
+  </si>
+  <si>
+    <t>Al Ittihad (EGY)</t>
+  </si>
+  <si>
+    <t>Wadi Degla</t>
+  </si>
+  <si>
+    <t>Bnei Sakhnin</t>
+  </si>
+  <si>
+    <t>Maccabi Netanya</t>
+  </si>
+  <si>
+    <t>Bodo Glimt</t>
   </si>
   <si>
     <t>Radomiak Radom</t>
   </si>
   <si>
-    <t>Bodo Glimt</t>
-  </si>
-  <si>
-    <t>Bnei Sakhnin</t>
-  </si>
-  <si>
-    <t>Maccabi Netanya</t>
-  </si>
-  <si>
-    <t>Al Ittihad (EGY)</t>
-  </si>
-  <si>
-    <t>Midtjylland</t>
-  </si>
-  <si>
-    <t>Wadi Degla</t>
-  </si>
-  <si>
     <t>LASK Linz</t>
   </si>
   <si>
@@ -340,33 +376,63 @@
     <t>Lahti</t>
   </si>
   <si>
+    <t>Bray Wanderers</t>
+  </si>
+  <si>
+    <t>Wexford F.C</t>
+  </si>
+  <si>
+    <t>UCD</t>
+  </si>
+  <si>
+    <t>Athlone Town</t>
+  </si>
+  <si>
+    <t>Cork City</t>
+  </si>
+  <si>
+    <t>Galway Utd</t>
+  </si>
+  <si>
+    <t>Dundalk</t>
+  </si>
+  <si>
+    <t>St Patricks</t>
+  </si>
+  <si>
+    <t>Shelbourne</t>
+  </si>
+  <si>
+    <t>Drogheda</t>
+  </si>
+  <si>
+    <t>Lazio</t>
+  </si>
+  <si>
     <t>RZ Pellets WAC</t>
   </si>
   <si>
-    <t>Lazio</t>
+    <t>Viborg</t>
+  </si>
+  <si>
+    <t>Petrojet</t>
+  </si>
+  <si>
+    <t>Kahraba Ismailia</t>
+  </si>
+  <si>
+    <t>Maccabi Bnei Raina</t>
+  </si>
+  <si>
+    <t>Hapoel Jerusalem</t>
+  </si>
+  <si>
+    <t>Molde</t>
   </si>
   <si>
     <t>Lechia Gdansk</t>
   </si>
   <si>
-    <t>Molde</t>
-  </si>
-  <si>
-    <t>Maccabi Bnei Raina</t>
-  </si>
-  <si>
-    <t>Hapoel Jerusalem</t>
-  </si>
-  <si>
-    <t>Petrojet</t>
-  </si>
-  <si>
-    <t>Viborg</t>
-  </si>
-  <si>
-    <t>Kahraba Ismailia</t>
-  </si>
-  <si>
     <t>Rapid Vienna</t>
   </si>
   <si>
@@ -391,7 +457,7 @@
     <t>Newells</t>
   </si>
   <si>
-    <t>2026-05-02 11:40:22</t>
+    <t>2026-05-02 14:10:58</t>
   </si>
 </sst>
 </file>
@@ -749,7 +815,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BH21"/>
+  <dimension ref="A1:BH31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:60">
@@ -939,31 +1005,31 @@
         <v>60</v>
       </c>
       <c r="B2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E2" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="F2">
         <v>3.15</v>
       </c>
       <c r="G2">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="H2">
         <v>2.58</v>
       </c>
       <c r="I2">
-        <v>3.4</v>
+        <v>2.98</v>
       </c>
       <c r="J2">
-        <v>2.1</v>
+        <v>2.74</v>
       </c>
       <c r="K2">
         <v>3.4</v>
@@ -972,148 +1038,148 @@
         <v>1.6</v>
       </c>
       <c r="M2">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="N2">
-        <v>1.33</v>
+        <v>2.32</v>
       </c>
       <c r="O2">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="P2">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="Q2">
-        <v>2.62</v>
+        <v>2.84</v>
       </c>
       <c r="R2">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="S2">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="T2">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="U2">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="V2">
-        <v>1.41</v>
+        <v>1.51</v>
       </c>
       <c r="W2">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="X2">
-        <v>9.6</v>
+        <v>7.8</v>
       </c>
       <c r="Y2">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="Z2">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AA2">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB2">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AC2">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AD2">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AE2">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF2">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AG2">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AH2">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AI2">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AJ2">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AK2">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AL2">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AM2">
         <v>1000</v>
       </c>
       <c r="AN2">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AO2">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AP2">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="AQ2">
-        <v>1.11</v>
+        <v>5.9</v>
       </c>
       <c r="AR2">
-        <v>1.11</v>
+        <v>4.3</v>
       </c>
       <c r="AS2">
-        <v>1.11</v>
+        <v>5.2</v>
       </c>
       <c r="AT2">
-        <v>1.11</v>
+        <v>3.65</v>
       </c>
       <c r="AU2">
-        <v>1.11</v>
+        <v>5.5</v>
       </c>
       <c r="AV2">
-        <v>1.11</v>
+        <v>10.5</v>
       </c>
       <c r="AW2">
-        <v>1.11</v>
+        <v>5.2</v>
       </c>
       <c r="AX2">
-        <v>1.11</v>
+        <v>4.7</v>
       </c>
       <c r="AY2">
-        <v>1.11</v>
+        <v>4.3</v>
       </c>
       <c r="AZ2">
-        <v>1.11</v>
+        <v>4.8</v>
       </c>
       <c r="BA2">
-        <v>1.11</v>
+        <v>5.4</v>
       </c>
       <c r="BB2">
-        <v>1.11</v>
+        <v>5.4</v>
       </c>
       <c r="BC2">
-        <v>1.11</v>
+        <v>5.3</v>
       </c>
       <c r="BD2">
-        <v>1.11</v>
+        <v>5.5</v>
       </c>
       <c r="BE2">
-        <v>1.11</v>
+        <v>3.25</v>
       </c>
       <c r="BF2">
-        <v>1.11</v>
+        <v>5.4</v>
       </c>
       <c r="BG2">
-        <v>1.11</v>
+        <v>5.3</v>
       </c>
       <c r="BH2" t="s">
-        <v>125</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" spans="1:60">
@@ -1121,16 +1187,16 @@
         <v>61</v>
       </c>
       <c r="B3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E3" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="F3">
         <v>1.72</v>
@@ -1139,7 +1205,7 @@
         <v>1.73</v>
       </c>
       <c r="H3">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="I3">
         <v>5.4</v>
@@ -1151,7 +1217,7 @@
         <v>4.3</v>
       </c>
       <c r="L3">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="M3">
         <v>1.05</v>
@@ -1178,10 +1244,10 @@
         <v>1.75</v>
       </c>
       <c r="U3">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="V3">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W3">
         <v>2.36</v>
@@ -1196,7 +1262,7 @@
         <v>42</v>
       </c>
       <c r="AA3">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AB3">
         <v>10.5</v>
@@ -1250,7 +1316,7 @@
         <v>40</v>
       </c>
       <c r="AS3">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="AT3">
         <v>9.800000000000001</v>
@@ -1259,10 +1325,10 @@
         <v>9</v>
       </c>
       <c r="AV3">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AW3">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AX3">
         <v>10.5</v>
@@ -1274,28 +1340,28 @@
         <v>17</v>
       </c>
       <c r="BA3">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BB3">
         <v>16.5</v>
       </c>
       <c r="BC3">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BD3">
         <v>27</v>
       </c>
       <c r="BE3">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="BF3">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BG3">
         <v>50</v>
       </c>
       <c r="BH3" t="s">
-        <v>125</v>
+        <v>147</v>
       </c>
     </row>
     <row r="4" spans="1:60">
@@ -1303,181 +1369,181 @@
         <v>62</v>
       </c>
       <c r="B4" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D4" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E4" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="F4">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="G4">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="H4">
-        <v>2.72</v>
+        <v>6.4</v>
       </c>
       <c r="I4">
+        <v>8.6</v>
+      </c>
+      <c r="J4">
+        <v>4.6</v>
+      </c>
+      <c r="K4">
+        <v>5.3</v>
+      </c>
+      <c r="L4">
+        <v>1.28</v>
+      </c>
+      <c r="M4">
+        <v>1.04</v>
+      </c>
+      <c r="N4">
+        <v>4.8</v>
+      </c>
+      <c r="O4">
+        <v>1.22</v>
+      </c>
+      <c r="P4">
+        <v>2.26</v>
+      </c>
+      <c r="Q4">
+        <v>1.64</v>
+      </c>
+      <c r="R4">
+        <v>1.5</v>
+      </c>
+      <c r="S4">
+        <v>2.46</v>
+      </c>
+      <c r="T4">
+        <v>1.69</v>
+      </c>
+      <c r="U4">
+        <v>1.86</v>
+      </c>
+      <c r="V4">
+        <v>1.14</v>
+      </c>
+      <c r="W4">
+        <v>2.74</v>
+      </c>
+      <c r="X4">
+        <v>26</v>
+      </c>
+      <c r="Y4">
+        <v>34</v>
+      </c>
+      <c r="Z4">
+        <v>65</v>
+      </c>
+      <c r="AA4">
+        <v>240</v>
+      </c>
+      <c r="AB4">
+        <v>10.5</v>
+      </c>
+      <c r="AC4">
+        <v>13.5</v>
+      </c>
+      <c r="AD4">
+        <v>34</v>
+      </c>
+      <c r="AE4">
+        <v>120</v>
+      </c>
+      <c r="AF4">
+        <v>12</v>
+      </c>
+      <c r="AG4">
+        <v>11</v>
+      </c>
+      <c r="AH4">
         <v>27</v>
       </c>
-      <c r="J4">
-        <v>4.2</v>
-      </c>
-      <c r="K4">
-        <v>950</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4">
-        <v>0</v>
-      </c>
-      <c r="O4">
-        <v>0</v>
-      </c>
-      <c r="P4">
-        <v>2.08</v>
-      </c>
-      <c r="Q4">
-        <v>1.54</v>
-      </c>
-      <c r="R4">
-        <v>0</v>
-      </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>0</v>
-      </c>
-      <c r="V4">
-        <v>0</v>
-      </c>
-      <c r="W4">
-        <v>0</v>
-      </c>
-      <c r="X4">
-        <v>0</v>
-      </c>
-      <c r="Y4">
-        <v>0</v>
-      </c>
-      <c r="Z4">
-        <v>0</v>
-      </c>
-      <c r="AA4">
-        <v>0</v>
-      </c>
-      <c r="AB4">
-        <v>0</v>
-      </c>
-      <c r="AC4">
-        <v>0</v>
-      </c>
-      <c r="AD4">
-        <v>0</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>0</v>
-      </c>
-      <c r="AG4">
-        <v>0</v>
-      </c>
-      <c r="AH4">
-        <v>0</v>
-      </c>
       <c r="AI4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AL4">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AM4">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AN4">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AO4">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AP4">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AQ4">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AR4">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AS4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AT4">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AU4">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV4">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AW4">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AX4">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AY4">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AZ4">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BA4">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BB4">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BC4">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BD4">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BE4">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BF4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BG4">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BH4" t="s">
-        <v>125</v>
+        <v>147</v>
       </c>
     </row>
     <row r="5" spans="1:60">
@@ -1485,2400 +1551,2400 @@
         <v>63</v>
       </c>
       <c r="B5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E5" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="F5">
-        <v>2.28</v>
+        <v>2.88</v>
       </c>
       <c r="G5">
-        <v>3.05</v>
+        <v>3.9</v>
       </c>
       <c r="H5">
-        <v>2.72</v>
+        <v>2.06</v>
       </c>
       <c r="I5">
-        <v>3.95</v>
+        <v>2.66</v>
       </c>
       <c r="J5">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="K5">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="P5">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="Q5">
-        <v>2.02</v>
+        <v>1.73</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP5">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AQ5">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AR5">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AS5">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AT5">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU5">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AV5">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AW5">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AX5">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AY5">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AZ5">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BA5">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BB5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF5">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BG5">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BH5" t="s">
-        <v>125</v>
+        <v>147</v>
       </c>
     </row>
     <row r="6" spans="1:60">
       <c r="A6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B6" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D6" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E6" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="F6">
+        <v>2.88</v>
+      </c>
+      <c r="G6">
+        <v>4.6</v>
+      </c>
+      <c r="H6">
+        <v>1.97</v>
+      </c>
+      <c r="I6">
+        <v>2.72</v>
+      </c>
+      <c r="J6">
         <v>3.1</v>
       </c>
-      <c r="G6">
-        <v>3.15</v>
-      </c>
-      <c r="H6">
-        <v>2.64</v>
-      </c>
-      <c r="I6">
-        <v>2.66</v>
-      </c>
-      <c r="J6">
-        <v>3.3</v>
-      </c>
       <c r="K6">
-        <v>3.35</v>
+        <v>7</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M6">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="N6">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="O6">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="P6">
-        <v>1.79</v>
+        <v>1.27</v>
       </c>
       <c r="Q6">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="R6">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="S6">
-        <v>4.1</v>
+        <v>2.92</v>
       </c>
       <c r="T6">
-        <v>1.9</v>
+        <v>1.01</v>
       </c>
       <c r="U6">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="X6">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Y6">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="Z6">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AA6">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AB6">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AC6">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="AD6">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AE6">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AF6">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AG6">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AH6">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AI6">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ6">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AK6">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AL6">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM6">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AN6">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AO6">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AP6">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ6">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AR6">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS6">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="AT6">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AU6">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV6">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AW6">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="AX6">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY6">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AZ6">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA6">
-        <v>28</v>
+        <v>1.01</v>
       </c>
       <c r="BB6">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="BC6">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BD6">
-        <v>29</v>
+        <v>1.01</v>
       </c>
       <c r="BE6">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BF6">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="BG6">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="BH6" t="s">
-        <v>125</v>
+        <v>147</v>
       </c>
     </row>
     <row r="7" spans="1:60">
       <c r="A7" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B7" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C7" t="s">
         <v>77</v>
       </c>
       <c r="D7" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E7" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="F7">
-        <v>2.16</v>
+        <v>2.26</v>
       </c>
       <c r="G7">
-        <v>2.76</v>
+        <v>3.2</v>
       </c>
       <c r="H7">
-        <v>2.74</v>
+        <v>2.4</v>
       </c>
       <c r="I7">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="J7">
-        <v>3.25</v>
+        <v>2.5</v>
       </c>
       <c r="K7">
-        <v>5.9</v>
+        <v>7.2</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="P7">
-        <v>2.02</v>
+        <v>1.24</v>
       </c>
       <c r="Q7">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH7" t="s">
-        <v>125</v>
+        <v>147</v>
       </c>
     </row>
     <row r="8" spans="1:60">
       <c r="A8" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B8" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C8" t="s">
         <v>77</v>
       </c>
       <c r="D8" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E8" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="F8">
-        <v>1.34</v>
+        <v>1.89</v>
       </c>
       <c r="G8">
-        <v>1.51</v>
+        <v>2.54</v>
       </c>
       <c r="H8">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I8">
-        <v>17.5</v>
+        <v>4.8</v>
       </c>
       <c r="J8">
-        <v>5.1</v>
+        <v>3.1</v>
       </c>
       <c r="K8">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="P8">
-        <v>3.15</v>
+        <v>1.81</v>
       </c>
       <c r="Q8">
-        <v>1.27</v>
+        <v>1.83</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH8" t="s">
-        <v>125</v>
+        <v>147</v>
       </c>
     </row>
     <row r="9" spans="1:60">
       <c r="A9" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B9" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C9" t="s">
         <v>77</v>
       </c>
       <c r="D9" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E9" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="F9">
-        <v>1.98</v>
+        <v>5.7</v>
       </c>
       <c r="G9">
-        <v>2.68</v>
+        <v>12</v>
       </c>
       <c r="H9">
+        <v>1.39</v>
+      </c>
+      <c r="I9">
+        <v>1.61</v>
+      </c>
+      <c r="J9">
+        <v>3.75</v>
+      </c>
+      <c r="K9">
+        <v>9.4</v>
+      </c>
+      <c r="L9">
+        <v>1.01</v>
+      </c>
+      <c r="M9">
+        <v>1.01</v>
+      </c>
+      <c r="N9">
+        <v>1.74</v>
+      </c>
+      <c r="O9">
+        <v>1.32</v>
+      </c>
+      <c r="P9">
+        <v>1.74</v>
+      </c>
+      <c r="Q9">
+        <v>1.78</v>
+      </c>
+      <c r="R9">
+        <v>1.27</v>
+      </c>
+      <c r="S9">
         <v>2.88</v>
       </c>
-      <c r="I9">
-        <v>4.4</v>
-      </c>
-      <c r="J9">
-        <v>3.15</v>
-      </c>
-      <c r="K9">
-        <v>6.8</v>
-      </c>
-      <c r="L9">
-        <v>0</v>
-      </c>
-      <c r="M9">
-        <v>0</v>
-      </c>
-      <c r="N9">
-        <v>0</v>
-      </c>
-      <c r="O9">
-        <v>0</v>
-      </c>
-      <c r="P9">
-        <v>1.58</v>
-      </c>
-      <c r="Q9">
-        <v>1.98</v>
-      </c>
-      <c r="R9">
-        <v>0</v>
-      </c>
-      <c r="S9">
-        <v>0</v>
-      </c>
       <c r="T9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH9" t="s">
-        <v>125</v>
+        <v>147</v>
       </c>
     </row>
     <row r="10" spans="1:60">
       <c r="A10" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B10" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C10" t="s">
         <v>77</v>
       </c>
       <c r="D10" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E10" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="F10">
-        <v>1.69</v>
+        <v>1.2</v>
       </c>
       <c r="G10">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="H10">
+        <v>1.91</v>
+      </c>
+      <c r="I10">
+        <v>6.2</v>
+      </c>
+      <c r="J10">
+        <v>2.68</v>
+      </c>
+      <c r="K10">
+        <v>85</v>
+      </c>
+      <c r="L10">
+        <v>1.39</v>
+      </c>
+      <c r="M10">
+        <v>1.01</v>
+      </c>
+      <c r="N10">
+        <v>1.71</v>
+      </c>
+      <c r="O10">
+        <v>1.32</v>
+      </c>
+      <c r="P10">
+        <v>1.71</v>
+      </c>
+      <c r="Q10">
+        <v>1.32</v>
+      </c>
+      <c r="R10">
+        <v>1.26</v>
+      </c>
+      <c r="S10">
         <v>3.1</v>
       </c>
-      <c r="I10">
-        <v>4.5</v>
-      </c>
-      <c r="J10">
-        <v>3.15</v>
-      </c>
-      <c r="K10">
-        <v>12</v>
-      </c>
-      <c r="L10">
-        <v>0</v>
-      </c>
-      <c r="M10">
-        <v>0</v>
-      </c>
-      <c r="N10">
-        <v>0</v>
-      </c>
-      <c r="O10">
-        <v>0</v>
-      </c>
-      <c r="P10">
-        <v>2.14</v>
-      </c>
-      <c r="Q10">
-        <v>1.64</v>
-      </c>
-      <c r="R10">
-        <v>0</v>
-      </c>
-      <c r="S10">
-        <v>0</v>
-      </c>
       <c r="T10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP10">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AQ10">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AS10">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AU10">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AV10">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AW10">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AX10">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AY10">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AZ10">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BA10">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BB10">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BC10">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BD10">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BE10">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BF10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH10" t="s">
-        <v>125</v>
+        <v>147</v>
       </c>
     </row>
     <row r="11" spans="1:60">
       <c r="A11" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B11" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C11" t="s">
         <v>77</v>
       </c>
       <c r="D11" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E11" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="F11">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="G11">
-        <v>2.9</v>
+        <v>100</v>
       </c>
       <c r="H11">
-        <v>3.2</v>
+        <v>1.63</v>
       </c>
       <c r="I11">
-        <v>5</v>
+        <v>1.9</v>
       </c>
       <c r="J11">
-        <v>2.62</v>
+        <v>2.14</v>
       </c>
       <c r="K11">
-        <v>4.7</v>
+        <v>85</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="M11">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="P11">
-        <v>1.51</v>
+        <v>1.45</v>
       </c>
       <c r="Q11">
-        <v>2.36</v>
+        <v>1.52</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP11">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AQ11">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR11">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AS11">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AT11">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AU11">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AV11">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AW11">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AX11">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AY11">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AZ11">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BA11">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BB11">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BC11">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BD11">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BE11">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BF11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH11" t="s">
-        <v>125</v>
+        <v>147</v>
       </c>
     </row>
     <row r="12" spans="1:60">
       <c r="A12" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B12" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C12" t="s">
         <v>77</v>
       </c>
       <c r="D12" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E12" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="F12">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="G12">
-        <v>1.66</v>
+        <v>430</v>
       </c>
       <c r="H12">
-        <v>5.5</v>
+        <v>1.04</v>
       </c>
       <c r="I12">
-        <v>6.6</v>
+        <v>1.95</v>
       </c>
       <c r="J12">
-        <v>4.5</v>
+        <v>2.06</v>
       </c>
       <c r="K12">
-        <v>5</v>
+        <v>85</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="M12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="P12">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q12">
-        <v>1.01</v>
+        <v>1.85</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP12">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AQ12">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AR12">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AS12">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AT12">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AU12">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AV12">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AW12">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AX12">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AY12">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AZ12">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BA12">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="BB12">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BC12">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BD12">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BE12">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BF12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH12" t="s">
-        <v>125</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13" spans="1:60">
       <c r="A13" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B13" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C13" t="s">
         <v>77</v>
       </c>
       <c r="D13" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E13" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="F13">
-        <v>1.63</v>
+        <v>2.04</v>
       </c>
       <c r="G13">
-        <v>2.06</v>
+        <v>2.28</v>
       </c>
       <c r="H13">
-        <v>1.98</v>
+        <v>3.75</v>
       </c>
       <c r="I13">
+        <v>4.6</v>
+      </c>
+      <c r="J13">
+        <v>3.2</v>
+      </c>
+      <c r="K13">
+        <v>3.7</v>
+      </c>
+      <c r="L13">
+        <v>1.43</v>
+      </c>
+      <c r="M13">
+        <v>1.01</v>
+      </c>
+      <c r="N13">
+        <v>3.05</v>
+      </c>
+      <c r="O13">
+        <v>1.37</v>
+      </c>
+      <c r="P13">
+        <v>1.73</v>
+      </c>
+      <c r="Q13">
+        <v>2.1</v>
+      </c>
+      <c r="R13">
+        <v>1.27</v>
+      </c>
+      <c r="S13">
+        <v>3.85</v>
+      </c>
+      <c r="T13">
+        <v>1.87</v>
+      </c>
+      <c r="U13">
+        <v>1.95</v>
+      </c>
+      <c r="V13">
+        <v>1.29</v>
+      </c>
+      <c r="W13">
+        <v>1.78</v>
+      </c>
+      <c r="X13">
+        <v>12.5</v>
+      </c>
+      <c r="Y13">
+        <v>13.5</v>
+      </c>
+      <c r="Z13">
+        <v>30</v>
+      </c>
+      <c r="AA13">
         <v>100</v>
       </c>
-      <c r="J13">
-        <v>1.98</v>
-      </c>
-      <c r="K13">
-        <v>85</v>
-      </c>
-      <c r="L13">
-        <v>0</v>
-      </c>
-      <c r="M13">
-        <v>0</v>
-      </c>
-      <c r="N13">
-        <v>0</v>
-      </c>
-      <c r="O13">
-        <v>0</v>
-      </c>
-      <c r="P13">
-        <v>1.56</v>
-      </c>
-      <c r="Q13">
-        <v>1.98</v>
-      </c>
-      <c r="R13">
-        <v>0</v>
-      </c>
-      <c r="S13">
-        <v>0</v>
-      </c>
-      <c r="T13">
-        <v>0</v>
-      </c>
-      <c r="U13">
-        <v>0</v>
-      </c>
-      <c r="V13">
-        <v>0</v>
-      </c>
-      <c r="W13">
-        <v>0</v>
-      </c>
-      <c r="X13">
-        <v>0</v>
-      </c>
-      <c r="Y13">
-        <v>0</v>
-      </c>
-      <c r="Z13">
-        <v>0</v>
-      </c>
-      <c r="AA13">
-        <v>0</v>
-      </c>
       <c r="AB13">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AH13">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AI13">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AL13">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AM13">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AN13">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AO13">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AP13">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AQ13">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AR13">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AS13">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT13">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AU13">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AV13">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AW13">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AX13">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AY13">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AZ13">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BA13">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BB13">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BC13">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BD13">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BE13">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="BF13">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BG13">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BH13" t="s">
-        <v>125</v>
+        <v>147</v>
       </c>
     </row>
     <row r="14" spans="1:60">
       <c r="A14" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B14" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D14" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E14" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="F14">
-        <v>1.97</v>
+        <v>1.45</v>
       </c>
       <c r="G14">
-        <v>2.38</v>
+        <v>1.63</v>
       </c>
       <c r="H14">
-        <v>3.25</v>
+        <v>6</v>
       </c>
       <c r="I14">
-        <v>4.9</v>
+        <v>11</v>
       </c>
       <c r="J14">
-        <v>3.25</v>
+        <v>1.09</v>
       </c>
       <c r="K14">
-        <v>5.5</v>
+        <v>85</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="M14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="P14">
-        <v>1.9</v>
+        <v>1.27</v>
       </c>
       <c r="Q14">
-        <v>1.66</v>
+        <v>1.95</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP14">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AQ14">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AR14">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AS14">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AT14">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AU14">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AV14">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AW14">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AX14">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AY14">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AZ14">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BA14">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BB14">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC14">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BD14">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="BE14">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BF14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH14" t="s">
-        <v>125</v>
+        <v>147</v>
       </c>
     </row>
     <row r="15" spans="1:60">
       <c r="A15" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B15" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C15" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D15" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E15" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="F15">
-        <v>1.66</v>
+        <v>3.1</v>
       </c>
       <c r="G15">
-        <v>1.68</v>
+        <v>3.15</v>
       </c>
       <c r="H15">
-        <v>5.7</v>
+        <v>2.64</v>
       </c>
       <c r="I15">
-        <v>6.2</v>
+        <v>2.66</v>
       </c>
       <c r="J15">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="K15">
-        <v>4.5</v>
+        <v>3.35</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="M15">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="N15">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="O15">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="P15">
-        <v>2</v>
+        <v>1.77</v>
       </c>
       <c r="Q15">
-        <v>1.94</v>
+        <v>2.22</v>
       </c>
       <c r="R15">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="S15">
-        <v>3.45</v>
+        <v>4.1</v>
       </c>
       <c r="T15">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="U15">
-        <v>1.97</v>
+        <v>2.04</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="X15">
+        <v>11</v>
+      </c>
+      <c r="Y15">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Z15">
         <v>16</v>
       </c>
-      <c r="Y15">
-        <v>19</v>
-      </c>
-      <c r="Z15">
+      <c r="AA15">
+        <v>40</v>
+      </c>
+      <c r="AB15">
+        <v>11</v>
+      </c>
+      <c r="AC15">
+        <v>7.4</v>
+      </c>
+      <c r="AD15">
+        <v>12</v>
+      </c>
+      <c r="AE15">
+        <v>32</v>
+      </c>
+      <c r="AF15">
+        <v>20</v>
+      </c>
+      <c r="AG15">
+        <v>13.5</v>
+      </c>
+      <c r="AH15">
+        <v>19.5</v>
+      </c>
+      <c r="AI15">
         <v>48</v>
       </c>
-      <c r="AA15">
-        <v>1000</v>
-      </c>
-      <c r="AB15">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AC15">
-        <v>9.6</v>
-      </c>
-      <c r="AD15">
-        <v>22</v>
-      </c>
-      <c r="AE15">
-        <v>1000</v>
-      </c>
-      <c r="AF15">
-        <v>9.6</v>
-      </c>
-      <c r="AG15">
+      <c r="AJ15">
+        <v>55</v>
+      </c>
+      <c r="AK15">
+        <v>40</v>
+      </c>
+      <c r="AL15">
+        <v>55</v>
+      </c>
+      <c r="AM15">
+        <v>120</v>
+      </c>
+      <c r="AN15">
+        <v>40</v>
+      </c>
+      <c r="AO15">
+        <v>30</v>
+      </c>
+      <c r="AP15">
+        <v>10.5</v>
+      </c>
+      <c r="AQ15">
+        <v>9</v>
+      </c>
+      <c r="AR15">
+        <v>14.5</v>
+      </c>
+      <c r="AS15">
+        <v>34</v>
+      </c>
+      <c r="AT15">
         <v>10</v>
       </c>
-      <c r="AH15">
-        <v>24</v>
-      </c>
-      <c r="AI15">
-        <v>1000</v>
-      </c>
-      <c r="AJ15">
-        <v>16.5</v>
-      </c>
-      <c r="AK15">
+      <c r="AU15">
+        <v>6.8</v>
+      </c>
+      <c r="AV15">
+        <v>11</v>
+      </c>
+      <c r="AW15">
+        <v>28</v>
+      </c>
+      <c r="AX15">
         <v>18</v>
       </c>
-      <c r="AL15">
-        <v>38</v>
-      </c>
-      <c r="AM15">
-        <v>150</v>
-      </c>
-      <c r="AN15">
-        <v>10</v>
-      </c>
-      <c r="AO15">
-        <v>120</v>
-      </c>
-      <c r="AP15">
-        <v>14</v>
-      </c>
-      <c r="AQ15">
-        <v>17</v>
-      </c>
-      <c r="AR15">
+      <c r="AY15">
+        <v>12.5</v>
+      </c>
+      <c r="AZ15">
+        <v>17.5</v>
+      </c>
+      <c r="BA15">
+        <v>42</v>
+      </c>
+      <c r="BB15">
+        <v>27</v>
+      </c>
+      <c r="BC15">
+        <v>34</v>
+      </c>
+      <c r="BD15">
+        <v>48</v>
+      </c>
+      <c r="BE15">
+        <v>40</v>
+      </c>
+      <c r="BF15">
+        <v>32</v>
+      </c>
+      <c r="BG15">
         <v>25</v>
       </c>
-      <c r="AS15">
-        <v>15</v>
-      </c>
-      <c r="AT15">
-        <v>7.6</v>
-      </c>
-      <c r="AU15">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AV15">
-        <v>20</v>
-      </c>
-      <c r="AW15">
-        <v>15.5</v>
-      </c>
-      <c r="AX15">
-        <v>9</v>
-      </c>
-      <c r="AY15">
-        <v>9</v>
-      </c>
-      <c r="AZ15">
-        <v>21</v>
-      </c>
-      <c r="BA15">
-        <v>15</v>
-      </c>
-      <c r="BB15">
-        <v>14.5</v>
-      </c>
-      <c r="BC15">
-        <v>16</v>
-      </c>
-      <c r="BD15">
-        <v>23</v>
-      </c>
-      <c r="BE15">
-        <v>15</v>
-      </c>
-      <c r="BF15">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BG15">
-        <v>16.5</v>
-      </c>
       <c r="BH15" t="s">
-        <v>125</v>
+        <v>147</v>
       </c>
     </row>
     <row r="16" spans="1:60">
       <c r="A16" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B16" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C16" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D16" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E16" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="F16">
-        <v>6.8</v>
+        <v>2.42</v>
       </c>
       <c r="G16">
-        <v>7</v>
+        <v>2.82</v>
       </c>
       <c r="H16">
-        <v>1.5</v>
+        <v>2.98</v>
       </c>
       <c r="I16">
-        <v>1.51</v>
+        <v>3.6</v>
       </c>
       <c r="J16">
-        <v>5.1</v>
+        <v>3.25</v>
       </c>
       <c r="K16">
-        <v>5.3</v>
+        <v>3.7</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M16">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="N16">
-        <v>5.1</v>
+        <v>1.67</v>
       </c>
       <c r="O16">
-        <v>1.23</v>
+        <v>1.01</v>
       </c>
       <c r="P16">
-        <v>2.42</v>
+        <v>1.67</v>
       </c>
       <c r="Q16">
-        <v>1.67</v>
+        <v>2.02</v>
       </c>
       <c r="R16">
-        <v>1.54</v>
+        <v>1.05</v>
       </c>
       <c r="S16">
-        <v>2.72</v>
+        <v>2.02</v>
       </c>
       <c r="T16">
-        <v>1.84</v>
+        <v>1.01</v>
       </c>
       <c r="U16">
-        <v>2.14</v>
+        <v>1.01</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X16">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="Y16">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="Z16">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AA16">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AB16">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AC16">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AD16">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AE16">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AF16">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AG16">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AH16">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AI16">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AJ16">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AK16">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AL16">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AM16">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AN16">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AO16">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="AP16">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AQ16">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AR16">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AS16">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AT16">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="AU16">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AV16">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AW16">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX16">
-        <v>48</v>
+        <v>1.01</v>
       </c>
       <c r="AY16">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="AZ16">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BA16">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="BB16">
-        <v>46</v>
+        <v>1.01</v>
       </c>
       <c r="BC16">
-        <v>55</v>
+        <v>1.01</v>
       </c>
       <c r="BD16">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BE16">
-        <v>65</v>
+        <v>1.01</v>
       </c>
       <c r="BF16">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BG16">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BH16" t="s">
-        <v>125</v>
+        <v>147</v>
       </c>
     </row>
     <row r="17" spans="1:60">
       <c r="A17" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B17" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C17" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D17" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E17" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="F17">
-        <v>2.36</v>
+        <v>1.6</v>
       </c>
       <c r="G17">
-        <v>2.56</v>
+        <v>1.66</v>
       </c>
       <c r="H17">
-        <v>3.5</v>
+        <v>5.6</v>
       </c>
       <c r="I17">
-        <v>4.1</v>
+        <v>6.2</v>
       </c>
       <c r="J17">
-        <v>2.78</v>
+        <v>4.5</v>
       </c>
       <c r="K17">
-        <v>3.2</v>
+        <v>5</v>
       </c>
       <c r="L17">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M17">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="N17">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O17">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="P17">
-        <v>1.35</v>
+        <v>2.52</v>
       </c>
       <c r="Q17">
-        <v>3</v>
+        <v>1.57</v>
       </c>
       <c r="R17">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="S17">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="T17">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U17">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="V17">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W17">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="X17">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="Y17">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="Z17">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="AA17">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="AB17">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AC17">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AD17">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AE17">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="AF17">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="AG17">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AH17">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AI17">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="AJ17">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="AK17">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="AL17">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="AM17">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="AN17">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="AO17">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="AP17">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="AQ17">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AR17">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AS17">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="AT17">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AU17">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="AV17">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AW17">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="AX17">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AY17">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AZ17">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="BA17">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="BB17">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="BC17">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="BD17">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="BE17">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BF17">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="BG17">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="BH17" t="s">
-        <v>125</v>
+        <v>147</v>
       </c>
     </row>
     <row r="18" spans="1:60">
       <c r="A18" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="B18" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C18" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D18" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E18" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="F18">
-        <v>1.34</v>
+        <v>2.28</v>
       </c>
       <c r="G18">
-        <v>1.62</v>
+        <v>2.6</v>
       </c>
       <c r="H18">
-        <v>2.68</v>
+        <v>3.45</v>
       </c>
       <c r="I18">
-        <v>100</v>
+        <v>4.1</v>
       </c>
       <c r="J18">
-        <v>2.68</v>
+        <v>2.88</v>
       </c>
       <c r="K18">
-        <v>85</v>
+        <v>3.35</v>
       </c>
       <c r="L18">
         <v>0</v>
@@ -3893,10 +3959,10 @@
         <v>0</v>
       </c>
       <c r="P18">
-        <v>1.91</v>
+        <v>1.52</v>
       </c>
       <c r="Q18">
-        <v>1.63</v>
+        <v>2.54</v>
       </c>
       <c r="R18">
         <v>0</v>
@@ -4025,42 +4091,42 @@
         <v>0</v>
       </c>
       <c r="BH18" t="s">
-        <v>125</v>
+        <v>147</v>
       </c>
     </row>
     <row r="19" spans="1:60">
       <c r="A19" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="B19" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C19" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D19" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E19" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="F19">
-        <v>1.55</v>
+        <v>1.72</v>
       </c>
       <c r="G19">
-        <v>2.64</v>
+        <v>1.89</v>
       </c>
       <c r="H19">
-        <v>2.84</v>
+        <v>5.2</v>
       </c>
       <c r="I19">
-        <v>4.5</v>
+        <v>7.2</v>
       </c>
       <c r="J19">
         <v>3.05</v>
       </c>
       <c r="K19">
-        <v>7.4</v>
+        <v>4.5</v>
       </c>
       <c r="L19">
         <v>0</v>
@@ -4075,10 +4141,10 @@
         <v>0</v>
       </c>
       <c r="P19">
-        <v>1.94</v>
+        <v>1.71</v>
       </c>
       <c r="Q19">
-        <v>1.69</v>
+        <v>2.14</v>
       </c>
       <c r="R19">
         <v>0</v>
@@ -4207,42 +4273,42 @@
         <v>0</v>
       </c>
       <c r="BH19" t="s">
-        <v>125</v>
+        <v>147</v>
       </c>
     </row>
     <row r="20" spans="1:60">
       <c r="A20" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B20" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C20" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D20" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E20" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="F20">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="G20">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="K20">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="L20">
         <v>0</v>
@@ -4257,10 +4323,10 @@
         <v>0</v>
       </c>
       <c r="P20">
-        <v>1.78</v>
+        <v>1.58</v>
       </c>
       <c r="Q20">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="R20">
         <v>0</v>
@@ -4389,189 +4455,2009 @@
         <v>0</v>
       </c>
       <c r="BH20" t="s">
-        <v>125</v>
+        <v>147</v>
       </c>
     </row>
     <row r="21" spans="1:60">
       <c r="A21" t="s">
+        <v>68</v>
+      </c>
+      <c r="B21" t="s">
+        <v>75</v>
+      </c>
+      <c r="C21" t="s">
+        <v>79</v>
+      </c>
+      <c r="D21" t="s">
+        <v>106</v>
+      </c>
+      <c r="E21" t="s">
+        <v>136</v>
+      </c>
+      <c r="F21">
+        <v>1.75</v>
+      </c>
+      <c r="G21">
+        <v>2.08</v>
+      </c>
+      <c r="H21">
+        <v>3.2</v>
+      </c>
+      <c r="I21">
+        <v>4.5</v>
+      </c>
+      <c r="J21">
+        <v>3.6</v>
+      </c>
+      <c r="K21">
+        <v>5.6</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21">
+        <v>2.14</v>
+      </c>
+      <c r="Q21">
+        <v>1.74</v>
+      </c>
+      <c r="R21">
+        <v>0</v>
+      </c>
+      <c r="S21">
+        <v>0</v>
+      </c>
+      <c r="T21">
+        <v>0</v>
+      </c>
+      <c r="U21">
+        <v>0</v>
+      </c>
+      <c r="V21">
+        <v>0</v>
+      </c>
+      <c r="W21">
+        <v>0</v>
+      </c>
+      <c r="X21">
+        <v>0</v>
+      </c>
+      <c r="Y21">
+        <v>0</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+      <c r="AA21">
+        <v>0</v>
+      </c>
+      <c r="AB21">
+        <v>0</v>
+      </c>
+      <c r="AC21">
+        <v>0</v>
+      </c>
+      <c r="AD21">
+        <v>0</v>
+      </c>
+      <c r="AE21">
+        <v>0</v>
+      </c>
+      <c r="AF21">
+        <v>0</v>
+      </c>
+      <c r="AG21">
+        <v>0</v>
+      </c>
+      <c r="AH21">
+        <v>0</v>
+      </c>
+      <c r="AI21">
+        <v>0</v>
+      </c>
+      <c r="AJ21">
+        <v>0</v>
+      </c>
+      <c r="AK21">
+        <v>0</v>
+      </c>
+      <c r="AL21">
+        <v>0</v>
+      </c>
+      <c r="AM21">
+        <v>0</v>
+      </c>
+      <c r="AN21">
+        <v>0</v>
+      </c>
+      <c r="AO21">
+        <v>0</v>
+      </c>
+      <c r="AP21">
+        <v>0</v>
+      </c>
+      <c r="AQ21">
+        <v>0</v>
+      </c>
+      <c r="AR21">
+        <v>0</v>
+      </c>
+      <c r="AS21">
+        <v>0</v>
+      </c>
+      <c r="AT21">
+        <v>0</v>
+      </c>
+      <c r="AU21">
+        <v>0</v>
+      </c>
+      <c r="AV21">
+        <v>0</v>
+      </c>
+      <c r="AW21">
+        <v>0</v>
+      </c>
+      <c r="AX21">
+        <v>0</v>
+      </c>
+      <c r="AY21">
+        <v>0</v>
+      </c>
+      <c r="AZ21">
+        <v>0</v>
+      </c>
+      <c r="BA21">
+        <v>0</v>
+      </c>
+      <c r="BB21">
+        <v>0</v>
+      </c>
+      <c r="BC21">
+        <v>0</v>
+      </c>
+      <c r="BD21">
+        <v>0</v>
+      </c>
+      <c r="BE21">
+        <v>0</v>
+      </c>
+      <c r="BF21">
+        <v>0</v>
+      </c>
+      <c r="BG21">
+        <v>0</v>
+      </c>
+      <c r="BH21" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="22" spans="1:60">
+      <c r="A22" t="s">
         <v>69</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B22" t="s">
+        <v>75</v>
+      </c>
+      <c r="C22" t="s">
+        <v>79</v>
+      </c>
+      <c r="D22" t="s">
+        <v>107</v>
+      </c>
+      <c r="E22" t="s">
+        <v>137</v>
+      </c>
+      <c r="F22">
+        <v>1.39</v>
+      </c>
+      <c r="G22">
+        <v>1.43</v>
+      </c>
+      <c r="H22">
+        <v>7.2</v>
+      </c>
+      <c r="I22">
+        <v>9.4</v>
+      </c>
+      <c r="J22">
+        <v>5.8</v>
+      </c>
+      <c r="K22">
+        <v>6.6</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <v>3.55</v>
+      </c>
+      <c r="Q22">
+        <v>1.33</v>
+      </c>
+      <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <v>0</v>
+      </c>
+      <c r="U22">
+        <v>0</v>
+      </c>
+      <c r="V22">
+        <v>0</v>
+      </c>
+      <c r="W22">
+        <v>0</v>
+      </c>
+      <c r="X22">
+        <v>0</v>
+      </c>
+      <c r="Y22">
+        <v>0</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+      <c r="AA22">
+        <v>0</v>
+      </c>
+      <c r="AB22">
+        <v>0</v>
+      </c>
+      <c r="AC22">
+        <v>0</v>
+      </c>
+      <c r="AD22">
+        <v>0</v>
+      </c>
+      <c r="AE22">
+        <v>0</v>
+      </c>
+      <c r="AF22">
+        <v>0</v>
+      </c>
+      <c r="AG22">
+        <v>0</v>
+      </c>
+      <c r="AH22">
+        <v>0</v>
+      </c>
+      <c r="AI22">
+        <v>0</v>
+      </c>
+      <c r="AJ22">
+        <v>0</v>
+      </c>
+      <c r="AK22">
+        <v>0</v>
+      </c>
+      <c r="AL22">
+        <v>0</v>
+      </c>
+      <c r="AM22">
+        <v>0</v>
+      </c>
+      <c r="AN22">
+        <v>0</v>
+      </c>
+      <c r="AO22">
+        <v>0</v>
+      </c>
+      <c r="AP22">
+        <v>0</v>
+      </c>
+      <c r="AQ22">
+        <v>0</v>
+      </c>
+      <c r="AR22">
+        <v>0</v>
+      </c>
+      <c r="AS22">
+        <v>0</v>
+      </c>
+      <c r="AT22">
+        <v>0</v>
+      </c>
+      <c r="AU22">
+        <v>0</v>
+      </c>
+      <c r="AV22">
+        <v>0</v>
+      </c>
+      <c r="AW22">
+        <v>0</v>
+      </c>
+      <c r="AX22">
+        <v>0</v>
+      </c>
+      <c r="AY22">
+        <v>0</v>
+      </c>
+      <c r="AZ22">
+        <v>0</v>
+      </c>
+      <c r="BA22">
+        <v>0</v>
+      </c>
+      <c r="BB22">
+        <v>0</v>
+      </c>
+      <c r="BC22">
+        <v>0</v>
+      </c>
+      <c r="BD22">
+        <v>0</v>
+      </c>
+      <c r="BE22">
+        <v>0</v>
+      </c>
+      <c r="BF22">
+        <v>0</v>
+      </c>
+      <c r="BG22">
+        <v>0</v>
+      </c>
+      <c r="BH22" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="23" spans="1:60">
+      <c r="A23" t="s">
+        <v>70</v>
+      </c>
+      <c r="B23" t="s">
+        <v>75</v>
+      </c>
+      <c r="C23" t="s">
+        <v>79</v>
+      </c>
+      <c r="D23" t="s">
+        <v>108</v>
+      </c>
+      <c r="E23" t="s">
+        <v>138</v>
+      </c>
+      <c r="F23">
+        <v>2.16</v>
+      </c>
+      <c r="G23">
+        <v>2.76</v>
+      </c>
+      <c r="H23">
+        <v>2.74</v>
+      </c>
+      <c r="I23">
+        <v>4</v>
+      </c>
+      <c r="J23">
+        <v>2.56</v>
+      </c>
+      <c r="K23">
+        <v>85</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23">
+        <v>0</v>
+      </c>
+      <c r="P23">
+        <v>2.02</v>
+      </c>
+      <c r="Q23">
+        <v>1.58</v>
+      </c>
+      <c r="R23">
+        <v>0</v>
+      </c>
+      <c r="S23">
+        <v>0</v>
+      </c>
+      <c r="T23">
+        <v>0</v>
+      </c>
+      <c r="U23">
+        <v>0</v>
+      </c>
+      <c r="V23">
+        <v>0</v>
+      </c>
+      <c r="W23">
+        <v>0</v>
+      </c>
+      <c r="X23">
+        <v>0</v>
+      </c>
+      <c r="Y23">
+        <v>0</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+      <c r="AA23">
+        <v>0</v>
+      </c>
+      <c r="AB23">
+        <v>0</v>
+      </c>
+      <c r="AC23">
+        <v>0</v>
+      </c>
+      <c r="AD23">
+        <v>0</v>
+      </c>
+      <c r="AE23">
+        <v>0</v>
+      </c>
+      <c r="AF23">
+        <v>0</v>
+      </c>
+      <c r="AG23">
+        <v>0</v>
+      </c>
+      <c r="AH23">
+        <v>0</v>
+      </c>
+      <c r="AI23">
+        <v>0</v>
+      </c>
+      <c r="AJ23">
+        <v>0</v>
+      </c>
+      <c r="AK23">
+        <v>0</v>
+      </c>
+      <c r="AL23">
+        <v>0</v>
+      </c>
+      <c r="AM23">
+        <v>0</v>
+      </c>
+      <c r="AN23">
+        <v>0</v>
+      </c>
+      <c r="AO23">
+        <v>0</v>
+      </c>
+      <c r="AP23">
+        <v>0</v>
+      </c>
+      <c r="AQ23">
+        <v>0</v>
+      </c>
+      <c r="AR23">
+        <v>0</v>
+      </c>
+      <c r="AS23">
+        <v>0</v>
+      </c>
+      <c r="AT23">
+        <v>0</v>
+      </c>
+      <c r="AU23">
+        <v>0</v>
+      </c>
+      <c r="AV23">
+        <v>0</v>
+      </c>
+      <c r="AW23">
+        <v>0</v>
+      </c>
+      <c r="AX23">
+        <v>0</v>
+      </c>
+      <c r="AY23">
+        <v>0</v>
+      </c>
+      <c r="AZ23">
+        <v>0</v>
+      </c>
+      <c r="BA23">
+        <v>0</v>
+      </c>
+      <c r="BB23">
+        <v>0</v>
+      </c>
+      <c r="BC23">
+        <v>0</v>
+      </c>
+      <c r="BD23">
+        <v>0</v>
+      </c>
+      <c r="BE23">
+        <v>0</v>
+      </c>
+      <c r="BF23">
+        <v>0</v>
+      </c>
+      <c r="BG23">
+        <v>0</v>
+      </c>
+      <c r="BH23" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="24" spans="1:60">
+      <c r="A24" t="s">
+        <v>66</v>
+      </c>
+      <c r="B24" t="s">
+        <v>75</v>
+      </c>
+      <c r="C24" t="s">
+        <v>80</v>
+      </c>
+      <c r="D24" t="s">
+        <v>109</v>
+      </c>
+      <c r="E24" t="s">
+        <v>139</v>
+      </c>
+      <c r="F24">
+        <v>1.97</v>
+      </c>
+      <c r="G24">
+        <v>2.38</v>
+      </c>
+      <c r="H24">
+        <v>3.25</v>
+      </c>
+      <c r="I24">
+        <v>4.9</v>
+      </c>
+      <c r="J24">
+        <v>3.25</v>
+      </c>
+      <c r="K24">
+        <v>5.5</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24">
+        <v>0</v>
+      </c>
+      <c r="O24">
+        <v>0</v>
+      </c>
+      <c r="P24">
+        <v>1.9</v>
+      </c>
+      <c r="Q24">
+        <v>1.66</v>
+      </c>
+      <c r="R24">
+        <v>0</v>
+      </c>
+      <c r="S24">
+        <v>0</v>
+      </c>
+      <c r="T24">
+        <v>0</v>
+      </c>
+      <c r="U24">
+        <v>0</v>
+      </c>
+      <c r="V24">
+        <v>0</v>
+      </c>
+      <c r="W24">
+        <v>0</v>
+      </c>
+      <c r="X24">
+        <v>0</v>
+      </c>
+      <c r="Y24">
+        <v>0</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+      <c r="AA24">
+        <v>0</v>
+      </c>
+      <c r="AB24">
+        <v>0</v>
+      </c>
+      <c r="AC24">
+        <v>0</v>
+      </c>
+      <c r="AD24">
+        <v>0</v>
+      </c>
+      <c r="AE24">
+        <v>0</v>
+      </c>
+      <c r="AF24">
+        <v>0</v>
+      </c>
+      <c r="AG24">
+        <v>0</v>
+      </c>
+      <c r="AH24">
+        <v>0</v>
+      </c>
+      <c r="AI24">
+        <v>0</v>
+      </c>
+      <c r="AJ24">
+        <v>0</v>
+      </c>
+      <c r="AK24">
+        <v>0</v>
+      </c>
+      <c r="AL24">
+        <v>0</v>
+      </c>
+      <c r="AM24">
+        <v>0</v>
+      </c>
+      <c r="AN24">
+        <v>0</v>
+      </c>
+      <c r="AO24">
+        <v>0</v>
+      </c>
+      <c r="AP24">
+        <v>0</v>
+      </c>
+      <c r="AQ24">
+        <v>0</v>
+      </c>
+      <c r="AR24">
+        <v>0</v>
+      </c>
+      <c r="AS24">
+        <v>0</v>
+      </c>
+      <c r="AT24">
+        <v>0</v>
+      </c>
+      <c r="AU24">
+        <v>0</v>
+      </c>
+      <c r="AV24">
+        <v>0</v>
+      </c>
+      <c r="AW24">
+        <v>0</v>
+      </c>
+      <c r="AX24">
+        <v>0</v>
+      </c>
+      <c r="AY24">
+        <v>0</v>
+      </c>
+      <c r="AZ24">
+        <v>0</v>
+      </c>
+      <c r="BA24">
+        <v>0</v>
+      </c>
+      <c r="BB24">
+        <v>0</v>
+      </c>
+      <c r="BC24">
+        <v>0</v>
+      </c>
+      <c r="BD24">
+        <v>0</v>
+      </c>
+      <c r="BE24">
+        <v>0</v>
+      </c>
+      <c r="BF24">
+        <v>0</v>
+      </c>
+      <c r="BG24">
+        <v>0</v>
+      </c>
+      <c r="BH24" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="25" spans="1:60">
+      <c r="A25" t="s">
+        <v>65</v>
+      </c>
+      <c r="B25" t="s">
+        <v>75</v>
+      </c>
+      <c r="C25" t="s">
+        <v>81</v>
+      </c>
+      <c r="D25" t="s">
+        <v>110</v>
+      </c>
+      <c r="E25" t="s">
+        <v>140</v>
+      </c>
+      <c r="F25">
+        <v>1.65</v>
+      </c>
+      <c r="G25">
+        <v>1.68</v>
+      </c>
+      <c r="H25">
+        <v>5.8</v>
+      </c>
+      <c r="I25">
+        <v>6.2</v>
+      </c>
+      <c r="J25">
+        <v>4.2</v>
+      </c>
+      <c r="K25">
+        <v>4.5</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25">
+        <v>1.07</v>
+      </c>
+      <c r="N25">
+        <v>3.95</v>
+      </c>
+      <c r="O25">
+        <v>1.32</v>
+      </c>
+      <c r="P25">
+        <v>2</v>
+      </c>
+      <c r="Q25">
+        <v>1.94</v>
+      </c>
+      <c r="R25">
+        <v>1.37</v>
+      </c>
+      <c r="S25">
+        <v>3.45</v>
+      </c>
+      <c r="T25">
+        <v>1.97</v>
+      </c>
+      <c r="U25">
+        <v>1.98</v>
+      </c>
+      <c r="V25">
+        <v>0</v>
+      </c>
+      <c r="W25">
+        <v>0</v>
+      </c>
+      <c r="X25">
+        <v>16</v>
+      </c>
+      <c r="Y25">
+        <v>19</v>
+      </c>
+      <c r="Z25">
+        <v>48</v>
+      </c>
+      <c r="AA25">
+        <v>1000</v>
+      </c>
+      <c r="AB25">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC25">
+        <v>9.4</v>
+      </c>
+      <c r="AD25">
+        <v>22</v>
+      </c>
+      <c r="AE25">
+        <v>1000</v>
+      </c>
+      <c r="AF25">
+        <v>9.4</v>
+      </c>
+      <c r="AG25">
+        <v>10</v>
+      </c>
+      <c r="AH25">
+        <v>24</v>
+      </c>
+      <c r="AI25">
+        <v>1000</v>
+      </c>
+      <c r="AJ25">
+        <v>16.5</v>
+      </c>
+      <c r="AK25">
+        <v>18</v>
+      </c>
+      <c r="AL25">
+        <v>38</v>
+      </c>
+      <c r="AM25">
+        <v>150</v>
+      </c>
+      <c r="AN25">
+        <v>10</v>
+      </c>
+      <c r="AO25">
+        <v>120</v>
+      </c>
+      <c r="AP25">
+        <v>14</v>
+      </c>
+      <c r="AQ25">
+        <v>17</v>
+      </c>
+      <c r="AR25">
+        <v>25</v>
+      </c>
+      <c r="AS25">
+        <v>44</v>
+      </c>
+      <c r="AT25">
+        <v>7.6</v>
+      </c>
+      <c r="AU25">
+        <v>9</v>
+      </c>
+      <c r="AV25">
+        <v>20</v>
+      </c>
+      <c r="AW25">
+        <v>34</v>
+      </c>
+      <c r="AX25">
+        <v>9</v>
+      </c>
+      <c r="AY25">
+        <v>9</v>
+      </c>
+      <c r="AZ25">
+        <v>21</v>
+      </c>
+      <c r="BA25">
+        <v>36</v>
+      </c>
+      <c r="BB25">
+        <v>14.5</v>
+      </c>
+      <c r="BC25">
+        <v>16</v>
+      </c>
+      <c r="BD25">
+        <v>23</v>
+      </c>
+      <c r="BE25">
+        <v>42</v>
+      </c>
+      <c r="BF25">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BG25">
+        <v>38</v>
+      </c>
+      <c r="BH25" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="26" spans="1:60">
+      <c r="A26" t="s">
+        <v>61</v>
+      </c>
+      <c r="B26" t="s">
+        <v>75</v>
+      </c>
+      <c r="C26" t="s">
+        <v>82</v>
+      </c>
+      <c r="D26" t="s">
+        <v>111</v>
+      </c>
+      <c r="E26" t="s">
+        <v>141</v>
+      </c>
+      <c r="F26">
+        <v>6.8</v>
+      </c>
+      <c r="G26">
+        <v>7</v>
+      </c>
+      <c r="H26">
+        <v>1.51</v>
+      </c>
+      <c r="I26">
+        <v>1.52</v>
+      </c>
+      <c r="J26">
+        <v>5.1</v>
+      </c>
+      <c r="K26">
+        <v>5.2</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26">
+        <v>1.04</v>
+      </c>
+      <c r="N26">
+        <v>5.1</v>
+      </c>
+      <c r="O26">
+        <v>1.23</v>
+      </c>
+      <c r="P26">
+        <v>2.42</v>
+      </c>
+      <c r="Q26">
+        <v>1.67</v>
+      </c>
+      <c r="R26">
+        <v>1.54</v>
+      </c>
+      <c r="S26">
+        <v>2.74</v>
+      </c>
+      <c r="T26">
+        <v>1.84</v>
+      </c>
+      <c r="U26">
+        <v>2.14</v>
+      </c>
+      <c r="V26">
+        <v>0</v>
+      </c>
+      <c r="W26">
+        <v>0</v>
+      </c>
+      <c r="X26">
+        <v>24</v>
+      </c>
+      <c r="Y26">
+        <v>9.4</v>
+      </c>
+      <c r="Z26">
+        <v>9.4</v>
+      </c>
+      <c r="AA26">
+        <v>14.5</v>
+      </c>
+      <c r="AB26">
+        <v>27</v>
+      </c>
+      <c r="AC26">
+        <v>11.5</v>
+      </c>
+      <c r="AD26">
+        <v>9.6</v>
+      </c>
+      <c r="AE26">
+        <v>14.5</v>
+      </c>
+      <c r="AF26">
+        <v>60</v>
+      </c>
+      <c r="AG26">
+        <v>25</v>
+      </c>
+      <c r="AH26">
+        <v>22</v>
+      </c>
+      <c r="AI26">
+        <v>29</v>
+      </c>
+      <c r="AJ26">
+        <v>200</v>
+      </c>
+      <c r="AK26">
+        <v>90</v>
+      </c>
+      <c r="AL26">
+        <v>75</v>
+      </c>
+      <c r="AM26">
+        <v>100</v>
+      </c>
+      <c r="AN26">
+        <v>95</v>
+      </c>
+      <c r="AO26">
+        <v>6.6</v>
+      </c>
+      <c r="AP26">
+        <v>21</v>
+      </c>
+      <c r="AQ26">
+        <v>9</v>
+      </c>
+      <c r="AR26">
+        <v>9</v>
+      </c>
+      <c r="AS26">
+        <v>13</v>
+      </c>
+      <c r="AT26">
+        <v>23</v>
+      </c>
+      <c r="AU26">
+        <v>10.5</v>
+      </c>
+      <c r="AV26">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW26">
+        <v>13.5</v>
+      </c>
+      <c r="AX26">
+        <v>48</v>
+      </c>
+      <c r="AY26">
+        <v>22</v>
+      </c>
+      <c r="AZ26">
+        <v>19.5</v>
+      </c>
+      <c r="BA26">
+        <v>25</v>
+      </c>
+      <c r="BB26">
+        <v>46</v>
+      </c>
+      <c r="BC26">
+        <v>55</v>
+      </c>
+      <c r="BD26">
+        <v>55</v>
+      </c>
+      <c r="BE26">
+        <v>65</v>
+      </c>
+      <c r="BF26">
+        <v>40</v>
+      </c>
+      <c r="BG26">
+        <v>6.2</v>
+      </c>
+      <c r="BH26" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="27" spans="1:60">
+      <c r="A27" t="s">
+        <v>71</v>
+      </c>
+      <c r="B27" t="s">
+        <v>75</v>
+      </c>
+      <c r="C27" t="s">
+        <v>83</v>
+      </c>
+      <c r="D27" t="s">
+        <v>112</v>
+      </c>
+      <c r="E27" t="s">
+        <v>142</v>
+      </c>
+      <c r="F27">
+        <v>2.36</v>
+      </c>
+      <c r="G27">
+        <v>2.56</v>
+      </c>
+      <c r="H27">
+        <v>3.5</v>
+      </c>
+      <c r="I27">
+        <v>4.1</v>
+      </c>
+      <c r="J27">
+        <v>2.9</v>
+      </c>
+      <c r="K27">
+        <v>3.2</v>
+      </c>
+      <c r="L27">
+        <v>1.01</v>
+      </c>
+      <c r="M27">
+        <v>1.15</v>
+      </c>
+      <c r="N27">
+        <v>2.28</v>
+      </c>
+      <c r="O27">
+        <v>1.68</v>
+      </c>
+      <c r="P27">
+        <v>1.44</v>
+      </c>
+      <c r="Q27">
+        <v>3</v>
+      </c>
+      <c r="R27">
+        <v>1.14</v>
+      </c>
+      <c r="S27">
+        <v>6.8</v>
+      </c>
+      <c r="T27">
+        <v>2.2</v>
+      </c>
+      <c r="U27">
+        <v>1.62</v>
+      </c>
+      <c r="V27">
+        <v>1.33</v>
+      </c>
+      <c r="W27">
+        <v>1.64</v>
+      </c>
+      <c r="X27">
+        <v>8.4</v>
+      </c>
+      <c r="Y27">
+        <v>9.6</v>
+      </c>
+      <c r="Z27">
+        <v>26</v>
+      </c>
+      <c r="AA27">
+        <v>110</v>
+      </c>
+      <c r="AB27">
+        <v>7</v>
+      </c>
+      <c r="AC27">
+        <v>7.6</v>
+      </c>
+      <c r="AD27">
+        <v>21</v>
+      </c>
+      <c r="AE27">
+        <v>80</v>
+      </c>
+      <c r="AF27">
+        <v>14.5</v>
+      </c>
+      <c r="AG27">
+        <v>15</v>
+      </c>
+      <c r="AH27">
+        <v>30</v>
+      </c>
+      <c r="AI27">
+        <v>130</v>
+      </c>
+      <c r="AJ27">
+        <v>46</v>
+      </c>
+      <c r="AK27">
+        <v>44</v>
+      </c>
+      <c r="AL27">
+        <v>95</v>
+      </c>
+      <c r="AM27">
+        <v>320</v>
+      </c>
+      <c r="AN27">
+        <v>60</v>
+      </c>
+      <c r="AO27">
+        <v>140</v>
+      </c>
+      <c r="AP27">
+        <v>6.2</v>
+      </c>
+      <c r="AQ27">
+        <v>7.8</v>
+      </c>
+      <c r="AR27">
+        <v>21</v>
+      </c>
+      <c r="AS27">
+        <v>6.8</v>
+      </c>
+      <c r="AT27">
+        <v>5.8</v>
+      </c>
+      <c r="AU27">
+        <v>6.2</v>
+      </c>
+      <c r="AV27">
+        <v>15</v>
+      </c>
+      <c r="AW27">
+        <v>6.6</v>
+      </c>
+      <c r="AX27">
+        <v>11.5</v>
+      </c>
+      <c r="AY27">
+        <v>11</v>
+      </c>
+      <c r="AZ27">
+        <v>5.9</v>
+      </c>
+      <c r="BA27">
+        <v>6.8</v>
+      </c>
+      <c r="BB27">
+        <v>6.2</v>
+      </c>
+      <c r="BC27">
+        <v>6.2</v>
+      </c>
+      <c r="BD27">
+        <v>6.8</v>
+      </c>
+      <c r="BE27">
+        <v>7</v>
+      </c>
+      <c r="BF27">
+        <v>36</v>
+      </c>
+      <c r="BG27">
+        <v>6.8</v>
+      </c>
+      <c r="BH27" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="28" spans="1:60">
+      <c r="A28" t="s">
+        <v>72</v>
+      </c>
+      <c r="B28" t="s">
+        <v>75</v>
+      </c>
+      <c r="C28" t="s">
+        <v>84</v>
+      </c>
+      <c r="D28" t="s">
+        <v>113</v>
+      </c>
+      <c r="E28" t="s">
+        <v>143</v>
+      </c>
+      <c r="F28">
+        <v>1.34</v>
+      </c>
+      <c r="G28">
+        <v>1.62</v>
+      </c>
+      <c r="H28">
+        <v>2.68</v>
+      </c>
+      <c r="I28">
+        <v>100</v>
+      </c>
+      <c r="J28">
+        <v>2.68</v>
+      </c>
+      <c r="K28">
+        <v>85</v>
+      </c>
+      <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28">
+        <v>0</v>
+      </c>
+      <c r="N28">
+        <v>0</v>
+      </c>
+      <c r="O28">
+        <v>0</v>
+      </c>
+      <c r="P28">
+        <v>1.91</v>
+      </c>
+      <c r="Q28">
+        <v>1.63</v>
+      </c>
+      <c r="R28">
+        <v>0</v>
+      </c>
+      <c r="S28">
+        <v>0</v>
+      </c>
+      <c r="T28">
+        <v>0</v>
+      </c>
+      <c r="U28">
+        <v>0</v>
+      </c>
+      <c r="V28">
+        <v>0</v>
+      </c>
+      <c r="W28">
+        <v>0</v>
+      </c>
+      <c r="X28">
+        <v>0</v>
+      </c>
+      <c r="Y28">
+        <v>0</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+      <c r="AA28">
+        <v>0</v>
+      </c>
+      <c r="AB28">
+        <v>0</v>
+      </c>
+      <c r="AC28">
+        <v>0</v>
+      </c>
+      <c r="AD28">
+        <v>0</v>
+      </c>
+      <c r="AE28">
+        <v>0</v>
+      </c>
+      <c r="AF28">
+        <v>0</v>
+      </c>
+      <c r="AG28">
+        <v>0</v>
+      </c>
+      <c r="AH28">
+        <v>0</v>
+      </c>
+      <c r="AI28">
+        <v>0</v>
+      </c>
+      <c r="AJ28">
+        <v>0</v>
+      </c>
+      <c r="AK28">
+        <v>0</v>
+      </c>
+      <c r="AL28">
+        <v>0</v>
+      </c>
+      <c r="AM28">
+        <v>0</v>
+      </c>
+      <c r="AN28">
+        <v>0</v>
+      </c>
+      <c r="AO28">
+        <v>0</v>
+      </c>
+      <c r="AP28">
+        <v>0</v>
+      </c>
+      <c r="AQ28">
+        <v>0</v>
+      </c>
+      <c r="AR28">
+        <v>0</v>
+      </c>
+      <c r="AS28">
+        <v>0</v>
+      </c>
+      <c r="AT28">
+        <v>0</v>
+      </c>
+      <c r="AU28">
+        <v>0</v>
+      </c>
+      <c r="AV28">
+        <v>0</v>
+      </c>
+      <c r="AW28">
+        <v>0</v>
+      </c>
+      <c r="AX28">
+        <v>0</v>
+      </c>
+      <c r="AY28">
+        <v>0</v>
+      </c>
+      <c r="AZ28">
+        <v>0</v>
+      </c>
+      <c r="BA28">
+        <v>0</v>
+      </c>
+      <c r="BB28">
+        <v>0</v>
+      </c>
+      <c r="BC28">
+        <v>0</v>
+      </c>
+      <c r="BD28">
+        <v>0</v>
+      </c>
+      <c r="BE28">
+        <v>0</v>
+      </c>
+      <c r="BF28">
+        <v>0</v>
+      </c>
+      <c r="BG28">
+        <v>0</v>
+      </c>
+      <c r="BH28" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="29" spans="1:60">
+      <c r="A29" t="s">
         <v>73</v>
       </c>
-      <c r="C21" t="s">
-        <v>84</v>
-      </c>
-      <c r="D21" t="s">
-        <v>104</v>
-      </c>
-      <c r="E21" t="s">
-        <v>124</v>
-      </c>
-      <c r="F21">
+      <c r="B29" t="s">
+        <v>75</v>
+      </c>
+      <c r="C29" t="s">
+        <v>85</v>
+      </c>
+      <c r="D29" t="s">
+        <v>114</v>
+      </c>
+      <c r="E29" t="s">
+        <v>144</v>
+      </c>
+      <c r="F29">
+        <v>1.55</v>
+      </c>
+      <c r="G29">
+        <v>2.64</v>
+      </c>
+      <c r="H29">
+        <v>2.84</v>
+      </c>
+      <c r="I29">
+        <v>4.5</v>
+      </c>
+      <c r="J29">
+        <v>3.05</v>
+      </c>
+      <c r="K29">
+        <v>150</v>
+      </c>
+      <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="M29">
+        <v>0</v>
+      </c>
+      <c r="N29">
+        <v>0</v>
+      </c>
+      <c r="O29">
+        <v>0</v>
+      </c>
+      <c r="P29">
+        <v>1.94</v>
+      </c>
+      <c r="Q29">
+        <v>1.69</v>
+      </c>
+      <c r="R29">
+        <v>0</v>
+      </c>
+      <c r="S29">
+        <v>0</v>
+      </c>
+      <c r="T29">
+        <v>0</v>
+      </c>
+      <c r="U29">
+        <v>0</v>
+      </c>
+      <c r="V29">
+        <v>0</v>
+      </c>
+      <c r="W29">
+        <v>0</v>
+      </c>
+      <c r="X29">
+        <v>0</v>
+      </c>
+      <c r="Y29">
+        <v>0</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+      <c r="AA29">
+        <v>0</v>
+      </c>
+      <c r="AB29">
+        <v>0</v>
+      </c>
+      <c r="AC29">
+        <v>0</v>
+      </c>
+      <c r="AD29">
+        <v>0</v>
+      </c>
+      <c r="AE29">
+        <v>0</v>
+      </c>
+      <c r="AF29">
+        <v>0</v>
+      </c>
+      <c r="AG29">
+        <v>0</v>
+      </c>
+      <c r="AH29">
+        <v>0</v>
+      </c>
+      <c r="AI29">
+        <v>0</v>
+      </c>
+      <c r="AJ29">
+        <v>0</v>
+      </c>
+      <c r="AK29">
+        <v>0</v>
+      </c>
+      <c r="AL29">
+        <v>0</v>
+      </c>
+      <c r="AM29">
+        <v>0</v>
+      </c>
+      <c r="AN29">
+        <v>0</v>
+      </c>
+      <c r="AO29">
+        <v>0</v>
+      </c>
+      <c r="AP29">
+        <v>0</v>
+      </c>
+      <c r="AQ29">
+        <v>0</v>
+      </c>
+      <c r="AR29">
+        <v>0</v>
+      </c>
+      <c r="AS29">
+        <v>0</v>
+      </c>
+      <c r="AT29">
+        <v>0</v>
+      </c>
+      <c r="AU29">
+        <v>0</v>
+      </c>
+      <c r="AV29">
+        <v>0</v>
+      </c>
+      <c r="AW29">
+        <v>0</v>
+      </c>
+      <c r="AX29">
+        <v>0</v>
+      </c>
+      <c r="AY29">
+        <v>0</v>
+      </c>
+      <c r="AZ29">
+        <v>0</v>
+      </c>
+      <c r="BA29">
+        <v>0</v>
+      </c>
+      <c r="BB29">
+        <v>0</v>
+      </c>
+      <c r="BC29">
+        <v>0</v>
+      </c>
+      <c r="BD29">
+        <v>0</v>
+      </c>
+      <c r="BE29">
+        <v>0</v>
+      </c>
+      <c r="BF29">
+        <v>0</v>
+      </c>
+      <c r="BG29">
+        <v>0</v>
+      </c>
+      <c r="BH29" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="30" spans="1:60">
+      <c r="A30" t="s">
+        <v>74</v>
+      </c>
+      <c r="B30" t="s">
+        <v>75</v>
+      </c>
+      <c r="C30" t="s">
+        <v>85</v>
+      </c>
+      <c r="D30" t="s">
+        <v>115</v>
+      </c>
+      <c r="E30" t="s">
+        <v>145</v>
+      </c>
+      <c r="F30">
+        <v>0</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30">
+        <v>0</v>
+      </c>
+      <c r="L30">
+        <v>0</v>
+      </c>
+      <c r="M30">
+        <v>0</v>
+      </c>
+      <c r="N30">
+        <v>0</v>
+      </c>
+      <c r="O30">
+        <v>0</v>
+      </c>
+      <c r="P30">
+        <v>1.78</v>
+      </c>
+      <c r="Q30">
+        <v>1.01</v>
+      </c>
+      <c r="R30">
+        <v>0</v>
+      </c>
+      <c r="S30">
+        <v>0</v>
+      </c>
+      <c r="T30">
+        <v>0</v>
+      </c>
+      <c r="U30">
+        <v>0</v>
+      </c>
+      <c r="V30">
+        <v>0</v>
+      </c>
+      <c r="W30">
+        <v>0</v>
+      </c>
+      <c r="X30">
+        <v>0</v>
+      </c>
+      <c r="Y30">
+        <v>0</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+      <c r="AA30">
+        <v>0</v>
+      </c>
+      <c r="AB30">
+        <v>0</v>
+      </c>
+      <c r="AC30">
+        <v>0</v>
+      </c>
+      <c r="AD30">
+        <v>0</v>
+      </c>
+      <c r="AE30">
+        <v>0</v>
+      </c>
+      <c r="AF30">
+        <v>0</v>
+      </c>
+      <c r="AG30">
+        <v>0</v>
+      </c>
+      <c r="AH30">
+        <v>0</v>
+      </c>
+      <c r="AI30">
+        <v>0</v>
+      </c>
+      <c r="AJ30">
+        <v>0</v>
+      </c>
+      <c r="AK30">
+        <v>0</v>
+      </c>
+      <c r="AL30">
+        <v>0</v>
+      </c>
+      <c r="AM30">
+        <v>0</v>
+      </c>
+      <c r="AN30">
+        <v>0</v>
+      </c>
+      <c r="AO30">
+        <v>0</v>
+      </c>
+      <c r="AP30">
+        <v>0</v>
+      </c>
+      <c r="AQ30">
+        <v>0</v>
+      </c>
+      <c r="AR30">
+        <v>0</v>
+      </c>
+      <c r="AS30">
+        <v>0</v>
+      </c>
+      <c r="AT30">
+        <v>0</v>
+      </c>
+      <c r="AU30">
+        <v>0</v>
+      </c>
+      <c r="AV30">
+        <v>0</v>
+      </c>
+      <c r="AW30">
+        <v>0</v>
+      </c>
+      <c r="AX30">
+        <v>0</v>
+      </c>
+      <c r="AY30">
+        <v>0</v>
+      </c>
+      <c r="AZ30">
+        <v>0</v>
+      </c>
+      <c r="BA30">
+        <v>0</v>
+      </c>
+      <c r="BB30">
+        <v>0</v>
+      </c>
+      <c r="BC30">
+        <v>0</v>
+      </c>
+      <c r="BD30">
+        <v>0</v>
+      </c>
+      <c r="BE30">
+        <v>0</v>
+      </c>
+      <c r="BF30">
+        <v>0</v>
+      </c>
+      <c r="BG30">
+        <v>0</v>
+      </c>
+      <c r="BH30" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="31" spans="1:60">
+      <c r="A31" t="s">
+        <v>71</v>
+      </c>
+      <c r="B31" t="s">
+        <v>75</v>
+      </c>
+      <c r="C31" t="s">
+        <v>86</v>
+      </c>
+      <c r="D31" t="s">
+        <v>116</v>
+      </c>
+      <c r="E31" t="s">
+        <v>146</v>
+      </c>
+      <c r="F31">
         <v>1.61</v>
       </c>
-      <c r="G21">
+      <c r="G31">
         <v>1.74</v>
       </c>
-      <c r="H21">
+      <c r="H31">
         <v>6.4</v>
       </c>
-      <c r="I21">
-        <v>9.6</v>
-      </c>
-      <c r="J21">
+      <c r="I31">
+        <v>7.8</v>
+      </c>
+      <c r="J31">
         <v>3.55</v>
       </c>
-      <c r="K21">
+      <c r="K31">
         <v>4.5</v>
       </c>
-      <c r="L21">
-        <v>1.01</v>
-      </c>
-      <c r="M21">
-        <v>1.01</v>
-      </c>
-      <c r="N21">
-        <v>1.01</v>
-      </c>
-      <c r="O21">
-        <v>1.02</v>
-      </c>
-      <c r="P21">
-        <v>1.25</v>
-      </c>
-      <c r="Q21">
+      <c r="L31">
+        <v>1.01</v>
+      </c>
+      <c r="M31">
+        <v>1.09</v>
+      </c>
+      <c r="N31">
+        <v>2.92</v>
+      </c>
+      <c r="O31">
         <v>1.44</v>
       </c>
-      <c r="R21">
-        <v>1.18</v>
-      </c>
-      <c r="S21">
-        <v>3.6</v>
-      </c>
-      <c r="T21">
-        <v>1.01</v>
-      </c>
-      <c r="U21">
-        <v>1.01</v>
-      </c>
-      <c r="V21">
-        <v>1.13</v>
-      </c>
-      <c r="W21">
+      <c r="P31">
+        <v>1.65</v>
+      </c>
+      <c r="Q31">
+        <v>2.26</v>
+      </c>
+      <c r="R31">
+        <v>1.23</v>
+      </c>
+      <c r="S31">
+        <v>4.4</v>
+      </c>
+      <c r="T31">
+        <v>2.16</v>
+      </c>
+      <c r="U31">
+        <v>1.68</v>
+      </c>
+      <c r="V31">
+        <v>1.14</v>
+      </c>
+      <c r="W31">
         <v>2.34</v>
       </c>
-      <c r="X21">
-        <v>1000</v>
-      </c>
-      <c r="Y21">
-        <v>1000</v>
-      </c>
-      <c r="Z21">
-        <v>1000</v>
-      </c>
-      <c r="AA21">
-        <v>1000</v>
-      </c>
-      <c r="AB21">
-        <v>1000</v>
-      </c>
-      <c r="AC21">
-        <v>1000</v>
-      </c>
-      <c r="AD21">
-        <v>1000</v>
-      </c>
-      <c r="AE21">
-        <v>1000</v>
-      </c>
-      <c r="AF21">
-        <v>1000</v>
-      </c>
-      <c r="AG21">
-        <v>1000</v>
-      </c>
-      <c r="AH21">
-        <v>1000</v>
-      </c>
-      <c r="AI21">
-        <v>1000</v>
-      </c>
-      <c r="AJ21">
-        <v>1000</v>
-      </c>
-      <c r="AK21">
-        <v>1000</v>
-      </c>
-      <c r="AL21">
-        <v>1000</v>
-      </c>
-      <c r="AM21">
-        <v>1000</v>
-      </c>
-      <c r="AN21">
-        <v>1000</v>
-      </c>
-      <c r="AO21">
-        <v>1000</v>
-      </c>
-      <c r="AP21">
-        <v>1.01</v>
-      </c>
-      <c r="AQ21">
-        <v>1.01</v>
-      </c>
-      <c r="AR21">
-        <v>1.01</v>
-      </c>
-      <c r="AS21">
-        <v>1.01</v>
-      </c>
-      <c r="AT21">
-        <v>1.01</v>
-      </c>
-      <c r="AU21">
-        <v>1.01</v>
-      </c>
-      <c r="AV21">
-        <v>1.01</v>
-      </c>
-      <c r="AW21">
-        <v>1.01</v>
-      </c>
-      <c r="AX21">
-        <v>1.01</v>
-      </c>
-      <c r="AY21">
-        <v>1.01</v>
-      </c>
-      <c r="AZ21">
-        <v>1.01</v>
-      </c>
-      <c r="BA21">
-        <v>1.01</v>
-      </c>
-      <c r="BB21">
-        <v>1.01</v>
-      </c>
-      <c r="BC21">
-        <v>1.01</v>
-      </c>
-      <c r="BD21">
-        <v>1.01</v>
-      </c>
-      <c r="BE21">
-        <v>1.01</v>
-      </c>
-      <c r="BF21">
-        <v>1.01</v>
-      </c>
-      <c r="BG21">
-        <v>1.01</v>
-      </c>
-      <c r="BH21" t="s">
-        <v>125</v>
+      <c r="X31">
+        <v>12.5</v>
+      </c>
+      <c r="Y31">
+        <v>21</v>
+      </c>
+      <c r="Z31">
+        <v>70</v>
+      </c>
+      <c r="AA31">
+        <v>300</v>
+      </c>
+      <c r="AB31">
+        <v>7.4</v>
+      </c>
+      <c r="AC31">
+        <v>10</v>
+      </c>
+      <c r="AD31">
+        <v>34</v>
+      </c>
+      <c r="AE31">
+        <v>160</v>
+      </c>
+      <c r="AF31">
+        <v>10</v>
+      </c>
+      <c r="AG31">
+        <v>12</v>
+      </c>
+      <c r="AH31">
+        <v>29</v>
+      </c>
+      <c r="AI31">
+        <v>160</v>
+      </c>
+      <c r="AJ31">
+        <v>19.5</v>
+      </c>
+      <c r="AK31">
+        <v>23</v>
+      </c>
+      <c r="AL31">
+        <v>65</v>
+      </c>
+      <c r="AM31">
+        <v>250</v>
+      </c>
+      <c r="AN31">
+        <v>17</v>
+      </c>
+      <c r="AO31">
+        <v>280</v>
+      </c>
+      <c r="AP31">
+        <v>3.85</v>
+      </c>
+      <c r="AQ31">
+        <v>14.5</v>
+      </c>
+      <c r="AR31">
+        <v>5.1</v>
+      </c>
+      <c r="AS31">
+        <v>5.5</v>
+      </c>
+      <c r="AT31">
+        <v>5.6</v>
+      </c>
+      <c r="AU31">
+        <v>7.4</v>
+      </c>
+      <c r="AV31">
+        <v>4.7</v>
+      </c>
+      <c r="AW31">
+        <v>5.4</v>
+      </c>
+      <c r="AX31">
+        <v>7.4</v>
+      </c>
+      <c r="AY31">
+        <v>3.8</v>
+      </c>
+      <c r="AZ31">
+        <v>4.7</v>
+      </c>
+      <c r="BA31">
+        <v>5.4</v>
+      </c>
+      <c r="BB31">
+        <v>14</v>
+      </c>
+      <c r="BC31">
+        <v>4.5</v>
+      </c>
+      <c r="BD31">
+        <v>5.1</v>
+      </c>
+      <c r="BE31">
+        <v>5.4</v>
+      </c>
+      <c r="BF31">
+        <v>11</v>
+      </c>
+      <c r="BG31">
+        <v>5.5</v>
+      </c>
+      <c r="BH31" t="s">
+        <v>147</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-04.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="187">
   <si>
     <t>League</t>
   </si>
@@ -202,31 +202,55 @@
     <t>English Premier League</t>
   </si>
   <si>
+    <t>Romanian Liga I</t>
+  </si>
+  <si>
+    <t>Irish Premier Division</t>
+  </si>
+  <si>
+    <t>Irish Division 1</t>
+  </si>
+  <si>
     <t>Finnish Veikkausliiga</t>
   </si>
   <si>
-    <t>Irish Division 1</t>
-  </si>
-  <si>
-    <t>Irish Premier Division</t>
+    <t>Saudi Professional League</t>
+  </si>
+  <si>
+    <t>Austrian Bundesliga</t>
   </si>
   <si>
     <t>Italian Serie A</t>
   </si>
   <si>
-    <t>Austrian Bundesliga</t>
+    <t>Scottish Premiership</t>
+  </si>
+  <si>
+    <t>Portuguese Segunda Liga</t>
+  </si>
+  <si>
+    <t>Swedish Allsvenskan</t>
+  </si>
+  <si>
+    <t>Polish Ekstraklasa</t>
+  </si>
+  <si>
+    <t>Israeli Premier League</t>
+  </si>
+  <si>
+    <t>Norwegian Eliteserien</t>
   </si>
   <si>
     <t>Danish Superliga</t>
   </si>
   <si>
-    <t>Israeli Premier League</t>
-  </si>
-  <si>
-    <t>Norwegian Eliteserien</t>
-  </si>
-  <si>
-    <t>Polish Ekstraklasa</t>
+    <t>Spanish Segunda Division</t>
+  </si>
+  <si>
+    <t>Spanish La Liga</t>
+  </si>
+  <si>
+    <t>Portuguese Primeira Liga</t>
   </si>
   <si>
     <t>Argentinian Primera Division</t>
@@ -247,15 +271,27 @@
     <t>11:00:00</t>
   </si>
   <si>
+    <t>11:30:00</t>
+  </si>
+  <si>
     <t>13:00:00</t>
   </si>
   <si>
+    <t>13:10:00</t>
+  </si>
+  <si>
     <t>13:30:00</t>
   </si>
   <si>
     <t>14:00:00</t>
   </si>
   <si>
+    <t>14:30:00</t>
+  </si>
+  <si>
+    <t>15:00:00</t>
+  </si>
+  <si>
     <t>15:30:00</t>
   </si>
   <si>
@@ -265,6 +301,9 @@
     <t>16:00:00</t>
   </si>
   <si>
+    <t>16:15:00</t>
+  </si>
+  <si>
     <t>17:00:00</t>
   </si>
   <si>
@@ -283,64 +322,97 @@
     <t>Chelsea</t>
   </si>
   <si>
+    <t>Unirea Slobozia</t>
+  </si>
+  <si>
+    <t>Shamrock Rovers</t>
+  </si>
+  <si>
+    <t>Bohemians</t>
+  </si>
+  <si>
+    <t>Waterford</t>
+  </si>
+  <si>
+    <t>Derry City</t>
+  </si>
+  <si>
+    <t>Kerry FC</t>
+  </si>
+  <si>
+    <t>Sligo Rovers</t>
+  </si>
+  <si>
+    <t>Cobh Ramblers</t>
+  </si>
+  <si>
+    <t>Treaty United</t>
+  </si>
+  <si>
+    <t>Finn Harps</t>
+  </si>
+  <si>
     <t>HJK Helsinki</t>
   </si>
   <si>
-    <t>Finn Harps</t>
-  </si>
-  <si>
-    <t>Treaty United</t>
-  </si>
-  <si>
-    <t>Cobh Ramblers</t>
-  </si>
-  <si>
     <t>Longford</t>
   </si>
   <si>
-    <t>Kerry FC</t>
-  </si>
-  <si>
-    <t>Derry City</t>
-  </si>
-  <si>
-    <t>Waterford</t>
-  </si>
-  <si>
-    <t>Sligo Rovers</t>
-  </si>
-  <si>
-    <t>Bohemians</t>
-  </si>
-  <si>
-    <t>Shamrock Rovers</t>
+    <t>Al-Feiha</t>
+  </si>
+  <si>
+    <t>SCR Altach</t>
   </si>
   <si>
     <t>US Cremonese</t>
   </si>
   <si>
-    <t>SCR Altach</t>
+    <t>Hearts</t>
+  </si>
+  <si>
+    <t>Torreense</t>
+  </si>
+  <si>
+    <t>Halmstads</t>
+  </si>
+  <si>
+    <t>Djurgardens</t>
+  </si>
+  <si>
+    <t>Porto B</t>
+  </si>
+  <si>
+    <t>Radomiak Radom</t>
+  </si>
+  <si>
+    <t>Bnei Sakhnin</t>
+  </si>
+  <si>
+    <t>Maccabi Netanya</t>
+  </si>
+  <si>
+    <t>Bodo Glimt</t>
+  </si>
+  <si>
+    <t>Wadi Degla</t>
+  </si>
+  <si>
+    <t>Al Ittihad (EGY)</t>
   </si>
   <si>
     <t>Midtjylland</t>
   </si>
   <si>
-    <t>Al Ittihad (EGY)</t>
-  </si>
-  <si>
-    <t>Wadi Degla</t>
-  </si>
-  <si>
-    <t>Bnei Sakhnin</t>
-  </si>
-  <si>
-    <t>Maccabi Netanya</t>
-  </si>
-  <si>
-    <t>Bodo Glimt</t>
-  </si>
-  <si>
-    <t>Radomiak Radom</t>
+    <t>Rapid Bucharest</t>
+  </si>
+  <si>
+    <t>Al-Ittihad</t>
+  </si>
+  <si>
+    <t>Al-Ettifaq</t>
+  </si>
+  <si>
+    <t>Almeria</t>
   </si>
   <si>
     <t>LASK Linz</t>
@@ -352,6 +424,12 @@
     <t>Everton</t>
   </si>
   <si>
+    <t>Sevilla</t>
+  </si>
+  <si>
+    <t>Sporting Lisbon</t>
+  </si>
+  <si>
     <t>Gimnasia Mendoza</t>
   </si>
   <si>
@@ -373,64 +451,97 @@
     <t>Nottm Forest</t>
   </si>
   <si>
+    <t>Hermannstadt</t>
+  </si>
+  <si>
+    <t>Drogheda</t>
+  </si>
+  <si>
+    <t>Shelbourne</t>
+  </si>
+  <si>
+    <t>Dundalk</t>
+  </si>
+  <si>
+    <t>Galway Utd</t>
+  </si>
+  <si>
+    <t>Cork City</t>
+  </si>
+  <si>
+    <t>St Patricks</t>
+  </si>
+  <si>
+    <t>UCD</t>
+  </si>
+  <si>
+    <t>Wexford F.C</t>
+  </si>
+  <si>
+    <t>Bray Wanderers</t>
+  </si>
+  <si>
     <t>Lahti</t>
   </si>
   <si>
-    <t>Bray Wanderers</t>
-  </si>
-  <si>
-    <t>Wexford F.C</t>
-  </si>
-  <si>
-    <t>UCD</t>
-  </si>
-  <si>
     <t>Athlone Town</t>
   </si>
   <si>
-    <t>Cork City</t>
-  </si>
-  <si>
-    <t>Galway Utd</t>
-  </si>
-  <si>
-    <t>Dundalk</t>
-  </si>
-  <si>
-    <t>St Patricks</t>
-  </si>
-  <si>
-    <t>Shelbourne</t>
-  </si>
-  <si>
-    <t>Drogheda</t>
+    <t>Al Riyadh SC</t>
+  </si>
+  <si>
+    <t>RZ Pellets WAC</t>
   </si>
   <si>
     <t>Lazio</t>
   </si>
   <si>
-    <t>RZ Pellets WAC</t>
+    <t>Rangers</t>
+  </si>
+  <si>
+    <t>Penafiel</t>
+  </si>
+  <si>
+    <t>Brommapojkarna</t>
+  </si>
+  <si>
+    <t>IFK Goteborg</t>
+  </si>
+  <si>
+    <t>Felgueiras</t>
+  </si>
+  <si>
+    <t>Lechia Gdansk</t>
+  </si>
+  <si>
+    <t>Maccabi Bnei Raina</t>
+  </si>
+  <si>
+    <t>Hapoel Jerusalem</t>
+  </si>
+  <si>
+    <t>Molde</t>
+  </si>
+  <si>
+    <t>Kahraba Ismailia</t>
+  </si>
+  <si>
+    <t>Petrojet</t>
   </si>
   <si>
     <t>Viborg</t>
   </si>
   <si>
-    <t>Petrojet</t>
-  </si>
-  <si>
-    <t>Kahraba Ismailia</t>
-  </si>
-  <si>
-    <t>Maccabi Bnei Raina</t>
-  </si>
-  <si>
-    <t>Hapoel Jerusalem</t>
-  </si>
-  <si>
-    <t>Molde</t>
-  </si>
-  <si>
-    <t>Lechia Gdansk</t>
+    <t>CFR Cluj</t>
+  </si>
+  <si>
+    <t>Al-Kholood Club</t>
+  </si>
+  <si>
+    <t>Al Najma Club</t>
+  </si>
+  <si>
+    <t>Mirandes</t>
   </si>
   <si>
     <t>Rapid Vienna</t>
@@ -442,6 +553,12 @@
     <t>Man City</t>
   </si>
   <si>
+    <t>Real Sociedad</t>
+  </si>
+  <si>
+    <t>Guimaraes</t>
+  </si>
+  <si>
     <t>Defensa y Justicia</t>
   </si>
   <si>
@@ -457,7 +574,7 @@
     <t>Newells</t>
   </si>
   <si>
-    <t>2026-05-02 14:10:58</t>
+    <t>2026-05-02 16:41:25</t>
   </si>
 </sst>
 </file>
@@ -815,7 +932,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BH31"/>
+  <dimension ref="A1:BH44"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:60">
@@ -1005,16 +1122,16 @@
         <v>60</v>
       </c>
       <c r="B2" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="C2" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="D2" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="E2" t="s">
-        <v>117</v>
+        <v>143</v>
       </c>
       <c r="F2">
         <v>3.15</v>
@@ -1026,7 +1143,7 @@
         <v>2.58</v>
       </c>
       <c r="I2">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="J2">
         <v>2.74</v>
@@ -1065,7 +1182,7 @@
         <v>1.61</v>
       </c>
       <c r="V2">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="W2">
         <v>1.37</v>
@@ -1131,13 +1248,13 @@
         <v>5.9</v>
       </c>
       <c r="AR2">
-        <v>4.3</v>
+        <v>12</v>
       </c>
       <c r="AS2">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AT2">
-        <v>3.65</v>
+        <v>7.4</v>
       </c>
       <c r="AU2">
         <v>5.5</v>
@@ -1146,40 +1263,40 @@
         <v>10.5</v>
       </c>
       <c r="AW2">
+        <v>5.1</v>
+      </c>
+      <c r="AX2">
+        <v>16</v>
+      </c>
+      <c r="AY2">
+        <v>12</v>
+      </c>
+      <c r="AZ2">
+        <v>4.7</v>
+      </c>
+      <c r="BA2">
+        <v>5.3</v>
+      </c>
+      <c r="BB2">
+        <v>5.3</v>
+      </c>
+      <c r="BC2">
         <v>5.2</v>
       </c>
-      <c r="AX2">
-        <v>4.7</v>
-      </c>
-      <c r="AY2">
-        <v>4.3</v>
-      </c>
-      <c r="AZ2">
-        <v>4.8</v>
-      </c>
-      <c r="BA2">
+      <c r="BD2">
         <v>5.4</v>
       </c>
-      <c r="BB2">
-        <v>5.4</v>
-      </c>
-      <c r="BC2">
+      <c r="BE2">
+        <v>5.5</v>
+      </c>
+      <c r="BF2">
         <v>5.3</v>
       </c>
-      <c r="BD2">
-        <v>5.5</v>
-      </c>
-      <c r="BE2">
-        <v>3.25</v>
-      </c>
-      <c r="BF2">
-        <v>5.4</v>
-      </c>
       <c r="BG2">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BH2" t="s">
-        <v>147</v>
+        <v>186</v>
       </c>
     </row>
     <row r="3" spans="1:60">
@@ -1187,22 +1304,22 @@
         <v>61</v>
       </c>
       <c r="B3" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="C3" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="D3" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="E3" t="s">
-        <v>118</v>
+        <v>144</v>
       </c>
       <c r="F3">
+        <v>1.71</v>
+      </c>
+      <c r="G3">
         <v>1.72</v>
-      </c>
-      <c r="G3">
-        <v>1.73</v>
       </c>
       <c r="H3">
         <v>5.3</v>
@@ -1247,10 +1364,10 @@
         <v>2.26</v>
       </c>
       <c r="V3">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="W3">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="X3">
         <v>19</v>
@@ -1262,7 +1379,7 @@
         <v>42</v>
       </c>
       <c r="AA3">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AB3">
         <v>10.5</v>
@@ -1295,7 +1412,7 @@
         <v>16</v>
       </c>
       <c r="AL3">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AM3">
         <v>85</v>
@@ -1313,7 +1430,7 @@
         <v>20</v>
       </c>
       <c r="AR3">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AS3">
         <v>95</v>
@@ -1325,7 +1442,7 @@
         <v>9</v>
       </c>
       <c r="AV3">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AW3">
         <v>50</v>
@@ -1340,7 +1457,7 @@
         <v>17</v>
       </c>
       <c r="BA3">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BB3">
         <v>16.5</v>
@@ -1352,7 +1469,7 @@
         <v>27</v>
       </c>
       <c r="BE3">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="BF3">
         <v>8</v>
@@ -1361,7 +1478,7 @@
         <v>50</v>
       </c>
       <c r="BH3" t="s">
-        <v>147</v>
+        <v>186</v>
       </c>
     </row>
     <row r="4" spans="1:60">
@@ -1369,181 +1486,181 @@
         <v>62</v>
       </c>
       <c r="B4" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="C4" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="D4" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="E4" t="s">
-        <v>119</v>
+        <v>145</v>
       </c>
       <c r="F4">
-        <v>1.48</v>
+        <v>3.75</v>
       </c>
       <c r="G4">
-        <v>1.57</v>
+        <v>4.6</v>
       </c>
       <c r="H4">
-        <v>6.4</v>
+        <v>2.08</v>
       </c>
       <c r="I4">
-        <v>8.6</v>
+        <v>2.32</v>
       </c>
       <c r="J4">
-        <v>4.6</v>
+        <v>3.15</v>
       </c>
       <c r="K4">
-        <v>5.3</v>
+        <v>3.6</v>
       </c>
       <c r="L4">
+        <v>1.01</v>
+      </c>
+      <c r="M4">
+        <v>1.09</v>
+      </c>
+      <c r="N4">
+        <v>2.98</v>
+      </c>
+      <c r="O4">
+        <v>1.4</v>
+      </c>
+      <c r="P4">
+        <v>1.67</v>
+      </c>
+      <c r="Q4">
+        <v>2.06</v>
+      </c>
+      <c r="R4">
+        <v>1.25</v>
+      </c>
+      <c r="S4">
+        <v>4.1</v>
+      </c>
+      <c r="T4">
+        <v>1.77</v>
+      </c>
+      <c r="U4">
+        <v>1.76</v>
+      </c>
+      <c r="V4">
+        <v>1.75</v>
+      </c>
+      <c r="W4">
         <v>1.28</v>
       </c>
-      <c r="M4">
-        <v>1.04</v>
-      </c>
-      <c r="N4">
-        <v>4.8</v>
-      </c>
-      <c r="O4">
-        <v>1.22</v>
-      </c>
-      <c r="P4">
-        <v>2.26</v>
-      </c>
-      <c r="Q4">
-        <v>1.64</v>
-      </c>
-      <c r="R4">
-        <v>1.5</v>
-      </c>
-      <c r="S4">
-        <v>2.46</v>
-      </c>
-      <c r="T4">
-        <v>1.69</v>
-      </c>
-      <c r="U4">
-        <v>1.86</v>
-      </c>
-      <c r="V4">
-        <v>1.14</v>
-      </c>
-      <c r="W4">
-        <v>2.74</v>
-      </c>
       <c r="X4">
-        <v>26</v>
+        <v>13.5</v>
       </c>
       <c r="Y4">
-        <v>34</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z4">
-        <v>65</v>
+        <v>16</v>
       </c>
       <c r="AA4">
-        <v>240</v>
+        <v>36</v>
       </c>
       <c r="AB4">
-        <v>10.5</v>
+        <v>15</v>
       </c>
       <c r="AC4">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD4">
         <v>13.5</v>
       </c>
-      <c r="AD4">
-        <v>34</v>
-      </c>
       <c r="AE4">
-        <v>120</v>
+        <v>32</v>
       </c>
       <c r="AF4">
+        <v>36</v>
+      </c>
+      <c r="AG4">
+        <v>21</v>
+      </c>
+      <c r="AH4">
+        <v>25</v>
+      </c>
+      <c r="AI4">
+        <v>70</v>
+      </c>
+      <c r="AJ4">
+        <v>110</v>
+      </c>
+      <c r="AK4">
+        <v>70</v>
+      </c>
+      <c r="AL4">
+        <v>85</v>
+      </c>
+      <c r="AM4">
+        <v>170</v>
+      </c>
+      <c r="AN4">
+        <v>90</v>
+      </c>
+      <c r="AO4">
+        <v>28</v>
+      </c>
+      <c r="AP4">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AQ4">
+        <v>6</v>
+      </c>
+      <c r="AR4">
+        <v>9.6</v>
+      </c>
+      <c r="AS4">
+        <v>3.85</v>
+      </c>
+      <c r="AT4">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU4">
+        <v>5.7</v>
+      </c>
+      <c r="AV4">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AW4">
+        <v>3.8</v>
+      </c>
+      <c r="AX4">
+        <v>3.85</v>
+      </c>
+      <c r="AY4">
         <v>12</v>
       </c>
-      <c r="AG4">
-        <v>11</v>
-      </c>
-      <c r="AH4">
-        <v>27</v>
-      </c>
-      <c r="AI4">
-        <v>100</v>
-      </c>
-      <c r="AJ4">
-        <v>15</v>
-      </c>
-      <c r="AK4">
-        <v>18.5</v>
-      </c>
-      <c r="AL4">
-        <v>34</v>
-      </c>
-      <c r="AM4">
-        <v>130</v>
-      </c>
-      <c r="AN4">
-        <v>8</v>
-      </c>
-      <c r="AO4">
-        <v>130</v>
-      </c>
-      <c r="AP4">
-        <v>15.5</v>
-      </c>
-      <c r="AQ4">
-        <v>19</v>
-      </c>
-      <c r="AR4">
-        <v>4.7</v>
-      </c>
-      <c r="AS4">
-        <v>5</v>
-      </c>
-      <c r="AT4">
-        <v>8.6</v>
-      </c>
-      <c r="AU4">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV4">
-        <v>4.4</v>
-      </c>
-      <c r="AW4">
-        <v>4.9</v>
-      </c>
-      <c r="AX4">
-        <v>8.6</v>
-      </c>
-      <c r="AY4">
-        <v>8.6</v>
-      </c>
       <c r="AZ4">
-        <v>18</v>
+        <v>14.5</v>
       </c>
       <c r="BA4">
-        <v>4.9</v>
+        <v>4</v>
       </c>
       <c r="BB4">
-        <v>11.5</v>
+        <v>4.2</v>
       </c>
       <c r="BC4">
-        <v>13</v>
+        <v>4.1</v>
       </c>
       <c r="BD4">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="BE4">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="BF4">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="BG4">
-        <v>4.9</v>
+        <v>3.75</v>
       </c>
       <c r="BH4" t="s">
-        <v>147</v>
+        <v>186</v>
       </c>
     </row>
     <row r="5" spans="1:60">
@@ -1551,181 +1668,181 @@
         <v>63</v>
       </c>
       <c r="B5" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="C5" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="D5" t="s">
+        <v>103</v>
+      </c>
+      <c r="E5" t="s">
+        <v>146</v>
+      </c>
+      <c r="F5">
+        <v>1.48</v>
+      </c>
+      <c r="G5">
+        <v>1.62</v>
+      </c>
+      <c r="H5">
+        <v>7.6</v>
+      </c>
+      <c r="I5">
+        <v>11</v>
+      </c>
+      <c r="J5">
+        <v>3.7</v>
+      </c>
+      <c r="K5">
+        <v>5.2</v>
+      </c>
+      <c r="L5">
+        <v>1.01</v>
+      </c>
+      <c r="M5">
+        <v>1.07</v>
+      </c>
+      <c r="N5">
+        <v>3.5</v>
+      </c>
+      <c r="O5">
+        <v>1.33</v>
+      </c>
+      <c r="P5">
+        <v>1.85</v>
+      </c>
+      <c r="Q5">
+        <v>1.97</v>
+      </c>
+      <c r="R5">
+        <v>1.31</v>
+      </c>
+      <c r="S5">
+        <v>3.5</v>
+      </c>
+      <c r="T5">
+        <v>1.93</v>
+      </c>
+      <c r="U5">
+        <v>1.63</v>
+      </c>
+      <c r="V5">
+        <v>1.11</v>
+      </c>
+      <c r="W5">
+        <v>2.6</v>
+      </c>
+      <c r="X5">
+        <v>17</v>
+      </c>
+      <c r="Y5">
+        <v>28</v>
+      </c>
+      <c r="Z5">
         <v>90</v>
       </c>
-      <c r="E5" t="s">
-        <v>120</v>
-      </c>
-      <c r="F5">
-        <v>2.88</v>
-      </c>
-      <c r="G5">
-        <v>3.9</v>
-      </c>
-      <c r="H5">
-        <v>2.06</v>
-      </c>
-      <c r="I5">
-        <v>2.66</v>
-      </c>
-      <c r="J5">
-        <v>3.3</v>
-      </c>
-      <c r="K5">
+      <c r="AA5">
+        <v>1000</v>
+      </c>
+      <c r="AB5">
+        <v>8.6</v>
+      </c>
+      <c r="AC5">
+        <v>12</v>
+      </c>
+      <c r="AD5">
+        <v>38</v>
+      </c>
+      <c r="AE5">
+        <v>180</v>
+      </c>
+      <c r="AF5">
+        <v>10</v>
+      </c>
+      <c r="AG5">
+        <v>12.5</v>
+      </c>
+      <c r="AH5">
+        <v>34</v>
+      </c>
+      <c r="AI5">
+        <v>170</v>
+      </c>
+      <c r="AJ5">
+        <v>16.5</v>
+      </c>
+      <c r="AK5">
+        <v>22</v>
+      </c>
+      <c r="AL5">
+        <v>55</v>
+      </c>
+      <c r="AM5">
+        <v>230</v>
+      </c>
+      <c r="AN5">
+        <v>11.5</v>
+      </c>
+      <c r="AO5">
+        <v>1000</v>
+      </c>
+      <c r="AP5">
+        <v>3.5</v>
+      </c>
+      <c r="AQ5">
+        <v>16.5</v>
+      </c>
+      <c r="AR5">
+        <v>4.2</v>
+      </c>
+      <c r="AS5">
+        <v>4.3</v>
+      </c>
+      <c r="AT5">
         <v>6</v>
       </c>
-      <c r="L5">
-        <v>1.01</v>
-      </c>
-      <c r="M5">
-        <v>1.01</v>
-      </c>
-      <c r="N5">
-        <v>1.8</v>
-      </c>
-      <c r="O5">
-        <v>1.27</v>
-      </c>
-      <c r="P5">
-        <v>1.8</v>
-      </c>
-      <c r="Q5">
-        <v>1.73</v>
-      </c>
-      <c r="R5">
-        <v>1.3</v>
-      </c>
-      <c r="S5">
-        <v>2.8</v>
-      </c>
-      <c r="T5">
-        <v>1.01</v>
-      </c>
-      <c r="U5">
-        <v>1.01</v>
-      </c>
-      <c r="V5">
-        <v>1.6</v>
-      </c>
-      <c r="W5">
-        <v>1.35</v>
-      </c>
-      <c r="X5">
-        <v>1000</v>
-      </c>
-      <c r="Y5">
-        <v>1000</v>
-      </c>
-      <c r="Z5">
-        <v>1000</v>
-      </c>
-      <c r="AA5">
-        <v>1000</v>
-      </c>
-      <c r="AB5">
-        <v>1000</v>
-      </c>
-      <c r="AC5">
-        <v>1000</v>
-      </c>
-      <c r="AD5">
-        <v>1000</v>
-      </c>
-      <c r="AE5">
-        <v>1000</v>
-      </c>
-      <c r="AF5">
-        <v>1000</v>
-      </c>
-      <c r="AG5">
-        <v>1000</v>
-      </c>
-      <c r="AH5">
-        <v>1000</v>
-      </c>
-      <c r="AI5">
-        <v>1000</v>
-      </c>
-      <c r="AJ5">
-        <v>1000</v>
-      </c>
-      <c r="AK5">
-        <v>1000</v>
-      </c>
-      <c r="AL5">
-        <v>1000</v>
-      </c>
-      <c r="AM5">
-        <v>1000</v>
-      </c>
-      <c r="AN5">
-        <v>1000</v>
-      </c>
-      <c r="AO5">
-        <v>1000</v>
-      </c>
-      <c r="AP5">
-        <v>11</v>
-      </c>
-      <c r="AQ5">
-        <v>8</v>
-      </c>
-      <c r="AR5">
-        <v>11.5</v>
-      </c>
-      <c r="AS5">
-        <v>21</v>
-      </c>
-      <c r="AT5">
-        <v>9.800000000000001</v>
-      </c>
       <c r="AU5">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV5">
-        <v>8.4</v>
+        <v>3.95</v>
       </c>
       <c r="AW5">
-        <v>18</v>
+        <v>4.3</v>
       </c>
       <c r="AX5">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="AY5">
+        <v>3.25</v>
+      </c>
+      <c r="AZ5">
+        <v>19.5</v>
+      </c>
+      <c r="BA5">
+        <v>4.3</v>
+      </c>
+      <c r="BB5">
         <v>10</v>
       </c>
-      <c r="AZ5">
-        <v>12.5</v>
-      </c>
-      <c r="BA5">
-        <v>26</v>
-      </c>
-      <c r="BB5">
-        <v>1.01</v>
-      </c>
       <c r="BC5">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BD5">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BE5">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BF5">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="BG5">
-        <v>13.5</v>
+        <v>4.3</v>
       </c>
       <c r="BH5" t="s">
-        <v>147</v>
+        <v>186</v>
       </c>
     </row>
     <row r="6" spans="1:60">
@@ -1733,181 +1850,181 @@
         <v>63</v>
       </c>
       <c r="B6" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="C6" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="D6" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="E6" t="s">
-        <v>121</v>
+        <v>147</v>
       </c>
       <c r="F6">
-        <v>2.88</v>
+        <v>2.04</v>
       </c>
       <c r="G6">
+        <v>2.28</v>
+      </c>
+      <c r="H6">
+        <v>3.75</v>
+      </c>
+      <c r="I6">
         <v>4.6</v>
       </c>
-      <c r="H6">
-        <v>1.97</v>
-      </c>
-      <c r="I6">
-        <v>2.72</v>
-      </c>
       <c r="J6">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="K6">
-        <v>7</v>
+        <v>3.7</v>
       </c>
       <c r="L6">
         <v>1.01</v>
       </c>
       <c r="M6">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N6">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="O6">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="P6">
-        <v>1.27</v>
+        <v>1.73</v>
       </c>
       <c r="Q6">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="R6">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="S6">
-        <v>2.92</v>
+        <v>3.85</v>
       </c>
       <c r="T6">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="U6">
-        <v>1.01</v>
+        <v>1.95</v>
       </c>
       <c r="V6">
-        <v>1.58</v>
+        <v>1.29</v>
       </c>
       <c r="W6">
-        <v>1.28</v>
+        <v>1.78</v>
       </c>
       <c r="X6">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y6">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Z6">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AA6">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AB6">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC6">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AD6">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AE6">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF6">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AG6">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AH6">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI6">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ6">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AK6">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AL6">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM6">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN6">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AO6">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AP6">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AQ6">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AR6">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AS6">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT6">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AU6">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AV6">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AW6">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AX6">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AY6">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AZ6">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BA6">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BB6">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BC6">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BD6">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BE6">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BF6">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BG6">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BH6" t="s">
-        <v>147</v>
+        <v>186</v>
       </c>
     </row>
     <row r="7" spans="1:60">
@@ -1915,58 +2032,58 @@
         <v>63</v>
       </c>
       <c r="B7" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="C7" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="D7" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="E7" t="s">
-        <v>122</v>
+        <v>148</v>
       </c>
       <c r="F7">
-        <v>2.26</v>
+        <v>4.7</v>
       </c>
       <c r="G7">
-        <v>3.2</v>
+        <v>110</v>
       </c>
       <c r="H7">
-        <v>2.4</v>
+        <v>1.63</v>
       </c>
       <c r="I7">
-        <v>3.45</v>
+        <v>1.9</v>
       </c>
       <c r="J7">
-        <v>2.5</v>
+        <v>2.14</v>
       </c>
       <c r="K7">
-        <v>7.2</v>
+        <v>110</v>
       </c>
       <c r="L7">
         <v>1.01</v>
       </c>
       <c r="M7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N7">
-        <v>1.24</v>
+        <v>1.45</v>
       </c>
       <c r="O7">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="P7">
-        <v>1.24</v>
+        <v>1.45</v>
       </c>
       <c r="Q7">
-        <v>1.66</v>
+        <v>1.52</v>
       </c>
       <c r="R7">
-        <v>1.2</v>
+        <v>1.45</v>
       </c>
       <c r="S7">
-        <v>2.66</v>
+        <v>2.3</v>
       </c>
       <c r="T7">
         <v>1.01</v>
@@ -1975,10 +2092,10 @@
         <v>1.01</v>
       </c>
       <c r="V7">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="W7">
-        <v>1.45</v>
+        <v>1.01</v>
       </c>
       <c r="X7">
         <v>1000</v>
@@ -2035,52 +2152,52 @@
         <v>1000</v>
       </c>
       <c r="AP7">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="AQ7">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR7">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AS7">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AT7">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AU7">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AV7">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AW7">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AX7">
-        <v>1.01</v>
+        <v>28</v>
       </c>
       <c r="AY7">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AZ7">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BA7">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BB7">
-        <v>1.01</v>
+        <v>40</v>
       </c>
       <c r="BC7">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="BD7">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="BE7">
-        <v>1.01</v>
+        <v>40</v>
       </c>
       <c r="BF7">
         <v>1.01</v>
@@ -2089,7 +2206,7 @@
         <v>1.01</v>
       </c>
       <c r="BH7" t="s">
-        <v>147</v>
+        <v>186</v>
       </c>
     </row>
     <row r="8" spans="1:60">
@@ -2097,172 +2214,172 @@
         <v>63</v>
       </c>
       <c r="B8" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="C8" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="D8" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="E8" t="s">
-        <v>123</v>
+        <v>149</v>
       </c>
       <c r="F8">
-        <v>1.89</v>
+        <v>1.2</v>
       </c>
       <c r="G8">
-        <v>2.54</v>
+        <v>2.14</v>
       </c>
       <c r="H8">
+        <v>1.09</v>
+      </c>
+      <c r="I8">
+        <v>6.2</v>
+      </c>
+      <c r="J8">
+        <v>3.6</v>
+      </c>
+      <c r="K8">
+        <v>110</v>
+      </c>
+      <c r="L8">
+        <v>1.01</v>
+      </c>
+      <c r="M8">
+        <v>1.01</v>
+      </c>
+      <c r="N8">
+        <v>1.71</v>
+      </c>
+      <c r="O8">
+        <v>1.32</v>
+      </c>
+      <c r="P8">
+        <v>1.71</v>
+      </c>
+      <c r="Q8">
+        <v>1.32</v>
+      </c>
+      <c r="R8">
+        <v>1.26</v>
+      </c>
+      <c r="S8">
         <v>3.1</v>
       </c>
-      <c r="I8">
-        <v>4.8</v>
-      </c>
-      <c r="J8">
-        <v>3.1</v>
-      </c>
-      <c r="K8">
+      <c r="T8">
+        <v>1.01</v>
+      </c>
+      <c r="U8">
+        <v>1.01</v>
+      </c>
+      <c r="V8">
+        <v>1.19</v>
+      </c>
+      <c r="W8">
+        <v>1.87</v>
+      </c>
+      <c r="X8">
+        <v>1000</v>
+      </c>
+      <c r="Y8">
+        <v>1000</v>
+      </c>
+      <c r="Z8">
+        <v>1000</v>
+      </c>
+      <c r="AA8">
+        <v>1000</v>
+      </c>
+      <c r="AB8">
+        <v>1000</v>
+      </c>
+      <c r="AC8">
+        <v>1000</v>
+      </c>
+      <c r="AD8">
+        <v>1000</v>
+      </c>
+      <c r="AE8">
+        <v>1000</v>
+      </c>
+      <c r="AF8">
+        <v>1000</v>
+      </c>
+      <c r="AG8">
+        <v>1000</v>
+      </c>
+      <c r="AH8">
+        <v>1000</v>
+      </c>
+      <c r="AI8">
+        <v>1000</v>
+      </c>
+      <c r="AJ8">
+        <v>1000</v>
+      </c>
+      <c r="AK8">
+        <v>1000</v>
+      </c>
+      <c r="AL8">
+        <v>1000</v>
+      </c>
+      <c r="AM8">
+        <v>1000</v>
+      </c>
+      <c r="AN8">
+        <v>1000</v>
+      </c>
+      <c r="AO8">
+        <v>1000</v>
+      </c>
+      <c r="AP8">
+        <v>10.5</v>
+      </c>
+      <c r="AQ8">
+        <v>11.5</v>
+      </c>
+      <c r="AR8">
+        <v>24</v>
+      </c>
+      <c r="AS8">
+        <v>40</v>
+      </c>
+      <c r="AT8">
+        <v>6.6</v>
+      </c>
+      <c r="AU8">
         <v>6.8</v>
       </c>
-      <c r="L8">
-        <v>1.01</v>
-      </c>
-      <c r="M8">
-        <v>1.01</v>
-      </c>
-      <c r="N8">
-        <v>1.81</v>
-      </c>
-      <c r="O8">
-        <v>1.28</v>
-      </c>
-      <c r="P8">
-        <v>1.81</v>
-      </c>
-      <c r="Q8">
-        <v>1.83</v>
-      </c>
-      <c r="R8">
-        <v>1.31</v>
-      </c>
-      <c r="S8">
-        <v>2.7</v>
-      </c>
-      <c r="T8">
-        <v>1.01</v>
-      </c>
-      <c r="U8">
-        <v>1.01</v>
-      </c>
-      <c r="V8">
-        <v>1.26</v>
-      </c>
-      <c r="W8">
-        <v>1.64</v>
-      </c>
-      <c r="X8">
-        <v>1000</v>
-      </c>
-      <c r="Y8">
-        <v>1000</v>
-      </c>
-      <c r="Z8">
-        <v>1000</v>
-      </c>
-      <c r="AA8">
-        <v>1000</v>
-      </c>
-      <c r="AB8">
-        <v>1000</v>
-      </c>
-      <c r="AC8">
-        <v>1000</v>
-      </c>
-      <c r="AD8">
-        <v>1000</v>
-      </c>
-      <c r="AE8">
-        <v>1000</v>
-      </c>
-      <c r="AF8">
-        <v>1000</v>
-      </c>
-      <c r="AG8">
-        <v>1000</v>
-      </c>
-      <c r="AH8">
-        <v>1000</v>
-      </c>
-      <c r="AI8">
-        <v>1000</v>
-      </c>
-      <c r="AJ8">
-        <v>1000</v>
-      </c>
-      <c r="AK8">
-        <v>1000</v>
-      </c>
-      <c r="AL8">
-        <v>1000</v>
-      </c>
-      <c r="AM8">
-        <v>1000</v>
-      </c>
-      <c r="AN8">
-        <v>1000</v>
-      </c>
-      <c r="AO8">
-        <v>1000</v>
-      </c>
-      <c r="AP8">
-        <v>1.01</v>
-      </c>
-      <c r="AQ8">
-        <v>1.01</v>
-      </c>
-      <c r="AR8">
-        <v>1.01</v>
-      </c>
-      <c r="AS8">
-        <v>1.01</v>
-      </c>
-      <c r="AT8">
-        <v>1.01</v>
-      </c>
-      <c r="AU8">
-        <v>1.01</v>
-      </c>
       <c r="AV8">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AW8">
-        <v>1.01</v>
+        <v>40</v>
       </c>
       <c r="AX8">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AY8">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AZ8">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BA8">
-        <v>1.01</v>
+        <v>40</v>
       </c>
       <c r="BB8">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BC8">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BD8">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="BE8">
-        <v>1.01</v>
+        <v>40</v>
       </c>
       <c r="BF8">
         <v>1.01</v>
@@ -2271,24 +2388,24 @@
         <v>1.01</v>
       </c>
       <c r="BH8" t="s">
-        <v>147</v>
+        <v>186</v>
       </c>
     </row>
     <row r="9" spans="1:60">
       <c r="A9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B9" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="C9" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="D9" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="E9" t="s">
-        <v>124</v>
+        <v>150</v>
       </c>
       <c r="F9">
         <v>5.7</v>
@@ -2453,66 +2570,66 @@
         <v>1.01</v>
       </c>
       <c r="BH9" t="s">
-        <v>147</v>
+        <v>186</v>
       </c>
     </row>
     <row r="10" spans="1:60">
       <c r="A10" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B10" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="C10" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="D10" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="E10" t="s">
-        <v>125</v>
+        <v>151</v>
       </c>
       <c r="F10">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="G10">
-        <v>2.14</v>
+        <v>430</v>
       </c>
       <c r="H10">
-        <v>1.91</v>
+        <v>1.04</v>
       </c>
       <c r="I10">
-        <v>6.2</v>
+        <v>1.95</v>
       </c>
       <c r="J10">
-        <v>2.68</v>
+        <v>1.09</v>
       </c>
       <c r="K10">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="L10">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="M10">
         <v>1.01</v>
       </c>
       <c r="N10">
-        <v>1.71</v>
+        <v>3.3</v>
       </c>
       <c r="O10">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="P10">
-        <v>1.71</v>
+        <v>1.25</v>
       </c>
       <c r="Q10">
-        <v>1.32</v>
+        <v>1.85</v>
       </c>
       <c r="R10">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S10">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="T10">
         <v>1.01</v>
@@ -2521,10 +2638,10 @@
         <v>1.01</v>
       </c>
       <c r="V10">
-        <v>1.19</v>
+        <v>2.04</v>
       </c>
       <c r="W10">
-        <v>1.87</v>
+        <v>1.01</v>
       </c>
       <c r="X10">
         <v>1000</v>
@@ -2584,46 +2701,46 @@
         <v>10.5</v>
       </c>
       <c r="AQ10">
-        <v>11.5</v>
+        <v>6.4</v>
       </c>
       <c r="AR10">
-        <v>24</v>
+        <v>7.6</v>
       </c>
       <c r="AS10">
+        <v>12.5</v>
+      </c>
+      <c r="AT10">
+        <v>13</v>
+      </c>
+      <c r="AU10">
+        <v>7.2</v>
+      </c>
+      <c r="AV10">
+        <v>8.6</v>
+      </c>
+      <c r="AW10">
+        <v>14</v>
+      </c>
+      <c r="AX10">
+        <v>27</v>
+      </c>
+      <c r="AY10">
+        <v>17</v>
+      </c>
+      <c r="AZ10">
+        <v>17.5</v>
+      </c>
+      <c r="BA10">
+        <v>27</v>
+      </c>
+      <c r="BB10">
         <v>40</v>
       </c>
-      <c r="AT10">
-        <v>6.6</v>
-      </c>
-      <c r="AU10">
-        <v>6.8</v>
-      </c>
-      <c r="AV10">
-        <v>14.5</v>
-      </c>
-      <c r="AW10">
+      <c r="BC10">
         <v>40</v>
       </c>
-      <c r="AX10">
-        <v>8.6</v>
-      </c>
-      <c r="AY10">
-        <v>8.6</v>
-      </c>
-      <c r="AZ10">
-        <v>16.5</v>
-      </c>
-      <c r="BA10">
+      <c r="BD10">
         <v>40</v>
-      </c>
-      <c r="BB10">
-        <v>15</v>
-      </c>
-      <c r="BC10">
-        <v>15.5</v>
-      </c>
-      <c r="BD10">
-        <v>26</v>
       </c>
       <c r="BE10">
         <v>40</v>
@@ -2635,7 +2752,7 @@
         <v>1.01</v>
       </c>
       <c r="BH10" t="s">
-        <v>147</v>
+        <v>186</v>
       </c>
     </row>
     <row r="11" spans="1:60">
@@ -2643,71 +2760,71 @@
         <v>64</v>
       </c>
       <c r="B11" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="C11" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="D11" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="E11" t="s">
-        <v>126</v>
+        <v>152</v>
       </c>
       <c r="F11">
-        <v>2.16</v>
+        <v>2.26</v>
       </c>
       <c r="G11">
-        <v>100</v>
+        <v>3.2</v>
       </c>
       <c r="H11">
-        <v>1.63</v>
+        <v>2.4</v>
       </c>
       <c r="I11">
-        <v>1.9</v>
+        <v>3.45</v>
       </c>
       <c r="J11">
-        <v>2.14</v>
+        <v>3.15</v>
       </c>
       <c r="K11">
-        <v>85</v>
+        <v>7.2</v>
       </c>
       <c r="L11">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="M11">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="N11">
+        <v>1.25</v>
+      </c>
+      <c r="O11">
+        <v>1.25</v>
+      </c>
+      <c r="P11">
+        <v>1.24</v>
+      </c>
+      <c r="Q11">
+        <v>1.66</v>
+      </c>
+      <c r="R11">
+        <v>1.2</v>
+      </c>
+      <c r="S11">
+        <v>2.66</v>
+      </c>
+      <c r="T11">
+        <v>1.01</v>
+      </c>
+      <c r="U11">
+        <v>1.01</v>
+      </c>
+      <c r="V11">
+        <v>1.4</v>
+      </c>
+      <c r="W11">
         <v>1.45</v>
       </c>
-      <c r="O11">
-        <v>1.18</v>
-      </c>
-      <c r="P11">
-        <v>1.45</v>
-      </c>
-      <c r="Q11">
-        <v>1.52</v>
-      </c>
-      <c r="R11">
-        <v>1.44</v>
-      </c>
-      <c r="S11">
-        <v>2.3</v>
-      </c>
-      <c r="T11">
-        <v>1.01</v>
-      </c>
-      <c r="U11">
-        <v>1.01</v>
-      </c>
-      <c r="V11">
-        <v>2.1</v>
-      </c>
-      <c r="W11">
-        <v>1.01</v>
-      </c>
       <c r="X11">
         <v>1000</v>
       </c>
@@ -2763,52 +2880,52 @@
         <v>1000</v>
       </c>
       <c r="AP11">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="AQ11">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AR11">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AS11">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AT11">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU11">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV11">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AW11">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AX11">
-        <v>28</v>
+        <v>1.01</v>
       </c>
       <c r="AY11">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AZ11">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA11">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BB11">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BC11">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="BD11">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="BE11">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BF11">
         <v>1.01</v>
@@ -2817,7 +2934,7 @@
         <v>1.01</v>
       </c>
       <c r="BH11" t="s">
-        <v>147</v>
+        <v>186</v>
       </c>
     </row>
     <row r="12" spans="1:60">
@@ -2825,58 +2942,58 @@
         <v>64</v>
       </c>
       <c r="B12" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="C12" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="D12" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="E12" t="s">
-        <v>127</v>
+        <v>153</v>
       </c>
       <c r="F12">
-        <v>2.1</v>
+        <v>2.88</v>
       </c>
       <c r="G12">
-        <v>430</v>
+        <v>4.6</v>
       </c>
       <c r="H12">
-        <v>1.04</v>
+        <v>1.97</v>
       </c>
       <c r="I12">
-        <v>1.95</v>
+        <v>2.72</v>
       </c>
       <c r="J12">
-        <v>2.06</v>
+        <v>3.1</v>
       </c>
       <c r="K12">
-        <v>85</v>
+        <v>7</v>
       </c>
       <c r="L12">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="M12">
         <v>1.01</v>
       </c>
       <c r="N12">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="O12">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P12">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="Q12">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="R12">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S12">
-        <v>3.15</v>
+        <v>2.92</v>
       </c>
       <c r="T12">
         <v>1.01</v>
@@ -2885,10 +3002,10 @@
         <v>1.01</v>
       </c>
       <c r="V12">
-        <v>2.04</v>
+        <v>1.58</v>
       </c>
       <c r="W12">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="X12">
         <v>1000</v>
@@ -2945,52 +3062,52 @@
         <v>1000</v>
       </c>
       <c r="AP12">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ12">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AR12">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AS12">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AT12">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AU12">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV12">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AW12">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AX12">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="AY12">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="AZ12">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA12">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="BB12">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BC12">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BD12">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BE12">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BF12">
         <v>1.01</v>
@@ -2999,7 +3116,7 @@
         <v>1.01</v>
       </c>
       <c r="BH12" t="s">
-        <v>147</v>
+        <v>186</v>
       </c>
     </row>
     <row r="13" spans="1:60">
@@ -3007,545 +3124,545 @@
         <v>64</v>
       </c>
       <c r="B13" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="C13" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="D13" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="E13" t="s">
-        <v>128</v>
+        <v>154</v>
       </c>
       <c r="F13">
-        <v>2.04</v>
+        <v>3.2</v>
       </c>
       <c r="G13">
-        <v>2.28</v>
+        <v>3.8</v>
       </c>
       <c r="H13">
-        <v>3.75</v>
+        <v>2.14</v>
       </c>
       <c r="I13">
-        <v>4.6</v>
+        <v>2.58</v>
       </c>
       <c r="J13">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K13">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="L13">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="M13">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N13">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="O13">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="P13">
-        <v>1.73</v>
+        <v>1.94</v>
       </c>
       <c r="Q13">
-        <v>2.1</v>
+        <v>1.74</v>
       </c>
       <c r="R13">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="S13">
-        <v>3.85</v>
+        <v>3.1</v>
       </c>
       <c r="T13">
-        <v>1.87</v>
+        <v>1.7</v>
       </c>
       <c r="U13">
-        <v>1.95</v>
+        <v>2.14</v>
       </c>
       <c r="V13">
-        <v>1.29</v>
+        <v>1.63</v>
       </c>
       <c r="W13">
-        <v>1.78</v>
+        <v>1.36</v>
       </c>
       <c r="X13">
-        <v>12.5</v>
+        <v>19</v>
       </c>
       <c r="Y13">
+        <v>13</v>
+      </c>
+      <c r="Z13">
+        <v>18.5</v>
+      </c>
+      <c r="AA13">
+        <v>36</v>
+      </c>
+      <c r="AB13">
+        <v>17</v>
+      </c>
+      <c r="AC13">
+        <v>10</v>
+      </c>
+      <c r="AD13">
         <v>13.5</v>
       </c>
-      <c r="Z13">
-        <v>30</v>
-      </c>
-      <c r="AA13">
-        <v>100</v>
-      </c>
-      <c r="AB13">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AC13">
-        <v>8</v>
-      </c>
-      <c r="AD13">
-        <v>17.5</v>
-      </c>
       <c r="AE13">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="AF13">
-        <v>13.5</v>
+        <v>32</v>
       </c>
       <c r="AG13">
-        <v>11.5</v>
+        <v>18</v>
       </c>
       <c r="AH13">
         <v>21</v>
       </c>
       <c r="AI13">
-        <v>70</v>
+        <v>44</v>
       </c>
       <c r="AJ13">
-        <v>28</v>
+        <v>75</v>
       </c>
       <c r="AK13">
+        <v>48</v>
+      </c>
+      <c r="AL13">
+        <v>60</v>
+      </c>
+      <c r="AM13">
+        <v>110</v>
+      </c>
+      <c r="AN13">
+        <v>44</v>
+      </c>
+      <c r="AO13">
+        <v>21</v>
+      </c>
+      <c r="AP13">
+        <v>11</v>
+      </c>
+      <c r="AQ13">
+        <v>8</v>
+      </c>
+      <c r="AR13">
+        <v>11.5</v>
+      </c>
+      <c r="AS13">
+        <v>21</v>
+      </c>
+      <c r="AT13">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU13">
+        <v>6.2</v>
+      </c>
+      <c r="AV13">
+        <v>8.4</v>
+      </c>
+      <c r="AW13">
+        <v>18</v>
+      </c>
+      <c r="AX13">
+        <v>17</v>
+      </c>
+      <c r="AY13">
+        <v>10.5</v>
+      </c>
+      <c r="AZ13">
+        <v>12.5</v>
+      </c>
+      <c r="BA13">
         <v>26</v>
       </c>
-      <c r="AL13">
-        <v>46</v>
-      </c>
-      <c r="AM13">
-        <v>140</v>
-      </c>
-      <c r="AN13">
-        <v>24</v>
-      </c>
-      <c r="AO13">
-        <v>80</v>
-      </c>
-      <c r="AP13">
-        <v>10</v>
-      </c>
-      <c r="AQ13">
-        <v>11</v>
-      </c>
-      <c r="AR13">
-        <v>6.8</v>
-      </c>
-      <c r="AS13">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AT13">
-        <v>7.2</v>
-      </c>
-      <c r="AU13">
-        <v>6.6</v>
-      </c>
-      <c r="AV13">
-        <v>14</v>
-      </c>
-      <c r="AW13">
-        <v>7.8</v>
-      </c>
-      <c r="AX13">
-        <v>11</v>
-      </c>
-      <c r="AY13">
-        <v>9.4</v>
-      </c>
-      <c r="AZ13">
-        <v>16.5</v>
-      </c>
-      <c r="BA13">
-        <v>8</v>
-      </c>
       <c r="BB13">
-        <v>6.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC13">
-        <v>21</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD13">
-        <v>7.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE13">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BF13">
-        <v>15.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG13">
-        <v>8</v>
+        <v>13.5</v>
       </c>
       <c r="BH13" t="s">
-        <v>147</v>
+        <v>186</v>
       </c>
     </row>
     <row r="14" spans="1:60">
       <c r="A14" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B14" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="C14" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="D14" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="E14" t="s">
-        <v>129</v>
+        <v>155</v>
       </c>
       <c r="F14">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="G14">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="H14">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="I14">
-        <v>11</v>
+        <v>8.6</v>
       </c>
       <c r="J14">
-        <v>1.09</v>
+        <v>4.6</v>
       </c>
       <c r="K14">
-        <v>85</v>
+        <v>5.4</v>
       </c>
       <c r="L14">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="M14">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N14">
-        <v>1.83</v>
+        <v>4.7</v>
       </c>
       <c r="O14">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="P14">
-        <v>1.27</v>
+        <v>2.28</v>
       </c>
       <c r="Q14">
-        <v>1.95</v>
+        <v>1.64</v>
       </c>
       <c r="R14">
-        <v>1.26</v>
+        <v>1.52</v>
       </c>
       <c r="S14">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="T14">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="U14">
-        <v>1.01</v>
+        <v>1.99</v>
       </c>
       <c r="V14">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="W14">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="X14">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="Y14">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Z14">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AA14">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AB14">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AC14">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AD14">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AE14">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AF14">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AG14">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH14">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI14">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ14">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AK14">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AL14">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM14">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN14">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AO14">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AP14">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="AQ14">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="AR14">
-        <v>38</v>
+        <v>4.1</v>
       </c>
       <c r="AS14">
-        <v>40</v>
+        <v>4.2</v>
       </c>
       <c r="AT14">
-        <v>5.8</v>
+        <v>7.2</v>
       </c>
       <c r="AU14">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV14">
         <v>20</v>
       </c>
       <c r="AW14">
-        <v>40</v>
+        <v>4.1</v>
       </c>
       <c r="AX14">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AY14">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="AZ14">
-        <v>19.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA14">
-        <v>40</v>
+        <v>4.1</v>
       </c>
       <c r="BB14">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BC14">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BD14">
-        <v>29</v>
+        <v>3.9</v>
       </c>
       <c r="BE14">
-        <v>40</v>
+        <v>4.2</v>
       </c>
       <c r="BF14">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BG14">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BH14" t="s">
-        <v>147</v>
+        <v>186</v>
       </c>
     </row>
     <row r="15" spans="1:60">
       <c r="A15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B15" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="C15" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="D15" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="E15" t="s">
-        <v>130</v>
+        <v>156</v>
       </c>
       <c r="F15">
+        <v>1.89</v>
+      </c>
+      <c r="G15">
+        <v>2.54</v>
+      </c>
+      <c r="H15">
         <v>3.1</v>
       </c>
-      <c r="G15">
-        <v>3.15</v>
-      </c>
-      <c r="H15">
-        <v>2.64</v>
-      </c>
       <c r="I15">
-        <v>2.66</v>
+        <v>4.8</v>
       </c>
       <c r="J15">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="K15">
-        <v>3.35</v>
+        <v>6.8</v>
       </c>
       <c r="L15">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="M15">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="N15">
-        <v>3.3</v>
+        <v>1.81</v>
       </c>
       <c r="O15">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="P15">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="Q15">
-        <v>2.22</v>
+        <v>1.83</v>
       </c>
       <c r="R15">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="S15">
-        <v>4.1</v>
+        <v>2.7</v>
       </c>
       <c r="T15">
-        <v>1.9</v>
+        <v>1.01</v>
       </c>
       <c r="U15">
-        <v>2.04</v>
+        <v>1.01</v>
       </c>
       <c r="V15">
-        <v>1.6</v>
+        <v>1.26</v>
       </c>
       <c r="W15">
-        <v>1.46</v>
+        <v>1.64</v>
       </c>
       <c r="X15">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="Y15">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="Z15">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AA15">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AB15">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AC15">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="AD15">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AE15">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AF15">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AG15">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AH15">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AI15">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AJ15">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AK15">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AL15">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM15">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN15">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AO15">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AP15">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ15">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AR15">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS15">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="AT15">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AU15">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV15">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AW15">
-        <v>28</v>
+        <v>1.01</v>
       </c>
       <c r="AX15">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="AY15">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ15">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA15">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="BB15">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="BC15">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="BD15">
-        <v>48</v>
+        <v>1.01</v>
       </c>
       <c r="BE15">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BF15">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BG15">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="BH15" t="s">
-        <v>147</v>
+        <v>186</v>
       </c>
     </row>
     <row r="16" spans="1:60">
@@ -3553,34 +3670,34 @@
         <v>66</v>
       </c>
       <c r="B16" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="C16" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="D16" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="E16" t="s">
-        <v>131</v>
+        <v>157</v>
       </c>
       <c r="F16">
+        <v>2.32</v>
+      </c>
+      <c r="G16">
+        <v>2.96</v>
+      </c>
+      <c r="H16">
+        <v>1.53</v>
+      </c>
+      <c r="I16">
+        <v>4</v>
+      </c>
+      <c r="J16">
         <v>2.42</v>
       </c>
-      <c r="G16">
-        <v>2.82</v>
-      </c>
-      <c r="H16">
-        <v>2.98</v>
-      </c>
-      <c r="I16">
-        <v>3.6</v>
-      </c>
-      <c r="J16">
-        <v>3.25</v>
-      </c>
       <c r="K16">
-        <v>3.7</v>
+        <v>110</v>
       </c>
       <c r="L16">
         <v>1.01</v>
@@ -3589,22 +3706,22 @@
         <v>1.01</v>
       </c>
       <c r="N16">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="O16">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="P16">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="Q16">
-        <v>2.02</v>
+        <v>1.93</v>
       </c>
       <c r="R16">
-        <v>1.05</v>
+        <v>1.23</v>
       </c>
       <c r="S16">
-        <v>2.02</v>
+        <v>1.93</v>
       </c>
       <c r="T16">
         <v>1.01</v>
@@ -3613,10 +3730,10 @@
         <v>1.01</v>
       </c>
       <c r="V16">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="W16">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="X16">
         <v>1000</v>
@@ -3673,52 +3790,52 @@
         <v>1000</v>
       </c>
       <c r="AP16">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AQ16">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR16">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AS16">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="AT16">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AU16">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AV16">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AW16">
-        <v>1.01</v>
+        <v>28</v>
       </c>
       <c r="AX16">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AY16">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ16">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BA16">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="BB16">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="BC16">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BD16">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BE16">
-        <v>1.01</v>
+        <v>40</v>
       </c>
       <c r="BF16">
         <v>1.01</v>
@@ -3727,7 +3844,7 @@
         <v>1.01</v>
       </c>
       <c r="BH16" t="s">
-        <v>147</v>
+        <v>186</v>
       </c>
     </row>
     <row r="17" spans="1:60">
@@ -3735,1091 +3852,1091 @@
         <v>67</v>
       </c>
       <c r="B17" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="C17" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="D17" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="E17" t="s">
-        <v>132</v>
+        <v>158</v>
       </c>
       <c r="F17">
-        <v>1.6</v>
+        <v>2.42</v>
       </c>
       <c r="G17">
-        <v>1.66</v>
+        <v>2.98</v>
       </c>
       <c r="H17">
-        <v>5.6</v>
+        <v>3.05</v>
       </c>
       <c r="I17">
-        <v>6.2</v>
+        <v>3.6</v>
       </c>
       <c r="J17">
-        <v>4.5</v>
+        <v>2.72</v>
       </c>
       <c r="K17">
-        <v>5</v>
+        <v>3.7</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M17">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="P17">
-        <v>2.52</v>
+        <v>1.67</v>
       </c>
       <c r="Q17">
-        <v>1.57</v>
+        <v>2.02</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP17">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AQ17">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AR17">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AS17">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AT17">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AU17">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AV17">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AW17">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AX17">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AY17">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AZ17">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BA17">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BB17">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BC17">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BD17">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BE17">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BF17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH17" t="s">
-        <v>147</v>
+        <v>186</v>
       </c>
     </row>
     <row r="18" spans="1:60">
       <c r="A18" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="B18" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="C18" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="D18" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="E18" t="s">
-        <v>133</v>
+        <v>159</v>
       </c>
       <c r="F18">
-        <v>2.28</v>
+        <v>3.1</v>
       </c>
       <c r="G18">
-        <v>2.6</v>
+        <v>3.15</v>
       </c>
       <c r="H18">
-        <v>3.45</v>
+        <v>2.64</v>
       </c>
       <c r="I18">
-        <v>4.1</v>
+        <v>2.66</v>
       </c>
       <c r="J18">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="K18">
         <v>3.35</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="M18">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="P18">
-        <v>1.52</v>
+        <v>1.77</v>
       </c>
       <c r="Q18">
-        <v>2.54</v>
+        <v>2.24</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AG18">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AH18">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AI18">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AJ18">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AK18">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AL18">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AM18">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AN18">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AO18">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AP18">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AQ18">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AR18">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AS18">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AT18">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AU18">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AV18">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AW18">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AX18">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AY18">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AZ18">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BA18">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="BB18">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="BC18">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BD18">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="BE18">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BF18">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BG18">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BH18" t="s">
-        <v>147</v>
+        <v>186</v>
       </c>
     </row>
     <row r="19" spans="1:60">
       <c r="A19" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="B19" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="C19" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="D19" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="E19" t="s">
-        <v>134</v>
+        <v>160</v>
       </c>
       <c r="F19">
-        <v>1.72</v>
+        <v>2.78</v>
       </c>
       <c r="G19">
-        <v>1.89</v>
+        <v>2.9</v>
       </c>
       <c r="H19">
-        <v>5.2</v>
+        <v>2.5</v>
       </c>
       <c r="I19">
-        <v>7.2</v>
+        <v>2.6</v>
       </c>
       <c r="J19">
-        <v>3.05</v>
+        <v>3.8</v>
       </c>
       <c r="K19">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M19">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="P19">
-        <v>1.71</v>
+        <v>2.22</v>
       </c>
       <c r="Q19">
-        <v>2.14</v>
+        <v>1.75</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AH19">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AI19">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AL19">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AM19">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AN19">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AO19">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AP19">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AQ19">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AR19">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AS19">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AT19">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AU19">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AV19">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AW19">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AX19">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AY19">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AZ19">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BA19">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BB19">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BC19">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BD19">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BE19">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BF19">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BG19">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BH19" t="s">
-        <v>147</v>
+        <v>186</v>
       </c>
     </row>
     <row r="20" spans="1:60">
       <c r="A20" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B20" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="C20" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="D20" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="E20" t="s">
-        <v>135</v>
+        <v>161</v>
       </c>
       <c r="F20">
-        <v>1.98</v>
+        <v>1.68</v>
       </c>
       <c r="G20">
-        <v>2.68</v>
+        <v>2.04</v>
       </c>
       <c r="H20">
-        <v>2.88</v>
+        <v>3.85</v>
       </c>
       <c r="I20">
-        <v>4.4</v>
+        <v>6.6</v>
       </c>
       <c r="J20">
+        <v>3.2</v>
+      </c>
+      <c r="K20">
+        <v>7</v>
+      </c>
+      <c r="L20">
+        <v>1.01</v>
+      </c>
+      <c r="M20">
+        <v>1.01</v>
+      </c>
+      <c r="N20">
+        <v>1.64</v>
+      </c>
+      <c r="O20">
+        <v>1.35</v>
+      </c>
+      <c r="P20">
+        <v>1.64</v>
+      </c>
+      <c r="Q20">
+        <v>2</v>
+      </c>
+      <c r="R20">
+        <v>1.23</v>
+      </c>
+      <c r="S20">
         <v>3.15</v>
       </c>
-      <c r="K20">
-        <v>6.8</v>
-      </c>
-      <c r="L20">
-        <v>0</v>
-      </c>
-      <c r="M20">
-        <v>0</v>
-      </c>
-      <c r="N20">
-        <v>0</v>
-      </c>
-      <c r="O20">
-        <v>0</v>
-      </c>
-      <c r="P20">
-        <v>1.58</v>
-      </c>
-      <c r="Q20">
-        <v>1.98</v>
-      </c>
-      <c r="R20">
-        <v>0</v>
-      </c>
-      <c r="S20">
-        <v>0</v>
-      </c>
       <c r="T20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH20" t="s">
-        <v>147</v>
+        <v>186</v>
       </c>
     </row>
     <row r="21" spans="1:60">
       <c r="A21" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B21" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="C21" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="D21" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="E21" t="s">
-        <v>136</v>
+        <v>162</v>
       </c>
       <c r="F21">
-        <v>1.75</v>
+        <v>3.05</v>
       </c>
       <c r="G21">
-        <v>2.08</v>
+        <v>3.25</v>
       </c>
       <c r="H21">
-        <v>3.2</v>
+        <v>2.48</v>
       </c>
       <c r="I21">
-        <v>4.5</v>
+        <v>2.6</v>
       </c>
       <c r="J21">
+        <v>3.45</v>
+      </c>
+      <c r="K21">
         <v>3.6</v>
       </c>
-      <c r="K21">
-        <v>5.6</v>
-      </c>
       <c r="L21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M21">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="P21">
+        <v>1.88</v>
+      </c>
+      <c r="Q21">
+        <v>2.02</v>
+      </c>
+      <c r="R21">
+        <v>1.35</v>
+      </c>
+      <c r="S21">
+        <v>3.6</v>
+      </c>
+      <c r="T21">
+        <v>1.79</v>
+      </c>
+      <c r="U21">
         <v>2.14</v>
       </c>
-      <c r="Q21">
-        <v>1.74</v>
-      </c>
-      <c r="R21">
-        <v>0</v>
-      </c>
-      <c r="S21">
-        <v>0</v>
-      </c>
-      <c r="T21">
-        <v>0</v>
-      </c>
-      <c r="U21">
-        <v>0</v>
-      </c>
       <c r="V21">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AH21">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AI21">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AL21">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AM21">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AN21">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AO21">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AP21">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AQ21">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR21">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AS21">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AT21">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AU21">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AV21">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AW21">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AX21">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AY21">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AZ21">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BA21">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BB21">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BC21">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BD21">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BE21">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BF21">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BG21">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BH21" t="s">
-        <v>147</v>
+        <v>186</v>
       </c>
     </row>
     <row r="22" spans="1:60">
       <c r="A22" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B22" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="C22" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="D22" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="E22" t="s">
-        <v>137</v>
+        <v>163</v>
       </c>
       <c r="F22">
-        <v>1.39</v>
+        <v>1.74</v>
       </c>
       <c r="G22">
-        <v>1.43</v>
+        <v>1.81</v>
       </c>
       <c r="H22">
-        <v>7.2</v>
+        <v>5.2</v>
       </c>
       <c r="I22">
-        <v>9.4</v>
+        <v>5.6</v>
       </c>
       <c r="J22">
-        <v>5.8</v>
+        <v>3.9</v>
       </c>
       <c r="K22">
-        <v>6.6</v>
+        <v>4.2</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M22">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="P22">
-        <v>3.55</v>
+        <v>1.87</v>
       </c>
       <c r="Q22">
-        <v>1.33</v>
+        <v>1.92</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AH22">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AI22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AJ22">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AK22">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AL22">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AM22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN22">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AO22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP22">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AQ22">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AR22">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AS22">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AT22">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AU22">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AV22">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AW22">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AX22">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AY22">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AZ22">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="BA22">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="BB22">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="BC22">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="BD22">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="BE22">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="BF22">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BG22">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="BH22" t="s">
-        <v>147</v>
+        <v>186</v>
       </c>
     </row>
     <row r="23" spans="1:60">
@@ -4827,1637 +4944,4003 @@
         <v>70</v>
       </c>
       <c r="B23" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="C23" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="D23" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="E23" t="s">
-        <v>138</v>
+        <v>164</v>
       </c>
       <c r="F23">
-        <v>2.16</v>
+        <v>2.66</v>
       </c>
       <c r="G23">
-        <v>2.76</v>
+        <v>3.95</v>
       </c>
       <c r="H23">
-        <v>2.74</v>
+        <v>2.18</v>
       </c>
       <c r="I23">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J23">
-        <v>2.56</v>
+        <v>3</v>
       </c>
       <c r="K23">
-        <v>85</v>
+        <v>6.2</v>
       </c>
       <c r="L23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="P23">
-        <v>2.02</v>
+        <v>1.53</v>
       </c>
       <c r="Q23">
-        <v>1.58</v>
+        <v>2.08</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH23" t="s">
-        <v>147</v>
+        <v>186</v>
       </c>
     </row>
     <row r="24" spans="1:60">
       <c r="A24" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="B24" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="C24" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="D24" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="E24" t="s">
-        <v>139</v>
+        <v>165</v>
       </c>
       <c r="F24">
-        <v>1.97</v>
+        <v>2.16</v>
       </c>
       <c r="G24">
-        <v>2.38</v>
+        <v>2.76</v>
       </c>
       <c r="H24">
-        <v>3.25</v>
+        <v>2.74</v>
       </c>
       <c r="I24">
-        <v>4.9</v>
+        <v>4</v>
       </c>
       <c r="J24">
-        <v>3.25</v>
+        <v>2.56</v>
       </c>
       <c r="K24">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="L24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M24">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="P24">
-        <v>1.9</v>
+        <v>2.02</v>
       </c>
       <c r="Q24">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W24">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP24">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AQ24">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AR24">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AS24">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AT24">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AU24">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AV24">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW24">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AX24">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AY24">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ24">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BA24">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="BB24">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BC24">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BD24">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BE24">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BF24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH24" t="s">
-        <v>147</v>
+        <v>186</v>
       </c>
     </row>
     <row r="25" spans="1:60">
       <c r="A25" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="B25" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="C25" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="D25" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="E25" t="s">
-        <v>140</v>
+        <v>166</v>
       </c>
       <c r="F25">
-        <v>1.65</v>
+        <v>2.16</v>
       </c>
       <c r="G25">
-        <v>1.68</v>
+        <v>2.44</v>
       </c>
       <c r="H25">
-        <v>5.8</v>
+        <v>3.4</v>
       </c>
       <c r="I25">
-        <v>6.2</v>
+        <v>4</v>
       </c>
       <c r="J25">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="K25">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="L25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M25">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="N25">
-        <v>3.95</v>
+        <v>1.71</v>
       </c>
       <c r="O25">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="P25">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="Q25">
-        <v>1.94</v>
+        <v>2.12</v>
       </c>
       <c r="R25">
-        <v>1.37</v>
+        <v>1.21</v>
       </c>
       <c r="S25">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="T25">
-        <v>1.97</v>
+        <v>1.01</v>
       </c>
       <c r="U25">
-        <v>1.98</v>
+        <v>1.01</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W25">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="X25">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="Y25">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="Z25">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AA25">
         <v>1000</v>
       </c>
       <c r="AB25">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AC25">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AD25">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AE25">
         <v>1000</v>
       </c>
       <c r="AF25">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AG25">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AH25">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AI25">
         <v>1000</v>
       </c>
       <c r="AJ25">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AK25">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AL25">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AM25">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AN25">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AO25">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AP25">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AQ25">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="AR25">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="AS25">
-        <v>44</v>
+        <v>1.01</v>
       </c>
       <c r="AT25">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU25">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AV25">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AW25">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="AX25">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AY25">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AZ25">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BA25">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BB25">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC25">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BD25">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="BE25">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="BF25">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BG25">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="BH25" t="s">
-        <v>147</v>
+        <v>186</v>
       </c>
     </row>
     <row r="26" spans="1:60">
       <c r="A26" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="B26" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="C26" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="D26" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="E26" t="s">
-        <v>141</v>
+        <v>167</v>
       </c>
       <c r="F26">
-        <v>6.8</v>
+        <v>1.75</v>
       </c>
       <c r="G26">
-        <v>7</v>
+        <v>2.08</v>
       </c>
       <c r="H26">
-        <v>1.51</v>
+        <v>3.2</v>
       </c>
       <c r="I26">
-        <v>1.52</v>
+        <v>4.5</v>
       </c>
       <c r="J26">
-        <v>5.1</v>
+        <v>3.6</v>
       </c>
       <c r="K26">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M26">
         <v>1.04</v>
       </c>
       <c r="N26">
-        <v>5.1</v>
+        <v>3.35</v>
       </c>
       <c r="O26">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="P26">
-        <v>2.42</v>
+        <v>2.14</v>
       </c>
       <c r="Q26">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="R26">
-        <v>1.54</v>
+        <v>1.46</v>
       </c>
       <c r="S26">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="T26">
-        <v>1.84</v>
+        <v>1.01</v>
       </c>
       <c r="U26">
-        <v>2.14</v>
+        <v>1.01</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W26">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="X26">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="Y26">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="Z26">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AA26">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AB26">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AC26">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AD26">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AE26">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AF26">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AG26">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AH26">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AI26">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AJ26">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AK26">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AL26">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AM26">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AN26">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AO26">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="AP26">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AQ26">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AR26">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AS26">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AT26">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="AU26">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AV26">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AW26">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX26">
-        <v>48</v>
+        <v>1.01</v>
       </c>
       <c r="AY26">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="AZ26">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA26">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="BB26">
-        <v>46</v>
+        <v>1.01</v>
       </c>
       <c r="BC26">
-        <v>55</v>
+        <v>1.01</v>
       </c>
       <c r="BD26">
-        <v>55</v>
+        <v>1.01</v>
       </c>
       <c r="BE26">
-        <v>65</v>
+        <v>1.01</v>
       </c>
       <c r="BF26">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BG26">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BH26" t="s">
-        <v>147</v>
+        <v>186</v>
       </c>
     </row>
     <row r="27" spans="1:60">
       <c r="A27" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B27" t="s">
+        <v>83</v>
+      </c>
+      <c r="C27" t="s">
+        <v>89</v>
+      </c>
+      <c r="D27" t="s">
+        <v>125</v>
+      </c>
+      <c r="E27" t="s">
+        <v>168</v>
+      </c>
+      <c r="F27">
+        <v>1.39</v>
+      </c>
+      <c r="G27">
+        <v>1.43</v>
+      </c>
+      <c r="H27">
+        <v>7.2</v>
+      </c>
+      <c r="I27">
+        <v>9.4</v>
+      </c>
+      <c r="J27">
+        <v>5.8</v>
+      </c>
+      <c r="K27">
+        <v>6.6</v>
+      </c>
+      <c r="L27">
+        <v>1.01</v>
+      </c>
+      <c r="M27">
+        <v>1.02</v>
+      </c>
+      <c r="N27">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="O27">
+        <v>1.11</v>
+      </c>
+      <c r="P27">
+        <v>3.55</v>
+      </c>
+      <c r="Q27">
+        <v>1.33</v>
+      </c>
+      <c r="R27">
+        <v>2.04</v>
+      </c>
+      <c r="S27">
+        <v>1.83</v>
+      </c>
+      <c r="T27">
+        <v>1.58</v>
+      </c>
+      <c r="U27">
+        <v>2.5</v>
+      </c>
+      <c r="V27">
+        <v>1.12</v>
+      </c>
+      <c r="W27">
+        <v>3.25</v>
+      </c>
+      <c r="X27">
+        <v>60</v>
+      </c>
+      <c r="Y27">
+        <v>55</v>
+      </c>
+      <c r="Z27">
+        <v>95</v>
+      </c>
+      <c r="AA27">
+        <v>230</v>
+      </c>
+      <c r="AB27">
+        <v>21</v>
+      </c>
+      <c r="AC27">
+        <v>19.5</v>
+      </c>
+      <c r="AD27">
+        <v>38</v>
+      </c>
+      <c r="AE27">
+        <v>95</v>
+      </c>
+      <c r="AF27">
+        <v>17</v>
+      </c>
+      <c r="AG27">
+        <v>14.5</v>
+      </c>
+      <c r="AH27">
+        <v>25</v>
+      </c>
+      <c r="AI27">
         <v>75</v>
       </c>
-      <c r="C27" t="s">
-        <v>83</v>
-      </c>
-      <c r="D27" t="s">
-        <v>112</v>
-      </c>
-      <c r="E27" t="s">
-        <v>142</v>
-      </c>
-      <c r="F27">
-        <v>2.36</v>
-      </c>
-      <c r="G27">
-        <v>2.56</v>
-      </c>
-      <c r="H27">
-        <v>3.5</v>
-      </c>
-      <c r="I27">
+      <c r="AJ27">
+        <v>17.5</v>
+      </c>
+      <c r="AK27">
+        <v>16.5</v>
+      </c>
+      <c r="AL27">
+        <v>29</v>
+      </c>
+      <c r="AM27">
+        <v>80</v>
+      </c>
+      <c r="AN27">
+        <v>4.4</v>
+      </c>
+      <c r="AO27">
+        <v>65</v>
+      </c>
+      <c r="AP27">
         <v>4.1</v>
       </c>
-      <c r="J27">
-        <v>2.9</v>
-      </c>
-      <c r="K27">
-        <v>3.2</v>
-      </c>
-      <c r="L27">
-        <v>1.01</v>
-      </c>
-      <c r="M27">
-        <v>1.15</v>
-      </c>
-      <c r="N27">
-        <v>2.28</v>
-      </c>
-      <c r="O27">
-        <v>1.68</v>
-      </c>
-      <c r="P27">
-        <v>1.44</v>
-      </c>
-      <c r="Q27">
-        <v>3</v>
-      </c>
-      <c r="R27">
-        <v>1.14</v>
-      </c>
-      <c r="S27">
-        <v>6.8</v>
-      </c>
-      <c r="T27">
-        <v>2.2</v>
-      </c>
-      <c r="U27">
-        <v>1.62</v>
-      </c>
-      <c r="V27">
-        <v>1.33</v>
-      </c>
-      <c r="W27">
-        <v>1.64</v>
-      </c>
-      <c r="X27">
-        <v>8.4</v>
-      </c>
-      <c r="Y27">
-        <v>9.6</v>
-      </c>
-      <c r="Z27">
-        <v>26</v>
-      </c>
-      <c r="AA27">
-        <v>110</v>
-      </c>
-      <c r="AB27">
-        <v>7</v>
-      </c>
-      <c r="AC27">
-        <v>7.6</v>
-      </c>
-      <c r="AD27">
-        <v>21</v>
-      </c>
-      <c r="AE27">
-        <v>80</v>
-      </c>
-      <c r="AF27">
-        <v>14.5</v>
-      </c>
-      <c r="AG27">
+      <c r="AQ27">
+        <v>4.1</v>
+      </c>
+      <c r="AR27">
+        <v>4.2</v>
+      </c>
+      <c r="AS27">
+        <v>4.3</v>
+      </c>
+      <c r="AT27">
         <v>15</v>
       </c>
-      <c r="AH27">
-        <v>30</v>
-      </c>
-      <c r="AI27">
-        <v>130</v>
-      </c>
-      <c r="AJ27">
-        <v>46</v>
-      </c>
-      <c r="AK27">
-        <v>44</v>
-      </c>
-      <c r="AL27">
-        <v>95</v>
-      </c>
-      <c r="AM27">
-        <v>320</v>
-      </c>
-      <c r="AN27">
-        <v>60</v>
-      </c>
-      <c r="AO27">
-        <v>140</v>
-      </c>
-      <c r="AP27">
-        <v>6.2</v>
-      </c>
-      <c r="AQ27">
-        <v>7.8</v>
-      </c>
-      <c r="AR27">
-        <v>21</v>
-      </c>
-      <c r="AS27">
-        <v>6.8</v>
-      </c>
-      <c r="AT27">
-        <v>5.8</v>
-      </c>
       <c r="AU27">
-        <v>6.2</v>
+        <v>14</v>
       </c>
       <c r="AV27">
-        <v>15</v>
+        <v>3.95</v>
       </c>
       <c r="AW27">
-        <v>6.6</v>
+        <v>4.2</v>
       </c>
       <c r="AX27">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AY27">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ27">
-        <v>5.9</v>
+        <v>17.5</v>
       </c>
       <c r="BA27">
-        <v>6.8</v>
+        <v>4.2</v>
       </c>
       <c r="BB27">
-        <v>6.2</v>
+        <v>12.5</v>
       </c>
       <c r="BC27">
-        <v>6.2</v>
+        <v>12</v>
       </c>
       <c r="BD27">
-        <v>6.8</v>
+        <v>20</v>
       </c>
       <c r="BE27">
-        <v>7</v>
+        <v>4.2</v>
       </c>
       <c r="BF27">
-        <v>36</v>
+        <v>2.96</v>
       </c>
       <c r="BG27">
-        <v>6.8</v>
+        <v>4.1</v>
       </c>
       <c r="BH27" t="s">
-        <v>147</v>
+        <v>186</v>
       </c>
     </row>
     <row r="28" spans="1:60">
       <c r="A28" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="B28" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="C28" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="D28" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="E28" t="s">
-        <v>143</v>
+        <v>169</v>
       </c>
       <c r="F28">
-        <v>1.34</v>
+        <v>1.71</v>
       </c>
       <c r="G28">
-        <v>1.62</v>
+        <v>1.89</v>
       </c>
       <c r="H28">
-        <v>2.68</v>
+        <v>5.2</v>
       </c>
       <c r="I28">
-        <v>100</v>
+        <v>7.2</v>
       </c>
       <c r="J28">
-        <v>2.68</v>
+        <v>3.45</v>
       </c>
       <c r="K28">
-        <v>85</v>
+        <v>4.5</v>
       </c>
       <c r="L28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="P28">
-        <v>1.91</v>
+        <v>1.71</v>
       </c>
       <c r="Q28">
-        <v>1.63</v>
+        <v>2.12</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="W28">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="X28">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="Y28">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Z28">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AA28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB28">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AC28">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AD28">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AE28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AG28">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AH28">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AI28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ28">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AK28">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AL28">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AM28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP28">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AQ28">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AR28">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AS28">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AT28">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AU28">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AV28">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AW28">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AX28">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AY28">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AZ28">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BA28">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="BB28">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="BC28">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BD28">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="BE28">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="BF28">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="BG28">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="BH28" t="s">
-        <v>147</v>
+        <v>186</v>
       </c>
     </row>
     <row r="29" spans="1:60">
       <c r="A29" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="B29" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="C29" t="s">
+        <v>89</v>
+      </c>
+      <c r="D29" t="s">
+        <v>127</v>
+      </c>
+      <c r="E29" t="s">
+        <v>170</v>
+      </c>
+      <c r="F29">
+        <v>2.32</v>
+      </c>
+      <c r="G29">
+        <v>2.66</v>
+      </c>
+      <c r="H29">
+        <v>3.55</v>
+      </c>
+      <c r="I29">
+        <v>4.4</v>
+      </c>
+      <c r="J29">
+        <v>2.94</v>
+      </c>
+      <c r="K29">
+        <v>3.35</v>
+      </c>
+      <c r="L29">
+        <v>1.01</v>
+      </c>
+      <c r="M29">
+        <v>1.01</v>
+      </c>
+      <c r="N29">
+        <v>1.52</v>
+      </c>
+      <c r="O29">
+        <v>1.52</v>
+      </c>
+      <c r="P29">
+        <v>1.52</v>
+      </c>
+      <c r="Q29">
+        <v>2.54</v>
+      </c>
+      <c r="R29">
+        <v>1.14</v>
+      </c>
+      <c r="S29">
+        <v>4.4</v>
+      </c>
+      <c r="T29">
+        <v>1.01</v>
+      </c>
+      <c r="U29">
+        <v>1.01</v>
+      </c>
+      <c r="V29">
+        <v>1.29</v>
+      </c>
+      <c r="W29">
+        <v>1.6</v>
+      </c>
+      <c r="X29">
+        <v>11.5</v>
+      </c>
+      <c r="Y29">
+        <v>14.5</v>
+      </c>
+      <c r="Z29">
+        <v>34</v>
+      </c>
+      <c r="AA29">
+        <v>1000</v>
+      </c>
+      <c r="AB29">
+        <v>10</v>
+      </c>
+      <c r="AC29">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD29">
+        <v>23</v>
+      </c>
+      <c r="AE29">
         <v>85</v>
       </c>
-      <c r="D29" t="s">
-        <v>114</v>
-      </c>
-      <c r="E29" t="s">
-        <v>144</v>
-      </c>
-      <c r="F29">
-        <v>1.55</v>
-      </c>
-      <c r="G29">
+      <c r="AF29">
+        <v>20</v>
+      </c>
+      <c r="AG29">
+        <v>17</v>
+      </c>
+      <c r="AH29">
+        <v>32</v>
+      </c>
+      <c r="AI29">
+        <v>1000</v>
+      </c>
+      <c r="AJ29">
+        <v>50</v>
+      </c>
+      <c r="AK29">
+        <v>48</v>
+      </c>
+      <c r="AL29">
+        <v>90</v>
+      </c>
+      <c r="AM29">
+        <v>1000</v>
+      </c>
+      <c r="AN29">
+        <v>1000</v>
+      </c>
+      <c r="AO29">
+        <v>1000</v>
+      </c>
+      <c r="AP29">
+        <v>2.2</v>
+      </c>
+      <c r="AQ29">
+        <v>2.3</v>
+      </c>
+      <c r="AR29">
+        <v>16</v>
+      </c>
+      <c r="AS29">
+        <v>2.72</v>
+      </c>
+      <c r="AT29">
+        <v>2.14</v>
+      </c>
+      <c r="AU29">
+        <v>2.12</v>
+      </c>
+      <c r="AV29">
+        <v>11.5</v>
+      </c>
+      <c r="AW29">
         <v>2.64</v>
       </c>
-      <c r="H29">
-        <v>2.84</v>
-      </c>
-      <c r="I29">
-        <v>4.5</v>
-      </c>
-      <c r="J29">
-        <v>3.05</v>
-      </c>
-      <c r="K29">
-        <v>150</v>
-      </c>
-      <c r="L29">
-        <v>0</v>
-      </c>
-      <c r="M29">
-        <v>0</v>
-      </c>
-      <c r="N29">
-        <v>0</v>
-      </c>
-      <c r="O29">
-        <v>0</v>
-      </c>
-      <c r="P29">
-        <v>1.94</v>
-      </c>
-      <c r="Q29">
-        <v>1.69</v>
-      </c>
-      <c r="R29">
-        <v>0</v>
-      </c>
-      <c r="S29">
-        <v>0</v>
-      </c>
-      <c r="T29">
-        <v>0</v>
-      </c>
-      <c r="U29">
-        <v>0</v>
-      </c>
-      <c r="V29">
-        <v>0</v>
-      </c>
-      <c r="W29">
-        <v>0</v>
-      </c>
-      <c r="X29">
-        <v>0</v>
-      </c>
-      <c r="Y29">
-        <v>0</v>
-      </c>
-      <c r="Z29">
-        <v>0</v>
-      </c>
-      <c r="AA29">
-        <v>0</v>
-      </c>
-      <c r="AB29">
-        <v>0</v>
-      </c>
-      <c r="AC29">
-        <v>0</v>
-      </c>
-      <c r="AD29">
-        <v>0</v>
-      </c>
-      <c r="AE29">
-        <v>0</v>
-      </c>
-      <c r="AF29">
-        <v>0</v>
-      </c>
-      <c r="AG29">
-        <v>0</v>
-      </c>
-      <c r="AH29">
-        <v>0</v>
-      </c>
-      <c r="AI29">
-        <v>0</v>
-      </c>
-      <c r="AJ29">
-        <v>0</v>
-      </c>
-      <c r="AK29">
-        <v>0</v>
-      </c>
-      <c r="AL29">
-        <v>0</v>
-      </c>
-      <c r="AM29">
-        <v>0</v>
-      </c>
-      <c r="AN29">
-        <v>0</v>
-      </c>
-      <c r="AO29">
-        <v>0</v>
-      </c>
-      <c r="AP29">
-        <v>0</v>
-      </c>
-      <c r="AQ29">
-        <v>0</v>
-      </c>
-      <c r="AR29">
-        <v>0</v>
-      </c>
-      <c r="AS29">
-        <v>0</v>
-      </c>
-      <c r="AT29">
-        <v>0</v>
-      </c>
-      <c r="AU29">
-        <v>0</v>
-      </c>
-      <c r="AV29">
-        <v>0</v>
-      </c>
-      <c r="AW29">
-        <v>0</v>
-      </c>
       <c r="AX29">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY29">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AZ29">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="BA29">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="BB29">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="BC29">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="BD29">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="BE29">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="BF29">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="BG29">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="BH29" t="s">
-        <v>147</v>
+        <v>186</v>
       </c>
     </row>
     <row r="30" spans="1:60">
       <c r="A30" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B30" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="C30" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D30" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="E30" t="s">
-        <v>145</v>
+        <v>171</v>
       </c>
       <c r="F30">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="G30">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="H30">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="I30">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="J30">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="K30">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M30">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="P30">
-        <v>1.78</v>
+        <v>2.54</v>
       </c>
       <c r="Q30">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="T30">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="U30">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V30">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="W30">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="X30">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="Y30">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="Z30">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AA30">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AB30">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AC30">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AD30">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AE30">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AF30">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AG30">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AH30">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AI30">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AJ30">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AK30">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AL30">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AM30">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AN30">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AO30">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AP30">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AQ30">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR30">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS30">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AT30">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AU30">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV30">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AW30">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AX30">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AY30">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ30">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BA30">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BB30">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BC30">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BD30">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="BE30">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BF30">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BG30">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BH30" t="s">
-        <v>147</v>
+        <v>186</v>
       </c>
     </row>
     <row r="31" spans="1:60">
       <c r="A31" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="B31" t="s">
+        <v>83</v>
+      </c>
+      <c r="C31" t="s">
+        <v>90</v>
+      </c>
+      <c r="D31" t="s">
+        <v>129</v>
+      </c>
+      <c r="E31" t="s">
+        <v>172</v>
+      </c>
+      <c r="F31">
+        <v>2.24</v>
+      </c>
+      <c r="G31">
+        <v>2.9</v>
+      </c>
+      <c r="H31">
+        <v>2.02</v>
+      </c>
+      <c r="I31">
+        <v>3.95</v>
+      </c>
+      <c r="J31">
+        <v>3.25</v>
+      </c>
+      <c r="K31">
+        <v>950</v>
+      </c>
+      <c r="L31">
+        <v>1.01</v>
+      </c>
+      <c r="M31">
+        <v>1.07</v>
+      </c>
+      <c r="N31">
+        <v>1.01</v>
+      </c>
+      <c r="O31">
+        <v>1.33</v>
+      </c>
+      <c r="P31">
+        <v>1.83</v>
+      </c>
+      <c r="Q31">
+        <v>1.97</v>
+      </c>
+      <c r="R31">
+        <v>1.18</v>
+      </c>
+      <c r="S31">
+        <v>1.97</v>
+      </c>
+      <c r="T31">
+        <v>1.01</v>
+      </c>
+      <c r="U31">
+        <v>1.01</v>
+      </c>
+      <c r="V31">
+        <v>1.33</v>
+      </c>
+      <c r="W31">
+        <v>1.52</v>
+      </c>
+      <c r="X31">
+        <v>1000</v>
+      </c>
+      <c r="Y31">
+        <v>1000</v>
+      </c>
+      <c r="Z31">
+        <v>1000</v>
+      </c>
+      <c r="AA31">
+        <v>1000</v>
+      </c>
+      <c r="AB31">
+        <v>1000</v>
+      </c>
+      <c r="AC31">
+        <v>1000</v>
+      </c>
+      <c r="AD31">
+        <v>1000</v>
+      </c>
+      <c r="AE31">
+        <v>1000</v>
+      </c>
+      <c r="AF31">
+        <v>1000</v>
+      </c>
+      <c r="AG31">
+        <v>1000</v>
+      </c>
+      <c r="AH31">
+        <v>1000</v>
+      </c>
+      <c r="AI31">
+        <v>1000</v>
+      </c>
+      <c r="AJ31">
+        <v>1000</v>
+      </c>
+      <c r="AK31">
+        <v>1000</v>
+      </c>
+      <c r="AL31">
+        <v>1000</v>
+      </c>
+      <c r="AM31">
+        <v>1000</v>
+      </c>
+      <c r="AN31">
+        <v>1000</v>
+      </c>
+      <c r="AO31">
+        <v>1000</v>
+      </c>
+      <c r="AP31">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AQ31">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR31">
+        <v>15.5</v>
+      </c>
+      <c r="AS31">
+        <v>36</v>
+      </c>
+      <c r="AT31">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU31">
+        <v>6.2</v>
+      </c>
+      <c r="AV31">
+        <v>10</v>
+      </c>
+      <c r="AW31">
+        <v>24</v>
+      </c>
+      <c r="AX31">
+        <v>10.5</v>
+      </c>
+      <c r="AY31">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ31">
+        <v>14</v>
+      </c>
+      <c r="BA31">
+        <v>34</v>
+      </c>
+      <c r="BB31">
+        <v>24</v>
+      </c>
+      <c r="BC31">
+        <v>18.5</v>
+      </c>
+      <c r="BD31">
+        <v>28</v>
+      </c>
+      <c r="BE31">
+        <v>40</v>
+      </c>
+      <c r="BF31">
+        <v>1.01</v>
+      </c>
+      <c r="BG31">
+        <v>1.01</v>
+      </c>
+      <c r="BH31" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="32" spans="1:60">
+      <c r="A32" t="s">
+        <v>66</v>
+      </c>
+      <c r="B32" t="s">
+        <v>83</v>
+      </c>
+      <c r="C32" t="s">
+        <v>91</v>
+      </c>
+      <c r="D32" t="s">
+        <v>130</v>
+      </c>
+      <c r="E32" t="s">
+        <v>173</v>
+      </c>
+      <c r="F32">
+        <v>1.49</v>
+      </c>
+      <c r="G32">
+        <v>1.56</v>
+      </c>
+      <c r="H32">
+        <v>6</v>
+      </c>
+      <c r="I32">
+        <v>7.4</v>
+      </c>
+      <c r="J32">
+        <v>4.8</v>
+      </c>
+      <c r="K32">
+        <v>5.8</v>
+      </c>
+      <c r="L32">
+        <v>1.22</v>
+      </c>
+      <c r="M32">
+        <v>1.03</v>
+      </c>
+      <c r="N32">
+        <v>6</v>
+      </c>
+      <c r="O32">
+        <v>1.15</v>
+      </c>
+      <c r="P32">
+        <v>2.74</v>
+      </c>
+      <c r="Q32">
+        <v>1.5</v>
+      </c>
+      <c r="R32">
+        <v>1.7</v>
+      </c>
+      <c r="S32">
+        <v>2.14</v>
+      </c>
+      <c r="T32">
+        <v>1.63</v>
+      </c>
+      <c r="U32">
+        <v>2.26</v>
+      </c>
+      <c r="V32">
+        <v>1.15</v>
+      </c>
+      <c r="W32">
+        <v>2.78</v>
+      </c>
+      <c r="X32">
+        <v>34</v>
+      </c>
+      <c r="Y32">
+        <v>34</v>
+      </c>
+      <c r="Z32">
+        <v>65</v>
+      </c>
+      <c r="AA32">
+        <v>180</v>
+      </c>
+      <c r="AB32">
+        <v>14</v>
+      </c>
+      <c r="AC32">
+        <v>13.5</v>
+      </c>
+      <c r="AD32">
+        <v>27</v>
+      </c>
+      <c r="AE32">
+        <v>80</v>
+      </c>
+      <c r="AF32">
+        <v>12.5</v>
+      </c>
+      <c r="AG32">
+        <v>11.5</v>
+      </c>
+      <c r="AH32">
+        <v>21</v>
+      </c>
+      <c r="AI32">
+        <v>65</v>
+      </c>
+      <c r="AJ32">
+        <v>15.5</v>
+      </c>
+      <c r="AK32">
+        <v>15</v>
+      </c>
+      <c r="AL32">
+        <v>27</v>
+      </c>
+      <c r="AM32">
+        <v>80</v>
+      </c>
+      <c r="AN32">
+        <v>5.4</v>
+      </c>
+      <c r="AO32">
+        <v>65</v>
+      </c>
+      <c r="AP32">
+        <v>7</v>
+      </c>
+      <c r="AQ32">
+        <v>7</v>
+      </c>
+      <c r="AR32">
+        <v>7.8</v>
+      </c>
+      <c r="AS32">
+        <v>8.4</v>
+      </c>
+      <c r="AT32">
+        <v>11</v>
+      </c>
+      <c r="AU32">
+        <v>10.5</v>
+      </c>
+      <c r="AV32">
+        <v>21</v>
+      </c>
+      <c r="AW32">
+        <v>8</v>
+      </c>
+      <c r="AX32">
+        <v>10</v>
+      </c>
+      <c r="AY32">
+        <v>9</v>
+      </c>
+      <c r="AZ32">
+        <v>16.5</v>
+      </c>
+      <c r="BA32">
+        <v>7.8</v>
+      </c>
+      <c r="BB32">
+        <v>12.5</v>
+      </c>
+      <c r="BC32">
+        <v>12</v>
+      </c>
+      <c r="BD32">
+        <v>6.6</v>
+      </c>
+      <c r="BE32">
+        <v>8</v>
+      </c>
+      <c r="BF32">
+        <v>4.1</v>
+      </c>
+      <c r="BG32">
+        <v>44</v>
+      </c>
+      <c r="BH32" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="33" spans="1:60">
+      <c r="A33" t="s">
+        <v>66</v>
+      </c>
+      <c r="B33" t="s">
+        <v>83</v>
+      </c>
+      <c r="C33" t="s">
+        <v>91</v>
+      </c>
+      <c r="D33" t="s">
+        <v>131</v>
+      </c>
+      <c r="E33" t="s">
+        <v>174</v>
+      </c>
+      <c r="F33">
+        <v>1.61</v>
+      </c>
+      <c r="G33">
+        <v>1.81</v>
+      </c>
+      <c r="H33">
+        <v>4.8</v>
+      </c>
+      <c r="I33">
+        <v>6.4</v>
+      </c>
+      <c r="J33">
+        <v>4.2</v>
+      </c>
+      <c r="K33">
+        <v>5.5</v>
+      </c>
+      <c r="L33">
+        <v>1.01</v>
+      </c>
+      <c r="M33">
+        <v>1.03</v>
+      </c>
+      <c r="N33">
+        <v>2.48</v>
+      </c>
+      <c r="O33">
+        <v>1.16</v>
+      </c>
+      <c r="P33">
+        <v>2.46</v>
+      </c>
+      <c r="Q33">
+        <v>1.54</v>
+      </c>
+      <c r="R33">
+        <v>1.24</v>
+      </c>
+      <c r="S33">
+        <v>2.12</v>
+      </c>
+      <c r="T33">
+        <v>1.01</v>
+      </c>
+      <c r="U33">
+        <v>1.01</v>
+      </c>
+      <c r="V33">
+        <v>1.18</v>
+      </c>
+      <c r="W33">
+        <v>2.24</v>
+      </c>
+      <c r="X33">
+        <v>36</v>
+      </c>
+      <c r="Y33">
+        <v>34</v>
+      </c>
+      <c r="Z33">
+        <v>65</v>
+      </c>
+      <c r="AA33">
+        <v>1000</v>
+      </c>
+      <c r="AB33">
+        <v>17</v>
+      </c>
+      <c r="AC33">
+        <v>15</v>
+      </c>
+      <c r="AD33">
+        <v>29</v>
+      </c>
+      <c r="AE33">
+        <v>85</v>
+      </c>
+      <c r="AF33">
+        <v>17.5</v>
+      </c>
+      <c r="AG33">
+        <v>14.5</v>
+      </c>
+      <c r="AH33">
+        <v>25</v>
+      </c>
+      <c r="AI33">
         <v>75</v>
       </c>
-      <c r="C31" t="s">
-        <v>86</v>
-      </c>
-      <c r="D31" t="s">
-        <v>116</v>
-      </c>
-      <c r="E31" t="s">
-        <v>146</v>
-      </c>
-      <c r="F31">
+      <c r="AJ33">
+        <v>24</v>
+      </c>
+      <c r="AK33">
+        <v>22</v>
+      </c>
+      <c r="AL33">
+        <v>38</v>
+      </c>
+      <c r="AM33">
+        <v>100</v>
+      </c>
+      <c r="AN33">
+        <v>1000</v>
+      </c>
+      <c r="AO33">
+        <v>1000</v>
+      </c>
+      <c r="AP33">
+        <v>2.08</v>
+      </c>
+      <c r="AQ33">
+        <v>2.06</v>
+      </c>
+      <c r="AR33">
+        <v>2.12</v>
+      </c>
+      <c r="AS33">
+        <v>2.2</v>
+      </c>
+      <c r="AT33">
+        <v>1.95</v>
+      </c>
+      <c r="AU33">
+        <v>1.92</v>
+      </c>
+      <c r="AV33">
+        <v>2.04</v>
+      </c>
+      <c r="AW33">
+        <v>2.14</v>
+      </c>
+      <c r="AX33">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY33">
+        <v>1.91</v>
+      </c>
+      <c r="AZ33">
+        <v>12.5</v>
+      </c>
+      <c r="BA33">
+        <v>2.14</v>
+      </c>
+      <c r="BB33">
+        <v>2.02</v>
+      </c>
+      <c r="BC33">
+        <v>11</v>
+      </c>
+      <c r="BD33">
+        <v>19</v>
+      </c>
+      <c r="BE33">
+        <v>2.16</v>
+      </c>
+      <c r="BF33">
+        <v>2.2</v>
+      </c>
+      <c r="BG33">
+        <v>2.2</v>
+      </c>
+      <c r="BH33" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="34" spans="1:60">
+      <c r="A34" t="s">
+        <v>76</v>
+      </c>
+      <c r="B34" t="s">
+        <v>83</v>
+      </c>
+      <c r="C34" t="s">
+        <v>92</v>
+      </c>
+      <c r="D34" t="s">
+        <v>132</v>
+      </c>
+      <c r="E34" t="s">
+        <v>175</v>
+      </c>
+      <c r="F34">
+        <v>1.48</v>
+      </c>
+      <c r="G34">
+        <v>1.58</v>
+      </c>
+      <c r="H34">
+        <v>6</v>
+      </c>
+      <c r="I34">
+        <v>7.2</v>
+      </c>
+      <c r="J34">
+        <v>4.8</v>
+      </c>
+      <c r="K34">
+        <v>5.6</v>
+      </c>
+      <c r="L34">
+        <v>1.01</v>
+      </c>
+      <c r="M34">
+        <v>1.03</v>
+      </c>
+      <c r="N34">
+        <v>2.62</v>
+      </c>
+      <c r="O34">
+        <v>1.15</v>
+      </c>
+      <c r="P34">
+        <v>2.62</v>
+      </c>
+      <c r="Q34">
+        <v>1.44</v>
+      </c>
+      <c r="R34">
+        <v>1.67</v>
+      </c>
+      <c r="S34">
+        <v>2.04</v>
+      </c>
+      <c r="T34">
+        <v>1.01</v>
+      </c>
+      <c r="U34">
+        <v>1.01</v>
+      </c>
+      <c r="V34">
+        <v>1.16</v>
+      </c>
+      <c r="W34">
+        <v>2.72</v>
+      </c>
+      <c r="X34">
+        <v>40</v>
+      </c>
+      <c r="Y34">
+        <v>44</v>
+      </c>
+      <c r="Z34">
+        <v>85</v>
+      </c>
+      <c r="AA34">
+        <v>1000</v>
+      </c>
+      <c r="AB34">
+        <v>17.5</v>
+      </c>
+      <c r="AC34">
+        <v>17</v>
+      </c>
+      <c r="AD34">
+        <v>34</v>
+      </c>
+      <c r="AE34">
+        <v>100</v>
+      </c>
+      <c r="AF34">
+        <v>16</v>
+      </c>
+      <c r="AG34">
+        <v>15</v>
+      </c>
+      <c r="AH34">
+        <v>28</v>
+      </c>
+      <c r="AI34">
+        <v>90</v>
+      </c>
+      <c r="AJ34">
+        <v>21</v>
+      </c>
+      <c r="AK34">
+        <v>20</v>
+      </c>
+      <c r="AL34">
+        <v>38</v>
+      </c>
+      <c r="AM34">
+        <v>100</v>
+      </c>
+      <c r="AN34">
+        <v>1000</v>
+      </c>
+      <c r="AO34">
+        <v>1000</v>
+      </c>
+      <c r="AP34">
+        <v>1.99</v>
+      </c>
+      <c r="AQ34">
+        <v>2</v>
+      </c>
+      <c r="AR34">
+        <v>2.04</v>
+      </c>
+      <c r="AS34">
+        <v>2.1</v>
+      </c>
+      <c r="AT34">
+        <v>1.87</v>
+      </c>
+      <c r="AU34">
+        <v>1.87</v>
+      </c>
+      <c r="AV34">
+        <v>1.98</v>
+      </c>
+      <c r="AW34">
+        <v>2.06</v>
+      </c>
+      <c r="AX34">
+        <v>1.85</v>
+      </c>
+      <c r="AY34">
+        <v>1.84</v>
+      </c>
+      <c r="AZ34">
+        <v>1.95</v>
+      </c>
+      <c r="BA34">
+        <v>2.04</v>
+      </c>
+      <c r="BB34">
+        <v>1.91</v>
+      </c>
+      <c r="BC34">
+        <v>10</v>
+      </c>
+      <c r="BD34">
+        <v>1.99</v>
+      </c>
+      <c r="BE34">
+        <v>2.06</v>
+      </c>
+      <c r="BF34">
+        <v>2.1</v>
+      </c>
+      <c r="BG34">
+        <v>2.1</v>
+      </c>
+      <c r="BH34" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="35" spans="1:60">
+      <c r="A35" t="s">
+        <v>67</v>
+      </c>
+      <c r="B35" t="s">
+        <v>83</v>
+      </c>
+      <c r="C35" t="s">
+        <v>92</v>
+      </c>
+      <c r="D35" t="s">
+        <v>133</v>
+      </c>
+      <c r="E35" t="s">
+        <v>176</v>
+      </c>
+      <c r="F35">
+        <v>1.97</v>
+      </c>
+      <c r="G35">
+        <v>2.38</v>
+      </c>
+      <c r="H35">
+        <v>3.25</v>
+      </c>
+      <c r="I35">
+        <v>4.9</v>
+      </c>
+      <c r="J35">
+        <v>2.66</v>
+      </c>
+      <c r="K35">
+        <v>5.5</v>
+      </c>
+      <c r="L35">
+        <v>1.32</v>
+      </c>
+      <c r="M35">
+        <v>1.05</v>
+      </c>
+      <c r="N35">
+        <v>1.91</v>
+      </c>
+      <c r="O35">
+        <v>1.24</v>
+      </c>
+      <c r="P35">
+        <v>1.9</v>
+      </c>
+      <c r="Q35">
+        <v>1.66</v>
+      </c>
+      <c r="R35">
+        <v>1.35</v>
+      </c>
+      <c r="S35">
+        <v>2.62</v>
+      </c>
+      <c r="T35">
+        <v>1.01</v>
+      </c>
+      <c r="U35">
+        <v>1.01</v>
+      </c>
+      <c r="V35">
+        <v>1.25</v>
+      </c>
+      <c r="W35">
+        <v>1.72</v>
+      </c>
+      <c r="X35">
+        <v>1000</v>
+      </c>
+      <c r="Y35">
+        <v>1000</v>
+      </c>
+      <c r="Z35">
+        <v>1000</v>
+      </c>
+      <c r="AA35">
+        <v>1000</v>
+      </c>
+      <c r="AB35">
+        <v>1000</v>
+      </c>
+      <c r="AC35">
+        <v>1000</v>
+      </c>
+      <c r="AD35">
+        <v>1000</v>
+      </c>
+      <c r="AE35">
+        <v>1000</v>
+      </c>
+      <c r="AF35">
+        <v>1000</v>
+      </c>
+      <c r="AG35">
+        <v>1000</v>
+      </c>
+      <c r="AH35">
+        <v>1000</v>
+      </c>
+      <c r="AI35">
+        <v>1000</v>
+      </c>
+      <c r="AJ35">
+        <v>1000</v>
+      </c>
+      <c r="AK35">
+        <v>1000</v>
+      </c>
+      <c r="AL35">
+        <v>1000</v>
+      </c>
+      <c r="AM35">
+        <v>1000</v>
+      </c>
+      <c r="AN35">
+        <v>1000</v>
+      </c>
+      <c r="AO35">
+        <v>1000</v>
+      </c>
+      <c r="AP35">
+        <v>14</v>
+      </c>
+      <c r="AQ35">
+        <v>11.5</v>
+      </c>
+      <c r="AR35">
+        <v>19</v>
+      </c>
+      <c r="AS35">
+        <v>40</v>
+      </c>
+      <c r="AT35">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU35">
+        <v>6.6</v>
+      </c>
+      <c r="AV35">
+        <v>11</v>
+      </c>
+      <c r="AW35">
+        <v>27</v>
+      </c>
+      <c r="AX35">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY35">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ35">
+        <v>12.5</v>
+      </c>
+      <c r="BA35">
+        <v>29</v>
+      </c>
+      <c r="BB35">
+        <v>5</v>
+      </c>
+      <c r="BC35">
+        <v>15.5</v>
+      </c>
+      <c r="BD35">
+        <v>24</v>
+      </c>
+      <c r="BE35">
+        <v>40</v>
+      </c>
+      <c r="BF35">
+        <v>1.01</v>
+      </c>
+      <c r="BG35">
+        <v>1.01</v>
+      </c>
+      <c r="BH35" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="36" spans="1:60">
+      <c r="A36" t="s">
+        <v>68</v>
+      </c>
+      <c r="B36" t="s">
+        <v>83</v>
+      </c>
+      <c r="C36" t="s">
+        <v>93</v>
+      </c>
+      <c r="D36" t="s">
+        <v>134</v>
+      </c>
+      <c r="E36" t="s">
+        <v>177</v>
+      </c>
+      <c r="F36">
+        <v>1.64</v>
+      </c>
+      <c r="G36">
+        <v>1.66</v>
+      </c>
+      <c r="H36">
+        <v>5.9</v>
+      </c>
+      <c r="I36">
+        <v>6.2</v>
+      </c>
+      <c r="J36">
+        <v>4.2</v>
+      </c>
+      <c r="K36">
+        <v>4.5</v>
+      </c>
+      <c r="L36">
+        <v>1.37</v>
+      </c>
+      <c r="M36">
+        <v>1.06</v>
+      </c>
+      <c r="N36">
+        <v>3.9</v>
+      </c>
+      <c r="O36">
+        <v>1.32</v>
+      </c>
+      <c r="P36">
+        <v>2</v>
+      </c>
+      <c r="Q36">
+        <v>1.94</v>
+      </c>
+      <c r="R36">
+        <v>1.37</v>
+      </c>
+      <c r="S36">
+        <v>3.45</v>
+      </c>
+      <c r="T36">
+        <v>1.98</v>
+      </c>
+      <c r="U36">
+        <v>1.97</v>
+      </c>
+      <c r="V36">
+        <v>1.19</v>
+      </c>
+      <c r="W36">
+        <v>2.5</v>
+      </c>
+      <c r="X36">
+        <v>15.5</v>
+      </c>
+      <c r="Y36">
+        <v>19</v>
+      </c>
+      <c r="Z36">
+        <v>48</v>
+      </c>
+      <c r="AA36">
+        <v>180</v>
+      </c>
+      <c r="AB36">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC36">
+        <v>9.4</v>
+      </c>
+      <c r="AD36">
+        <v>23</v>
+      </c>
+      <c r="AE36">
+        <v>90</v>
+      </c>
+      <c r="AF36">
+        <v>9.4</v>
+      </c>
+      <c r="AG36">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AH36">
+        <v>23</v>
+      </c>
+      <c r="AI36">
+        <v>90</v>
+      </c>
+      <c r="AJ36">
+        <v>16</v>
+      </c>
+      <c r="AK36">
+        <v>17.5</v>
+      </c>
+      <c r="AL36">
+        <v>38</v>
+      </c>
+      <c r="AM36">
+        <v>140</v>
+      </c>
+      <c r="AN36">
+        <v>10</v>
+      </c>
+      <c r="AO36">
+        <v>110</v>
+      </c>
+      <c r="AP36">
+        <v>14.5</v>
+      </c>
+      <c r="AQ36">
+        <v>17.5</v>
+      </c>
+      <c r="AR36">
+        <v>42</v>
+      </c>
+      <c r="AS36">
+        <v>44</v>
+      </c>
+      <c r="AT36">
+        <v>7.8</v>
+      </c>
+      <c r="AU36">
+        <v>9</v>
+      </c>
+      <c r="AV36">
+        <v>21</v>
+      </c>
+      <c r="AW36">
+        <v>34</v>
+      </c>
+      <c r="AX36">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY36">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ36">
+        <v>21</v>
+      </c>
+      <c r="BA36">
+        <v>36</v>
+      </c>
+      <c r="BB36">
+        <v>14.5</v>
+      </c>
+      <c r="BC36">
+        <v>16</v>
+      </c>
+      <c r="BD36">
+        <v>32</v>
+      </c>
+      <c r="BE36">
+        <v>42</v>
+      </c>
+      <c r="BF36">
+        <v>9</v>
+      </c>
+      <c r="BG36">
+        <v>38</v>
+      </c>
+      <c r="BH36" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="37" spans="1:60">
+      <c r="A37" t="s">
+        <v>61</v>
+      </c>
+      <c r="B37" t="s">
+        <v>83</v>
+      </c>
+      <c r="C37" t="s">
+        <v>94</v>
+      </c>
+      <c r="D37" t="s">
+        <v>135</v>
+      </c>
+      <c r="E37" t="s">
+        <v>178</v>
+      </c>
+      <c r="F37">
+        <v>6.8</v>
+      </c>
+      <c r="G37">
+        <v>7</v>
+      </c>
+      <c r="H37">
+        <v>1.5</v>
+      </c>
+      <c r="I37">
+        <v>1.51</v>
+      </c>
+      <c r="J37">
+        <v>5.1</v>
+      </c>
+      <c r="K37">
+        <v>5.2</v>
+      </c>
+      <c r="L37">
+        <v>1.32</v>
+      </c>
+      <c r="M37">
+        <v>1.04</v>
+      </c>
+      <c r="N37">
+        <v>5.1</v>
+      </c>
+      <c r="O37">
+        <v>1.23</v>
+      </c>
+      <c r="P37">
+        <v>2.42</v>
+      </c>
+      <c r="Q37">
+        <v>1.67</v>
+      </c>
+      <c r="R37">
+        <v>1.54</v>
+      </c>
+      <c r="S37">
+        <v>2.74</v>
+      </c>
+      <c r="T37">
+        <v>1.84</v>
+      </c>
+      <c r="U37">
+        <v>2.14</v>
+      </c>
+      <c r="V37">
+        <v>2.96</v>
+      </c>
+      <c r="W37">
+        <v>1.16</v>
+      </c>
+      <c r="X37">
+        <v>24</v>
+      </c>
+      <c r="Y37">
+        <v>9.4</v>
+      </c>
+      <c r="Z37">
+        <v>9.4</v>
+      </c>
+      <c r="AA37">
+        <v>13.5</v>
+      </c>
+      <c r="AB37">
+        <v>27</v>
+      </c>
+      <c r="AC37">
+        <v>11</v>
+      </c>
+      <c r="AD37">
+        <v>9.6</v>
+      </c>
+      <c r="AE37">
+        <v>14</v>
+      </c>
+      <c r="AF37">
+        <v>60</v>
+      </c>
+      <c r="AG37">
+        <v>26</v>
+      </c>
+      <c r="AH37">
+        <v>21</v>
+      </c>
+      <c r="AI37">
+        <v>29</v>
+      </c>
+      <c r="AJ37">
+        <v>190</v>
+      </c>
+      <c r="AK37">
+        <v>90</v>
+      </c>
+      <c r="AL37">
+        <v>75</v>
+      </c>
+      <c r="AM37">
+        <v>100</v>
+      </c>
+      <c r="AN37">
+        <v>85</v>
+      </c>
+      <c r="AO37">
+        <v>6.6</v>
+      </c>
+      <c r="AP37">
+        <v>21</v>
+      </c>
+      <c r="AQ37">
+        <v>9</v>
+      </c>
+      <c r="AR37">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AS37">
+        <v>13</v>
+      </c>
+      <c r="AT37">
+        <v>25</v>
+      </c>
+      <c r="AU37">
+        <v>10.5</v>
+      </c>
+      <c r="AV37">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW37">
+        <v>13.5</v>
+      </c>
+      <c r="AX37">
+        <v>50</v>
+      </c>
+      <c r="AY37">
+        <v>23</v>
+      </c>
+      <c r="AZ37">
+        <v>20</v>
+      </c>
+      <c r="BA37">
+        <v>27</v>
+      </c>
+      <c r="BB37">
+        <v>90</v>
+      </c>
+      <c r="BC37">
+        <v>80</v>
+      </c>
+      <c r="BD37">
+        <v>55</v>
+      </c>
+      <c r="BE37">
+        <v>70</v>
+      </c>
+      <c r="BF37">
+        <v>75</v>
+      </c>
+      <c r="BG37">
+        <v>6.2</v>
+      </c>
+      <c r="BH37" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="38" spans="1:60">
+      <c r="A38" t="s">
+        <v>77</v>
+      </c>
+      <c r="B38" t="s">
+        <v>83</v>
+      </c>
+      <c r="C38" t="s">
+        <v>94</v>
+      </c>
+      <c r="D38" t="s">
+        <v>136</v>
+      </c>
+      <c r="E38" t="s">
+        <v>179</v>
+      </c>
+      <c r="F38">
+        <v>2.5</v>
+      </c>
+      <c r="G38">
+        <v>2.54</v>
+      </c>
+      <c r="H38">
+        <v>3</v>
+      </c>
+      <c r="I38">
+        <v>3.1</v>
+      </c>
+      <c r="J38">
+        <v>3.6</v>
+      </c>
+      <c r="K38">
+        <v>3.65</v>
+      </c>
+      <c r="L38">
+        <v>1.39</v>
+      </c>
+      <c r="M38">
+        <v>1.07</v>
+      </c>
+      <c r="N38">
+        <v>3.8</v>
+      </c>
+      <c r="O38">
+        <v>1.33</v>
+      </c>
+      <c r="P38">
+        <v>1.95</v>
+      </c>
+      <c r="Q38">
+        <v>2.02</v>
+      </c>
+      <c r="R38">
+        <v>1.36</v>
+      </c>
+      <c r="S38">
+        <v>3.55</v>
+      </c>
+      <c r="T38">
+        <v>1.8</v>
+      </c>
+      <c r="U38">
+        <v>2.18</v>
+      </c>
+      <c r="V38">
+        <v>1.47</v>
+      </c>
+      <c r="W38">
+        <v>1.64</v>
+      </c>
+      <c r="X38">
+        <v>14</v>
+      </c>
+      <c r="Y38">
+        <v>12.5</v>
+      </c>
+      <c r="Z38">
+        <v>20</v>
+      </c>
+      <c r="AA38">
+        <v>50</v>
+      </c>
+      <c r="AB38">
+        <v>10.5</v>
+      </c>
+      <c r="AC38">
+        <v>7.8</v>
+      </c>
+      <c r="AD38">
+        <v>13</v>
+      </c>
+      <c r="AE38">
+        <v>36</v>
+      </c>
+      <c r="AF38">
+        <v>16</v>
+      </c>
+      <c r="AG38">
+        <v>11.5</v>
+      </c>
+      <c r="AH38">
+        <v>17.5</v>
+      </c>
+      <c r="AI38">
+        <v>46</v>
+      </c>
+      <c r="AJ38">
+        <v>36</v>
+      </c>
+      <c r="AK38">
+        <v>27</v>
+      </c>
+      <c r="AL38">
+        <v>40</v>
+      </c>
+      <c r="AM38">
+        <v>95</v>
+      </c>
+      <c r="AN38">
+        <v>22</v>
+      </c>
+      <c r="AO38">
+        <v>32</v>
+      </c>
+      <c r="AP38">
+        <v>13</v>
+      </c>
+      <c r="AQ38">
+        <v>11.5</v>
+      </c>
+      <c r="AR38">
+        <v>19</v>
+      </c>
+      <c r="AS38">
+        <v>44</v>
+      </c>
+      <c r="AT38">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU38">
+        <v>7.4</v>
+      </c>
+      <c r="AV38">
+        <v>12</v>
+      </c>
+      <c r="AW38">
+        <v>30</v>
+      </c>
+      <c r="AX38">
+        <v>15</v>
+      </c>
+      <c r="AY38">
+        <v>10.5</v>
+      </c>
+      <c r="AZ38">
+        <v>16</v>
+      </c>
+      <c r="BA38">
+        <v>40</v>
+      </c>
+      <c r="BB38">
+        <v>32</v>
+      </c>
+      <c r="BC38">
+        <v>25</v>
+      </c>
+      <c r="BD38">
+        <v>34</v>
+      </c>
+      <c r="BE38">
+        <v>38</v>
+      </c>
+      <c r="BF38">
+        <v>20</v>
+      </c>
+      <c r="BG38">
+        <v>28</v>
+      </c>
+      <c r="BH38" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="39" spans="1:60">
+      <c r="A39" t="s">
+        <v>78</v>
+      </c>
+      <c r="B39" t="s">
+        <v>83</v>
+      </c>
+      <c r="C39" t="s">
+        <v>95</v>
+      </c>
+      <c r="D39" t="s">
+        <v>137</v>
+      </c>
+      <c r="E39" t="s">
+        <v>180</v>
+      </c>
+      <c r="F39">
+        <v>1.29</v>
+      </c>
+      <c r="G39">
+        <v>1.32</v>
+      </c>
+      <c r="H39">
+        <v>12</v>
+      </c>
+      <c r="I39">
+        <v>13</v>
+      </c>
+      <c r="J39">
+        <v>6</v>
+      </c>
+      <c r="K39">
+        <v>6.8</v>
+      </c>
+      <c r="L39">
+        <v>1.25</v>
+      </c>
+      <c r="M39">
+        <v>1.03</v>
+      </c>
+      <c r="N39">
+        <v>2.62</v>
+      </c>
+      <c r="O39">
+        <v>1.14</v>
+      </c>
+      <c r="P39">
+        <v>2.62</v>
+      </c>
+      <c r="Q39">
+        <v>1.51</v>
+      </c>
+      <c r="R39">
+        <v>1.56</v>
+      </c>
+      <c r="S39">
+        <v>2.04</v>
+      </c>
+      <c r="T39">
+        <v>1.01</v>
+      </c>
+      <c r="U39">
+        <v>1.01</v>
+      </c>
+      <c r="V39">
+        <v>1.08</v>
+      </c>
+      <c r="W39">
+        <v>4.1</v>
+      </c>
+      <c r="X39">
+        <v>36</v>
+      </c>
+      <c r="Y39">
+        <v>60</v>
+      </c>
+      <c r="Z39">
+        <v>1000</v>
+      </c>
+      <c r="AA39">
+        <v>1000</v>
+      </c>
+      <c r="AB39">
+        <v>15</v>
+      </c>
+      <c r="AC39">
+        <v>20</v>
+      </c>
+      <c r="AD39">
+        <v>60</v>
+      </c>
+      <c r="AE39">
+        <v>1000</v>
+      </c>
+      <c r="AF39">
+        <v>12.5</v>
+      </c>
+      <c r="AG39">
+        <v>15.5</v>
+      </c>
+      <c r="AH39">
+        <v>40</v>
+      </c>
+      <c r="AI39">
+        <v>1000</v>
+      </c>
+      <c r="AJ39">
+        <v>14.5</v>
+      </c>
+      <c r="AK39">
+        <v>19</v>
+      </c>
+      <c r="AL39">
+        <v>48</v>
+      </c>
+      <c r="AM39">
+        <v>1000</v>
+      </c>
+      <c r="AN39">
+        <v>1000</v>
+      </c>
+      <c r="AO39">
+        <v>1000</v>
+      </c>
+      <c r="AP39">
+        <v>1.85</v>
+      </c>
+      <c r="AQ39">
+        <v>1.89</v>
+      </c>
+      <c r="AR39">
+        <v>1.95</v>
+      </c>
+      <c r="AS39">
+        <v>1.95</v>
+      </c>
+      <c r="AT39">
+        <v>1.73</v>
+      </c>
+      <c r="AU39">
+        <v>1.78</v>
+      </c>
+      <c r="AV39">
+        <v>1.89</v>
+      </c>
+      <c r="AW39">
+        <v>1.95</v>
+      </c>
+      <c r="AX39">
+        <v>1.69</v>
+      </c>
+      <c r="AY39">
+        <v>1.73</v>
+      </c>
+      <c r="AZ39">
+        <v>1.86</v>
+      </c>
+      <c r="BA39">
+        <v>1.95</v>
+      </c>
+      <c r="BB39">
+        <v>1.72</v>
+      </c>
+      <c r="BC39">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BD39">
+        <v>1.88</v>
+      </c>
+      <c r="BE39">
+        <v>1.95</v>
+      </c>
+      <c r="BF39">
+        <v>1.95</v>
+      </c>
+      <c r="BG39">
+        <v>1.95</v>
+      </c>
+      <c r="BH39" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="40" spans="1:60">
+      <c r="A40" t="s">
+        <v>79</v>
+      </c>
+      <c r="B40" t="s">
+        <v>83</v>
+      </c>
+      <c r="C40" t="s">
+        <v>96</v>
+      </c>
+      <c r="D40" t="s">
+        <v>138</v>
+      </c>
+      <c r="E40" t="s">
+        <v>181</v>
+      </c>
+      <c r="F40">
+        <v>2.36</v>
+      </c>
+      <c r="G40">
+        <v>2.56</v>
+      </c>
+      <c r="H40">
+        <v>3.5</v>
+      </c>
+      <c r="I40">
+        <v>4.1</v>
+      </c>
+      <c r="J40">
+        <v>2.9</v>
+      </c>
+      <c r="K40">
+        <v>3.2</v>
+      </c>
+      <c r="L40">
+        <v>1.01</v>
+      </c>
+      <c r="M40">
+        <v>1.15</v>
+      </c>
+      <c r="N40">
+        <v>2.28</v>
+      </c>
+      <c r="O40">
+        <v>1.68</v>
+      </c>
+      <c r="P40">
+        <v>1.44</v>
+      </c>
+      <c r="Q40">
+        <v>3</v>
+      </c>
+      <c r="R40">
+        <v>1.14</v>
+      </c>
+      <c r="S40">
+        <v>6.8</v>
+      </c>
+      <c r="T40">
+        <v>2.2</v>
+      </c>
+      <c r="U40">
+        <v>1.62</v>
+      </c>
+      <c r="V40">
+        <v>1.33</v>
+      </c>
+      <c r="W40">
+        <v>1.64</v>
+      </c>
+      <c r="X40">
+        <v>8.4</v>
+      </c>
+      <c r="Y40">
+        <v>9.6</v>
+      </c>
+      <c r="Z40">
+        <v>26</v>
+      </c>
+      <c r="AA40">
+        <v>110</v>
+      </c>
+      <c r="AB40">
+        <v>7</v>
+      </c>
+      <c r="AC40">
+        <v>7.6</v>
+      </c>
+      <c r="AD40">
+        <v>21</v>
+      </c>
+      <c r="AE40">
+        <v>80</v>
+      </c>
+      <c r="AF40">
+        <v>14.5</v>
+      </c>
+      <c r="AG40">
+        <v>15</v>
+      </c>
+      <c r="AH40">
+        <v>30</v>
+      </c>
+      <c r="AI40">
+        <v>130</v>
+      </c>
+      <c r="AJ40">
+        <v>46</v>
+      </c>
+      <c r="AK40">
+        <v>44</v>
+      </c>
+      <c r="AL40">
+        <v>95</v>
+      </c>
+      <c r="AM40">
+        <v>320</v>
+      </c>
+      <c r="AN40">
+        <v>60</v>
+      </c>
+      <c r="AO40">
+        <v>140</v>
+      </c>
+      <c r="AP40">
+        <v>6.2</v>
+      </c>
+      <c r="AQ40">
+        <v>7.8</v>
+      </c>
+      <c r="AR40">
+        <v>21</v>
+      </c>
+      <c r="AS40">
+        <v>6.8</v>
+      </c>
+      <c r="AT40">
+        <v>5.8</v>
+      </c>
+      <c r="AU40">
+        <v>6.2</v>
+      </c>
+      <c r="AV40">
+        <v>15</v>
+      </c>
+      <c r="AW40">
+        <v>6.6</v>
+      </c>
+      <c r="AX40">
+        <v>11.5</v>
+      </c>
+      <c r="AY40">
+        <v>11</v>
+      </c>
+      <c r="AZ40">
+        <v>5.9</v>
+      </c>
+      <c r="BA40">
+        <v>6.8</v>
+      </c>
+      <c r="BB40">
+        <v>6.2</v>
+      </c>
+      <c r="BC40">
+        <v>6.2</v>
+      </c>
+      <c r="BD40">
+        <v>6.8</v>
+      </c>
+      <c r="BE40">
+        <v>7</v>
+      </c>
+      <c r="BF40">
+        <v>36</v>
+      </c>
+      <c r="BG40">
+        <v>6.8</v>
+      </c>
+      <c r="BH40" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="41" spans="1:60">
+      <c r="A41" t="s">
+        <v>80</v>
+      </c>
+      <c r="B41" t="s">
+        <v>83</v>
+      </c>
+      <c r="C41" t="s">
+        <v>97</v>
+      </c>
+      <c r="D41" t="s">
+        <v>139</v>
+      </c>
+      <c r="E41" t="s">
+        <v>182</v>
+      </c>
+      <c r="F41">
+        <v>1.34</v>
+      </c>
+      <c r="G41">
+        <v>1.62</v>
+      </c>
+      <c r="H41">
+        <v>2.68</v>
+      </c>
+      <c r="I41">
+        <v>100</v>
+      </c>
+      <c r="J41">
+        <v>2.68</v>
+      </c>
+      <c r="K41">
+        <v>85</v>
+      </c>
+      <c r="L41">
+        <v>0</v>
+      </c>
+      <c r="M41">
+        <v>0</v>
+      </c>
+      <c r="N41">
+        <v>0</v>
+      </c>
+      <c r="O41">
+        <v>0</v>
+      </c>
+      <c r="P41">
+        <v>1.91</v>
+      </c>
+      <c r="Q41">
+        <v>1.63</v>
+      </c>
+      <c r="R41">
+        <v>0</v>
+      </c>
+      <c r="S41">
+        <v>0</v>
+      </c>
+      <c r="T41">
+        <v>0</v>
+      </c>
+      <c r="U41">
+        <v>0</v>
+      </c>
+      <c r="V41">
+        <v>0</v>
+      </c>
+      <c r="W41">
+        <v>0</v>
+      </c>
+      <c r="X41">
+        <v>0</v>
+      </c>
+      <c r="Y41">
+        <v>0</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+      <c r="AA41">
+        <v>0</v>
+      </c>
+      <c r="AB41">
+        <v>0</v>
+      </c>
+      <c r="AC41">
+        <v>0</v>
+      </c>
+      <c r="AD41">
+        <v>0</v>
+      </c>
+      <c r="AE41">
+        <v>0</v>
+      </c>
+      <c r="AF41">
+        <v>0</v>
+      </c>
+      <c r="AG41">
+        <v>0</v>
+      </c>
+      <c r="AH41">
+        <v>0</v>
+      </c>
+      <c r="AI41">
+        <v>0</v>
+      </c>
+      <c r="AJ41">
+        <v>0</v>
+      </c>
+      <c r="AK41">
+        <v>0</v>
+      </c>
+      <c r="AL41">
+        <v>0</v>
+      </c>
+      <c r="AM41">
+        <v>0</v>
+      </c>
+      <c r="AN41">
+        <v>0</v>
+      </c>
+      <c r="AO41">
+        <v>0</v>
+      </c>
+      <c r="AP41">
+        <v>0</v>
+      </c>
+      <c r="AQ41">
+        <v>0</v>
+      </c>
+      <c r="AR41">
+        <v>0</v>
+      </c>
+      <c r="AS41">
+        <v>0</v>
+      </c>
+      <c r="AT41">
+        <v>0</v>
+      </c>
+      <c r="AU41">
+        <v>0</v>
+      </c>
+      <c r="AV41">
+        <v>0</v>
+      </c>
+      <c r="AW41">
+        <v>0</v>
+      </c>
+      <c r="AX41">
+        <v>0</v>
+      </c>
+      <c r="AY41">
+        <v>0</v>
+      </c>
+      <c r="AZ41">
+        <v>0</v>
+      </c>
+      <c r="BA41">
+        <v>0</v>
+      </c>
+      <c r="BB41">
+        <v>0</v>
+      </c>
+      <c r="BC41">
+        <v>0</v>
+      </c>
+      <c r="BD41">
+        <v>0</v>
+      </c>
+      <c r="BE41">
+        <v>0</v>
+      </c>
+      <c r="BF41">
+        <v>0</v>
+      </c>
+      <c r="BG41">
+        <v>0</v>
+      </c>
+      <c r="BH41" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="42" spans="1:60">
+      <c r="A42" t="s">
+        <v>81</v>
+      </c>
+      <c r="B42" t="s">
+        <v>83</v>
+      </c>
+      <c r="C42" t="s">
+        <v>98</v>
+      </c>
+      <c r="D42" t="s">
+        <v>140</v>
+      </c>
+      <c r="E42" t="s">
+        <v>183</v>
+      </c>
+      <c r="F42">
+        <v>1.55</v>
+      </c>
+      <c r="G42">
+        <v>2.64</v>
+      </c>
+      <c r="H42">
+        <v>2.84</v>
+      </c>
+      <c r="I42">
+        <v>4.5</v>
+      </c>
+      <c r="J42">
+        <v>3.05</v>
+      </c>
+      <c r="K42">
+        <v>150</v>
+      </c>
+      <c r="L42">
+        <v>0</v>
+      </c>
+      <c r="M42">
+        <v>0</v>
+      </c>
+      <c r="N42">
+        <v>0</v>
+      </c>
+      <c r="O42">
+        <v>0</v>
+      </c>
+      <c r="P42">
+        <v>1.96</v>
+      </c>
+      <c r="Q42">
+        <v>1.69</v>
+      </c>
+      <c r="R42">
+        <v>0</v>
+      </c>
+      <c r="S42">
+        <v>0</v>
+      </c>
+      <c r="T42">
+        <v>0</v>
+      </c>
+      <c r="U42">
+        <v>0</v>
+      </c>
+      <c r="V42">
+        <v>0</v>
+      </c>
+      <c r="W42">
+        <v>0</v>
+      </c>
+      <c r="X42">
+        <v>0</v>
+      </c>
+      <c r="Y42">
+        <v>0</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+      <c r="AA42">
+        <v>0</v>
+      </c>
+      <c r="AB42">
+        <v>0</v>
+      </c>
+      <c r="AC42">
+        <v>0</v>
+      </c>
+      <c r="AD42">
+        <v>0</v>
+      </c>
+      <c r="AE42">
+        <v>0</v>
+      </c>
+      <c r="AF42">
+        <v>0</v>
+      </c>
+      <c r="AG42">
+        <v>0</v>
+      </c>
+      <c r="AH42">
+        <v>0</v>
+      </c>
+      <c r="AI42">
+        <v>0</v>
+      </c>
+      <c r="AJ42">
+        <v>0</v>
+      </c>
+      <c r="AK42">
+        <v>0</v>
+      </c>
+      <c r="AL42">
+        <v>0</v>
+      </c>
+      <c r="AM42">
+        <v>0</v>
+      </c>
+      <c r="AN42">
+        <v>0</v>
+      </c>
+      <c r="AO42">
+        <v>0</v>
+      </c>
+      <c r="AP42">
+        <v>0</v>
+      </c>
+      <c r="AQ42">
+        <v>0</v>
+      </c>
+      <c r="AR42">
+        <v>0</v>
+      </c>
+      <c r="AS42">
+        <v>0</v>
+      </c>
+      <c r="AT42">
+        <v>0</v>
+      </c>
+      <c r="AU42">
+        <v>0</v>
+      </c>
+      <c r="AV42">
+        <v>0</v>
+      </c>
+      <c r="AW42">
+        <v>0</v>
+      </c>
+      <c r="AX42">
+        <v>0</v>
+      </c>
+      <c r="AY42">
+        <v>0</v>
+      </c>
+      <c r="AZ42">
+        <v>0</v>
+      </c>
+      <c r="BA42">
+        <v>0</v>
+      </c>
+      <c r="BB42">
+        <v>0</v>
+      </c>
+      <c r="BC42">
+        <v>0</v>
+      </c>
+      <c r="BD42">
+        <v>0</v>
+      </c>
+      <c r="BE42">
+        <v>0</v>
+      </c>
+      <c r="BF42">
+        <v>0</v>
+      </c>
+      <c r="BG42">
+        <v>0</v>
+      </c>
+      <c r="BH42" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="43" spans="1:60">
+      <c r="A43" t="s">
+        <v>82</v>
+      </c>
+      <c r="B43" t="s">
+        <v>83</v>
+      </c>
+      <c r="C43" t="s">
+        <v>98</v>
+      </c>
+      <c r="D43" t="s">
+        <v>141</v>
+      </c>
+      <c r="E43" t="s">
+        <v>184</v>
+      </c>
+      <c r="F43">
+        <v>0</v>
+      </c>
+      <c r="G43">
+        <v>0</v>
+      </c>
+      <c r="H43">
+        <v>0</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>0</v>
+      </c>
+      <c r="K43">
+        <v>0</v>
+      </c>
+      <c r="L43">
+        <v>0</v>
+      </c>
+      <c r="M43">
+        <v>0</v>
+      </c>
+      <c r="N43">
+        <v>0</v>
+      </c>
+      <c r="O43">
+        <v>0</v>
+      </c>
+      <c r="P43">
+        <v>1.78</v>
+      </c>
+      <c r="Q43">
+        <v>1.01</v>
+      </c>
+      <c r="R43">
+        <v>0</v>
+      </c>
+      <c r="S43">
+        <v>0</v>
+      </c>
+      <c r="T43">
+        <v>0</v>
+      </c>
+      <c r="U43">
+        <v>0</v>
+      </c>
+      <c r="V43">
+        <v>0</v>
+      </c>
+      <c r="W43">
+        <v>0</v>
+      </c>
+      <c r="X43">
+        <v>0</v>
+      </c>
+      <c r="Y43">
+        <v>0</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+      <c r="AA43">
+        <v>0</v>
+      </c>
+      <c r="AB43">
+        <v>0</v>
+      </c>
+      <c r="AC43">
+        <v>0</v>
+      </c>
+      <c r="AD43">
+        <v>0</v>
+      </c>
+      <c r="AE43">
+        <v>0</v>
+      </c>
+      <c r="AF43">
+        <v>0</v>
+      </c>
+      <c r="AG43">
+        <v>0</v>
+      </c>
+      <c r="AH43">
+        <v>0</v>
+      </c>
+      <c r="AI43">
+        <v>0</v>
+      </c>
+      <c r="AJ43">
+        <v>0</v>
+      </c>
+      <c r="AK43">
+        <v>0</v>
+      </c>
+      <c r="AL43">
+        <v>0</v>
+      </c>
+      <c r="AM43">
+        <v>0</v>
+      </c>
+      <c r="AN43">
+        <v>0</v>
+      </c>
+      <c r="AO43">
+        <v>0</v>
+      </c>
+      <c r="AP43">
+        <v>0</v>
+      </c>
+      <c r="AQ43">
+        <v>0</v>
+      </c>
+      <c r="AR43">
+        <v>0</v>
+      </c>
+      <c r="AS43">
+        <v>0</v>
+      </c>
+      <c r="AT43">
+        <v>0</v>
+      </c>
+      <c r="AU43">
+        <v>0</v>
+      </c>
+      <c r="AV43">
+        <v>0</v>
+      </c>
+      <c r="AW43">
+        <v>0</v>
+      </c>
+      <c r="AX43">
+        <v>0</v>
+      </c>
+      <c r="AY43">
+        <v>0</v>
+      </c>
+      <c r="AZ43">
+        <v>0</v>
+      </c>
+      <c r="BA43">
+        <v>0</v>
+      </c>
+      <c r="BB43">
+        <v>0</v>
+      </c>
+      <c r="BC43">
+        <v>0</v>
+      </c>
+      <c r="BD43">
+        <v>0</v>
+      </c>
+      <c r="BE43">
+        <v>0</v>
+      </c>
+      <c r="BF43">
+        <v>0</v>
+      </c>
+      <c r="BG43">
+        <v>0</v>
+      </c>
+      <c r="BH43" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="44" spans="1:60">
+      <c r="A44" t="s">
+        <v>79</v>
+      </c>
+      <c r="B44" t="s">
+        <v>83</v>
+      </c>
+      <c r="C44" t="s">
+        <v>99</v>
+      </c>
+      <c r="D44" t="s">
+        <v>142</v>
+      </c>
+      <c r="E44" t="s">
+        <v>185</v>
+      </c>
+      <c r="F44">
         <v>1.61</v>
       </c>
-      <c r="G31">
+      <c r="G44">
         <v>1.74</v>
       </c>
-      <c r="H31">
+      <c r="H44">
         <v>6.4</v>
       </c>
-      <c r="I31">
+      <c r="I44">
         <v>7.8</v>
       </c>
-      <c r="J31">
+      <c r="J44">
         <v>3.55</v>
       </c>
-      <c r="K31">
+      <c r="K44">
         <v>4.5</v>
       </c>
-      <c r="L31">
-        <v>1.01</v>
-      </c>
-      <c r="M31">
+      <c r="L44">
+        <v>1.43</v>
+      </c>
+      <c r="M44">
         <v>1.09</v>
       </c>
-      <c r="N31">
+      <c r="N44">
         <v>2.92</v>
       </c>
-      <c r="O31">
+      <c r="O44">
         <v>1.44</v>
       </c>
-      <c r="P31">
+      <c r="P44">
         <v>1.65</v>
       </c>
-      <c r="Q31">
-        <v>2.26</v>
-      </c>
-      <c r="R31">
+      <c r="Q44">
+        <v>2.18</v>
+      </c>
+      <c r="R44">
         <v>1.23</v>
       </c>
-      <c r="S31">
+      <c r="S44">
         <v>4.4</v>
       </c>
-      <c r="T31">
-        <v>2.16</v>
-      </c>
-      <c r="U31">
-        <v>1.68</v>
-      </c>
-      <c r="V31">
+      <c r="T44">
+        <v>2.2</v>
+      </c>
+      <c r="U44">
+        <v>1.7</v>
+      </c>
+      <c r="V44">
         <v>1.14</v>
       </c>
-      <c r="W31">
+      <c r="W44">
         <v>2.34</v>
       </c>
-      <c r="X31">
+      <c r="X44">
         <v>12.5</v>
       </c>
-      <c r="Y31">
+      <c r="Y44">
         <v>21</v>
       </c>
-      <c r="Z31">
+      <c r="Z44">
         <v>70</v>
       </c>
-      <c r="AA31">
+      <c r="AA44">
         <v>300</v>
       </c>
-      <c r="AB31">
+      <c r="AB44">
         <v>7.4</v>
       </c>
-      <c r="AC31">
+      <c r="AC44">
         <v>10</v>
       </c>
-      <c r="AD31">
+      <c r="AD44">
         <v>34</v>
       </c>
-      <c r="AE31">
+      <c r="AE44">
         <v>160</v>
       </c>
-      <c r="AF31">
+      <c r="AF44">
         <v>10</v>
       </c>
-      <c r="AG31">
+      <c r="AG44">
         <v>12</v>
       </c>
-      <c r="AH31">
+      <c r="AH44">
         <v>29</v>
       </c>
-      <c r="AI31">
+      <c r="AI44">
         <v>160</v>
       </c>
-      <c r="AJ31">
+      <c r="AJ44">
         <v>19.5</v>
       </c>
-      <c r="AK31">
+      <c r="AK44">
         <v>23</v>
       </c>
-      <c r="AL31">
+      <c r="AL44">
         <v>65</v>
       </c>
-      <c r="AM31">
+      <c r="AM44">
         <v>250</v>
       </c>
-      <c r="AN31">
+      <c r="AN44">
         <v>17</v>
       </c>
-      <c r="AO31">
+      <c r="AO44">
         <v>280</v>
       </c>
-      <c r="AP31">
+      <c r="AP44">
         <v>3.85</v>
       </c>
-      <c r="AQ31">
+      <c r="AQ44">
         <v>14.5</v>
       </c>
-      <c r="AR31">
+      <c r="AR44">
         <v>5.1</v>
       </c>
-      <c r="AS31">
+      <c r="AS44">
         <v>5.5</v>
       </c>
-      <c r="AT31">
+      <c r="AT44">
         <v>5.6</v>
       </c>
-      <c r="AU31">
+      <c r="AU44">
         <v>7.4</v>
       </c>
-      <c r="AV31">
+      <c r="AV44">
         <v>4.7</v>
       </c>
-      <c r="AW31">
+      <c r="AW44">
         <v>5.4</v>
       </c>
-      <c r="AX31">
+      <c r="AX44">
         <v>7.4</v>
       </c>
-      <c r="AY31">
+      <c r="AY44">
         <v>3.8</v>
       </c>
-      <c r="AZ31">
+      <c r="AZ44">
         <v>4.7</v>
       </c>
-      <c r="BA31">
+      <c r="BA44">
         <v>5.4</v>
       </c>
-      <c r="BB31">
+      <c r="BB44">
         <v>14</v>
       </c>
-      <c r="BC31">
+      <c r="BC44">
         <v>4.5</v>
       </c>
-      <c r="BD31">
+      <c r="BD44">
         <v>5.1</v>
       </c>
-      <c r="BE31">
+      <c r="BE44">
         <v>5.4</v>
       </c>
-      <c r="BF31">
+      <c r="BF44">
         <v>11</v>
       </c>
-      <c r="BG31">
+      <c r="BG44">
         <v>5.5</v>
       </c>
-      <c r="BH31" t="s">
-        <v>147</v>
+      <c r="BH44" t="s">
+        <v>186</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-04.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="191">
   <si>
     <t>League</t>
   </si>
@@ -238,10 +238,13 @@
     <t>Israeli Premier League</t>
   </si>
   <si>
+    <t>Danish Superliga</t>
+  </si>
+  <si>
     <t>Norwegian Eliteserien</t>
   </si>
   <si>
-    <t>Danish Superliga</t>
+    <t>Swedish Superettan</t>
   </si>
   <si>
     <t>Spanish Segunda Division</t>
@@ -259,12 +262,12 @@
     <t>Colombian Primera B</t>
   </si>
   <si>
+    <t>Brazilian Serie B</t>
+  </si>
+  <si>
     <t>Chilean Primera B</t>
   </si>
   <si>
-    <t>Brazilian Serie B</t>
-  </si>
-  <si>
     <t>2026-05-04</t>
   </si>
   <si>
@@ -286,6 +289,9 @@
     <t>14:00:00</t>
   </si>
   <si>
+    <t>14:05:00</t>
+  </si>
+  <si>
     <t>14:30:00</t>
   </si>
   <si>
@@ -391,16 +397,19 @@
     <t>Maccabi Netanya</t>
   </si>
   <si>
+    <t>Wadi Degla</t>
+  </si>
+  <si>
+    <t>Al Ittihad (EGY)</t>
+  </si>
+  <si>
+    <t>Midtjylland</t>
+  </si>
+  <si>
     <t>Bodo Glimt</t>
   </si>
   <si>
-    <t>Wadi Degla</t>
-  </si>
-  <si>
-    <t>Al Ittihad (EGY)</t>
-  </si>
-  <si>
-    <t>Midtjylland</t>
+    <t>Landskrona</t>
   </si>
   <si>
     <t>Rapid Bucharest</t>
@@ -436,12 +445,12 @@
     <t>Union Magdalena</t>
   </si>
   <si>
+    <t>Vila Nova</t>
+  </si>
+  <si>
     <t>San Luis</t>
   </si>
   <si>
-    <t>Vila Nova</t>
-  </si>
-  <si>
     <t>Velez Sarsfield</t>
   </si>
   <si>
@@ -520,16 +529,19 @@
     <t>Hapoel Jerusalem</t>
   </si>
   <si>
+    <t>Kahraba Ismailia</t>
+  </si>
+  <si>
+    <t>Petrojet</t>
+  </si>
+  <si>
+    <t>Viborg</t>
+  </si>
+  <si>
     <t>Molde</t>
   </si>
   <si>
-    <t>Kahraba Ismailia</t>
-  </si>
-  <si>
-    <t>Petrojet</t>
-  </si>
-  <si>
-    <t>Viborg</t>
+    <t>Osters</t>
   </si>
   <si>
     <t>CFR Cluj</t>
@@ -565,16 +577,16 @@
     <t>Barranquilla</t>
   </si>
   <si>
+    <t>Athletic Club</t>
+  </si>
+  <si>
     <t>Union San Felipe</t>
   </si>
   <si>
-    <t>Athletic Club</t>
-  </si>
-  <si>
     <t>Newells</t>
   </si>
   <si>
-    <t>2026-05-02 16:41:25</t>
+    <t>2026-05-02 19:11:45</t>
   </si>
 </sst>
 </file>
@@ -932,7 +944,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BH44"/>
+  <dimension ref="A1:BH45"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:60">
@@ -1122,22 +1134,22 @@
         <v>60</v>
       </c>
       <c r="B2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E2" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="F2">
         <v>3.15</v>
       </c>
       <c r="G2">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="H2">
         <v>2.58</v>
@@ -1179,16 +1191,16 @@
         <v>2.06</v>
       </c>
       <c r="U2">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="V2">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W2">
         <v>1.37</v>
       </c>
       <c r="X2">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y2">
         <v>8.6</v>
@@ -1251,7 +1263,7 @@
         <v>12</v>
       </c>
       <c r="AS2">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AT2">
         <v>7.4</v>
@@ -1263,7 +1275,7 @@
         <v>10.5</v>
       </c>
       <c r="AW2">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AX2">
         <v>16</v>
@@ -1272,31 +1284,31 @@
         <v>12</v>
       </c>
       <c r="AZ2">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BA2">
+        <v>5.2</v>
+      </c>
+      <c r="BB2">
+        <v>5.1</v>
+      </c>
+      <c r="BC2">
+        <v>5.1</v>
+      </c>
+      <c r="BD2">
+        <v>5.2</v>
+      </c>
+      <c r="BE2">
         <v>5.3</v>
       </c>
-      <c r="BB2">
-        <v>5.3</v>
-      </c>
-      <c r="BC2">
+      <c r="BF2">
         <v>5.2</v>
       </c>
-      <c r="BD2">
-        <v>5.4</v>
-      </c>
-      <c r="BE2">
-        <v>5.5</v>
-      </c>
-      <c r="BF2">
-        <v>5.3</v>
-      </c>
       <c r="BG2">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BH2" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="3" spans="1:60">
@@ -1304,34 +1316,34 @@
         <v>61</v>
       </c>
       <c r="B3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E3" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="F3">
         <v>1.71</v>
       </c>
       <c r="G3">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="H3">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="I3">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="J3">
         <v>4.2</v>
       </c>
       <c r="K3">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L3">
         <v>1.34</v>
@@ -1361,16 +1373,16 @@
         <v>1.75</v>
       </c>
       <c r="U3">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V3">
         <v>1.22</v>
       </c>
       <c r="W3">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="X3">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="Y3">
         <v>22</v>
@@ -1424,7 +1436,7 @@
         <v>55</v>
       </c>
       <c r="AP3">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AQ3">
         <v>20</v>
@@ -1433,7 +1445,7 @@
         <v>38</v>
       </c>
       <c r="AS3">
-        <v>95</v>
+        <v>46</v>
       </c>
       <c r="AT3">
         <v>9.800000000000001</v>
@@ -1469,7 +1481,7 @@
         <v>27</v>
       </c>
       <c r="BE3">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BF3">
         <v>8</v>
@@ -1478,7 +1490,7 @@
         <v>50</v>
       </c>
       <c r="BH3" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="4" spans="1:60">
@@ -1486,22 +1498,22 @@
         <v>62</v>
       </c>
       <c r="B4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D4" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E4" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="F4">
         <v>3.75</v>
       </c>
       <c r="G4">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="H4">
         <v>2.08</v>
@@ -1513,7 +1525,7 @@
         <v>3.15</v>
       </c>
       <c r="K4">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L4">
         <v>1.01</v>
@@ -1525,7 +1537,7 @@
         <v>2.98</v>
       </c>
       <c r="O4">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P4">
         <v>1.67</v>
@@ -1537,7 +1549,7 @@
         <v>1.25</v>
       </c>
       <c r="S4">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="T4">
         <v>1.77</v>
@@ -1549,7 +1561,7 @@
         <v>1.75</v>
       </c>
       <c r="W4">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="X4">
         <v>13.5</v>
@@ -1573,7 +1585,7 @@
         <v>13.5</v>
       </c>
       <c r="AE4">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AF4">
         <v>36</v>
@@ -1639,13 +1651,13 @@
         <v>14.5</v>
       </c>
       <c r="BA4">
+        <v>3.95</v>
+      </c>
+      <c r="BB4">
+        <v>4.1</v>
+      </c>
+      <c r="BC4">
         <v>4</v>
-      </c>
-      <c r="BB4">
-        <v>4.2</v>
-      </c>
-      <c r="BC4">
-        <v>4.1</v>
       </c>
       <c r="BD4">
         <v>4.1</v>
@@ -1660,7 +1672,7 @@
         <v>3.75</v>
       </c>
       <c r="BH4" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="5" spans="1:60">
@@ -1668,16 +1680,16 @@
         <v>63</v>
       </c>
       <c r="B5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E5" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="F5">
         <v>1.48</v>
@@ -1710,16 +1722,16 @@
         <v>1.33</v>
       </c>
       <c r="P5">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="Q5">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="R5">
         <v>1.31</v>
       </c>
       <c r="S5">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="T5">
         <v>1.93</v>
@@ -1734,7 +1746,7 @@
         <v>2.6</v>
       </c>
       <c r="X5">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="Y5">
         <v>28</v>
@@ -1794,34 +1806,34 @@
         <v>16.5</v>
       </c>
       <c r="AR5">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AS5">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AT5">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="AU5">
         <v>7.4</v>
       </c>
       <c r="AV5">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AW5">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AX5">
         <v>7</v>
       </c>
       <c r="AY5">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="AZ5">
         <v>19.5</v>
       </c>
       <c r="BA5">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BB5">
         <v>10</v>
@@ -1830,19 +1842,19 @@
         <v>13</v>
       </c>
       <c r="BD5">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BE5">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BF5">
         <v>7</v>
       </c>
       <c r="BG5">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BH5" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="6" spans="1:60">
@@ -1850,16 +1862,16 @@
         <v>63</v>
       </c>
       <c r="B6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D6" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E6" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="F6">
         <v>2.04</v>
@@ -2024,7 +2036,7 @@
         <v>8</v>
       </c>
       <c r="BH6" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="7" spans="1:60">
@@ -2032,16 +2044,16 @@
         <v>63</v>
       </c>
       <c r="B7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D7" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E7" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="F7">
         <v>4.7</v>
@@ -2050,7 +2062,7 @@
         <v>110</v>
       </c>
       <c r="H7">
-        <v>1.63</v>
+        <v>1.04</v>
       </c>
       <c r="I7">
         <v>1.9</v>
@@ -2152,52 +2164,52 @@
         <v>1000</v>
       </c>
       <c r="AP7">
-        <v>18</v>
+        <v>1.03</v>
       </c>
       <c r="AQ7">
-        <v>8.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AR7">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AS7">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="AT7">
-        <v>17.5</v>
+        <v>1.03</v>
       </c>
       <c r="AU7">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="AV7">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="AW7">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AX7">
-        <v>28</v>
+        <v>1.03</v>
       </c>
       <c r="AY7">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="AZ7">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA7">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="BB7">
-        <v>40</v>
+        <v>1.03</v>
       </c>
       <c r="BC7">
-        <v>38</v>
+        <v>1.03</v>
       </c>
       <c r="BD7">
-        <v>38</v>
+        <v>1.03</v>
       </c>
       <c r="BE7">
-        <v>40</v>
+        <v>1.03</v>
       </c>
       <c r="BF7">
         <v>1.01</v>
@@ -2206,7 +2218,7 @@
         <v>1.01</v>
       </c>
       <c r="BH7" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="8" spans="1:60">
@@ -2214,22 +2226,22 @@
         <v>63</v>
       </c>
       <c r="B8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D8" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E8" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F8">
         <v>1.2</v>
       </c>
       <c r="G8">
-        <v>2.14</v>
+        <v>2.02</v>
       </c>
       <c r="H8">
         <v>1.09</v>
@@ -2277,7 +2289,7 @@
         <v>1.19</v>
       </c>
       <c r="W8">
-        <v>1.87</v>
+        <v>1.98</v>
       </c>
       <c r="X8">
         <v>1000</v>
@@ -2334,52 +2346,52 @@
         <v>1000</v>
       </c>
       <c r="AP8">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ8">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR8">
-        <v>24</v>
+        <v>1.03</v>
       </c>
       <c r="AS8">
-        <v>40</v>
+        <v>1.03</v>
       </c>
       <c r="AT8">
-        <v>6.6</v>
+        <v>1.03</v>
       </c>
       <c r="AU8">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="AV8">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW8">
-        <v>40</v>
+        <v>1.03</v>
       </c>
       <c r="AX8">
-        <v>8.6</v>
+        <v>1.03</v>
       </c>
       <c r="AY8">
-        <v>8.6</v>
+        <v>1.03</v>
       </c>
       <c r="AZ8">
-        <v>16.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA8">
-        <v>40</v>
+        <v>1.03</v>
       </c>
       <c r="BB8">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="BC8">
-        <v>15.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD8">
-        <v>26</v>
+        <v>1.03</v>
       </c>
       <c r="BE8">
-        <v>40</v>
+        <v>1.03</v>
       </c>
       <c r="BF8">
         <v>1.01</v>
@@ -2388,7 +2400,7 @@
         <v>1.01</v>
       </c>
       <c r="BH8" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="9" spans="1:60">
@@ -2396,16 +2408,16 @@
         <v>64</v>
       </c>
       <c r="B9" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D9" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E9" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="F9">
         <v>5.7</v>
@@ -2417,7 +2429,7 @@
         <v>1.39</v>
       </c>
       <c r="I9">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="J9">
         <v>3.75</v>
@@ -2456,7 +2468,7 @@
         <v>1.01</v>
       </c>
       <c r="V9">
-        <v>2.62</v>
+        <v>2.42</v>
       </c>
       <c r="W9">
         <v>1.09</v>
@@ -2516,52 +2528,52 @@
         <v>1000</v>
       </c>
       <c r="AP9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF9">
         <v>1.01</v>
@@ -2570,7 +2582,7 @@
         <v>1.01</v>
       </c>
       <c r="BH9" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="10" spans="1:60">
@@ -2578,16 +2590,16 @@
         <v>63</v>
       </c>
       <c r="B10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D10" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E10" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="F10">
         <v>2.1</v>
@@ -2614,16 +2626,16 @@
         <v>1.01</v>
       </c>
       <c r="N10">
-        <v>3.3</v>
+        <v>1.72</v>
       </c>
       <c r="O10">
         <v>1.31</v>
       </c>
       <c r="P10">
-        <v>1.25</v>
+        <v>1.71</v>
       </c>
       <c r="Q10">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="R10">
         <v>1.25</v>
@@ -2698,52 +2710,52 @@
         <v>1000</v>
       </c>
       <c r="AP10">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ10">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="AR10">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="AS10">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="AT10">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="AU10">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="AV10">
-        <v>8.6</v>
+        <v>1.03</v>
       </c>
       <c r="AW10">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="AX10">
-        <v>27</v>
+        <v>1.03</v>
       </c>
       <c r="AY10">
-        <v>17</v>
+        <v>1.03</v>
       </c>
       <c r="AZ10">
-        <v>17.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA10">
-        <v>27</v>
+        <v>1.03</v>
       </c>
       <c r="BB10">
-        <v>40</v>
+        <v>1.03</v>
       </c>
       <c r="BC10">
-        <v>40</v>
+        <v>1.03</v>
       </c>
       <c r="BD10">
-        <v>40</v>
+        <v>1.03</v>
       </c>
       <c r="BE10">
-        <v>40</v>
+        <v>1.03</v>
       </c>
       <c r="BF10">
         <v>1.01</v>
@@ -2752,7 +2764,7 @@
         <v>1.01</v>
       </c>
       <c r="BH10" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="11" spans="1:60">
@@ -2760,16 +2772,16 @@
         <v>64</v>
       </c>
       <c r="B11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D11" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E11" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="F11">
         <v>2.26</v>
@@ -2880,52 +2892,52 @@
         <v>1000</v>
       </c>
       <c r="AP11">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ11">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR11">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS11">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT11">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU11">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV11">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW11">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX11">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY11">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ11">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA11">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB11">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC11">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD11">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE11">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF11">
         <v>1.01</v>
@@ -2934,7 +2946,7 @@
         <v>1.01</v>
       </c>
       <c r="BH11" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="12" spans="1:60">
@@ -2942,16 +2954,16 @@
         <v>64</v>
       </c>
       <c r="B12" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C12" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D12" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E12" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="F12">
         <v>2.88</v>
@@ -2978,13 +2990,13 @@
         <v>1.01</v>
       </c>
       <c r="N12">
-        <v>3.25</v>
+        <v>1.72</v>
       </c>
       <c r="O12">
         <v>1.3</v>
       </c>
       <c r="P12">
-        <v>1.27</v>
+        <v>1.72</v>
       </c>
       <c r="Q12">
         <v>1.8</v>
@@ -3062,52 +3074,52 @@
         <v>1000</v>
       </c>
       <c r="AP12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF12">
         <v>1.01</v>
@@ -3116,7 +3128,7 @@
         <v>1.01</v>
       </c>
       <c r="BH12" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="13" spans="1:60">
@@ -3124,16 +3136,16 @@
         <v>64</v>
       </c>
       <c r="B13" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C13" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D13" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E13" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="F13">
         <v>3.2</v>
@@ -3166,7 +3178,7 @@
         <v>1.28</v>
       </c>
       <c r="P13">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="Q13">
         <v>1.74</v>
@@ -3244,52 +3256,52 @@
         <v>21</v>
       </c>
       <c r="AP13">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AQ13">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="AR13">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AS13">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="AT13">
-        <v>9.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AU13">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="AV13">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="AW13">
-        <v>18</v>
+        <v>1.03</v>
       </c>
       <c r="AX13">
-        <v>17</v>
+        <v>1.03</v>
       </c>
       <c r="AY13">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AZ13">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA13">
-        <v>26</v>
+        <v>1.03</v>
       </c>
       <c r="BB13">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="BC13">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="BD13">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="BE13">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF13">
         <v>9.199999999999999</v>
@@ -3298,7 +3310,7 @@
         <v>13.5</v>
       </c>
       <c r="BH13" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="14" spans="1:60">
@@ -3306,16 +3318,16 @@
         <v>65</v>
       </c>
       <c r="B14" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C14" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D14" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E14" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="F14">
         <v>1.48</v>
@@ -3354,16 +3366,16 @@
         <v>1.64</v>
       </c>
       <c r="R14">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="S14">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="T14">
-        <v>1.69</v>
+        <v>1.81</v>
       </c>
       <c r="U14">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="V14">
         <v>1.14</v>
@@ -3426,7 +3438,7 @@
         <v>140</v>
       </c>
       <c r="AP14">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AQ14">
         <v>19.5</v>
@@ -3441,7 +3453,7 @@
         <v>7.2</v>
       </c>
       <c r="AU14">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AV14">
         <v>20</v>
@@ -3456,7 +3468,7 @@
         <v>7.6</v>
       </c>
       <c r="AZ14">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BA14">
         <v>4.1</v>
@@ -3480,7 +3492,7 @@
         <v>4.2</v>
       </c>
       <c r="BH14" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="15" spans="1:60">
@@ -3488,16 +3500,16 @@
         <v>64</v>
       </c>
       <c r="B15" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C15" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D15" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E15" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="F15">
         <v>1.89</v>
@@ -3608,52 +3620,52 @@
         <v>1000</v>
       </c>
       <c r="AP15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF15">
         <v>1.01</v>
@@ -3662,7 +3674,7 @@
         <v>1.01</v>
       </c>
       <c r="BH15" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="16" spans="1:60">
@@ -3670,31 +3682,31 @@
         <v>66</v>
       </c>
       <c r="B16" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C16" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D16" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E16" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="F16">
-        <v>2.32</v>
+        <v>1.81</v>
       </c>
       <c r="G16">
-        <v>2.96</v>
+        <v>110</v>
       </c>
       <c r="H16">
-        <v>1.53</v>
+        <v>1.09</v>
       </c>
       <c r="I16">
         <v>4</v>
       </c>
       <c r="J16">
-        <v>2.42</v>
+        <v>1.09</v>
       </c>
       <c r="K16">
         <v>110</v>
@@ -3718,10 +3730,10 @@
         <v>1.93</v>
       </c>
       <c r="R16">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S16">
-        <v>1.93</v>
+        <v>3.25</v>
       </c>
       <c r="T16">
         <v>1.01</v>
@@ -3733,7 +3745,7 @@
         <v>1.33</v>
       </c>
       <c r="W16">
-        <v>1.51</v>
+        <v>1.01</v>
       </c>
       <c r="X16">
         <v>1000</v>
@@ -3790,52 +3802,52 @@
         <v>1000</v>
       </c>
       <c r="AP16">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="AQ16">
-        <v>8.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AR16">
-        <v>16</v>
+        <v>1.03</v>
       </c>
       <c r="AS16">
-        <v>38</v>
+        <v>1.03</v>
       </c>
       <c r="AT16">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="AU16">
-        <v>5.9</v>
+        <v>1.03</v>
       </c>
       <c r="AV16">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AW16">
-        <v>28</v>
+        <v>1.03</v>
       </c>
       <c r="AX16">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AY16">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AZ16">
-        <v>16</v>
+        <v>1.03</v>
       </c>
       <c r="BA16">
-        <v>38</v>
+        <v>1.03</v>
       </c>
       <c r="BB16">
-        <v>24</v>
+        <v>1.03</v>
       </c>
       <c r="BC16">
-        <v>19</v>
+        <v>1.03</v>
       </c>
       <c r="BD16">
-        <v>32</v>
+        <v>1.03</v>
       </c>
       <c r="BE16">
-        <v>40</v>
+        <v>1.03</v>
       </c>
       <c r="BF16">
         <v>1.01</v>
@@ -3844,7 +3856,7 @@
         <v>1.01</v>
       </c>
       <c r="BH16" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="17" spans="1:60">
@@ -3852,22 +3864,22 @@
         <v>67</v>
       </c>
       <c r="B17" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C17" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D17" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E17" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="F17">
         <v>2.42</v>
       </c>
       <c r="G17">
-        <v>2.98</v>
+        <v>2.76</v>
       </c>
       <c r="H17">
         <v>3.05</v>
@@ -3876,7 +3888,7 @@
         <v>3.6</v>
       </c>
       <c r="J17">
-        <v>2.72</v>
+        <v>3.25</v>
       </c>
       <c r="K17">
         <v>3.7</v>
@@ -3894,10 +3906,10 @@
         <v>1.37</v>
       </c>
       <c r="P17">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="Q17">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="R17">
         <v>1.26</v>
@@ -3912,10 +3924,10 @@
         <v>1.01</v>
       </c>
       <c r="V17">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="W17">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="X17">
         <v>1000</v>
@@ -3972,52 +3984,52 @@
         <v>1000</v>
       </c>
       <c r="AP17">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="AQ17">
-        <v>8.6</v>
+        <v>1.03</v>
       </c>
       <c r="AR17">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="AS17">
-        <v>32</v>
+        <v>1.03</v>
       </c>
       <c r="AT17">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="AU17">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="AV17">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="AW17">
-        <v>24</v>
+        <v>1.03</v>
       </c>
       <c r="AX17">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY17">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="AZ17">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="BA17">
-        <v>38</v>
+        <v>1.03</v>
       </c>
       <c r="BB17">
-        <v>26</v>
+        <v>1.03</v>
       </c>
       <c r="BC17">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="BD17">
-        <v>32</v>
+        <v>1.03</v>
       </c>
       <c r="BE17">
-        <v>40</v>
+        <v>1.03</v>
       </c>
       <c r="BF17">
         <v>1.01</v>
@@ -4026,7 +4038,7 @@
         <v>1.01</v>
       </c>
       <c r="BH17" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="18" spans="1:60">
@@ -4034,16 +4046,16 @@
         <v>68</v>
       </c>
       <c r="B18" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C18" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D18" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E18" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="F18">
         <v>3.1</v>
@@ -4115,7 +4127,7 @@
         <v>11</v>
       </c>
       <c r="AC18">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD18">
         <v>12</v>
@@ -4157,7 +4169,7 @@
         <v>10</v>
       </c>
       <c r="AQ18">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR18">
         <v>14.5</v>
@@ -4208,7 +4220,7 @@
         <v>26</v>
       </c>
       <c r="BH18" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="19" spans="1:60">
@@ -4216,16 +4228,16 @@
         <v>69</v>
       </c>
       <c r="B19" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C19" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D19" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E19" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="F19">
         <v>2.78</v>
@@ -4306,7 +4318,7 @@
         <v>27</v>
       </c>
       <c r="AF19">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG19">
         <v>13</v>
@@ -4390,7 +4402,7 @@
         <v>15.5</v>
       </c>
       <c r="BH19" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="20" spans="1:60">
@@ -4398,22 +4410,22 @@
         <v>70</v>
       </c>
       <c r="B20" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C20" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D20" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E20" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="F20">
         <v>1.68</v>
       </c>
       <c r="G20">
-        <v>2.04</v>
+        <v>2.14</v>
       </c>
       <c r="H20">
         <v>3.85</v>
@@ -4461,7 +4473,7 @@
         <v>1.17</v>
       </c>
       <c r="W20">
-        <v>1.96</v>
+        <v>1.87</v>
       </c>
       <c r="X20">
         <v>1000</v>
@@ -4572,7 +4584,7 @@
         <v>1.01</v>
       </c>
       <c r="BH20" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="21" spans="1:60">
@@ -4580,16 +4592,16 @@
         <v>71</v>
       </c>
       <c r="B21" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C21" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D21" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E21" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="F21">
         <v>3.05</v>
@@ -4754,7 +4766,7 @@
         <v>18</v>
       </c>
       <c r="BH21" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="22" spans="1:60">
@@ -4762,22 +4774,22 @@
         <v>71</v>
       </c>
       <c r="B22" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C22" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D22" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E22" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="F22">
         <v>1.74</v>
       </c>
       <c r="G22">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="H22">
         <v>5.2</v>
@@ -4798,145 +4810,145 @@
         <v>1.06</v>
       </c>
       <c r="N22">
-        <v>1.97</v>
+        <v>3.8</v>
       </c>
       <c r="O22">
         <v>1.3</v>
       </c>
       <c r="P22">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="Q22">
         <v>1.92</v>
       </c>
       <c r="R22">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="S22">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="T22">
-        <v>1.76</v>
+        <v>1.86</v>
       </c>
       <c r="U22">
-        <v>1.92</v>
+        <v>2.02</v>
       </c>
       <c r="V22">
         <v>1.21</v>
       </c>
       <c r="W22">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="X22">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="Y22">
-        <v>28</v>
+        <v>19.5</v>
       </c>
       <c r="Z22">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="AA22">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AB22">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AC22">
+        <v>9.4</v>
+      </c>
+      <c r="AD22">
+        <v>22</v>
+      </c>
+      <c r="AE22">
+        <v>80</v>
+      </c>
+      <c r="AF22">
+        <v>11.5</v>
+      </c>
+      <c r="AG22">
+        <v>10.5</v>
+      </c>
+      <c r="AH22">
+        <v>21</v>
+      </c>
+      <c r="AI22">
+        <v>80</v>
+      </c>
+      <c r="AJ22">
+        <v>19</v>
+      </c>
+      <c r="AK22">
+        <v>19.5</v>
+      </c>
+      <c r="AL22">
+        <v>38</v>
+      </c>
+      <c r="AM22">
+        <v>140</v>
+      </c>
+      <c r="AN22">
+        <v>11.5</v>
+      </c>
+      <c r="AO22">
+        <v>110</v>
+      </c>
+      <c r="AP22">
         <v>13</v>
       </c>
-      <c r="AD22">
-        <v>30</v>
-      </c>
-      <c r="AE22">
-        <v>100</v>
-      </c>
-      <c r="AF22">
+      <c r="AQ22">
         <v>15.5</v>
       </c>
-      <c r="AG22">
-        <v>15</v>
-      </c>
-      <c r="AH22">
-        <v>30</v>
-      </c>
-      <c r="AI22">
-        <v>100</v>
-      </c>
-      <c r="AJ22">
-        <v>28</v>
-      </c>
-      <c r="AK22">
-        <v>28</v>
-      </c>
-      <c r="AL22">
-        <v>50</v>
-      </c>
-      <c r="AM22">
-        <v>1000</v>
-      </c>
-      <c r="AN22">
-        <v>16</v>
-      </c>
-      <c r="AO22">
-        <v>1000</v>
-      </c>
-      <c r="AP22">
-        <v>1.99</v>
-      </c>
-      <c r="AQ22">
-        <v>1.86</v>
-      </c>
       <c r="AR22">
-        <v>1.93</v>
+        <v>6.4</v>
       </c>
       <c r="AS22">
-        <v>1.99</v>
+        <v>7</v>
       </c>
       <c r="AT22">
-        <v>1.99</v>
+        <v>7.6</v>
       </c>
       <c r="AU22">
-        <v>1.73</v>
+        <v>8</v>
       </c>
       <c r="AV22">
-        <v>1.87</v>
+        <v>17.5</v>
       </c>
       <c r="AW22">
-        <v>1.96</v>
+        <v>6.8</v>
       </c>
       <c r="AX22">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AY22">
-        <v>1.76</v>
+        <v>9</v>
       </c>
       <c r="AZ22">
-        <v>1.87</v>
+        <v>17</v>
       </c>
       <c r="BA22">
-        <v>1.96</v>
+        <v>6.8</v>
       </c>
       <c r="BB22">
-        <v>1.86</v>
+        <v>15.5</v>
       </c>
       <c r="BC22">
-        <v>1.86</v>
+        <v>15.5</v>
       </c>
       <c r="BD22">
-        <v>1.92</v>
+        <v>6.2</v>
       </c>
       <c r="BE22">
-        <v>1.99</v>
+        <v>7</v>
       </c>
       <c r="BF22">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="BG22">
-        <v>1.99</v>
+        <v>7</v>
       </c>
       <c r="BH22" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="23" spans="1:60">
@@ -4944,16 +4956,16 @@
         <v>70</v>
       </c>
       <c r="B23" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C23" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D23" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E23" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="F23">
         <v>2.66</v>
@@ -4971,7 +4983,7 @@
         <v>3</v>
       </c>
       <c r="K23">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="L23">
         <v>1.01</v>
@@ -5064,52 +5076,52 @@
         <v>1000</v>
       </c>
       <c r="AP23">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ23">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR23">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS23">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT23">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU23">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV23">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW23">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX23">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY23">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ23">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA23">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB23">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC23">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD23">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE23">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF23">
         <v>1.01</v>
@@ -5118,7 +5130,7 @@
         <v>1.01</v>
       </c>
       <c r="BH23" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="24" spans="1:60">
@@ -5126,19 +5138,19 @@
         <v>72</v>
       </c>
       <c r="B24" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C24" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D24" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E24" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="F24">
-        <v>2.16</v>
+        <v>1.73</v>
       </c>
       <c r="G24">
         <v>2.76</v>
@@ -5153,7 +5165,7 @@
         <v>2.56</v>
       </c>
       <c r="K24">
-        <v>5.8</v>
+        <v>110</v>
       </c>
       <c r="L24">
         <v>1.01</v>
@@ -5174,10 +5186,10 @@
         <v>1.58</v>
       </c>
       <c r="R24">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="S24">
-        <v>1.58</v>
+        <v>2.38</v>
       </c>
       <c r="T24">
         <v>1.01</v>
@@ -5246,52 +5258,52 @@
         <v>1000</v>
       </c>
       <c r="AP24">
-        <v>16</v>
+        <v>1.03</v>
       </c>
       <c r="AQ24">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AR24">
-        <v>17.5</v>
+        <v>1.03</v>
       </c>
       <c r="AS24">
-        <v>34</v>
+        <v>1.03</v>
       </c>
       <c r="AT24">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="AU24">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="AV24">
-        <v>9.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AW24">
-        <v>24</v>
+        <v>1.03</v>
       </c>
       <c r="AX24">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AY24">
-        <v>8.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AZ24">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="BA24">
-        <v>27</v>
+        <v>1.03</v>
       </c>
       <c r="BB24">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="BC24">
-        <v>16.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD24">
-        <v>22</v>
+        <v>1.03</v>
       </c>
       <c r="BE24">
-        <v>40</v>
+        <v>1.03</v>
       </c>
       <c r="BF24">
         <v>1.01</v>
@@ -5300,7 +5312,7 @@
         <v>1.01</v>
       </c>
       <c r="BH24" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="25" spans="1:60">
@@ -5308,22 +5320,22 @@
         <v>73</v>
       </c>
       <c r="B25" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C25" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D25" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E25" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="F25">
         <v>2.16</v>
       </c>
       <c r="G25">
-        <v>2.44</v>
+        <v>2.56</v>
       </c>
       <c r="H25">
         <v>3.4</v>
@@ -5371,7 +5383,7 @@
         <v>1.33</v>
       </c>
       <c r="W25">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="X25">
         <v>1000</v>
@@ -5428,52 +5440,52 @@
         <v>1000</v>
       </c>
       <c r="AP25">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ25">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR25">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS25">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT25">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU25">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV25">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW25">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX25">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY25">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ25">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA25">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB25">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC25">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD25">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE25">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF25">
         <v>1.01</v>
@@ -5482,7 +5494,7 @@
         <v>1.01</v>
       </c>
       <c r="BH25" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="26" spans="1:60">
@@ -5490,16 +5502,16 @@
         <v>73</v>
       </c>
       <c r="B26" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C26" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D26" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E26" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="F26">
         <v>1.75</v>
@@ -5532,13 +5544,13 @@
         <v>1.2</v>
       </c>
       <c r="P26">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="Q26">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="R26">
-        <v>1.46</v>
+        <v>1.32</v>
       </c>
       <c r="S26">
         <v>2.66</v>
@@ -5559,46 +5571,46 @@
         <v>1000</v>
       </c>
       <c r="Y26">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Z26">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AA26">
         <v>1000</v>
       </c>
       <c r="AB26">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AC26">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AD26">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AE26">
         <v>1000</v>
       </c>
       <c r="AF26">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AG26">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH26">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AI26">
         <v>1000</v>
       </c>
       <c r="AJ26">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AK26">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AL26">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM26">
         <v>1000</v>
@@ -5610,52 +5622,52 @@
         <v>1000</v>
       </c>
       <c r="AP26">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ26">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR26">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS26">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT26">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AU26">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AV26">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW26">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX26">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AY26">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AZ26">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA26">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB26">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC26">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD26">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE26">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF26">
         <v>1.01</v>
@@ -5664,189 +5676,189 @@
         <v>1.01</v>
       </c>
       <c r="BH26" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="27" spans="1:60">
       <c r="A27" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="B27" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C27" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D27" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E27" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="F27">
-        <v>1.39</v>
+        <v>1.72</v>
       </c>
       <c r="G27">
-        <v>1.43</v>
+        <v>1.89</v>
       </c>
       <c r="H27">
+        <v>5.2</v>
+      </c>
+      <c r="I27">
         <v>7.2</v>
       </c>
-      <c r="I27">
-        <v>9.4</v>
-      </c>
       <c r="J27">
-        <v>5.8</v>
+        <v>3.45</v>
       </c>
       <c r="K27">
-        <v>6.6</v>
+        <v>4.5</v>
       </c>
       <c r="L27">
         <v>1.01</v>
       </c>
       <c r="M27">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N27">
-        <v>8.800000000000001</v>
+        <v>1.71</v>
       </c>
       <c r="O27">
-        <v>1.11</v>
+        <v>1.4</v>
       </c>
       <c r="P27">
-        <v>3.55</v>
+        <v>1.71</v>
       </c>
       <c r="Q27">
-        <v>1.33</v>
+        <v>2.14</v>
       </c>
       <c r="R27">
-        <v>2.04</v>
+        <v>1.2</v>
       </c>
       <c r="S27">
-        <v>1.83</v>
+        <v>3.4</v>
       </c>
       <c r="T27">
-        <v>1.58</v>
+        <v>1.01</v>
       </c>
       <c r="U27">
-        <v>2.5</v>
+        <v>1.01</v>
       </c>
       <c r="V27">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="W27">
-        <v>3.25</v>
+        <v>2.12</v>
       </c>
       <c r="X27">
-        <v>60</v>
+        <v>17.5</v>
       </c>
       <c r="Y27">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="Z27">
-        <v>95</v>
+        <v>65</v>
       </c>
       <c r="AA27">
-        <v>230</v>
+        <v>1000</v>
       </c>
       <c r="AB27">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="AC27">
-        <v>19.5</v>
+        <v>12</v>
       </c>
       <c r="AD27">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AE27">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AF27">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AG27">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AH27">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="AI27">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AJ27">
-        <v>17.5</v>
+        <v>29</v>
       </c>
       <c r="AK27">
-        <v>16.5</v>
+        <v>30</v>
       </c>
       <c r="AL27">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="AM27">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AN27">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="AO27">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AP27">
-        <v>4.1</v>
+        <v>2.06</v>
       </c>
       <c r="AQ27">
-        <v>4.1</v>
+        <v>10</v>
       </c>
       <c r="AR27">
-        <v>4.2</v>
+        <v>2.26</v>
       </c>
       <c r="AS27">
-        <v>4.3</v>
+        <v>2.34</v>
       </c>
       <c r="AT27">
-        <v>15</v>
+        <v>1.9</v>
       </c>
       <c r="AU27">
-        <v>14</v>
+        <v>1.96</v>
       </c>
       <c r="AV27">
-        <v>3.95</v>
+        <v>2.2</v>
       </c>
       <c r="AW27">
-        <v>4.2</v>
+        <v>2.34</v>
       </c>
       <c r="AX27">
-        <v>12</v>
+        <v>2.02</v>
       </c>
       <c r="AY27">
-        <v>10</v>
+        <v>2.02</v>
       </c>
       <c r="AZ27">
-        <v>17.5</v>
+        <v>2.2</v>
       </c>
       <c r="BA27">
-        <v>4.2</v>
+        <v>2.34</v>
       </c>
       <c r="BB27">
-        <v>12.5</v>
+        <v>2.16</v>
       </c>
       <c r="BC27">
-        <v>12</v>
+        <v>2.18</v>
       </c>
       <c r="BD27">
-        <v>20</v>
+        <v>2.26</v>
       </c>
       <c r="BE27">
-        <v>4.2</v>
+        <v>2.34</v>
       </c>
       <c r="BF27">
-        <v>2.96</v>
+        <v>2.34</v>
       </c>
       <c r="BG27">
-        <v>4.1</v>
+        <v>2.34</v>
       </c>
       <c r="BH27" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="28" spans="1:60">
@@ -5854,34 +5866,34 @@
         <v>60</v>
       </c>
       <c r="B28" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C28" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D28" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E28" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="F28">
-        <v>1.71</v>
+        <v>2.32</v>
       </c>
       <c r="G28">
-        <v>1.89</v>
+        <v>2.6</v>
       </c>
       <c r="H28">
-        <v>5.2</v>
+        <v>3.55</v>
       </c>
       <c r="I28">
-        <v>7.2</v>
+        <v>4.4</v>
       </c>
       <c r="J28">
-        <v>3.45</v>
+        <v>2.94</v>
       </c>
       <c r="K28">
-        <v>4.5</v>
+        <v>3.35</v>
       </c>
       <c r="L28">
         <v>1.01</v>
@@ -5890,22 +5902,22 @@
         <v>1.01</v>
       </c>
       <c r="N28">
-        <v>1.71</v>
+        <v>1.52</v>
       </c>
       <c r="O28">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="P28">
-        <v>1.71</v>
+        <v>1.52</v>
       </c>
       <c r="Q28">
-        <v>2.12</v>
+        <v>2.54</v>
       </c>
       <c r="R28">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="S28">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="T28">
         <v>1.01</v>
@@ -5914,19 +5926,19 @@
         <v>1.01</v>
       </c>
       <c r="V28">
-        <v>1.16</v>
+        <v>1.29</v>
       </c>
       <c r="W28">
-        <v>2.12</v>
+        <v>1.62</v>
       </c>
       <c r="X28">
-        <v>17.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y28">
-        <v>24</v>
+        <v>14.5</v>
       </c>
       <c r="Z28">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="AA28">
         <v>1000</v>
@@ -5935,34 +5947,34 @@
         <v>10</v>
       </c>
       <c r="AC28">
-        <v>12</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD28">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="AE28">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AF28">
-        <v>14.5</v>
+        <v>20</v>
       </c>
       <c r="AG28">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AH28">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AI28">
         <v>1000</v>
       </c>
       <c r="AJ28">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="AK28">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="AL28">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="AM28">
         <v>1000</v>
@@ -5974,243 +5986,243 @@
         <v>1000</v>
       </c>
       <c r="AP28">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="AQ28">
-        <v>10</v>
+        <v>2.3</v>
       </c>
       <c r="AR28">
-        <v>2.26</v>
+        <v>16</v>
       </c>
       <c r="AS28">
+        <v>2.72</v>
+      </c>
+      <c r="AT28">
+        <v>2.14</v>
+      </c>
+      <c r="AU28">
+        <v>2.12</v>
+      </c>
+      <c r="AV28">
+        <v>11.5</v>
+      </c>
+      <c r="AW28">
+        <v>2.64</v>
+      </c>
+      <c r="AX28">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY28">
         <v>2.34</v>
       </c>
-      <c r="AT28">
-        <v>1.9</v>
-      </c>
-      <c r="AU28">
-        <v>1.96</v>
-      </c>
-      <c r="AV28">
-        <v>2.2</v>
-      </c>
-      <c r="AW28">
-        <v>2.34</v>
-      </c>
-      <c r="AX28">
-        <v>2.02</v>
-      </c>
-      <c r="AY28">
-        <v>2.02</v>
-      </c>
       <c r="AZ28">
-        <v>2.2</v>
+        <v>2.52</v>
       </c>
       <c r="BA28">
-        <v>2.34</v>
+        <v>2.72</v>
       </c>
       <c r="BB28">
-        <v>2.16</v>
+        <v>2.58</v>
       </c>
       <c r="BC28">
-        <v>2.18</v>
+        <v>2.58</v>
       </c>
       <c r="BD28">
-        <v>2.26</v>
+        <v>2.64</v>
       </c>
       <c r="BE28">
-        <v>2.34</v>
+        <v>2.72</v>
       </c>
       <c r="BF28">
-        <v>2.34</v>
+        <v>2.72</v>
       </c>
       <c r="BG28">
-        <v>2.34</v>
+        <v>2.72</v>
       </c>
       <c r="BH28" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="29" spans="1:60">
       <c r="A29" t="s">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="B29" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C29" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D29" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E29" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="F29">
-        <v>2.32</v>
+        <v>1.6</v>
       </c>
       <c r="G29">
-        <v>2.66</v>
+        <v>1.66</v>
       </c>
       <c r="H29">
-        <v>3.55</v>
+        <v>5.6</v>
       </c>
       <c r="I29">
-        <v>4.4</v>
+        <v>6.2</v>
       </c>
       <c r="J29">
-        <v>2.94</v>
+        <v>4.5</v>
       </c>
       <c r="K29">
-        <v>3.35</v>
+        <v>5</v>
       </c>
       <c r="L29">
         <v>1.01</v>
       </c>
       <c r="M29">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N29">
-        <v>1.52</v>
+        <v>5.5</v>
       </c>
       <c r="O29">
-        <v>1.52</v>
+        <v>1.19</v>
       </c>
       <c r="P29">
-        <v>1.52</v>
+        <v>2.54</v>
       </c>
       <c r="Q29">
-        <v>2.54</v>
+        <v>1.58</v>
       </c>
       <c r="R29">
-        <v>1.14</v>
+        <v>1.61</v>
       </c>
       <c r="S29">
-        <v>4.4</v>
+        <v>2.42</v>
       </c>
       <c r="T29">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="U29">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="V29">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="W29">
-        <v>1.6</v>
+        <v>2.52</v>
       </c>
       <c r="X29">
+        <v>30</v>
+      </c>
+      <c r="Y29">
+        <v>26</v>
+      </c>
+      <c r="Z29">
+        <v>50</v>
+      </c>
+      <c r="AA29">
+        <v>150</v>
+      </c>
+      <c r="AB29">
+        <v>12</v>
+      </c>
+      <c r="AC29">
         <v>11.5</v>
-      </c>
-      <c r="Y29">
-        <v>14.5</v>
-      </c>
-      <c r="Z29">
-        <v>34</v>
-      </c>
-      <c r="AA29">
-        <v>1000</v>
-      </c>
-      <c r="AB29">
-        <v>10</v>
-      </c>
-      <c r="AC29">
-        <v>9.800000000000001</v>
       </c>
       <c r="AD29">
         <v>23</v>
       </c>
       <c r="AE29">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AF29">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AG29">
-        <v>17</v>
+        <v>10.5</v>
       </c>
       <c r="AH29">
-        <v>32</v>
+        <v>18.5</v>
       </c>
       <c r="AI29">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ29">
-        <v>50</v>
+        <v>16.5</v>
       </c>
       <c r="AK29">
-        <v>48</v>
+        <v>15.5</v>
       </c>
       <c r="AL29">
-        <v>90</v>
+        <v>28</v>
       </c>
       <c r="AM29">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AN29">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="AO29">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AP29">
-        <v>2.2</v>
+        <v>8.6</v>
       </c>
       <c r="AQ29">
-        <v>2.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR29">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AS29">
+        <v>11</v>
+      </c>
+      <c r="AT29">
+        <v>10.5</v>
+      </c>
+      <c r="AU29">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AV29">
+        <v>19.5</v>
+      </c>
+      <c r="AW29">
+        <v>10</v>
+      </c>
+      <c r="AX29">
+        <v>10.5</v>
+      </c>
+      <c r="AY29">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ29">
         <v>16</v>
       </c>
-      <c r="AS29">
-        <v>2.72</v>
-      </c>
-      <c r="AT29">
-        <v>2.14</v>
-      </c>
-      <c r="AU29">
-        <v>2.12</v>
-      </c>
-      <c r="AV29">
-        <v>11.5</v>
-      </c>
-      <c r="AW29">
-        <v>2.64</v>
-      </c>
-      <c r="AX29">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AY29">
-        <v>2.34</v>
-      </c>
-      <c r="AZ29">
-        <v>2.52</v>
-      </c>
       <c r="BA29">
-        <v>2.72</v>
+        <v>10</v>
       </c>
       <c r="BB29">
-        <v>2.58</v>
+        <v>14</v>
       </c>
       <c r="BC29">
-        <v>2.58</v>
+        <v>13.5</v>
       </c>
       <c r="BD29">
-        <v>2.64</v>
+        <v>8.4</v>
       </c>
       <c r="BE29">
-        <v>2.72</v>
+        <v>10.5</v>
       </c>
       <c r="BF29">
-        <v>2.72</v>
+        <v>5.2</v>
       </c>
       <c r="BG29">
-        <v>2.72</v>
+        <v>10</v>
       </c>
       <c r="BH29" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="30" spans="1:60">
@@ -6218,240 +6230,240 @@
         <v>75</v>
       </c>
       <c r="B30" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C30" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D30" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E30" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="F30">
-        <v>1.6</v>
+        <v>1.39</v>
       </c>
       <c r="G30">
-        <v>1.66</v>
+        <v>1.43</v>
       </c>
       <c r="H30">
-        <v>5.6</v>
+        <v>7.2</v>
       </c>
       <c r="I30">
-        <v>6.2</v>
+        <v>9.4</v>
       </c>
       <c r="J30">
-        <v>4.5</v>
+        <v>5.8</v>
       </c>
       <c r="K30">
-        <v>5</v>
+        <v>6.6</v>
       </c>
       <c r="L30">
         <v>1.01</v>
       </c>
       <c r="M30">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="N30">
-        <v>5.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O30">
-        <v>1.19</v>
+        <v>1.11</v>
       </c>
       <c r="P30">
-        <v>2.54</v>
+        <v>3.55</v>
       </c>
       <c r="Q30">
-        <v>1.58</v>
+        <v>1.33</v>
       </c>
       <c r="R30">
-        <v>1.61</v>
+        <v>2.04</v>
       </c>
       <c r="S30">
-        <v>2.42</v>
+        <v>1.83</v>
       </c>
       <c r="T30">
         <v>1.58</v>
       </c>
       <c r="U30">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="V30">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="W30">
-        <v>2.52</v>
+        <v>3.25</v>
       </c>
       <c r="X30">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="Y30">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="Z30">
-        <v>50</v>
+        <v>95</v>
       </c>
       <c r="AA30">
-        <v>150</v>
+        <v>230</v>
       </c>
       <c r="AB30">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="AC30">
-        <v>11.5</v>
+        <v>19.5</v>
       </c>
       <c r="AD30">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="AE30">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="AF30">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="AG30">
-        <v>10.5</v>
+        <v>14.5</v>
       </c>
       <c r="AH30">
-        <v>18.5</v>
+        <v>25</v>
       </c>
       <c r="AI30">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AJ30">
+        <v>17.5</v>
+      </c>
+      <c r="AK30">
         <v>16.5</v>
       </c>
-      <c r="AK30">
-        <v>15.5</v>
-      </c>
       <c r="AL30">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AM30">
         <v>80</v>
       </c>
       <c r="AN30">
-        <v>6.6</v>
+        <v>4.4</v>
       </c>
       <c r="AO30">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AP30">
-        <v>8.6</v>
+        <v>4.1</v>
       </c>
       <c r="AQ30">
-        <v>8.199999999999999</v>
+        <v>4.1</v>
       </c>
       <c r="AR30">
-        <v>9.800000000000001</v>
+        <v>4.2</v>
       </c>
       <c r="AS30">
-        <v>11</v>
+        <v>4.3</v>
       </c>
       <c r="AT30">
-        <v>10.5</v>
+        <v>15</v>
       </c>
       <c r="AU30">
-        <v>9.800000000000001</v>
+        <v>14</v>
       </c>
       <c r="AV30">
-        <v>19.5</v>
+        <v>3.95</v>
       </c>
       <c r="AW30">
+        <v>4.2</v>
+      </c>
+      <c r="AX30">
+        <v>12</v>
+      </c>
+      <c r="AY30">
         <v>10</v>
       </c>
-      <c r="AX30">
-        <v>10.5</v>
-      </c>
-      <c r="AY30">
-        <v>9.199999999999999</v>
-      </c>
       <c r="AZ30">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="BA30">
-        <v>10</v>
+        <v>4.2</v>
       </c>
       <c r="BB30">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="BC30">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="BD30">
-        <v>8.4</v>
+        <v>20</v>
       </c>
       <c r="BE30">
-        <v>10.5</v>
+        <v>4.2</v>
       </c>
       <c r="BF30">
-        <v>5.2</v>
+        <v>2.96</v>
       </c>
       <c r="BG30">
-        <v>10</v>
+        <v>4.1</v>
       </c>
       <c r="BH30" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="31" spans="1:60">
       <c r="A31" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="B31" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C31" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D31" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E31" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="F31">
-        <v>2.24</v>
+        <v>2.56</v>
       </c>
       <c r="G31">
-        <v>2.9</v>
+        <v>3.35</v>
       </c>
       <c r="H31">
-        <v>2.02</v>
+        <v>2.6</v>
       </c>
       <c r="I31">
-        <v>3.95</v>
+        <v>3.6</v>
       </c>
       <c r="J31">
-        <v>3.25</v>
+        <v>2.36</v>
       </c>
       <c r="K31">
-        <v>950</v>
+        <v>4.5</v>
       </c>
       <c r="L31">
         <v>1.01</v>
       </c>
       <c r="M31">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="N31">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="O31">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="P31">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="Q31">
-        <v>1.97</v>
+        <v>1.75</v>
       </c>
       <c r="R31">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="S31">
-        <v>1.97</v>
+        <v>2.78</v>
       </c>
       <c r="T31">
         <v>1.01</v>
@@ -6460,10 +6472,10 @@
         <v>1.01</v>
       </c>
       <c r="V31">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="W31">
-        <v>1.52</v>
+        <v>1.42</v>
       </c>
       <c r="X31">
         <v>1000</v>
@@ -6520,49 +6532,49 @@
         <v>1000</v>
       </c>
       <c r="AP31">
-        <v>9.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="AQ31">
+        <v>9.4</v>
+      </c>
+      <c r="AR31">
+        <v>14.5</v>
+      </c>
+      <c r="AS31">
+        <v>30</v>
+      </c>
+      <c r="AT31">
         <v>9.199999999999999</v>
       </c>
-      <c r="AR31">
-        <v>15.5</v>
-      </c>
-      <c r="AS31">
-        <v>36</v>
-      </c>
-      <c r="AT31">
-        <v>8.199999999999999</v>
-      </c>
       <c r="AU31">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV31">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AW31">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AX31">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="AY31">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ31">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BA31">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="BB31">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BC31">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BD31">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="BE31">
         <v>40</v>
@@ -6574,189 +6586,189 @@
         <v>1.01</v>
       </c>
       <c r="BH31" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="32" spans="1:60">
       <c r="A32" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B32" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C32" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D32" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E32" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="F32">
-        <v>1.49</v>
+        <v>1.7</v>
       </c>
       <c r="G32">
-        <v>1.56</v>
+        <v>2.9</v>
       </c>
       <c r="H32">
-        <v>6</v>
+        <v>2.02</v>
       </c>
       <c r="I32">
-        <v>7.4</v>
+        <v>3.95</v>
       </c>
       <c r="J32">
-        <v>4.8</v>
+        <v>3.25</v>
       </c>
       <c r="K32">
-        <v>5.8</v>
+        <v>950</v>
       </c>
       <c r="L32">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="M32">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="N32">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="O32">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="P32">
-        <v>2.74</v>
+        <v>1.83</v>
       </c>
       <c r="Q32">
-        <v>1.5</v>
+        <v>1.97</v>
       </c>
       <c r="R32">
-        <v>1.7</v>
+        <v>1.18</v>
       </c>
       <c r="S32">
-        <v>2.14</v>
+        <v>1.97</v>
       </c>
       <c r="T32">
-        <v>1.63</v>
+        <v>1.01</v>
       </c>
       <c r="U32">
-        <v>2.26</v>
+        <v>1.01</v>
       </c>
       <c r="V32">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="W32">
-        <v>2.78</v>
+        <v>1.52</v>
       </c>
       <c r="X32">
+        <v>1000</v>
+      </c>
+      <c r="Y32">
+        <v>1000</v>
+      </c>
+      <c r="Z32">
+        <v>1000</v>
+      </c>
+      <c r="AA32">
+        <v>1000</v>
+      </c>
+      <c r="AB32">
+        <v>1000</v>
+      </c>
+      <c r="AC32">
+        <v>1000</v>
+      </c>
+      <c r="AD32">
+        <v>1000</v>
+      </c>
+      <c r="AE32">
+        <v>1000</v>
+      </c>
+      <c r="AF32">
+        <v>1000</v>
+      </c>
+      <c r="AG32">
+        <v>1000</v>
+      </c>
+      <c r="AH32">
+        <v>1000</v>
+      </c>
+      <c r="AI32">
+        <v>1000</v>
+      </c>
+      <c r="AJ32">
+        <v>1000</v>
+      </c>
+      <c r="AK32">
+        <v>1000</v>
+      </c>
+      <c r="AL32">
+        <v>1000</v>
+      </c>
+      <c r="AM32">
+        <v>1000</v>
+      </c>
+      <c r="AN32">
+        <v>1000</v>
+      </c>
+      <c r="AO32">
+        <v>1000</v>
+      </c>
+      <c r="AP32">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AQ32">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR32">
+        <v>15.5</v>
+      </c>
+      <c r="AS32">
+        <v>36</v>
+      </c>
+      <c r="AT32">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU32">
+        <v>6.2</v>
+      </c>
+      <c r="AV32">
+        <v>10</v>
+      </c>
+      <c r="AW32">
+        <v>24</v>
+      </c>
+      <c r="AX32">
+        <v>10.5</v>
+      </c>
+      <c r="AY32">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ32">
+        <v>14</v>
+      </c>
+      <c r="BA32">
         <v>34</v>
       </c>
-      <c r="Y32">
-        <v>34</v>
-      </c>
-      <c r="Z32">
-        <v>65</v>
-      </c>
-      <c r="AA32">
-        <v>180</v>
-      </c>
-      <c r="AB32">
-        <v>14</v>
-      </c>
-      <c r="AC32">
-        <v>13.5</v>
-      </c>
-      <c r="AD32">
-        <v>27</v>
-      </c>
-      <c r="AE32">
-        <v>80</v>
-      </c>
-      <c r="AF32">
-        <v>12.5</v>
-      </c>
-      <c r="AG32">
-        <v>11.5</v>
-      </c>
-      <c r="AH32">
-        <v>21</v>
-      </c>
-      <c r="AI32">
-        <v>65</v>
-      </c>
-      <c r="AJ32">
-        <v>15.5</v>
-      </c>
-      <c r="AK32">
-        <v>15</v>
-      </c>
-      <c r="AL32">
-        <v>27</v>
-      </c>
-      <c r="AM32">
-        <v>80</v>
-      </c>
-      <c r="AN32">
-        <v>5.4</v>
-      </c>
-      <c r="AO32">
-        <v>65</v>
-      </c>
-      <c r="AP32">
-        <v>7</v>
-      </c>
-      <c r="AQ32">
-        <v>7</v>
-      </c>
-      <c r="AR32">
-        <v>7.8</v>
-      </c>
-      <c r="AS32">
-        <v>8.4</v>
-      </c>
-      <c r="AT32">
-        <v>11</v>
-      </c>
-      <c r="AU32">
-        <v>10.5</v>
-      </c>
-      <c r="AV32">
-        <v>21</v>
-      </c>
-      <c r="AW32">
-        <v>8</v>
-      </c>
-      <c r="AX32">
-        <v>10</v>
-      </c>
-      <c r="AY32">
-        <v>9</v>
-      </c>
-      <c r="AZ32">
-        <v>16.5</v>
-      </c>
-      <c r="BA32">
-        <v>7.8</v>
-      </c>
       <c r="BB32">
-        <v>12.5</v>
+        <v>24</v>
       </c>
       <c r="BC32">
-        <v>12</v>
+        <v>18.5</v>
       </c>
       <c r="BD32">
-        <v>6.6</v>
+        <v>28</v>
       </c>
       <c r="BE32">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="BF32">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BG32">
-        <v>44</v>
+        <v>1.01</v>
       </c>
       <c r="BH32" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="33" spans="1:60">
@@ -6764,73 +6776,73 @@
         <v>66</v>
       </c>
       <c r="B33" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C33" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D33" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E33" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="F33">
-        <v>1.61</v>
+        <v>1.49</v>
       </c>
       <c r="G33">
-        <v>1.81</v>
+        <v>1.56</v>
       </c>
       <c r="H33">
+        <v>6</v>
+      </c>
+      <c r="I33">
+        <v>7.4</v>
+      </c>
+      <c r="J33">
         <v>4.8</v>
       </c>
-      <c r="I33">
-        <v>6.4</v>
-      </c>
-      <c r="J33">
-        <v>4.2</v>
-      </c>
       <c r="K33">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="L33">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="M33">
         <v>1.03</v>
       </c>
       <c r="N33">
-        <v>2.48</v>
+        <v>6</v>
       </c>
       <c r="O33">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="P33">
-        <v>2.46</v>
+        <v>2.74</v>
       </c>
       <c r="Q33">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="R33">
-        <v>1.24</v>
+        <v>1.7</v>
       </c>
       <c r="S33">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="T33">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="U33">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="V33">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="W33">
-        <v>2.24</v>
+        <v>2.78</v>
       </c>
       <c r="X33">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="Y33">
         <v>34</v>
@@ -6839,141 +6851,141 @@
         <v>65</v>
       </c>
       <c r="AA33">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AB33">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AC33">
+        <v>13.5</v>
+      </c>
+      <c r="AD33">
+        <v>27</v>
+      </c>
+      <c r="AE33">
+        <v>80</v>
+      </c>
+      <c r="AF33">
+        <v>12.5</v>
+      </c>
+      <c r="AG33">
+        <v>11.5</v>
+      </c>
+      <c r="AH33">
+        <v>21</v>
+      </c>
+      <c r="AI33">
+        <v>65</v>
+      </c>
+      <c r="AJ33">
+        <v>15.5</v>
+      </c>
+      <c r="AK33">
         <v>15</v>
       </c>
-      <c r="AD33">
-        <v>29</v>
-      </c>
-      <c r="AE33">
-        <v>85</v>
-      </c>
-      <c r="AF33">
-        <v>17.5</v>
-      </c>
-      <c r="AG33">
-        <v>14.5</v>
-      </c>
-      <c r="AH33">
-        <v>25</v>
-      </c>
-      <c r="AI33">
-        <v>75</v>
-      </c>
-      <c r="AJ33">
-        <v>24</v>
-      </c>
-      <c r="AK33">
-        <v>22</v>
-      </c>
       <c r="AL33">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="AM33">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AN33">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="AO33">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AP33">
-        <v>2.08</v>
+        <v>7</v>
       </c>
       <c r="AQ33">
-        <v>2.06</v>
+        <v>7</v>
       </c>
       <c r="AR33">
-        <v>2.12</v>
+        <v>7.8</v>
       </c>
       <c r="AS33">
-        <v>2.2</v>
+        <v>8.4</v>
       </c>
       <c r="AT33">
-        <v>1.95</v>
+        <v>11</v>
       </c>
       <c r="AU33">
-        <v>1.92</v>
+        <v>10.5</v>
       </c>
       <c r="AV33">
-        <v>2.04</v>
+        <v>21</v>
       </c>
       <c r="AW33">
-        <v>2.14</v>
+        <v>8</v>
       </c>
       <c r="AX33">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AY33">
-        <v>1.91</v>
+        <v>9</v>
       </c>
       <c r="AZ33">
+        <v>16.5</v>
+      </c>
+      <c r="BA33">
+        <v>7.8</v>
+      </c>
+      <c r="BB33">
         <v>12.5</v>
       </c>
-      <c r="BA33">
-        <v>2.14</v>
-      </c>
-      <c r="BB33">
-        <v>2.02</v>
-      </c>
       <c r="BC33">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BD33">
-        <v>19</v>
+        <v>6.6</v>
       </c>
       <c r="BE33">
-        <v>2.16</v>
+        <v>8</v>
       </c>
       <c r="BF33">
-        <v>2.2</v>
+        <v>4.1</v>
       </c>
       <c r="BG33">
-        <v>2.2</v>
+        <v>44</v>
       </c>
       <c r="BH33" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="34" spans="1:60">
       <c r="A34" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="B34" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C34" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D34" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E34" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="F34">
-        <v>1.48</v>
+        <v>1.61</v>
       </c>
       <c r="G34">
-        <v>1.58</v>
+        <v>1.81</v>
       </c>
       <c r="H34">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="I34">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="J34">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="K34">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="L34">
         <v>1.01</v>
@@ -6982,22 +6994,22 @@
         <v>1.03</v>
       </c>
       <c r="N34">
-        <v>2.62</v>
+        <v>2.46</v>
       </c>
       <c r="O34">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="P34">
-        <v>2.62</v>
+        <v>2.46</v>
       </c>
       <c r="Q34">
-        <v>1.44</v>
+        <v>1.54</v>
       </c>
       <c r="R34">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="S34">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="T34">
         <v>1.01</v>
@@ -7006,52 +7018,52 @@
         <v>1.01</v>
       </c>
       <c r="V34">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="W34">
-        <v>2.72</v>
+        <v>2.24</v>
       </c>
       <c r="X34">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="Y34">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="Z34">
+        <v>65</v>
+      </c>
+      <c r="AA34">
+        <v>1000</v>
+      </c>
+      <c r="AB34">
+        <v>17</v>
+      </c>
+      <c r="AC34">
+        <v>15</v>
+      </c>
+      <c r="AD34">
+        <v>29</v>
+      </c>
+      <c r="AE34">
         <v>85</v>
       </c>
-      <c r="AA34">
-        <v>1000</v>
-      </c>
-      <c r="AB34">
+      <c r="AF34">
         <v>17.5</v>
       </c>
-      <c r="AC34">
-        <v>17</v>
-      </c>
-      <c r="AD34">
-        <v>34</v>
-      </c>
-      <c r="AE34">
-        <v>100</v>
-      </c>
-      <c r="AF34">
-        <v>16</v>
-      </c>
       <c r="AG34">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH34">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AI34">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AJ34">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AK34">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AL34">
         <v>38</v>
@@ -7066,789 +7078,789 @@
         <v>1000</v>
       </c>
       <c r="AP34">
-        <v>1.99</v>
+        <v>2.08</v>
       </c>
       <c r="AQ34">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AR34">
+        <v>2.12</v>
+      </c>
+      <c r="AS34">
+        <v>2.2</v>
+      </c>
+      <c r="AT34">
+        <v>1.95</v>
+      </c>
+      <c r="AU34">
+        <v>1.92</v>
+      </c>
+      <c r="AV34">
         <v>2.04</v>
       </c>
-      <c r="AS34">
-        <v>2.1</v>
-      </c>
-      <c r="AT34">
-        <v>1.87</v>
-      </c>
-      <c r="AU34">
-        <v>1.87</v>
-      </c>
-      <c r="AV34">
-        <v>1.98</v>
-      </c>
       <c r="AW34">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="AX34">
-        <v>1.85</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY34">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="AZ34">
-        <v>1.95</v>
+        <v>12.5</v>
       </c>
       <c r="BA34">
-        <v>2.04</v>
+        <v>2.14</v>
       </c>
       <c r="BB34">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="BC34">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BD34">
-        <v>1.99</v>
+        <v>19</v>
       </c>
       <c r="BE34">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="BF34">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="BG34">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="BH34" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="35" spans="1:60">
       <c r="A35" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="B35" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C35" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D35" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E35" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="F35">
-        <v>1.97</v>
+        <v>1.48</v>
       </c>
       <c r="G35">
-        <v>2.38</v>
+        <v>1.58</v>
       </c>
       <c r="H35">
-        <v>3.25</v>
+        <v>6</v>
       </c>
       <c r="I35">
-        <v>4.9</v>
+        <v>7.2</v>
       </c>
       <c r="J35">
-        <v>2.66</v>
+        <v>4.8</v>
       </c>
       <c r="K35">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="L35">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="M35">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="N35">
+        <v>2.8</v>
+      </c>
+      <c r="O35">
+        <v>1.15</v>
+      </c>
+      <c r="P35">
+        <v>2.8</v>
+      </c>
+      <c r="Q35">
+        <v>1.44</v>
+      </c>
+      <c r="R35">
+        <v>1.58</v>
+      </c>
+      <c r="S35">
+        <v>2.04</v>
+      </c>
+      <c r="T35">
+        <v>1.47</v>
+      </c>
+      <c r="U35">
+        <v>1.9</v>
+      </c>
+      <c r="V35">
+        <v>1.16</v>
+      </c>
+      <c r="W35">
+        <v>2.72</v>
+      </c>
+      <c r="X35">
+        <v>40</v>
+      </c>
+      <c r="Y35">
+        <v>44</v>
+      </c>
+      <c r="Z35">
+        <v>85</v>
+      </c>
+      <c r="AA35">
+        <v>1000</v>
+      </c>
+      <c r="AB35">
+        <v>17.5</v>
+      </c>
+      <c r="AC35">
+        <v>17</v>
+      </c>
+      <c r="AD35">
+        <v>34</v>
+      </c>
+      <c r="AE35">
+        <v>100</v>
+      </c>
+      <c r="AF35">
+        <v>16</v>
+      </c>
+      <c r="AG35">
+        <v>15</v>
+      </c>
+      <c r="AH35">
+        <v>28</v>
+      </c>
+      <c r="AI35">
+        <v>90</v>
+      </c>
+      <c r="AJ35">
+        <v>21</v>
+      </c>
+      <c r="AK35">
+        <v>20</v>
+      </c>
+      <c r="AL35">
+        <v>38</v>
+      </c>
+      <c r="AM35">
+        <v>100</v>
+      </c>
+      <c r="AN35">
+        <v>1000</v>
+      </c>
+      <c r="AO35">
+        <v>1000</v>
+      </c>
+      <c r="AP35">
+        <v>1.99</v>
+      </c>
+      <c r="AQ35">
+        <v>2</v>
+      </c>
+      <c r="AR35">
+        <v>2.04</v>
+      </c>
+      <c r="AS35">
+        <v>2.1</v>
+      </c>
+      <c r="AT35">
+        <v>1.87</v>
+      </c>
+      <c r="AU35">
+        <v>1.87</v>
+      </c>
+      <c r="AV35">
+        <v>1.98</v>
+      </c>
+      <c r="AW35">
+        <v>2.06</v>
+      </c>
+      <c r="AX35">
+        <v>1.85</v>
+      </c>
+      <c r="AY35">
+        <v>1.84</v>
+      </c>
+      <c r="AZ35">
+        <v>1.95</v>
+      </c>
+      <c r="BA35">
+        <v>2.04</v>
+      </c>
+      <c r="BB35">
         <v>1.91</v>
       </c>
-      <c r="O35">
-        <v>1.24</v>
-      </c>
-      <c r="P35">
-        <v>1.9</v>
-      </c>
-      <c r="Q35">
-        <v>1.66</v>
-      </c>
-      <c r="R35">
-        <v>1.35</v>
-      </c>
-      <c r="S35">
-        <v>2.62</v>
-      </c>
-      <c r="T35">
-        <v>1.01</v>
-      </c>
-      <c r="U35">
-        <v>1.01</v>
-      </c>
-      <c r="V35">
-        <v>1.25</v>
-      </c>
-      <c r="W35">
-        <v>1.72</v>
-      </c>
-      <c r="X35">
-        <v>1000</v>
-      </c>
-      <c r="Y35">
-        <v>1000</v>
-      </c>
-      <c r="Z35">
-        <v>1000</v>
-      </c>
-      <c r="AA35">
-        <v>1000</v>
-      </c>
-      <c r="AB35">
-        <v>1000</v>
-      </c>
-      <c r="AC35">
-        <v>1000</v>
-      </c>
-      <c r="AD35">
-        <v>1000</v>
-      </c>
-      <c r="AE35">
-        <v>1000</v>
-      </c>
-      <c r="AF35">
-        <v>1000</v>
-      </c>
-      <c r="AG35">
-        <v>1000</v>
-      </c>
-      <c r="AH35">
-        <v>1000</v>
-      </c>
-      <c r="AI35">
-        <v>1000</v>
-      </c>
-      <c r="AJ35">
-        <v>1000</v>
-      </c>
-      <c r="AK35">
-        <v>1000</v>
-      </c>
-      <c r="AL35">
-        <v>1000</v>
-      </c>
-      <c r="AM35">
-        <v>1000</v>
-      </c>
-      <c r="AN35">
-        <v>1000</v>
-      </c>
-      <c r="AO35">
-        <v>1000</v>
-      </c>
-      <c r="AP35">
-        <v>14</v>
-      </c>
-      <c r="AQ35">
-        <v>11.5</v>
-      </c>
-      <c r="AR35">
-        <v>19</v>
-      </c>
-      <c r="AS35">
-        <v>40</v>
-      </c>
-      <c r="AT35">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU35">
-        <v>6.6</v>
-      </c>
-      <c r="AV35">
-        <v>11</v>
-      </c>
-      <c r="AW35">
-        <v>27</v>
-      </c>
-      <c r="AX35">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AY35">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ35">
-        <v>12.5</v>
-      </c>
-      <c r="BA35">
-        <v>29</v>
-      </c>
-      <c r="BB35">
-        <v>5</v>
-      </c>
       <c r="BC35">
-        <v>15.5</v>
+        <v>10</v>
       </c>
       <c r="BD35">
-        <v>24</v>
+        <v>1.99</v>
       </c>
       <c r="BE35">
-        <v>40</v>
+        <v>2.06</v>
       </c>
       <c r="BF35">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="BG35">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="BH35" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="36" spans="1:60">
       <c r="A36" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B36" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C36" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D36" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E36" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="F36">
-        <v>1.64</v>
+        <v>1.81</v>
       </c>
       <c r="G36">
+        <v>2.28</v>
+      </c>
+      <c r="H36">
+        <v>3.4</v>
+      </c>
+      <c r="I36">
+        <v>4.9</v>
+      </c>
+      <c r="J36">
+        <v>3.65</v>
+      </c>
+      <c r="K36">
+        <v>6.6</v>
+      </c>
+      <c r="L36">
+        <v>1.31</v>
+      </c>
+      <c r="M36">
+        <v>1.05</v>
+      </c>
+      <c r="N36">
+        <v>1.91</v>
+      </c>
+      <c r="O36">
+        <v>1.24</v>
+      </c>
+      <c r="P36">
+        <v>1.91</v>
+      </c>
+      <c r="Q36">
         <v>1.66</v>
       </c>
-      <c r="H36">
-        <v>5.9</v>
-      </c>
-      <c r="I36">
-        <v>6.2</v>
-      </c>
-      <c r="J36">
-        <v>4.2</v>
-      </c>
-      <c r="K36">
-        <v>4.5</v>
-      </c>
-      <c r="L36">
-        <v>1.37</v>
-      </c>
-      <c r="M36">
-        <v>1.06</v>
-      </c>
-      <c r="N36">
-        <v>3.9</v>
-      </c>
-      <c r="O36">
-        <v>1.32</v>
-      </c>
-      <c r="P36">
-        <v>2</v>
-      </c>
-      <c r="Q36">
-        <v>1.94</v>
-      </c>
       <c r="R36">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="S36">
-        <v>3.45</v>
+        <v>2.62</v>
       </c>
       <c r="T36">
-        <v>1.98</v>
+        <v>1.01</v>
       </c>
       <c r="U36">
-        <v>1.97</v>
+        <v>1.01</v>
       </c>
       <c r="V36">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="W36">
-        <v>2.5</v>
+        <v>1.78</v>
       </c>
       <c r="X36">
+        <v>1000</v>
+      </c>
+      <c r="Y36">
+        <v>1000</v>
+      </c>
+      <c r="Z36">
+        <v>1000</v>
+      </c>
+      <c r="AA36">
+        <v>1000</v>
+      </c>
+      <c r="AB36">
+        <v>1000</v>
+      </c>
+      <c r="AC36">
+        <v>1000</v>
+      </c>
+      <c r="AD36">
+        <v>1000</v>
+      </c>
+      <c r="AE36">
+        <v>1000</v>
+      </c>
+      <c r="AF36">
+        <v>1000</v>
+      </c>
+      <c r="AG36">
+        <v>1000</v>
+      </c>
+      <c r="AH36">
+        <v>1000</v>
+      </c>
+      <c r="AI36">
+        <v>1000</v>
+      </c>
+      <c r="AJ36">
+        <v>1000</v>
+      </c>
+      <c r="AK36">
+        <v>1000</v>
+      </c>
+      <c r="AL36">
+        <v>1000</v>
+      </c>
+      <c r="AM36">
+        <v>1000</v>
+      </c>
+      <c r="AN36">
+        <v>1000</v>
+      </c>
+      <c r="AO36">
+        <v>1000</v>
+      </c>
+      <c r="AP36">
+        <v>14</v>
+      </c>
+      <c r="AQ36">
+        <v>11.5</v>
+      </c>
+      <c r="AR36">
+        <v>19</v>
+      </c>
+      <c r="AS36">
+        <v>40</v>
+      </c>
+      <c r="AT36">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU36">
+        <v>6.6</v>
+      </c>
+      <c r="AV36">
+        <v>11</v>
+      </c>
+      <c r="AW36">
+        <v>27</v>
+      </c>
+      <c r="AX36">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY36">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ36">
+        <v>12.5</v>
+      </c>
+      <c r="BA36">
+        <v>29</v>
+      </c>
+      <c r="BB36">
+        <v>5</v>
+      </c>
+      <c r="BC36">
         <v>15.5</v>
       </c>
-      <c r="Y36">
-        <v>19</v>
-      </c>
-      <c r="Z36">
-        <v>48</v>
-      </c>
-      <c r="AA36">
-        <v>180</v>
-      </c>
-      <c r="AB36">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AC36">
-        <v>9.4</v>
-      </c>
-      <c r="AD36">
-        <v>23</v>
-      </c>
-      <c r="AE36">
-        <v>90</v>
-      </c>
-      <c r="AF36">
-        <v>9.4</v>
-      </c>
-      <c r="AG36">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AH36">
-        <v>23</v>
-      </c>
-      <c r="AI36">
-        <v>90</v>
-      </c>
-      <c r="AJ36">
-        <v>16</v>
-      </c>
-      <c r="AK36">
-        <v>17.5</v>
-      </c>
-      <c r="AL36">
-        <v>38</v>
-      </c>
-      <c r="AM36">
-        <v>140</v>
-      </c>
-      <c r="AN36">
-        <v>10</v>
-      </c>
-      <c r="AO36">
-        <v>110</v>
-      </c>
-      <c r="AP36">
-        <v>14.5</v>
-      </c>
-      <c r="AQ36">
-        <v>17.5</v>
-      </c>
-      <c r="AR36">
-        <v>42</v>
-      </c>
-      <c r="AS36">
-        <v>44</v>
-      </c>
-      <c r="AT36">
-        <v>7.8</v>
-      </c>
-      <c r="AU36">
-        <v>9</v>
-      </c>
-      <c r="AV36">
-        <v>21</v>
-      </c>
-      <c r="AW36">
-        <v>34</v>
-      </c>
-      <c r="AX36">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AY36">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ36">
-        <v>21</v>
-      </c>
-      <c r="BA36">
-        <v>36</v>
-      </c>
-      <c r="BB36">
-        <v>14.5</v>
-      </c>
-      <c r="BC36">
-        <v>16</v>
-      </c>
       <c r="BD36">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="BE36">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BF36">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BG36">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="BH36" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="37" spans="1:60">
       <c r="A37" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="B37" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C37" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D37" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E37" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="F37">
-        <v>6.8</v>
+        <v>1.64</v>
       </c>
       <c r="G37">
-        <v>7</v>
+        <v>1.66</v>
       </c>
       <c r="H37">
-        <v>1.5</v>
+        <v>5.9</v>
       </c>
       <c r="I37">
-        <v>1.51</v>
+        <v>6</v>
       </c>
       <c r="J37">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="K37">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="L37">
+        <v>1.41</v>
+      </c>
+      <c r="M37">
+        <v>1.06</v>
+      </c>
+      <c r="N37">
+        <v>4</v>
+      </c>
+      <c r="O37">
         <v>1.32</v>
       </c>
-      <c r="M37">
-        <v>1.04</v>
-      </c>
-      <c r="N37">
-        <v>5.1</v>
-      </c>
-      <c r="O37">
-        <v>1.23</v>
-      </c>
       <c r="P37">
-        <v>2.42</v>
+        <v>2</v>
       </c>
       <c r="Q37">
-        <v>1.67</v>
+        <v>1.96</v>
       </c>
       <c r="R37">
-        <v>1.54</v>
+        <v>1.37</v>
       </c>
       <c r="S37">
-        <v>2.74</v>
+        <v>3.5</v>
       </c>
       <c r="T37">
-        <v>1.84</v>
+        <v>1.98</v>
       </c>
       <c r="U37">
-        <v>2.14</v>
+        <v>1.95</v>
       </c>
       <c r="V37">
-        <v>2.96</v>
+        <v>1.2</v>
       </c>
       <c r="W37">
-        <v>1.16</v>
+        <v>2.52</v>
       </c>
       <c r="X37">
-        <v>24</v>
+        <v>15.5</v>
       </c>
       <c r="Y37">
+        <v>19</v>
+      </c>
+      <c r="Z37">
+        <v>48</v>
+      </c>
+      <c r="AA37">
+        <v>170</v>
+      </c>
+      <c r="AB37">
+        <v>8</v>
+      </c>
+      <c r="AC37">
         <v>9.4</v>
       </c>
-      <c r="Z37">
+      <c r="AD37">
+        <v>23</v>
+      </c>
+      <c r="AE37">
+        <v>90</v>
+      </c>
+      <c r="AF37">
         <v>9.4</v>
       </c>
-      <c r="AA37">
-        <v>13.5</v>
-      </c>
-      <c r="AB37">
-        <v>27</v>
-      </c>
-      <c r="AC37">
-        <v>11</v>
-      </c>
-      <c r="AD37">
-        <v>9.6</v>
-      </c>
-      <c r="AE37">
-        <v>14</v>
-      </c>
-      <c r="AF37">
-        <v>60</v>
-      </c>
       <c r="AG37">
-        <v>26</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH37">
+        <v>23</v>
+      </c>
+      <c r="AI37">
+        <v>90</v>
+      </c>
+      <c r="AJ37">
+        <v>16</v>
+      </c>
+      <c r="AK37">
+        <v>17.5</v>
+      </c>
+      <c r="AL37">
+        <v>38</v>
+      </c>
+      <c r="AM37">
+        <v>140</v>
+      </c>
+      <c r="AN37">
+        <v>10</v>
+      </c>
+      <c r="AO37">
+        <v>110</v>
+      </c>
+      <c r="AP37">
+        <v>14.5</v>
+      </c>
+      <c r="AQ37">
+        <v>17.5</v>
+      </c>
+      <c r="AR37">
+        <v>42</v>
+      </c>
+      <c r="AS37">
+        <v>44</v>
+      </c>
+      <c r="AT37">
+        <v>7.6</v>
+      </c>
+      <c r="AU37">
+        <v>9</v>
+      </c>
+      <c r="AV37">
         <v>21</v>
       </c>
-      <c r="AI37">
-        <v>29</v>
-      </c>
-      <c r="AJ37">
+      <c r="AW37">
+        <v>34</v>
+      </c>
+      <c r="AX37">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY37">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ37">
+        <v>21</v>
+      </c>
+      <c r="BA37">
+        <v>36</v>
+      </c>
+      <c r="BB37">
+        <v>14.5</v>
+      </c>
+      <c r="BC37">
+        <v>16</v>
+      </c>
+      <c r="BD37">
+        <v>32</v>
+      </c>
+      <c r="BE37">
+        <v>42</v>
+      </c>
+      <c r="BF37">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BG37">
+        <v>38</v>
+      </c>
+      <c r="BH37" t="s">
         <v>190</v>
-      </c>
-      <c r="AK37">
-        <v>90</v>
-      </c>
-      <c r="AL37">
-        <v>75</v>
-      </c>
-      <c r="AM37">
-        <v>100</v>
-      </c>
-      <c r="AN37">
-        <v>85</v>
-      </c>
-      <c r="AO37">
-        <v>6.6</v>
-      </c>
-      <c r="AP37">
-        <v>21</v>
-      </c>
-      <c r="AQ37">
-        <v>9</v>
-      </c>
-      <c r="AR37">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AS37">
-        <v>13</v>
-      </c>
-      <c r="AT37">
-        <v>25</v>
-      </c>
-      <c r="AU37">
-        <v>10.5</v>
-      </c>
-      <c r="AV37">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AW37">
-        <v>13.5</v>
-      </c>
-      <c r="AX37">
-        <v>50</v>
-      </c>
-      <c r="AY37">
-        <v>23</v>
-      </c>
-      <c r="AZ37">
-        <v>20</v>
-      </c>
-      <c r="BA37">
-        <v>27</v>
-      </c>
-      <c r="BB37">
-        <v>90</v>
-      </c>
-      <c r="BC37">
-        <v>80</v>
-      </c>
-      <c r="BD37">
-        <v>55</v>
-      </c>
-      <c r="BE37">
-        <v>70</v>
-      </c>
-      <c r="BF37">
-        <v>75</v>
-      </c>
-      <c r="BG37">
-        <v>6.2</v>
-      </c>
-      <c r="BH37" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="38" spans="1:60">
       <c r="A38" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="B38" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C38" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D38" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E38" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="F38">
-        <v>2.5</v>
+        <v>6.8</v>
       </c>
       <c r="G38">
-        <v>2.54</v>
+        <v>7.2</v>
       </c>
       <c r="H38">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="I38">
-        <v>3.1</v>
+        <v>1.51</v>
       </c>
       <c r="J38">
-        <v>3.6</v>
+        <v>5.1</v>
       </c>
       <c r="K38">
-        <v>3.65</v>
+        <v>5.2</v>
       </c>
       <c r="L38">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="M38">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="N38">
-        <v>3.8</v>
+        <v>5.1</v>
       </c>
       <c r="O38">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="P38">
-        <v>1.95</v>
+        <v>2.42</v>
       </c>
       <c r="Q38">
-        <v>2.02</v>
+        <v>1.67</v>
       </c>
       <c r="R38">
-        <v>1.36</v>
+        <v>1.55</v>
       </c>
       <c r="S38">
-        <v>3.55</v>
+        <v>2.74</v>
       </c>
       <c r="T38">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="U38">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="V38">
-        <v>1.47</v>
+        <v>2.96</v>
       </c>
       <c r="W38">
-        <v>1.64</v>
+        <v>1.16</v>
       </c>
       <c r="X38">
+        <v>24</v>
+      </c>
+      <c r="Y38">
+        <v>9.6</v>
+      </c>
+      <c r="Z38">
+        <v>9.6</v>
+      </c>
+      <c r="AA38">
+        <v>13.5</v>
+      </c>
+      <c r="AB38">
+        <v>27</v>
+      </c>
+      <c r="AC38">
+        <v>11</v>
+      </c>
+      <c r="AD38">
+        <v>9.6</v>
+      </c>
+      <c r="AE38">
         <v>14</v>
       </c>
-      <c r="Y38">
-        <v>12.5</v>
-      </c>
-      <c r="Z38">
-        <v>20</v>
-      </c>
-      <c r="AA38">
-        <v>50</v>
-      </c>
-      <c r="AB38">
-        <v>10.5</v>
-      </c>
-      <c r="AC38">
-        <v>7.8</v>
-      </c>
-      <c r="AD38">
-        <v>13</v>
-      </c>
-      <c r="AE38">
-        <v>36</v>
-      </c>
       <c r="AF38">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="AG38">
-        <v>11.5</v>
+        <v>26</v>
       </c>
       <c r="AH38">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AI38">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="AJ38">
-        <v>36</v>
+        <v>190</v>
       </c>
       <c r="AK38">
-        <v>27</v>
+        <v>90</v>
       </c>
       <c r="AL38">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="AM38">
         <v>95</v>
       </c>
       <c r="AN38">
-        <v>22</v>
+        <v>85</v>
       </c>
       <c r="AO38">
-        <v>32</v>
+        <v>6.6</v>
       </c>
       <c r="AP38">
+        <v>23</v>
+      </c>
+      <c r="AQ38">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR38">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AS38">
         <v>13</v>
       </c>
-      <c r="AQ38">
-        <v>11.5</v>
-      </c>
-      <c r="AR38">
-        <v>19</v>
-      </c>
-      <c r="AS38">
-        <v>44</v>
-      </c>
       <c r="AT38">
-        <v>9.800000000000001</v>
+        <v>25</v>
       </c>
       <c r="AU38">
-        <v>7.4</v>
+        <v>10.5</v>
       </c>
       <c r="AV38">
-        <v>12</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW38">
-        <v>30</v>
+        <v>13.5</v>
       </c>
       <c r="AX38">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="AY38">
-        <v>10.5</v>
+        <v>23</v>
       </c>
       <c r="AZ38">
-        <v>16</v>
+        <v>19.5</v>
       </c>
       <c r="BA38">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="BB38">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="BC38">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="BD38">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="BE38">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="BF38">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c r="BG38">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="BH38" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="39" spans="1:60">
@@ -7856,181 +7868,181 @@
         <v>78</v>
       </c>
       <c r="B39" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C39" t="s">
+        <v>96</v>
+      </c>
+      <c r="D39" t="s">
+        <v>139</v>
+      </c>
+      <c r="E39" t="s">
+        <v>183</v>
+      </c>
+      <c r="F39">
+        <v>2.5</v>
+      </c>
+      <c r="G39">
+        <v>2.54</v>
+      </c>
+      <c r="H39">
+        <v>3</v>
+      </c>
+      <c r="I39">
+        <v>3.1</v>
+      </c>
+      <c r="J39">
+        <v>3.6</v>
+      </c>
+      <c r="K39">
+        <v>3.65</v>
+      </c>
+      <c r="L39">
+        <v>1.42</v>
+      </c>
+      <c r="M39">
+        <v>1.07</v>
+      </c>
+      <c r="N39">
+        <v>3.85</v>
+      </c>
+      <c r="O39">
+        <v>1.33</v>
+      </c>
+      <c r="P39">
+        <v>1.95</v>
+      </c>
+      <c r="Q39">
+        <v>2.02</v>
+      </c>
+      <c r="R39">
+        <v>1.36</v>
+      </c>
+      <c r="S39">
+        <v>3.6</v>
+      </c>
+      <c r="T39">
+        <v>1.8</v>
+      </c>
+      <c r="U39">
+        <v>2.18</v>
+      </c>
+      <c r="V39">
+        <v>1.47</v>
+      </c>
+      <c r="W39">
+        <v>1.64</v>
+      </c>
+      <c r="X39">
+        <v>14</v>
+      </c>
+      <c r="Y39">
+        <v>12.5</v>
+      </c>
+      <c r="Z39">
+        <v>20</v>
+      </c>
+      <c r="AA39">
+        <v>50</v>
+      </c>
+      <c r="AB39">
+        <v>10.5</v>
+      </c>
+      <c r="AC39">
+        <v>7.8</v>
+      </c>
+      <c r="AD39">
+        <v>13</v>
+      </c>
+      <c r="AE39">
+        <v>34</v>
+      </c>
+      <c r="AF39">
+        <v>16</v>
+      </c>
+      <c r="AG39">
+        <v>11.5</v>
+      </c>
+      <c r="AH39">
+        <v>17.5</v>
+      </c>
+      <c r="AI39">
+        <v>46</v>
+      </c>
+      <c r="AJ39">
+        <v>36</v>
+      </c>
+      <c r="AK39">
+        <v>27</v>
+      </c>
+      <c r="AL39">
+        <v>40</v>
+      </c>
+      <c r="AM39">
         <v>95</v>
       </c>
-      <c r="D39" t="s">
-        <v>137</v>
-      </c>
-      <c r="E39" t="s">
-        <v>180</v>
-      </c>
-      <c r="F39">
-        <v>1.29</v>
-      </c>
-      <c r="G39">
-        <v>1.32</v>
-      </c>
-      <c r="H39">
+      <c r="AN39">
+        <v>22</v>
+      </c>
+      <c r="AO39">
+        <v>32</v>
+      </c>
+      <c r="AP39">
+        <v>13</v>
+      </c>
+      <c r="AQ39">
+        <v>11.5</v>
+      </c>
+      <c r="AR39">
+        <v>19</v>
+      </c>
+      <c r="AS39">
+        <v>44</v>
+      </c>
+      <c r="AT39">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU39">
+        <v>7.4</v>
+      </c>
+      <c r="AV39">
         <v>12</v>
       </c>
-      <c r="I39">
-        <v>13</v>
-      </c>
-      <c r="J39">
-        <v>6</v>
-      </c>
-      <c r="K39">
-        <v>6.8</v>
-      </c>
-      <c r="L39">
-        <v>1.25</v>
-      </c>
-      <c r="M39">
-        <v>1.03</v>
-      </c>
-      <c r="N39">
-        <v>2.62</v>
-      </c>
-      <c r="O39">
-        <v>1.14</v>
-      </c>
-      <c r="P39">
-        <v>2.62</v>
-      </c>
-      <c r="Q39">
-        <v>1.51</v>
-      </c>
-      <c r="R39">
-        <v>1.56</v>
-      </c>
-      <c r="S39">
-        <v>2.04</v>
-      </c>
-      <c r="T39">
-        <v>1.01</v>
-      </c>
-      <c r="U39">
-        <v>1.01</v>
-      </c>
-      <c r="V39">
-        <v>1.08</v>
-      </c>
-      <c r="W39">
-        <v>4.1</v>
-      </c>
-      <c r="X39">
-        <v>36</v>
-      </c>
-      <c r="Y39">
-        <v>60</v>
-      </c>
-      <c r="Z39">
-        <v>1000</v>
-      </c>
-      <c r="AA39">
-        <v>1000</v>
-      </c>
-      <c r="AB39">
-        <v>15</v>
-      </c>
-      <c r="AC39">
+      <c r="AW39">
+        <v>30</v>
+      </c>
+      <c r="AX39">
+        <v>14.5</v>
+      </c>
+      <c r="AY39">
+        <v>10.5</v>
+      </c>
+      <c r="AZ39">
+        <v>16</v>
+      </c>
+      <c r="BA39">
+        <v>40</v>
+      </c>
+      <c r="BB39">
+        <v>32</v>
+      </c>
+      <c r="BC39">
+        <v>25</v>
+      </c>
+      <c r="BD39">
+        <v>34</v>
+      </c>
+      <c r="BE39">
+        <v>38</v>
+      </c>
+      <c r="BF39">
         <v>20</v>
       </c>
-      <c r="AD39">
-        <v>60</v>
-      </c>
-      <c r="AE39">
-        <v>1000</v>
-      </c>
-      <c r="AF39">
-        <v>12.5</v>
-      </c>
-      <c r="AG39">
-        <v>15.5</v>
-      </c>
-      <c r="AH39">
-        <v>40</v>
-      </c>
-      <c r="AI39">
-        <v>1000</v>
-      </c>
-      <c r="AJ39">
-        <v>14.5</v>
-      </c>
-      <c r="AK39">
-        <v>19</v>
-      </c>
-      <c r="AL39">
-        <v>48</v>
-      </c>
-      <c r="AM39">
-        <v>1000</v>
-      </c>
-      <c r="AN39">
-        <v>1000</v>
-      </c>
-      <c r="AO39">
-        <v>1000</v>
-      </c>
-      <c r="AP39">
-        <v>1.85</v>
-      </c>
-      <c r="AQ39">
-        <v>1.89</v>
-      </c>
-      <c r="AR39">
-        <v>1.95</v>
-      </c>
-      <c r="AS39">
-        <v>1.95</v>
-      </c>
-      <c r="AT39">
-        <v>1.73</v>
-      </c>
-      <c r="AU39">
-        <v>1.78</v>
-      </c>
-      <c r="AV39">
-        <v>1.89</v>
-      </c>
-      <c r="AW39">
-        <v>1.95</v>
-      </c>
-      <c r="AX39">
-        <v>1.69</v>
-      </c>
-      <c r="AY39">
-        <v>1.73</v>
-      </c>
-      <c r="AZ39">
-        <v>1.86</v>
-      </c>
-      <c r="BA39">
-        <v>1.95</v>
-      </c>
-      <c r="BB39">
-        <v>1.72</v>
-      </c>
-      <c r="BC39">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BD39">
-        <v>1.88</v>
-      </c>
-      <c r="BE39">
-        <v>1.95</v>
-      </c>
-      <c r="BF39">
-        <v>1.95</v>
-      </c>
       <c r="BG39">
-        <v>1.95</v>
+        <v>28</v>
       </c>
       <c r="BH39" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="40" spans="1:60">
@@ -8038,181 +8050,181 @@
         <v>79</v>
       </c>
       <c r="B40" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C40" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D40" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E40" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="F40">
-        <v>2.36</v>
+        <v>1.29</v>
       </c>
       <c r="G40">
-        <v>2.56</v>
+        <v>1.32</v>
       </c>
       <c r="H40">
-        <v>3.5</v>
+        <v>12</v>
       </c>
       <c r="I40">
+        <v>13</v>
+      </c>
+      <c r="J40">
+        <v>6.4</v>
+      </c>
+      <c r="K40">
+        <v>6.8</v>
+      </c>
+      <c r="L40">
+        <v>1.01</v>
+      </c>
+      <c r="M40">
+        <v>1.03</v>
+      </c>
+      <c r="N40">
+        <v>5.7</v>
+      </c>
+      <c r="O40">
+        <v>1.18</v>
+      </c>
+      <c r="P40">
+        <v>2.62</v>
+      </c>
+      <c r="Q40">
+        <v>1.51</v>
+      </c>
+      <c r="R40">
+        <v>1.65</v>
+      </c>
+      <c r="S40">
+        <v>2.3</v>
+      </c>
+      <c r="T40">
+        <v>1.96</v>
+      </c>
+      <c r="U40">
+        <v>1.91</v>
+      </c>
+      <c r="V40">
+        <v>1.08</v>
+      </c>
+      <c r="W40">
         <v>4.1</v>
       </c>
-      <c r="J40">
-        <v>2.9</v>
-      </c>
-      <c r="K40">
-        <v>3.2</v>
-      </c>
-      <c r="L40">
-        <v>1.01</v>
-      </c>
-      <c r="M40">
-        <v>1.15</v>
-      </c>
-      <c r="N40">
-        <v>2.28</v>
-      </c>
-      <c r="O40">
-        <v>1.68</v>
-      </c>
-      <c r="P40">
-        <v>1.44</v>
-      </c>
-      <c r="Q40">
-        <v>3</v>
-      </c>
-      <c r="R40">
-        <v>1.14</v>
-      </c>
-      <c r="S40">
-        <v>6.8</v>
-      </c>
-      <c r="T40">
-        <v>2.2</v>
-      </c>
-      <c r="U40">
-        <v>1.62</v>
-      </c>
-      <c r="V40">
-        <v>1.33</v>
-      </c>
-      <c r="W40">
-        <v>1.64</v>
-      </c>
       <c r="X40">
-        <v>8.4</v>
+        <v>29</v>
       </c>
       <c r="Y40">
+        <v>42</v>
+      </c>
+      <c r="Z40">
+        <v>130</v>
+      </c>
+      <c r="AA40">
+        <v>480</v>
+      </c>
+      <c r="AB40">
+        <v>11</v>
+      </c>
+      <c r="AC40">
+        <v>14.5</v>
+      </c>
+      <c r="AD40">
+        <v>42</v>
+      </c>
+      <c r="AE40">
+        <v>200</v>
+      </c>
+      <c r="AF40">
+        <v>9</v>
+      </c>
+      <c r="AG40">
+        <v>11</v>
+      </c>
+      <c r="AH40">
+        <v>29</v>
+      </c>
+      <c r="AI40">
+        <v>150</v>
+      </c>
+      <c r="AJ40">
+        <v>11</v>
+      </c>
+      <c r="AK40">
+        <v>14</v>
+      </c>
+      <c r="AL40">
+        <v>34</v>
+      </c>
+      <c r="AM40">
+        <v>160</v>
+      </c>
+      <c r="AN40">
+        <v>4.4</v>
+      </c>
+      <c r="AO40">
+        <v>230</v>
+      </c>
+      <c r="AP40">
+        <v>9.4</v>
+      </c>
+      <c r="AQ40">
+        <v>10.5</v>
+      </c>
+      <c r="AR40">
+        <v>12.5</v>
+      </c>
+      <c r="AS40">
+        <v>4.3</v>
+      </c>
+      <c r="AT40">
+        <v>9.4</v>
+      </c>
+      <c r="AU40">
+        <v>12.5</v>
+      </c>
+      <c r="AV40">
+        <v>10.5</v>
+      </c>
+      <c r="AW40">
+        <v>13</v>
+      </c>
+      <c r="AX40">
+        <v>7.8</v>
+      </c>
+      <c r="AY40">
         <v>9.6</v>
       </c>
-      <c r="Z40">
-        <v>26</v>
-      </c>
-      <c r="AA40">
-        <v>110</v>
-      </c>
-      <c r="AB40">
-        <v>7</v>
-      </c>
-      <c r="AC40">
-        <v>7.6</v>
-      </c>
-      <c r="AD40">
-        <v>21</v>
-      </c>
-      <c r="AE40">
-        <v>80</v>
-      </c>
-      <c r="AF40">
-        <v>14.5</v>
-      </c>
-      <c r="AG40">
-        <v>15</v>
-      </c>
-      <c r="AH40">
-        <v>30</v>
-      </c>
-      <c r="AI40">
-        <v>130</v>
-      </c>
-      <c r="AJ40">
-        <v>46</v>
-      </c>
-      <c r="AK40">
-        <v>44</v>
-      </c>
-      <c r="AL40">
-        <v>95</v>
-      </c>
-      <c r="AM40">
-        <v>320</v>
-      </c>
-      <c r="AN40">
-        <v>60</v>
-      </c>
-      <c r="AO40">
-        <v>140</v>
-      </c>
-      <c r="AP40">
-        <v>6.2</v>
-      </c>
-      <c r="AQ40">
-        <v>7.8</v>
-      </c>
-      <c r="AR40">
-        <v>21</v>
-      </c>
-      <c r="AS40">
-        <v>6.8</v>
-      </c>
-      <c r="AT40">
-        <v>5.8</v>
-      </c>
-      <c r="AU40">
-        <v>6.2</v>
-      </c>
-      <c r="AV40">
-        <v>15</v>
-      </c>
-      <c r="AW40">
-        <v>6.6</v>
-      </c>
-      <c r="AX40">
-        <v>11.5</v>
-      </c>
-      <c r="AY40">
-        <v>11</v>
-      </c>
       <c r="AZ40">
-        <v>5.9</v>
+        <v>9.4</v>
       </c>
       <c r="BA40">
-        <v>6.8</v>
+        <v>12.5</v>
       </c>
       <c r="BB40">
-        <v>6.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC40">
-        <v>6.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BD40">
-        <v>6.8</v>
+        <v>10</v>
       </c>
       <c r="BE40">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="BF40">
-        <v>36</v>
+        <v>3.55</v>
       </c>
       <c r="BG40">
-        <v>6.8</v>
+        <v>13</v>
       </c>
       <c r="BH40" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="41" spans="1:60">
@@ -8220,181 +8232,181 @@
         <v>80</v>
       </c>
       <c r="B41" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C41" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D41" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E41" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="F41">
-        <v>1.34</v>
+        <v>2.36</v>
       </c>
       <c r="G41">
+        <v>2.56</v>
+      </c>
+      <c r="H41">
+        <v>3.5</v>
+      </c>
+      <c r="I41">
+        <v>4.1</v>
+      </c>
+      <c r="J41">
+        <v>2.9</v>
+      </c>
+      <c r="K41">
+        <v>3.2</v>
+      </c>
+      <c r="L41">
+        <v>1.58</v>
+      </c>
+      <c r="M41">
+        <v>1.15</v>
+      </c>
+      <c r="N41">
+        <v>2.28</v>
+      </c>
+      <c r="O41">
+        <v>1.68</v>
+      </c>
+      <c r="P41">
+        <v>1.44</v>
+      </c>
+      <c r="Q41">
+        <v>3</v>
+      </c>
+      <c r="R41">
+        <v>1.14</v>
+      </c>
+      <c r="S41">
+        <v>6.8</v>
+      </c>
+      <c r="T41">
+        <v>2.2</v>
+      </c>
+      <c r="U41">
         <v>1.62</v>
       </c>
-      <c r="H41">
-        <v>2.68</v>
-      </c>
-      <c r="I41">
-        <v>100</v>
-      </c>
-      <c r="J41">
-        <v>2.68</v>
-      </c>
-      <c r="K41">
+      <c r="V41">
+        <v>1.33</v>
+      </c>
+      <c r="W41">
+        <v>1.64</v>
+      </c>
+      <c r="X41">
+        <v>8.4</v>
+      </c>
+      <c r="Y41">
+        <v>9.6</v>
+      </c>
+      <c r="Z41">
+        <v>26</v>
+      </c>
+      <c r="AA41">
+        <v>110</v>
+      </c>
+      <c r="AB41">
+        <v>7</v>
+      </c>
+      <c r="AC41">
+        <v>7.6</v>
+      </c>
+      <c r="AD41">
+        <v>21</v>
+      </c>
+      <c r="AE41">
+        <v>80</v>
+      </c>
+      <c r="AF41">
+        <v>14.5</v>
+      </c>
+      <c r="AG41">
+        <v>15</v>
+      </c>
+      <c r="AH41">
+        <v>30</v>
+      </c>
+      <c r="AI41">
+        <v>130</v>
+      </c>
+      <c r="AJ41">
+        <v>46</v>
+      </c>
+      <c r="AK41">
+        <v>44</v>
+      </c>
+      <c r="AL41">
         <v>85</v>
       </c>
-      <c r="L41">
-        <v>0</v>
-      </c>
-      <c r="M41">
-        <v>0</v>
-      </c>
-      <c r="N41">
-        <v>0</v>
-      </c>
-      <c r="O41">
-        <v>0</v>
-      </c>
-      <c r="P41">
-        <v>1.91</v>
-      </c>
-      <c r="Q41">
-        <v>1.63</v>
-      </c>
-      <c r="R41">
-        <v>0</v>
-      </c>
-      <c r="S41">
-        <v>0</v>
-      </c>
-      <c r="T41">
-        <v>0</v>
-      </c>
-      <c r="U41">
-        <v>0</v>
-      </c>
-      <c r="V41">
-        <v>0</v>
-      </c>
-      <c r="W41">
-        <v>0</v>
-      </c>
-      <c r="X41">
-        <v>0</v>
-      </c>
-      <c r="Y41">
-        <v>0</v>
-      </c>
-      <c r="Z41">
-        <v>0</v>
-      </c>
-      <c r="AA41">
-        <v>0</v>
-      </c>
-      <c r="AB41">
-        <v>0</v>
-      </c>
-      <c r="AC41">
-        <v>0</v>
-      </c>
-      <c r="AD41">
-        <v>0</v>
-      </c>
-      <c r="AE41">
-        <v>0</v>
-      </c>
-      <c r="AF41">
-        <v>0</v>
-      </c>
-      <c r="AG41">
-        <v>0</v>
-      </c>
-      <c r="AH41">
-        <v>0</v>
-      </c>
-      <c r="AI41">
-        <v>0</v>
-      </c>
-      <c r="AJ41">
-        <v>0</v>
-      </c>
-      <c r="AK41">
-        <v>0</v>
-      </c>
-      <c r="AL41">
-        <v>0</v>
-      </c>
       <c r="AM41">
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="AN41">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AO41">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AP41">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AQ41">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AR41">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AS41">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AT41">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AU41">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AV41">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AW41">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AX41">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AY41">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AZ41">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="BA41">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BB41">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BC41">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BD41">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BE41">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BF41">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BG41">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BH41" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="42" spans="1:60">
@@ -8402,181 +8414,181 @@
         <v>81</v>
       </c>
       <c r="B42" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C42" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D42" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E42" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="F42">
-        <v>1.55</v>
+        <v>1.34</v>
       </c>
       <c r="G42">
-        <v>2.64</v>
+        <v>1.62</v>
       </c>
       <c r="H42">
-        <v>2.84</v>
+        <v>2.68</v>
       </c>
       <c r="I42">
-        <v>4.5</v>
+        <v>100</v>
       </c>
       <c r="J42">
-        <v>3.05</v>
+        <v>2.68</v>
       </c>
       <c r="K42">
-        <v>150</v>
+        <v>85</v>
       </c>
       <c r="L42">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M42">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N42">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O42">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="P42">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="Q42">
-        <v>1.69</v>
+        <v>1.63</v>
       </c>
       <c r="R42">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S42">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T42">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U42">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V42">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W42">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="X42">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y42">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z42">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA42">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB42">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC42">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD42">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE42">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF42">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG42">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH42">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI42">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ42">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK42">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL42">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM42">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN42">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO42">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP42">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ42">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR42">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS42">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT42">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU42">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV42">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW42">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX42">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY42">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ42">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA42">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB42">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC42">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD42">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE42">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF42">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG42">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH42" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="43" spans="1:60">
@@ -8584,16 +8596,16 @@
         <v>82</v>
       </c>
       <c r="B43" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C43" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D43" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E43" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="F43">
         <v>0</v>
@@ -8758,189 +8770,371 @@
         <v>0</v>
       </c>
       <c r="BH43" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="44" spans="1:60">
       <c r="A44" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="B44" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C44" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D44" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E44" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="F44">
+        <v>1.55</v>
+      </c>
+      <c r="G44">
+        <v>2.64</v>
+      </c>
+      <c r="H44">
+        <v>2.84</v>
+      </c>
+      <c r="I44">
+        <v>4.5</v>
+      </c>
+      <c r="J44">
+        <v>3.05</v>
+      </c>
+      <c r="K44">
+        <v>150</v>
+      </c>
+      <c r="L44">
+        <v>0</v>
+      </c>
+      <c r="M44">
+        <v>0</v>
+      </c>
+      <c r="N44">
+        <v>0</v>
+      </c>
+      <c r="O44">
+        <v>0</v>
+      </c>
+      <c r="P44">
+        <v>1.96</v>
+      </c>
+      <c r="Q44">
+        <v>1.69</v>
+      </c>
+      <c r="R44">
+        <v>0</v>
+      </c>
+      <c r="S44">
+        <v>0</v>
+      </c>
+      <c r="T44">
+        <v>0</v>
+      </c>
+      <c r="U44">
+        <v>0</v>
+      </c>
+      <c r="V44">
+        <v>0</v>
+      </c>
+      <c r="W44">
+        <v>0</v>
+      </c>
+      <c r="X44">
+        <v>0</v>
+      </c>
+      <c r="Y44">
+        <v>0</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+      <c r="AA44">
+        <v>0</v>
+      </c>
+      <c r="AB44">
+        <v>0</v>
+      </c>
+      <c r="AC44">
+        <v>0</v>
+      </c>
+      <c r="AD44">
+        <v>0</v>
+      </c>
+      <c r="AE44">
+        <v>0</v>
+      </c>
+      <c r="AF44">
+        <v>0</v>
+      </c>
+      <c r="AG44">
+        <v>0</v>
+      </c>
+      <c r="AH44">
+        <v>0</v>
+      </c>
+      <c r="AI44">
+        <v>0</v>
+      </c>
+      <c r="AJ44">
+        <v>0</v>
+      </c>
+      <c r="AK44">
+        <v>0</v>
+      </c>
+      <c r="AL44">
+        <v>0</v>
+      </c>
+      <c r="AM44">
+        <v>0</v>
+      </c>
+      <c r="AN44">
+        <v>0</v>
+      </c>
+      <c r="AO44">
+        <v>0</v>
+      </c>
+      <c r="AP44">
+        <v>0</v>
+      </c>
+      <c r="AQ44">
+        <v>0</v>
+      </c>
+      <c r="AR44">
+        <v>0</v>
+      </c>
+      <c r="AS44">
+        <v>0</v>
+      </c>
+      <c r="AT44">
+        <v>0</v>
+      </c>
+      <c r="AU44">
+        <v>0</v>
+      </c>
+      <c r="AV44">
+        <v>0</v>
+      </c>
+      <c r="AW44">
+        <v>0</v>
+      </c>
+      <c r="AX44">
+        <v>0</v>
+      </c>
+      <c r="AY44">
+        <v>0</v>
+      </c>
+      <c r="AZ44">
+        <v>0</v>
+      </c>
+      <c r="BA44">
+        <v>0</v>
+      </c>
+      <c r="BB44">
+        <v>0</v>
+      </c>
+      <c r="BC44">
+        <v>0</v>
+      </c>
+      <c r="BD44">
+        <v>0</v>
+      </c>
+      <c r="BE44">
+        <v>0</v>
+      </c>
+      <c r="BF44">
+        <v>0</v>
+      </c>
+      <c r="BG44">
+        <v>0</v>
+      </c>
+      <c r="BH44" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="45" spans="1:60">
+      <c r="A45" t="s">
+        <v>80</v>
+      </c>
+      <c r="B45" t="s">
+        <v>84</v>
+      </c>
+      <c r="C45" t="s">
+        <v>101</v>
+      </c>
+      <c r="D45" t="s">
+        <v>145</v>
+      </c>
+      <c r="E45" t="s">
+        <v>189</v>
+      </c>
+      <c r="F45">
         <v>1.61</v>
       </c>
-      <c r="G44">
+      <c r="G45">
         <v>1.74</v>
       </c>
-      <c r="H44">
+      <c r="H45">
         <v>6.4</v>
       </c>
-      <c r="I44">
+      <c r="I45">
         <v>7.8</v>
       </c>
-      <c r="J44">
+      <c r="J45">
         <v>3.55</v>
       </c>
-      <c r="K44">
+      <c r="K45">
         <v>4.5</v>
       </c>
-      <c r="L44">
-        <v>1.43</v>
-      </c>
-      <c r="M44">
+      <c r="L45">
+        <v>1.48</v>
+      </c>
+      <c r="M45">
         <v>1.09</v>
       </c>
-      <c r="N44">
+      <c r="N45">
         <v>2.92</v>
       </c>
-      <c r="O44">
+      <c r="O45">
         <v>1.44</v>
       </c>
-      <c r="P44">
+      <c r="P45">
         <v>1.65</v>
       </c>
-      <c r="Q44">
-        <v>2.18</v>
-      </c>
-      <c r="R44">
+      <c r="Q45">
+        <v>2.26</v>
+      </c>
+      <c r="R45">
         <v>1.23</v>
       </c>
-      <c r="S44">
+      <c r="S45">
         <v>4.4</v>
       </c>
-      <c r="T44">
+      <c r="T45">
         <v>2.2</v>
       </c>
-      <c r="U44">
+      <c r="U45">
         <v>1.7</v>
       </c>
-      <c r="V44">
+      <c r="V45">
         <v>1.14</v>
       </c>
-      <c r="W44">
+      <c r="W45">
         <v>2.34</v>
       </c>
-      <c r="X44">
+      <c r="X45">
         <v>12.5</v>
       </c>
-      <c r="Y44">
+      <c r="Y45">
         <v>21</v>
       </c>
-      <c r="Z44">
+      <c r="Z45">
         <v>70</v>
       </c>
-      <c r="AA44">
+      <c r="AA45">
         <v>300</v>
       </c>
-      <c r="AB44">
+      <c r="AB45">
         <v>7.4</v>
       </c>
-      <c r="AC44">
+      <c r="AC45">
         <v>10</v>
       </c>
-      <c r="AD44">
+      <c r="AD45">
         <v>34</v>
       </c>
-      <c r="AE44">
+      <c r="AE45">
         <v>160</v>
       </c>
-      <c r="AF44">
+      <c r="AF45">
         <v>10</v>
       </c>
-      <c r="AG44">
+      <c r="AG45">
         <v>12</v>
       </c>
-      <c r="AH44">
+      <c r="AH45">
         <v>29</v>
       </c>
-      <c r="AI44">
+      <c r="AI45">
         <v>160</v>
       </c>
-      <c r="AJ44">
+      <c r="AJ45">
         <v>19.5</v>
       </c>
-      <c r="AK44">
+      <c r="AK45">
         <v>23</v>
       </c>
-      <c r="AL44">
+      <c r="AL45">
         <v>65</v>
       </c>
-      <c r="AM44">
+      <c r="AM45">
         <v>250</v>
       </c>
-      <c r="AN44">
+      <c r="AN45">
         <v>17</v>
       </c>
-      <c r="AO44">
+      <c r="AO45">
         <v>280</v>
       </c>
-      <c r="AP44">
+      <c r="AP45">
         <v>3.85</v>
       </c>
-      <c r="AQ44">
+      <c r="AQ45">
         <v>14.5</v>
       </c>
-      <c r="AR44">
+      <c r="AR45">
         <v>5.1</v>
       </c>
-      <c r="AS44">
+      <c r="AS45">
         <v>5.5</v>
       </c>
-      <c r="AT44">
+      <c r="AT45">
         <v>5.6</v>
       </c>
-      <c r="AU44">
+      <c r="AU45">
         <v>7.4</v>
       </c>
-      <c r="AV44">
+      <c r="AV45">
         <v>4.7</v>
       </c>
-      <c r="AW44">
+      <c r="AW45">
         <v>5.4</v>
       </c>
-      <c r="AX44">
+      <c r="AX45">
         <v>7.4</v>
       </c>
-      <c r="AY44">
+      <c r="AY45">
         <v>3.8</v>
       </c>
-      <c r="AZ44">
+      <c r="AZ45">
         <v>4.7</v>
       </c>
-      <c r="BA44">
+      <c r="BA45">
         <v>5.4</v>
       </c>
-      <c r="BB44">
+      <c r="BB45">
         <v>14</v>
       </c>
-      <c r="BC44">
+      <c r="BC45">
         <v>4.5</v>
       </c>
-      <c r="BD44">
+      <c r="BD45">
         <v>5.1</v>
       </c>
-      <c r="BE44">
+      <c r="BE45">
         <v>5.4</v>
       </c>
-      <c r="BF44">
+      <c r="BF45">
         <v>11</v>
       </c>
-      <c r="BG44">
+      <c r="BG45">
         <v>5.5</v>
       </c>
-      <c r="BH44" t="s">
-        <v>186</v>
+      <c r="BH45" t="s">
+        <v>190</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-04.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="181">
   <si>
     <t>League</t>
   </si>
@@ -205,6 +205,9 @@
     <t>Romanian Liga I</t>
   </si>
   <si>
+    <t>Azerbaijan Premier League</t>
+  </si>
+  <si>
     <t>Irish Premier Division</t>
   </si>
   <si>
@@ -214,45 +217,36 @@
     <t>Finnish Veikkausliiga</t>
   </si>
   <si>
+    <t>Austrian Bundesliga</t>
+  </si>
+  <si>
+    <t>Italian Serie A</t>
+  </si>
+  <si>
+    <t>Scottish Premiership</t>
+  </si>
+  <si>
+    <t>Algerian Ligue 1</t>
+  </si>
+  <si>
+    <t>Polish Ekstraklasa</t>
+  </si>
+  <si>
+    <t>Portuguese Segunda Liga</t>
+  </si>
+  <si>
+    <t>Norwegian Eliteserien</t>
+  </si>
+  <si>
+    <t>Danish Superliga</t>
+  </si>
+  <si>
+    <t>Israeli Premier League</t>
+  </si>
+  <si>
     <t>Saudi Professional League</t>
   </si>
   <si>
-    <t>Austrian Bundesliga</t>
-  </si>
-  <si>
-    <t>Italian Serie A</t>
-  </si>
-  <si>
-    <t>Scottish Premiership</t>
-  </si>
-  <si>
-    <t>Portuguese Segunda Liga</t>
-  </si>
-  <si>
-    <t>Swedish Allsvenskan</t>
-  </si>
-  <si>
-    <t>Polish Ekstraklasa</t>
-  </si>
-  <si>
-    <t>Israeli Premier League</t>
-  </si>
-  <si>
-    <t>Danish Superliga</t>
-  </si>
-  <si>
-    <t>Norwegian Eliteserien</t>
-  </si>
-  <si>
-    <t>Swedish Superettan</t>
-  </si>
-  <si>
-    <t>Spanish Segunda Division</t>
-  </si>
-  <si>
-    <t>Spanish La Liga</t>
-  </si>
-  <si>
     <t>Portuguese Primeira Liga</t>
   </si>
   <si>
@@ -262,12 +256,12 @@
     <t>Colombian Primera B</t>
   </si>
   <si>
+    <t>Chilean Primera B</t>
+  </si>
+  <si>
     <t>Brazilian Serie B</t>
   </si>
   <si>
-    <t>Chilean Primera B</t>
-  </si>
-  <si>
     <t>2026-05-04</t>
   </si>
   <si>
@@ -277,21 +271,21 @@
     <t>11:30:00</t>
   </si>
   <si>
+    <t>12:30:00</t>
+  </si>
+  <si>
     <t>13:00:00</t>
   </si>
   <si>
-    <t>13:10:00</t>
-  </si>
-  <si>
     <t>13:30:00</t>
   </si>
   <si>
+    <t>13:45:00</t>
+  </si>
+  <si>
     <t>14:00:00</t>
   </si>
   <si>
-    <t>14:05:00</t>
-  </si>
-  <si>
     <t>14:30:00</t>
   </si>
   <si>
@@ -331,24 +325,27 @@
     <t>Unirea Slobozia</t>
   </si>
   <si>
+    <t>Qarabag FK</t>
+  </si>
+  <si>
     <t>Shamrock Rovers</t>
   </si>
   <si>
     <t>Bohemians</t>
   </si>
   <si>
+    <t>Sligo Rovers</t>
+  </si>
+  <si>
+    <t>Derry City</t>
+  </si>
+  <si>
+    <t>Kerry FC</t>
+  </si>
+  <si>
     <t>Waterford</t>
   </si>
   <si>
-    <t>Derry City</t>
-  </si>
-  <si>
-    <t>Kerry FC</t>
-  </si>
-  <si>
-    <t>Sligo Rovers</t>
-  </si>
-  <si>
     <t>Cobh Ramblers</t>
   </si>
   <si>
@@ -364,9 +361,6 @@
     <t>Longford</t>
   </si>
   <si>
-    <t>Al-Feiha</t>
-  </si>
-  <si>
     <t>SCR Altach</t>
   </si>
   <si>
@@ -376,42 +370,36 @@
     <t>Hearts</t>
   </si>
   <si>
+    <t>Belouizdad</t>
+  </si>
+  <si>
+    <t>Radomiak Radom</t>
+  </si>
+  <si>
+    <t>Porto B</t>
+  </si>
+  <si>
     <t>Torreense</t>
   </si>
   <si>
-    <t>Halmstads</t>
-  </si>
-  <si>
-    <t>Djurgardens</t>
-  </si>
-  <si>
-    <t>Porto B</t>
-  </si>
-  <si>
-    <t>Radomiak Radom</t>
+    <t>Bodo Glimt</t>
+  </si>
+  <si>
+    <t>Midtjylland</t>
   </si>
   <si>
     <t>Bnei Sakhnin</t>
   </si>
   <si>
+    <t>Wadi Degla</t>
+  </si>
+  <si>
+    <t>Al Ittihad (EGY)</t>
+  </si>
+  <si>
     <t>Maccabi Netanya</t>
   </si>
   <si>
-    <t>Wadi Degla</t>
-  </si>
-  <si>
-    <t>Al Ittihad (EGY)</t>
-  </si>
-  <si>
-    <t>Midtjylland</t>
-  </si>
-  <si>
-    <t>Bodo Glimt</t>
-  </si>
-  <si>
-    <t>Landskrona</t>
-  </si>
-  <si>
     <t>Rapid Bucharest</t>
   </si>
   <si>
@@ -421,9 +409,6 @@
     <t>Al-Ettifaq</t>
   </si>
   <si>
-    <t>Almeria</t>
-  </si>
-  <si>
     <t>LASK Linz</t>
   </si>
   <si>
@@ -433,9 +418,6 @@
     <t>Everton</t>
   </si>
   <si>
-    <t>Sevilla</t>
-  </si>
-  <si>
     <t>Sporting Lisbon</t>
   </si>
   <si>
@@ -445,12 +427,12 @@
     <t>Union Magdalena</t>
   </si>
   <si>
+    <t>San Luis</t>
+  </si>
+  <si>
     <t>Vila Nova</t>
   </si>
   <si>
-    <t>San Luis</t>
-  </si>
-  <si>
     <t>Velez Sarsfield</t>
   </si>
   <si>
@@ -463,24 +445,27 @@
     <t>Hermannstadt</t>
   </si>
   <si>
+    <t>PFK Turan Tovuz</t>
+  </si>
+  <si>
     <t>Drogheda</t>
   </si>
   <si>
     <t>Shelbourne</t>
   </si>
   <si>
+    <t>St Patricks</t>
+  </si>
+  <si>
+    <t>Galway Utd</t>
+  </si>
+  <si>
+    <t>Cork City</t>
+  </si>
+  <si>
     <t>Dundalk</t>
   </si>
   <si>
-    <t>Galway Utd</t>
-  </si>
-  <si>
-    <t>Cork City</t>
-  </si>
-  <si>
-    <t>St Patricks</t>
-  </si>
-  <si>
     <t>UCD</t>
   </si>
   <si>
@@ -496,9 +481,6 @@
     <t>Athlone Town</t>
   </si>
   <si>
-    <t>Al Riyadh SC</t>
-  </si>
-  <si>
     <t>RZ Pellets WAC</t>
   </si>
   <si>
@@ -508,42 +490,36 @@
     <t>Rangers</t>
   </si>
   <si>
+    <t>USM Khenchela</t>
+  </si>
+  <si>
+    <t>Lechia Gdansk</t>
+  </si>
+  <si>
+    <t>Felgueiras</t>
+  </si>
+  <si>
     <t>Penafiel</t>
   </si>
   <si>
-    <t>Brommapojkarna</t>
-  </si>
-  <si>
-    <t>IFK Goteborg</t>
-  </si>
-  <si>
-    <t>Felgueiras</t>
-  </si>
-  <si>
-    <t>Lechia Gdansk</t>
+    <t>Molde</t>
+  </si>
+  <si>
+    <t>Viborg</t>
   </si>
   <si>
     <t>Maccabi Bnei Raina</t>
   </si>
   <si>
+    <t>Kahraba Ismailia</t>
+  </si>
+  <si>
+    <t>Petrojet</t>
+  </si>
+  <si>
     <t>Hapoel Jerusalem</t>
   </si>
   <si>
-    <t>Kahraba Ismailia</t>
-  </si>
-  <si>
-    <t>Petrojet</t>
-  </si>
-  <si>
-    <t>Viborg</t>
-  </si>
-  <si>
-    <t>Molde</t>
-  </si>
-  <si>
-    <t>Osters</t>
-  </si>
-  <si>
     <t>CFR Cluj</t>
   </si>
   <si>
@@ -553,9 +529,6 @@
     <t>Al Najma Club</t>
   </si>
   <si>
-    <t>Mirandes</t>
-  </si>
-  <si>
     <t>Rapid Vienna</t>
   </si>
   <si>
@@ -565,9 +538,6 @@
     <t>Man City</t>
   </si>
   <si>
-    <t>Real Sociedad</t>
-  </si>
-  <si>
     <t>Guimaraes</t>
   </si>
   <si>
@@ -577,16 +547,16 @@
     <t>Barranquilla</t>
   </si>
   <si>
+    <t>Union San Felipe</t>
+  </si>
+  <si>
     <t>Athletic Club</t>
   </si>
   <si>
-    <t>Union San Felipe</t>
-  </si>
-  <si>
     <t>Newells</t>
   </si>
   <si>
-    <t>2026-05-02 19:11:45</t>
+    <t>2026-05-02 21:42:10</t>
   </si>
 </sst>
 </file>
@@ -944,7 +914,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BH45"/>
+  <dimension ref="A1:BH41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:60">
@@ -1134,16 +1104,16 @@
         <v>60</v>
       </c>
       <c r="B2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E2" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="F2">
         <v>3.15</v>
@@ -1155,7 +1125,7 @@
         <v>2.58</v>
       </c>
       <c r="I2">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="J2">
         <v>2.74</v>
@@ -1194,13 +1164,13 @@
         <v>1.68</v>
       </c>
       <c r="V2">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W2">
         <v>1.37</v>
       </c>
       <c r="X2">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="Y2">
         <v>8.6</v>
@@ -1263,19 +1233,19 @@
         <v>12</v>
       </c>
       <c r="AS2">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AT2">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AU2">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AV2">
         <v>10.5</v>
       </c>
       <c r="AW2">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AX2">
         <v>16</v>
@@ -1284,31 +1254,31 @@
         <v>12</v>
       </c>
       <c r="AZ2">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BA2">
+        <v>5</v>
+      </c>
+      <c r="BB2">
+        <v>5</v>
+      </c>
+      <c r="BC2">
+        <v>4.9</v>
+      </c>
+      <c r="BD2">
+        <v>5</v>
+      </c>
+      <c r="BE2">
         <v>5.2</v>
       </c>
-      <c r="BB2">
-        <v>5.1</v>
-      </c>
-      <c r="BC2">
-        <v>5.1</v>
-      </c>
-      <c r="BD2">
-        <v>5.2</v>
-      </c>
-      <c r="BE2">
-        <v>5.3</v>
-      </c>
       <c r="BF2">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BG2">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BH2" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
     </row>
     <row r="3" spans="1:60">
@@ -1316,16 +1286,16 @@
         <v>61</v>
       </c>
       <c r="B3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E3" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="F3">
         <v>1.71</v>
@@ -1334,16 +1304,16 @@
         <v>1.73</v>
       </c>
       <c r="H3">
+        <v>5.3</v>
+      </c>
+      <c r="I3">
         <v>5.4</v>
-      </c>
-      <c r="I3">
-        <v>5.5</v>
       </c>
       <c r="J3">
         <v>4.2</v>
       </c>
       <c r="K3">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L3">
         <v>1.34</v>
@@ -1388,7 +1358,7 @@
         <v>22</v>
       </c>
       <c r="Z3">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AA3">
         <v>130</v>
@@ -1436,13 +1406,13 @@
         <v>55</v>
       </c>
       <c r="AP3">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AQ3">
         <v>20</v>
       </c>
       <c r="AR3">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AS3">
         <v>46</v>
@@ -1463,13 +1433,13 @@
         <v>10.5</v>
       </c>
       <c r="AY3">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ3">
         <v>17</v>
       </c>
       <c r="BA3">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BB3">
         <v>16.5</v>
@@ -1481,7 +1451,7 @@
         <v>27</v>
       </c>
       <c r="BE3">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BF3">
         <v>8</v>
@@ -1490,7 +1460,7 @@
         <v>50</v>
       </c>
       <c r="BH3" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
     </row>
     <row r="4" spans="1:60">
@@ -1498,22 +1468,22 @@
         <v>62</v>
       </c>
       <c r="B4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C4" t="s">
         <v>84</v>
       </c>
-      <c r="C4" t="s">
-        <v>86</v>
-      </c>
       <c r="D4" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E4" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="F4">
         <v>3.75</v>
       </c>
       <c r="G4">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="H4">
         <v>2.08</v>
@@ -1540,7 +1510,7 @@
         <v>1.41</v>
       </c>
       <c r="P4">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="Q4">
         <v>2.06</v>
@@ -1672,7 +1642,7 @@
         <v>3.75</v>
       </c>
       <c r="BH4" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
     </row>
     <row r="5" spans="1:60">
@@ -1680,577 +1650,577 @@
         <v>63</v>
       </c>
       <c r="B5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D5" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E5" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="F5">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="G5">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="H5">
-        <v>7.6</v>
+        <v>5.3</v>
       </c>
       <c r="I5">
-        <v>11</v>
+        <v>150</v>
       </c>
       <c r="J5">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="K5">
-        <v>5.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="L5">
         <v>1.01</v>
       </c>
       <c r="M5">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="N5">
-        <v>3.5</v>
+        <v>1.81</v>
       </c>
       <c r="O5">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="P5">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="Q5">
-        <v>1.98</v>
+        <v>1.71</v>
       </c>
       <c r="R5">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="S5">
-        <v>3.15</v>
+        <v>1.71</v>
       </c>
       <c r="T5">
-        <v>1.93</v>
+        <v>1.01</v>
       </c>
       <c r="U5">
-        <v>1.63</v>
+        <v>1.01</v>
       </c>
       <c r="V5">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="W5">
-        <v>2.6</v>
+        <v>2.28</v>
       </c>
       <c r="X5">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="Y5">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="Z5">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AA5">
         <v>1000</v>
       </c>
       <c r="AB5">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AC5">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AD5">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AE5">
+        <v>1000</v>
+      </c>
+      <c r="AF5">
+        <v>1000</v>
+      </c>
+      <c r="AG5">
+        <v>1000</v>
+      </c>
+      <c r="AH5">
+        <v>1000</v>
+      </c>
+      <c r="AI5">
+        <v>1000</v>
+      </c>
+      <c r="AJ5">
+        <v>1000</v>
+      </c>
+      <c r="AK5">
+        <v>1000</v>
+      </c>
+      <c r="AL5">
+        <v>1000</v>
+      </c>
+      <c r="AM5">
+        <v>1000</v>
+      </c>
+      <c r="AN5">
+        <v>1000</v>
+      </c>
+      <c r="AO5">
+        <v>1000</v>
+      </c>
+      <c r="AP5">
+        <v>1.01</v>
+      </c>
+      <c r="AQ5">
+        <v>1.01</v>
+      </c>
+      <c r="AR5">
+        <v>1.01</v>
+      </c>
+      <c r="AS5">
+        <v>1.01</v>
+      </c>
+      <c r="AT5">
+        <v>1.01</v>
+      </c>
+      <c r="AU5">
+        <v>1.01</v>
+      </c>
+      <c r="AV5">
+        <v>1.01</v>
+      </c>
+      <c r="AW5">
+        <v>1.01</v>
+      </c>
+      <c r="AX5">
+        <v>1.01</v>
+      </c>
+      <c r="AY5">
+        <v>1.01</v>
+      </c>
+      <c r="AZ5">
+        <v>1.01</v>
+      </c>
+      <c r="BA5">
+        <v>1.01</v>
+      </c>
+      <c r="BB5">
+        <v>1.01</v>
+      </c>
+      <c r="BC5">
+        <v>1.01</v>
+      </c>
+      <c r="BD5">
+        <v>1.01</v>
+      </c>
+      <c r="BE5">
+        <v>1.01</v>
+      </c>
+      <c r="BF5">
+        <v>1.01</v>
+      </c>
+      <c r="BG5">
+        <v>1.01</v>
+      </c>
+      <c r="BH5" t="s">
         <v>180</v>
-      </c>
-      <c r="AF5">
-        <v>10</v>
-      </c>
-      <c r="AG5">
-        <v>12.5</v>
-      </c>
-      <c r="AH5">
-        <v>34</v>
-      </c>
-      <c r="AI5">
-        <v>170</v>
-      </c>
-      <c r="AJ5">
-        <v>16.5</v>
-      </c>
-      <c r="AK5">
-        <v>22</v>
-      </c>
-      <c r="AL5">
-        <v>55</v>
-      </c>
-      <c r="AM5">
-        <v>230</v>
-      </c>
-      <c r="AN5">
-        <v>11.5</v>
-      </c>
-      <c r="AO5">
-        <v>1000</v>
-      </c>
-      <c r="AP5">
-        <v>3.5</v>
-      </c>
-      <c r="AQ5">
-        <v>16.5</v>
-      </c>
-      <c r="AR5">
-        <v>4.3</v>
-      </c>
-      <c r="AS5">
-        <v>4.5</v>
-      </c>
-      <c r="AT5">
-        <v>5.4</v>
-      </c>
-      <c r="AU5">
-        <v>7.4</v>
-      </c>
-      <c r="AV5">
-        <v>4</v>
-      </c>
-      <c r="AW5">
-        <v>4.4</v>
-      </c>
-      <c r="AX5">
-        <v>7</v>
-      </c>
-      <c r="AY5">
-        <v>3.35</v>
-      </c>
-      <c r="AZ5">
-        <v>19.5</v>
-      </c>
-      <c r="BA5">
-        <v>4.4</v>
-      </c>
-      <c r="BB5">
-        <v>10</v>
-      </c>
-      <c r="BC5">
-        <v>13</v>
-      </c>
-      <c r="BD5">
-        <v>4.2</v>
-      </c>
-      <c r="BE5">
-        <v>4.4</v>
-      </c>
-      <c r="BF5">
-        <v>7</v>
-      </c>
-      <c r="BG5">
-        <v>4.5</v>
-      </c>
-      <c r="BH5" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="6" spans="1:60">
       <c r="A6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B6" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D6" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E6" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="F6">
-        <v>2.04</v>
+        <v>1.49</v>
       </c>
       <c r="G6">
-        <v>2.28</v>
+        <v>1.62</v>
       </c>
       <c r="H6">
-        <v>3.75</v>
+        <v>7.6</v>
       </c>
       <c r="I6">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="J6">
+        <v>3.7</v>
+      </c>
+      <c r="K6">
+        <v>5.1</v>
+      </c>
+      <c r="L6">
+        <v>1.01</v>
+      </c>
+      <c r="M6">
+        <v>1.07</v>
+      </c>
+      <c r="N6">
+        <v>3.45</v>
+      </c>
+      <c r="O6">
+        <v>1.33</v>
+      </c>
+      <c r="P6">
+        <v>1.84</v>
+      </c>
+      <c r="Q6">
+        <v>1.98</v>
+      </c>
+      <c r="R6">
+        <v>1.32</v>
+      </c>
+      <c r="S6">
+        <v>3.55</v>
+      </c>
+      <c r="T6">
+        <v>1.93</v>
+      </c>
+      <c r="U6">
+        <v>1.63</v>
+      </c>
+      <c r="V6">
+        <v>1.12</v>
+      </c>
+      <c r="W6">
+        <v>2.52</v>
+      </c>
+      <c r="X6">
+        <v>17</v>
+      </c>
+      <c r="Y6">
+        <v>27</v>
+      </c>
+      <c r="Z6">
+        <v>75</v>
+      </c>
+      <c r="AA6">
+        <v>1000</v>
+      </c>
+      <c r="AB6">
+        <v>8.6</v>
+      </c>
+      <c r="AC6">
+        <v>12</v>
+      </c>
+      <c r="AD6">
+        <v>32</v>
+      </c>
+      <c r="AE6">
+        <v>180</v>
+      </c>
+      <c r="AF6">
+        <v>10</v>
+      </c>
+      <c r="AG6">
+        <v>12.5</v>
+      </c>
+      <c r="AH6">
+        <v>29</v>
+      </c>
+      <c r="AI6">
+        <v>160</v>
+      </c>
+      <c r="AJ6">
+        <v>16.5</v>
+      </c>
+      <c r="AK6">
+        <v>22</v>
+      </c>
+      <c r="AL6">
+        <v>48</v>
+      </c>
+      <c r="AM6">
+        <v>220</v>
+      </c>
+      <c r="AN6">
+        <v>11.5</v>
+      </c>
+      <c r="AO6">
+        <v>280</v>
+      </c>
+      <c r="AP6">
+        <v>3.7</v>
+      </c>
+      <c r="AQ6">
+        <v>16.5</v>
+      </c>
+      <c r="AR6">
+        <v>4.4</v>
+      </c>
+      <c r="AS6">
+        <v>4.7</v>
+      </c>
+      <c r="AT6">
+        <v>6</v>
+      </c>
+      <c r="AU6">
+        <v>7.4</v>
+      </c>
+      <c r="AV6">
+        <v>4.1</v>
+      </c>
+      <c r="AW6">
         <v>4.6</v>
       </c>
-      <c r="J6">
-        <v>3.2</v>
-      </c>
-      <c r="K6">
-        <v>3.7</v>
-      </c>
-      <c r="L6">
-        <v>1.01</v>
-      </c>
-      <c r="M6">
-        <v>1.08</v>
-      </c>
-      <c r="N6">
-        <v>3.15</v>
-      </c>
-      <c r="O6">
-        <v>1.38</v>
-      </c>
-      <c r="P6">
-        <v>1.73</v>
-      </c>
-      <c r="Q6">
-        <v>2.1</v>
-      </c>
-      <c r="R6">
-        <v>1.28</v>
-      </c>
-      <c r="S6">
-        <v>3.85</v>
-      </c>
-      <c r="T6">
-        <v>1.87</v>
-      </c>
-      <c r="U6">
-        <v>1.95</v>
-      </c>
-      <c r="V6">
-        <v>1.29</v>
-      </c>
-      <c r="W6">
-        <v>1.78</v>
-      </c>
-      <c r="X6">
-        <v>12.5</v>
-      </c>
-      <c r="Y6">
-        <v>13.5</v>
-      </c>
-      <c r="Z6">
-        <v>30</v>
-      </c>
-      <c r="AA6">
-        <v>100</v>
-      </c>
-      <c r="AB6">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AC6">
-        <v>8</v>
-      </c>
-      <c r="AD6">
-        <v>17.5</v>
-      </c>
-      <c r="AE6">
-        <v>60</v>
-      </c>
-      <c r="AF6">
-        <v>13.5</v>
-      </c>
-      <c r="AG6">
-        <v>11.5</v>
-      </c>
-      <c r="AH6">
-        <v>21</v>
-      </c>
-      <c r="AI6">
-        <v>70</v>
-      </c>
-      <c r="AJ6">
-        <v>28</v>
-      </c>
-      <c r="AK6">
-        <v>26</v>
-      </c>
-      <c r="AL6">
-        <v>46</v>
-      </c>
-      <c r="AM6">
-        <v>140</v>
-      </c>
-      <c r="AN6">
-        <v>24</v>
-      </c>
-      <c r="AO6">
-        <v>80</v>
-      </c>
-      <c r="AP6">
+      <c r="AX6">
+        <v>7.2</v>
+      </c>
+      <c r="AY6">
+        <v>3.45</v>
+      </c>
+      <c r="AZ6">
+        <v>19.5</v>
+      </c>
+      <c r="BA6">
+        <v>4.6</v>
+      </c>
+      <c r="BB6">
         <v>10</v>
       </c>
-      <c r="AQ6">
-        <v>11</v>
-      </c>
-      <c r="AR6">
-        <v>6.8</v>
-      </c>
-      <c r="AS6">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AT6">
-        <v>7.2</v>
-      </c>
-      <c r="AU6">
-        <v>6.6</v>
-      </c>
-      <c r="AV6">
-        <v>14</v>
-      </c>
-      <c r="AW6">
-        <v>7.8</v>
-      </c>
-      <c r="AX6">
-        <v>11</v>
-      </c>
-      <c r="AY6">
-        <v>9.4</v>
-      </c>
-      <c r="AZ6">
-        <v>16.5</v>
-      </c>
-      <c r="BA6">
-        <v>8</v>
-      </c>
-      <c r="BB6">
-        <v>6.8</v>
-      </c>
       <c r="BC6">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="BD6">
-        <v>7.4</v>
+        <v>4.3</v>
       </c>
       <c r="BE6">
-        <v>8.4</v>
+        <v>4.6</v>
       </c>
       <c r="BF6">
-        <v>15.5</v>
+        <v>3.35</v>
       </c>
       <c r="BG6">
-        <v>8</v>
+        <v>4.7</v>
       </c>
       <c r="BH6" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
     </row>
     <row r="7" spans="1:60">
       <c r="A7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B7" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D7" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E7" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="F7">
-        <v>4.7</v>
+        <v>2.04</v>
       </c>
       <c r="G7">
-        <v>110</v>
+        <v>2.28</v>
       </c>
       <c r="H7">
-        <v>1.04</v>
+        <v>3.75</v>
       </c>
       <c r="I7">
-        <v>1.9</v>
+        <v>4.6</v>
       </c>
       <c r="J7">
-        <v>2.14</v>
+        <v>3.2</v>
       </c>
       <c r="K7">
-        <v>110</v>
+        <v>3.7</v>
       </c>
       <c r="L7">
         <v>1.01</v>
       </c>
       <c r="M7">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="N7">
-        <v>1.45</v>
+        <v>3.15</v>
       </c>
       <c r="O7">
-        <v>1.18</v>
+        <v>1.38</v>
       </c>
       <c r="P7">
-        <v>1.45</v>
+        <v>1.73</v>
       </c>
       <c r="Q7">
-        <v>1.52</v>
+        <v>2.1</v>
       </c>
       <c r="R7">
-        <v>1.45</v>
+        <v>1.28</v>
       </c>
       <c r="S7">
-        <v>2.3</v>
+        <v>3.85</v>
       </c>
       <c r="T7">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="U7">
-        <v>1.01</v>
+        <v>1.95</v>
       </c>
       <c r="V7">
-        <v>2.1</v>
+        <v>1.29</v>
       </c>
       <c r="W7">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="X7">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y7">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Z7">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AA7">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AB7">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC7">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AD7">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AE7">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF7">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AG7">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AH7">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI7">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ7">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AK7">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AL7">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM7">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN7">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AO7">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AP7">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AQ7">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AR7">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AS7">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT7">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AU7">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AV7">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="AW7">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AX7">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AY7">
-        <v>1.03</v>
+        <v>9.4</v>
       </c>
       <c r="AZ7">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="BA7">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="BB7">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="BC7">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="BD7">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="BE7">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="BF7">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BG7">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BH7" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
     </row>
     <row r="8" spans="1:60">
       <c r="A8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D8" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E8" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="F8">
-        <v>1.2</v>
+        <v>4</v>
       </c>
       <c r="G8">
-        <v>2.02</v>
+        <v>7.8</v>
       </c>
       <c r="H8">
-        <v>1.09</v>
+        <v>1.53</v>
       </c>
       <c r="I8">
-        <v>6.2</v>
+        <v>1.95</v>
       </c>
       <c r="J8">
-        <v>3.6</v>
+        <v>2.78</v>
       </c>
       <c r="K8">
         <v>110</v>
@@ -2262,22 +2232,22 @@
         <v>1.01</v>
       </c>
       <c r="N8">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="O8">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="P8">
         <v>1.71</v>
       </c>
       <c r="Q8">
-        <v>1.32</v>
+        <v>1.86</v>
       </c>
       <c r="R8">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S8">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="T8">
         <v>1.01</v>
@@ -2286,10 +2256,10 @@
         <v>1.01</v>
       </c>
       <c r="V8">
-        <v>1.19</v>
+        <v>2.04</v>
       </c>
       <c r="W8">
-        <v>1.98</v>
+        <v>1.16</v>
       </c>
       <c r="X8">
         <v>1000</v>
@@ -2400,7 +2370,7 @@
         <v>1.01</v>
       </c>
       <c r="BH8" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
     </row>
     <row r="9" spans="1:60">
@@ -2408,34 +2378,34 @@
         <v>64</v>
       </c>
       <c r="B9" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E9" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="F9">
-        <v>5.7</v>
+        <v>1.62</v>
       </c>
       <c r="G9">
-        <v>12</v>
+        <v>2.02</v>
       </c>
       <c r="H9">
-        <v>1.39</v>
+        <v>1.09</v>
       </c>
       <c r="I9">
-        <v>1.7</v>
+        <v>6.2</v>
       </c>
       <c r="J9">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="K9">
-        <v>9.4</v>
+        <v>110</v>
       </c>
       <c r="L9">
         <v>1.01</v>
@@ -2444,22 +2414,22 @@
         <v>1.01</v>
       </c>
       <c r="N9">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="O9">
         <v>1.32</v>
       </c>
       <c r="P9">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="Q9">
-        <v>1.78</v>
+        <v>1.32</v>
       </c>
       <c r="R9">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S9">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="T9">
         <v>1.01</v>
@@ -2468,10 +2438,10 @@
         <v>1.01</v>
       </c>
       <c r="V9">
-        <v>2.42</v>
+        <v>1.2</v>
       </c>
       <c r="W9">
-        <v>1.09</v>
+        <v>1.98</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -2582,79 +2552,79 @@
         <v>1.01</v>
       </c>
       <c r="BH9" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
     </row>
     <row r="10" spans="1:60">
       <c r="A10" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B10" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E10" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="F10">
-        <v>2.1</v>
+        <v>5.7</v>
       </c>
       <c r="G10">
-        <v>430</v>
+        <v>12</v>
       </c>
       <c r="H10">
-        <v>1.04</v>
+        <v>1.39</v>
       </c>
       <c r="I10">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="J10">
+        <v>3.75</v>
+      </c>
+      <c r="K10">
+        <v>9.4</v>
+      </c>
+      <c r="L10">
+        <v>1.01</v>
+      </c>
+      <c r="M10">
+        <v>1.01</v>
+      </c>
+      <c r="N10">
+        <v>1.74</v>
+      </c>
+      <c r="O10">
+        <v>1.32</v>
+      </c>
+      <c r="P10">
+        <v>1.74</v>
+      </c>
+      <c r="Q10">
+        <v>1.78</v>
+      </c>
+      <c r="R10">
+        <v>1.27</v>
+      </c>
+      <c r="S10">
+        <v>2.88</v>
+      </c>
+      <c r="T10">
+        <v>1.01</v>
+      </c>
+      <c r="U10">
+        <v>1.01</v>
+      </c>
+      <c r="V10">
+        <v>2.42</v>
+      </c>
+      <c r="W10">
         <v>1.09</v>
       </c>
-      <c r="K10">
-        <v>110</v>
-      </c>
-      <c r="L10">
-        <v>1.01</v>
-      </c>
-      <c r="M10">
-        <v>1.01</v>
-      </c>
-      <c r="N10">
-        <v>1.72</v>
-      </c>
-      <c r="O10">
-        <v>1.31</v>
-      </c>
-      <c r="P10">
-        <v>1.71</v>
-      </c>
-      <c r="Q10">
-        <v>1.86</v>
-      </c>
-      <c r="R10">
-        <v>1.25</v>
-      </c>
-      <c r="S10">
-        <v>3.15</v>
-      </c>
-      <c r="T10">
-        <v>1.01</v>
-      </c>
-      <c r="U10">
-        <v>1.01</v>
-      </c>
-      <c r="V10">
-        <v>2.04</v>
-      </c>
-      <c r="W10">
-        <v>1.01</v>
-      </c>
       <c r="X10">
         <v>1000</v>
       </c>
@@ -2764,7 +2734,7 @@
         <v>1.01</v>
       </c>
       <c r="BH10" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11" spans="1:60">
@@ -2772,58 +2742,58 @@
         <v>64</v>
       </c>
       <c r="B11" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D11" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E11" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="F11">
-        <v>2.26</v>
+        <v>4.7</v>
       </c>
       <c r="G11">
-        <v>3.2</v>
+        <v>7.6</v>
       </c>
       <c r="H11">
-        <v>2.4</v>
+        <v>1.51</v>
       </c>
       <c r="I11">
-        <v>3.45</v>
+        <v>1.9</v>
       </c>
       <c r="J11">
-        <v>3.15</v>
+        <v>2.92</v>
       </c>
       <c r="K11">
-        <v>7.2</v>
+        <v>110</v>
       </c>
       <c r="L11">
         <v>1.01</v>
       </c>
       <c r="M11">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N11">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="O11">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="P11">
-        <v>1.24</v>
+        <v>1.45</v>
       </c>
       <c r="Q11">
-        <v>1.66</v>
+        <v>1.52</v>
       </c>
       <c r="R11">
-        <v>1.2</v>
+        <v>1.45</v>
       </c>
       <c r="S11">
-        <v>2.66</v>
+        <v>2.3</v>
       </c>
       <c r="T11">
         <v>1.01</v>
@@ -2832,10 +2802,10 @@
         <v>1.01</v>
       </c>
       <c r="V11">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="W11">
-        <v>1.45</v>
+        <v>1.16</v>
       </c>
       <c r="X11">
         <v>1000</v>
@@ -2946,42 +2916,42 @@
         <v>1.01</v>
       </c>
       <c r="BH11" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
     </row>
     <row r="12" spans="1:60">
       <c r="A12" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B12" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C12" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D12" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E12" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="F12">
-        <v>2.88</v>
+        <v>2.26</v>
       </c>
       <c r="G12">
-        <v>4.6</v>
+        <v>3.2</v>
       </c>
       <c r="H12">
-        <v>1.97</v>
+        <v>2.4</v>
       </c>
       <c r="I12">
-        <v>2.72</v>
+        <v>3.45</v>
       </c>
       <c r="J12">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K12">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="L12">
         <v>1.01</v>
@@ -2990,22 +2960,22 @@
         <v>1.01</v>
       </c>
       <c r="N12">
-        <v>1.72</v>
+        <v>1.25</v>
       </c>
       <c r="O12">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="P12">
-        <v>1.72</v>
+        <v>1.24</v>
       </c>
       <c r="Q12">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="R12">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="S12">
-        <v>2.92</v>
+        <v>2.66</v>
       </c>
       <c r="T12">
         <v>1.01</v>
@@ -3014,10 +2984,10 @@
         <v>1.01</v>
       </c>
       <c r="V12">
-        <v>1.58</v>
+        <v>1.4</v>
       </c>
       <c r="W12">
-        <v>1.28</v>
+        <v>1.45</v>
       </c>
       <c r="X12">
         <v>1000</v>
@@ -3128,132 +3098,132 @@
         <v>1.01</v>
       </c>
       <c r="BH12" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
     </row>
     <row r="13" spans="1:60">
       <c r="A13" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B13" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C13" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D13" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E13" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="F13">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="G13">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="H13">
-        <v>2.14</v>
+        <v>1.97</v>
       </c>
       <c r="I13">
-        <v>2.58</v>
+        <v>2.68</v>
       </c>
       <c r="J13">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="K13">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="L13">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="M13">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="N13">
-        <v>3.3</v>
+        <v>1.72</v>
       </c>
       <c r="O13">
+        <v>1.3</v>
+      </c>
+      <c r="P13">
+        <v>1.72</v>
+      </c>
+      <c r="Q13">
+        <v>1.8</v>
+      </c>
+      <c r="R13">
+        <v>1.26</v>
+      </c>
+      <c r="S13">
+        <v>2.92</v>
+      </c>
+      <c r="T13">
+        <v>1.01</v>
+      </c>
+      <c r="U13">
+        <v>1.01</v>
+      </c>
+      <c r="V13">
+        <v>1.6</v>
+      </c>
+      <c r="W13">
         <v>1.28</v>
       </c>
-      <c r="P13">
-        <v>1.92</v>
-      </c>
-      <c r="Q13">
-        <v>1.74</v>
-      </c>
-      <c r="R13">
-        <v>1.36</v>
-      </c>
-      <c r="S13">
-        <v>3.1</v>
-      </c>
-      <c r="T13">
-        <v>1.7</v>
-      </c>
-      <c r="U13">
-        <v>2.14</v>
-      </c>
-      <c r="V13">
-        <v>1.63</v>
-      </c>
-      <c r="W13">
-        <v>1.36</v>
-      </c>
       <c r="X13">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="Y13">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Z13">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AA13">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AB13">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AC13">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AD13">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AE13">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AF13">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AG13">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AH13">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI13">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AJ13">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AK13">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AL13">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AM13">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN13">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AO13">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AP13">
         <v>1.03</v>
@@ -3304,13 +3274,13 @@
         <v>1.03</v>
       </c>
       <c r="BF13">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BG13">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH13" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
     </row>
     <row r="14" spans="1:60">
@@ -3318,422 +3288,422 @@
         <v>65</v>
       </c>
       <c r="B14" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C14" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D14" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E14" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="F14">
-        <v>1.48</v>
+        <v>3.2</v>
       </c>
       <c r="G14">
-        <v>1.55</v>
+        <v>3.8</v>
       </c>
       <c r="H14">
-        <v>6.8</v>
+        <v>2.14</v>
       </c>
       <c r="I14">
-        <v>8.6</v>
+        <v>2.58</v>
       </c>
       <c r="J14">
-        <v>4.6</v>
+        <v>3.3</v>
       </c>
       <c r="K14">
-        <v>5.4</v>
+        <v>4.5</v>
       </c>
       <c r="L14">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M14">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="N14">
-        <v>4.7</v>
+        <v>3.3</v>
       </c>
       <c r="O14">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="P14">
-        <v>2.28</v>
+        <v>1.94</v>
       </c>
       <c r="Q14">
-        <v>1.64</v>
+        <v>1.74</v>
       </c>
       <c r="R14">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="S14">
-        <v>2.58</v>
+        <v>3.1</v>
       </c>
       <c r="T14">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="U14">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="V14">
-        <v>1.14</v>
+        <v>1.63</v>
       </c>
       <c r="W14">
-        <v>2.8</v>
+        <v>1.36</v>
       </c>
       <c r="X14">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="Y14">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="Z14">
-        <v>80</v>
+        <v>18.5</v>
       </c>
       <c r="AA14">
-        <v>260</v>
+        <v>36</v>
       </c>
       <c r="AB14">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="AC14">
+        <v>10</v>
+      </c>
+      <c r="AD14">
         <v>13.5</v>
       </c>
-      <c r="AD14">
-        <v>34</v>
-      </c>
       <c r="AE14">
-        <v>120</v>
+        <v>29</v>
       </c>
       <c r="AF14">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="AG14">
-        <v>12.5</v>
+        <v>18</v>
       </c>
       <c r="AH14">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="AI14">
+        <v>44</v>
+      </c>
+      <c r="AJ14">
+        <v>75</v>
+      </c>
+      <c r="AK14">
+        <v>48</v>
+      </c>
+      <c r="AL14">
+        <v>60</v>
+      </c>
+      <c r="AM14">
         <v>110</v>
       </c>
-      <c r="AJ14">
-        <v>16.5</v>
-      </c>
-      <c r="AK14">
-        <v>18.5</v>
-      </c>
-      <c r="AL14">
-        <v>40</v>
-      </c>
-      <c r="AM14">
-        <v>130</v>
-      </c>
       <c r="AN14">
-        <v>7.8</v>
+        <v>44</v>
       </c>
       <c r="AO14">
-        <v>140</v>
+        <v>21</v>
       </c>
       <c r="AP14">
-        <v>15.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ14">
-        <v>19.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR14">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="AS14">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="AT14">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="AU14">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="AV14">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="AW14">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="AX14">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="AY14">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="AZ14">
-        <v>16</v>
+        <v>1.03</v>
       </c>
       <c r="BA14">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="BB14">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="BC14">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="BD14">
-        <v>3.9</v>
+        <v>1.03</v>
       </c>
       <c r="BE14">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="BF14">
-        <v>4.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG14">
-        <v>4.2</v>
+        <v>13.5</v>
       </c>
       <c r="BH14" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
     </row>
     <row r="15" spans="1:60">
       <c r="A15" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B15" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C15" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D15" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E15" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="F15">
-        <v>1.89</v>
+        <v>1.48</v>
       </c>
       <c r="G15">
-        <v>2.54</v>
+        <v>1.55</v>
       </c>
       <c r="H15">
-        <v>3.1</v>
+        <v>6.8</v>
       </c>
       <c r="I15">
-        <v>4.8</v>
+        <v>8.6</v>
       </c>
       <c r="J15">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="K15">
-        <v>6.8</v>
+        <v>5.4</v>
       </c>
       <c r="L15">
         <v>1.01</v>
       </c>
       <c r="M15">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N15">
-        <v>1.81</v>
+        <v>4.7</v>
       </c>
       <c r="O15">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="P15">
-        <v>1.81</v>
+        <v>2.26</v>
       </c>
       <c r="Q15">
-        <v>1.83</v>
+        <v>1.64</v>
       </c>
       <c r="R15">
-        <v>1.31</v>
+        <v>1.5</v>
       </c>
       <c r="S15">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="T15">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="U15">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="V15">
-        <v>1.26</v>
+        <v>1.14</v>
       </c>
       <c r="W15">
-        <v>1.64</v>
+        <v>2.8</v>
       </c>
       <c r="X15">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="Y15">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Z15">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AA15">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AB15">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AC15">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AD15">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AE15">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AF15">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AG15">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH15">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI15">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ15">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AK15">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AL15">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM15">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN15">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AO15">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AP15">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="AQ15">
-        <v>1.03</v>
+        <v>19.5</v>
       </c>
       <c r="AR15">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AS15">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AT15">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AU15">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV15">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="AW15">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AX15">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AY15">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AZ15">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="BA15">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BB15">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="BC15">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="BD15">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="BE15">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BF15">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BG15">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BH15" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
     </row>
     <row r="16" spans="1:60">
       <c r="A16" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B16" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C16" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D16" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E16" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="F16">
+        <v>1.89</v>
+      </c>
+      <c r="G16">
+        <v>2.54</v>
+      </c>
+      <c r="H16">
+        <v>3.1</v>
+      </c>
+      <c r="I16">
+        <v>4.8</v>
+      </c>
+      <c r="J16">
+        <v>3.1</v>
+      </c>
+      <c r="K16">
+        <v>6.8</v>
+      </c>
+      <c r="L16">
+        <v>1.01</v>
+      </c>
+      <c r="M16">
+        <v>1.01</v>
+      </c>
+      <c r="N16">
         <v>1.81</v>
       </c>
-      <c r="G16">
-        <v>110</v>
-      </c>
-      <c r="H16">
-        <v>1.09</v>
-      </c>
-      <c r="I16">
-        <v>4</v>
-      </c>
-      <c r="J16">
-        <v>1.09</v>
-      </c>
-      <c r="K16">
-        <v>110</v>
-      </c>
-      <c r="L16">
-        <v>1.01</v>
-      </c>
-      <c r="M16">
-        <v>1.01</v>
-      </c>
-      <c r="N16">
-        <v>1.61</v>
-      </c>
       <c r="O16">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="P16">
-        <v>1.61</v>
+        <v>1.81</v>
       </c>
       <c r="Q16">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="R16">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="S16">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="T16">
         <v>1.01</v>
@@ -3742,10 +3712,10 @@
         <v>1.01</v>
       </c>
       <c r="V16">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="W16">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="X16">
         <v>1000</v>
@@ -3856,7 +3826,7 @@
         <v>1.01</v>
       </c>
       <c r="BH16" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
     </row>
     <row r="17" spans="1:60">
@@ -3864,16 +3834,16 @@
         <v>67</v>
       </c>
       <c r="B17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C17" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D17" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E17" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="F17">
         <v>2.42</v>
@@ -4038,7 +4008,7 @@
         <v>1.01</v>
       </c>
       <c r="BH17" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
     </row>
     <row r="18" spans="1:60">
@@ -4046,16 +4016,16 @@
         <v>68</v>
       </c>
       <c r="B18" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C18" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D18" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E18" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="F18">
         <v>3.1</v>
@@ -4220,7 +4190,7 @@
         <v>26</v>
       </c>
       <c r="BH18" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
     </row>
     <row r="19" spans="1:60">
@@ -4228,16 +4198,16 @@
         <v>69</v>
       </c>
       <c r="B19" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C19" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D19" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E19" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="F19">
         <v>2.78</v>
@@ -4264,28 +4234,28 @@
         <v>1.05</v>
       </c>
       <c r="N19">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="O19">
         <v>1.26</v>
       </c>
       <c r="P19">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="Q19">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="R19">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="S19">
-        <v>2.92</v>
+        <v>2.76</v>
       </c>
       <c r="T19">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="U19">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V19">
         <v>1.62</v>
@@ -4294,10 +4264,10 @@
         <v>1.52</v>
       </c>
       <c r="X19">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="Y19">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z19">
         <v>20</v>
@@ -4330,7 +4300,7 @@
         <v>34</v>
       </c>
       <c r="AJ19">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AK19">
         <v>30</v>
@@ -4342,7 +4312,7 @@
         <v>70</v>
       </c>
       <c r="AN19">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AO19">
         <v>18.5</v>
@@ -4363,7 +4333,7 @@
         <v>12</v>
       </c>
       <c r="AU19">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AV19">
         <v>10.5</v>
@@ -4372,7 +4342,7 @@
         <v>22</v>
       </c>
       <c r="AX19">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AY19">
         <v>11.5</v>
@@ -4381,19 +4351,19 @@
         <v>14</v>
       </c>
       <c r="BA19">
+        <v>28</v>
+      </c>
+      <c r="BB19">
         <v>8.6</v>
       </c>
-      <c r="BB19">
-        <v>34</v>
-      </c>
       <c r="BC19">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BD19">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="BE19">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="BF19">
         <v>19</v>
@@ -4402,7 +4372,7 @@
         <v>15.5</v>
       </c>
       <c r="BH19" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
     </row>
     <row r="20" spans="1:60">
@@ -4410,34 +4380,34 @@
         <v>70</v>
       </c>
       <c r="B20" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C20" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D20" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E20" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="F20">
-        <v>1.68</v>
+        <v>1.01</v>
       </c>
       <c r="G20">
-        <v>2.14</v>
+        <v>1000</v>
       </c>
       <c r="H20">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="I20">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="J20">
-        <v>3.2</v>
+        <v>1.01</v>
       </c>
       <c r="K20">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="L20">
         <v>1.01</v>
@@ -4446,22 +4416,22 @@
         <v>1.01</v>
       </c>
       <c r="N20">
-        <v>1.64</v>
+        <v>1.08</v>
       </c>
       <c r="O20">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="P20">
-        <v>1.64</v>
+        <v>1.24</v>
       </c>
       <c r="Q20">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="R20">
-        <v>1.23</v>
+        <v>1.12</v>
       </c>
       <c r="S20">
-        <v>3.15</v>
+        <v>1.25</v>
       </c>
       <c r="T20">
         <v>1.01</v>
@@ -4470,10 +4440,10 @@
         <v>1.01</v>
       </c>
       <c r="V20">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="W20">
-        <v>1.87</v>
+        <v>1.01</v>
       </c>
       <c r="X20">
         <v>1000</v>
@@ -4584,7 +4554,7 @@
         <v>1.01</v>
       </c>
       <c r="BH20" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
     </row>
     <row r="21" spans="1:60">
@@ -4592,398 +4562,398 @@
         <v>71</v>
       </c>
       <c r="B21" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C21" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D21" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E21" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="F21">
-        <v>3.05</v>
+        <v>1.98</v>
       </c>
       <c r="G21">
-        <v>3.25</v>
+        <v>2.66</v>
       </c>
       <c r="H21">
-        <v>2.48</v>
+        <v>2.74</v>
       </c>
       <c r="I21">
-        <v>2.6</v>
+        <v>4</v>
       </c>
       <c r="J21">
-        <v>3.45</v>
+        <v>2.56</v>
       </c>
       <c r="K21">
-        <v>3.6</v>
+        <v>110</v>
       </c>
       <c r="L21">
         <v>1.01</v>
       </c>
       <c r="M21">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="N21">
-        <v>3.6</v>
+        <v>2.02</v>
       </c>
       <c r="O21">
-        <v>1.35</v>
+        <v>1.21</v>
       </c>
       <c r="P21">
-        <v>1.88</v>
+        <v>2.02</v>
       </c>
       <c r="Q21">
-        <v>2.02</v>
+        <v>1.58</v>
       </c>
       <c r="R21">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="S21">
-        <v>3.6</v>
+        <v>2.38</v>
       </c>
       <c r="T21">
-        <v>1.79</v>
+        <v>1.01</v>
       </c>
       <c r="U21">
-        <v>2.14</v>
+        <v>1.01</v>
       </c>
       <c r="V21">
-        <v>1.62</v>
+        <v>1.33</v>
       </c>
       <c r="W21">
-        <v>1.45</v>
+        <v>1.64</v>
       </c>
       <c r="X21">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="Y21">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="Z21">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AA21">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AB21">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AC21">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD21">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AE21">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AF21">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AG21">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AH21">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AI21">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AJ21">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AK21">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AL21">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AM21">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN21">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AO21">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AP21">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ21">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AR21">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="AS21">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="AT21">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AU21">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="AV21">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW21">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="AX21">
-        <v>18</v>
+        <v>1.03</v>
       </c>
       <c r="AY21">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AZ21">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="BA21">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="BB21">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="BC21">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="BD21">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="BE21">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="BF21">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BG21">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BH21" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
     </row>
     <row r="22" spans="1:60">
       <c r="A22" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B22" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C22" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D22" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E22" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="F22">
-        <v>1.74</v>
+        <v>2.66</v>
       </c>
       <c r="G22">
-        <v>1.79</v>
+        <v>3.95</v>
       </c>
       <c r="H22">
-        <v>5.2</v>
+        <v>2.18</v>
       </c>
       <c r="I22">
-        <v>5.6</v>
+        <v>3</v>
       </c>
       <c r="J22">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="K22">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="L22">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="M22">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="N22">
-        <v>3.8</v>
+        <v>1.53</v>
       </c>
       <c r="O22">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="P22">
-        <v>1.93</v>
+        <v>1.53</v>
       </c>
       <c r="Q22">
-        <v>1.92</v>
+        <v>2.08</v>
       </c>
       <c r="R22">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="S22">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="T22">
-        <v>1.86</v>
+        <v>1.01</v>
       </c>
       <c r="U22">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="V22">
-        <v>1.21</v>
+        <v>1.5</v>
       </c>
       <c r="W22">
-        <v>2.26</v>
+        <v>1.34</v>
       </c>
       <c r="X22">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="Y22">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="Z22">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AA22">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AB22">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AC22">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AD22">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AE22">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AF22">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AG22">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AH22">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI22">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AJ22">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AK22">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AL22">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AM22">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN22">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AO22">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AP22">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="AQ22">
-        <v>15.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR22">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="AS22">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="AT22">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="AU22">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="AV22">
-        <v>17.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW22">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="AX22">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AY22">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AZ22">
-        <v>17</v>
+        <v>1.03</v>
       </c>
       <c r="BA22">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="BB22">
-        <v>15.5</v>
+        <v>1.03</v>
       </c>
       <c r="BC22">
-        <v>15.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD22">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="BE22">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="BF22">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG22">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BH22" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
     </row>
     <row r="23" spans="1:60">
       <c r="A23" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B23" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C23" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D23" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E23" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="F23">
-        <v>2.66</v>
+        <v>1.68</v>
       </c>
       <c r="G23">
-        <v>3.95</v>
+        <v>2.14</v>
       </c>
       <c r="H23">
-        <v>2.18</v>
+        <v>3.85</v>
       </c>
       <c r="I23">
-        <v>3</v>
+        <v>6.6</v>
       </c>
       <c r="J23">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="K23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L23">
         <v>1.01</v>
@@ -4992,22 +4962,22 @@
         <v>1.01</v>
       </c>
       <c r="N23">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="O23">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="P23">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="Q23">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="R23">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="S23">
-        <v>3.6</v>
+        <v>3.15</v>
       </c>
       <c r="T23">
         <v>1.01</v>
@@ -5016,10 +4986,10 @@
         <v>1.01</v>
       </c>
       <c r="V23">
-        <v>1.5</v>
+        <v>1.17</v>
       </c>
       <c r="W23">
-        <v>1.34</v>
+        <v>1.87</v>
       </c>
       <c r="X23">
         <v>1000</v>
@@ -5130,430 +5100,430 @@
         <v>1.01</v>
       </c>
       <c r="BH23" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
     </row>
     <row r="24" spans="1:60">
       <c r="A24" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B24" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C24" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D24" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E24" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="F24">
-        <v>1.73</v>
+        <v>1.39</v>
       </c>
       <c r="G24">
-        <v>2.76</v>
+        <v>1.43</v>
       </c>
       <c r="H24">
-        <v>2.74</v>
+        <v>7.2</v>
       </c>
       <c r="I24">
+        <v>9.4</v>
+      </c>
+      <c r="J24">
+        <v>5.8</v>
+      </c>
+      <c r="K24">
+        <v>6.6</v>
+      </c>
+      <c r="L24">
+        <v>1.01</v>
+      </c>
+      <c r="M24">
+        <v>1.02</v>
+      </c>
+      <c r="N24">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="O24">
+        <v>1.11</v>
+      </c>
+      <c r="P24">
+        <v>3.55</v>
+      </c>
+      <c r="Q24">
+        <v>1.33</v>
+      </c>
+      <c r="R24">
+        <v>2.04</v>
+      </c>
+      <c r="S24">
+        <v>1.83</v>
+      </c>
+      <c r="T24">
+        <v>1.58</v>
+      </c>
+      <c r="U24">
+        <v>2.5</v>
+      </c>
+      <c r="V24">
+        <v>1.12</v>
+      </c>
+      <c r="W24">
+        <v>3.25</v>
+      </c>
+      <c r="X24">
+        <v>60</v>
+      </c>
+      <c r="Y24">
+        <v>55</v>
+      </c>
+      <c r="Z24">
+        <v>95</v>
+      </c>
+      <c r="AA24">
+        <v>230</v>
+      </c>
+      <c r="AB24">
+        <v>21</v>
+      </c>
+      <c r="AC24">
+        <v>19.5</v>
+      </c>
+      <c r="AD24">
+        <v>36</v>
+      </c>
+      <c r="AE24">
+        <v>95</v>
+      </c>
+      <c r="AF24">
+        <v>16.5</v>
+      </c>
+      <c r="AG24">
+        <v>14.5</v>
+      </c>
+      <c r="AH24">
+        <v>25</v>
+      </c>
+      <c r="AI24">
+        <v>75</v>
+      </c>
+      <c r="AJ24">
+        <v>17.5</v>
+      </c>
+      <c r="AK24">
+        <v>16.5</v>
+      </c>
+      <c r="AL24">
+        <v>29</v>
+      </c>
+      <c r="AM24">
+        <v>80</v>
+      </c>
+      <c r="AN24">
+        <v>4.4</v>
+      </c>
+      <c r="AO24">
+        <v>65</v>
+      </c>
+      <c r="AP24">
+        <v>4.2</v>
+      </c>
+      <c r="AQ24">
+        <v>4.1</v>
+      </c>
+      <c r="AR24">
+        <v>4.3</v>
+      </c>
+      <c r="AS24">
+        <v>4.4</v>
+      </c>
+      <c r="AT24">
+        <v>15</v>
+      </c>
+      <c r="AU24">
+        <v>14</v>
+      </c>
+      <c r="AV24">
         <v>4</v>
       </c>
-      <c r="J24">
-        <v>2.56</v>
-      </c>
-      <c r="K24">
-        <v>110</v>
-      </c>
-      <c r="L24">
-        <v>1.01</v>
-      </c>
-      <c r="M24">
-        <v>1.04</v>
-      </c>
-      <c r="N24">
-        <v>2.02</v>
-      </c>
-      <c r="O24">
-        <v>1.21</v>
-      </c>
-      <c r="P24">
-        <v>2.02</v>
-      </c>
-      <c r="Q24">
-        <v>1.58</v>
-      </c>
-      <c r="R24">
-        <v>1.43</v>
-      </c>
-      <c r="S24">
-        <v>2.38</v>
-      </c>
-      <c r="T24">
-        <v>1.01</v>
-      </c>
-      <c r="U24">
-        <v>1.01</v>
-      </c>
-      <c r="V24">
-        <v>1.33</v>
-      </c>
-      <c r="W24">
-        <v>1.56</v>
-      </c>
-      <c r="X24">
-        <v>1000</v>
-      </c>
-      <c r="Y24">
-        <v>1000</v>
-      </c>
-      <c r="Z24">
-        <v>1000</v>
-      </c>
-      <c r="AA24">
-        <v>1000</v>
-      </c>
-      <c r="AB24">
-        <v>1000</v>
-      </c>
-      <c r="AC24">
-        <v>1000</v>
-      </c>
-      <c r="AD24">
-        <v>1000</v>
-      </c>
-      <c r="AE24">
-        <v>1000</v>
-      </c>
-      <c r="AF24">
-        <v>1000</v>
-      </c>
-      <c r="AG24">
-        <v>1000</v>
-      </c>
-      <c r="AH24">
-        <v>1000</v>
-      </c>
-      <c r="AI24">
-        <v>1000</v>
-      </c>
-      <c r="AJ24">
-        <v>1000</v>
-      </c>
-      <c r="AK24">
-        <v>1000</v>
-      </c>
-      <c r="AL24">
-        <v>1000</v>
-      </c>
-      <c r="AM24">
-        <v>1000</v>
-      </c>
-      <c r="AN24">
-        <v>1000</v>
-      </c>
-      <c r="AO24">
-        <v>1000</v>
-      </c>
-      <c r="AP24">
-        <v>1.03</v>
-      </c>
-      <c r="AQ24">
-        <v>1.03</v>
-      </c>
-      <c r="AR24">
-        <v>1.03</v>
-      </c>
-      <c r="AS24">
-        <v>1.03</v>
-      </c>
-      <c r="AT24">
-        <v>1.03</v>
-      </c>
-      <c r="AU24">
-        <v>1.03</v>
-      </c>
-      <c r="AV24">
-        <v>1.03</v>
-      </c>
       <c r="AW24">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AX24">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AY24">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AZ24">
-        <v>1.03</v>
+        <v>17.5</v>
       </c>
       <c r="BA24">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BB24">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="BC24">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="BD24">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="BE24">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BF24">
-        <v>1.01</v>
+        <v>2.96</v>
       </c>
       <c r="BG24">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BH24" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
     </row>
     <row r="25" spans="1:60">
       <c r="A25" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B25" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C25" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D25" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E25" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="F25">
-        <v>2.16</v>
+        <v>1.59</v>
       </c>
       <c r="G25">
-        <v>2.56</v>
+        <v>1.66</v>
       </c>
       <c r="H25">
-        <v>3.4</v>
+        <v>5.6</v>
       </c>
       <c r="I25">
-        <v>4</v>
+        <v>6.2</v>
       </c>
       <c r="J25">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="K25">
-        <v>3.75</v>
+        <v>5</v>
       </c>
       <c r="L25">
         <v>1.01</v>
       </c>
       <c r="M25">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N25">
-        <v>1.71</v>
+        <v>5.5</v>
       </c>
       <c r="O25">
-        <v>1.37</v>
+        <v>1.19</v>
       </c>
       <c r="P25">
-        <v>1.71</v>
+        <v>2.54</v>
       </c>
       <c r="Q25">
-        <v>2.12</v>
+        <v>1.58</v>
       </c>
       <c r="R25">
-        <v>1.21</v>
+        <v>1.61</v>
       </c>
       <c r="S25">
-        <v>3.4</v>
+        <v>2.42</v>
       </c>
       <c r="T25">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="U25">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="V25">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="W25">
-        <v>1.64</v>
+        <v>2.5</v>
       </c>
       <c r="X25">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="Y25">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Z25">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AA25">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AB25">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AC25">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD25">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AE25">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF25">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AG25">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AH25">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AI25">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ25">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AK25">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AL25">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AM25">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AN25">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="AO25">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AP25">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="AQ25">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR25">
-        <v>1.03</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS25">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AT25">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AU25">
-        <v>1.03</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV25">
-        <v>1.03</v>
+        <v>19.5</v>
       </c>
       <c r="AW25">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AX25">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AY25">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ25">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="BA25">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="BB25">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="BC25">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="BD25">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="BE25">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="BF25">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BG25">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BH25" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
     </row>
     <row r="26" spans="1:60">
       <c r="A26" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B26" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C26" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D26" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E26" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="F26">
-        <v>1.75</v>
+        <v>2.16</v>
       </c>
       <c r="G26">
-        <v>2.08</v>
+        <v>2.56</v>
       </c>
       <c r="H26">
+        <v>3.4</v>
+      </c>
+      <c r="I26">
+        <v>4</v>
+      </c>
+      <c r="J26">
         <v>3.2</v>
       </c>
-      <c r="I26">
-        <v>4.5</v>
-      </c>
-      <c r="J26">
-        <v>3.6</v>
-      </c>
       <c r="K26">
-        <v>5.6</v>
+        <v>3.75</v>
       </c>
       <c r="L26">
         <v>1.01</v>
       </c>
       <c r="M26">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="N26">
-        <v>3.35</v>
+        <v>1.71</v>
       </c>
       <c r="O26">
-        <v>1.2</v>
+        <v>1.37</v>
       </c>
       <c r="P26">
-        <v>2.08</v>
+        <v>1.71</v>
       </c>
       <c r="Q26">
-        <v>1.73</v>
+        <v>2.12</v>
       </c>
       <c r="R26">
-        <v>1.32</v>
+        <v>1.21</v>
       </c>
       <c r="S26">
-        <v>2.66</v>
+        <v>3.4</v>
       </c>
       <c r="T26">
         <v>1.01</v>
@@ -5562,55 +5532,55 @@
         <v>1.01</v>
       </c>
       <c r="V26">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="W26">
-        <v>1.92</v>
+        <v>1.64</v>
       </c>
       <c r="X26">
         <v>1000</v>
       </c>
       <c r="Y26">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="Z26">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AA26">
         <v>1000</v>
       </c>
       <c r="AB26">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AC26">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AD26">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AE26">
         <v>1000</v>
       </c>
       <c r="AF26">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AG26">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AH26">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AI26">
         <v>1000</v>
       </c>
       <c r="AJ26">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AK26">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AL26">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AM26">
         <v>1000</v>
@@ -5634,10 +5604,10 @@
         <v>1.03</v>
       </c>
       <c r="AT26">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="AU26">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="AV26">
         <v>1.03</v>
@@ -5646,10 +5616,10 @@
         <v>1.03</v>
       </c>
       <c r="AX26">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="AY26">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="AZ26">
         <v>1.03</v>
@@ -5676,7 +5646,7 @@
         <v>1.01</v>
       </c>
       <c r="BH26" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
     </row>
     <row r="27" spans="1:60">
@@ -5684,19 +5654,19 @@
         <v>60</v>
       </c>
       <c r="B27" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C27" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D27" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E27" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="F27">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="G27">
         <v>1.89</v>
@@ -5729,7 +5699,7 @@
         <v>1.71</v>
       </c>
       <c r="Q27">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="R27">
         <v>1.2</v>
@@ -5738,10 +5708,10 @@
         <v>3.4</v>
       </c>
       <c r="T27">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="U27">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="V27">
         <v>1.16</v>
@@ -5858,7 +5828,7 @@
         <v>2.34</v>
       </c>
       <c r="BH27" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
     </row>
     <row r="28" spans="1:60">
@@ -5866,25 +5836,25 @@
         <v>60</v>
       </c>
       <c r="B28" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C28" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D28" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E28" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="F28">
         <v>2.32</v>
       </c>
       <c r="G28">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="H28">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="I28">
         <v>4.4</v>
@@ -5905,7 +5875,7 @@
         <v>1.52</v>
       </c>
       <c r="O28">
-        <v>1.52</v>
+        <v>1.02</v>
       </c>
       <c r="P28">
         <v>1.52</v>
@@ -5920,16 +5890,16 @@
         <v>4.4</v>
       </c>
       <c r="T28">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="U28">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="V28">
         <v>1.29</v>
       </c>
       <c r="W28">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="X28">
         <v>11.5</v>
@@ -6040,42 +6010,42 @@
         <v>2.72</v>
       </c>
       <c r="BH28" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
     </row>
     <row r="29" spans="1:60">
       <c r="A29" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B29" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C29" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D29" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E29" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="F29">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="G29">
-        <v>1.66</v>
+        <v>2.08</v>
       </c>
       <c r="H29">
+        <v>3.2</v>
+      </c>
+      <c r="I29">
+        <v>4.5</v>
+      </c>
+      <c r="J29">
+        <v>3.6</v>
+      </c>
+      <c r="K29">
         <v>5.6</v>
-      </c>
-      <c r="I29">
-        <v>6.2</v>
-      </c>
-      <c r="J29">
-        <v>4.5</v>
-      </c>
-      <c r="K29">
-        <v>5</v>
       </c>
       <c r="L29">
         <v>1.01</v>
@@ -6084,327 +6054,327 @@
         <v>1.04</v>
       </c>
       <c r="N29">
-        <v>5.5</v>
+        <v>3.35</v>
       </c>
       <c r="O29">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P29">
-        <v>2.54</v>
+        <v>2.08</v>
       </c>
       <c r="Q29">
-        <v>1.58</v>
+        <v>1.73</v>
       </c>
       <c r="R29">
-        <v>1.61</v>
+        <v>1.32</v>
       </c>
       <c r="S29">
-        <v>2.42</v>
+        <v>2.66</v>
       </c>
       <c r="T29">
-        <v>1.58</v>
+        <v>1.01</v>
       </c>
       <c r="U29">
-        <v>2.1</v>
+        <v>1.01</v>
       </c>
       <c r="V29">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="W29">
-        <v>2.52</v>
+        <v>1.92</v>
       </c>
       <c r="X29">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="Y29">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Z29">
         <v>50</v>
       </c>
       <c r="AA29">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AB29">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="AC29">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="AD29">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AE29">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AF29">
-        <v>12</v>
+        <v>17.5</v>
       </c>
       <c r="AG29">
-        <v>10.5</v>
+        <v>15</v>
       </c>
       <c r="AH29">
-        <v>18.5</v>
+        <v>29</v>
       </c>
       <c r="AI29">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ29">
-        <v>16.5</v>
+        <v>30</v>
       </c>
       <c r="AK29">
-        <v>15.5</v>
+        <v>28</v>
       </c>
       <c r="AL29">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="AM29">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AN29">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="AO29">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AP29">
-        <v>8.6</v>
+        <v>1.03</v>
       </c>
       <c r="AQ29">
-        <v>8.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AR29">
-        <v>9.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AS29">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AT29">
-        <v>10.5</v>
+        <v>6.2</v>
       </c>
       <c r="AU29">
-        <v>9.800000000000001</v>
+        <v>6.2</v>
       </c>
       <c r="AV29">
-        <v>19.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW29">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AX29">
-        <v>10.5</v>
+        <v>7.4</v>
       </c>
       <c r="AY29">
-        <v>9.199999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="AZ29">
-        <v>16</v>
+        <v>1.03</v>
       </c>
       <c r="BA29">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="BB29">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="BC29">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD29">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="BE29">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="BF29">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BG29">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BH29" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
     </row>
     <row r="30" spans="1:60">
       <c r="A30" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="B30" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C30" t="s">
         <v>90</v>
       </c>
       <c r="D30" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E30" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="F30">
-        <v>1.39</v>
+        <v>2.04</v>
       </c>
       <c r="G30">
-        <v>1.43</v>
+        <v>2.74</v>
       </c>
       <c r="H30">
-        <v>7.2</v>
+        <v>2.52</v>
       </c>
       <c r="I30">
-        <v>9.4</v>
+        <v>3.85</v>
       </c>
       <c r="J30">
-        <v>5.8</v>
+        <v>3.25</v>
       </c>
       <c r="K30">
-        <v>6.6</v>
+        <v>950</v>
       </c>
       <c r="L30">
         <v>1.01</v>
       </c>
       <c r="M30">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="N30">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="O30">
-        <v>1.11</v>
+        <v>1.33</v>
       </c>
       <c r="P30">
-        <v>3.55</v>
+        <v>1.83</v>
       </c>
       <c r="Q30">
-        <v>1.33</v>
+        <v>1.97</v>
       </c>
       <c r="R30">
-        <v>2.04</v>
+        <v>1.18</v>
       </c>
       <c r="S30">
-        <v>1.83</v>
+        <v>1.97</v>
       </c>
       <c r="T30">
+        <v>1.01</v>
+      </c>
+      <c r="U30">
+        <v>1.01</v>
+      </c>
+      <c r="V30">
+        <v>1.35</v>
+      </c>
+      <c r="W30">
         <v>1.58</v>
       </c>
-      <c r="U30">
-        <v>2.5</v>
-      </c>
-      <c r="V30">
-        <v>1.12</v>
-      </c>
-      <c r="W30">
-        <v>3.25</v>
-      </c>
       <c r="X30">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="Y30">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="Z30">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AA30">
-        <v>230</v>
+        <v>1000</v>
       </c>
       <c r="AB30">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AC30">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AD30">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AE30">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AF30">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AG30">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AH30">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AI30">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AJ30">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AK30">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AL30">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AM30">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AN30">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="AO30">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AP30">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="AQ30">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="AR30">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="AS30">
-        <v>4.3</v>
+        <v>1.03</v>
       </c>
       <c r="AT30">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="AU30">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="AV30">
-        <v>3.95</v>
+        <v>1.03</v>
       </c>
       <c r="AW30">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="AX30">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AY30">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AZ30">
-        <v>17.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA30">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="BB30">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="BC30">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="BD30">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="BE30">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="BF30">
-        <v>2.96</v>
+        <v>1.01</v>
       </c>
       <c r="BG30">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BH30" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
     </row>
     <row r="31" spans="1:60">
@@ -6412,2729 +6382,2001 @@
         <v>76</v>
       </c>
       <c r="B31" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C31" t="s">
         <v>91</v>
       </c>
       <c r="D31" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E31" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="F31">
-        <v>2.56</v>
+        <v>1.48</v>
       </c>
       <c r="G31">
-        <v>3.35</v>
+        <v>1.57</v>
       </c>
       <c r="H31">
-        <v>2.6</v>
+        <v>6</v>
       </c>
       <c r="I31">
-        <v>3.6</v>
+        <v>7.4</v>
       </c>
       <c r="J31">
-        <v>2.36</v>
+        <v>4.8</v>
       </c>
       <c r="K31">
-        <v>4.5</v>
+        <v>5.8</v>
       </c>
       <c r="L31">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="M31">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N31">
-        <v>1.83</v>
+        <v>6</v>
       </c>
       <c r="O31">
-        <v>1.26</v>
+        <v>1.15</v>
       </c>
       <c r="P31">
-        <v>1.82</v>
+        <v>2.74</v>
       </c>
       <c r="Q31">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="R31">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="S31">
-        <v>2.78</v>
+        <v>2.14</v>
       </c>
       <c r="T31">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="U31">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="V31">
-        <v>1.38</v>
+        <v>1.15</v>
       </c>
       <c r="W31">
-        <v>1.42</v>
+        <v>2.74</v>
       </c>
       <c r="X31">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Y31">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Z31">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AA31">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AB31">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AC31">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AD31">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AE31">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AF31">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AG31">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AH31">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI31">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ31">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AK31">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AL31">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AM31">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AN31">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="AO31">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AP31">
-        <v>12.5</v>
+        <v>7</v>
       </c>
       <c r="AQ31">
-        <v>9.4</v>
+        <v>7</v>
       </c>
       <c r="AR31">
-        <v>14.5</v>
+        <v>7.8</v>
       </c>
       <c r="AS31">
-        <v>30</v>
+        <v>8.6</v>
       </c>
       <c r="AT31">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AU31">
-        <v>6.4</v>
+        <v>10.5</v>
       </c>
       <c r="AV31">
-        <v>9.4</v>
+        <v>21</v>
       </c>
       <c r="AW31">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="AX31">
-        <v>13.5</v>
+        <v>10</v>
       </c>
       <c r="AY31">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ31">
+        <v>16.5</v>
+      </c>
+      <c r="BA31">
+        <v>7.8</v>
+      </c>
+      <c r="BB31">
         <v>12</v>
       </c>
-      <c r="BA31">
-        <v>26</v>
-      </c>
-      <c r="BB31">
-        <v>26</v>
-      </c>
       <c r="BC31">
-        <v>19.5</v>
+        <v>12</v>
       </c>
       <c r="BD31">
-        <v>26</v>
+        <v>6.8</v>
       </c>
       <c r="BE31">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="BF31">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BG31">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BH31" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
     </row>
     <row r="32" spans="1:60">
       <c r="A32" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="B32" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C32" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D32" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E32" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="F32">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="G32">
-        <v>2.9</v>
+        <v>1.81</v>
       </c>
       <c r="H32">
+        <v>4.8</v>
+      </c>
+      <c r="I32">
+        <v>6.4</v>
+      </c>
+      <c r="J32">
+        <v>4.2</v>
+      </c>
+      <c r="K32">
+        <v>5.5</v>
+      </c>
+      <c r="L32">
+        <v>1.01</v>
+      </c>
+      <c r="M32">
+        <v>1.03</v>
+      </c>
+      <c r="N32">
+        <v>2.46</v>
+      </c>
+      <c r="O32">
+        <v>1.16</v>
+      </c>
+      <c r="P32">
+        <v>2.46</v>
+      </c>
+      <c r="Q32">
+        <v>1.54</v>
+      </c>
+      <c r="R32">
+        <v>1.5</v>
+      </c>
+      <c r="S32">
+        <v>2.12</v>
+      </c>
+      <c r="T32">
+        <v>1.46</v>
+      </c>
+      <c r="U32">
+        <v>1.96</v>
+      </c>
+      <c r="V32">
+        <v>1.18</v>
+      </c>
+      <c r="W32">
+        <v>2.24</v>
+      </c>
+      <c r="X32">
+        <v>36</v>
+      </c>
+      <c r="Y32">
+        <v>34</v>
+      </c>
+      <c r="Z32">
+        <v>65</v>
+      </c>
+      <c r="AA32">
+        <v>1000</v>
+      </c>
+      <c r="AB32">
+        <v>17</v>
+      </c>
+      <c r="AC32">
+        <v>15</v>
+      </c>
+      <c r="AD32">
+        <v>29</v>
+      </c>
+      <c r="AE32">
+        <v>85</v>
+      </c>
+      <c r="AF32">
+        <v>17.5</v>
+      </c>
+      <c r="AG32">
+        <v>14.5</v>
+      </c>
+      <c r="AH32">
+        <v>25</v>
+      </c>
+      <c r="AI32">
+        <v>75</v>
+      </c>
+      <c r="AJ32">
+        <v>24</v>
+      </c>
+      <c r="AK32">
+        <v>22</v>
+      </c>
+      <c r="AL32">
+        <v>38</v>
+      </c>
+      <c r="AM32">
+        <v>100</v>
+      </c>
+      <c r="AN32">
+        <v>1000</v>
+      </c>
+      <c r="AO32">
+        <v>1000</v>
+      </c>
+      <c r="AP32">
+        <v>2.08</v>
+      </c>
+      <c r="AQ32">
+        <v>2.06</v>
+      </c>
+      <c r="AR32">
+        <v>2.12</v>
+      </c>
+      <c r="AS32">
+        <v>2.2</v>
+      </c>
+      <c r="AT32">
+        <v>1.95</v>
+      </c>
+      <c r="AU32">
+        <v>1.92</v>
+      </c>
+      <c r="AV32">
+        <v>2.04</v>
+      </c>
+      <c r="AW32">
+        <v>2.14</v>
+      </c>
+      <c r="AX32">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY32">
+        <v>1.91</v>
+      </c>
+      <c r="AZ32">
+        <v>12.5</v>
+      </c>
+      <c r="BA32">
+        <v>2.14</v>
+      </c>
+      <c r="BB32">
         <v>2.02</v>
       </c>
-      <c r="I32">
-        <v>3.95</v>
-      </c>
-      <c r="J32">
-        <v>3.25</v>
-      </c>
-      <c r="K32">
-        <v>950</v>
-      </c>
-      <c r="L32">
-        <v>1.01</v>
-      </c>
-      <c r="M32">
-        <v>1.07</v>
-      </c>
-      <c r="N32">
-        <v>1.01</v>
-      </c>
-      <c r="O32">
-        <v>1.33</v>
-      </c>
-      <c r="P32">
-        <v>1.83</v>
-      </c>
-      <c r="Q32">
-        <v>1.97</v>
-      </c>
-      <c r="R32">
-        <v>1.18</v>
-      </c>
-      <c r="S32">
-        <v>1.97</v>
-      </c>
-      <c r="T32">
-        <v>1.01</v>
-      </c>
-      <c r="U32">
-        <v>1.01</v>
-      </c>
-      <c r="V32">
-        <v>1.33</v>
-      </c>
-      <c r="W32">
-        <v>1.52</v>
-      </c>
-      <c r="X32">
-        <v>1000</v>
-      </c>
-      <c r="Y32">
-        <v>1000</v>
-      </c>
-      <c r="Z32">
-        <v>1000</v>
-      </c>
-      <c r="AA32">
-        <v>1000</v>
-      </c>
-      <c r="AB32">
-        <v>1000</v>
-      </c>
-      <c r="AC32">
-        <v>1000</v>
-      </c>
-      <c r="AD32">
-        <v>1000</v>
-      </c>
-      <c r="AE32">
-        <v>1000</v>
-      </c>
-      <c r="AF32">
-        <v>1000</v>
-      </c>
-      <c r="AG32">
-        <v>1000</v>
-      </c>
-      <c r="AH32">
-        <v>1000</v>
-      </c>
-      <c r="AI32">
-        <v>1000</v>
-      </c>
-      <c r="AJ32">
-        <v>1000</v>
-      </c>
-      <c r="AK32">
-        <v>1000</v>
-      </c>
-      <c r="AL32">
-        <v>1000</v>
-      </c>
-      <c r="AM32">
-        <v>1000</v>
-      </c>
-      <c r="AN32">
-        <v>1000</v>
-      </c>
-      <c r="AO32">
-        <v>1000</v>
-      </c>
-      <c r="AP32">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AQ32">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AR32">
-        <v>15.5</v>
-      </c>
-      <c r="AS32">
-        <v>36</v>
-      </c>
-      <c r="AT32">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU32">
-        <v>6.2</v>
-      </c>
-      <c r="AV32">
-        <v>10</v>
-      </c>
-      <c r="AW32">
-        <v>24</v>
-      </c>
-      <c r="AX32">
-        <v>10.5</v>
-      </c>
-      <c r="AY32">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ32">
-        <v>14</v>
-      </c>
-      <c r="BA32">
-        <v>34</v>
-      </c>
-      <c r="BB32">
-        <v>24</v>
-      </c>
       <c r="BC32">
-        <v>18.5</v>
+        <v>11</v>
       </c>
       <c r="BD32">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="BE32">
-        <v>40</v>
+        <v>2.16</v>
       </c>
       <c r="BF32">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="BG32">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="BH32" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
     </row>
     <row r="33" spans="1:60">
       <c r="A33" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B33" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C33" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D33" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E33" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="F33">
-        <v>1.49</v>
+        <v>1.81</v>
       </c>
       <c r="G33">
-        <v>1.56</v>
+        <v>2.28</v>
       </c>
       <c r="H33">
-        <v>6</v>
+        <v>3.4</v>
       </c>
       <c r="I33">
-        <v>7.4</v>
+        <v>4.9</v>
       </c>
       <c r="J33">
-        <v>4.8</v>
+        <v>3.65</v>
       </c>
       <c r="K33">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="L33">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="M33">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="N33">
-        <v>6</v>
+        <v>1.91</v>
       </c>
       <c r="O33">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="P33">
-        <v>2.74</v>
+        <v>1.91</v>
       </c>
       <c r="Q33">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="R33">
-        <v>1.7</v>
+        <v>1.35</v>
       </c>
       <c r="S33">
-        <v>2.14</v>
+        <v>2.62</v>
       </c>
       <c r="T33">
-        <v>1.63</v>
+        <v>1.01</v>
       </c>
       <c r="U33">
-        <v>2.26</v>
+        <v>1.01</v>
       </c>
       <c r="V33">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="W33">
-        <v>2.78</v>
+        <v>1.78</v>
       </c>
       <c r="X33">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="Y33">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="Z33">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AA33">
+        <v>1000</v>
+      </c>
+      <c r="AB33">
+        <v>1000</v>
+      </c>
+      <c r="AC33">
+        <v>1000</v>
+      </c>
+      <c r="AD33">
+        <v>1000</v>
+      </c>
+      <c r="AE33">
+        <v>1000</v>
+      </c>
+      <c r="AF33">
+        <v>1000</v>
+      </c>
+      <c r="AG33">
+        <v>1000</v>
+      </c>
+      <c r="AH33">
+        <v>1000</v>
+      </c>
+      <c r="AI33">
+        <v>1000</v>
+      </c>
+      <c r="AJ33">
+        <v>1000</v>
+      </c>
+      <c r="AK33">
+        <v>1000</v>
+      </c>
+      <c r="AL33">
+        <v>1000</v>
+      </c>
+      <c r="AM33">
+        <v>1000</v>
+      </c>
+      <c r="AN33">
+        <v>1000</v>
+      </c>
+      <c r="AO33">
+        <v>1000</v>
+      </c>
+      <c r="AP33">
+        <v>1.03</v>
+      </c>
+      <c r="AQ33">
+        <v>1.03</v>
+      </c>
+      <c r="AR33">
+        <v>1.03</v>
+      </c>
+      <c r="AS33">
+        <v>1.03</v>
+      </c>
+      <c r="AT33">
+        <v>1.03</v>
+      </c>
+      <c r="AU33">
+        <v>1.03</v>
+      </c>
+      <c r="AV33">
+        <v>1.03</v>
+      </c>
+      <c r="AW33">
+        <v>1.03</v>
+      </c>
+      <c r="AX33">
+        <v>1.03</v>
+      </c>
+      <c r="AY33">
+        <v>1.03</v>
+      </c>
+      <c r="AZ33">
+        <v>1.03</v>
+      </c>
+      <c r="BA33">
+        <v>1.03</v>
+      </c>
+      <c r="BB33">
+        <v>1.03</v>
+      </c>
+      <c r="BC33">
+        <v>1.03</v>
+      </c>
+      <c r="BD33">
+        <v>1.03</v>
+      </c>
+      <c r="BE33">
+        <v>1.03</v>
+      </c>
+      <c r="BF33">
+        <v>1.01</v>
+      </c>
+      <c r="BG33">
+        <v>1.01</v>
+      </c>
+      <c r="BH33" t="s">
         <v>180</v>
-      </c>
-      <c r="AB33">
-        <v>14</v>
-      </c>
-      <c r="AC33">
-        <v>13.5</v>
-      </c>
-      <c r="AD33">
-        <v>27</v>
-      </c>
-      <c r="AE33">
-        <v>80</v>
-      </c>
-      <c r="AF33">
-        <v>12.5</v>
-      </c>
-      <c r="AG33">
-        <v>11.5</v>
-      </c>
-      <c r="AH33">
-        <v>21</v>
-      </c>
-      <c r="AI33">
-        <v>65</v>
-      </c>
-      <c r="AJ33">
-        <v>15.5</v>
-      </c>
-      <c r="AK33">
-        <v>15</v>
-      </c>
-      <c r="AL33">
-        <v>27</v>
-      </c>
-      <c r="AM33">
-        <v>80</v>
-      </c>
-      <c r="AN33">
-        <v>5.4</v>
-      </c>
-      <c r="AO33">
-        <v>65</v>
-      </c>
-      <c r="AP33">
-        <v>7</v>
-      </c>
-      <c r="AQ33">
-        <v>7</v>
-      </c>
-      <c r="AR33">
-        <v>7.8</v>
-      </c>
-      <c r="AS33">
-        <v>8.4</v>
-      </c>
-      <c r="AT33">
-        <v>11</v>
-      </c>
-      <c r="AU33">
-        <v>10.5</v>
-      </c>
-      <c r="AV33">
-        <v>21</v>
-      </c>
-      <c r="AW33">
-        <v>8</v>
-      </c>
-      <c r="AX33">
-        <v>10</v>
-      </c>
-      <c r="AY33">
-        <v>9</v>
-      </c>
-      <c r="AZ33">
-        <v>16.5</v>
-      </c>
-      <c r="BA33">
-        <v>7.8</v>
-      </c>
-      <c r="BB33">
-        <v>12.5</v>
-      </c>
-      <c r="BC33">
-        <v>12</v>
-      </c>
-      <c r="BD33">
-        <v>6.6</v>
-      </c>
-      <c r="BE33">
-        <v>8</v>
-      </c>
-      <c r="BF33">
-        <v>4.1</v>
-      </c>
-      <c r="BG33">
-        <v>44</v>
-      </c>
-      <c r="BH33" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="34" spans="1:60">
       <c r="A34" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B34" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C34" t="s">
         <v>93</v>
       </c>
       <c r="D34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E34" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="F34">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="G34">
-        <v>1.81</v>
+        <v>1.65</v>
       </c>
       <c r="H34">
-        <v>4.8</v>
+        <v>5.9</v>
       </c>
       <c r="I34">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="J34">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="K34">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="L34">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="M34">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="N34">
-        <v>2.46</v>
+        <v>4</v>
       </c>
       <c r="O34">
-        <v>1.16</v>
+        <v>1.32</v>
       </c>
       <c r="P34">
-        <v>2.46</v>
+        <v>2</v>
       </c>
       <c r="Q34">
-        <v>1.54</v>
+        <v>1.96</v>
       </c>
       <c r="R34">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="S34">
-        <v>2.12</v>
+        <v>3.5</v>
       </c>
       <c r="T34">
-        <v>1.01</v>
+        <v>1.99</v>
       </c>
       <c r="U34">
-        <v>1.01</v>
+        <v>1.95</v>
       </c>
       <c r="V34">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="W34">
-        <v>2.24</v>
+        <v>2.52</v>
       </c>
       <c r="X34">
-        <v>36</v>
+        <v>15.5</v>
       </c>
       <c r="Y34">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="Z34">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="AA34">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AB34">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="AC34">
-        <v>15</v>
+        <v>9.4</v>
       </c>
       <c r="AD34">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AE34">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AF34">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AG34">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AH34">
+        <v>23</v>
+      </c>
+      <c r="AI34">
+        <v>90</v>
+      </c>
+      <c r="AJ34">
+        <v>16</v>
+      </c>
+      <c r="AK34">
         <v>17.5</v>
-      </c>
-      <c r="AG34">
-        <v>14.5</v>
-      </c>
-      <c r="AH34">
-        <v>25</v>
-      </c>
-      <c r="AI34">
-        <v>75</v>
-      </c>
-      <c r="AJ34">
-        <v>24</v>
-      </c>
-      <c r="AK34">
-        <v>22</v>
       </c>
       <c r="AL34">
         <v>38</v>
       </c>
       <c r="AM34">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="AN34">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AO34">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AP34">
-        <v>2.08</v>
+        <v>14.5</v>
       </c>
       <c r="AQ34">
-        <v>2.06</v>
+        <v>17.5</v>
       </c>
       <c r="AR34">
-        <v>2.12</v>
+        <v>42</v>
       </c>
       <c r="AS34">
-        <v>2.2</v>
+        <v>44</v>
       </c>
       <c r="AT34">
-        <v>1.95</v>
+        <v>7.6</v>
       </c>
       <c r="AU34">
-        <v>1.92</v>
+        <v>9</v>
       </c>
       <c r="AV34">
-        <v>2.04</v>
+        <v>21</v>
       </c>
       <c r="AW34">
-        <v>2.14</v>
+        <v>34</v>
       </c>
       <c r="AX34">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY34">
         <v>9.199999999999999</v>
       </c>
-      <c r="AY34">
-        <v>1.91</v>
-      </c>
       <c r="AZ34">
-        <v>12.5</v>
+        <v>21</v>
       </c>
       <c r="BA34">
-        <v>2.14</v>
+        <v>36</v>
       </c>
       <c r="BB34">
-        <v>2.02</v>
+        <v>14.5</v>
       </c>
       <c r="BC34">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="BD34">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="BE34">
-        <v>2.16</v>
+        <v>42</v>
       </c>
       <c r="BF34">
-        <v>2.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG34">
-        <v>2.2</v>
+        <v>38</v>
       </c>
       <c r="BH34" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
     </row>
     <row r="35" spans="1:60">
       <c r="A35" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="B35" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C35" t="s">
         <v>94</v>
       </c>
       <c r="D35" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E35" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="F35">
-        <v>1.48</v>
+        <v>7</v>
       </c>
       <c r="G35">
-        <v>1.58</v>
+        <v>7.2</v>
       </c>
       <c r="H35">
+        <v>1.5</v>
+      </c>
+      <c r="I35">
+        <v>1.51</v>
+      </c>
+      <c r="J35">
+        <v>5.1</v>
+      </c>
+      <c r="K35">
+        <v>5.2</v>
+      </c>
+      <c r="L35">
+        <v>1.32</v>
+      </c>
+      <c r="M35">
+        <v>1.04</v>
+      </c>
+      <c r="N35">
+        <v>5.2</v>
+      </c>
+      <c r="O35">
+        <v>1.23</v>
+      </c>
+      <c r="P35">
+        <v>2.42</v>
+      </c>
+      <c r="Q35">
+        <v>1.67</v>
+      </c>
+      <c r="R35">
+        <v>1.55</v>
+      </c>
+      <c r="S35">
+        <v>2.72</v>
+      </c>
+      <c r="T35">
+        <v>1.84</v>
+      </c>
+      <c r="U35">
+        <v>2.14</v>
+      </c>
+      <c r="V35">
+        <v>2.96</v>
+      </c>
+      <c r="W35">
+        <v>1.16</v>
+      </c>
+      <c r="X35">
+        <v>24</v>
+      </c>
+      <c r="Y35">
+        <v>9.6</v>
+      </c>
+      <c r="Z35">
+        <v>9.6</v>
+      </c>
+      <c r="AA35">
+        <v>13.5</v>
+      </c>
+      <c r="AB35">
+        <v>27</v>
+      </c>
+      <c r="AC35">
+        <v>11</v>
+      </c>
+      <c r="AD35">
+        <v>9.6</v>
+      </c>
+      <c r="AE35">
+        <v>14</v>
+      </c>
+      <c r="AF35">
+        <v>60</v>
+      </c>
+      <c r="AG35">
+        <v>26</v>
+      </c>
+      <c r="AH35">
+        <v>21</v>
+      </c>
+      <c r="AI35">
+        <v>29</v>
+      </c>
+      <c r="AJ35">
+        <v>190</v>
+      </c>
+      <c r="AK35">
+        <v>90</v>
+      </c>
+      <c r="AL35">
+        <v>75</v>
+      </c>
+      <c r="AM35">
+        <v>95</v>
+      </c>
+      <c r="AN35">
+        <v>85</v>
+      </c>
+      <c r="AO35">
+        <v>6.4</v>
+      </c>
+      <c r="AP35">
+        <v>23</v>
+      </c>
+      <c r="AQ35">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR35">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AS35">
+        <v>13</v>
+      </c>
+      <c r="AT35">
+        <v>25</v>
+      </c>
+      <c r="AU35">
+        <v>10.5</v>
+      </c>
+      <c r="AV35">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW35">
+        <v>13.5</v>
+      </c>
+      <c r="AX35">
+        <v>50</v>
+      </c>
+      <c r="AY35">
+        <v>23</v>
+      </c>
+      <c r="AZ35">
+        <v>20</v>
+      </c>
+      <c r="BA35">
+        <v>27</v>
+      </c>
+      <c r="BB35">
+        <v>46</v>
+      </c>
+      <c r="BC35">
+        <v>80</v>
+      </c>
+      <c r="BD35">
+        <v>60</v>
+      </c>
+      <c r="BE35">
+        <v>85</v>
+      </c>
+      <c r="BF35">
+        <v>75</v>
+      </c>
+      <c r="BG35">
         <v>6</v>
       </c>
-      <c r="I35">
-        <v>7.2</v>
-      </c>
-      <c r="J35">
-        <v>4.8</v>
-      </c>
-      <c r="K35">
-        <v>5.6</v>
-      </c>
-      <c r="L35">
-        <v>1.01</v>
-      </c>
-      <c r="M35">
-        <v>1.03</v>
-      </c>
-      <c r="N35">
-        <v>2.8</v>
-      </c>
-      <c r="O35">
-        <v>1.15</v>
-      </c>
-      <c r="P35">
-        <v>2.8</v>
-      </c>
-      <c r="Q35">
-        <v>1.44</v>
-      </c>
-      <c r="R35">
-        <v>1.58</v>
-      </c>
-      <c r="S35">
-        <v>2.04</v>
-      </c>
-      <c r="T35">
-        <v>1.47</v>
-      </c>
-      <c r="U35">
-        <v>1.9</v>
-      </c>
-      <c r="V35">
-        <v>1.16</v>
-      </c>
-      <c r="W35">
-        <v>2.72</v>
-      </c>
-      <c r="X35">
-        <v>40</v>
-      </c>
-      <c r="Y35">
-        <v>44</v>
-      </c>
-      <c r="Z35">
-        <v>85</v>
-      </c>
-      <c r="AA35">
-        <v>1000</v>
-      </c>
-      <c r="AB35">
-        <v>17.5</v>
-      </c>
-      <c r="AC35">
-        <v>17</v>
-      </c>
-      <c r="AD35">
-        <v>34</v>
-      </c>
-      <c r="AE35">
-        <v>100</v>
-      </c>
-      <c r="AF35">
-        <v>16</v>
-      </c>
-      <c r="AG35">
-        <v>15</v>
-      </c>
-      <c r="AH35">
-        <v>28</v>
-      </c>
-      <c r="AI35">
-        <v>90</v>
-      </c>
-      <c r="AJ35">
-        <v>21</v>
-      </c>
-      <c r="AK35">
-        <v>20</v>
-      </c>
-      <c r="AL35">
-        <v>38</v>
-      </c>
-      <c r="AM35">
-        <v>100</v>
-      </c>
-      <c r="AN35">
-        <v>1000</v>
-      </c>
-      <c r="AO35">
-        <v>1000</v>
-      </c>
-      <c r="AP35">
-        <v>1.99</v>
-      </c>
-      <c r="AQ35">
-        <v>2</v>
-      </c>
-      <c r="AR35">
-        <v>2.04</v>
-      </c>
-      <c r="AS35">
-        <v>2.1</v>
-      </c>
-      <c r="AT35">
-        <v>1.87</v>
-      </c>
-      <c r="AU35">
-        <v>1.87</v>
-      </c>
-      <c r="AV35">
-        <v>1.98</v>
-      </c>
-      <c r="AW35">
-        <v>2.06</v>
-      </c>
-      <c r="AX35">
-        <v>1.85</v>
-      </c>
-      <c r="AY35">
-        <v>1.84</v>
-      </c>
-      <c r="AZ35">
-        <v>1.95</v>
-      </c>
-      <c r="BA35">
-        <v>2.04</v>
-      </c>
-      <c r="BB35">
-        <v>1.91</v>
-      </c>
-      <c r="BC35">
-        <v>10</v>
-      </c>
-      <c r="BD35">
-        <v>1.99</v>
-      </c>
-      <c r="BE35">
-        <v>2.06</v>
-      </c>
-      <c r="BF35">
-        <v>2.1</v>
-      </c>
-      <c r="BG35">
-        <v>2.1</v>
-      </c>
       <c r="BH35" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
     </row>
     <row r="36" spans="1:60">
       <c r="A36" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="B36" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C36" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D36" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E36" t="s">
+        <v>174</v>
+      </c>
+      <c r="F36">
+        <v>1.29</v>
+      </c>
+      <c r="G36">
+        <v>1.32</v>
+      </c>
+      <c r="H36">
+        <v>12</v>
+      </c>
+      <c r="I36">
+        <v>13</v>
+      </c>
+      <c r="J36">
+        <v>6.4</v>
+      </c>
+      <c r="K36">
+        <v>6.8</v>
+      </c>
+      <c r="L36">
+        <v>1.01</v>
+      </c>
+      <c r="M36">
+        <v>1.03</v>
+      </c>
+      <c r="N36">
+        <v>5.7</v>
+      </c>
+      <c r="O36">
+        <v>1.18</v>
+      </c>
+      <c r="P36">
+        <v>2.62</v>
+      </c>
+      <c r="Q36">
+        <v>1.53</v>
+      </c>
+      <c r="R36">
+        <v>1.65</v>
+      </c>
+      <c r="S36">
+        <v>2.3</v>
+      </c>
+      <c r="T36">
+        <v>1.82</v>
+      </c>
+      <c r="U36">
+        <v>1.79</v>
+      </c>
+      <c r="V36">
+        <v>1.08</v>
+      </c>
+      <c r="W36">
+        <v>4.1</v>
+      </c>
+      <c r="X36">
+        <v>29</v>
+      </c>
+      <c r="Y36">
+        <v>42</v>
+      </c>
+      <c r="Z36">
+        <v>130</v>
+      </c>
+      <c r="AA36">
+        <v>480</v>
+      </c>
+      <c r="AB36">
+        <v>11</v>
+      </c>
+      <c r="AC36">
+        <v>14.5</v>
+      </c>
+      <c r="AD36">
+        <v>42</v>
+      </c>
+      <c r="AE36">
+        <v>200</v>
+      </c>
+      <c r="AF36">
+        <v>9</v>
+      </c>
+      <c r="AG36">
+        <v>11</v>
+      </c>
+      <c r="AH36">
+        <v>29</v>
+      </c>
+      <c r="AI36">
+        <v>150</v>
+      </c>
+      <c r="AJ36">
+        <v>11</v>
+      </c>
+      <c r="AK36">
+        <v>14</v>
+      </c>
+      <c r="AL36">
+        <v>34</v>
+      </c>
+      <c r="AM36">
+        <v>160</v>
+      </c>
+      <c r="AN36">
+        <v>4.4</v>
+      </c>
+      <c r="AO36">
+        <v>230</v>
+      </c>
+      <c r="AP36">
+        <v>9.4</v>
+      </c>
+      <c r="AQ36">
+        <v>10.5</v>
+      </c>
+      <c r="AR36">
+        <v>12.5</v>
+      </c>
+      <c r="AS36">
+        <v>4.3</v>
+      </c>
+      <c r="AT36">
+        <v>9.4</v>
+      </c>
+      <c r="AU36">
+        <v>12.5</v>
+      </c>
+      <c r="AV36">
+        <v>10.5</v>
+      </c>
+      <c r="AW36">
+        <v>13</v>
+      </c>
+      <c r="AX36">
+        <v>7.8</v>
+      </c>
+      <c r="AY36">
+        <v>9.6</v>
+      </c>
+      <c r="AZ36">
+        <v>9.4</v>
+      </c>
+      <c r="BA36">
+        <v>12.5</v>
+      </c>
+      <c r="BB36">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BC36">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BD36">
+        <v>10</v>
+      </c>
+      <c r="BE36">
+        <v>13</v>
+      </c>
+      <c r="BF36">
+        <v>3.55</v>
+      </c>
+      <c r="BG36">
+        <v>13</v>
+      </c>
+      <c r="BH36" t="s">
         <v>180</v>
-      </c>
-      <c r="F36">
-        <v>1.81</v>
-      </c>
-      <c r="G36">
-        <v>2.28</v>
-      </c>
-      <c r="H36">
-        <v>3.4</v>
-      </c>
-      <c r="I36">
-        <v>4.9</v>
-      </c>
-      <c r="J36">
-        <v>3.65</v>
-      </c>
-      <c r="K36">
-        <v>6.6</v>
-      </c>
-      <c r="L36">
-        <v>1.31</v>
-      </c>
-      <c r="M36">
-        <v>1.05</v>
-      </c>
-      <c r="N36">
-        <v>1.91</v>
-      </c>
-      <c r="O36">
-        <v>1.24</v>
-      </c>
-      <c r="P36">
-        <v>1.91</v>
-      </c>
-      <c r="Q36">
-        <v>1.66</v>
-      </c>
-      <c r="R36">
-        <v>1.35</v>
-      </c>
-      <c r="S36">
-        <v>2.62</v>
-      </c>
-      <c r="T36">
-        <v>1.01</v>
-      </c>
-      <c r="U36">
-        <v>1.01</v>
-      </c>
-      <c r="V36">
-        <v>1.25</v>
-      </c>
-      <c r="W36">
-        <v>1.78</v>
-      </c>
-      <c r="X36">
-        <v>1000</v>
-      </c>
-      <c r="Y36">
-        <v>1000</v>
-      </c>
-      <c r="Z36">
-        <v>1000</v>
-      </c>
-      <c r="AA36">
-        <v>1000</v>
-      </c>
-      <c r="AB36">
-        <v>1000</v>
-      </c>
-      <c r="AC36">
-        <v>1000</v>
-      </c>
-      <c r="AD36">
-        <v>1000</v>
-      </c>
-      <c r="AE36">
-        <v>1000</v>
-      </c>
-      <c r="AF36">
-        <v>1000</v>
-      </c>
-      <c r="AG36">
-        <v>1000</v>
-      </c>
-      <c r="AH36">
-        <v>1000</v>
-      </c>
-      <c r="AI36">
-        <v>1000</v>
-      </c>
-      <c r="AJ36">
-        <v>1000</v>
-      </c>
-      <c r="AK36">
-        <v>1000</v>
-      </c>
-      <c r="AL36">
-        <v>1000</v>
-      </c>
-      <c r="AM36">
-        <v>1000</v>
-      </c>
-      <c r="AN36">
-        <v>1000</v>
-      </c>
-      <c r="AO36">
-        <v>1000</v>
-      </c>
-      <c r="AP36">
-        <v>14</v>
-      </c>
-      <c r="AQ36">
-        <v>11.5</v>
-      </c>
-      <c r="AR36">
-        <v>19</v>
-      </c>
-      <c r="AS36">
-        <v>40</v>
-      </c>
-      <c r="AT36">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU36">
-        <v>6.6</v>
-      </c>
-      <c r="AV36">
-        <v>11</v>
-      </c>
-      <c r="AW36">
-        <v>27</v>
-      </c>
-      <c r="AX36">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AY36">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ36">
-        <v>12.5</v>
-      </c>
-      <c r="BA36">
-        <v>29</v>
-      </c>
-      <c r="BB36">
-        <v>5</v>
-      </c>
-      <c r="BC36">
-        <v>15.5</v>
-      </c>
-      <c r="BD36">
-        <v>24</v>
-      </c>
-      <c r="BE36">
-        <v>40</v>
-      </c>
-      <c r="BF36">
-        <v>1.01</v>
-      </c>
-      <c r="BG36">
-        <v>1.01</v>
-      </c>
-      <c r="BH36" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="37" spans="1:60">
       <c r="A37" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="B37" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C37" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D37" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E37" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="F37">
+        <v>2.36</v>
+      </c>
+      <c r="G37">
+        <v>2.56</v>
+      </c>
+      <c r="H37">
+        <v>3.5</v>
+      </c>
+      <c r="I37">
+        <v>4.1</v>
+      </c>
+      <c r="J37">
+        <v>2.9</v>
+      </c>
+      <c r="K37">
+        <v>3.2</v>
+      </c>
+      <c r="L37">
+        <v>1.58</v>
+      </c>
+      <c r="M37">
+        <v>1.15</v>
+      </c>
+      <c r="N37">
+        <v>2.28</v>
+      </c>
+      <c r="O37">
+        <v>1.68</v>
+      </c>
+      <c r="P37">
+        <v>1.44</v>
+      </c>
+      <c r="Q37">
+        <v>3</v>
+      </c>
+      <c r="R37">
+        <v>1.14</v>
+      </c>
+      <c r="S37">
+        <v>6.8</v>
+      </c>
+      <c r="T37">
+        <v>2.32</v>
+      </c>
+      <c r="U37">
+        <v>1.62</v>
+      </c>
+      <c r="V37">
+        <v>1.33</v>
+      </c>
+      <c r="W37">
         <v>1.64</v>
       </c>
-      <c r="G37">
-        <v>1.66</v>
-      </c>
-      <c r="H37">
+      <c r="X37">
+        <v>8.4</v>
+      </c>
+      <c r="Y37">
+        <v>9.6</v>
+      </c>
+      <c r="Z37">
+        <v>26</v>
+      </c>
+      <c r="AA37">
+        <v>110</v>
+      </c>
+      <c r="AB37">
+        <v>7</v>
+      </c>
+      <c r="AC37">
+        <v>7.6</v>
+      </c>
+      <c r="AD37">
+        <v>21</v>
+      </c>
+      <c r="AE37">
+        <v>80</v>
+      </c>
+      <c r="AF37">
+        <v>14.5</v>
+      </c>
+      <c r="AG37">
+        <v>15</v>
+      </c>
+      <c r="AH37">
+        <v>30</v>
+      </c>
+      <c r="AI37">
+        <v>130</v>
+      </c>
+      <c r="AJ37">
+        <v>46</v>
+      </c>
+      <c r="AK37">
+        <v>44</v>
+      </c>
+      <c r="AL37">
+        <v>85</v>
+      </c>
+      <c r="AM37">
+        <v>320</v>
+      </c>
+      <c r="AN37">
+        <v>55</v>
+      </c>
+      <c r="AO37">
+        <v>140</v>
+      </c>
+      <c r="AP37">
+        <v>6.2</v>
+      </c>
+      <c r="AQ37">
+        <v>7.8</v>
+      </c>
+      <c r="AR37">
+        <v>21</v>
+      </c>
+      <c r="AS37">
+        <v>7</v>
+      </c>
+      <c r="AT37">
+        <v>5.8</v>
+      </c>
+      <c r="AU37">
+        <v>6.2</v>
+      </c>
+      <c r="AV37">
+        <v>15</v>
+      </c>
+      <c r="AW37">
+        <v>6.8</v>
+      </c>
+      <c r="AX37">
+        <v>11.5</v>
+      </c>
+      <c r="AY37">
+        <v>11</v>
+      </c>
+      <c r="AZ37">
         <v>5.9</v>
       </c>
-      <c r="I37">
-        <v>6</v>
-      </c>
-      <c r="J37">
-        <v>4.4</v>
-      </c>
-      <c r="K37">
-        <v>4.5</v>
-      </c>
-      <c r="L37">
-        <v>1.41</v>
-      </c>
-      <c r="M37">
-        <v>1.06</v>
-      </c>
-      <c r="N37">
-        <v>4</v>
-      </c>
-      <c r="O37">
-        <v>1.32</v>
-      </c>
-      <c r="P37">
-        <v>2</v>
-      </c>
-      <c r="Q37">
-        <v>1.96</v>
-      </c>
-      <c r="R37">
-        <v>1.37</v>
-      </c>
-      <c r="S37">
-        <v>3.5</v>
-      </c>
-      <c r="T37">
-        <v>1.98</v>
-      </c>
-      <c r="U37">
-        <v>1.95</v>
-      </c>
-      <c r="V37">
-        <v>1.2</v>
-      </c>
-      <c r="W37">
-        <v>2.52</v>
-      </c>
-      <c r="X37">
-        <v>15.5</v>
-      </c>
-      <c r="Y37">
-        <v>19</v>
-      </c>
-      <c r="Z37">
-        <v>48</v>
-      </c>
-      <c r="AA37">
-        <v>170</v>
-      </c>
-      <c r="AB37">
-        <v>8</v>
-      </c>
-      <c r="AC37">
-        <v>9.4</v>
-      </c>
-      <c r="AD37">
-        <v>23</v>
-      </c>
-      <c r="AE37">
-        <v>90</v>
-      </c>
-      <c r="AF37">
-        <v>9.4</v>
-      </c>
-      <c r="AG37">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AH37">
-        <v>23</v>
-      </c>
-      <c r="AI37">
-        <v>90</v>
-      </c>
-      <c r="AJ37">
-        <v>16</v>
-      </c>
-      <c r="AK37">
-        <v>17.5</v>
-      </c>
-      <c r="AL37">
-        <v>38</v>
-      </c>
-      <c r="AM37">
-        <v>140</v>
-      </c>
-      <c r="AN37">
-        <v>10</v>
-      </c>
-      <c r="AO37">
-        <v>110</v>
-      </c>
-      <c r="AP37">
-        <v>14.5</v>
-      </c>
-      <c r="AQ37">
-        <v>17.5</v>
-      </c>
-      <c r="AR37">
-        <v>42</v>
-      </c>
-      <c r="AS37">
-        <v>44</v>
-      </c>
-      <c r="AT37">
-        <v>7.6</v>
-      </c>
-      <c r="AU37">
-        <v>9</v>
-      </c>
-      <c r="AV37">
-        <v>21</v>
-      </c>
-      <c r="AW37">
-        <v>34</v>
-      </c>
-      <c r="AX37">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AY37">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ37">
-        <v>21</v>
-      </c>
       <c r="BA37">
+        <v>7</v>
+      </c>
+      <c r="BB37">
+        <v>32</v>
+      </c>
+      <c r="BC37">
+        <v>6.4</v>
+      </c>
+      <c r="BD37">
+        <v>6.8</v>
+      </c>
+      <c r="BE37">
+        <v>7.2</v>
+      </c>
+      <c r="BF37">
         <v>36</v>
       </c>
-      <c r="BB37">
-        <v>14.5</v>
-      </c>
-      <c r="BC37">
-        <v>16</v>
-      </c>
-      <c r="BD37">
-        <v>32</v>
-      </c>
-      <c r="BE37">
-        <v>42</v>
-      </c>
-      <c r="BF37">
-        <v>9.199999999999999</v>
-      </c>
       <c r="BG37">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="BH37" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
     </row>
     <row r="38" spans="1:60">
       <c r="A38" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="B38" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C38" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D38" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E38" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="F38">
-        <v>6.8</v>
+        <v>1.34</v>
       </c>
       <c r="G38">
-        <v>7.2</v>
+        <v>1.62</v>
       </c>
       <c r="H38">
-        <v>1.5</v>
+        <v>6.4</v>
       </c>
       <c r="I38">
-        <v>1.51</v>
+        <v>190</v>
       </c>
       <c r="J38">
-        <v>5.1</v>
+        <v>3.9</v>
       </c>
       <c r="K38">
-        <v>5.2</v>
+        <v>10</v>
       </c>
       <c r="L38">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="M38">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="N38">
-        <v>5.1</v>
+        <v>1.91</v>
       </c>
       <c r="O38">
         <v>1.23</v>
       </c>
       <c r="P38">
-        <v>2.42</v>
+        <v>1.91</v>
       </c>
       <c r="Q38">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="R38">
-        <v>1.55</v>
+        <v>1.33</v>
       </c>
       <c r="S38">
-        <v>2.74</v>
+        <v>2.6</v>
       </c>
       <c r="T38">
-        <v>1.84</v>
+        <v>1.01</v>
       </c>
       <c r="U38">
-        <v>2.14</v>
+        <v>1.01</v>
       </c>
       <c r="V38">
-        <v>2.96</v>
+        <v>1.01</v>
       </c>
       <c r="W38">
-        <v>1.16</v>
+        <v>2.6</v>
       </c>
       <c r="X38">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="Y38">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="Z38">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AA38">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AB38">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AC38">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AD38">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AE38">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AF38">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AG38">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AH38">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI38">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AJ38">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AK38">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AL38">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AM38">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AN38">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AO38">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="AP38">
-        <v>23</v>
+        <v>1.03</v>
       </c>
       <c r="AQ38">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AR38">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AS38">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="AT38">
-        <v>25</v>
+        <v>1.03</v>
       </c>
       <c r="AU38">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AV38">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AW38">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="AX38">
-        <v>50</v>
+        <v>1.03</v>
       </c>
       <c r="AY38">
-        <v>23</v>
+        <v>1.03</v>
       </c>
       <c r="AZ38">
-        <v>19.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA38">
-        <v>27</v>
+        <v>1.03</v>
       </c>
       <c r="BB38">
-        <v>50</v>
+        <v>1.03</v>
       </c>
       <c r="BC38">
-        <v>65</v>
+        <v>1.03</v>
       </c>
       <c r="BD38">
-        <v>65</v>
+        <v>1.03</v>
       </c>
       <c r="BE38">
-        <v>65</v>
+        <v>1.03</v>
       </c>
       <c r="BF38">
-        <v>75</v>
+        <v>1.01</v>
       </c>
       <c r="BG38">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BH38" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
     </row>
     <row r="39" spans="1:60">
       <c r="A39" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B39" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C39" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D39" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E39" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="F39">
-        <v>2.5</v>
+        <v>1.83</v>
       </c>
       <c r="G39">
-        <v>2.54</v>
+        <v>2.64</v>
       </c>
       <c r="H39">
-        <v>3</v>
+        <v>2.84</v>
       </c>
       <c r="I39">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="J39">
-        <v>3.6</v>
+        <v>3.05</v>
       </c>
       <c r="K39">
-        <v>3.65</v>
+        <v>11.5</v>
       </c>
       <c r="L39">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="M39">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="N39">
-        <v>3.85</v>
+        <v>1.96</v>
       </c>
       <c r="O39">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="P39">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="Q39">
-        <v>2.02</v>
+        <v>1.69</v>
       </c>
       <c r="R39">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="S39">
-        <v>3.6</v>
+        <v>1.69</v>
       </c>
       <c r="T39">
-        <v>1.8</v>
+        <v>1.01</v>
       </c>
       <c r="U39">
-        <v>2.18</v>
+        <v>1.01</v>
       </c>
       <c r="V39">
-        <v>1.47</v>
+        <v>1.28</v>
       </c>
       <c r="W39">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="X39">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Y39">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Z39">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AA39">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AB39">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AC39">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AD39">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AE39">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AF39">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AG39">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AH39">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AI39">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AJ39">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AK39">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AL39">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AM39">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AN39">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AO39">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AP39">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="AQ39">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR39">
-        <v>19</v>
+        <v>1.03</v>
       </c>
       <c r="AS39">
-        <v>44</v>
+        <v>1.03</v>
       </c>
       <c r="AT39">
-        <v>9.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AU39">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="AV39">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AW39">
-        <v>30</v>
+        <v>1.03</v>
       </c>
       <c r="AX39">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY39">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AZ39">
-        <v>16</v>
+        <v>1.03</v>
       </c>
       <c r="BA39">
-        <v>40</v>
+        <v>1.03</v>
       </c>
       <c r="BB39">
-        <v>32</v>
+        <v>1.03</v>
       </c>
       <c r="BC39">
-        <v>25</v>
+        <v>1.03</v>
       </c>
       <c r="BD39">
-        <v>34</v>
+        <v>1.03</v>
       </c>
       <c r="BE39">
-        <v>38</v>
+        <v>1.03</v>
       </c>
       <c r="BF39">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BG39">
-        <v>28</v>
+        <v>1.01</v>
       </c>
       <c r="BH39" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
     </row>
     <row r="40" spans="1:60">
       <c r="A40" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B40" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C40" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D40" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E40" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="F40">
-        <v>1.29</v>
+        <v>1.75</v>
       </c>
       <c r="G40">
-        <v>1.32</v>
+        <v>1.91</v>
       </c>
       <c r="H40">
+        <v>5.2</v>
+      </c>
+      <c r="I40">
+        <v>6.2</v>
+      </c>
+      <c r="J40">
+        <v>3.4</v>
+      </c>
+      <c r="K40">
+        <v>4.4</v>
+      </c>
+      <c r="L40">
+        <v>1.01</v>
+      </c>
+      <c r="M40">
+        <v>1.1</v>
+      </c>
+      <c r="N40">
+        <v>2.98</v>
+      </c>
+      <c r="O40">
+        <v>1.43</v>
+      </c>
+      <c r="P40">
+        <v>1.78</v>
+      </c>
+      <c r="Q40">
+        <v>2.24</v>
+      </c>
+      <c r="R40">
+        <v>1.25</v>
+      </c>
+      <c r="S40">
+        <v>4.3</v>
+      </c>
+      <c r="T40">
+        <v>1.01</v>
+      </c>
+      <c r="U40">
+        <v>1.01</v>
+      </c>
+      <c r="V40">
+        <v>1.2</v>
+      </c>
+      <c r="W40">
+        <v>2.1</v>
+      </c>
+      <c r="X40">
+        <v>11</v>
+      </c>
+      <c r="Y40">
+        <v>15.5</v>
+      </c>
+      <c r="Z40">
+        <v>44</v>
+      </c>
+      <c r="AA40">
+        <v>200</v>
+      </c>
+      <c r="AB40">
+        <v>7.2</v>
+      </c>
+      <c r="AC40">
+        <v>10</v>
+      </c>
+      <c r="AD40">
+        <v>23</v>
+      </c>
+      <c r="AE40">
+        <v>120</v>
+      </c>
+      <c r="AF40">
+        <v>10.5</v>
+      </c>
+      <c r="AG40">
+        <v>12.5</v>
+      </c>
+      <c r="AH40">
+        <v>24</v>
+      </c>
+      <c r="AI40">
+        <v>130</v>
+      </c>
+      <c r="AJ40">
+        <v>21</v>
+      </c>
+      <c r="AK40">
+        <v>23</v>
+      </c>
+      <c r="AL40">
+        <v>60</v>
+      </c>
+      <c r="AM40">
+        <v>210</v>
+      </c>
+      <c r="AN40">
+        <v>17</v>
+      </c>
+      <c r="AO40">
+        <v>180</v>
+      </c>
+      <c r="AP40">
+        <v>4.6</v>
+      </c>
+      <c r="AQ40">
+        <v>5.2</v>
+      </c>
+      <c r="AR40">
+        <v>2.76</v>
+      </c>
+      <c r="AS40">
+        <v>2.72</v>
+      </c>
+      <c r="AT40">
+        <v>3.75</v>
+      </c>
+      <c r="AU40">
+        <v>4.4</v>
+      </c>
+      <c r="AV40">
+        <v>5.9</v>
+      </c>
+      <c r="AW40">
+        <v>3.9</v>
+      </c>
+      <c r="AX40">
+        <v>4.5</v>
+      </c>
+      <c r="AY40">
+        <v>4.8</v>
+      </c>
+      <c r="AZ40">
+        <v>4.3</v>
+      </c>
+      <c r="BA40">
+        <v>3.9</v>
+      </c>
+      <c r="BB40">
+        <v>5.8</v>
+      </c>
+      <c r="BC40">
+        <v>5.9</v>
+      </c>
+      <c r="BD40">
+        <v>3.75</v>
+      </c>
+      <c r="BE40">
+        <v>2.44</v>
+      </c>
+      <c r="BF40">
         <v>12</v>
       </c>
-      <c r="I40">
-        <v>13</v>
-      </c>
-      <c r="J40">
-        <v>6.4</v>
-      </c>
-      <c r="K40">
-        <v>6.8</v>
-      </c>
-      <c r="L40">
-        <v>1.01</v>
-      </c>
-      <c r="M40">
-        <v>1.03</v>
-      </c>
-      <c r="N40">
-        <v>5.7</v>
-      </c>
-      <c r="O40">
-        <v>1.18</v>
-      </c>
-      <c r="P40">
-        <v>2.62</v>
-      </c>
-      <c r="Q40">
-        <v>1.51</v>
-      </c>
-      <c r="R40">
-        <v>1.65</v>
-      </c>
-      <c r="S40">
-        <v>2.3</v>
-      </c>
-      <c r="T40">
-        <v>1.96</v>
-      </c>
-      <c r="U40">
-        <v>1.91</v>
-      </c>
-      <c r="V40">
-        <v>1.08</v>
-      </c>
-      <c r="W40">
-        <v>4.1</v>
-      </c>
-      <c r="X40">
-        <v>29</v>
-      </c>
-      <c r="Y40">
-        <v>42</v>
-      </c>
-      <c r="Z40">
-        <v>130</v>
-      </c>
-      <c r="AA40">
-        <v>480</v>
-      </c>
-      <c r="AB40">
-        <v>11</v>
-      </c>
-      <c r="AC40">
-        <v>14.5</v>
-      </c>
-      <c r="AD40">
-        <v>42</v>
-      </c>
-      <c r="AE40">
-        <v>200</v>
-      </c>
-      <c r="AF40">
-        <v>9</v>
-      </c>
-      <c r="AG40">
-        <v>11</v>
-      </c>
-      <c r="AH40">
-        <v>29</v>
-      </c>
-      <c r="AI40">
-        <v>150</v>
-      </c>
-      <c r="AJ40">
-        <v>11</v>
-      </c>
-      <c r="AK40">
-        <v>14</v>
-      </c>
-      <c r="AL40">
-        <v>34</v>
-      </c>
-      <c r="AM40">
-        <v>160</v>
-      </c>
-      <c r="AN40">
-        <v>4.4</v>
-      </c>
-      <c r="AO40">
-        <v>230</v>
-      </c>
-      <c r="AP40">
-        <v>9.4</v>
-      </c>
-      <c r="AQ40">
-        <v>10.5</v>
-      </c>
-      <c r="AR40">
-        <v>12.5</v>
-      </c>
-      <c r="AS40">
-        <v>4.3</v>
-      </c>
-      <c r="AT40">
-        <v>9.4</v>
-      </c>
-      <c r="AU40">
-        <v>12.5</v>
-      </c>
-      <c r="AV40">
-        <v>10.5</v>
-      </c>
-      <c r="AW40">
-        <v>13</v>
-      </c>
-      <c r="AX40">
-        <v>7.8</v>
-      </c>
-      <c r="AY40">
-        <v>9.6</v>
-      </c>
-      <c r="AZ40">
-        <v>9.4</v>
-      </c>
-      <c r="BA40">
-        <v>12.5</v>
-      </c>
-      <c r="BB40">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BC40">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BD40">
-        <v>10</v>
-      </c>
-      <c r="BE40">
-        <v>13</v>
-      </c>
-      <c r="BF40">
-        <v>3.55</v>
-      </c>
       <c r="BG40">
-        <v>13</v>
+        <v>2.72</v>
       </c>
       <c r="BH40" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
     </row>
     <row r="41" spans="1:60">
       <c r="A41" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B41" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C41" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D41" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E41" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="F41">
-        <v>2.36</v>
+        <v>1.61</v>
       </c>
       <c r="G41">
-        <v>2.56</v>
+        <v>1.74</v>
       </c>
       <c r="H41">
-        <v>3.5</v>
+        <v>6.4</v>
       </c>
       <c r="I41">
-        <v>4.1</v>
+        <v>7.8</v>
       </c>
       <c r="J41">
-        <v>2.9</v>
+        <v>3.55</v>
       </c>
       <c r="K41">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="L41">
-        <v>1.58</v>
+        <v>1.43</v>
       </c>
       <c r="M41">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="N41">
-        <v>2.28</v>
+        <v>2.92</v>
       </c>
       <c r="O41">
-        <v>1.68</v>
+        <v>1.44</v>
       </c>
       <c r="P41">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="Q41">
-        <v>3</v>
+        <v>2.18</v>
       </c>
       <c r="R41">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="S41">
-        <v>6.8</v>
+        <v>4.4</v>
       </c>
       <c r="T41">
         <v>2.2</v>
       </c>
       <c r="U41">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="V41">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="W41">
-        <v>1.64</v>
+        <v>2.34</v>
       </c>
       <c r="X41">
-        <v>8.4</v>
+        <v>12.5</v>
       </c>
       <c r="Y41">
-        <v>9.6</v>
+        <v>21</v>
       </c>
       <c r="Z41">
-        <v>26</v>
+        <v>70</v>
       </c>
       <c r="AA41">
-        <v>110</v>
+        <v>300</v>
       </c>
       <c r="AB41">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AC41">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="AD41">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="AE41">
-        <v>80</v>
+        <v>160</v>
       </c>
       <c r="AF41">
+        <v>10</v>
+      </c>
+      <c r="AG41">
+        <v>12</v>
+      </c>
+      <c r="AH41">
+        <v>29</v>
+      </c>
+      <c r="AI41">
+        <v>160</v>
+      </c>
+      <c r="AJ41">
+        <v>19.5</v>
+      </c>
+      <c r="AK41">
+        <v>23</v>
+      </c>
+      <c r="AL41">
+        <v>65</v>
+      </c>
+      <c r="AM41">
+        <v>250</v>
+      </c>
+      <c r="AN41">
+        <v>17</v>
+      </c>
+      <c r="AO41">
+        <v>280</v>
+      </c>
+      <c r="AP41">
+        <v>3.85</v>
+      </c>
+      <c r="AQ41">
         <v>14.5</v>
       </c>
-      <c r="AG41">
-        <v>15</v>
-      </c>
-      <c r="AH41">
-        <v>30</v>
-      </c>
-      <c r="AI41">
-        <v>130</v>
-      </c>
-      <c r="AJ41">
-        <v>46</v>
-      </c>
-      <c r="AK41">
-        <v>44</v>
-      </c>
-      <c r="AL41">
-        <v>85</v>
-      </c>
-      <c r="AM41">
-        <v>320</v>
-      </c>
-      <c r="AN41">
-        <v>55</v>
-      </c>
-      <c r="AO41">
-        <v>140</v>
-      </c>
-      <c r="AP41">
-        <v>6.2</v>
-      </c>
-      <c r="AQ41">
-        <v>7.8</v>
-      </c>
       <c r="AR41">
-        <v>21</v>
+        <v>5.1</v>
       </c>
       <c r="AS41">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="AT41">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="AU41">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV41">
-        <v>15</v>
+        <v>4.7</v>
       </c>
       <c r="AW41">
-        <v>6.8</v>
+        <v>5.4</v>
       </c>
       <c r="AX41">
-        <v>11.5</v>
+        <v>7.4</v>
       </c>
       <c r="AY41">
+        <v>3.8</v>
+      </c>
+      <c r="AZ41">
+        <v>4.7</v>
+      </c>
+      <c r="BA41">
+        <v>5.4</v>
+      </c>
+      <c r="BB41">
+        <v>14</v>
+      </c>
+      <c r="BC41">
+        <v>4.5</v>
+      </c>
+      <c r="BD41">
+        <v>5.1</v>
+      </c>
+      <c r="BE41">
+        <v>5.4</v>
+      </c>
+      <c r="BF41">
         <v>11</v>
       </c>
-      <c r="AZ41">
-        <v>5.9</v>
-      </c>
-      <c r="BA41">
-        <v>7</v>
-      </c>
-      <c r="BB41">
-        <v>32</v>
-      </c>
-      <c r="BC41">
-        <v>6.4</v>
-      </c>
-      <c r="BD41">
-        <v>6.8</v>
-      </c>
-      <c r="BE41">
-        <v>7.2</v>
-      </c>
-      <c r="BF41">
-        <v>36</v>
-      </c>
       <c r="BG41">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="BH41" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="42" spans="1:60">
-      <c r="A42" t="s">
-        <v>81</v>
-      </c>
-      <c r="B42" t="s">
-        <v>84</v>
-      </c>
-      <c r="C42" t="s">
-        <v>99</v>
-      </c>
-      <c r="D42" t="s">
-        <v>142</v>
-      </c>
-      <c r="E42" t="s">
-        <v>186</v>
-      </c>
-      <c r="F42">
-        <v>1.34</v>
-      </c>
-      <c r="G42">
-        <v>1.62</v>
-      </c>
-      <c r="H42">
-        <v>2.68</v>
-      </c>
-      <c r="I42">
-        <v>100</v>
-      </c>
-      <c r="J42">
-        <v>2.68</v>
-      </c>
-      <c r="K42">
-        <v>85</v>
-      </c>
-      <c r="L42">
-        <v>1.01</v>
-      </c>
-      <c r="M42">
-        <v>1.01</v>
-      </c>
-      <c r="N42">
-        <v>1.91</v>
-      </c>
-      <c r="O42">
-        <v>1.23</v>
-      </c>
-      <c r="P42">
-        <v>1.91</v>
-      </c>
-      <c r="Q42">
-        <v>1.63</v>
-      </c>
-      <c r="R42">
-        <v>1.33</v>
-      </c>
-      <c r="S42">
-        <v>2.6</v>
-      </c>
-      <c r="T42">
-        <v>1.01</v>
-      </c>
-      <c r="U42">
-        <v>1.01</v>
-      </c>
-      <c r="V42">
-        <v>1.01</v>
-      </c>
-      <c r="W42">
-        <v>2.6</v>
-      </c>
-      <c r="X42">
-        <v>1000</v>
-      </c>
-      <c r="Y42">
-        <v>1000</v>
-      </c>
-      <c r="Z42">
-        <v>1000</v>
-      </c>
-      <c r="AA42">
-        <v>1000</v>
-      </c>
-      <c r="AB42">
-        <v>1000</v>
-      </c>
-      <c r="AC42">
-        <v>1000</v>
-      </c>
-      <c r="AD42">
-        <v>1000</v>
-      </c>
-      <c r="AE42">
-        <v>1000</v>
-      </c>
-      <c r="AF42">
-        <v>1000</v>
-      </c>
-      <c r="AG42">
-        <v>1000</v>
-      </c>
-      <c r="AH42">
-        <v>1000</v>
-      </c>
-      <c r="AI42">
-        <v>1000</v>
-      </c>
-      <c r="AJ42">
-        <v>1000</v>
-      </c>
-      <c r="AK42">
-        <v>1000</v>
-      </c>
-      <c r="AL42">
-        <v>1000</v>
-      </c>
-      <c r="AM42">
-        <v>1000</v>
-      </c>
-      <c r="AN42">
-        <v>1000</v>
-      </c>
-      <c r="AO42">
-        <v>1000</v>
-      </c>
-      <c r="AP42">
-        <v>1.01</v>
-      </c>
-      <c r="AQ42">
-        <v>1.01</v>
-      </c>
-      <c r="AR42">
-        <v>1.01</v>
-      </c>
-      <c r="AS42">
-        <v>1.01</v>
-      </c>
-      <c r="AT42">
-        <v>1.01</v>
-      </c>
-      <c r="AU42">
-        <v>1.01</v>
-      </c>
-      <c r="AV42">
-        <v>1.01</v>
-      </c>
-      <c r="AW42">
-        <v>1.01</v>
-      </c>
-      <c r="AX42">
-        <v>1.01</v>
-      </c>
-      <c r="AY42">
-        <v>1.01</v>
-      </c>
-      <c r="AZ42">
-        <v>1.01</v>
-      </c>
-      <c r="BA42">
-        <v>1.01</v>
-      </c>
-      <c r="BB42">
-        <v>1.01</v>
-      </c>
-      <c r="BC42">
-        <v>1.01</v>
-      </c>
-      <c r="BD42">
-        <v>1.01</v>
-      </c>
-      <c r="BE42">
-        <v>1.01</v>
-      </c>
-      <c r="BF42">
-        <v>1.01</v>
-      </c>
-      <c r="BG42">
-        <v>1.01</v>
-      </c>
-      <c r="BH42" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="43" spans="1:60">
-      <c r="A43" t="s">
-        <v>82</v>
-      </c>
-      <c r="B43" t="s">
-        <v>84</v>
-      </c>
-      <c r="C43" t="s">
-        <v>100</v>
-      </c>
-      <c r="D43" t="s">
-        <v>143</v>
-      </c>
-      <c r="E43" t="s">
-        <v>187</v>
-      </c>
-      <c r="F43">
-        <v>0</v>
-      </c>
-      <c r="G43">
-        <v>0</v>
-      </c>
-      <c r="H43">
-        <v>0</v>
-      </c>
-      <c r="I43">
-        <v>0</v>
-      </c>
-      <c r="J43">
-        <v>0</v>
-      </c>
-      <c r="K43">
-        <v>0</v>
-      </c>
-      <c r="L43">
-        <v>0</v>
-      </c>
-      <c r="M43">
-        <v>0</v>
-      </c>
-      <c r="N43">
-        <v>0</v>
-      </c>
-      <c r="O43">
-        <v>0</v>
-      </c>
-      <c r="P43">
-        <v>1.78</v>
-      </c>
-      <c r="Q43">
-        <v>1.01</v>
-      </c>
-      <c r="R43">
-        <v>0</v>
-      </c>
-      <c r="S43">
-        <v>0</v>
-      </c>
-      <c r="T43">
-        <v>0</v>
-      </c>
-      <c r="U43">
-        <v>0</v>
-      </c>
-      <c r="V43">
-        <v>0</v>
-      </c>
-      <c r="W43">
-        <v>0</v>
-      </c>
-      <c r="X43">
-        <v>0</v>
-      </c>
-      <c r="Y43">
-        <v>0</v>
-      </c>
-      <c r="Z43">
-        <v>0</v>
-      </c>
-      <c r="AA43">
-        <v>0</v>
-      </c>
-      <c r="AB43">
-        <v>0</v>
-      </c>
-      <c r="AC43">
-        <v>0</v>
-      </c>
-      <c r="AD43">
-        <v>0</v>
-      </c>
-      <c r="AE43">
-        <v>0</v>
-      </c>
-      <c r="AF43">
-        <v>0</v>
-      </c>
-      <c r="AG43">
-        <v>0</v>
-      </c>
-      <c r="AH43">
-        <v>0</v>
-      </c>
-      <c r="AI43">
-        <v>0</v>
-      </c>
-      <c r="AJ43">
-        <v>0</v>
-      </c>
-      <c r="AK43">
-        <v>0</v>
-      </c>
-      <c r="AL43">
-        <v>0</v>
-      </c>
-      <c r="AM43">
-        <v>0</v>
-      </c>
-      <c r="AN43">
-        <v>0</v>
-      </c>
-      <c r="AO43">
-        <v>0</v>
-      </c>
-      <c r="AP43">
-        <v>0</v>
-      </c>
-      <c r="AQ43">
-        <v>0</v>
-      </c>
-      <c r="AR43">
-        <v>0</v>
-      </c>
-      <c r="AS43">
-        <v>0</v>
-      </c>
-      <c r="AT43">
-        <v>0</v>
-      </c>
-      <c r="AU43">
-        <v>0</v>
-      </c>
-      <c r="AV43">
-        <v>0</v>
-      </c>
-      <c r="AW43">
-        <v>0</v>
-      </c>
-      <c r="AX43">
-        <v>0</v>
-      </c>
-      <c r="AY43">
-        <v>0</v>
-      </c>
-      <c r="AZ43">
-        <v>0</v>
-      </c>
-      <c r="BA43">
-        <v>0</v>
-      </c>
-      <c r="BB43">
-        <v>0</v>
-      </c>
-      <c r="BC43">
-        <v>0</v>
-      </c>
-      <c r="BD43">
-        <v>0</v>
-      </c>
-      <c r="BE43">
-        <v>0</v>
-      </c>
-      <c r="BF43">
-        <v>0</v>
-      </c>
-      <c r="BG43">
-        <v>0</v>
-      </c>
-      <c r="BH43" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="44" spans="1:60">
-      <c r="A44" t="s">
-        <v>83</v>
-      </c>
-      <c r="B44" t="s">
-        <v>84</v>
-      </c>
-      <c r="C44" t="s">
-        <v>100</v>
-      </c>
-      <c r="D44" t="s">
-        <v>144</v>
-      </c>
-      <c r="E44" t="s">
-        <v>188</v>
-      </c>
-      <c r="F44">
-        <v>1.55</v>
-      </c>
-      <c r="G44">
-        <v>2.64</v>
-      </c>
-      <c r="H44">
-        <v>2.84</v>
-      </c>
-      <c r="I44">
-        <v>4.5</v>
-      </c>
-      <c r="J44">
-        <v>3.05</v>
-      </c>
-      <c r="K44">
-        <v>150</v>
-      </c>
-      <c r="L44">
-        <v>0</v>
-      </c>
-      <c r="M44">
-        <v>0</v>
-      </c>
-      <c r="N44">
-        <v>0</v>
-      </c>
-      <c r="O44">
-        <v>0</v>
-      </c>
-      <c r="P44">
-        <v>1.96</v>
-      </c>
-      <c r="Q44">
-        <v>1.69</v>
-      </c>
-      <c r="R44">
-        <v>0</v>
-      </c>
-      <c r="S44">
-        <v>0</v>
-      </c>
-      <c r="T44">
-        <v>0</v>
-      </c>
-      <c r="U44">
-        <v>0</v>
-      </c>
-      <c r="V44">
-        <v>0</v>
-      </c>
-      <c r="W44">
-        <v>0</v>
-      </c>
-      <c r="X44">
-        <v>0</v>
-      </c>
-      <c r="Y44">
-        <v>0</v>
-      </c>
-      <c r="Z44">
-        <v>0</v>
-      </c>
-      <c r="AA44">
-        <v>0</v>
-      </c>
-      <c r="AB44">
-        <v>0</v>
-      </c>
-      <c r="AC44">
-        <v>0</v>
-      </c>
-      <c r="AD44">
-        <v>0</v>
-      </c>
-      <c r="AE44">
-        <v>0</v>
-      </c>
-      <c r="AF44">
-        <v>0</v>
-      </c>
-      <c r="AG44">
-        <v>0</v>
-      </c>
-      <c r="AH44">
-        <v>0</v>
-      </c>
-      <c r="AI44">
-        <v>0</v>
-      </c>
-      <c r="AJ44">
-        <v>0</v>
-      </c>
-      <c r="AK44">
-        <v>0</v>
-      </c>
-      <c r="AL44">
-        <v>0</v>
-      </c>
-      <c r="AM44">
-        <v>0</v>
-      </c>
-      <c r="AN44">
-        <v>0</v>
-      </c>
-      <c r="AO44">
-        <v>0</v>
-      </c>
-      <c r="AP44">
-        <v>0</v>
-      </c>
-      <c r="AQ44">
-        <v>0</v>
-      </c>
-      <c r="AR44">
-        <v>0</v>
-      </c>
-      <c r="AS44">
-        <v>0</v>
-      </c>
-      <c r="AT44">
-        <v>0</v>
-      </c>
-      <c r="AU44">
-        <v>0</v>
-      </c>
-      <c r="AV44">
-        <v>0</v>
-      </c>
-      <c r="AW44">
-        <v>0</v>
-      </c>
-      <c r="AX44">
-        <v>0</v>
-      </c>
-      <c r="AY44">
-        <v>0</v>
-      </c>
-      <c r="AZ44">
-        <v>0</v>
-      </c>
-      <c r="BA44">
-        <v>0</v>
-      </c>
-      <c r="BB44">
-        <v>0</v>
-      </c>
-      <c r="BC44">
-        <v>0</v>
-      </c>
-      <c r="BD44">
-        <v>0</v>
-      </c>
-      <c r="BE44">
-        <v>0</v>
-      </c>
-      <c r="BF44">
-        <v>0</v>
-      </c>
-      <c r="BG44">
-        <v>0</v>
-      </c>
-      <c r="BH44" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="45" spans="1:60">
-      <c r="A45" t="s">
-        <v>80</v>
-      </c>
-      <c r="B45" t="s">
-        <v>84</v>
-      </c>
-      <c r="C45" t="s">
-        <v>101</v>
-      </c>
-      <c r="D45" t="s">
-        <v>145</v>
-      </c>
-      <c r="E45" t="s">
-        <v>189</v>
-      </c>
-      <c r="F45">
-        <v>1.61</v>
-      </c>
-      <c r="G45">
-        <v>1.74</v>
-      </c>
-      <c r="H45">
-        <v>6.4</v>
-      </c>
-      <c r="I45">
-        <v>7.8</v>
-      </c>
-      <c r="J45">
-        <v>3.55</v>
-      </c>
-      <c r="K45">
-        <v>4.5</v>
-      </c>
-      <c r="L45">
-        <v>1.48</v>
-      </c>
-      <c r="M45">
-        <v>1.09</v>
-      </c>
-      <c r="N45">
-        <v>2.92</v>
-      </c>
-      <c r="O45">
-        <v>1.44</v>
-      </c>
-      <c r="P45">
-        <v>1.65</v>
-      </c>
-      <c r="Q45">
-        <v>2.26</v>
-      </c>
-      <c r="R45">
-        <v>1.23</v>
-      </c>
-      <c r="S45">
-        <v>4.4</v>
-      </c>
-      <c r="T45">
-        <v>2.2</v>
-      </c>
-      <c r="U45">
-        <v>1.7</v>
-      </c>
-      <c r="V45">
-        <v>1.14</v>
-      </c>
-      <c r="W45">
-        <v>2.34</v>
-      </c>
-      <c r="X45">
-        <v>12.5</v>
-      </c>
-      <c r="Y45">
-        <v>21</v>
-      </c>
-      <c r="Z45">
-        <v>70</v>
-      </c>
-      <c r="AA45">
-        <v>300</v>
-      </c>
-      <c r="AB45">
-        <v>7.4</v>
-      </c>
-      <c r="AC45">
-        <v>10</v>
-      </c>
-      <c r="AD45">
-        <v>34</v>
-      </c>
-      <c r="AE45">
-        <v>160</v>
-      </c>
-      <c r="AF45">
-        <v>10</v>
-      </c>
-      <c r="AG45">
-        <v>12</v>
-      </c>
-      <c r="AH45">
-        <v>29</v>
-      </c>
-      <c r="AI45">
-        <v>160</v>
-      </c>
-      <c r="AJ45">
-        <v>19.5</v>
-      </c>
-      <c r="AK45">
-        <v>23</v>
-      </c>
-      <c r="AL45">
-        <v>65</v>
-      </c>
-      <c r="AM45">
-        <v>250</v>
-      </c>
-      <c r="AN45">
-        <v>17</v>
-      </c>
-      <c r="AO45">
-        <v>280</v>
-      </c>
-      <c r="AP45">
-        <v>3.85</v>
-      </c>
-      <c r="AQ45">
-        <v>14.5</v>
-      </c>
-      <c r="AR45">
-        <v>5.1</v>
-      </c>
-      <c r="AS45">
-        <v>5.5</v>
-      </c>
-      <c r="AT45">
-        <v>5.6</v>
-      </c>
-      <c r="AU45">
-        <v>7.4</v>
-      </c>
-      <c r="AV45">
-        <v>4.7</v>
-      </c>
-      <c r="AW45">
-        <v>5.4</v>
-      </c>
-      <c r="AX45">
-        <v>7.4</v>
-      </c>
-      <c r="AY45">
-        <v>3.8</v>
-      </c>
-      <c r="AZ45">
-        <v>4.7</v>
-      </c>
-      <c r="BA45">
-        <v>5.4</v>
-      </c>
-      <c r="BB45">
-        <v>14</v>
-      </c>
-      <c r="BC45">
-        <v>4.5</v>
-      </c>
-      <c r="BD45">
-        <v>5.1</v>
-      </c>
-      <c r="BE45">
-        <v>5.4</v>
-      </c>
-      <c r="BF45">
-        <v>11</v>
-      </c>
-      <c r="BG45">
-        <v>5.5</v>
-      </c>
-      <c r="BH45" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-04.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="235">
   <si>
     <t>League</t>
   </si>
@@ -226,18 +226,27 @@
     <t>Saudi Professional League</t>
   </si>
   <si>
+    <t>Austrian Bundesliga</t>
+  </si>
+  <si>
     <t>Italian Serie A</t>
   </si>
   <si>
-    <t>Austrian Bundesliga</t>
-  </si>
-  <si>
     <t>Scottish Premiership</t>
   </si>
   <si>
     <t>Algerian Ligue 1</t>
   </si>
   <si>
+    <t>Portuguese Segunda Liga</t>
+  </si>
+  <si>
+    <t>Swedish Allsvenskan</t>
+  </si>
+  <si>
+    <t>Polish Ekstraklasa</t>
+  </si>
+  <si>
     <t>Danish Superliga</t>
   </si>
   <si>
@@ -247,15 +256,6 @@
     <t>Norwegian Eliteserien</t>
   </si>
   <si>
-    <t>Polish Ekstraklasa</t>
-  </si>
-  <si>
-    <t>Portuguese Segunda Liga</t>
-  </si>
-  <si>
-    <t>Swedish Allsvenskan</t>
-  </si>
-  <si>
     <t>Swedish Superettan</t>
   </si>
   <si>
@@ -283,6 +283,9 @@
     <t>Uruguayan Primera Division</t>
   </si>
   <si>
+    <t>Bolivian Liga de Futbol Profesional</t>
+  </si>
+  <si>
     <t>2026-05-04</t>
   </si>
   <si>
@@ -361,6 +364,12 @@
     <t>19:30:00</t>
   </si>
   <si>
+    <t>21:00:00</t>
+  </si>
+  <si>
+    <t>21:30:00</t>
+  </si>
+  <si>
     <t>Shanghai Second</t>
   </si>
   <si>
@@ -412,18 +421,18 @@
     <t>Derry City</t>
   </si>
   <si>
+    <t>Longford</t>
+  </si>
+  <si>
+    <t>Cobh Ramblers</t>
+  </si>
+  <si>
+    <t>Treaty United</t>
+  </si>
+  <si>
     <t>Finn Harps</t>
   </si>
   <si>
-    <t>Longford</t>
-  </si>
-  <si>
-    <t>Cobh Ramblers</t>
-  </si>
-  <si>
-    <t>Treaty United</t>
-  </si>
-  <si>
     <t>HJK Helsinki</t>
   </si>
   <si>
@@ -433,63 +442,63 @@
     <t>Al-Feiha</t>
   </si>
   <si>
+    <t>SCR Altach</t>
+  </si>
+  <si>
     <t>US Cremonese</t>
   </si>
   <si>
-    <t>SCR Altach</t>
-  </si>
-  <si>
     <t>Hearts</t>
   </si>
   <si>
     <t>Belouizdad</t>
   </si>
   <si>
+    <t>Torreense</t>
+  </si>
+  <si>
+    <t>Halmstads</t>
+  </si>
+  <si>
+    <t>Djurgardens</t>
+  </si>
+  <si>
+    <t>Porto B</t>
+  </si>
+  <si>
+    <t>Radomiak Radom</t>
+  </si>
+  <si>
     <t>Midtjylland</t>
   </si>
   <si>
+    <t>Maccabi Netanya</t>
+  </si>
+  <si>
+    <t>Bnei Sakhnin</t>
+  </si>
+  <si>
+    <t>Wadi Degla</t>
+  </si>
+  <si>
     <t>Al Ittihad (EGY)</t>
   </si>
   <si>
-    <t>Wadi Degla</t>
-  </si>
-  <si>
-    <t>Bnei Sakhnin</t>
-  </si>
-  <si>
-    <t>Maccabi Netanya</t>
-  </si>
-  <si>
     <t>Bodo Glimt</t>
   </si>
   <si>
-    <t>Radomiak Radom</t>
-  </si>
-  <si>
-    <t>Torreense</t>
-  </si>
-  <si>
-    <t>Porto B</t>
-  </si>
-  <si>
-    <t>Djurgardens</t>
-  </si>
-  <si>
-    <t>Halmstads</t>
-  </si>
-  <si>
     <t>Landskrona</t>
   </si>
   <si>
     <t>Rapid Bucharest</t>
   </si>
   <si>
+    <t>Al-Ittihad</t>
+  </si>
+  <si>
     <t>Al-Ettifaq</t>
   </si>
   <si>
-    <t>Al-Ittihad</t>
-  </si>
-  <si>
     <t>LASK Linz</t>
   </si>
   <si>
@@ -526,6 +535,15 @@
     <t>Penarol</t>
   </si>
   <si>
+    <t>Universitario de Vinto</t>
+  </si>
+  <si>
+    <t>Estudiantes Rio Cuarto</t>
+  </si>
+  <si>
+    <t>San Marcos</t>
+  </si>
+  <si>
     <t>Lanzhou Longyuan Athletic</t>
   </si>
   <si>
@@ -577,18 +595,18 @@
     <t>Galway Utd</t>
   </si>
   <si>
+    <t>Athlone Town</t>
+  </si>
+  <si>
+    <t>UCD</t>
+  </si>
+  <si>
+    <t>Wexford F.C</t>
+  </si>
+  <si>
     <t>Bray Wanderers</t>
   </si>
   <si>
-    <t>Athlone Town</t>
-  </si>
-  <si>
-    <t>UCD</t>
-  </si>
-  <si>
-    <t>Wexford F.C</t>
-  </si>
-  <si>
     <t>Lahti</t>
   </si>
   <si>
@@ -598,63 +616,63 @@
     <t>Al Riyadh SC</t>
   </si>
   <si>
+    <t>RZ Pellets WAC</t>
+  </si>
+  <si>
     <t>Lazio</t>
   </si>
   <si>
-    <t>RZ Pellets WAC</t>
-  </si>
-  <si>
     <t>Rangers</t>
   </si>
   <si>
     <t>USM Khenchela</t>
   </si>
   <si>
+    <t>Penafiel</t>
+  </si>
+  <si>
+    <t>Brommapojkarna</t>
+  </si>
+  <si>
+    <t>IFK Goteborg</t>
+  </si>
+  <si>
+    <t>Felgueiras</t>
+  </si>
+  <si>
+    <t>Lechia Gdansk</t>
+  </si>
+  <si>
     <t>Viborg</t>
   </si>
   <si>
+    <t>Hapoel Jerusalem</t>
+  </si>
+  <si>
+    <t>Maccabi Bnei Raina</t>
+  </si>
+  <si>
+    <t>Kahraba Ismailia</t>
+  </si>
+  <si>
     <t>Petrojet</t>
   </si>
   <si>
-    <t>Kahraba Ismailia</t>
-  </si>
-  <si>
-    <t>Maccabi Bnei Raina</t>
-  </si>
-  <si>
-    <t>Hapoel Jerusalem</t>
-  </si>
-  <si>
     <t>Molde</t>
   </si>
   <si>
-    <t>Lechia Gdansk</t>
-  </si>
-  <si>
-    <t>Penafiel</t>
-  </si>
-  <si>
-    <t>Felgueiras</t>
-  </si>
-  <si>
-    <t>IFK Goteborg</t>
-  </si>
-  <si>
-    <t>Brommapojkarna</t>
-  </si>
-  <si>
     <t>Osters</t>
   </si>
   <si>
     <t>CFR Cluj</t>
   </si>
   <si>
+    <t>Al-Kholood Club</t>
+  </si>
+  <si>
     <t>Al Najma Club</t>
   </si>
   <si>
-    <t>Al-Kholood Club</t>
-  </si>
-  <si>
     <t>Rapid Vienna</t>
   </si>
   <si>
@@ -691,7 +709,16 @@
     <t>Defensor Sporting</t>
   </si>
   <si>
-    <t>2026-05-03 00:11:14</t>
+    <t>Blooming Santa Cruz</t>
+  </si>
+  <si>
+    <t>Instituto</t>
+  </si>
+  <si>
+    <t>Deportes Recoleta</t>
+  </si>
+  <si>
+    <t>2026-05-03 02:41:31</t>
   </si>
 </sst>
 </file>
@@ -1049,7 +1076,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BH56"/>
+  <dimension ref="A1:BH59"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:60">
@@ -1239,25 +1266,25 @@
         <v>60</v>
       </c>
       <c r="B2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D2" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="E2" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="F2">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G2">
         <v>1000</v>
       </c>
       <c r="H2">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I2">
         <v>1000</v>
@@ -1275,19 +1302,19 @@
         <v>1.01</v>
       </c>
       <c r="N2">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
       <c r="O2">
-        <v>1.49</v>
+        <v>1.02</v>
       </c>
       <c r="P2">
-        <v>1.07</v>
+        <v>1.24</v>
       </c>
       <c r="Q2">
         <v>1.49</v>
       </c>
       <c r="R2">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="S2">
         <v>1.49</v>
@@ -1359,52 +1386,52 @@
         <v>1000</v>
       </c>
       <c r="AP2">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ2">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR2">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS2">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT2">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU2">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV2">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW2">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX2">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY2">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ2">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA2">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB2">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC2">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD2">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE2">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF2">
         <v>1.01</v>
@@ -1413,7 +1440,7 @@
         <v>1.01</v>
       </c>
       <c r="BH2" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
     </row>
     <row r="3" spans="1:60">
@@ -1421,31 +1448,31 @@
         <v>60</v>
       </c>
       <c r="B3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D3" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="E3" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="F3">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G3">
         <v>1000</v>
       </c>
       <c r="H3">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I3">
         <v>1000</v>
       </c>
       <c r="J3">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K3">
         <v>1000</v>
@@ -1460,19 +1487,19 @@
         <v>1.25</v>
       </c>
       <c r="O3">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P3">
         <v>1.24</v>
       </c>
       <c r="Q3">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="R3">
         <v>1.18</v>
       </c>
       <c r="S3">
-        <v>1.02</v>
+        <v>1.5</v>
       </c>
       <c r="T3">
         <v>1.01</v>
@@ -1541,52 +1568,52 @@
         <v>1000</v>
       </c>
       <c r="AP3">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ3">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR3">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS3">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT3">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU3">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV3">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW3">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX3">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY3">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ3">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA3">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB3">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC3">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD3">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE3">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF3">
         <v>1.01</v>
@@ -1595,7 +1622,7 @@
         <v>1.01</v>
       </c>
       <c r="BH3" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
     </row>
     <row r="4" spans="1:60">
@@ -1603,31 +1630,31 @@
         <v>60</v>
       </c>
       <c r="B4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D4" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E4" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="F4">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G4">
         <v>1000</v>
       </c>
       <c r="H4">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I4">
         <v>1000</v>
       </c>
       <c r="J4">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K4">
         <v>1000</v>
@@ -1642,19 +1669,19 @@
         <v>1.25</v>
       </c>
       <c r="O4">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P4">
         <v>1.24</v>
       </c>
       <c r="Q4">
-        <v>1.02</v>
+        <v>1.42</v>
       </c>
       <c r="R4">
         <v>1.18</v>
       </c>
       <c r="S4">
-        <v>1.02</v>
+        <v>1.42</v>
       </c>
       <c r="T4">
         <v>1.01</v>
@@ -1723,52 +1750,52 @@
         <v>1000</v>
       </c>
       <c r="AP4">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ4">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR4">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS4">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT4">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU4">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV4">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW4">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX4">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY4">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ4">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA4">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB4">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC4">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD4">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE4">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF4">
         <v>1.01</v>
@@ -1777,7 +1804,7 @@
         <v>1.01</v>
       </c>
       <c r="BH4" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
     </row>
     <row r="5" spans="1:60">
@@ -1785,31 +1812,31 @@
         <v>60</v>
       </c>
       <c r="B5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D5" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E5" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="F5">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G5">
         <v>1000</v>
       </c>
       <c r="H5">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I5">
         <v>1000</v>
       </c>
       <c r="J5">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K5">
         <v>1000</v>
@@ -1824,19 +1851,19 @@
         <v>1.25</v>
       </c>
       <c r="O5">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P5">
         <v>1.24</v>
       </c>
       <c r="Q5">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="R5">
         <v>1.18</v>
       </c>
       <c r="S5">
-        <v>1.02</v>
+        <v>1.5</v>
       </c>
       <c r="T5">
         <v>1.01</v>
@@ -1905,52 +1932,52 @@
         <v>1000</v>
       </c>
       <c r="AP5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF5">
         <v>1.01</v>
@@ -1959,7 +1986,7 @@
         <v>1.01</v>
       </c>
       <c r="BH5" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
     </row>
     <row r="6" spans="1:60">
@@ -1967,31 +1994,31 @@
         <v>60</v>
       </c>
       <c r="B6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D6" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="E6" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="F6">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G6">
         <v>1000</v>
       </c>
       <c r="H6">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I6">
         <v>1000</v>
       </c>
       <c r="J6">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K6">
         <v>1000</v>
@@ -2087,52 +2114,52 @@
         <v>1000</v>
       </c>
       <c r="AP6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF6">
         <v>1.01</v>
@@ -2141,7 +2168,7 @@
         <v>1.01</v>
       </c>
       <c r="BH6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
     </row>
     <row r="7" spans="1:60">
@@ -2149,31 +2176,31 @@
         <v>60</v>
       </c>
       <c r="B7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D7" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="E7" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="F7">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G7">
         <v>1000</v>
       </c>
       <c r="H7">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I7">
         <v>1000</v>
       </c>
       <c r="J7">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K7">
         <v>1000</v>
@@ -2188,19 +2215,19 @@
         <v>1.25</v>
       </c>
       <c r="O7">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P7">
         <v>1.24</v>
       </c>
       <c r="Q7">
-        <v>1.02</v>
+        <v>1.44</v>
       </c>
       <c r="R7">
         <v>1.18</v>
       </c>
       <c r="S7">
-        <v>1.02</v>
+        <v>1.44</v>
       </c>
       <c r="T7">
         <v>1.01</v>
@@ -2269,52 +2296,52 @@
         <v>1000</v>
       </c>
       <c r="AP7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF7">
         <v>1.01</v>
@@ -2323,7 +2350,7 @@
         <v>1.01</v>
       </c>
       <c r="BH7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
     </row>
     <row r="8" spans="1:60">
@@ -2331,31 +2358,31 @@
         <v>60</v>
       </c>
       <c r="B8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D8" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E8" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="F8">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G8">
         <v>1000</v>
       </c>
       <c r="H8">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I8">
         <v>1000</v>
       </c>
       <c r="J8">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K8">
         <v>1000</v>
@@ -2367,19 +2394,19 @@
         <v>1.01</v>
       </c>
       <c r="N8">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
       <c r="O8">
         <v>1.38</v>
       </c>
       <c r="P8">
-        <v>1.07</v>
+        <v>1.24</v>
       </c>
       <c r="Q8">
         <v>1.38</v>
       </c>
       <c r="R8">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="S8">
         <v>1.38</v>
@@ -2451,52 +2478,52 @@
         <v>1000</v>
       </c>
       <c r="AP8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF8">
         <v>1.01</v>
@@ -2505,7 +2532,7 @@
         <v>1.01</v>
       </c>
       <c r="BH8" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
     </row>
     <row r="9" spans="1:60">
@@ -2513,16 +2540,16 @@
         <v>61</v>
       </c>
       <c r="B9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D9" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="E9" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="F9">
         <v>1.71</v>
@@ -2570,7 +2597,7 @@
         <v>1.75</v>
       </c>
       <c r="U9">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="V9">
         <v>1.22</v>
@@ -2597,7 +2624,7 @@
         <v>9.4</v>
       </c>
       <c r="AD9">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AE9">
         <v>60</v>
@@ -2687,7 +2714,7 @@
         <v>50</v>
       </c>
       <c r="BH9" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
     </row>
     <row r="10" spans="1:60">
@@ -2695,19 +2722,19 @@
         <v>62</v>
       </c>
       <c r="B10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D10" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E10" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="F10">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="G10">
         <v>3.75</v>
@@ -2716,13 +2743,13 @@
         <v>2.58</v>
       </c>
       <c r="I10">
-        <v>2.98</v>
+        <v>2.92</v>
       </c>
       <c r="J10">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="K10">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="L10">
         <v>1.6</v>
@@ -2731,7 +2758,7 @@
         <v>1.14</v>
       </c>
       <c r="N10">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="O10">
         <v>1.61</v>
@@ -2749,25 +2776,25 @@
         <v>6.2</v>
       </c>
       <c r="T10">
-        <v>2.06</v>
+        <v>2.18</v>
       </c>
       <c r="U10">
         <v>1.68</v>
       </c>
       <c r="V10">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="W10">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="X10">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="Y10">
         <v>8.6</v>
       </c>
       <c r="Z10">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AA10">
         <v>60</v>
@@ -2812,10 +2839,10 @@
         <v>100</v>
       </c>
       <c r="AO10">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AP10">
-        <v>5.8</v>
+        <v>3.2</v>
       </c>
       <c r="AQ10">
         <v>5.9</v>
@@ -2824,19 +2851,19 @@
         <v>12</v>
       </c>
       <c r="AS10">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="AT10">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AU10">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="AV10">
         <v>10.5</v>
       </c>
       <c r="AW10">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="AX10">
         <v>16</v>
@@ -2845,31 +2872,31 @@
         <v>12</v>
       </c>
       <c r="AZ10">
-        <v>4.7</v>
+        <v>19.5</v>
       </c>
       <c r="BA10">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="BB10">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="BC10">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="BD10">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="BE10">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="BF10">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="BG10">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BH10" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
     </row>
     <row r="11" spans="1:60">
@@ -2877,25 +2904,25 @@
         <v>63</v>
       </c>
       <c r="B11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D11" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E11" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="F11">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="G11">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="H11">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="I11">
         <v>2.32</v>
@@ -2904,10 +2931,10 @@
         <v>3.15</v>
       </c>
       <c r="K11">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L11">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M11">
         <v>1.09</v>
@@ -2916,7 +2943,7 @@
         <v>2.98</v>
       </c>
       <c r="O11">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="P11">
         <v>1.68</v>
@@ -2940,25 +2967,25 @@
         <v>1.75</v>
       </c>
       <c r="W11">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="X11">
         <v>13.5</v>
       </c>
       <c r="Y11">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="Z11">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AA11">
         <v>36</v>
       </c>
       <c r="AB11">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AC11">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD11">
         <v>13.5</v>
@@ -2982,10 +3009,10 @@
         <v>110</v>
       </c>
       <c r="AK11">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AL11">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AM11">
         <v>170</v>
@@ -3003,10 +3030,10 @@
         <v>6</v>
       </c>
       <c r="AR11">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AS11">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AT11">
         <v>9.199999999999999</v>
@@ -3018,25 +3045,25 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AW11">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="AX11">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AY11">
-        <v>12</v>
+        <v>3.6</v>
       </c>
       <c r="AZ11">
         <v>14.5</v>
       </c>
       <c r="BA11">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BB11">
+        <v>4.2</v>
+      </c>
+      <c r="BC11">
         <v>4.1</v>
-      </c>
-      <c r="BC11">
-        <v>4</v>
       </c>
       <c r="BD11">
         <v>4.1</v>
@@ -3051,7 +3078,7 @@
         <v>3.75</v>
       </c>
       <c r="BH11" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
     </row>
     <row r="12" spans="1:60">
@@ -3059,16 +3086,16 @@
         <v>64</v>
       </c>
       <c r="B12" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C12" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D12" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E12" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="F12">
         <v>4.7</v>
@@ -3092,7 +3119,7 @@
         <v>1.01</v>
       </c>
       <c r="M12">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N12">
         <v>3.5</v>
@@ -3107,7 +3134,7 @@
         <v>1.89</v>
       </c>
       <c r="R12">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S12">
         <v>3.3</v>
@@ -3170,13 +3197,13 @@
         <v>85</v>
       </c>
       <c r="AM12">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN12">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AO12">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AP12">
         <v>1.03</v>
@@ -3227,13 +3254,13 @@
         <v>1.03</v>
       </c>
       <c r="BF12">
-        <v>60</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG12">
         <v>9</v>
       </c>
       <c r="BH12" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
     </row>
     <row r="13" spans="1:60">
@@ -3241,58 +3268,58 @@
         <v>65</v>
       </c>
       <c r="B13" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C13" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D13" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E13" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="F13">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="G13">
         <v>1.84</v>
       </c>
       <c r="H13">
-        <v>5.3</v>
+        <v>4.7</v>
       </c>
       <c r="I13">
-        <v>150</v>
+        <v>28</v>
       </c>
       <c r="J13">
         <v>3.55</v>
       </c>
       <c r="K13">
-        <v>7.8</v>
+        <v>17</v>
       </c>
       <c r="L13">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="M13">
         <v>1.01</v>
       </c>
       <c r="N13">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="O13">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="P13">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="Q13">
-        <v>1.27</v>
+        <v>1.84</v>
       </c>
       <c r="R13">
         <v>1.18</v>
       </c>
       <c r="S13">
-        <v>1.27</v>
+        <v>1.84</v>
       </c>
       <c r="T13">
         <v>1.01</v>
@@ -3301,7 +3328,7 @@
         <v>1.01</v>
       </c>
       <c r="V13">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="W13">
         <v>2.18</v>
@@ -3415,7 +3442,7 @@
         <v>1.01</v>
       </c>
       <c r="BH13" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14" spans="1:60">
@@ -3423,31 +3450,31 @@
         <v>66</v>
       </c>
       <c r="B14" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C14" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D14" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="E14" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="F14">
         <v>4.7</v>
       </c>
       <c r="G14">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="H14">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="I14">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="J14">
-        <v>2.92</v>
+        <v>3.15</v>
       </c>
       <c r="K14">
         <v>110</v>
@@ -3459,19 +3486,19 @@
         <v>1.04</v>
       </c>
       <c r="N14">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="O14">
         <v>1.18</v>
       </c>
       <c r="P14">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="Q14">
         <v>1.52</v>
       </c>
       <c r="R14">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="S14">
         <v>2.3</v>
@@ -3483,7 +3510,7 @@
         <v>1.01</v>
       </c>
       <c r="V14">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="W14">
         <v>1.16</v>
@@ -3597,7 +3624,7 @@
         <v>1.01</v>
       </c>
       <c r="BH14" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
     </row>
     <row r="15" spans="1:60">
@@ -3605,34 +3632,34 @@
         <v>66</v>
       </c>
       <c r="B15" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C15" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D15" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E15" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="F15">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="G15">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="H15">
         <v>7.6</v>
       </c>
       <c r="I15">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J15">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="K15">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="L15">
         <v>1.01</v>
@@ -3641,40 +3668,40 @@
         <v>1.07</v>
       </c>
       <c r="N15">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="O15">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="P15">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="Q15">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="R15">
         <v>1.32</v>
       </c>
       <c r="S15">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="T15">
-        <v>1.93</v>
+        <v>2.14</v>
       </c>
       <c r="U15">
-        <v>1.63</v>
+        <v>1.76</v>
       </c>
       <c r="V15">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="W15">
-        <v>2.52</v>
+        <v>2.74</v>
       </c>
       <c r="X15">
         <v>17</v>
       </c>
       <c r="Y15">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="Z15">
         <v>75</v>
@@ -3683,7 +3710,7 @@
         <v>1000</v>
       </c>
       <c r="AB15">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="AC15">
         <v>12</v>
@@ -3725,40 +3752,40 @@
         <v>280</v>
       </c>
       <c r="AP15">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="AQ15">
         <v>16.5</v>
       </c>
       <c r="AR15">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="AS15">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="AT15">
         <v>6</v>
       </c>
       <c r="AU15">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="AV15">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AW15">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="AX15">
         <v>7.2</v>
       </c>
       <c r="AY15">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="AZ15">
         <v>19.5</v>
       </c>
       <c r="BA15">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="BB15">
         <v>10</v>
@@ -3767,19 +3794,19 @@
         <v>13</v>
       </c>
       <c r="BD15">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="BE15">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="BF15">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="BG15">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="BH15" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
     </row>
     <row r="16" spans="1:60">
@@ -3787,31 +3814,31 @@
         <v>66</v>
       </c>
       <c r="B16" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C16" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D16" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="E16" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="F16">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="G16">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="H16">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="I16">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="J16">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K16">
         <v>3.7</v>
@@ -3829,10 +3856,10 @@
         <v>1.38</v>
       </c>
       <c r="P16">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="Q16">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="R16">
         <v>1.28</v>
@@ -3850,7 +3877,7 @@
         <v>1.29</v>
       </c>
       <c r="W16">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="X16">
         <v>12.5</v>
@@ -3961,7 +3988,7 @@
         <v>8</v>
       </c>
       <c r="BH16" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
     </row>
     <row r="17" spans="1:60">
@@ -3969,34 +3996,34 @@
         <v>66</v>
       </c>
       <c r="B17" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C17" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D17" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="E17" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="F17">
-        <v>4</v>
+        <v>5.2</v>
       </c>
       <c r="G17">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="H17">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="I17">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="J17">
-        <v>2.78</v>
+        <v>3.7</v>
       </c>
       <c r="K17">
-        <v>110</v>
+        <v>4.6</v>
       </c>
       <c r="L17">
         <v>1.01</v>
@@ -4005,16 +4032,16 @@
         <v>1.01</v>
       </c>
       <c r="N17">
-        <v>1.72</v>
+        <v>1.82</v>
       </c>
       <c r="O17">
         <v>1.31</v>
       </c>
       <c r="P17">
-        <v>1.71</v>
+        <v>1.82</v>
       </c>
       <c r="Q17">
-        <v>1.86</v>
+        <v>1.98</v>
       </c>
       <c r="R17">
         <v>1.25</v>
@@ -4029,7 +4056,7 @@
         <v>1.01</v>
       </c>
       <c r="V17">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="W17">
         <v>1.16</v>
@@ -4143,7 +4170,7 @@
         <v>1.01</v>
       </c>
       <c r="BH17" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
     </row>
     <row r="18" spans="1:60">
@@ -4151,22 +4178,22 @@
         <v>66</v>
       </c>
       <c r="B18" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C18" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D18" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="E18" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="F18">
         <v>1.62</v>
       </c>
       <c r="G18">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="H18">
         <v>1.09</v>
@@ -4214,7 +4241,7 @@
         <v>1.2</v>
       </c>
       <c r="W18">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="X18">
         <v>1000</v>
@@ -4325,7 +4352,7 @@
         <v>1.01</v>
       </c>
       <c r="BH18" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
     </row>
     <row r="19" spans="1:60">
@@ -4333,124 +4360,124 @@
         <v>67</v>
       </c>
       <c r="B19" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C19" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D19" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="E19" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="F19">
+        <v>1.89</v>
+      </c>
+      <c r="G19">
+        <v>2.54</v>
+      </c>
+      <c r="H19">
         <v>3.2</v>
       </c>
-      <c r="G19">
-        <v>3.8</v>
-      </c>
-      <c r="H19">
-        <v>2.14</v>
-      </c>
       <c r="I19">
-        <v>2.58</v>
+        <v>4.8</v>
       </c>
       <c r="J19">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="K19">
-        <v>4.5</v>
+        <v>6.4</v>
       </c>
       <c r="L19">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="M19">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="N19">
-        <v>3.3</v>
+        <v>1.81</v>
       </c>
       <c r="O19">
         <v>1.28</v>
       </c>
       <c r="P19">
-        <v>1.94</v>
+        <v>1.81</v>
       </c>
       <c r="Q19">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
       <c r="R19">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="S19">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="T19">
-        <v>1.7</v>
+        <v>1.01</v>
       </c>
       <c r="U19">
-        <v>2.14</v>
+        <v>1.01</v>
       </c>
       <c r="V19">
-        <v>1.63</v>
+        <v>1.26</v>
       </c>
       <c r="W19">
-        <v>1.36</v>
+        <v>1.65</v>
       </c>
       <c r="X19">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="Y19">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Z19">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AA19">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AB19">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AC19">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AD19">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AE19">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AF19">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AG19">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AH19">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI19">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AJ19">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AK19">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AL19">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AM19">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN19">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AO19">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AP19">
         <v>1.03</v>
@@ -4501,13 +4528,13 @@
         <v>1.03</v>
       </c>
       <c r="BF19">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BG19">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH19" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
     </row>
     <row r="20" spans="1:60">
@@ -4515,34 +4542,34 @@
         <v>67</v>
       </c>
       <c r="B20" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C20" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D20" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="E20" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="F20">
-        <v>1.89</v>
+        <v>2.26</v>
       </c>
       <c r="G20">
-        <v>2.54</v>
+        <v>3.2</v>
       </c>
       <c r="H20">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="I20">
-        <v>4.8</v>
+        <v>3.45</v>
       </c>
       <c r="J20">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K20">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="L20">
         <v>1.01</v>
@@ -4551,22 +4578,22 @@
         <v>1.01</v>
       </c>
       <c r="N20">
-        <v>1.81</v>
+        <v>1.25</v>
       </c>
       <c r="O20">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="P20">
-        <v>1.81</v>
+        <v>1.24</v>
       </c>
       <c r="Q20">
-        <v>1.83</v>
+        <v>1.66</v>
       </c>
       <c r="R20">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="S20">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="T20">
         <v>1.01</v>
@@ -4575,10 +4602,10 @@
         <v>1.01</v>
       </c>
       <c r="V20">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="W20">
-        <v>1.64</v>
+        <v>1.45</v>
       </c>
       <c r="X20">
         <v>1000</v>
@@ -4689,7 +4716,7 @@
         <v>1.01</v>
       </c>
       <c r="BH20" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
     </row>
     <row r="21" spans="1:60">
@@ -4697,157 +4724,157 @@
         <v>67</v>
       </c>
       <c r="B21" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C21" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D21" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E21" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="F21">
-        <v>2.26</v>
+        <v>3.3</v>
       </c>
       <c r="G21">
-        <v>3.2</v>
+        <v>4.3</v>
       </c>
       <c r="H21">
-        <v>2.4</v>
+        <v>2.14</v>
       </c>
       <c r="I21">
-        <v>3.45</v>
+        <v>2.5</v>
       </c>
       <c r="J21">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K21">
+        <v>3.85</v>
+      </c>
+      <c r="L21">
+        <v>1.34</v>
+      </c>
+      <c r="M21">
+        <v>1.07</v>
+      </c>
+      <c r="N21">
+        <v>3.55</v>
+      </c>
+      <c r="O21">
+        <v>1.32</v>
+      </c>
+      <c r="P21">
+        <v>1.85</v>
+      </c>
+      <c r="Q21">
+        <v>1.94</v>
+      </c>
+      <c r="R21">
+        <v>1.33</v>
+      </c>
+      <c r="S21">
+        <v>3.4</v>
+      </c>
+      <c r="T21">
+        <v>1.77</v>
+      </c>
+      <c r="U21">
+        <v>2.1</v>
+      </c>
+      <c r="V21">
+        <v>1.69</v>
+      </c>
+      <c r="W21">
+        <v>1.34</v>
+      </c>
+      <c r="X21">
+        <v>17</v>
+      </c>
+      <c r="Y21">
+        <v>12</v>
+      </c>
+      <c r="Z21">
+        <v>18</v>
+      </c>
+      <c r="AA21">
+        <v>38</v>
+      </c>
+      <c r="AB21">
+        <v>16</v>
+      </c>
+      <c r="AC21">
+        <v>9.6</v>
+      </c>
+      <c r="AD21">
+        <v>13.5</v>
+      </c>
+      <c r="AE21">
+        <v>32</v>
+      </c>
+      <c r="AF21">
+        <v>32</v>
+      </c>
+      <c r="AG21">
+        <v>18</v>
+      </c>
+      <c r="AH21">
+        <v>22</v>
+      </c>
+      <c r="AI21">
+        <v>48</v>
+      </c>
+      <c r="AJ21">
+        <v>80</v>
+      </c>
+      <c r="AK21">
+        <v>55</v>
+      </c>
+      <c r="AL21">
+        <v>65</v>
+      </c>
+      <c r="AM21">
+        <v>120</v>
+      </c>
+      <c r="AN21">
+        <v>55</v>
+      </c>
+      <c r="AO21">
+        <v>23</v>
+      </c>
+      <c r="AP21">
+        <v>10</v>
+      </c>
+      <c r="AQ21">
         <v>7.2</v>
       </c>
-      <c r="L21">
-        <v>1.01</v>
-      </c>
-      <c r="M21">
-        <v>1.01</v>
-      </c>
-      <c r="N21">
-        <v>1.25</v>
-      </c>
-      <c r="O21">
-        <v>1.25</v>
-      </c>
-      <c r="P21">
-        <v>1.24</v>
-      </c>
-      <c r="Q21">
-        <v>1.66</v>
-      </c>
-      <c r="R21">
-        <v>1.2</v>
-      </c>
-      <c r="S21">
-        <v>2.66</v>
-      </c>
-      <c r="T21">
-        <v>1.01</v>
-      </c>
-      <c r="U21">
-        <v>1.01</v>
-      </c>
-      <c r="V21">
-        <v>1.4</v>
-      </c>
-      <c r="W21">
-        <v>1.45</v>
-      </c>
-      <c r="X21">
-        <v>1000</v>
-      </c>
-      <c r="Y21">
-        <v>1000</v>
-      </c>
-      <c r="Z21">
-        <v>1000</v>
-      </c>
-      <c r="AA21">
-        <v>1000</v>
-      </c>
-      <c r="AB21">
-        <v>1000</v>
-      </c>
-      <c r="AC21">
-        <v>1000</v>
-      </c>
-      <c r="AD21">
-        <v>1000</v>
-      </c>
-      <c r="AE21">
-        <v>1000</v>
-      </c>
-      <c r="AF21">
-        <v>1000</v>
-      </c>
-      <c r="AG21">
-        <v>1000</v>
-      </c>
-      <c r="AH21">
-        <v>1000</v>
-      </c>
-      <c r="AI21">
-        <v>1000</v>
-      </c>
-      <c r="AJ21">
-        <v>1000</v>
-      </c>
-      <c r="AK21">
-        <v>1000</v>
-      </c>
-      <c r="AL21">
-        <v>1000</v>
-      </c>
-      <c r="AM21">
-        <v>1000</v>
-      </c>
-      <c r="AN21">
-        <v>1000</v>
-      </c>
-      <c r="AO21">
-        <v>1000</v>
-      </c>
-      <c r="AP21">
-        <v>1.03</v>
-      </c>
-      <c r="AQ21">
-        <v>1.03</v>
-      </c>
       <c r="AR21">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AS21">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="AT21">
-        <v>1.03</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU21">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AV21">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW21">
-        <v>1.03</v>
+        <v>18</v>
       </c>
       <c r="AX21">
-        <v>1.03</v>
+        <v>18</v>
       </c>
       <c r="AY21">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AZ21">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="BA21">
         <v>1.03</v>
@@ -4865,13 +4892,13 @@
         <v>1.03</v>
       </c>
       <c r="BF21">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="BG21">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BH21" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
     </row>
     <row r="22" spans="1:60">
@@ -4879,124 +4906,124 @@
         <v>67</v>
       </c>
       <c r="B22" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C22" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D22" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E22" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="F22">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="G22">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="H22">
-        <v>1.97</v>
+        <v>2.18</v>
       </c>
       <c r="I22">
-        <v>2.68</v>
+        <v>2.42</v>
       </c>
       <c r="J22">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="K22">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="L22">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M22">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N22">
-        <v>1.72</v>
+        <v>3.7</v>
       </c>
       <c r="O22">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P22">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="Q22">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="R22">
-        <v>1.26</v>
+        <v>1.37</v>
       </c>
       <c r="S22">
-        <v>2.92</v>
+        <v>3.15</v>
       </c>
       <c r="T22">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="U22">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="V22">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="W22">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="X22">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="Y22">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Z22">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AA22">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AB22">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AC22">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD22">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AE22">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AF22">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AG22">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AH22">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI22">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AJ22">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AK22">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AL22">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM22">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN22">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AO22">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AP22">
         <v>1.03</v>
@@ -5014,7 +5041,7 @@
         <v>1.03</v>
       </c>
       <c r="AU22">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AV22">
         <v>1.03</v>
@@ -5047,13 +5074,13 @@
         <v>1.03</v>
       </c>
       <c r="BF22">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BG22">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BH22" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
     </row>
     <row r="23" spans="1:60">
@@ -5061,34 +5088,34 @@
         <v>68</v>
       </c>
       <c r="B23" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C23" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D23" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E23" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="F23">
         <v>1.48</v>
       </c>
       <c r="G23">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="H23">
         <v>6.8</v>
       </c>
       <c r="I23">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J23">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="K23">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="L23">
         <v>1.01</v>
@@ -5097,34 +5124,34 @@
         <v>1.04</v>
       </c>
       <c r="N23">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="O23">
         <v>1.22</v>
       </c>
       <c r="P23">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="Q23">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="R23">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="S23">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="T23">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="U23">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="V23">
         <v>1.14</v>
       </c>
       <c r="W23">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="X23">
         <v>27</v>
@@ -5133,16 +5160,16 @@
         <v>34</v>
       </c>
       <c r="Z23">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AA23">
         <v>260</v>
       </c>
       <c r="AB23">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AC23">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AD23">
         <v>34</v>
@@ -5151,22 +5178,22 @@
         <v>120</v>
       </c>
       <c r="AF23">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AG23">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AH23">
         <v>27</v>
       </c>
       <c r="AI23">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AJ23">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AK23">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="AL23">
         <v>40</v>
@@ -5175,67 +5202,67 @@
         <v>130</v>
       </c>
       <c r="AN23">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="AO23">
         <v>140</v>
       </c>
       <c r="AP23">
-        <v>15.5</v>
+        <v>19.5</v>
       </c>
       <c r="AQ23">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AR23">
-        <v>4.1</v>
+        <v>29</v>
       </c>
       <c r="AS23">
-        <v>4.2</v>
+        <v>46</v>
       </c>
       <c r="AT23">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU23">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AV23">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AW23">
-        <v>4.1</v>
+        <v>36</v>
       </c>
       <c r="AX23">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="AY23">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ23">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="BA23">
-        <v>4.1</v>
+        <v>34</v>
       </c>
       <c r="BB23">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BC23">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BD23">
-        <v>3.9</v>
+        <v>21</v>
       </c>
       <c r="BE23">
-        <v>4.2</v>
+        <v>40</v>
       </c>
       <c r="BF23">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="BG23">
-        <v>4.2</v>
+        <v>38</v>
       </c>
       <c r="BH23" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
     </row>
     <row r="24" spans="1:60">
@@ -5243,28 +5270,28 @@
         <v>67</v>
       </c>
       <c r="B24" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C24" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D24" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E24" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="F24">
-        <v>5.2</v>
+        <v>6.6</v>
       </c>
       <c r="G24">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="H24">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="I24">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="J24">
         <v>3.75</v>
@@ -5273,7 +5300,7 @@
         <v>5.6</v>
       </c>
       <c r="L24">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="M24">
         <v>1.06</v>
@@ -5285,7 +5312,7 @@
         <v>1.32</v>
       </c>
       <c r="P24">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="Q24">
         <v>1.79</v>
@@ -5297,19 +5324,19 @@
         <v>3</v>
       </c>
       <c r="T24">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="U24">
         <v>1.65</v>
       </c>
       <c r="V24">
-        <v>2.72</v>
+        <v>2.52</v>
       </c>
       <c r="W24">
         <v>1.1</v>
       </c>
       <c r="X24">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Y24">
         <v>8.800000000000001</v>
@@ -5333,7 +5360,7 @@
         <v>21</v>
       </c>
       <c r="AF24">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AG24">
         <v>40</v>
@@ -5366,22 +5393,22 @@
         <v>1.03</v>
       </c>
       <c r="AQ24">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="AR24">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AS24">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="AT24">
         <v>1.03</v>
       </c>
       <c r="AU24">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AV24">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AW24">
         <v>1.03</v>
@@ -5414,10 +5441,10 @@
         <v>1.01</v>
       </c>
       <c r="BG24">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BH24" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
     </row>
     <row r="25" spans="1:60">
@@ -5425,22 +5452,22 @@
         <v>69</v>
       </c>
       <c r="B25" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C25" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D25" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="E25" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="F25">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="G25">
-        <v>110</v>
+        <v>3.15</v>
       </c>
       <c r="H25">
         <v>2.58</v>
@@ -5449,7 +5476,7 @@
         <v>4</v>
       </c>
       <c r="J25">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="K25">
         <v>110</v>
@@ -5488,7 +5515,7 @@
         <v>1.33</v>
       </c>
       <c r="W25">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="X25">
         <v>1000</v>
@@ -5599,7 +5626,7 @@
         <v>1.01</v>
       </c>
       <c r="BH25" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
     </row>
     <row r="26" spans="1:60">
@@ -5607,181 +5634,181 @@
         <v>70</v>
       </c>
       <c r="B26" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C26" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D26" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="E26" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="F26">
-        <v>3.1</v>
+        <v>2.46</v>
       </c>
       <c r="G26">
-        <v>3.15</v>
+        <v>2.84</v>
       </c>
       <c r="H26">
-        <v>2.64</v>
+        <v>3</v>
       </c>
       <c r="I26">
-        <v>2.66</v>
+        <v>3.6</v>
       </c>
       <c r="J26">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="K26">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="L26">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="M26">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="N26">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="O26">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="P26">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="Q26">
-        <v>2.24</v>
+        <v>2.08</v>
       </c>
       <c r="R26">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="S26">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="T26">
-        <v>1.92</v>
+        <v>1.55</v>
       </c>
       <c r="U26">
-        <v>2.04</v>
+        <v>1.71</v>
       </c>
       <c r="V26">
-        <v>1.6</v>
+        <v>1.39</v>
       </c>
       <c r="W26">
-        <v>1.46</v>
+        <v>1.54</v>
       </c>
       <c r="X26">
+        <v>1000</v>
+      </c>
+      <c r="Y26">
+        <v>17</v>
+      </c>
+      <c r="Z26">
+        <v>30</v>
+      </c>
+      <c r="AA26">
+        <v>85</v>
+      </c>
+      <c r="AB26">
+        <v>14.5</v>
+      </c>
+      <c r="AC26">
         <v>11</v>
       </c>
-      <c r="Y26">
-        <v>9.6</v>
-      </c>
-      <c r="Z26">
-        <v>16</v>
-      </c>
-      <c r="AA26">
-        <v>40</v>
-      </c>
-      <c r="AB26">
-        <v>11</v>
-      </c>
-      <c r="AC26">
-        <v>7.2</v>
-      </c>
       <c r="AD26">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AE26">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="AF26">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AG26">
-        <v>13.5</v>
+        <v>17.5</v>
       </c>
       <c r="AH26">
-        <v>19.5</v>
+        <v>26</v>
       </c>
       <c r="AI26">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="AJ26">
         <v>55</v>
       </c>
       <c r="AK26">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="AL26">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AM26">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN26">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AO26">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AP26">
-        <v>10</v>
+        <v>2.16</v>
       </c>
       <c r="AQ26">
-        <v>8.800000000000001</v>
+        <v>1.91</v>
       </c>
       <c r="AR26">
         <v>14.5</v>
       </c>
       <c r="AS26">
-        <v>34</v>
+        <v>2.1</v>
       </c>
       <c r="AT26">
-        <v>10</v>
+        <v>1.88</v>
       </c>
       <c r="AU26">
-        <v>6.8</v>
+        <v>1.8</v>
       </c>
       <c r="AV26">
-        <v>11</v>
+        <v>1.95</v>
       </c>
       <c r="AW26">
-        <v>28</v>
+        <v>2.08</v>
       </c>
       <c r="AX26">
-        <v>18</v>
+        <v>1.98</v>
       </c>
       <c r="AY26">
-        <v>12.5</v>
+        <v>1.92</v>
       </c>
       <c r="AZ26">
-        <v>17.5</v>
+        <v>1.99</v>
       </c>
       <c r="BA26">
-        <v>44</v>
+        <v>2.1</v>
       </c>
       <c r="BB26">
-        <v>46</v>
+        <v>2.08</v>
       </c>
       <c r="BC26">
-        <v>34</v>
+        <v>2.06</v>
       </c>
       <c r="BD26">
-        <v>48</v>
+        <v>2.08</v>
       </c>
       <c r="BE26">
-        <v>40</v>
+        <v>2.16</v>
       </c>
       <c r="BF26">
-        <v>34</v>
+        <v>2.16</v>
       </c>
       <c r="BG26">
-        <v>26</v>
+        <v>2.16</v>
       </c>
       <c r="BH26" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
     </row>
     <row r="27" spans="1:60">
@@ -5789,181 +5816,181 @@
         <v>71</v>
       </c>
       <c r="B27" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C27" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D27" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E27" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="F27">
-        <v>2.42</v>
+        <v>3.1</v>
       </c>
       <c r="G27">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="H27">
-        <v>3</v>
+        <v>2.64</v>
       </c>
       <c r="I27">
-        <v>3.9</v>
+        <v>2.66</v>
       </c>
       <c r="J27">
-        <v>2.42</v>
+        <v>3.3</v>
       </c>
       <c r="K27">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="L27">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="M27">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="N27">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O27">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="P27">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="Q27">
+        <v>2.24</v>
+      </c>
+      <c r="R27">
+        <v>1.29</v>
+      </c>
+      <c r="S27">
+        <v>4.3</v>
+      </c>
+      <c r="T27">
+        <v>1.92</v>
+      </c>
+      <c r="U27">
         <v>2.04</v>
       </c>
-      <c r="R27">
-        <v>1.26</v>
-      </c>
-      <c r="S27">
-        <v>3.25</v>
-      </c>
-      <c r="T27">
-        <v>1.01</v>
-      </c>
-      <c r="U27">
-        <v>1.01</v>
-      </c>
       <c r="V27">
-        <v>1.38</v>
+        <v>1.6</v>
       </c>
       <c r="W27">
-        <v>1.57</v>
+        <v>1.46</v>
       </c>
       <c r="X27">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Y27">
-        <v>17</v>
+        <v>9.6</v>
       </c>
       <c r="Z27">
+        <v>16</v>
+      </c>
+      <c r="AA27">
+        <v>40</v>
+      </c>
+      <c r="AB27">
+        <v>11</v>
+      </c>
+      <c r="AC27">
+        <v>7.2</v>
+      </c>
+      <c r="AD27">
+        <v>12</v>
+      </c>
+      <c r="AE27">
         <v>32</v>
       </c>
-      <c r="AA27">
-        <v>85</v>
-      </c>
-      <c r="AB27">
-        <v>14.5</v>
-      </c>
-      <c r="AC27">
-        <v>11</v>
-      </c>
-      <c r="AD27">
+      <c r="AF27">
         <v>20</v>
       </c>
-      <c r="AE27">
-        <v>55</v>
-      </c>
-      <c r="AF27">
-        <v>23</v>
-      </c>
       <c r="AG27">
-        <v>17.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH27">
-        <v>26</v>
+        <v>19.5</v>
       </c>
       <c r="AI27">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="AJ27">
         <v>55</v>
       </c>
       <c r="AK27">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AL27">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AM27">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN27">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AO27">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AP27">
-        <v>2.16</v>
+        <v>10</v>
       </c>
       <c r="AQ27">
-        <v>1.92</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR27">
         <v>14.5</v>
       </c>
       <c r="AS27">
-        <v>2.1</v>
+        <v>34</v>
       </c>
       <c r="AT27">
-        <v>1.88</v>
+        <v>10</v>
       </c>
       <c r="AU27">
-        <v>1.81</v>
+        <v>6.8</v>
       </c>
       <c r="AV27">
-        <v>1.95</v>
+        <v>11</v>
       </c>
       <c r="AW27">
-        <v>2.08</v>
+        <v>28</v>
       </c>
       <c r="AX27">
-        <v>1.98</v>
+        <v>18</v>
       </c>
       <c r="AY27">
-        <v>1.92</v>
+        <v>12.5</v>
       </c>
       <c r="AZ27">
-        <v>2</v>
+        <v>17.5</v>
       </c>
       <c r="BA27">
-        <v>2.1</v>
+        <v>44</v>
       </c>
       <c r="BB27">
-        <v>2.08</v>
+        <v>46</v>
       </c>
       <c r="BC27">
-        <v>2.06</v>
+        <v>34</v>
       </c>
       <c r="BD27">
-        <v>2.08</v>
+        <v>48</v>
       </c>
       <c r="BE27">
-        <v>2.16</v>
+        <v>40</v>
       </c>
       <c r="BF27">
-        <v>2.16</v>
+        <v>34</v>
       </c>
       <c r="BG27">
-        <v>2.16</v>
+        <v>26</v>
       </c>
       <c r="BH27" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
     </row>
     <row r="28" spans="1:60">
@@ -5971,19 +5998,19 @@
         <v>72</v>
       </c>
       <c r="B28" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C28" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D28" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E28" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="F28">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="G28">
         <v>2.9</v>
@@ -6007,7 +6034,7 @@
         <v>1.05</v>
       </c>
       <c r="N28">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="O28">
         <v>1.26</v>
@@ -6016,10 +6043,10 @@
         <v>2.24</v>
       </c>
       <c r="Q28">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="R28">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S28">
         <v>2.82</v>
@@ -6028,10 +6055,10 @@
         <v>1.63</v>
       </c>
       <c r="U28">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="V28">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="W28">
         <v>1.52</v>
@@ -6046,19 +6073,19 @@
         <v>20</v>
       </c>
       <c r="AA28">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AB28">
         <v>14.5</v>
       </c>
       <c r="AC28">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AD28">
         <v>12</v>
       </c>
       <c r="AE28">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AF28">
         <v>22</v>
@@ -6094,13 +6121,13 @@
         <v>15.5</v>
       </c>
       <c r="AQ28">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AR28">
         <v>16.5</v>
       </c>
       <c r="AS28">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="AT28">
         <v>12</v>
@@ -6127,7 +6154,7 @@
         <v>28</v>
       </c>
       <c r="BB28">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BC28">
         <v>25</v>
@@ -6145,7 +6172,7 @@
         <v>15.5</v>
       </c>
       <c r="BH28" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
     </row>
     <row r="29" spans="1:60">
@@ -6153,16 +6180,16 @@
         <v>73</v>
       </c>
       <c r="B29" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C29" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D29" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E29" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="F29">
         <v>1.02</v>
@@ -6327,7 +6354,7 @@
         <v>1.01</v>
       </c>
       <c r="BH29" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
     </row>
     <row r="30" spans="1:60">
@@ -6335,703 +6362,703 @@
         <v>74</v>
       </c>
       <c r="B30" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C30" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D30" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E30" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="F30">
-        <v>1.59</v>
+        <v>1.69</v>
       </c>
       <c r="G30">
-        <v>1.66</v>
+        <v>2</v>
       </c>
       <c r="H30">
-        <v>5.6</v>
+        <v>3.85</v>
       </c>
       <c r="I30">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="J30">
-        <v>4.5</v>
+        <v>3.2</v>
       </c>
       <c r="K30">
-        <v>5</v>
+        <v>6.8</v>
       </c>
       <c r="L30">
         <v>1.01</v>
       </c>
       <c r="M30">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="N30">
-        <v>5.5</v>
+        <v>1.64</v>
       </c>
       <c r="O30">
-        <v>1.19</v>
+        <v>1.35</v>
       </c>
       <c r="P30">
-        <v>2.54</v>
+        <v>1.64</v>
       </c>
       <c r="Q30">
-        <v>1.58</v>
+        <v>2</v>
       </c>
       <c r="R30">
-        <v>1.61</v>
+        <v>1.23</v>
       </c>
       <c r="S30">
-        <v>2.42</v>
+        <v>3.15</v>
       </c>
       <c r="T30">
-        <v>1.58</v>
+        <v>1.01</v>
       </c>
       <c r="U30">
-        <v>2.1</v>
+        <v>1.01</v>
       </c>
       <c r="V30">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="W30">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="X30">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="Y30">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="Z30">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AA30">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AB30">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AC30">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AD30">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AE30">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AF30">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AG30">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AH30">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AI30">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ30">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AK30">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AL30">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AM30">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AN30">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="AO30">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AP30">
-        <v>8.6</v>
+        <v>1.03</v>
       </c>
       <c r="AQ30">
-        <v>8.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AR30">
-        <v>9.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AS30">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AT30">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AU30">
-        <v>9.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AV30">
-        <v>19.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW30">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AX30">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY30">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AZ30">
-        <v>16</v>
+        <v>1.03</v>
       </c>
       <c r="BA30">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="BB30">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="BC30">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD30">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="BE30">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="BF30">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BG30">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BH30" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
     </row>
     <row r="31" spans="1:60">
       <c r="A31" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="B31" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C31" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D31" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E31" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="F31">
-        <v>2.32</v>
+        <v>3.05</v>
       </c>
       <c r="G31">
-        <v>2.66</v>
+        <v>3.25</v>
       </c>
       <c r="H31">
+        <v>2.48</v>
+      </c>
+      <c r="I31">
+        <v>2.6</v>
+      </c>
+      <c r="J31">
+        <v>3.45</v>
+      </c>
+      <c r="K31">
+        <v>3.6</v>
+      </c>
+      <c r="L31">
+        <v>1.01</v>
+      </c>
+      <c r="M31">
+        <v>1.08</v>
+      </c>
+      <c r="N31">
         <v>3.55</v>
       </c>
-      <c r="I31">
-        <v>4.4</v>
-      </c>
-      <c r="J31">
-        <v>2.94</v>
-      </c>
-      <c r="K31">
-        <v>3.35</v>
-      </c>
-      <c r="L31">
-        <v>1.01</v>
-      </c>
-      <c r="M31">
-        <v>1.01</v>
-      </c>
-      <c r="N31">
-        <v>1.52</v>
-      </c>
       <c r="O31">
-        <v>1.02</v>
+        <v>1.35</v>
       </c>
       <c r="P31">
-        <v>1.52</v>
+        <v>1.85</v>
       </c>
       <c r="Q31">
-        <v>2.54</v>
+        <v>2.02</v>
       </c>
       <c r="R31">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="S31">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
       <c r="T31">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="U31">
-        <v>1.56</v>
+        <v>2.12</v>
       </c>
       <c r="V31">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="W31">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="X31">
+        <v>15.5</v>
+      </c>
+      <c r="Y31">
+        <v>10.5</v>
+      </c>
+      <c r="Z31">
+        <v>17.5</v>
+      </c>
+      <c r="AA31">
+        <v>38</v>
+      </c>
+      <c r="AB31">
+        <v>12.5</v>
+      </c>
+      <c r="AC31">
+        <v>7.8</v>
+      </c>
+      <c r="AD31">
+        <v>12.5</v>
+      </c>
+      <c r="AE31">
+        <v>30</v>
+      </c>
+      <c r="AF31">
+        <v>23</v>
+      </c>
+      <c r="AG31">
+        <v>14.5</v>
+      </c>
+      <c r="AH31">
+        <v>18.5</v>
+      </c>
+      <c r="AI31">
+        <v>44</v>
+      </c>
+      <c r="AJ31">
+        <v>55</v>
+      </c>
+      <c r="AK31">
+        <v>40</v>
+      </c>
+      <c r="AL31">
+        <v>50</v>
+      </c>
+      <c r="AM31">
+        <v>110</v>
+      </c>
+      <c r="AN31">
+        <v>36</v>
+      </c>
+      <c r="AO31">
+        <v>25</v>
+      </c>
+      <c r="AP31">
         <v>11.5</v>
       </c>
-      <c r="Y31">
-        <v>14.5</v>
-      </c>
-      <c r="Z31">
-        <v>34</v>
-      </c>
-      <c r="AA31">
-        <v>1000</v>
-      </c>
-      <c r="AB31">
-        <v>10</v>
-      </c>
-      <c r="AC31">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD31">
-        <v>23</v>
-      </c>
-      <c r="AE31">
-        <v>85</v>
-      </c>
-      <c r="AF31">
-        <v>20</v>
-      </c>
-      <c r="AG31">
-        <v>17</v>
-      </c>
-      <c r="AH31">
-        <v>32</v>
-      </c>
-      <c r="AI31">
-        <v>1000</v>
-      </c>
-      <c r="AJ31">
-        <v>50</v>
-      </c>
-      <c r="AK31">
-        <v>48</v>
-      </c>
-      <c r="AL31">
-        <v>90</v>
-      </c>
-      <c r="AM31">
-        <v>1000</v>
-      </c>
-      <c r="AN31">
-        <v>1000</v>
-      </c>
-      <c r="AO31">
-        <v>1000</v>
-      </c>
-      <c r="AP31">
-        <v>2.2</v>
-      </c>
       <c r="AQ31">
-        <v>2.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR31">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AS31">
-        <v>2.72</v>
+        <v>7.4</v>
       </c>
       <c r="AT31">
-        <v>2.14</v>
+        <v>10.5</v>
       </c>
       <c r="AU31">
-        <v>2.12</v>
+        <v>7</v>
       </c>
       <c r="AV31">
+        <v>10.5</v>
+      </c>
+      <c r="AW31">
+        <v>7</v>
+      </c>
+      <c r="AX31">
+        <v>18</v>
+      </c>
+      <c r="AY31">
         <v>11.5</v>
       </c>
-      <c r="AW31">
-        <v>2.64</v>
-      </c>
-      <c r="AX31">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AY31">
-        <v>2.34</v>
-      </c>
       <c r="AZ31">
-        <v>2.52</v>
+        <v>15</v>
       </c>
       <c r="BA31">
-        <v>2.72</v>
+        <v>7.6</v>
       </c>
       <c r="BB31">
-        <v>2.58</v>
+        <v>8</v>
       </c>
       <c r="BC31">
-        <v>2.58</v>
+        <v>7.6</v>
       </c>
       <c r="BD31">
-        <v>2.64</v>
+        <v>7.8</v>
       </c>
       <c r="BE31">
-        <v>2.72</v>
+        <v>8.6</v>
       </c>
       <c r="BF31">
-        <v>2.72</v>
+        <v>7.4</v>
       </c>
       <c r="BG31">
-        <v>2.72</v>
+        <v>18</v>
       </c>
       <c r="BH31" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
     </row>
     <row r="32" spans="1:60">
       <c r="A32" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="B32" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C32" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D32" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E32" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="F32">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="G32">
-        <v>1.89</v>
+        <v>1.79</v>
       </c>
       <c r="H32">
         <v>5.2</v>
       </c>
       <c r="I32">
+        <v>5.6</v>
+      </c>
+      <c r="J32">
+        <v>3.9</v>
+      </c>
+      <c r="K32">
+        <v>4.2</v>
+      </c>
+      <c r="L32">
+        <v>1.01</v>
+      </c>
+      <c r="M32">
+        <v>1.06</v>
+      </c>
+      <c r="N32">
+        <v>3.8</v>
+      </c>
+      <c r="O32">
+        <v>1.3</v>
+      </c>
+      <c r="P32">
+        <v>1.96</v>
+      </c>
+      <c r="Q32">
+        <v>1.92</v>
+      </c>
+      <c r="R32">
+        <v>1.37</v>
+      </c>
+      <c r="S32">
+        <v>3.25</v>
+      </c>
+      <c r="T32">
+        <v>1.86</v>
+      </c>
+      <c r="U32">
+        <v>2.02</v>
+      </c>
+      <c r="V32">
+        <v>1.21</v>
+      </c>
+      <c r="W32">
+        <v>2.26</v>
+      </c>
+      <c r="X32">
+        <v>19</v>
+      </c>
+      <c r="Y32">
+        <v>19.5</v>
+      </c>
+      <c r="Z32">
+        <v>46</v>
+      </c>
+      <c r="AA32">
+        <v>160</v>
+      </c>
+      <c r="AB32">
+        <v>10.5</v>
+      </c>
+      <c r="AC32">
+        <v>9.4</v>
+      </c>
+      <c r="AD32">
+        <v>22</v>
+      </c>
+      <c r="AE32">
+        <v>80</v>
+      </c>
+      <c r="AF32">
+        <v>11.5</v>
+      </c>
+      <c r="AG32">
+        <v>10.5</v>
+      </c>
+      <c r="AH32">
+        <v>21</v>
+      </c>
+      <c r="AI32">
+        <v>80</v>
+      </c>
+      <c r="AJ32">
+        <v>19</v>
+      </c>
+      <c r="AK32">
+        <v>19.5</v>
+      </c>
+      <c r="AL32">
+        <v>38</v>
+      </c>
+      <c r="AM32">
+        <v>140</v>
+      </c>
+      <c r="AN32">
+        <v>11.5</v>
+      </c>
+      <c r="AO32">
+        <v>100</v>
+      </c>
+      <c r="AP32">
+        <v>13</v>
+      </c>
+      <c r="AQ32">
+        <v>15.5</v>
+      </c>
+      <c r="AR32">
+        <v>6.4</v>
+      </c>
+      <c r="AS32">
         <v>7.2</v>
       </c>
-      <c r="J32">
-        <v>3.45</v>
-      </c>
-      <c r="K32">
-        <v>4.5</v>
-      </c>
-      <c r="L32">
-        <v>1.01</v>
-      </c>
-      <c r="M32">
-        <v>1.01</v>
-      </c>
-      <c r="N32">
-        <v>1.71</v>
-      </c>
-      <c r="O32">
-        <v>1.4</v>
-      </c>
-      <c r="P32">
-        <v>1.71</v>
-      </c>
-      <c r="Q32">
-        <v>2.12</v>
-      </c>
-      <c r="R32">
-        <v>1.2</v>
-      </c>
-      <c r="S32">
-        <v>3.4</v>
-      </c>
-      <c r="T32">
-        <v>1.69</v>
-      </c>
-      <c r="U32">
-        <v>1.57</v>
-      </c>
-      <c r="V32">
-        <v>1.16</v>
-      </c>
-      <c r="W32">
-        <v>2.12</v>
-      </c>
-      <c r="X32">
+      <c r="AT32">
+        <v>7.8</v>
+      </c>
+      <c r="AU32">
+        <v>8</v>
+      </c>
+      <c r="AV32">
         <v>17.5</v>
       </c>
-      <c r="Y32">
-        <v>24</v>
-      </c>
-      <c r="Z32">
-        <v>65</v>
-      </c>
-      <c r="AA32">
-        <v>1000</v>
-      </c>
-      <c r="AB32">
-        <v>10</v>
-      </c>
-      <c r="AC32">
-        <v>12</v>
-      </c>
-      <c r="AD32">
-        <v>34</v>
-      </c>
-      <c r="AE32">
-        <v>1000</v>
-      </c>
-      <c r="AF32">
-        <v>14.5</v>
-      </c>
-      <c r="AG32">
-        <v>15</v>
-      </c>
-      <c r="AH32">
-        <v>34</v>
-      </c>
-      <c r="AI32">
-        <v>1000</v>
-      </c>
-      <c r="AJ32">
-        <v>29</v>
-      </c>
-      <c r="AK32">
-        <v>30</v>
-      </c>
-      <c r="AL32">
-        <v>65</v>
-      </c>
-      <c r="AM32">
-        <v>1000</v>
-      </c>
-      <c r="AN32">
-        <v>1000</v>
-      </c>
-      <c r="AO32">
-        <v>1000</v>
-      </c>
-      <c r="AP32">
-        <v>2.06</v>
-      </c>
-      <c r="AQ32">
-        <v>10</v>
-      </c>
-      <c r="AR32">
-        <v>2.26</v>
-      </c>
-      <c r="AS32">
-        <v>2.34</v>
-      </c>
-      <c r="AT32">
-        <v>1.9</v>
-      </c>
-      <c r="AU32">
-        <v>1.96</v>
-      </c>
-      <c r="AV32">
-        <v>2.2</v>
-      </c>
       <c r="AW32">
-        <v>2.34</v>
+        <v>6.8</v>
       </c>
       <c r="AX32">
-        <v>2.02</v>
+        <v>9</v>
       </c>
       <c r="AY32">
-        <v>2.02</v>
+        <v>9</v>
       </c>
       <c r="AZ32">
-        <v>2.2</v>
+        <v>17</v>
       </c>
       <c r="BA32">
-        <v>2.34</v>
+        <v>6.8</v>
       </c>
       <c r="BB32">
-        <v>2.16</v>
+        <v>15.5</v>
       </c>
       <c r="BC32">
-        <v>2.18</v>
+        <v>15.5</v>
       </c>
       <c r="BD32">
-        <v>2.26</v>
+        <v>6.2</v>
       </c>
       <c r="BE32">
-        <v>2.34</v>
+        <v>7</v>
       </c>
       <c r="BF32">
-        <v>2.34</v>
+        <v>9.4</v>
       </c>
       <c r="BG32">
-        <v>2.34</v>
+        <v>7</v>
       </c>
       <c r="BH32" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
     </row>
     <row r="33" spans="1:60">
       <c r="A33" t="s">
+        <v>74</v>
+      </c>
+      <c r="B33" t="s">
+        <v>90</v>
+      </c>
+      <c r="C33" t="s">
+        <v>103</v>
+      </c>
+      <c r="D33" t="s">
+        <v>149</v>
+      </c>
+      <c r="E33" t="s">
+        <v>207</v>
+      </c>
+      <c r="F33">
+        <v>3.05</v>
+      </c>
+      <c r="G33">
+        <v>3.6</v>
+      </c>
+      <c r="H33">
+        <v>2.4</v>
+      </c>
+      <c r="I33">
+        <v>2.9</v>
+      </c>
+      <c r="J33">
+        <v>3</v>
+      </c>
+      <c r="K33">
+        <v>3.6</v>
+      </c>
+      <c r="L33">
+        <v>1.41</v>
+      </c>
+      <c r="M33">
+        <v>1.09</v>
+      </c>
+      <c r="N33">
+        <v>2.96</v>
+      </c>
+      <c r="O33">
+        <v>1.42</v>
+      </c>
+      <c r="P33">
+        <v>1.64</v>
+      </c>
+      <c r="Q33">
+        <v>2.26</v>
+      </c>
+      <c r="R33">
+        <v>1.24</v>
+      </c>
+      <c r="S33">
+        <v>4.3</v>
+      </c>
+      <c r="T33">
+        <v>1.9</v>
+      </c>
+      <c r="U33">
+        <v>1.89</v>
+      </c>
+      <c r="V33">
+        <v>1.57</v>
+      </c>
+      <c r="W33">
+        <v>1.38</v>
+      </c>
+      <c r="X33">
+        <v>13</v>
+      </c>
+      <c r="Y33">
+        <v>10.5</v>
+      </c>
+      <c r="Z33">
+        <v>19</v>
+      </c>
+      <c r="AA33">
+        <v>46</v>
+      </c>
+      <c r="AB33">
+        <v>13</v>
+      </c>
+      <c r="AC33">
+        <v>9</v>
+      </c>
+      <c r="AD33">
+        <v>14.5</v>
+      </c>
+      <c r="AE33">
+        <v>40</v>
+      </c>
+      <c r="AF33">
+        <v>27</v>
+      </c>
+      <c r="AG33">
+        <v>17.5</v>
+      </c>
+      <c r="AH33">
+        <v>25</v>
+      </c>
+      <c r="AI33">
+        <v>65</v>
+      </c>
+      <c r="AJ33">
+        <v>80</v>
+      </c>
+      <c r="AK33">
+        <v>55</v>
+      </c>
+      <c r="AL33">
         <v>75</v>
       </c>
-      <c r="B33" t="s">
-        <v>89</v>
-      </c>
-      <c r="C33" t="s">
-        <v>102</v>
-      </c>
-      <c r="D33" t="s">
-        <v>146</v>
-      </c>
-      <c r="E33" t="s">
-        <v>201</v>
-      </c>
-      <c r="F33">
-        <v>2.16</v>
-      </c>
-      <c r="G33">
-        <v>2.56</v>
-      </c>
-      <c r="H33">
-        <v>3.4</v>
-      </c>
-      <c r="I33">
-        <v>4</v>
-      </c>
-      <c r="J33">
-        <v>3.2</v>
-      </c>
-      <c r="K33">
-        <v>3.75</v>
-      </c>
-      <c r="L33">
-        <v>1.01</v>
-      </c>
-      <c r="M33">
-        <v>1.01</v>
-      </c>
-      <c r="N33">
-        <v>1.71</v>
-      </c>
-      <c r="O33">
-        <v>1.37</v>
-      </c>
-      <c r="P33">
-        <v>1.71</v>
-      </c>
-      <c r="Q33">
-        <v>2.12</v>
-      </c>
-      <c r="R33">
-        <v>1.21</v>
-      </c>
-      <c r="S33">
-        <v>3.4</v>
-      </c>
-      <c r="T33">
-        <v>1.01</v>
-      </c>
-      <c r="U33">
-        <v>1.01</v>
-      </c>
-      <c r="V33">
-        <v>1.33</v>
-      </c>
-      <c r="W33">
-        <v>1.64</v>
-      </c>
-      <c r="X33">
-        <v>1000</v>
-      </c>
-      <c r="Y33">
-        <v>1000</v>
-      </c>
-      <c r="Z33">
-        <v>1000</v>
-      </c>
-      <c r="AA33">
-        <v>1000</v>
-      </c>
-      <c r="AB33">
-        <v>1000</v>
-      </c>
-      <c r="AC33">
-        <v>1000</v>
-      </c>
-      <c r="AD33">
-        <v>1000</v>
-      </c>
-      <c r="AE33">
-        <v>1000</v>
-      </c>
-      <c r="AF33">
-        <v>1000</v>
-      </c>
-      <c r="AG33">
-        <v>1000</v>
-      </c>
-      <c r="AH33">
-        <v>1000</v>
-      </c>
-      <c r="AI33">
-        <v>1000</v>
-      </c>
-      <c r="AJ33">
-        <v>1000</v>
-      </c>
-      <c r="AK33">
-        <v>1000</v>
-      </c>
-      <c r="AL33">
-        <v>1000</v>
-      </c>
       <c r="AM33">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AN33">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AO33">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AP33">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AQ33">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AR33">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AS33">
         <v>1.03</v>
       </c>
       <c r="AT33">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AU33">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="AV33">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW33">
         <v>1.03</v>
       </c>
       <c r="AX33">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="AY33">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AZ33">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="BA33">
         <v>1.03</v>
@@ -7049,48 +7076,48 @@
         <v>1.03</v>
       </c>
       <c r="BF33">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BG33">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BH33" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
     </row>
     <row r="34" spans="1:60">
       <c r="A34" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B34" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C34" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D34" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="E34" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="F34">
-        <v>1.75</v>
+        <v>1.99</v>
       </c>
       <c r="G34">
-        <v>2.08</v>
+        <v>2.66</v>
       </c>
       <c r="H34">
-        <v>3.2</v>
+        <v>2.74</v>
       </c>
       <c r="I34">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="J34">
-        <v>3.6</v>
+        <v>2.56</v>
       </c>
       <c r="K34">
-        <v>5.6</v>
+        <v>110</v>
       </c>
       <c r="L34">
         <v>1.01</v>
@@ -7099,22 +7126,22 @@
         <v>1.04</v>
       </c>
       <c r="N34">
-        <v>3.35</v>
+        <v>2.02</v>
       </c>
       <c r="O34">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P34">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="Q34">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="R34">
-        <v>1.32</v>
+        <v>1.43</v>
       </c>
       <c r="S34">
-        <v>2.66</v>
+        <v>2.38</v>
       </c>
       <c r="T34">
         <v>1.01</v>
@@ -7123,55 +7150,55 @@
         <v>1.01</v>
       </c>
       <c r="V34">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="W34">
-        <v>1.92</v>
+        <v>1.64</v>
       </c>
       <c r="X34">
         <v>1000</v>
       </c>
       <c r="Y34">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="Z34">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AA34">
         <v>1000</v>
       </c>
       <c r="AB34">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AC34">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AD34">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AE34">
         <v>1000</v>
       </c>
       <c r="AF34">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AG34">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AH34">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AI34">
         <v>1000</v>
       </c>
       <c r="AJ34">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AK34">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AL34">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AM34">
         <v>1000</v>
@@ -7195,10 +7222,10 @@
         <v>1.03</v>
       </c>
       <c r="AT34">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="AU34">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="AV34">
         <v>1.03</v>
@@ -7207,10 +7234,10 @@
         <v>1.03</v>
       </c>
       <c r="AX34">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="AY34">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="AZ34">
         <v>1.03</v>
@@ -7237,314 +7264,314 @@
         <v>1.01</v>
       </c>
       <c r="BH34" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
     </row>
     <row r="35" spans="1:60">
       <c r="A35" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B35" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C35" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D35" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="E35" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="F35">
-        <v>1.39</v>
+        <v>1.59</v>
       </c>
       <c r="G35">
-        <v>1.43</v>
+        <v>1.66</v>
       </c>
       <c r="H35">
-        <v>7.2</v>
+        <v>5.6</v>
       </c>
       <c r="I35">
-        <v>9.4</v>
+        <v>6.2</v>
       </c>
       <c r="J35">
-        <v>5.8</v>
+        <v>4.5</v>
       </c>
       <c r="K35">
-        <v>6.6</v>
+        <v>5</v>
       </c>
       <c r="L35">
         <v>1.01</v>
       </c>
       <c r="M35">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N35">
-        <v>8.800000000000001</v>
+        <v>5.5</v>
       </c>
       <c r="O35">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="P35">
-        <v>3.55</v>
+        <v>2.56</v>
       </c>
       <c r="Q35">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="R35">
-        <v>2.06</v>
+        <v>1.62</v>
       </c>
       <c r="S35">
-        <v>1.83</v>
+        <v>2.42</v>
       </c>
       <c r="T35">
         <v>1.58</v>
       </c>
       <c r="U35">
+        <v>2.12</v>
+      </c>
+      <c r="V35">
+        <v>1.19</v>
+      </c>
+      <c r="W35">
         <v>2.5</v>
       </c>
-      <c r="V35">
-        <v>1.12</v>
-      </c>
-      <c r="W35">
-        <v>3.25</v>
-      </c>
       <c r="X35">
+        <v>30</v>
+      </c>
+      <c r="Y35">
+        <v>26</v>
+      </c>
+      <c r="Z35">
+        <v>50</v>
+      </c>
+      <c r="AA35">
+        <v>150</v>
+      </c>
+      <c r="AB35">
+        <v>12</v>
+      </c>
+      <c r="AC35">
+        <v>11.5</v>
+      </c>
+      <c r="AD35">
+        <v>23</v>
+      </c>
+      <c r="AE35">
+        <v>65</v>
+      </c>
+      <c r="AF35">
+        <v>12</v>
+      </c>
+      <c r="AG35">
+        <v>10.5</v>
+      </c>
+      <c r="AH35">
+        <v>18.5</v>
+      </c>
+      <c r="AI35">
         <v>60</v>
       </c>
-      <c r="Y35">
-        <v>55</v>
-      </c>
-      <c r="Z35">
-        <v>95</v>
-      </c>
-      <c r="AA35">
-        <v>230</v>
-      </c>
-      <c r="AB35">
-        <v>21</v>
-      </c>
-      <c r="AC35">
+      <c r="AJ35">
+        <v>16.5</v>
+      </c>
+      <c r="AK35">
+        <v>15.5</v>
+      </c>
+      <c r="AL35">
+        <v>28</v>
+      </c>
+      <c r="AM35">
+        <v>80</v>
+      </c>
+      <c r="AN35">
+        <v>6.6</v>
+      </c>
+      <c r="AO35">
+        <v>60</v>
+      </c>
+      <c r="AP35">
+        <v>8.6</v>
+      </c>
+      <c r="AQ35">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AR35">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AS35">
+        <v>11</v>
+      </c>
+      <c r="AT35">
+        <v>10.5</v>
+      </c>
+      <c r="AU35">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AV35">
         <v>19.5</v>
       </c>
-      <c r="AD35">
-        <v>36</v>
-      </c>
-      <c r="AE35">
-        <v>95</v>
-      </c>
-      <c r="AF35">
-        <v>16.5</v>
-      </c>
-      <c r="AG35">
-        <v>14.5</v>
-      </c>
-      <c r="AH35">
-        <v>25</v>
-      </c>
-      <c r="AI35">
-        <v>75</v>
-      </c>
-      <c r="AJ35">
-        <v>17.5</v>
-      </c>
-      <c r="AK35">
-        <v>16.5</v>
-      </c>
-      <c r="AL35">
-        <v>29</v>
-      </c>
-      <c r="AM35">
-        <v>75</v>
-      </c>
-      <c r="AN35">
-        <v>4.3</v>
-      </c>
-      <c r="AO35">
-        <v>65</v>
-      </c>
-      <c r="AP35">
-        <v>4.3</v>
-      </c>
-      <c r="AQ35">
-        <v>4.3</v>
-      </c>
-      <c r="AR35">
-        <v>4.4</v>
-      </c>
-      <c r="AS35">
-        <v>4.5</v>
-      </c>
-      <c r="AT35">
-        <v>15</v>
-      </c>
-      <c r="AU35">
+      <c r="AW35">
+        <v>10</v>
+      </c>
+      <c r="AX35">
+        <v>10.5</v>
+      </c>
+      <c r="AY35">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ35">
+        <v>16</v>
+      </c>
+      <c r="BA35">
+        <v>10</v>
+      </c>
+      <c r="BB35">
         <v>14</v>
       </c>
-      <c r="AV35">
-        <v>4.1</v>
-      </c>
-      <c r="AW35">
-        <v>4.4</v>
-      </c>
-      <c r="AX35">
-        <v>12</v>
-      </c>
-      <c r="AY35">
+      <c r="BC35">
+        <v>13.5</v>
+      </c>
+      <c r="BD35">
+        <v>8.4</v>
+      </c>
+      <c r="BE35">
+        <v>10.5</v>
+      </c>
+      <c r="BF35">
+        <v>5.2</v>
+      </c>
+      <c r="BG35">
         <v>10</v>
       </c>
-      <c r="AZ35">
-        <v>17.5</v>
-      </c>
-      <c r="BA35">
-        <v>4.3</v>
-      </c>
-      <c r="BB35">
-        <v>12.5</v>
-      </c>
-      <c r="BC35">
-        <v>12</v>
-      </c>
-      <c r="BD35">
-        <v>20</v>
-      </c>
-      <c r="BE35">
-        <v>4.3</v>
-      </c>
-      <c r="BF35">
-        <v>2.96</v>
-      </c>
-      <c r="BG35">
-        <v>4.3</v>
-      </c>
       <c r="BH35" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
     </row>
     <row r="36" spans="1:60">
       <c r="A36" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B36" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C36" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D36" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="E36" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="F36">
-        <v>1.98</v>
+        <v>1.77</v>
       </c>
       <c r="G36">
-        <v>2.66</v>
+        <v>2.08</v>
       </c>
       <c r="H36">
-        <v>2.74</v>
+        <v>3.55</v>
       </c>
       <c r="I36">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="J36">
-        <v>2.56</v>
+        <v>3.6</v>
       </c>
       <c r="K36">
-        <v>110</v>
+        <v>5.5</v>
       </c>
       <c r="L36">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M36">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N36">
-        <v>2.02</v>
+        <v>3.7</v>
       </c>
       <c r="O36">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="P36">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="Q36">
-        <v>1.58</v>
+        <v>1.74</v>
       </c>
       <c r="R36">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="S36">
-        <v>2.38</v>
+        <v>2.92</v>
       </c>
       <c r="T36">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="U36">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="V36">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="W36">
-        <v>1.64</v>
+        <v>1.92</v>
       </c>
       <c r="X36">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Y36">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Z36">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AA36">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AB36">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AC36">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AD36">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE36">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF36">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AG36">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH36">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI36">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ36">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AK36">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AL36">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM36">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN36">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AO36">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AP36">
         <v>1.03</v>
@@ -7559,10 +7586,10 @@
         <v>1.03</v>
       </c>
       <c r="AT36">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AU36">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AV36">
         <v>1.03</v>
@@ -7571,10 +7598,10 @@
         <v>1.03</v>
       </c>
       <c r="AX36">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY36">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AZ36">
         <v>1.03</v>
@@ -7595,13 +7622,13 @@
         <v>1.03</v>
       </c>
       <c r="BF36">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BG36">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BH36" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
     </row>
     <row r="37" spans="1:60">
@@ -7609,34 +7636,34 @@
         <v>78</v>
       </c>
       <c r="B37" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C37" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D37" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="E37" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="F37">
-        <v>1.68</v>
+        <v>2.16</v>
       </c>
       <c r="G37">
-        <v>2.14</v>
+        <v>2.56</v>
       </c>
       <c r="H37">
-        <v>3.85</v>
+        <v>3.4</v>
       </c>
       <c r="I37">
-        <v>6.6</v>
+        <v>4</v>
       </c>
       <c r="J37">
         <v>3.2</v>
       </c>
       <c r="K37">
-        <v>7</v>
+        <v>3.7</v>
       </c>
       <c r="L37">
         <v>1.01</v>
@@ -7645,35 +7672,35 @@
         <v>1.01</v>
       </c>
       <c r="N37">
+        <v>1.7</v>
+      </c>
+      <c r="O37">
+        <v>1.37</v>
+      </c>
+      <c r="P37">
+        <v>1.7</v>
+      </c>
+      <c r="Q37">
+        <v>2.12</v>
+      </c>
+      <c r="R37">
+        <v>1.21</v>
+      </c>
+      <c r="S37">
+        <v>3.4</v>
+      </c>
+      <c r="T37">
+        <v>1.01</v>
+      </c>
+      <c r="U37">
+        <v>1.01</v>
+      </c>
+      <c r="V37">
+        <v>1.33</v>
+      </c>
+      <c r="W37">
         <v>1.64</v>
       </c>
-      <c r="O37">
-        <v>1.35</v>
-      </c>
-      <c r="P37">
-        <v>1.64</v>
-      </c>
-      <c r="Q37">
-        <v>2</v>
-      </c>
-      <c r="R37">
-        <v>1.23</v>
-      </c>
-      <c r="S37">
-        <v>3.15</v>
-      </c>
-      <c r="T37">
-        <v>1.01</v>
-      </c>
-      <c r="U37">
-        <v>1.01</v>
-      </c>
-      <c r="V37">
-        <v>1.17</v>
-      </c>
-      <c r="W37">
-        <v>1.87</v>
-      </c>
       <c r="X37">
         <v>1000</v>
       </c>
@@ -7783,371 +7810,371 @@
         <v>1.01</v>
       </c>
       <c r="BH37" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
     </row>
     <row r="38" spans="1:60">
       <c r="A38" t="s">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="B38" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C38" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D38" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="E38" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="F38">
-        <v>3.05</v>
+        <v>1.7</v>
       </c>
       <c r="G38">
-        <v>3.6</v>
+        <v>1.89</v>
       </c>
       <c r="H38">
+        <v>5.2</v>
+      </c>
+      <c r="I38">
+        <v>6.8</v>
+      </c>
+      <c r="J38">
+        <v>3.55</v>
+      </c>
+      <c r="K38">
+        <v>4.5</v>
+      </c>
+      <c r="L38">
+        <v>1.01</v>
+      </c>
+      <c r="M38">
+        <v>1.01</v>
+      </c>
+      <c r="N38">
+        <v>1.73</v>
+      </c>
+      <c r="O38">
+        <v>1.37</v>
+      </c>
+      <c r="P38">
+        <v>1.73</v>
+      </c>
+      <c r="Q38">
+        <v>2.12</v>
+      </c>
+      <c r="R38">
+        <v>1.22</v>
+      </c>
+      <c r="S38">
+        <v>3.4</v>
+      </c>
+      <c r="T38">
+        <v>1.7</v>
+      </c>
+      <c r="U38">
+        <v>1.57</v>
+      </c>
+      <c r="V38">
+        <v>1.17</v>
+      </c>
+      <c r="W38">
+        <v>2.12</v>
+      </c>
+      <c r="X38">
+        <v>17</v>
+      </c>
+      <c r="Y38">
+        <v>23</v>
+      </c>
+      <c r="Z38">
+        <v>65</v>
+      </c>
+      <c r="AA38">
+        <v>1000</v>
+      </c>
+      <c r="AB38">
+        <v>10.5</v>
+      </c>
+      <c r="AC38">
+        <v>12</v>
+      </c>
+      <c r="AD38">
+        <v>32</v>
+      </c>
+      <c r="AE38">
+        <v>1000</v>
+      </c>
+      <c r="AF38">
+        <v>14.5</v>
+      </c>
+      <c r="AG38">
+        <v>15</v>
+      </c>
+      <c r="AH38">
+        <v>32</v>
+      </c>
+      <c r="AI38">
+        <v>1000</v>
+      </c>
+      <c r="AJ38">
+        <v>28</v>
+      </c>
+      <c r="AK38">
+        <v>30</v>
+      </c>
+      <c r="AL38">
+        <v>65</v>
+      </c>
+      <c r="AM38">
+        <v>1000</v>
+      </c>
+      <c r="AN38">
+        <v>1000</v>
+      </c>
+      <c r="AO38">
+        <v>1000</v>
+      </c>
+      <c r="AP38">
+        <v>2.08</v>
+      </c>
+      <c r="AQ38">
+        <v>10.5</v>
+      </c>
+      <c r="AR38">
+        <v>2.28</v>
+      </c>
+      <c r="AS38">
         <v>2.36</v>
       </c>
-      <c r="I38">
-        <v>2.78</v>
-      </c>
-      <c r="J38">
-        <v>3</v>
-      </c>
-      <c r="K38">
-        <v>3.6</v>
-      </c>
-      <c r="L38">
-        <v>1.41</v>
-      </c>
-      <c r="M38">
-        <v>1.09</v>
-      </c>
-      <c r="N38">
-        <v>2.94</v>
-      </c>
-      <c r="O38">
-        <v>1.42</v>
-      </c>
-      <c r="P38">
-        <v>1.65</v>
-      </c>
-      <c r="Q38">
-        <v>2.22</v>
-      </c>
-      <c r="R38">
-        <v>1.24</v>
-      </c>
-      <c r="S38">
-        <v>3.85</v>
-      </c>
-      <c r="T38">
-        <v>1.77</v>
-      </c>
-      <c r="U38">
-        <v>1.76</v>
-      </c>
-      <c r="V38">
-        <v>1.57</v>
-      </c>
-      <c r="W38">
-        <v>1.38</v>
-      </c>
-      <c r="X38">
-        <v>13</v>
-      </c>
-      <c r="Y38">
-        <v>10.5</v>
-      </c>
-      <c r="Z38">
-        <v>19</v>
-      </c>
-      <c r="AA38">
-        <v>46</v>
-      </c>
-      <c r="AB38">
-        <v>13</v>
-      </c>
-      <c r="AC38">
-        <v>9</v>
-      </c>
-      <c r="AD38">
-        <v>14.5</v>
-      </c>
-      <c r="AE38">
-        <v>40</v>
-      </c>
-      <c r="AF38">
-        <v>27</v>
-      </c>
-      <c r="AG38">
-        <v>17.5</v>
-      </c>
-      <c r="AH38">
-        <v>25</v>
-      </c>
-      <c r="AI38">
-        <v>65</v>
-      </c>
-      <c r="AJ38">
-        <v>80</v>
-      </c>
-      <c r="AK38">
-        <v>55</v>
-      </c>
-      <c r="AL38">
-        <v>75</v>
-      </c>
-      <c r="AM38">
-        <v>170</v>
-      </c>
-      <c r="AN38">
-        <v>65</v>
-      </c>
-      <c r="AO38">
-        <v>38</v>
-      </c>
-      <c r="AP38">
-        <v>8</v>
-      </c>
-      <c r="AQ38">
-        <v>6.4</v>
-      </c>
-      <c r="AR38">
-        <v>11</v>
-      </c>
-      <c r="AS38">
-        <v>1.03</v>
-      </c>
       <c r="AT38">
-        <v>7.8</v>
+        <v>1.93</v>
       </c>
       <c r="AU38">
-        <v>5.6</v>
+        <v>1.98</v>
       </c>
       <c r="AV38">
-        <v>8.800000000000001</v>
+        <v>15.5</v>
       </c>
       <c r="AW38">
-        <v>1.03</v>
+        <v>2.36</v>
       </c>
       <c r="AX38">
-        <v>15.5</v>
+        <v>2.04</v>
       </c>
       <c r="AY38">
-        <v>10.5</v>
+        <v>2.04</v>
       </c>
       <c r="AZ38">
-        <v>14.5</v>
+        <v>2.2</v>
       </c>
       <c r="BA38">
-        <v>1.03</v>
+        <v>2.36</v>
       </c>
       <c r="BB38">
-        <v>1.03</v>
+        <v>2.18</v>
       </c>
       <c r="BC38">
-        <v>1.03</v>
+        <v>2.2</v>
       </c>
       <c r="BD38">
-        <v>1.03</v>
+        <v>2.28</v>
       </c>
       <c r="BE38">
-        <v>1.03</v>
+        <v>2.36</v>
       </c>
       <c r="BF38">
-        <v>36</v>
+        <v>2.36</v>
       </c>
       <c r="BG38">
-        <v>22</v>
+        <v>2.36</v>
       </c>
       <c r="BH38" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
     </row>
     <row r="39" spans="1:60">
       <c r="A39" t="s">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="B39" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C39" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D39" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="E39" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="F39">
-        <v>1.74</v>
+        <v>2.34</v>
       </c>
       <c r="G39">
-        <v>1.79</v>
+        <v>2.74</v>
       </c>
       <c r="H39">
-        <v>5.2</v>
+        <v>3.5</v>
       </c>
       <c r="I39">
-        <v>5.6</v>
+        <v>4.5</v>
       </c>
       <c r="J39">
-        <v>3.9</v>
+        <v>2.7</v>
       </c>
       <c r="K39">
-        <v>4.2</v>
+        <v>3.35</v>
       </c>
       <c r="L39">
         <v>1.01</v>
       </c>
       <c r="M39">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="N39">
-        <v>3.8</v>
+        <v>1.54</v>
       </c>
       <c r="O39">
-        <v>1.3</v>
+        <v>1.02</v>
       </c>
       <c r="P39">
-        <v>1.95</v>
+        <v>1.54</v>
       </c>
       <c r="Q39">
-        <v>1.92</v>
+        <v>2.56</v>
       </c>
       <c r="R39">
-        <v>1.36</v>
+        <v>1.14</v>
       </c>
       <c r="S39">
-        <v>3.25</v>
+        <v>4.4</v>
       </c>
       <c r="T39">
-        <v>1.86</v>
+        <v>1.78</v>
       </c>
       <c r="U39">
-        <v>2.02</v>
+        <v>1.57</v>
       </c>
       <c r="V39">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="W39">
-        <v>2.26</v>
+        <v>1.57</v>
       </c>
       <c r="X39">
+        <v>11</v>
+      </c>
+      <c r="Y39">
+        <v>14.5</v>
+      </c>
+      <c r="Z39">
+        <v>34</v>
+      </c>
+      <c r="AA39">
+        <v>1000</v>
+      </c>
+      <c r="AB39">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC39">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD39">
+        <v>23</v>
+      </c>
+      <c r="AE39">
+        <v>85</v>
+      </c>
+      <c r="AF39">
         <v>19</v>
       </c>
-      <c r="Y39">
-        <v>19.5</v>
-      </c>
-      <c r="Z39">
-        <v>46</v>
-      </c>
-      <c r="AA39">
-        <v>170</v>
-      </c>
-      <c r="AB39">
-        <v>10.5</v>
-      </c>
-      <c r="AC39">
-        <v>9.4</v>
-      </c>
-      <c r="AD39">
-        <v>22</v>
-      </c>
-      <c r="AE39">
-        <v>80</v>
-      </c>
-      <c r="AF39">
+      <c r="AG39">
+        <v>17</v>
+      </c>
+      <c r="AH39">
+        <v>32</v>
+      </c>
+      <c r="AI39">
+        <v>1000</v>
+      </c>
+      <c r="AJ39">
+        <v>50</v>
+      </c>
+      <c r="AK39">
+        <v>48</v>
+      </c>
+      <c r="AL39">
+        <v>85</v>
+      </c>
+      <c r="AM39">
+        <v>1000</v>
+      </c>
+      <c r="AN39">
+        <v>1000</v>
+      </c>
+      <c r="AO39">
+        <v>1000</v>
+      </c>
+      <c r="AP39">
+        <v>2.22</v>
+      </c>
+      <c r="AQ39">
+        <v>2.34</v>
+      </c>
+      <c r="AR39">
+        <v>16</v>
+      </c>
+      <c r="AS39">
+        <v>2.8</v>
+      </c>
+      <c r="AT39">
+        <v>2.18</v>
+      </c>
+      <c r="AU39">
+        <v>2.18</v>
+      </c>
+      <c r="AV39">
         <v>11.5</v>
       </c>
-      <c r="AG39">
-        <v>10.5</v>
-      </c>
-      <c r="AH39">
-        <v>21</v>
-      </c>
-      <c r="AI39">
-        <v>80</v>
-      </c>
-      <c r="AJ39">
-        <v>19</v>
-      </c>
-      <c r="AK39">
-        <v>19.5</v>
-      </c>
-      <c r="AL39">
-        <v>38</v>
-      </c>
-      <c r="AM39">
-        <v>140</v>
-      </c>
-      <c r="AN39">
-        <v>11.5</v>
-      </c>
-      <c r="AO39">
-        <v>110</v>
-      </c>
-      <c r="AP39">
-        <v>13</v>
-      </c>
-      <c r="AQ39">
-        <v>15.5</v>
-      </c>
-      <c r="AR39">
-        <v>6.4</v>
-      </c>
-      <c r="AS39">
-        <v>7</v>
-      </c>
-      <c r="AT39">
-        <v>7.6</v>
-      </c>
-      <c r="AU39">
-        <v>8</v>
-      </c>
-      <c r="AV39">
-        <v>17.5</v>
-      </c>
       <c r="AW39">
-        <v>6.8</v>
+        <v>2.7</v>
       </c>
       <c r="AX39">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY39">
-        <v>9</v>
+        <v>2.4</v>
       </c>
       <c r="AZ39">
-        <v>17</v>
+        <v>2.58</v>
       </c>
       <c r="BA39">
-        <v>6.8</v>
+        <v>2.8</v>
       </c>
       <c r="BB39">
-        <v>15.5</v>
+        <v>2.64</v>
       </c>
       <c r="BC39">
-        <v>15.5</v>
+        <v>2.64</v>
       </c>
       <c r="BD39">
-        <v>6.2</v>
+        <v>2.7</v>
       </c>
       <c r="BE39">
-        <v>7</v>
+        <v>2.8</v>
       </c>
       <c r="BF39">
-        <v>9.4</v>
+        <v>2.8</v>
       </c>
       <c r="BG39">
-        <v>7</v>
+        <v>2.8</v>
       </c>
       <c r="BH39" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
     </row>
     <row r="40" spans="1:60">
@@ -8155,181 +8182,181 @@
         <v>79</v>
       </c>
       <c r="B40" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C40" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D40" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="E40" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="F40">
-        <v>3.05</v>
+        <v>1.38</v>
       </c>
       <c r="G40">
-        <v>3.25</v>
+        <v>1.43</v>
       </c>
       <c r="H40">
-        <v>2.48</v>
+        <v>7.4</v>
       </c>
       <c r="I40">
-        <v>2.6</v>
+        <v>9.6</v>
       </c>
       <c r="J40">
-        <v>3.45</v>
+        <v>5.8</v>
       </c>
       <c r="K40">
-        <v>3.6</v>
+        <v>6.6</v>
       </c>
       <c r="L40">
         <v>1.01</v>
       </c>
       <c r="M40">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="N40">
-        <v>3.6</v>
+        <v>9</v>
       </c>
       <c r="O40">
-        <v>1.35</v>
+        <v>1.11</v>
       </c>
       <c r="P40">
-        <v>1.88</v>
+        <v>3.55</v>
       </c>
       <c r="Q40">
-        <v>2.02</v>
+        <v>1.33</v>
       </c>
       <c r="R40">
-        <v>1.34</v>
+        <v>2.06</v>
       </c>
       <c r="S40">
-        <v>3.6</v>
+        <v>1.81</v>
       </c>
       <c r="T40">
-        <v>1.79</v>
+        <v>1.58</v>
       </c>
       <c r="U40">
-        <v>2.14</v>
+        <v>2.5</v>
       </c>
       <c r="V40">
-        <v>1.62</v>
+        <v>1.11</v>
       </c>
       <c r="W40">
-        <v>1.45</v>
+        <v>3.3</v>
       </c>
       <c r="X40">
-        <v>15.5</v>
+        <v>60</v>
       </c>
       <c r="Y40">
-        <v>11</v>
+        <v>55</v>
       </c>
       <c r="Z40">
+        <v>95</v>
+      </c>
+      <c r="AA40">
+        <v>230</v>
+      </c>
+      <c r="AB40">
+        <v>21</v>
+      </c>
+      <c r="AC40">
+        <v>19</v>
+      </c>
+      <c r="AD40">
+        <v>36</v>
+      </c>
+      <c r="AE40">
+        <v>95</v>
+      </c>
+      <c r="AF40">
+        <v>16</v>
+      </c>
+      <c r="AG40">
+        <v>14</v>
+      </c>
+      <c r="AH40">
+        <v>25</v>
+      </c>
+      <c r="AI40">
+        <v>75</v>
+      </c>
+      <c r="AJ40">
+        <v>17</v>
+      </c>
+      <c r="AK40">
+        <v>16.5</v>
+      </c>
+      <c r="AL40">
+        <v>29</v>
+      </c>
+      <c r="AM40">
+        <v>75</v>
+      </c>
+      <c r="AN40">
+        <v>4.3</v>
+      </c>
+      <c r="AO40">
+        <v>65</v>
+      </c>
+      <c r="AP40">
+        <v>4.4</v>
+      </c>
+      <c r="AQ40">
+        <v>4.4</v>
+      </c>
+      <c r="AR40">
+        <v>4.6</v>
+      </c>
+      <c r="AS40">
+        <v>4.7</v>
+      </c>
+      <c r="AT40">
+        <v>15</v>
+      </c>
+      <c r="AU40">
+        <v>14</v>
+      </c>
+      <c r="AV40">
+        <v>4.2</v>
+      </c>
+      <c r="AW40">
+        <v>4.6</v>
+      </c>
+      <c r="AX40">
+        <v>12</v>
+      </c>
+      <c r="AY40">
+        <v>10</v>
+      </c>
+      <c r="AZ40">
         <v>17.5</v>
       </c>
-      <c r="AA40">
-        <v>38</v>
-      </c>
-      <c r="AB40">
+      <c r="BA40">
+        <v>4.5</v>
+      </c>
+      <c r="BB40">
         <v>12.5</v>
       </c>
-      <c r="AC40">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD40">
-        <v>12.5</v>
-      </c>
-      <c r="AE40">
-        <v>30</v>
-      </c>
-      <c r="AF40">
-        <v>23</v>
-      </c>
-      <c r="AG40">
-        <v>14.5</v>
-      </c>
-      <c r="AH40">
-        <v>18.5</v>
-      </c>
-      <c r="AI40">
-        <v>44</v>
-      </c>
-      <c r="AJ40">
-        <v>55</v>
-      </c>
-      <c r="AK40">
-        <v>40</v>
-      </c>
-      <c r="AL40">
-        <v>50</v>
-      </c>
-      <c r="AM40">
-        <v>110</v>
-      </c>
-      <c r="AN40">
-        <v>36</v>
-      </c>
-      <c r="AO40">
-        <v>25</v>
-      </c>
-      <c r="AP40">
-        <v>11.5</v>
-      </c>
-      <c r="AQ40">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AR40">
-        <v>14</v>
-      </c>
-      <c r="AS40">
-        <v>6.8</v>
-      </c>
-      <c r="AT40">
-        <v>10.5</v>
-      </c>
-      <c r="AU40">
-        <v>7</v>
-      </c>
-      <c r="AV40">
-        <v>10.5</v>
-      </c>
-      <c r="AW40">
-        <v>6.8</v>
-      </c>
-      <c r="AX40">
-        <v>18</v>
-      </c>
-      <c r="AY40">
-        <v>11.5</v>
-      </c>
-      <c r="AZ40">
-        <v>15</v>
-      </c>
-      <c r="BA40">
-        <v>7</v>
-      </c>
-      <c r="BB40">
-        <v>7.4</v>
-      </c>
       <c r="BC40">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="BD40">
-        <v>7.2</v>
+        <v>20</v>
       </c>
       <c r="BE40">
-        <v>7.8</v>
+        <v>4.5</v>
       </c>
       <c r="BF40">
-        <v>7</v>
+        <v>2.98</v>
       </c>
       <c r="BG40">
-        <v>18</v>
+        <v>4.5</v>
       </c>
       <c r="BH40" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
     </row>
     <row r="41" spans="1:60">
@@ -8337,16 +8364,16 @@
         <v>80</v>
       </c>
       <c r="B41" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C41" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D41" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="E41" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="F41">
         <v>2.26</v>
@@ -8397,7 +8424,7 @@
         <v>1.01</v>
       </c>
       <c r="V41">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W41">
         <v>1.43</v>
@@ -8511,7 +8538,7 @@
         <v>1.01</v>
       </c>
       <c r="BH41" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
     </row>
     <row r="42" spans="1:60">
@@ -8519,19 +8546,19 @@
         <v>63</v>
       </c>
       <c r="B42" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C42" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D42" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="E42" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="F42">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="G42">
         <v>2.74</v>
@@ -8540,13 +8567,13 @@
         <v>3</v>
       </c>
       <c r="I42">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="J42">
         <v>3.25</v>
       </c>
       <c r="K42">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L42">
         <v>1.01</v>
@@ -8555,13 +8582,13 @@
         <v>1.07</v>
       </c>
       <c r="N42">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="O42">
         <v>1.33</v>
       </c>
       <c r="P42">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="Q42">
         <v>1.97</v>
@@ -8570,7 +8597,7 @@
         <v>1.18</v>
       </c>
       <c r="S42">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="T42">
         <v>1.01</v>
@@ -8579,7 +8606,7 @@
         <v>1.01</v>
       </c>
       <c r="V42">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W42">
         <v>1.57</v>
@@ -8693,7 +8720,7 @@
         <v>1.01</v>
       </c>
       <c r="BH42" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
     </row>
     <row r="43" spans="1:60">
@@ -8701,181 +8728,181 @@
         <v>69</v>
       </c>
       <c r="B43" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C43" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D43" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E43" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="F43">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="G43">
-        <v>1.81</v>
+        <v>1.58</v>
       </c>
       <c r="H43">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="I43">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="J43">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="K43">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="L43">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="M43">
         <v>1.03</v>
       </c>
       <c r="N43">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="O43">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="P43">
-        <v>2.46</v>
+        <v>2.74</v>
       </c>
       <c r="Q43">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="R43">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="S43">
-        <v>2.22</v>
+        <v>2.14</v>
       </c>
       <c r="T43">
-        <v>1.46</v>
+        <v>1.62</v>
       </c>
       <c r="U43">
-        <v>1.96</v>
+        <v>2.28</v>
       </c>
       <c r="V43">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="W43">
-        <v>2.26</v>
+        <v>2.74</v>
       </c>
       <c r="X43">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Y43">
         <v>34</v>
       </c>
       <c r="Z43">
+        <v>70</v>
+      </c>
+      <c r="AA43">
+        <v>160</v>
+      </c>
+      <c r="AB43">
+        <v>14</v>
+      </c>
+      <c r="AC43">
+        <v>13.5</v>
+      </c>
+      <c r="AD43">
+        <v>27</v>
+      </c>
+      <c r="AE43">
+        <v>75</v>
+      </c>
+      <c r="AF43">
+        <v>12.5</v>
+      </c>
+      <c r="AG43">
+        <v>11.5</v>
+      </c>
+      <c r="AH43">
+        <v>21</v>
+      </c>
+      <c r="AI43">
         <v>65</v>
       </c>
-      <c r="AA43">
-        <v>1000</v>
-      </c>
-      <c r="AB43">
-        <v>17</v>
-      </c>
-      <c r="AC43">
+      <c r="AJ43">
+        <v>15.5</v>
+      </c>
+      <c r="AK43">
         <v>15</v>
       </c>
-      <c r="AD43">
-        <v>29</v>
-      </c>
-      <c r="AE43">
-        <v>85</v>
-      </c>
-      <c r="AF43">
-        <v>17.5</v>
-      </c>
-      <c r="AG43">
-        <v>14.5</v>
-      </c>
-      <c r="AH43">
-        <v>25</v>
-      </c>
-      <c r="AI43">
-        <v>75</v>
-      </c>
-      <c r="AJ43">
-        <v>24</v>
-      </c>
-      <c r="AK43">
-        <v>22</v>
-      </c>
       <c r="AL43">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="AM43">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AN43">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="AO43">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AP43">
-        <v>2.08</v>
+        <v>6.8</v>
       </c>
       <c r="AQ43">
-        <v>1.96</v>
+        <v>6.8</v>
       </c>
       <c r="AR43">
-        <v>2</v>
+        <v>7.6</v>
       </c>
       <c r="AS43">
-        <v>2.08</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT43">
-        <v>1.85</v>
+        <v>11</v>
       </c>
       <c r="AU43">
-        <v>1.82</v>
+        <v>10.5</v>
       </c>
       <c r="AV43">
-        <v>1.94</v>
+        <v>20</v>
       </c>
       <c r="AW43">
-        <v>2.02</v>
+        <v>7.6</v>
       </c>
       <c r="AX43">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AY43">
-        <v>1.81</v>
+        <v>9</v>
       </c>
       <c r="AZ43">
-        <v>12.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA43">
-        <v>2.02</v>
+        <v>7.6</v>
       </c>
       <c r="BB43">
-        <v>1.91</v>
+        <v>12</v>
       </c>
       <c r="BC43">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BD43">
-        <v>19</v>
+        <v>6.6</v>
       </c>
       <c r="BE43">
-        <v>2.02</v>
+        <v>7.8</v>
       </c>
       <c r="BF43">
-        <v>2.08</v>
+        <v>4.5</v>
       </c>
       <c r="BG43">
-        <v>2.08</v>
+        <v>7.4</v>
       </c>
       <c r="BH43" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
     </row>
     <row r="44" spans="1:60">
@@ -8883,100 +8910,100 @@
         <v>69</v>
       </c>
       <c r="B44" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C44" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D44" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E44" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="F44">
-        <v>1.48</v>
+        <v>1.61</v>
       </c>
       <c r="G44">
-        <v>1.57</v>
+        <v>1.77</v>
       </c>
       <c r="H44">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="I44">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="J44">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="K44">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="L44">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="M44">
         <v>1.03</v>
       </c>
       <c r="N44">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="O44">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="P44">
-        <v>2.74</v>
+        <v>2.46</v>
       </c>
       <c r="Q44">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="R44">
-        <v>1.7</v>
+        <v>1.59</v>
       </c>
       <c r="S44">
-        <v>2.14</v>
+        <v>2.34</v>
       </c>
       <c r="T44">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="U44">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="V44">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="W44">
-        <v>2.74</v>
+        <v>2.3</v>
       </c>
       <c r="X44">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="Y44">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="Z44">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AA44">
-        <v>180</v>
+        <v>130</v>
       </c>
       <c r="AB44">
         <v>14</v>
       </c>
       <c r="AC44">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AD44">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AE44">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AF44">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AG44">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH44">
         <v>21</v>
@@ -8985,99 +9012,99 @@
         <v>65</v>
       </c>
       <c r="AJ44">
+        <v>20</v>
+      </c>
+      <c r="AK44">
+        <v>18.5</v>
+      </c>
+      <c r="AL44">
+        <v>32</v>
+      </c>
+      <c r="AM44">
+        <v>85</v>
+      </c>
+      <c r="AN44">
+        <v>8</v>
+      </c>
+      <c r="AO44">
+        <v>55</v>
+      </c>
+      <c r="AP44">
+        <v>19.5</v>
+      </c>
+      <c r="AQ44">
+        <v>18.5</v>
+      </c>
+      <c r="AR44">
+        <v>34</v>
+      </c>
+      <c r="AS44">
+        <v>5</v>
+      </c>
+      <c r="AT44">
+        <v>9.4</v>
+      </c>
+      <c r="AU44">
+        <v>8.6</v>
+      </c>
+      <c r="AV44">
         <v>15.5</v>
       </c>
-      <c r="AK44">
-        <v>15</v>
-      </c>
-      <c r="AL44">
-        <v>28</v>
-      </c>
-      <c r="AM44">
-        <v>80</v>
-      </c>
-      <c r="AN44">
-        <v>5.3</v>
-      </c>
-      <c r="AO44">
-        <v>75</v>
-      </c>
-      <c r="AP44">
-        <v>7</v>
-      </c>
-      <c r="AQ44">
-        <v>7</v>
-      </c>
-      <c r="AR44">
-        <v>7.8</v>
-      </c>
-      <c r="AS44">
-        <v>8.6</v>
-      </c>
-      <c r="AT44">
-        <v>11</v>
-      </c>
-      <c r="AU44">
-        <v>10.5</v>
-      </c>
-      <c r="AV44">
-        <v>21</v>
-      </c>
       <c r="AW44">
-        <v>8</v>
+        <v>4.8</v>
       </c>
       <c r="AX44">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AY44">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ44">
-        <v>16.5</v>
+        <v>13.5</v>
       </c>
       <c r="BA44">
-        <v>7.8</v>
+        <v>4.8</v>
       </c>
       <c r="BB44">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="BC44">
         <v>12</v>
       </c>
       <c r="BD44">
-        <v>6.8</v>
+        <v>20</v>
       </c>
       <c r="BE44">
-        <v>8</v>
+        <v>4.9</v>
       </c>
       <c r="BF44">
-        <v>4.1</v>
+        <v>5.4</v>
       </c>
       <c r="BG44">
-        <v>7.8</v>
+        <v>4.7</v>
       </c>
       <c r="BH44" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
     </row>
     <row r="45" spans="1:60">
       <c r="A45" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B45" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C45" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D45" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="E45" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="F45">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="G45">
         <v>2.14</v>
@@ -9101,7 +9128,7 @@
         <v>1.06</v>
       </c>
       <c r="N45">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O45">
         <v>1.26</v>
@@ -9140,7 +9167,7 @@
         <v>34</v>
       </c>
       <c r="AA45">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AB45">
         <v>11</v>
@@ -9176,7 +9203,7 @@
         <v>34</v>
       </c>
       <c r="AM45">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AN45">
         <v>13.5</v>
@@ -9185,13 +9212,13 @@
         <v>46</v>
       </c>
       <c r="AP45">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AQ45">
         <v>5.5</v>
       </c>
       <c r="AR45">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AS45">
         <v>7.4</v>
@@ -9206,7 +9233,7 @@
         <v>5.5</v>
       </c>
       <c r="AW45">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AX45">
         <v>11</v>
@@ -9215,7 +9242,7 @@
         <v>9</v>
       </c>
       <c r="AZ45">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BA45">
         <v>7</v>
@@ -9227,7 +9254,7 @@
         <v>5.9</v>
       </c>
       <c r="BD45">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BE45">
         <v>7.4</v>
@@ -9239,7 +9266,7 @@
         <v>6.8</v>
       </c>
       <c r="BH45" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
     </row>
     <row r="46" spans="1:60">
@@ -9247,16 +9274,16 @@
         <v>81</v>
       </c>
       <c r="B46" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C46" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D46" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="E46" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="F46">
         <v>1.48</v>
@@ -9271,7 +9298,7 @@
         <v>7.2</v>
       </c>
       <c r="J46">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="K46">
         <v>5.6</v>
@@ -9292,7 +9319,7 @@
         <v>2.68</v>
       </c>
       <c r="Q46">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="R46">
         <v>1.58</v>
@@ -9349,7 +9376,7 @@
         <v>90</v>
       </c>
       <c r="AJ46">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK46">
         <v>20</v>
@@ -9376,28 +9403,28 @@
         <v>2.06</v>
       </c>
       <c r="AS46">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AT46">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AU46">
         <v>1.88</v>
       </c>
       <c r="AV46">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AW46">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="AX46">
+        <v>1.87</v>
+      </c>
+      <c r="AY46">
         <v>1.86</v>
       </c>
-      <c r="AY46">
-        <v>1.85</v>
-      </c>
       <c r="AZ46">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="BA46">
         <v>2.06</v>
@@ -9412,33 +9439,33 @@
         <v>2</v>
       </c>
       <c r="BE46">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="BF46">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="BG46">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="BH46" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
     </row>
     <row r="47" spans="1:60">
       <c r="A47" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B47" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C47" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D47" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="E47" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="F47">
         <v>1.64</v>
@@ -9447,10 +9474,10 @@
         <v>1.65</v>
       </c>
       <c r="H47">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="I47">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="J47">
         <v>4.4</v>
@@ -9471,16 +9498,16 @@
         <v>1.32</v>
       </c>
       <c r="P47">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q47">
         <v>1.96</v>
       </c>
       <c r="R47">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S47">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="T47">
         <v>1.99</v>
@@ -9489,7 +9516,7 @@
         <v>1.95</v>
       </c>
       <c r="V47">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="W47">
         <v>2.52</v>
@@ -9537,7 +9564,7 @@
         <v>17.5</v>
       </c>
       <c r="AL47">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM47">
         <v>140</v>
@@ -9603,7 +9630,7 @@
         <v>38</v>
       </c>
       <c r="BH47" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
     </row>
     <row r="48" spans="1:60">
@@ -9611,16 +9638,16 @@
         <v>61</v>
       </c>
       <c r="B48" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C48" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D48" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="E48" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="F48">
         <v>7</v>
@@ -9638,7 +9665,7 @@
         <v>5.1</v>
       </c>
       <c r="K48">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="L48">
         <v>1.32</v>
@@ -9647,7 +9674,7 @@
         <v>1.04</v>
       </c>
       <c r="N48">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="O48">
         <v>1.23</v>
@@ -9659,7 +9686,7 @@
         <v>1.67</v>
       </c>
       <c r="R48">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="S48">
         <v>2.72</v>
@@ -9668,7 +9695,7 @@
         <v>1.84</v>
       </c>
       <c r="U48">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="V48">
         <v>2.96</v>
@@ -9695,7 +9722,7 @@
         <v>11</v>
       </c>
       <c r="AD48">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AE48">
         <v>14</v>
@@ -9785,7 +9812,7 @@
         <v>6</v>
       </c>
       <c r="BH48" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
     </row>
     <row r="49" spans="1:60">
@@ -9793,16 +9820,16 @@
         <v>82</v>
       </c>
       <c r="B49" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C49" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D49" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E49" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="F49">
         <v>2.52</v>
@@ -9856,7 +9883,7 @@
         <v>1.48</v>
       </c>
       <c r="W49">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="X49">
         <v>14</v>
@@ -9967,7 +9994,7 @@
         <v>28</v>
       </c>
       <c r="BH49" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
     </row>
     <row r="50" spans="1:60">
@@ -9975,16 +10002,16 @@
         <v>83</v>
       </c>
       <c r="B50" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C50" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D50" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E50" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="F50">
         <v>1.29</v>
@@ -10002,7 +10029,7 @@
         <v>6.4</v>
       </c>
       <c r="K50">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="L50">
         <v>1.01</v>
@@ -10029,10 +10056,10 @@
         <v>2.3</v>
       </c>
       <c r="T50">
-        <v>1.96</v>
+        <v>1.82</v>
       </c>
       <c r="U50">
-        <v>1.91</v>
+        <v>1.79</v>
       </c>
       <c r="V50">
         <v>1.08</v>
@@ -10050,7 +10077,7 @@
         <v>130</v>
       </c>
       <c r="AA50">
-        <v>480</v>
+        <v>440</v>
       </c>
       <c r="AB50">
         <v>11</v>
@@ -10062,7 +10089,7 @@
         <v>42</v>
       </c>
       <c r="AE50">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AF50">
         <v>9</v>
@@ -10074,10 +10101,10 @@
         <v>29</v>
       </c>
       <c r="AI50">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AJ50">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AK50">
         <v>14</v>
@@ -10086,25 +10113,25 @@
         <v>34</v>
       </c>
       <c r="AM50">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AN50">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AO50">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="AP50">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ50">
+        <v>9</v>
+      </c>
+      <c r="AR50">
         <v>10.5</v>
       </c>
-      <c r="AR50">
-        <v>12.5</v>
-      </c>
       <c r="AS50">
-        <v>4.3</v>
+        <v>11</v>
       </c>
       <c r="AT50">
         <v>9.4</v>
@@ -10113,10 +10140,10 @@
         <v>12.5</v>
       </c>
       <c r="AV50">
+        <v>9</v>
+      </c>
+      <c r="AW50">
         <v>10.5</v>
-      </c>
-      <c r="AW50">
-        <v>13</v>
       </c>
       <c r="AX50">
         <v>7.8</v>
@@ -10125,10 +10152,10 @@
         <v>9.6</v>
       </c>
       <c r="AZ50">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BA50">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="BB50">
         <v>8.800000000000001</v>
@@ -10137,19 +10164,19 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BD50">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="BE50">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="BF50">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BG50">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="BH50" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
     </row>
     <row r="51" spans="1:60">
@@ -10157,43 +10184,43 @@
         <v>84</v>
       </c>
       <c r="B51" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C51" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D51" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="E51" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="F51">
         <v>2.38</v>
       </c>
       <c r="G51">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="H51">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="I51">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="J51">
-        <v>2.92</v>
+        <v>2.8</v>
       </c>
       <c r="K51">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="L51">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="M51">
         <v>1.15</v>
       </c>
       <c r="N51">
-        <v>2.28</v>
+        <v>2.18</v>
       </c>
       <c r="O51">
         <v>1.68</v>
@@ -10202,28 +10229,28 @@
         <v>1.44</v>
       </c>
       <c r="Q51">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="R51">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="S51">
         <v>6.8</v>
       </c>
       <c r="T51">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="U51">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="V51">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W51">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="X51">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="Y51">
         <v>9.6</v>
@@ -10253,7 +10280,7 @@
         <v>15</v>
       </c>
       <c r="AH51">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AI51">
         <v>130</v>
@@ -10262,16 +10289,16 @@
         <v>46</v>
       </c>
       <c r="AK51">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AL51">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AM51">
         <v>320</v>
       </c>
       <c r="AN51">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AO51">
         <v>140</v>
@@ -10280,13 +10307,13 @@
         <v>6.2</v>
       </c>
       <c r="AQ51">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AR51">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS51">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AT51">
         <v>5.8</v>
@@ -10298,7 +10325,7 @@
         <v>15</v>
       </c>
       <c r="AW51">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AX51">
         <v>11.5</v>
@@ -10307,31 +10334,31 @@
         <v>11</v>
       </c>
       <c r="AZ51">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BA51">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BB51">
         <v>32</v>
       </c>
       <c r="BC51">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BD51">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BE51">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BF51">
         <v>36</v>
       </c>
       <c r="BG51">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BH51" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
     </row>
     <row r="52" spans="1:60">
@@ -10339,16 +10366,16 @@
         <v>85</v>
       </c>
       <c r="B52" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C52" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D52" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="E52" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="F52">
         <v>1.34</v>
@@ -10513,7 +10540,7 @@
         <v>1.01</v>
       </c>
       <c r="BH52" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
     </row>
     <row r="53" spans="1:60">
@@ -10521,31 +10548,31 @@
         <v>86</v>
       </c>
       <c r="B53" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C53" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D53" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="E53" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="F53">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="G53">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="H53">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="I53">
         <v>6.2</v>
       </c>
       <c r="J53">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K53">
         <v>4.4</v>
@@ -10554,19 +10581,19 @@
         <v>1.01</v>
       </c>
       <c r="M53">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N53">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="O53">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="P53">
         <v>1.78</v>
       </c>
       <c r="Q53">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="R53">
         <v>1.25</v>
@@ -10578,16 +10605,16 @@
         <v>1.88</v>
       </c>
       <c r="U53">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="V53">
         <v>1.2</v>
       </c>
       <c r="W53">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="X53">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="Y53">
         <v>15.5</v>
@@ -10596,19 +10623,19 @@
         <v>44</v>
       </c>
       <c r="AA53">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AB53">
         <v>7.2</v>
       </c>
       <c r="AC53">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD53">
         <v>23</v>
       </c>
       <c r="AE53">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AF53">
         <v>10.5</v>
@@ -10620,7 +10647,7 @@
         <v>24</v>
       </c>
       <c r="AI53">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AJ53">
         <v>21</v>
@@ -10632,70 +10659,70 @@
         <v>60</v>
       </c>
       <c r="AM53">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AN53">
         <v>17</v>
       </c>
       <c r="AO53">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="AP53">
+        <v>4.7</v>
+      </c>
+      <c r="AQ53">
+        <v>4.9</v>
+      </c>
+      <c r="AR53">
+        <v>3.5</v>
+      </c>
+      <c r="AS53">
+        <v>3.75</v>
+      </c>
+      <c r="AT53">
+        <v>3.6</v>
+      </c>
+      <c r="AU53">
+        <v>4.1</v>
+      </c>
+      <c r="AV53">
+        <v>5.5</v>
+      </c>
+      <c r="AW53">
+        <v>3.4</v>
+      </c>
+      <c r="AX53">
+        <v>4.3</v>
+      </c>
+      <c r="AY53">
         <v>4.6</v>
       </c>
-      <c r="AQ53">
-        <v>5.2</v>
-      </c>
-      <c r="AR53">
-        <v>2.76</v>
-      </c>
-      <c r="AS53">
-        <v>2.72</v>
-      </c>
-      <c r="AT53">
-        <v>3.75</v>
-      </c>
-      <c r="AU53">
-        <v>4.4</v>
-      </c>
-      <c r="AV53">
-        <v>5.9</v>
-      </c>
-      <c r="AW53">
-        <v>3.9</v>
-      </c>
-      <c r="AX53">
+      <c r="AZ53">
+        <v>4.1</v>
+      </c>
+      <c r="BA53">
+        <v>4.7</v>
+      </c>
+      <c r="BB53">
+        <v>5.4</v>
+      </c>
+      <c r="BC53">
+        <v>5.5</v>
+      </c>
+      <c r="BD53">
         <v>4.5</v>
       </c>
-      <c r="AY53">
-        <v>4.8</v>
-      </c>
-      <c r="AZ53">
-        <v>4.3</v>
-      </c>
-      <c r="BA53">
-        <v>3.9</v>
-      </c>
-      <c r="BB53">
-        <v>5.8</v>
-      </c>
-      <c r="BC53">
-        <v>5.9</v>
-      </c>
-      <c r="BD53">
-        <v>3.75</v>
-      </c>
       <c r="BE53">
-        <v>2.44</v>
+        <v>3</v>
       </c>
       <c r="BF53">
         <v>12</v>
       </c>
       <c r="BG53">
-        <v>2.72</v>
+        <v>3.45</v>
       </c>
       <c r="BH53" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
     </row>
     <row r="54" spans="1:60">
@@ -10703,28 +10730,28 @@
         <v>87</v>
       </c>
       <c r="B54" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C54" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D54" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="E54" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="F54">
         <v>2.12</v>
       </c>
       <c r="G54">
-        <v>2.34</v>
+        <v>2.52</v>
       </c>
       <c r="H54">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="I54">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="J54">
         <v>3.25</v>
@@ -10748,13 +10775,13 @@
         <v>2</v>
       </c>
       <c r="Q54">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
       <c r="R54">
         <v>1.18</v>
       </c>
       <c r="S54">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
       <c r="T54">
         <v>1.01</v>
@@ -10763,10 +10790,10 @@
         <v>1.01</v>
       </c>
       <c r="V54">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="W54">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="X54">
         <v>1000</v>
@@ -10877,7 +10904,7 @@
         <v>1.01</v>
       </c>
       <c r="BH54" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
     </row>
     <row r="55" spans="1:60">
@@ -10885,16 +10912,16 @@
         <v>84</v>
       </c>
       <c r="B55" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C55" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D55" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="E55" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="F55">
         <v>1.61</v>
@@ -10909,28 +10936,28 @@
         <v>7.8</v>
       </c>
       <c r="J55">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K55">
         <v>4.5</v>
       </c>
       <c r="L55">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="M55">
         <v>1.09</v>
       </c>
       <c r="N55">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="O55">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="P55">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="Q55">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="R55">
         <v>1.23</v>
@@ -10957,7 +10984,7 @@
         <v>21</v>
       </c>
       <c r="Z55">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AA55">
         <v>300</v>
@@ -10999,22 +11026,22 @@
         <v>250</v>
       </c>
       <c r="AN55">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AO55">
         <v>280</v>
       </c>
       <c r="AP55">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AQ55">
         <v>14.5</v>
       </c>
       <c r="AR55">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AS55">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AT55">
         <v>5.6</v>
@@ -11023,22 +11050,22 @@
         <v>7.4</v>
       </c>
       <c r="AV55">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AW55">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AX55">
         <v>7.4</v>
       </c>
       <c r="AY55">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="AZ55">
         <v>4.7</v>
       </c>
       <c r="BA55">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BB55">
         <v>14</v>
@@ -11047,19 +11074,19 @@
         <v>4.5</v>
       </c>
       <c r="BD55">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BE55">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BF55">
         <v>11</v>
       </c>
       <c r="BG55">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BH55" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
     </row>
     <row r="56" spans="1:60">
@@ -11067,16 +11094,16 @@
         <v>88</v>
       </c>
       <c r="B56" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C56" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D56" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="E56" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="F56">
         <v>1.57</v>
@@ -11100,13 +11127,13 @@
         <v>1.01</v>
       </c>
       <c r="M56">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N56">
         <v>1.54</v>
       </c>
       <c r="O56">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="P56">
         <v>1.53</v>
@@ -11241,7 +11268,553 @@
         <v>1.01</v>
       </c>
       <c r="BH56" t="s">
-        <v>225</v>
+        <v>234</v>
+      </c>
+    </row>
+    <row r="57" spans="1:60">
+      <c r="A57" t="s">
+        <v>89</v>
+      </c>
+      <c r="B57" t="s">
+        <v>90</v>
+      </c>
+      <c r="C57" t="s">
+        <v>116</v>
+      </c>
+      <c r="D57" t="s">
+        <v>173</v>
+      </c>
+      <c r="E57" t="s">
+        <v>231</v>
+      </c>
+      <c r="F57">
+        <v>1.04</v>
+      </c>
+      <c r="G57">
+        <v>110</v>
+      </c>
+      <c r="H57">
+        <v>1.04</v>
+      </c>
+      <c r="I57">
+        <v>110</v>
+      </c>
+      <c r="J57">
+        <v>1.03</v>
+      </c>
+      <c r="K57">
+        <v>110</v>
+      </c>
+      <c r="L57">
+        <v>1.01</v>
+      </c>
+      <c r="M57">
+        <v>1.01</v>
+      </c>
+      <c r="N57">
+        <v>1.01</v>
+      </c>
+      <c r="O57">
+        <v>1.13</v>
+      </c>
+      <c r="P57">
+        <v>1.29</v>
+      </c>
+      <c r="Q57">
+        <v>1.13</v>
+      </c>
+      <c r="R57">
+        <v>1.29</v>
+      </c>
+      <c r="S57">
+        <v>1.13</v>
+      </c>
+      <c r="T57">
+        <v>1.01</v>
+      </c>
+      <c r="U57">
+        <v>1.01</v>
+      </c>
+      <c r="V57">
+        <v>1.01</v>
+      </c>
+      <c r="W57">
+        <v>1.01</v>
+      </c>
+      <c r="X57">
+        <v>1000</v>
+      </c>
+      <c r="Y57">
+        <v>1000</v>
+      </c>
+      <c r="Z57">
+        <v>1000</v>
+      </c>
+      <c r="AA57">
+        <v>1000</v>
+      </c>
+      <c r="AB57">
+        <v>1000</v>
+      </c>
+      <c r="AC57">
+        <v>1000</v>
+      </c>
+      <c r="AD57">
+        <v>1000</v>
+      </c>
+      <c r="AE57">
+        <v>1000</v>
+      </c>
+      <c r="AF57">
+        <v>1000</v>
+      </c>
+      <c r="AG57">
+        <v>1000</v>
+      </c>
+      <c r="AH57">
+        <v>1000</v>
+      </c>
+      <c r="AI57">
+        <v>1000</v>
+      </c>
+      <c r="AJ57">
+        <v>1000</v>
+      </c>
+      <c r="AK57">
+        <v>1000</v>
+      </c>
+      <c r="AL57">
+        <v>1000</v>
+      </c>
+      <c r="AM57">
+        <v>1000</v>
+      </c>
+      <c r="AN57">
+        <v>1000</v>
+      </c>
+      <c r="AO57">
+        <v>1000</v>
+      </c>
+      <c r="AP57">
+        <v>1.03</v>
+      </c>
+      <c r="AQ57">
+        <v>1.03</v>
+      </c>
+      <c r="AR57">
+        <v>1.03</v>
+      </c>
+      <c r="AS57">
+        <v>1.03</v>
+      </c>
+      <c r="AT57">
+        <v>1.03</v>
+      </c>
+      <c r="AU57">
+        <v>1.03</v>
+      </c>
+      <c r="AV57">
+        <v>1.03</v>
+      </c>
+      <c r="AW57">
+        <v>1.03</v>
+      </c>
+      <c r="AX57">
+        <v>1.03</v>
+      </c>
+      <c r="AY57">
+        <v>1.03</v>
+      </c>
+      <c r="AZ57">
+        <v>1.03</v>
+      </c>
+      <c r="BA57">
+        <v>1.03</v>
+      </c>
+      <c r="BB57">
+        <v>1.03</v>
+      </c>
+      <c r="BC57">
+        <v>1.03</v>
+      </c>
+      <c r="BD57">
+        <v>1.03</v>
+      </c>
+      <c r="BE57">
+        <v>1.03</v>
+      </c>
+      <c r="BF57">
+        <v>1.01</v>
+      </c>
+      <c r="BG57">
+        <v>1.01</v>
+      </c>
+      <c r="BH57" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="58" spans="1:60">
+      <c r="A58" t="s">
+        <v>84</v>
+      </c>
+      <c r="B58" t="s">
+        <v>90</v>
+      </c>
+      <c r="C58" t="s">
+        <v>117</v>
+      </c>
+      <c r="D58" t="s">
+        <v>174</v>
+      </c>
+      <c r="E58" t="s">
+        <v>232</v>
+      </c>
+      <c r="F58">
+        <v>3.5</v>
+      </c>
+      <c r="G58">
+        <v>4.1</v>
+      </c>
+      <c r="H58">
+        <v>2.42</v>
+      </c>
+      <c r="I58">
+        <v>2.7</v>
+      </c>
+      <c r="J58">
+        <v>2.72</v>
+      </c>
+      <c r="K58">
+        <v>3.15</v>
+      </c>
+      <c r="L58">
+        <v>1.67</v>
+      </c>
+      <c r="M58">
+        <v>1.17</v>
+      </c>
+      <c r="N58">
+        <v>2.06</v>
+      </c>
+      <c r="O58">
+        <v>1.73</v>
+      </c>
+      <c r="P58">
+        <v>1.35</v>
+      </c>
+      <c r="Q58">
+        <v>3.2</v>
+      </c>
+      <c r="R58">
+        <v>1.12</v>
+      </c>
+      <c r="S58">
+        <v>7.2</v>
+      </c>
+      <c r="T58">
+        <v>2.36</v>
+      </c>
+      <c r="U58">
+        <v>1.55</v>
+      </c>
+      <c r="V58">
+        <v>1.58</v>
+      </c>
+      <c r="W58">
+        <v>1.33</v>
+      </c>
+      <c r="X58">
+        <v>7.8</v>
+      </c>
+      <c r="Y58">
+        <v>7.6</v>
+      </c>
+      <c r="Z58">
+        <v>17</v>
+      </c>
+      <c r="AA58">
+        <v>55</v>
+      </c>
+      <c r="AB58">
+        <v>10.5</v>
+      </c>
+      <c r="AC58">
+        <v>8.6</v>
+      </c>
+      <c r="AD58">
+        <v>16.5</v>
+      </c>
+      <c r="AE58">
+        <v>55</v>
+      </c>
+      <c r="AF58">
+        <v>30</v>
+      </c>
+      <c r="AG58">
+        <v>23</v>
+      </c>
+      <c r="AH58">
+        <v>38</v>
+      </c>
+      <c r="AI58">
+        <v>110</v>
+      </c>
+      <c r="AJ58">
+        <v>120</v>
+      </c>
+      <c r="AK58">
+        <v>95</v>
+      </c>
+      <c r="AL58">
+        <v>150</v>
+      </c>
+      <c r="AM58">
+        <v>380</v>
+      </c>
+      <c r="AN58">
+        <v>170</v>
+      </c>
+      <c r="AO58">
+        <v>70</v>
+      </c>
+      <c r="AP58">
+        <v>5.6</v>
+      </c>
+      <c r="AQ58">
+        <v>5.5</v>
+      </c>
+      <c r="AR58">
+        <v>11.5</v>
+      </c>
+      <c r="AS58">
+        <v>4.3</v>
+      </c>
+      <c r="AT58">
+        <v>7.2</v>
+      </c>
+      <c r="AU58">
+        <v>6.2</v>
+      </c>
+      <c r="AV58">
+        <v>11.5</v>
+      </c>
+      <c r="AW58">
+        <v>4.3</v>
+      </c>
+      <c r="AX58">
+        <v>21</v>
+      </c>
+      <c r="AY58">
+        <v>15.5</v>
+      </c>
+      <c r="AZ58">
+        <v>4.1</v>
+      </c>
+      <c r="BA58">
+        <v>4.5</v>
+      </c>
+      <c r="BB58">
+        <v>4.5</v>
+      </c>
+      <c r="BC58">
+        <v>4.4</v>
+      </c>
+      <c r="BD58">
+        <v>4.5</v>
+      </c>
+      <c r="BE58">
+        <v>4.6</v>
+      </c>
+      <c r="BF58">
+        <v>4.5</v>
+      </c>
+      <c r="BG58">
+        <v>4.4</v>
+      </c>
+      <c r="BH58" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="59" spans="1:60">
+      <c r="A59" t="s">
+        <v>87</v>
+      </c>
+      <c r="B59" t="s">
+        <v>90</v>
+      </c>
+      <c r="C59" t="s">
+        <v>117</v>
+      </c>
+      <c r="D59" t="s">
+        <v>175</v>
+      </c>
+      <c r="E59" t="s">
+        <v>233</v>
+      </c>
+      <c r="F59">
+        <v>1.74</v>
+      </c>
+      <c r="G59">
+        <v>2.26</v>
+      </c>
+      <c r="H59">
+        <v>3.6</v>
+      </c>
+      <c r="I59">
+        <v>6.4</v>
+      </c>
+      <c r="J59">
+        <v>2.96</v>
+      </c>
+      <c r="K59">
+        <v>6.8</v>
+      </c>
+      <c r="L59">
+        <v>1.01</v>
+      </c>
+      <c r="M59">
+        <v>1.01</v>
+      </c>
+      <c r="N59">
+        <v>1.56</v>
+      </c>
+      <c r="O59">
+        <v>1.37</v>
+      </c>
+      <c r="P59">
+        <v>1.56</v>
+      </c>
+      <c r="Q59">
+        <v>2.14</v>
+      </c>
+      <c r="R59">
+        <v>1.18</v>
+      </c>
+      <c r="S59">
+        <v>2.14</v>
+      </c>
+      <c r="T59">
+        <v>1.01</v>
+      </c>
+      <c r="U59">
+        <v>1.01</v>
+      </c>
+      <c r="V59">
+        <v>1.18</v>
+      </c>
+      <c r="W59">
+        <v>1.79</v>
+      </c>
+      <c r="X59">
+        <v>1000</v>
+      </c>
+      <c r="Y59">
+        <v>1000</v>
+      </c>
+      <c r="Z59">
+        <v>1000</v>
+      </c>
+      <c r="AA59">
+        <v>1000</v>
+      </c>
+      <c r="AB59">
+        <v>1000</v>
+      </c>
+      <c r="AC59">
+        <v>1000</v>
+      </c>
+      <c r="AD59">
+        <v>1000</v>
+      </c>
+      <c r="AE59">
+        <v>1000</v>
+      </c>
+      <c r="AF59">
+        <v>1000</v>
+      </c>
+      <c r="AG59">
+        <v>1000</v>
+      </c>
+      <c r="AH59">
+        <v>1000</v>
+      </c>
+      <c r="AI59">
+        <v>1000</v>
+      </c>
+      <c r="AJ59">
+        <v>1000</v>
+      </c>
+      <c r="AK59">
+        <v>1000</v>
+      </c>
+      <c r="AL59">
+        <v>1000</v>
+      </c>
+      <c r="AM59">
+        <v>1000</v>
+      </c>
+      <c r="AN59">
+        <v>1000</v>
+      </c>
+      <c r="AO59">
+        <v>1000</v>
+      </c>
+      <c r="AP59">
+        <v>1.03</v>
+      </c>
+      <c r="AQ59">
+        <v>1.03</v>
+      </c>
+      <c r="AR59">
+        <v>1.03</v>
+      </c>
+      <c r="AS59">
+        <v>1.03</v>
+      </c>
+      <c r="AT59">
+        <v>1.03</v>
+      </c>
+      <c r="AU59">
+        <v>1.03</v>
+      </c>
+      <c r="AV59">
+        <v>1.03</v>
+      </c>
+      <c r="AW59">
+        <v>1.03</v>
+      </c>
+      <c r="AX59">
+        <v>1.03</v>
+      </c>
+      <c r="AY59">
+        <v>1.03</v>
+      </c>
+      <c r="AZ59">
+        <v>1.03</v>
+      </c>
+      <c r="BA59">
+        <v>1.03</v>
+      </c>
+      <c r="BB59">
+        <v>1.03</v>
+      </c>
+      <c r="BC59">
+        <v>1.03</v>
+      </c>
+      <c r="BD59">
+        <v>1.03</v>
+      </c>
+      <c r="BE59">
+        <v>1.03</v>
+      </c>
+      <c r="BF59">
+        <v>1.01</v>
+      </c>
+      <c r="BG59">
+        <v>1.01</v>
+      </c>
+      <c r="BH59" t="s">
+        <v>234</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-04.xlsx
@@ -718,7 +718,7 @@
     <t>Deportes Recoleta</t>
   </si>
   <si>
-    <t>2026-05-03 02:41:31</t>
+    <t>2026-05-03 05:10:42</t>
   </si>
 </sst>
 </file>
@@ -1281,19 +1281,19 @@
         <v>1.02</v>
       </c>
       <c r="G2">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H2">
         <v>1.02</v>
       </c>
       <c r="I2">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J2">
         <v>1.02</v>
       </c>
       <c r="K2">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L2">
         <v>1.01</v>
@@ -1463,19 +1463,19 @@
         <v>1.02</v>
       </c>
       <c r="G3">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H3">
         <v>1.02</v>
       </c>
       <c r="I3">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J3">
         <v>1.02</v>
       </c>
       <c r="K3">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L3">
         <v>1.01</v>
@@ -1645,19 +1645,19 @@
         <v>1.02</v>
       </c>
       <c r="G4">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H4">
         <v>1.02</v>
       </c>
       <c r="I4">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J4">
         <v>1.02</v>
       </c>
       <c r="K4">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L4">
         <v>1.01</v>
@@ -1827,19 +1827,19 @@
         <v>1.02</v>
       </c>
       <c r="G5">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H5">
         <v>1.02</v>
       </c>
       <c r="I5">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J5">
         <v>1.02</v>
       </c>
       <c r="K5">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L5">
         <v>1.01</v>
@@ -2009,19 +2009,19 @@
         <v>1.02</v>
       </c>
       <c r="G6">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H6">
         <v>1.02</v>
       </c>
       <c r="I6">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J6">
         <v>1.02</v>
       </c>
       <c r="K6">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L6">
         <v>1.01</v>
@@ -2191,19 +2191,19 @@
         <v>1.02</v>
       </c>
       <c r="G7">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H7">
         <v>1.02</v>
       </c>
       <c r="I7">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J7">
         <v>1.02</v>
       </c>
       <c r="K7">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L7">
         <v>1.01</v>
@@ -2373,19 +2373,19 @@
         <v>1.02</v>
       </c>
       <c r="G8">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H8">
         <v>1.02</v>
       </c>
       <c r="I8">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J8">
         <v>1.02</v>
       </c>
       <c r="K8">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L8">
         <v>1.01</v>
@@ -2558,10 +2558,10 @@
         <v>1.72</v>
       </c>
       <c r="H9">
+        <v>5.3</v>
+      </c>
+      <c r="I9">
         <v>5.4</v>
-      </c>
-      <c r="I9">
-        <v>5.5</v>
       </c>
       <c r="J9">
         <v>4.2</v>
@@ -2597,7 +2597,7 @@
         <v>1.75</v>
       </c>
       <c r="U9">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V9">
         <v>1.22</v>
@@ -2642,7 +2642,7 @@
         <v>60</v>
       </c>
       <c r="AJ9">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AK9">
         <v>16</v>
@@ -2657,7 +2657,7 @@
         <v>8.4</v>
       </c>
       <c r="AO9">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AP9">
         <v>18.5</v>
@@ -2734,22 +2734,22 @@
         <v>184</v>
       </c>
       <c r="F10">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="G10">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="H10">
         <v>2.58</v>
       </c>
       <c r="I10">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="J10">
         <v>2.8</v>
       </c>
       <c r="K10">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="L10">
         <v>1.6</v>
@@ -2764,10 +2764,10 @@
         <v>1.61</v>
       </c>
       <c r="P10">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="Q10">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="R10">
         <v>1.15</v>
@@ -2776,31 +2776,31 @@
         <v>6.2</v>
       </c>
       <c r="T10">
-        <v>2.18</v>
+        <v>2.06</v>
       </c>
       <c r="U10">
         <v>1.68</v>
       </c>
       <c r="V10">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W10">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="X10">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y10">
         <v>8.6</v>
       </c>
       <c r="Z10">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AA10">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AB10">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AC10">
         <v>8</v>
@@ -2821,7 +2821,7 @@
         <v>30</v>
       </c>
       <c r="AI10">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AJ10">
         <v>85</v>
@@ -2836,16 +2836,16 @@
         <v>1000</v>
       </c>
       <c r="AN10">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AO10">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AP10">
         <v>3.2</v>
       </c>
       <c r="AQ10">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AR10">
         <v>12</v>
@@ -2854,10 +2854,10 @@
         <v>4.8</v>
       </c>
       <c r="AT10">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="AU10">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AV10">
         <v>10.5</v>
@@ -2866,31 +2866,31 @@
         <v>4.8</v>
       </c>
       <c r="AX10">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AY10">
         <v>12</v>
       </c>
       <c r="AZ10">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BA10">
         <v>5</v>
       </c>
       <c r="BB10">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BC10">
         <v>4.9</v>
       </c>
       <c r="BD10">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BE10">
+        <v>5.2</v>
+      </c>
+      <c r="BF10">
         <v>5.1</v>
-      </c>
-      <c r="BF10">
-        <v>5</v>
       </c>
       <c r="BG10">
         <v>4.9</v>
@@ -2916,10 +2916,10 @@
         <v>185</v>
       </c>
       <c r="F11">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="G11">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="H11">
         <v>2.06</v>
@@ -2931,7 +2931,7 @@
         <v>3.15</v>
       </c>
       <c r="K11">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="L11">
         <v>1.4</v>
@@ -2955,7 +2955,7 @@
         <v>1.25</v>
       </c>
       <c r="S11">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="T11">
         <v>1.77</v>
@@ -2964,10 +2964,10 @@
         <v>1.76</v>
       </c>
       <c r="V11">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="W11">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="X11">
         <v>13.5</v>
@@ -3215,10 +3215,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AS12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU12">
         <v>7.2</v>
@@ -3227,34 +3227,34 @@
         <v>7.8</v>
       </c>
       <c r="AW12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF12">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BG12">
         <v>9</v>
@@ -3280,118 +3280,118 @@
         <v>187</v>
       </c>
       <c r="F13">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="G13">
-        <v>1.84</v>
+        <v>1.67</v>
       </c>
       <c r="H13">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="I13">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="J13">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="K13">
-        <v>17</v>
+        <v>5.6</v>
       </c>
       <c r="L13">
         <v>1.33</v>
       </c>
       <c r="M13">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N13">
-        <v>1.68</v>
+        <v>1.88</v>
       </c>
       <c r="O13">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="P13">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="Q13">
-        <v>1.84</v>
+        <v>1.77</v>
       </c>
       <c r="R13">
-        <v>1.18</v>
+        <v>1.34</v>
       </c>
       <c r="S13">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="T13">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="U13">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="V13">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="W13">
-        <v>2.18</v>
+        <v>2.5</v>
       </c>
       <c r="X13">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="Y13">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="Z13">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AA13">
-        <v>1000</v>
+        <v>370</v>
       </c>
       <c r="AB13">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AC13">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AD13">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AE13">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AF13">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AG13">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH13">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AI13">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AJ13">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AK13">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AL13">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM13">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AN13">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AO13">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AP13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR13">
         <v>1.03</v>
@@ -3400,37 +3400,37 @@
         <v>1.03</v>
       </c>
       <c r="AT13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW13">
         <v>1.03</v>
       </c>
       <c r="AX13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA13">
         <v>1.03</v>
       </c>
       <c r="BB13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE13">
         <v>1.03</v>
@@ -3465,7 +3465,7 @@
         <v>4.7</v>
       </c>
       <c r="G14">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="H14">
         <v>1.52</v>
@@ -3474,7 +3474,7 @@
         <v>1.83</v>
       </c>
       <c r="J14">
-        <v>3.15</v>
+        <v>4.1</v>
       </c>
       <c r="K14">
         <v>110</v>
@@ -3486,22 +3486,22 @@
         <v>1.04</v>
       </c>
       <c r="N14">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="O14">
         <v>1.18</v>
       </c>
       <c r="P14">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="Q14">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="R14">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S14">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="T14">
         <v>1.01</v>
@@ -3513,7 +3513,7 @@
         <v>2.2</v>
       </c>
       <c r="W14">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X14">
         <v>1000</v>
@@ -3570,52 +3570,52 @@
         <v>1000</v>
       </c>
       <c r="AP14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF14">
         <v>1.01</v>
@@ -3677,7 +3677,7 @@
         <v>1.87</v>
       </c>
       <c r="Q15">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="R15">
         <v>1.32</v>
@@ -3689,7 +3689,7 @@
         <v>2.14</v>
       </c>
       <c r="U15">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="V15">
         <v>1.13</v>
@@ -3841,7 +3841,7 @@
         <v>3.25</v>
       </c>
       <c r="K16">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L16">
         <v>1.01</v>
@@ -4017,7 +4017,7 @@
         <v>1.68</v>
       </c>
       <c r="I17">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="J17">
         <v>3.7</v>
@@ -4026,25 +4026,25 @@
         <v>4.6</v>
       </c>
       <c r="L17">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M17">
         <v>1.01</v>
       </c>
       <c r="N17">
-        <v>1.82</v>
+        <v>1.01</v>
       </c>
       <c r="O17">
         <v>1.31</v>
       </c>
       <c r="P17">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="Q17">
         <v>1.98</v>
       </c>
       <c r="R17">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="S17">
         <v>3.15</v>
@@ -4056,7 +4056,7 @@
         <v>1.01</v>
       </c>
       <c r="V17">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="W17">
         <v>1.16</v>
@@ -4116,52 +4116,52 @@
         <v>1000</v>
       </c>
       <c r="AP17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF17">
         <v>1.01</v>
@@ -4199,10 +4199,10 @@
         <v>1.09</v>
       </c>
       <c r="I18">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="J18">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K18">
         <v>110</v>
@@ -4211,7 +4211,7 @@
         <v>1.01</v>
       </c>
       <c r="M18">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N18">
         <v>1.71</v>
@@ -4223,7 +4223,7 @@
         <v>1.71</v>
       </c>
       <c r="Q18">
-        <v>1.32</v>
+        <v>1.94</v>
       </c>
       <c r="R18">
         <v>1.26</v>
@@ -4298,52 +4298,52 @@
         <v>1000</v>
       </c>
       <c r="AP18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF18">
         <v>1.01</v>
@@ -4384,16 +4384,16 @@
         <v>4.8</v>
       </c>
       <c r="J19">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K19">
-        <v>6.4</v>
+        <v>4.5</v>
       </c>
       <c r="L19">
         <v>1.01</v>
       </c>
       <c r="M19">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N19">
         <v>1.81</v>
@@ -4554,22 +4554,22 @@
         <v>194</v>
       </c>
       <c r="F20">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="G20">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="H20">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="I20">
         <v>3.45</v>
       </c>
       <c r="J20">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K20">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="L20">
         <v>1.01</v>
@@ -4602,10 +4602,10 @@
         <v>1.01</v>
       </c>
       <c r="V20">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W20">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="X20">
         <v>1000</v>
@@ -4739,13 +4739,13 @@
         <v>3.3</v>
       </c>
       <c r="G21">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="H21">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="I21">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="J21">
         <v>3.1</v>
@@ -4766,16 +4766,16 @@
         <v>1.32</v>
       </c>
       <c r="P21">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="Q21">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="R21">
         <v>1.33</v>
       </c>
       <c r="S21">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="T21">
         <v>1.77</v>
@@ -4784,10 +4784,10 @@
         <v>2.1</v>
       </c>
       <c r="V21">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="W21">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="X21">
         <v>17</v>
@@ -4877,22 +4877,22 @@
         <v>13</v>
       </c>
       <c r="BA21">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB21">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC21">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD21">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE21">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF21">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="BG21">
         <v>14</v>
@@ -4918,13 +4918,13 @@
         <v>196</v>
       </c>
       <c r="F22">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="G22">
         <v>3.8</v>
       </c>
       <c r="H22">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="I22">
         <v>2.42</v>
@@ -4942,7 +4942,7 @@
         <v>1.06</v>
       </c>
       <c r="N22">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="O22">
         <v>1.29</v>
@@ -4954,7 +4954,7 @@
         <v>1.84</v>
       </c>
       <c r="R22">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S22">
         <v>3.15</v>
@@ -4981,7 +4981,7 @@
         <v>18.5</v>
       </c>
       <c r="AA22">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AB22">
         <v>17</v>
@@ -5020,64 +5020,64 @@
         <v>110</v>
       </c>
       <c r="AN22">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AO22">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AP22">
         <v>1.03</v>
       </c>
       <c r="AQ22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU22">
         <v>6.2</v>
       </c>
       <c r="AV22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY22">
         <v>1.03</v>
       </c>
       <c r="AZ22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF22">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BG22">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH22" t="s">
         <v>234</v>
@@ -5115,7 +5115,7 @@
         <v>4.7</v>
       </c>
       <c r="K23">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="L23">
         <v>1.01</v>
@@ -5133,13 +5133,13 @@
         <v>2.32</v>
       </c>
       <c r="Q23">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="R23">
         <v>1.52</v>
       </c>
       <c r="S23">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="T23">
         <v>1.85</v>
@@ -5151,7 +5151,7 @@
         <v>1.14</v>
       </c>
       <c r="W23">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="X23">
         <v>27</v>
@@ -5300,7 +5300,7 @@
         <v>5.6</v>
       </c>
       <c r="L24">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="M24">
         <v>1.06</v>
@@ -5330,10 +5330,10 @@
         <v>1.65</v>
       </c>
       <c r="V24">
-        <v>2.52</v>
+        <v>2.66</v>
       </c>
       <c r="W24">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X24">
         <v>18</v>
@@ -5402,7 +5402,7 @@
         <v>9.6</v>
       </c>
       <c r="AT24">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU24">
         <v>7.6</v>
@@ -5411,31 +5411,31 @@
         <v>7.4</v>
       </c>
       <c r="AW24">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX24">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY24">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ24">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA24">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB24">
         <v>1.03</v>
       </c>
       <c r="BC24">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD24">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE24">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF24">
         <v>1.01</v>
@@ -5464,7 +5464,7 @@
         <v>199</v>
       </c>
       <c r="F25">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="G25">
         <v>3.15</v>
@@ -5485,7 +5485,7 @@
         <v>1.01</v>
       </c>
       <c r="M25">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N25">
         <v>1.61</v>
@@ -5497,7 +5497,7 @@
         <v>1.61</v>
       </c>
       <c r="Q25">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="R25">
         <v>1.24</v>
@@ -5572,52 +5572,52 @@
         <v>1000</v>
       </c>
       <c r="AP25">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ25">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR25">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS25">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT25">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU25">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV25">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW25">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX25">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY25">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ25">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA25">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB25">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC25">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD25">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE25">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF25">
         <v>1.01</v>
@@ -5646,10 +5646,10 @@
         <v>200</v>
       </c>
       <c r="F26">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="G26">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="H26">
         <v>3</v>
@@ -5658,7 +5658,7 @@
         <v>3.6</v>
       </c>
       <c r="J26">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K26">
         <v>3.7</v>
@@ -5667,7 +5667,7 @@
         <v>1.01</v>
       </c>
       <c r="M26">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N26">
         <v>3.25</v>
@@ -5676,10 +5676,10 @@
         <v>1.37</v>
       </c>
       <c r="P26">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="Q26">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="R26">
         <v>1.26</v>
@@ -5691,13 +5691,13 @@
         <v>1.55</v>
       </c>
       <c r="U26">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="V26">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W26">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="X26">
         <v>1000</v>
@@ -5724,7 +5724,7 @@
         <v>55</v>
       </c>
       <c r="AF26">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AG26">
         <v>17.5</v>
@@ -5739,7 +5739,7 @@
         <v>55</v>
       </c>
       <c r="AK26">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AL26">
         <v>65</v>
@@ -5757,22 +5757,22 @@
         <v>2.16</v>
       </c>
       <c r="AQ26">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AR26">
         <v>14.5</v>
       </c>
       <c r="AS26">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AT26">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AU26">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AV26">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AW26">
         <v>2.08</v>
@@ -5781,10 +5781,10 @@
         <v>1.98</v>
       </c>
       <c r="AY26">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AZ26">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="BA26">
         <v>2.1</v>
@@ -5796,7 +5796,7 @@
         <v>2.06</v>
       </c>
       <c r="BD26">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="BE26">
         <v>2.16</v>
@@ -5870,7 +5870,7 @@
         <v>4.3</v>
       </c>
       <c r="T27">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="U27">
         <v>2.04</v>
@@ -6010,7 +6010,7 @@
         <v>202</v>
       </c>
       <c r="F28">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="G28">
         <v>2.9</v>
@@ -6034,28 +6034,28 @@
         <v>1.05</v>
       </c>
       <c r="N28">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="O28">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P28">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="Q28">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="R28">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="S28">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="T28">
         <v>1.63</v>
       </c>
       <c r="U28">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="V28">
         <v>1.63</v>
@@ -6195,25 +6195,25 @@
         <v>1.02</v>
       </c>
       <c r="G29">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H29">
         <v>1.02</v>
       </c>
       <c r="I29">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J29">
         <v>1.02</v>
       </c>
       <c r="K29">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="L29">
         <v>1.01</v>
       </c>
       <c r="M29">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N29">
         <v>1.25</v>
@@ -6377,7 +6377,7 @@
         <v>1.69</v>
       </c>
       <c r="G30">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="H30">
         <v>3.85</v>
@@ -6386,7 +6386,7 @@
         <v>6.6</v>
       </c>
       <c r="J30">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="K30">
         <v>6.8</v>
@@ -6395,7 +6395,7 @@
         <v>1.01</v>
       </c>
       <c r="M30">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N30">
         <v>1.64</v>
@@ -6407,7 +6407,7 @@
         <v>1.64</v>
       </c>
       <c r="Q30">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="R30">
         <v>1.23</v>
@@ -6422,7 +6422,7 @@
         <v>1.01</v>
       </c>
       <c r="V30">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W30">
         <v>2</v>
@@ -6586,19 +6586,19 @@
         <v>1.35</v>
       </c>
       <c r="P31">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="Q31">
         <v>2.02</v>
       </c>
       <c r="R31">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S31">
         <v>3.7</v>
       </c>
       <c r="T31">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="U31">
         <v>2.12</v>
@@ -6607,7 +6607,7 @@
         <v>1.62</v>
       </c>
       <c r="W31">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="X31">
         <v>15.5</v>
@@ -6768,19 +6768,19 @@
         <v>1.3</v>
       </c>
       <c r="P32">
-        <v>1.96</v>
+        <v>2.06</v>
       </c>
       <c r="Q32">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="R32">
         <v>1.37</v>
       </c>
       <c r="S32">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="T32">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="U32">
         <v>2.02</v>
@@ -6926,10 +6926,10 @@
         <v>3.6</v>
       </c>
       <c r="H33">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="I33">
-        <v>2.9</v>
+        <v>2.78</v>
       </c>
       <c r="J33">
         <v>3</v>
@@ -6953,7 +6953,7 @@
         <v>1.64</v>
       </c>
       <c r="Q33">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="R33">
         <v>1.24</v>
@@ -6962,10 +6962,10 @@
         <v>4.3</v>
       </c>
       <c r="T33">
-        <v>1.9</v>
+        <v>1.77</v>
       </c>
       <c r="U33">
-        <v>1.89</v>
+        <v>1.76</v>
       </c>
       <c r="V33">
         <v>1.57</v>
@@ -7037,7 +7037,7 @@
         <v>11</v>
       </c>
       <c r="AS33">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT33">
         <v>7.8</v>
@@ -7061,25 +7061,25 @@
         <v>14.5</v>
       </c>
       <c r="BA33">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB33">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC33">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD33">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE33">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF33">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BG33">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BH33" t="s">
         <v>234</v>
@@ -7102,22 +7102,22 @@
         <v>208</v>
       </c>
       <c r="F34">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="G34">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="H34">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="I34">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="J34">
-        <v>2.56</v>
+        <v>3.5</v>
       </c>
       <c r="K34">
-        <v>110</v>
+        <v>4.6</v>
       </c>
       <c r="L34">
         <v>1.01</v>
@@ -7150,7 +7150,7 @@
         <v>1.01</v>
       </c>
       <c r="V34">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W34">
         <v>1.64</v>
@@ -7210,52 +7210,52 @@
         <v>1000</v>
       </c>
       <c r="AP34">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ34">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR34">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS34">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT34">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU34">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV34">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW34">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX34">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY34">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ34">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA34">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB34">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC34">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD34">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE34">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF34">
         <v>1.01</v>
@@ -7287,7 +7287,7 @@
         <v>1.59</v>
       </c>
       <c r="G35">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="H35">
         <v>5.6</v>
@@ -7326,16 +7326,16 @@
         <v>2.42</v>
       </c>
       <c r="T35">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="U35">
-        <v>2.12</v>
+        <v>2.28</v>
       </c>
       <c r="V35">
         <v>1.19</v>
       </c>
       <c r="W35">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="X35">
         <v>30</v>
@@ -7496,7 +7496,7 @@
         <v>1.23</v>
       </c>
       <c r="P36">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="Q36">
         <v>1.74</v>
@@ -7574,16 +7574,16 @@
         <v>65</v>
       </c>
       <c r="AP36">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ36">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR36">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS36">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT36">
         <v>7.2</v>
@@ -7592,10 +7592,10 @@
         <v>7.4</v>
       </c>
       <c r="AV36">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW36">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX36">
         <v>8.800000000000001</v>
@@ -7604,28 +7604,28 @@
         <v>7.4</v>
       </c>
       <c r="AZ36">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA36">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB36">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC36">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD36">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE36">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF36">
         <v>8</v>
       </c>
       <c r="BG36">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BH36" t="s">
         <v>234</v>
@@ -7669,16 +7669,16 @@
         <v>1.01</v>
       </c>
       <c r="M37">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N37">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="O37">
         <v>1.37</v>
       </c>
       <c r="P37">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="Q37">
         <v>2.12</v>
@@ -7830,28 +7830,28 @@
         <v>212</v>
       </c>
       <c r="F38">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="G38">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="H38">
         <v>5.2</v>
       </c>
       <c r="I38">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="J38">
         <v>3.55</v>
       </c>
       <c r="K38">
-        <v>4.5</v>
+        <v>3.95</v>
       </c>
       <c r="L38">
         <v>1.01</v>
       </c>
       <c r="M38">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N38">
         <v>1.73</v>
@@ -7863,7 +7863,7 @@
         <v>1.73</v>
       </c>
       <c r="Q38">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="R38">
         <v>1.22</v>
@@ -7878,13 +7878,13 @@
         <v>1.57</v>
       </c>
       <c r="V38">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W38">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="X38">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="Y38">
         <v>23</v>
@@ -7944,52 +7944,52 @@
         <v>10.5</v>
       </c>
       <c r="AR38">
-        <v>2.28</v>
+        <v>2</v>
       </c>
       <c r="AS38">
-        <v>2.36</v>
+        <v>2.08</v>
       </c>
       <c r="AT38">
-        <v>1.93</v>
+        <v>1.73</v>
       </c>
       <c r="AU38">
-        <v>1.98</v>
+        <v>1.77</v>
       </c>
       <c r="AV38">
         <v>15.5</v>
       </c>
       <c r="AW38">
-        <v>2.36</v>
+        <v>2.08</v>
       </c>
       <c r="AX38">
-        <v>2.04</v>
+        <v>1.82</v>
       </c>
       <c r="AY38">
-        <v>2.04</v>
+        <v>1.82</v>
       </c>
       <c r="AZ38">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="BA38">
-        <v>2.36</v>
+        <v>2.08</v>
       </c>
       <c r="BB38">
-        <v>2.18</v>
+        <v>1.93</v>
       </c>
       <c r="BC38">
-        <v>2.2</v>
+        <v>1.94</v>
       </c>
       <c r="BD38">
-        <v>2.28</v>
+        <v>2</v>
       </c>
       <c r="BE38">
-        <v>2.36</v>
+        <v>2.08</v>
       </c>
       <c r="BF38">
-        <v>2.36</v>
+        <v>2.08</v>
       </c>
       <c r="BG38">
-        <v>2.36</v>
+        <v>2.08</v>
       </c>
       <c r="BH38" t="s">
         <v>234</v>
@@ -8015,16 +8015,16 @@
         <v>2.34</v>
       </c>
       <c r="G39">
-        <v>2.74</v>
+        <v>2.64</v>
       </c>
       <c r="H39">
         <v>3.5</v>
       </c>
       <c r="I39">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="J39">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="K39">
         <v>3.35</v>
@@ -8033,19 +8033,19 @@
         <v>1.01</v>
       </c>
       <c r="M39">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N39">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="O39">
-        <v>1.02</v>
+        <v>1.5</v>
       </c>
       <c r="P39">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="Q39">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="R39">
         <v>1.14</v>
@@ -8060,10 +8060,10 @@
         <v>1.57</v>
       </c>
       <c r="V39">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="W39">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="X39">
         <v>11</v>
@@ -8376,28 +8376,28 @@
         <v>215</v>
       </c>
       <c r="F41">
-        <v>2.26</v>
+        <v>2.5</v>
       </c>
       <c r="G41">
-        <v>3.3</v>
+        <v>2.74</v>
       </c>
       <c r="H41">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="I41">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="J41">
-        <v>2.38</v>
+        <v>3.4</v>
       </c>
       <c r="K41">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="L41">
         <v>1.01</v>
       </c>
       <c r="M41">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N41">
         <v>1.83</v>
@@ -8406,7 +8406,7 @@
         <v>1.26</v>
       </c>
       <c r="P41">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="Q41">
         <v>1.75</v>
@@ -8424,10 +8424,10 @@
         <v>1.01</v>
       </c>
       <c r="V41">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="W41">
-        <v>1.43</v>
+        <v>1.57</v>
       </c>
       <c r="X41">
         <v>1000</v>
@@ -8484,52 +8484,52 @@
         <v>1000</v>
       </c>
       <c r="AP41">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ41">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR41">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS41">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT41">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU41">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV41">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW41">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX41">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY41">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ41">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA41">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB41">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC41">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD41">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE41">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF41">
         <v>1.01</v>
@@ -8561,16 +8561,16 @@
         <v>2.32</v>
       </c>
       <c r="G42">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="H42">
         <v>3</v>
       </c>
       <c r="I42">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="J42">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K42">
         <v>3.8</v>
@@ -8606,10 +8606,10 @@
         <v>1.01</v>
       </c>
       <c r="V42">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W42">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="X42">
         <v>1000</v>
@@ -8666,52 +8666,52 @@
         <v>1000</v>
       </c>
       <c r="AP42">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ42">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR42">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS42">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT42">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU42">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV42">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW42">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX42">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY42">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ42">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA42">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB42">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC42">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD42">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE42">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF42">
         <v>1.01</v>
@@ -8752,7 +8752,7 @@
         <v>7.2</v>
       </c>
       <c r="J43">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="K43">
         <v>5.7</v>
@@ -8779,7 +8779,7 @@
         <v>1.7</v>
       </c>
       <c r="S43">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="T43">
         <v>1.62</v>
@@ -8922,7 +8922,7 @@
         <v>218</v>
       </c>
       <c r="F44">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="G44">
         <v>1.77</v>
@@ -8937,7 +8937,7 @@
         <v>4.2</v>
       </c>
       <c r="K44">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="L44">
         <v>1.25</v>
@@ -8961,19 +8961,19 @@
         <v>1.59</v>
       </c>
       <c r="S44">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="T44">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="U44">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="V44">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="W44">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="X44">
         <v>30</v>
@@ -8982,7 +8982,7 @@
         <v>29</v>
       </c>
       <c r="Z44">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AA44">
         <v>130</v>
@@ -9021,49 +9021,49 @@
         <v>32</v>
       </c>
       <c r="AM44">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AN44">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="AO44">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AP44">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AQ44">
         <v>18.5</v>
       </c>
       <c r="AR44">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AS44">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AT44">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AU44">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV44">
         <v>15.5</v>
       </c>
       <c r="AW44">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="AX44">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AY44">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ44">
         <v>13.5</v>
       </c>
       <c r="BA44">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BB44">
         <v>14.5</v>
@@ -9075,13 +9075,13 @@
         <v>20</v>
       </c>
       <c r="BE44">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BF44">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BG44">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BH44" t="s">
         <v>234</v>
@@ -9107,7 +9107,7 @@
         <v>1.94</v>
       </c>
       <c r="G45">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="H45">
         <v>3.75</v>
@@ -9155,7 +9155,7 @@
         <v>1.28</v>
       </c>
       <c r="W45">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="X45">
         <v>21</v>
@@ -9289,7 +9289,7 @@
         <v>1.48</v>
       </c>
       <c r="G46">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="H46">
         <v>6</v>
@@ -9301,7 +9301,7 @@
         <v>4.9</v>
       </c>
       <c r="K46">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="L46">
         <v>1.01</v>
@@ -9319,7 +9319,7 @@
         <v>2.68</v>
       </c>
       <c r="Q46">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="R46">
         <v>1.58</v>
@@ -9337,7 +9337,7 @@
         <v>1.16</v>
       </c>
       <c r="W46">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="X46">
         <v>40</v>
@@ -9388,64 +9388,64 @@
         <v>100</v>
       </c>
       <c r="AN46">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AO46">
         <v>1000</v>
       </c>
       <c r="AP46">
-        <v>2</v>
+        <v>2.76</v>
       </c>
       <c r="AQ46">
-        <v>2</v>
+        <v>2.76</v>
       </c>
       <c r="AR46">
-        <v>2.06</v>
+        <v>2.88</v>
       </c>
       <c r="AS46">
-        <v>2.12</v>
+        <v>2.98</v>
       </c>
       <c r="AT46">
-        <v>1.89</v>
+        <v>2.54</v>
       </c>
       <c r="AU46">
-        <v>1.88</v>
+        <v>2.52</v>
       </c>
       <c r="AV46">
-        <v>2</v>
+        <v>2.74</v>
       </c>
       <c r="AW46">
-        <v>2.08</v>
+        <v>2.88</v>
       </c>
       <c r="AX46">
-        <v>1.87</v>
+        <v>2.5</v>
       </c>
       <c r="AY46">
-        <v>1.86</v>
+        <v>2.48</v>
       </c>
       <c r="AZ46">
-        <v>1.97</v>
+        <v>2.68</v>
       </c>
       <c r="BA46">
-        <v>2.06</v>
+        <v>2.88</v>
       </c>
       <c r="BB46">
-        <v>1.92</v>
+        <v>2.58</v>
       </c>
       <c r="BC46">
         <v>10</v>
       </c>
       <c r="BD46">
-        <v>2</v>
+        <v>2.76</v>
       </c>
       <c r="BE46">
-        <v>2.08</v>
+        <v>2.88</v>
       </c>
       <c r="BF46">
-        <v>2.12</v>
+        <v>3.8</v>
       </c>
       <c r="BG46">
-        <v>2.12</v>
+        <v>2.98</v>
       </c>
       <c r="BH46" t="s">
         <v>234</v>
@@ -9546,7 +9546,7 @@
         <v>90</v>
       </c>
       <c r="AF47">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AG47">
         <v>9.800000000000001</v>
@@ -9570,7 +9570,7 @@
         <v>140</v>
       </c>
       <c r="AN47">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AO47">
         <v>110</v>
@@ -9650,16 +9650,16 @@
         <v>222</v>
       </c>
       <c r="F48">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="G48">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="H48">
         <v>1.49</v>
       </c>
       <c r="I48">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="J48">
         <v>5.1</v>
@@ -9686,7 +9686,7 @@
         <v>1.67</v>
       </c>
       <c r="R48">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="S48">
         <v>2.72</v>
@@ -9698,10 +9698,10 @@
         <v>2.12</v>
       </c>
       <c r="V48">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="W48">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="X48">
         <v>24</v>
@@ -9722,7 +9722,7 @@
         <v>11</v>
       </c>
       <c r="AD48">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AE48">
         <v>14</v>
@@ -9734,7 +9734,7 @@
         <v>26</v>
       </c>
       <c r="AH48">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI48">
         <v>29</v>
@@ -9797,7 +9797,7 @@
         <v>46</v>
       </c>
       <c r="BC48">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="BD48">
         <v>60</v>
@@ -9844,10 +9844,10 @@
         <v>3.1</v>
       </c>
       <c r="J49">
+        <v>3.55</v>
+      </c>
+      <c r="K49">
         <v>3.6</v>
-      </c>
-      <c r="K49">
-        <v>3.65</v>
       </c>
       <c r="L49">
         <v>1.42</v>
@@ -9868,7 +9868,7 @@
         <v>2.02</v>
       </c>
       <c r="R49">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S49">
         <v>3.6</v>
@@ -9940,13 +9940,13 @@
         <v>32</v>
       </c>
       <c r="AP49">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AQ49">
         <v>11.5</v>
       </c>
       <c r="AR49">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AS49">
         <v>44</v>
@@ -10014,7 +10014,7 @@
         <v>224</v>
       </c>
       <c r="F50">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="G50">
         <v>1.32</v>
@@ -10038,7 +10038,7 @@
         <v>1.03</v>
       </c>
       <c r="N50">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="O50">
         <v>1.18</v>
@@ -10050,16 +10050,16 @@
         <v>1.53</v>
       </c>
       <c r="R50">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="S50">
         <v>2.3</v>
       </c>
       <c r="T50">
-        <v>1.82</v>
+        <v>1.95</v>
       </c>
       <c r="U50">
-        <v>1.79</v>
+        <v>1.92</v>
       </c>
       <c r="V50">
         <v>1.08</v>
@@ -10199,28 +10199,28 @@
         <v>2.38</v>
       </c>
       <c r="G51">
-        <v>2.7</v>
+        <v>2.58</v>
       </c>
       <c r="H51">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="I51">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="J51">
-        <v>2.8</v>
+        <v>2.92</v>
       </c>
       <c r="K51">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L51">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="M51">
         <v>1.15</v>
       </c>
       <c r="N51">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="O51">
         <v>1.68</v>
@@ -10232,7 +10232,7 @@
         <v>3.05</v>
       </c>
       <c r="R51">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="S51">
         <v>6.8</v>
@@ -10241,13 +10241,13 @@
         <v>2.34</v>
       </c>
       <c r="U51">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="V51">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W51">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="X51">
         <v>7.4</v>
@@ -10283,22 +10283,22 @@
         <v>32</v>
       </c>
       <c r="AI51">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AJ51">
         <v>46</v>
       </c>
       <c r="AK51">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AL51">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AM51">
         <v>320</v>
       </c>
       <c r="AN51">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AO51">
         <v>140</v>
@@ -10313,7 +10313,7 @@
         <v>20</v>
       </c>
       <c r="AS51">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AT51">
         <v>5.8</v>
@@ -10325,7 +10325,7 @@
         <v>15</v>
       </c>
       <c r="AW51">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AX51">
         <v>11.5</v>
@@ -10334,28 +10334,28 @@
         <v>11</v>
       </c>
       <c r="AZ51">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BA51">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BB51">
         <v>32</v>
       </c>
       <c r="BC51">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BD51">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BE51">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BF51">
         <v>36</v>
       </c>
       <c r="BG51">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BH51" t="s">
         <v>234</v>
@@ -10560,19 +10560,19 @@
         <v>227</v>
       </c>
       <c r="F53">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="G53">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="H53">
         <v>5</v>
       </c>
       <c r="I53">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="J53">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K53">
         <v>4.4</v>
@@ -10587,13 +10587,13 @@
         <v>3</v>
       </c>
       <c r="O53">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="P53">
         <v>1.78</v>
       </c>
       <c r="Q53">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="R53">
         <v>1.25</v>
@@ -10614,7 +10614,7 @@
         <v>2.04</v>
       </c>
       <c r="X53">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y53">
         <v>15.5</v>
@@ -10671,25 +10671,25 @@
         <v>4.7</v>
       </c>
       <c r="AQ53">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AR53">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="AS53">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AT53">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="AU53">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AV53">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AW53">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="AX53">
         <v>4.3</v>
@@ -10701,19 +10701,19 @@
         <v>4.1</v>
       </c>
       <c r="BA53">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BB53">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BC53">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BD53">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BE53">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BF53">
         <v>12</v>
@@ -10745,13 +10745,13 @@
         <v>2.12</v>
       </c>
       <c r="G54">
-        <v>2.52</v>
+        <v>2.34</v>
       </c>
       <c r="H54">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="I54">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="J54">
         <v>3.25</v>
@@ -10763,7 +10763,7 @@
         <v>1.01</v>
       </c>
       <c r="M54">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N54">
         <v>2</v>
@@ -10790,7 +10790,7 @@
         <v>1.01</v>
       </c>
       <c r="V54">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="W54">
         <v>1.65</v>
@@ -10936,28 +10936,28 @@
         <v>7.8</v>
       </c>
       <c r="J55">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K55">
         <v>4.5</v>
       </c>
       <c r="L55">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="M55">
         <v>1.09</v>
       </c>
       <c r="N55">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="O55">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="P55">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="Q55">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="R55">
         <v>1.23</v>
@@ -10984,7 +10984,7 @@
         <v>21</v>
       </c>
       <c r="Z55">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AA55">
         <v>300</v>
@@ -11032,7 +11032,7 @@
         <v>280</v>
       </c>
       <c r="AP55">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AQ55">
         <v>14.5</v>
@@ -11062,7 +11062,7 @@
         <v>3.85</v>
       </c>
       <c r="AZ55">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BA55">
         <v>5.5</v>
@@ -11071,10 +11071,10 @@
         <v>14</v>
       </c>
       <c r="BC55">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BD55">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BE55">
         <v>5.6</v>
@@ -11109,7 +11109,7 @@
         <v>1.57</v>
       </c>
       <c r="G56">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="H56">
         <v>4.8</v>
@@ -11139,7 +11139,7 @@
         <v>1.53</v>
       </c>
       <c r="Q56">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="R56">
         <v>1.18</v>
@@ -11157,7 +11157,7 @@
         <v>1.13</v>
       </c>
       <c r="W56">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="X56">
         <v>1000</v>
@@ -11288,19 +11288,19 @@
         <v>231</v>
       </c>
       <c r="F57">
-        <v>1.04</v>
+        <v>1.84</v>
       </c>
       <c r="G57">
-        <v>110</v>
+        <v>970</v>
       </c>
       <c r="H57">
-        <v>1.04</v>
+        <v>1.27</v>
       </c>
       <c r="I57">
-        <v>110</v>
+        <v>970</v>
       </c>
       <c r="J57">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="K57">
         <v>110</v>
@@ -11312,13 +11312,13 @@
         <v>1.01</v>
       </c>
       <c r="N57">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="O57">
         <v>1.13</v>
       </c>
       <c r="P57">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Q57">
         <v>1.13</v>
@@ -11336,7 +11336,7 @@
         <v>1.01</v>
       </c>
       <c r="V57">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="W57">
         <v>1.01</v>
@@ -11396,52 +11396,52 @@
         <v>1000</v>
       </c>
       <c r="AP57">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ57">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR57">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS57">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT57">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU57">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV57">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW57">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX57">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY57">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ57">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA57">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB57">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC57">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD57">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE57">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF57">
         <v>1.01</v>
@@ -11473,16 +11473,16 @@
         <v>3.5</v>
       </c>
       <c r="G58">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="H58">
         <v>2.42</v>
       </c>
       <c r="I58">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="J58">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="K58">
         <v>3.15</v>
@@ -11494,19 +11494,19 @@
         <v>1.17</v>
       </c>
       <c r="N58">
-        <v>2.06</v>
+        <v>2.18</v>
       </c>
       <c r="O58">
         <v>1.73</v>
       </c>
       <c r="P58">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="Q58">
         <v>3.2</v>
       </c>
       <c r="R58">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="S58">
         <v>7.2</v>
@@ -11515,10 +11515,10 @@
         <v>2.36</v>
       </c>
       <c r="U58">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="V58">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="W58">
         <v>1.33</v>
@@ -11539,7 +11539,7 @@
         <v>10.5</v>
       </c>
       <c r="AC58">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="AD58">
         <v>16.5</v>
@@ -11578,16 +11578,16 @@
         <v>70</v>
       </c>
       <c r="AP58">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AQ58">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AR58">
         <v>11.5</v>
       </c>
       <c r="AS58">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="AT58">
         <v>7.2</v>
@@ -11599,7 +11599,7 @@
         <v>11.5</v>
       </c>
       <c r="AW58">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="AX58">
         <v>21</v>
@@ -11608,28 +11608,28 @@
         <v>15.5</v>
       </c>
       <c r="AZ58">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BA58">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BB58">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BC58">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BD58">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BE58">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BF58">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BG58">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BH58" t="s">
         <v>234</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-04.xlsx
@@ -718,7 +718,7 @@
     <t>Deportes Recoleta</t>
   </si>
   <si>
-    <t>2026-05-03 05:10:42</t>
+    <t>2026-05-03 07:41:00</t>
   </si>
 </sst>
 </file>
@@ -1311,13 +1311,13 @@
         <v>1.24</v>
       </c>
       <c r="Q2">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="R2">
         <v>1.18</v>
       </c>
       <c r="S2">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="T2">
         <v>1.01</v>
@@ -1493,13 +1493,13 @@
         <v>1.24</v>
       </c>
       <c r="Q3">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="R3">
         <v>1.18</v>
       </c>
       <c r="S3">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="T3">
         <v>1.01</v>
@@ -2552,22 +2552,22 @@
         <v>183</v>
       </c>
       <c r="F9">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="G9">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="H9">
+        <v>5.2</v>
+      </c>
+      <c r="I9">
         <v>5.3</v>
       </c>
-      <c r="I9">
-        <v>5.4</v>
-      </c>
       <c r="J9">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K9">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L9">
         <v>1.34</v>
@@ -2597,16 +2597,16 @@
         <v>1.75</v>
       </c>
       <c r="U9">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="V9">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W9">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="X9">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="Y9">
         <v>22</v>
@@ -2642,7 +2642,7 @@
         <v>60</v>
       </c>
       <c r="AJ9">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AK9">
         <v>16</v>
@@ -2705,13 +2705,13 @@
         <v>27</v>
       </c>
       <c r="BE9">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BF9">
         <v>8</v>
       </c>
       <c r="BG9">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BH9" t="s">
         <v>234</v>
@@ -2740,34 +2740,34 @@
         <v>3.65</v>
       </c>
       <c r="H10">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="I10">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="J10">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="K10">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L10">
         <v>1.6</v>
       </c>
       <c r="M10">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="N10">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="O10">
         <v>1.61</v>
       </c>
       <c r="P10">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="Q10">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="R10">
         <v>1.15</v>
@@ -2776,19 +2776,19 @@
         <v>6.2</v>
       </c>
       <c r="T10">
-        <v>2.06</v>
+        <v>2.18</v>
       </c>
       <c r="U10">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="V10">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W10">
         <v>1.38</v>
       </c>
       <c r="X10">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="Y10">
         <v>8.6</v>
@@ -2797,16 +2797,16 @@
         <v>18.5</v>
       </c>
       <c r="AA10">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AB10">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC10">
         <v>8</v>
       </c>
       <c r="AD10">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="AE10">
         <v>55</v>
@@ -2821,7 +2821,7 @@
         <v>30</v>
       </c>
       <c r="AI10">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AJ10">
         <v>85</v>
@@ -2836,25 +2836,25 @@
         <v>1000</v>
       </c>
       <c r="AN10">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AO10">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AP10">
-        <v>3.2</v>
+        <v>6.4</v>
       </c>
       <c r="AQ10">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AR10">
         <v>12</v>
       </c>
       <c r="AS10">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AT10">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AU10">
         <v>6</v>
@@ -2866,13 +2866,13 @@
         <v>4.8</v>
       </c>
       <c r="AX10">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AY10">
         <v>12</v>
       </c>
       <c r="AZ10">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BA10">
         <v>5</v>
@@ -2884,13 +2884,13 @@
         <v>4.9</v>
       </c>
       <c r="BD10">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BE10">
         <v>5.2</v>
       </c>
       <c r="BF10">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BG10">
         <v>4.9</v>
@@ -2916,19 +2916,19 @@
         <v>185</v>
       </c>
       <c r="F11">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="G11">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="H11">
-        <v>2.06</v>
+        <v>2.32</v>
       </c>
       <c r="I11">
-        <v>2.32</v>
+        <v>2.6</v>
       </c>
       <c r="J11">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="K11">
         <v>3.5</v>
@@ -2943,10 +2943,10 @@
         <v>2.98</v>
       </c>
       <c r="O11">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="P11">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="Q11">
         <v>2.06</v>
@@ -2955,127 +2955,127 @@
         <v>1.25</v>
       </c>
       <c r="S11">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="T11">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="U11">
         <v>1.76</v>
       </c>
       <c r="V11">
-        <v>1.76</v>
+        <v>1.63</v>
       </c>
       <c r="W11">
-        <v>1.28</v>
+        <v>1.39</v>
       </c>
       <c r="X11">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="Y11">
         <v>9.6</v>
       </c>
       <c r="Z11">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="AA11">
         <v>36</v>
       </c>
       <c r="AB11">
-        <v>15.5</v>
+        <v>11.5</v>
       </c>
       <c r="AC11">
         <v>9</v>
       </c>
       <c r="AD11">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AE11">
         <v>34</v>
       </c>
       <c r="AF11">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="AG11">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AH11">
         <v>25</v>
       </c>
       <c r="AI11">
+        <v>60</v>
+      </c>
+      <c r="AJ11">
+        <v>80</v>
+      </c>
+      <c r="AK11">
+        <v>55</v>
+      </c>
+      <c r="AL11">
         <v>70</v>
-      </c>
-      <c r="AJ11">
-        <v>110</v>
-      </c>
-      <c r="AK11">
-        <v>75</v>
-      </c>
-      <c r="AL11">
-        <v>90</v>
       </c>
       <c r="AM11">
         <v>170</v>
       </c>
       <c r="AN11">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="AO11">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AP11">
         <v>8.199999999999999</v>
       </c>
       <c r="AQ11">
-        <v>6</v>
+        <v>3.6</v>
       </c>
       <c r="AR11">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="AS11">
-        <v>3.9</v>
+        <v>5</v>
       </c>
       <c r="AT11">
-        <v>9.199999999999999</v>
+        <v>3.85</v>
       </c>
       <c r="AU11">
         <v>5.7</v>
       </c>
       <c r="AV11">
-        <v>8.199999999999999</v>
+        <v>4</v>
       </c>
       <c r="AW11">
-        <v>3.85</v>
+        <v>19</v>
       </c>
       <c r="AX11">
-        <v>3.9</v>
+        <v>4.7</v>
       </c>
       <c r="AY11">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="AZ11">
         <v>14.5</v>
       </c>
       <c r="BA11">
-        <v>4</v>
+        <v>5.3</v>
       </c>
       <c r="BB11">
-        <v>4.2</v>
+        <v>5.4</v>
       </c>
       <c r="BC11">
-        <v>4.1</v>
+        <v>5.2</v>
       </c>
       <c r="BD11">
-        <v>4.1</v>
+        <v>5.4</v>
       </c>
       <c r="BE11">
-        <v>4.2</v>
+        <v>5.6</v>
       </c>
       <c r="BF11">
-        <v>4.1</v>
+        <v>5.3</v>
       </c>
       <c r="BG11">
-        <v>3.75</v>
+        <v>4.9</v>
       </c>
       <c r="BH11" t="s">
         <v>234</v>
@@ -3152,13 +3152,13 @@
         <v>1.2</v>
       </c>
       <c r="X12">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="Y12">
         <v>9.800000000000001</v>
       </c>
       <c r="Z12">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AA12">
         <v>22</v>
@@ -3170,7 +3170,7 @@
         <v>10</v>
       </c>
       <c r="AD12">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AE12">
         <v>22</v>
@@ -3203,7 +3203,7 @@
         <v>95</v>
       </c>
       <c r="AO12">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="AP12">
         <v>1.03</v>
@@ -3280,82 +3280,82 @@
         <v>187</v>
       </c>
       <c r="F13">
-        <v>1.39</v>
+        <v>1.47</v>
       </c>
       <c r="G13">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="H13">
-        <v>4.5</v>
+        <v>6.2</v>
       </c>
       <c r="I13">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="J13">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K13">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="L13">
         <v>1.33</v>
       </c>
       <c r="M13">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N13">
-        <v>1.88</v>
+        <v>3.1</v>
       </c>
       <c r="O13">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="P13">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="Q13">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="R13">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="S13">
-        <v>1.9</v>
+        <v>3</v>
       </c>
       <c r="T13">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="U13">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="V13">
         <v>1.1</v>
       </c>
       <c r="W13">
-        <v>2.5</v>
+        <v>2.66</v>
       </c>
       <c r="X13">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Y13">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Z13">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AA13">
-        <v>370</v>
+        <v>350</v>
       </c>
       <c r="AB13">
         <v>9</v>
       </c>
       <c r="AC13">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AD13">
         <v>38</v>
       </c>
       <c r="AE13">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AF13">
         <v>10.5</v>
@@ -3364,13 +3364,13 @@
         <v>12.5</v>
       </c>
       <c r="AH13">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AI13">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AJ13">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AK13">
         <v>21</v>
@@ -3382,64 +3382,64 @@
         <v>210</v>
       </c>
       <c r="AN13">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AO13">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="AP13">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AQ13">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AR13">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AS13">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AT13">
-        <v>1.01</v>
+        <v>2.88</v>
       </c>
       <c r="AU13">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="AV13">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AW13">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AX13">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="AY13">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="AZ13">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BA13">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BB13">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="BC13">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BD13">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BE13">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BF13">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="BG13">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BH13" t="s">
         <v>234</v>
@@ -3477,7 +3477,7 @@
         <v>4.1</v>
       </c>
       <c r="K14">
-        <v>110</v>
+        <v>950</v>
       </c>
       <c r="L14">
         <v>1.01</v>
@@ -3826,13 +3826,13 @@
         <v>190</v>
       </c>
       <c r="F16">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="G16">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="H16">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="I16">
         <v>4.4</v>
@@ -3871,13 +3871,13 @@
         <v>1.87</v>
       </c>
       <c r="U16">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="V16">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W16">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="X16">
         <v>12.5</v>
@@ -3931,7 +3931,7 @@
         <v>24</v>
       </c>
       <c r="AO16">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AP16">
         <v>10</v>
@@ -3940,7 +3940,7 @@
         <v>11</v>
       </c>
       <c r="AR16">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AS16">
         <v>8.199999999999999</v>
@@ -3976,7 +3976,7 @@
         <v>21</v>
       </c>
       <c r="BD16">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BE16">
         <v>8.4</v>
@@ -4023,151 +4023,151 @@
         <v>3.7</v>
       </c>
       <c r="K17">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="L17">
         <v>1.38</v>
       </c>
       <c r="M17">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N17">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="O17">
+        <v>1.34</v>
+      </c>
+      <c r="P17">
+        <v>1.83</v>
+      </c>
+      <c r="Q17">
+        <v>2</v>
+      </c>
+      <c r="R17">
         <v>1.31</v>
       </c>
-      <c r="P17">
-        <v>1.84</v>
-      </c>
-      <c r="Q17">
-        <v>1.98</v>
-      </c>
-      <c r="R17">
-        <v>1.27</v>
-      </c>
       <c r="S17">
-        <v>3.15</v>
+        <v>3.65</v>
       </c>
       <c r="T17">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="U17">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="V17">
         <v>2.2</v>
       </c>
       <c r="W17">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="X17">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Y17">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="Z17">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AA17">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AB17">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AC17">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD17">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AE17">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AF17">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AG17">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AH17">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI17">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AJ17">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AK17">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AL17">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AM17">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AN17">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AO17">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AP17">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AQ17">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AR17">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AS17">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AT17">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AU17">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AV17">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW17">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AX17">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AY17">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="AZ17">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BA17">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BB17">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BC17">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BD17">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BE17">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BF17">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BG17">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH17" t="s">
         <v>234</v>
@@ -4205,7 +4205,7 @@
         <v>3.65</v>
       </c>
       <c r="K18">
-        <v>110</v>
+        <v>950</v>
       </c>
       <c r="L18">
         <v>1.01</v>
@@ -4766,16 +4766,16 @@
         <v>1.32</v>
       </c>
       <c r="P21">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="Q21">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="R21">
         <v>1.33</v>
       </c>
       <c r="S21">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="T21">
         <v>1.77</v>
@@ -4784,10 +4784,10 @@
         <v>2.1</v>
       </c>
       <c r="V21">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="W21">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="X21">
         <v>17</v>
@@ -4841,7 +4841,7 @@
         <v>55</v>
       </c>
       <c r="AO21">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AP21">
         <v>10</v>
@@ -4918,7 +4918,7 @@
         <v>196</v>
       </c>
       <c r="F22">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="G22">
         <v>3.8</v>
@@ -4942,13 +4942,13 @@
         <v>1.06</v>
       </c>
       <c r="N22">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="O22">
         <v>1.29</v>
       </c>
       <c r="P22">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="Q22">
         <v>1.84</v>
@@ -4957,13 +4957,13 @@
         <v>1.38</v>
       </c>
       <c r="S22">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="T22">
         <v>1.71</v>
       </c>
       <c r="U22">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V22">
         <v>1.7</v>
@@ -4972,34 +4972,34 @@
         <v>1.36</v>
       </c>
       <c r="X22">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="Y22">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="Z22">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AA22">
         <v>34</v>
       </c>
       <c r="AB22">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AC22">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AD22">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AE22">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AF22">
         <v>30</v>
       </c>
       <c r="AG22">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="AH22">
         <v>21</v>
@@ -5023,61 +5023,61 @@
         <v>40</v>
       </c>
       <c r="AO22">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="AP22">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="AQ22">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AR22">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AS22">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AT22">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AU22">
         <v>6.2</v>
       </c>
       <c r="AV22">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AW22">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AX22">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AY22">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AZ22">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BA22">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BB22">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BC22">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BD22">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BE22">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BF22">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BG22">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BH22" t="s">
         <v>234</v>
@@ -5115,7 +5115,7 @@
         <v>4.7</v>
       </c>
       <c r="K23">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="L23">
         <v>1.01</v>
@@ -5160,7 +5160,7 @@
         <v>34</v>
       </c>
       <c r="Z23">
-        <v>500</v>
+        <v>480</v>
       </c>
       <c r="AA23">
         <v>260</v>
@@ -5181,7 +5181,7 @@
         <v>10.5</v>
       </c>
       <c r="AG23">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH23">
         <v>27</v>
@@ -5223,7 +5223,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AU23">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AV23">
         <v>17.5</v>
@@ -5232,13 +5232,13 @@
         <v>36</v>
       </c>
       <c r="AX23">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY23">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ23">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BA23">
         <v>34</v>
@@ -5256,7 +5256,7 @@
         <v>40</v>
       </c>
       <c r="BF23">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="BG23">
         <v>38</v>
@@ -5285,13 +5285,13 @@
         <v>6.6</v>
       </c>
       <c r="G24">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="H24">
         <v>1.47</v>
       </c>
       <c r="I24">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="J24">
         <v>3.75</v>
@@ -5303,7 +5303,7 @@
         <v>1.33</v>
       </c>
       <c r="M24">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N24">
         <v>3.15</v>
@@ -5312,7 +5312,7 @@
         <v>1.32</v>
       </c>
       <c r="P24">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="Q24">
         <v>1.79</v>
@@ -5330,37 +5330,37 @@
         <v>1.65</v>
       </c>
       <c r="V24">
-        <v>2.66</v>
+        <v>2.56</v>
       </c>
       <c r="W24">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X24">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="Y24">
         <v>8.800000000000001</v>
       </c>
       <c r="Z24">
-        <v>10</v>
+        <v>970</v>
       </c>
       <c r="AA24">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="AB24">
         <v>30</v>
       </c>
       <c r="AC24">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AD24">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AE24">
         <v>21</v>
       </c>
       <c r="AF24">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AG24">
         <v>40</v>
@@ -5378,7 +5378,7 @@
         <v>1000</v>
       </c>
       <c r="AL24">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AM24">
         <v>1000</v>
@@ -5387,7 +5387,7 @@
         <v>1000</v>
       </c>
       <c r="AO24">
-        <v>10.5</v>
+        <v>970</v>
       </c>
       <c r="AP24">
         <v>1.03</v>
@@ -5399,7 +5399,7 @@
         <v>6.2</v>
       </c>
       <c r="AS24">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT24">
         <v>1.01</v>
@@ -5426,7 +5426,7 @@
         <v>1.01</v>
       </c>
       <c r="BB24">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC24">
         <v>1.01</v>
@@ -5479,7 +5479,7 @@
         <v>2.32</v>
       </c>
       <c r="K25">
-        <v>110</v>
+        <v>950</v>
       </c>
       <c r="L25">
         <v>1.01</v>
@@ -5646,7 +5646,7 @@
         <v>200</v>
       </c>
       <c r="F26">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="G26">
         <v>2.78</v>
@@ -5655,7 +5655,7 @@
         <v>3</v>
       </c>
       <c r="I26">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="J26">
         <v>3.25</v>
@@ -5676,10 +5676,10 @@
         <v>1.37</v>
       </c>
       <c r="P26">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="Q26">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="R26">
         <v>1.26</v>
@@ -5694,7 +5694,7 @@
         <v>1.72</v>
       </c>
       <c r="V26">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W26">
         <v>1.56</v>
@@ -5834,7 +5834,7 @@
         <v>3.15</v>
       </c>
       <c r="H27">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="I27">
         <v>2.66</v>
@@ -5852,13 +5852,13 @@
         <v>1.09</v>
       </c>
       <c r="N27">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O27">
         <v>1.41</v>
       </c>
       <c r="P27">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="Q27">
         <v>2.24</v>
@@ -5933,7 +5933,7 @@
         <v>40</v>
       </c>
       <c r="AO27">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AP27">
         <v>10</v>
@@ -5948,7 +5948,7 @@
         <v>34</v>
       </c>
       <c r="AT27">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU27">
         <v>6.8</v>
@@ -6016,10 +6016,10 @@
         <v>2.9</v>
       </c>
       <c r="H28">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="I28">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="J28">
         <v>3.8</v>
@@ -6028,7 +6028,7 @@
         <v>3.9</v>
       </c>
       <c r="L28">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M28">
         <v>1.05</v>
@@ -6043,22 +6043,22 @@
         <v>2.28</v>
       </c>
       <c r="Q28">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="R28">
         <v>1.5</v>
       </c>
       <c r="S28">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="T28">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="U28">
         <v>2.42</v>
       </c>
       <c r="V28">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="W28">
         <v>1.52</v>
@@ -6082,10 +6082,10 @@
         <v>9</v>
       </c>
       <c r="AD28">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AE28">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AF28">
         <v>22</v>
@@ -6106,7 +6106,7 @@
         <v>30</v>
       </c>
       <c r="AL28">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM28">
         <v>70</v>
@@ -6115,7 +6115,7 @@
         <v>22</v>
       </c>
       <c r="AO28">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AP28">
         <v>15.5</v>
@@ -6127,7 +6127,7 @@
         <v>16.5</v>
       </c>
       <c r="AS28">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="AT28">
         <v>12</v>
@@ -6151,25 +6151,25 @@
         <v>14</v>
       </c>
       <c r="BA28">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="BB28">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="BC28">
         <v>25</v>
       </c>
       <c r="BD28">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="BE28">
-        <v>55</v>
+        <v>11.5</v>
       </c>
       <c r="BF28">
-        <v>19</v>
+        <v>8.6</v>
       </c>
       <c r="BG28">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BH28" t="s">
         <v>234</v>
@@ -6207,7 +6207,7 @@
         <v>1.02</v>
       </c>
       <c r="K29">
-        <v>110</v>
+        <v>950</v>
       </c>
       <c r="L29">
         <v>1.01</v>
@@ -6568,7 +6568,7 @@
         <v>2.6</v>
       </c>
       <c r="J31">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="K31">
         <v>3.6</v>
@@ -6586,10 +6586,10 @@
         <v>1.35</v>
       </c>
       <c r="P31">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="Q31">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="R31">
         <v>1.34</v>
@@ -6598,16 +6598,16 @@
         <v>3.7</v>
       </c>
       <c r="T31">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="U31">
         <v>2.12</v>
       </c>
       <c r="V31">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="W31">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="X31">
         <v>15.5</v>
@@ -6685,7 +6685,7 @@
         <v>10.5</v>
       </c>
       <c r="AW31">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="AX31">
         <v>18</v>
@@ -6738,7 +6738,7 @@
         <v>206</v>
       </c>
       <c r="F32">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="G32">
         <v>1.79</v>
@@ -6753,7 +6753,7 @@
         <v>3.9</v>
       </c>
       <c r="K32">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L32">
         <v>1.01</v>
@@ -6771,22 +6771,22 @@
         <v>2.06</v>
       </c>
       <c r="Q32">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="R32">
         <v>1.37</v>
       </c>
       <c r="S32">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="T32">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="U32">
         <v>2.02</v>
       </c>
       <c r="V32">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W32">
         <v>2.26</v>
@@ -6819,7 +6819,7 @@
         <v>11.5</v>
       </c>
       <c r="AG32">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH32">
         <v>21</v>
@@ -6852,10 +6852,10 @@
         <v>15.5</v>
       </c>
       <c r="AR32">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AS32">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AT32">
         <v>7.8</v>
@@ -6867,7 +6867,7 @@
         <v>17.5</v>
       </c>
       <c r="AW32">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AX32">
         <v>9</v>
@@ -6879,7 +6879,7 @@
         <v>17</v>
       </c>
       <c r="BA32">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BB32">
         <v>15.5</v>
@@ -6888,16 +6888,16 @@
         <v>15.5</v>
       </c>
       <c r="BD32">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BE32">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BF32">
         <v>9.4</v>
       </c>
       <c r="BG32">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BH32" t="s">
         <v>234</v>
@@ -6926,7 +6926,7 @@
         <v>3.6</v>
       </c>
       <c r="H33">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="I33">
         <v>2.78</v>
@@ -6950,10 +6950,10 @@
         <v>1.42</v>
       </c>
       <c r="P33">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="Q33">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="R33">
         <v>1.24</v>
@@ -6962,10 +6962,10 @@
         <v>4.3</v>
       </c>
       <c r="T33">
-        <v>1.77</v>
+        <v>1.91</v>
       </c>
       <c r="U33">
-        <v>1.76</v>
+        <v>1.91</v>
       </c>
       <c r="V33">
         <v>1.57</v>
@@ -7284,7 +7284,7 @@
         <v>209</v>
       </c>
       <c r="F35">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="G35">
         <v>1.65</v>
@@ -7296,7 +7296,7 @@
         <v>6.2</v>
       </c>
       <c r="J35">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="K35">
         <v>5</v>
@@ -7395,7 +7395,7 @@
         <v>8.6</v>
       </c>
       <c r="AQ35">
-        <v>8.199999999999999</v>
+        <v>22</v>
       </c>
       <c r="AR35">
         <v>9.800000000000001</v>
@@ -7472,7 +7472,7 @@
         <v>2.08</v>
       </c>
       <c r="H36">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="I36">
         <v>4.5</v>
@@ -7484,40 +7484,40 @@
         <v>5.5</v>
       </c>
       <c r="L36">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="M36">
         <v>1.05</v>
       </c>
       <c r="N36">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="O36">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="P36">
         <v>2.12</v>
       </c>
       <c r="Q36">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="R36">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="S36">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="T36">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="U36">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="V36">
         <v>1.28</v>
       </c>
       <c r="W36">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="X36">
         <v>24</v>
@@ -7529,13 +7529,13 @@
         <v>42</v>
       </c>
       <c r="AA36">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AB36">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="AC36">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="AD36">
         <v>21</v>
@@ -7544,7 +7544,7 @@
         <v>65</v>
       </c>
       <c r="AF36">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="AG36">
         <v>12.5</v>
@@ -7562,13 +7562,13 @@
         <v>23</v>
       </c>
       <c r="AL36">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AM36">
         <v>120</v>
       </c>
       <c r="AN36">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AO36">
         <v>65</v>
@@ -7586,7 +7586,7 @@
         <v>1.01</v>
       </c>
       <c r="AT36">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AU36">
         <v>7.4</v>
@@ -7598,13 +7598,13 @@
         <v>1.01</v>
       </c>
       <c r="AX36">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AY36">
         <v>7.4</v>
       </c>
       <c r="AZ36">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BA36">
         <v>1.01</v>
@@ -7648,7 +7648,7 @@
         <v>211</v>
       </c>
       <c r="F37">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="G37">
         <v>2.56</v>
@@ -7663,7 +7663,7 @@
         <v>3.2</v>
       </c>
       <c r="K37">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L37">
         <v>1.01</v>
@@ -7672,16 +7672,16 @@
         <v>1.06</v>
       </c>
       <c r="N37">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="O37">
         <v>1.37</v>
       </c>
       <c r="P37">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="Q37">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="R37">
         <v>1.21</v>
@@ -7830,7 +7830,7 @@
         <v>212</v>
       </c>
       <c r="F38">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="G38">
         <v>1.87</v>
@@ -7845,7 +7845,7 @@
         <v>3.55</v>
       </c>
       <c r="K38">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L38">
         <v>1.01</v>
@@ -7863,7 +7863,7 @@
         <v>1.73</v>
       </c>
       <c r="Q38">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="R38">
         <v>1.22</v>
@@ -7956,7 +7956,7 @@
         <v>1.77</v>
       </c>
       <c r="AV38">
-        <v>15.5</v>
+        <v>1.95</v>
       </c>
       <c r="AW38">
         <v>2.08</v>
@@ -8015,16 +8015,16 @@
         <v>2.34</v>
       </c>
       <c r="G39">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="H39">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="I39">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="J39">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="K39">
         <v>3.35</v>
@@ -8045,7 +8045,7 @@
         <v>1.52</v>
       </c>
       <c r="Q39">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="R39">
         <v>1.14</v>
@@ -8060,10 +8060,10 @@
         <v>1.57</v>
       </c>
       <c r="V39">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W39">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="X39">
         <v>11</v>
@@ -8194,13 +8194,13 @@
         <v>214</v>
       </c>
       <c r="F40">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="G40">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="H40">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="I40">
         <v>9.6</v>
@@ -8209,7 +8209,7 @@
         <v>5.8</v>
       </c>
       <c r="K40">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="L40">
         <v>1.01</v>
@@ -8218,7 +8218,7 @@
         <v>1.02</v>
       </c>
       <c r="N40">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O40">
         <v>1.11</v>
@@ -8230,13 +8230,13 @@
         <v>1.33</v>
       </c>
       <c r="R40">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="S40">
         <v>1.81</v>
       </c>
       <c r="T40">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="U40">
         <v>2.5</v>
@@ -8245,7 +8245,7 @@
         <v>1.11</v>
       </c>
       <c r="W40">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="X40">
         <v>60</v>
@@ -8287,7 +8287,7 @@
         <v>17</v>
       </c>
       <c r="AK40">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AL40">
         <v>29</v>
@@ -8296,22 +8296,22 @@
         <v>75</v>
       </c>
       <c r="AN40">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AO40">
         <v>65</v>
       </c>
       <c r="AP40">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AQ40">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AR40">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AS40">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AT40">
         <v>15</v>
@@ -8320,13 +8320,13 @@
         <v>14</v>
       </c>
       <c r="AV40">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AW40">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AX40">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AY40">
         <v>10</v>
@@ -8335,7 +8335,7 @@
         <v>17.5</v>
       </c>
       <c r="BA40">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BB40">
         <v>12.5</v>
@@ -8347,13 +8347,13 @@
         <v>20</v>
       </c>
       <c r="BE40">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BF40">
         <v>2.98</v>
       </c>
       <c r="BG40">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BH40" t="s">
         <v>234</v>
@@ -8561,16 +8561,16 @@
         <v>2.32</v>
       </c>
       <c r="G42">
-        <v>2.72</v>
+        <v>2.66</v>
       </c>
       <c r="H42">
         <v>3</v>
       </c>
       <c r="I42">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="J42">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="K42">
         <v>3.8</v>
@@ -8597,7 +8597,7 @@
         <v>1.18</v>
       </c>
       <c r="S42">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="T42">
         <v>1.01</v>
@@ -8606,10 +8606,10 @@
         <v>1.01</v>
       </c>
       <c r="V42">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="W42">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="X42">
         <v>1000</v>
@@ -8740,73 +8740,73 @@
         <v>217</v>
       </c>
       <c r="F43">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="G43">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="H43">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="I43">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="J43">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="K43">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="L43">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="M43">
         <v>1.03</v>
       </c>
       <c r="N43">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="O43">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="P43">
-        <v>2.74</v>
+        <v>2.58</v>
       </c>
       <c r="Q43">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="R43">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="S43">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="T43">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="U43">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="V43">
         <v>1.16</v>
       </c>
       <c r="W43">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="X43">
         <v>32</v>
       </c>
       <c r="Y43">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="Z43">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AA43">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AB43">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AC43">
         <v>13.5</v>
@@ -8842,37 +8842,37 @@
         <v>80</v>
       </c>
       <c r="AN43">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AO43">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AP43">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AQ43">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AR43">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AS43">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AT43">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AU43">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AV43">
         <v>20</v>
       </c>
       <c r="AW43">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AX43">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY43">
         <v>9</v>
@@ -8881,7 +8881,7 @@
         <v>16.5</v>
       </c>
       <c r="BA43">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BB43">
         <v>12</v>
@@ -8890,16 +8890,16 @@
         <v>12</v>
       </c>
       <c r="BD43">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BE43">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BF43">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BG43">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BH43" t="s">
         <v>234</v>
@@ -8922,16 +8922,16 @@
         <v>218</v>
       </c>
       <c r="F44">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="G44">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="H44">
         <v>4.8</v>
       </c>
       <c r="I44">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="J44">
         <v>4.2</v>
@@ -8940,7 +8940,7 @@
         <v>5.1</v>
       </c>
       <c r="L44">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="M44">
         <v>1.03</v>
@@ -8955,7 +8955,7 @@
         <v>2.46</v>
       </c>
       <c r="Q44">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="R44">
         <v>1.59</v>
@@ -8964,16 +8964,16 @@
         <v>2.36</v>
       </c>
       <c r="T44">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="U44">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V44">
         <v>1.2</v>
       </c>
       <c r="W44">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="X44">
         <v>30</v>
@@ -9024,7 +9024,7 @@
         <v>80</v>
       </c>
       <c r="AN44">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AO44">
         <v>50</v>
@@ -9039,7 +9039,7 @@
         <v>36</v>
       </c>
       <c r="AS44">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AT44">
         <v>10</v>
@@ -9051,7 +9051,7 @@
         <v>15.5</v>
       </c>
       <c r="AW44">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AX44">
         <v>10.5</v>
@@ -9063,7 +9063,7 @@
         <v>13.5</v>
       </c>
       <c r="BA44">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BB44">
         <v>14.5</v>
@@ -9075,13 +9075,13 @@
         <v>20</v>
       </c>
       <c r="BE44">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BF44">
         <v>5.5</v>
       </c>
       <c r="BG44">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BH44" t="s">
         <v>234</v>
@@ -9107,7 +9107,7 @@
         <v>1.94</v>
       </c>
       <c r="G45">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="H45">
         <v>3.75</v>
@@ -9155,13 +9155,13 @@
         <v>1.28</v>
       </c>
       <c r="W45">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="X45">
         <v>21</v>
       </c>
       <c r="Y45">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="Z45">
         <v>34</v>
@@ -9176,19 +9176,19 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD45">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="AE45">
         <v>50</v>
       </c>
       <c r="AF45">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="AG45">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="AH45">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="AI45">
         <v>55</v>
@@ -9331,7 +9331,7 @@
         <v>1.48</v>
       </c>
       <c r="U46">
-        <v>1.9</v>
+        <v>1.01</v>
       </c>
       <c r="V46">
         <v>1.16</v>
@@ -9421,7 +9421,7 @@
         <v>2.5</v>
       </c>
       <c r="AY46">
-        <v>2.48</v>
+        <v>9</v>
       </c>
       <c r="AZ46">
         <v>2.68</v>
@@ -9501,7 +9501,7 @@
         <v>2.02</v>
       </c>
       <c r="Q47">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="R47">
         <v>1.38</v>
@@ -9549,7 +9549,7 @@
         <v>9.4</v>
       </c>
       <c r="AG47">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AH47">
         <v>23</v>
@@ -9567,10 +9567,10 @@
         <v>36</v>
       </c>
       <c r="AM47">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN47">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AO47">
         <v>110</v>
@@ -9591,7 +9591,7 @@
         <v>7.6</v>
       </c>
       <c r="AU47">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV47">
         <v>21</v>
@@ -9650,22 +9650,22 @@
         <v>222</v>
       </c>
       <c r="F48">
+        <v>6.8</v>
+      </c>
+      <c r="G48">
         <v>7.2</v>
       </c>
-      <c r="G48">
-        <v>7.4</v>
-      </c>
       <c r="H48">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="I48">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="J48">
+        <v>5</v>
+      </c>
+      <c r="K48">
         <v>5.1</v>
-      </c>
-      <c r="K48">
-        <v>5.2</v>
       </c>
       <c r="L48">
         <v>1.32</v>
@@ -9689,19 +9689,19 @@
         <v>1.55</v>
       </c>
       <c r="S48">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="T48">
         <v>1.84</v>
       </c>
       <c r="U48">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V48">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="W48">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="X48">
         <v>24</v>
@@ -9713,7 +9713,7 @@
         <v>9.6</v>
       </c>
       <c r="AA48">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AB48">
         <v>27</v>
@@ -9725,16 +9725,16 @@
         <v>9.6</v>
       </c>
       <c r="AE48">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AF48">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AG48">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AH48">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI48">
         <v>29</v>
@@ -9755,7 +9755,7 @@
         <v>90</v>
       </c>
       <c r="AO48">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AP48">
         <v>23</v>
@@ -9767,13 +9767,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AS48">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AT48">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AU48">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AV48">
         <v>9.199999999999999</v>
@@ -9788,7 +9788,7 @@
         <v>23</v>
       </c>
       <c r="AZ48">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BA48">
         <v>27</v>
@@ -9797,7 +9797,7 @@
         <v>46</v>
       </c>
       <c r="BC48">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BD48">
         <v>60</v>
@@ -9806,10 +9806,10 @@
         <v>85</v>
       </c>
       <c r="BF48">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="BG48">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BH48" t="s">
         <v>234</v>
@@ -9835,7 +9835,7 @@
         <v>2.52</v>
       </c>
       <c r="G49">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="H49">
         <v>3</v>
@@ -9844,10 +9844,10 @@
         <v>3.1</v>
       </c>
       <c r="J49">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K49">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L49">
         <v>1.42</v>
@@ -9877,16 +9877,16 @@
         <v>1.8</v>
       </c>
       <c r="U49">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V49">
         <v>1.48</v>
       </c>
       <c r="W49">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="X49">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Y49">
         <v>12.5</v>
@@ -9940,7 +9940,7 @@
         <v>32</v>
       </c>
       <c r="AP49">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AQ49">
         <v>11.5</v>
@@ -9964,7 +9964,7 @@
         <v>30</v>
       </c>
       <c r="AX49">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AY49">
         <v>10.5</v>
@@ -10014,22 +10014,22 @@
         <v>224</v>
       </c>
       <c r="F50">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="G50">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="H50">
         <v>12</v>
       </c>
       <c r="I50">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="J50">
         <v>6.4</v>
       </c>
       <c r="K50">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="L50">
         <v>1.01</v>
@@ -10038,40 +10038,40 @@
         <v>1.03</v>
       </c>
       <c r="N50">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="O50">
         <v>1.18</v>
       </c>
       <c r="P50">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="Q50">
         <v>1.53</v>
       </c>
       <c r="R50">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="S50">
         <v>2.3</v>
       </c>
       <c r="T50">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="U50">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="V50">
         <v>1.08</v>
       </c>
       <c r="W50">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="X50">
         <v>29</v>
       </c>
       <c r="Y50">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="Z50">
         <v>130</v>
@@ -10083,10 +10083,10 @@
         <v>11</v>
       </c>
       <c r="AC50">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="AD50">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AE50">
         <v>190</v>
@@ -10122,16 +10122,16 @@
         <v>210</v>
       </c>
       <c r="AP50">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AQ50">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR50">
+        <v>10</v>
+      </c>
+      <c r="AS50">
         <v>10.5</v>
-      </c>
-      <c r="AS50">
-        <v>11</v>
       </c>
       <c r="AT50">
         <v>9.4</v>
@@ -10140,40 +10140,40 @@
         <v>12.5</v>
       </c>
       <c r="AV50">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW50">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AX50">
         <v>7.8</v>
       </c>
       <c r="AY50">
+        <v>10</v>
+      </c>
+      <c r="AZ50">
+        <v>7.8</v>
+      </c>
+      <c r="BA50">
+        <v>10</v>
+      </c>
+      <c r="BB50">
         <v>9.6</v>
       </c>
-      <c r="AZ50">
+      <c r="BC50">
+        <v>12</v>
+      </c>
+      <c r="BD50">
         <v>8.199999999999999</v>
       </c>
-      <c r="BA50">
-        <v>10.5</v>
-      </c>
-      <c r="BB50">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BC50">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BD50">
-        <v>8.6</v>
-      </c>
       <c r="BE50">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BF50">
         <v>3.6</v>
       </c>
       <c r="BG50">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BH50" t="s">
         <v>234</v>
@@ -10196,46 +10196,46 @@
         <v>225</v>
       </c>
       <c r="F51">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="G51">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="H51">
         <v>3.5</v>
       </c>
       <c r="I51">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="J51">
         <v>2.92</v>
       </c>
       <c r="K51">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L51">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="M51">
         <v>1.15</v>
       </c>
       <c r="N51">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="O51">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="P51">
         <v>1.44</v>
       </c>
       <c r="Q51">
-        <v>3.05</v>
+        <v>2.94</v>
       </c>
       <c r="R51">
         <v>1.14</v>
       </c>
       <c r="S51">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="T51">
         <v>2.34</v>
@@ -10247,7 +10247,7 @@
         <v>1.35</v>
       </c>
       <c r="W51">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="X51">
         <v>7.4</v>
@@ -10289,16 +10289,16 @@
         <v>46</v>
       </c>
       <c r="AK51">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AL51">
         <v>85</v>
       </c>
       <c r="AM51">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="AN51">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AO51">
         <v>140</v>
@@ -10313,7 +10313,7 @@
         <v>20</v>
       </c>
       <c r="AS51">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT51">
         <v>5.8</v>
@@ -10325,7 +10325,7 @@
         <v>15</v>
       </c>
       <c r="AW51">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AX51">
         <v>11.5</v>
@@ -10337,7 +10337,7 @@
         <v>6.8</v>
       </c>
       <c r="BA51">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB51">
         <v>32</v>
@@ -10346,16 +10346,16 @@
         <v>7.2</v>
       </c>
       <c r="BD51">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BE51">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF51">
         <v>36</v>
       </c>
       <c r="BG51">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH51" t="s">
         <v>234</v>
@@ -10581,7 +10581,7 @@
         <v>1.01</v>
       </c>
       <c r="M53">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N53">
         <v>3</v>
@@ -10617,7 +10617,7 @@
         <v>13</v>
       </c>
       <c r="Y53">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="Z53">
         <v>44</v>
@@ -10626,7 +10626,7 @@
         <v>190</v>
       </c>
       <c r="AB53">
-        <v>7.2</v>
+        <v>970</v>
       </c>
       <c r="AC53">
         <v>9.800000000000001</v>
@@ -10638,7 +10638,7 @@
         <v>110</v>
       </c>
       <c r="AF53">
-        <v>10.5</v>
+        <v>970</v>
       </c>
       <c r="AG53">
         <v>12.5</v>
@@ -10662,7 +10662,7 @@
         <v>200</v>
       </c>
       <c r="AN53">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AO53">
         <v>160</v>
@@ -10719,7 +10719,7 @@
         <v>12</v>
       </c>
       <c r="BG53">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BH53" t="s">
         <v>234</v>
@@ -10748,13 +10748,13 @@
         <v>2.34</v>
       </c>
       <c r="H54">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="I54">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="J54">
-        <v>3.25</v>
+        <v>2.98</v>
       </c>
       <c r="K54">
         <v>4</v>
@@ -10769,7 +10769,7 @@
         <v>2</v>
       </c>
       <c r="O54">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P54">
         <v>2</v>
@@ -10781,7 +10781,7 @@
         <v>1.18</v>
       </c>
       <c r="S54">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="T54">
         <v>1.01</v>
@@ -10790,10 +10790,10 @@
         <v>1.01</v>
       </c>
       <c r="V54">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="W54">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="X54">
         <v>1000</v>
@@ -10924,7 +10924,7 @@
         <v>229</v>
       </c>
       <c r="F55">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="G55">
         <v>1.74</v>
@@ -10933,19 +10933,19 @@
         <v>6.4</v>
       </c>
       <c r="I55">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="J55">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K55">
-        <v>4.5</v>
+        <v>3.95</v>
       </c>
       <c r="L55">
         <v>1.43</v>
       </c>
       <c r="M55">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N55">
         <v>2.92</v>
@@ -10957,13 +10957,13 @@
         <v>1.65</v>
       </c>
       <c r="Q55">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
       <c r="R55">
         <v>1.23</v>
       </c>
       <c r="S55">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T55">
         <v>2.2</v>
@@ -10972,7 +10972,7 @@
         <v>1.7</v>
       </c>
       <c r="V55">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="W55">
         <v>2.34</v>
@@ -10981,19 +10981,19 @@
         <v>12.5</v>
       </c>
       <c r="Y55">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="Z55">
         <v>60</v>
       </c>
       <c r="AA55">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="AB55">
         <v>7.4</v>
       </c>
       <c r="AC55">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD55">
         <v>34</v>
@@ -11002,7 +11002,7 @@
         <v>160</v>
       </c>
       <c r="AF55">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AG55">
         <v>12</v>
@@ -11032,16 +11032,16 @@
         <v>280</v>
       </c>
       <c r="AP55">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="AQ55">
         <v>14.5</v>
       </c>
       <c r="AR55">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="AS55">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AT55">
         <v>5.6</v>
@@ -11050,40 +11050,40 @@
         <v>7.4</v>
       </c>
       <c r="AV55">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="AW55">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="AX55">
         <v>7.4</v>
       </c>
       <c r="AY55">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="AZ55">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BA55">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BB55">
         <v>14</v>
       </c>
       <c r="BC55">
-        <v>4.6</v>
+        <v>18</v>
       </c>
       <c r="BD55">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BE55">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BF55">
         <v>11</v>
       </c>
       <c r="BG55">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BH55" t="s">
         <v>234</v>
@@ -11109,7 +11109,7 @@
         <v>1.57</v>
       </c>
       <c r="G56">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="H56">
         <v>4.8</v>
@@ -11157,7 +11157,7 @@
         <v>1.13</v>
       </c>
       <c r="W56">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="X56">
         <v>1000</v>
@@ -11300,7 +11300,7 @@
         <v>970</v>
       </c>
       <c r="J57">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K57">
         <v>110</v>
@@ -11312,13 +11312,13 @@
         <v>1.01</v>
       </c>
       <c r="N57">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="O57">
         <v>1.13</v>
       </c>
       <c r="P57">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Q57">
         <v>1.13</v>
@@ -11473,7 +11473,7 @@
         <v>3.5</v>
       </c>
       <c r="G58">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="H58">
         <v>2.42</v>
@@ -11485,7 +11485,7 @@
         <v>2.8</v>
       </c>
       <c r="K58">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="L58">
         <v>1.67</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-04.xlsx
@@ -781,7 +781,7 @@
     <t>Deportes Recoleta</t>
   </si>
   <si>
-    <t>2026-05-03 12:38:03</t>
+    <t>2026-05-03 14:57:17</t>
   </si>
 </sst>
 </file>
@@ -1526,16 +1526,16 @@
         <v>1.02</v>
       </c>
       <c r="G3">
-        <v>110</v>
+        <v>600</v>
       </c>
       <c r="H3">
         <v>1.02</v>
       </c>
       <c r="I3">
-        <v>110</v>
+        <v>870</v>
       </c>
       <c r="J3">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K3">
         <v>950</v>
@@ -1708,10 +1708,10 @@
         <v>3.15</v>
       </c>
       <c r="G4">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="H4">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="I4">
         <v>2.58</v>
@@ -1756,7 +1756,7 @@
         <v>1.63</v>
       </c>
       <c r="W4">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="X4">
         <v>12.5</v>
@@ -1813,22 +1813,22 @@
         <v>30</v>
       </c>
       <c r="AP4">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="AQ4">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="AR4">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AS4">
         <v>4.5</v>
       </c>
       <c r="AT4">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AU4">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AV4">
         <v>3.75</v>
@@ -1840,7 +1840,7 @@
         <v>4.4</v>
       </c>
       <c r="AY4">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AZ4">
         <v>4.2</v>
@@ -1926,7 +1926,7 @@
         <v>1.2</v>
       </c>
       <c r="S5">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="T5">
         <v>1.93</v>
@@ -1941,10 +1941,10 @@
         <v>1.42</v>
       </c>
       <c r="X5">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="Y5">
-        <v>970</v>
+        <v>10</v>
       </c>
       <c r="Z5">
         <v>970</v>
@@ -2010,7 +2010,7 @@
         <v>3.7</v>
       </c>
       <c r="AU5">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="AV5">
         <v>4.1</v>
@@ -2075,49 +2075,49 @@
         <v>1.82</v>
       </c>
       <c r="H6">
-        <v>4.8</v>
+        <v>3.9</v>
       </c>
       <c r="I6">
-        <v>10.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J6">
         <v>3.1</v>
       </c>
       <c r="K6">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="L6">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="M6">
         <v>1.01</v>
       </c>
       <c r="N6">
-        <v>1.25</v>
+        <v>1.69</v>
       </c>
       <c r="O6">
         <v>1.35</v>
       </c>
       <c r="P6">
-        <v>1.24</v>
+        <v>1.69</v>
       </c>
       <c r="Q6">
-        <v>1.35</v>
+        <v>1.92</v>
       </c>
       <c r="R6">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="S6">
-        <v>1.35</v>
+        <v>1.93</v>
       </c>
       <c r="T6">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="U6">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="V6">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="W6">
         <v>2.2</v>
@@ -2457,7 +2457,7 @@
         <v>1.07</v>
       </c>
       <c r="N8">
-        <v>1.84</v>
+        <v>2.66</v>
       </c>
       <c r="O8">
         <v>1.35</v>
@@ -2472,13 +2472,13 @@
         <v>1.32</v>
       </c>
       <c r="S8">
-        <v>1.87</v>
+        <v>1.05</v>
       </c>
       <c r="T8">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="U8">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="V8">
         <v>1.13</v>
@@ -2615,16 +2615,16 @@
         <v>196</v>
       </c>
       <c r="F9">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="G9">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="H9">
         <v>3.95</v>
       </c>
       <c r="I9">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="J9">
         <v>3</v>
@@ -2633,7 +2633,7 @@
         <v>3.7</v>
       </c>
       <c r="L9">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="M9">
         <v>1.1</v>
@@ -2648,7 +2648,7 @@
         <v>1.59</v>
       </c>
       <c r="Q9">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="R9">
         <v>1.22</v>
@@ -2663,7 +2663,7 @@
         <v>1.78</v>
       </c>
       <c r="V9">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="W9">
         <v>1.76</v>
@@ -2723,58 +2723,58 @@
         <v>130</v>
       </c>
       <c r="AP9">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AQ9">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AR9">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AS9">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AT9">
-        <v>1.03</v>
+        <v>3.2</v>
       </c>
       <c r="AU9">
-        <v>1.03</v>
+        <v>3.3</v>
       </c>
       <c r="AV9">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AW9">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AX9">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="AY9">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="AZ9">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BA9">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BB9">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BC9">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BD9">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BE9">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="BF9">
-        <v>17</v>
+        <v>4.3</v>
       </c>
       <c r="BG9">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BH9" t="s">
         <v>255</v>
@@ -2797,13 +2797,13 @@
         <v>197</v>
       </c>
       <c r="F10">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="G10">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="H10">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="I10">
         <v>2.98</v>
@@ -2812,7 +2812,7 @@
         <v>2.78</v>
       </c>
       <c r="K10">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="L10">
         <v>1.56</v>
@@ -2848,7 +2848,7 @@
         <v>1.5</v>
       </c>
       <c r="W10">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="X10">
         <v>8.4</v>
@@ -2905,7 +2905,7 @@
         <v>70</v>
       </c>
       <c r="AP10">
-        <v>3.2</v>
+        <v>6.4</v>
       </c>
       <c r="AQ10">
         <v>5.9</v>
@@ -2917,10 +2917,10 @@
         <v>4.8</v>
       </c>
       <c r="AT10">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AU10">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AV10">
         <v>10.5</v>
@@ -2979,64 +2979,64 @@
         <v>198</v>
       </c>
       <c r="F11">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="G11">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="H11">
+        <v>5.2</v>
+      </c>
+      <c r="I11">
         <v>5.3</v>
       </c>
-      <c r="I11">
-        <v>5.4</v>
-      </c>
       <c r="J11">
+        <v>4.3</v>
+      </c>
+      <c r="K11">
         <v>4.4</v>
       </c>
-      <c r="K11">
-        <v>4.5</v>
-      </c>
       <c r="L11">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="M11">
         <v>1.05</v>
       </c>
       <c r="N11">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="O11">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="P11">
+        <v>2.2</v>
+      </c>
+      <c r="Q11">
+        <v>1.8</v>
+      </c>
+      <c r="R11">
+        <v>1.48</v>
+      </c>
+      <c r="S11">
+        <v>3</v>
+      </c>
+      <c r="T11">
+        <v>1.8</v>
+      </c>
+      <c r="U11">
+        <v>2.18</v>
+      </c>
+      <c r="V11">
+        <v>1.23</v>
+      </c>
+      <c r="W11">
         <v>2.34</v>
       </c>
-      <c r="Q11">
-        <v>1.72</v>
-      </c>
-      <c r="R11">
-        <v>1.51</v>
-      </c>
-      <c r="S11">
-        <v>2.84</v>
-      </c>
-      <c r="T11">
-        <v>1.75</v>
-      </c>
-      <c r="U11">
-        <v>2.26</v>
-      </c>
-      <c r="V11">
-        <v>1.22</v>
-      </c>
-      <c r="W11">
-        <v>2.4</v>
-      </c>
       <c r="X11">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Y11">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Z11">
         <v>42</v>
@@ -3045,64 +3045,64 @@
         <v>130</v>
       </c>
       <c r="AB11">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AC11">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD11">
         <v>19.5</v>
       </c>
       <c r="AE11">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AF11">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG11">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH11">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AI11">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AJ11">
+        <v>17.5</v>
+      </c>
+      <c r="AK11">
+        <v>16.5</v>
+      </c>
+      <c r="AL11">
+        <v>30</v>
+      </c>
+      <c r="AM11">
+        <v>95</v>
+      </c>
+      <c r="AN11">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AO11">
+        <v>65</v>
+      </c>
+      <c r="AP11">
         <v>17</v>
       </c>
-      <c r="AK11">
-        <v>15.5</v>
-      </c>
-      <c r="AL11">
-        <v>28</v>
-      </c>
-      <c r="AM11">
-        <v>85</v>
-      </c>
-      <c r="AN11">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AO11">
-        <v>55</v>
-      </c>
-      <c r="AP11">
+      <c r="AQ11">
         <v>18.5</v>
       </c>
-      <c r="AQ11">
-        <v>20</v>
-      </c>
       <c r="AR11">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AS11">
-        <v>50</v>
+        <v>95</v>
       </c>
       <c r="AT11">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AU11">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV11">
         <v>18.5</v>
@@ -3111,31 +3111,31 @@
         <v>50</v>
       </c>
       <c r="AX11">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AY11">
         <v>9.4</v>
       </c>
       <c r="AZ11">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BA11">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BB11">
         <v>16.5</v>
       </c>
       <c r="BC11">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BD11">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BE11">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="BF11">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG11">
         <v>50</v>
@@ -3161,7 +3161,7 @@
         <v>199</v>
       </c>
       <c r="F12">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="G12">
         <v>3.6</v>
@@ -3170,13 +3170,13 @@
         <v>2.34</v>
       </c>
       <c r="I12">
-        <v>2.6</v>
+        <v>2.44</v>
       </c>
       <c r="J12">
         <v>3.35</v>
       </c>
       <c r="K12">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="L12">
         <v>1.4</v>
@@ -3194,7 +3194,7 @@
         <v>1.69</v>
       </c>
       <c r="Q12">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="R12">
         <v>1.25</v>
@@ -3209,13 +3209,13 @@
         <v>1.78</v>
       </c>
       <c r="V12">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="W12">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="X12">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="Y12">
         <v>9.6</v>
@@ -3269,10 +3269,10 @@
         <v>32</v>
       </c>
       <c r="AP12">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ12">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="AR12">
         <v>11</v>
@@ -3281,7 +3281,7 @@
         <v>20</v>
       </c>
       <c r="AT12">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AU12">
         <v>6.2</v>
@@ -3296,31 +3296,31 @@
         <v>5.1</v>
       </c>
       <c r="AY12">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AZ12">
         <v>14.5</v>
       </c>
       <c r="BA12">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BB12">
         <v>5.8</v>
       </c>
       <c r="BC12">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BD12">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BE12">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="BF12">
         <v>5.7</v>
       </c>
       <c r="BG12">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BH12" t="s">
         <v>255</v>
@@ -3343,19 +3343,19 @@
         <v>200</v>
       </c>
       <c r="F13">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G13">
         <v>1000</v>
       </c>
       <c r="H13">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I13">
         <v>1000</v>
       </c>
       <c r="J13">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K13">
         <v>950</v>
@@ -3367,7 +3367,7 @@
         <v>1.01</v>
       </c>
       <c r="N13">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O13">
         <v>1.01</v>
@@ -3382,13 +3382,13 @@
         <v>1.12</v>
       </c>
       <c r="S13">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="T13">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U13">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V13">
         <v>1.01</v>
@@ -3525,19 +3525,19 @@
         <v>201</v>
       </c>
       <c r="F14">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G14">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="H14">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I14">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J14">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K14">
         <v>950</v>
@@ -3549,16 +3549,16 @@
         <v>1.01</v>
       </c>
       <c r="N14">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O14">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="P14">
         <v>1.24</v>
       </c>
       <c r="Q14">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="R14">
         <v>1.12</v>
@@ -3567,10 +3567,10 @@
         <v>1.36</v>
       </c>
       <c r="T14">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U14">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V14">
         <v>1.01</v>
@@ -3815,7 +3815,7 @@
         <v>970</v>
       </c>
       <c r="AP15">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AQ15">
         <v>6.6</v>
@@ -3839,31 +3839,31 @@
         <v>14.5</v>
       </c>
       <c r="AX15">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AY15">
         <v>15.5</v>
       </c>
       <c r="AZ15">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BA15">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BB15">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BC15">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BD15">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BE15">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BF15">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BG15">
         <v>9</v>
@@ -3889,19 +3889,19 @@
         <v>203</v>
       </c>
       <c r="F16">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G16">
         <v>1000</v>
       </c>
       <c r="H16">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I16">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J16">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K16">
         <v>950</v>
@@ -3913,7 +3913,7 @@
         <v>1.01</v>
       </c>
       <c r="N16">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O16">
         <v>1.01</v>
@@ -3922,19 +3922,19 @@
         <v>1.24</v>
       </c>
       <c r="Q16">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R16">
         <v>1.12</v>
       </c>
       <c r="S16">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="T16">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U16">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V16">
         <v>1.01</v>
@@ -4071,19 +4071,19 @@
         <v>204</v>
       </c>
       <c r="F17">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G17">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="H17">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I17">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J17">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K17">
         <v>950</v>
@@ -4095,13 +4095,13 @@
         <v>1.01</v>
       </c>
       <c r="N17">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O17">
         <v>1.01</v>
       </c>
       <c r="P17">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q17">
         <v>1.01</v>
@@ -4110,13 +4110,13 @@
         <v>1.12</v>
       </c>
       <c r="S17">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="T17">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U17">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V17">
         <v>1.01</v>
@@ -4256,16 +4256,16 @@
         <v>1.47</v>
       </c>
       <c r="G18">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="H18">
         <v>6.4</v>
       </c>
       <c r="I18">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="J18">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="K18">
         <v>4.8</v>
@@ -4283,10 +4283,10 @@
         <v>1.31</v>
       </c>
       <c r="P18">
-        <v>1.74</v>
+        <v>1.82</v>
       </c>
       <c r="Q18">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="R18">
         <v>1.33</v>
@@ -4295,13 +4295,13 @@
         <v>3</v>
       </c>
       <c r="T18">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="U18">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="V18">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="W18">
         <v>2.66</v>
@@ -4435,10 +4435,10 @@
         <v>206</v>
       </c>
       <c r="F19">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="G19">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="H19">
         <v>7.6</v>
@@ -4453,7 +4453,7 @@
         <v>4.5</v>
       </c>
       <c r="L19">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M19">
         <v>1.07</v>
@@ -4474,10 +4474,10 @@
         <v>1.32</v>
       </c>
       <c r="S19">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="T19">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="U19">
         <v>1.77</v>
@@ -4486,7 +4486,7 @@
         <v>1.13</v>
       </c>
       <c r="W19">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="X19">
         <v>17</v>
@@ -4528,7 +4528,7 @@
         <v>14.5</v>
       </c>
       <c r="AK19">
-        <v>970</v>
+        <v>18.5</v>
       </c>
       <c r="AL19">
         <v>48</v>
@@ -4543,7 +4543,7 @@
         <v>280</v>
       </c>
       <c r="AP19">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AQ19">
         <v>16.5</v>
@@ -4561,7 +4561,7 @@
         <v>8.4</v>
       </c>
       <c r="AV19">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AW19">
         <v>8</v>
@@ -4579,7 +4579,7 @@
         <v>8</v>
       </c>
       <c r="BB19">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BC19">
         <v>13</v>
@@ -4591,7 +4591,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BF19">
-        <v>4.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG19">
         <v>8.199999999999999</v>
@@ -4617,37 +4617,37 @@
         <v>207</v>
       </c>
       <c r="F20">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="G20">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="H20">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="I20">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="J20">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K20">
         <v>3.6</v>
       </c>
       <c r="L20">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="M20">
         <v>1.08</v>
       </c>
       <c r="N20">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O20">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P20">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="Q20">
         <v>2.12</v>
@@ -4656,19 +4656,19 @@
         <v>1.28</v>
       </c>
       <c r="S20">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="T20">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="U20">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="V20">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W20">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="X20">
         <v>12.5</v>
@@ -4713,7 +4713,7 @@
         <v>26</v>
       </c>
       <c r="AL20">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AM20">
         <v>140</v>
@@ -4731,7 +4731,7 @@
         <v>11</v>
       </c>
       <c r="AR20">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AS20">
         <v>9.199999999999999</v>
@@ -4746,7 +4746,7 @@
         <v>14</v>
       </c>
       <c r="AW20">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX20">
         <v>11</v>
@@ -4758,7 +4758,7 @@
         <v>16.5</v>
       </c>
       <c r="BA20">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BB20">
         <v>7.4</v>
@@ -4770,7 +4770,7 @@
         <v>36</v>
       </c>
       <c r="BE20">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BF20">
         <v>15.5</v>
@@ -4799,25 +4799,25 @@
         <v>208</v>
       </c>
       <c r="F21">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="G21">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="H21">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="I21">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="J21">
         <v>3.7</v>
       </c>
       <c r="K21">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="L21">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="M21">
         <v>1.07</v>
@@ -4844,16 +4844,16 @@
         <v>1.93</v>
       </c>
       <c r="U21">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="V21">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="W21">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X21">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="Y21">
         <v>8.199999999999999</v>
@@ -4868,7 +4868,7 @@
         <v>18.5</v>
       </c>
       <c r="AC21">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD21">
         <v>10.5</v>
@@ -4880,13 +4880,13 @@
         <v>50</v>
       </c>
       <c r="AG21">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AH21">
         <v>23</v>
       </c>
       <c r="AI21">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AJ21">
         <v>180</v>
@@ -4937,25 +4937,25 @@
         <v>18.5</v>
       </c>
       <c r="AZ21">
-        <v>6</v>
+        <v>18.5</v>
       </c>
       <c r="BA21">
         <v>32</v>
       </c>
       <c r="BB21">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC21">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BD21">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BE21">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF21">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BG21">
         <v>9.800000000000001</v>
@@ -4984,13 +4984,13 @@
         <v>4.8</v>
       </c>
       <c r="G22">
-        <v>6.4</v>
+        <v>5.5</v>
       </c>
       <c r="H22">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="I22">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="J22">
         <v>4.2</v>
@@ -5005,142 +5005,142 @@
         <v>1.04</v>
       </c>
       <c r="N22">
-        <v>2.42</v>
+        <v>5.2</v>
       </c>
       <c r="O22">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="P22">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="Q22">
+        <v>1.51</v>
+      </c>
+      <c r="R22">
         <v>1.58</v>
       </c>
-      <c r="R22">
-        <v>1.5</v>
-      </c>
       <c r="S22">
-        <v>2.34</v>
+        <v>2.22</v>
       </c>
       <c r="T22">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="U22">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="V22">
         <v>2.28</v>
       </c>
       <c r="W22">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="X22">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="Y22">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Z22">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AA22">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AB22">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AC22">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AD22">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AE22">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AF22">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AG22">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AH22">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI22">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AJ22">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AK22">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AL22">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM22">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AN22">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AO22">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AP22">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AQ22">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="AR22">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="AS22">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AT22">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AU22">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="AV22">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="AW22">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AX22">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AY22">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AZ22">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BA22">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BB22">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BC22">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BD22">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BE22">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BF22">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BG22">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BH22" t="s">
         <v>255</v>
@@ -5163,31 +5163,31 @@
         <v>210</v>
       </c>
       <c r="F23">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="G23">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="H23">
         <v>4.6</v>
       </c>
       <c r="I23">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="J23">
         <v>3.65</v>
       </c>
       <c r="K23">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L23">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="M23">
         <v>1.08</v>
       </c>
       <c r="N23">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="O23">
         <v>1.35</v>
@@ -5211,10 +5211,10 @@
         <v>1.98</v>
       </c>
       <c r="V23">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W23">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="X23">
         <v>16.5</v>
@@ -5235,7 +5235,7 @@
         <v>10</v>
       </c>
       <c r="AD23">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AE23">
         <v>85</v>
@@ -5283,19 +5283,19 @@
         <v>4.2</v>
       </c>
       <c r="AT23">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="AU23">
         <v>7.4</v>
       </c>
       <c r="AV23">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="AW23">
         <v>4.1</v>
       </c>
       <c r="AX23">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="AY23">
         <v>9.199999999999999</v>
@@ -5310,10 +5310,10 @@
         <v>15.5</v>
       </c>
       <c r="BC23">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="BD23">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BE23">
         <v>4.2</v>
@@ -5322,7 +5322,7 @@
         <v>10.5</v>
       </c>
       <c r="BG23">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BH23" t="s">
         <v>255</v>
@@ -5345,22 +5345,22 @@
         <v>211</v>
       </c>
       <c r="F24">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="G24">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="H24">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="I24">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="J24">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K24">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="L24">
         <v>1.33</v>
@@ -5378,7 +5378,7 @@
         <v>1.91</v>
       </c>
       <c r="Q24">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="R24">
         <v>1.35</v>
@@ -5393,16 +5393,16 @@
         <v>1.65</v>
       </c>
       <c r="V24">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="W24">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X24">
+        <v>18</v>
+      </c>
+      <c r="Y24">
         <v>970</v>
-      </c>
-      <c r="Y24">
-        <v>8.800000000000001</v>
       </c>
       <c r="Z24">
         <v>970</v>
@@ -5411,19 +5411,19 @@
         <v>970</v>
       </c>
       <c r="AB24">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AC24">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="AD24">
         <v>970</v>
       </c>
       <c r="AE24">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AF24">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AG24">
         <v>40</v>
@@ -5438,13 +5438,13 @@
         <v>1000</v>
       </c>
       <c r="AK24">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AL24">
         <v>160</v>
       </c>
       <c r="AM24">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AN24">
         <v>1000</v>
@@ -5453,58 +5453,58 @@
         <v>970</v>
       </c>
       <c r="AP24">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AQ24">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AR24">
         <v>6.2</v>
       </c>
       <c r="AS24">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT24">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AU24">
         <v>7.6</v>
       </c>
       <c r="AV24">
-        <v>7.4</v>
+        <v>4.2</v>
       </c>
       <c r="AW24">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AX24">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AY24">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AZ24">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BA24">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BB24">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BC24">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BD24">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BE24">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="BF24">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="BG24">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BH24" t="s">
         <v>255</v>
@@ -5527,166 +5527,166 @@
         <v>212</v>
       </c>
       <c r="F25">
-        <v>2.3</v>
+        <v>2.48</v>
       </c>
       <c r="G25">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="H25">
-        <v>2.42</v>
+        <v>2.7</v>
       </c>
       <c r="I25">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="J25">
         <v>3.2</v>
       </c>
       <c r="K25">
-        <v>6.6</v>
+        <v>3.95</v>
       </c>
       <c r="L25">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M25">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N25">
-        <v>1.25</v>
+        <v>4</v>
       </c>
       <c r="O25">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="P25">
-        <v>1.24</v>
+        <v>2.04</v>
       </c>
       <c r="Q25">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="R25">
-        <v>1.2</v>
+        <v>1.41</v>
       </c>
       <c r="S25">
-        <v>2.66</v>
+        <v>2.9</v>
       </c>
       <c r="T25">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="U25">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="V25">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="W25">
-        <v>1.46</v>
+        <v>1.54</v>
       </c>
       <c r="X25">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Y25">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Z25">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AA25">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB25">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AC25">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD25">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AE25">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AF25">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AG25">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH25">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AI25">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AJ25">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AK25">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL25">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM25">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AN25">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AO25">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AP25">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AQ25">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="AR25">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="AS25">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT25">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU25">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AV25">
-        <v>1.03</v>
+        <v>9.4</v>
       </c>
       <c r="AW25">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="AX25">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="AY25">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AZ25">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="BA25">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB25">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC25">
-        <v>1.03</v>
+        <v>19.5</v>
       </c>
       <c r="BD25">
         <v>1.03</v>
       </c>
       <c r="BE25">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF25">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BG25">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BH25" t="s">
         <v>255</v>
@@ -5712,16 +5712,16 @@
         <v>3.35</v>
       </c>
       <c r="G26">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="H26">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="I26">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="J26">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="K26">
         <v>3.85</v>
@@ -5739,10 +5739,10 @@
         <v>1.32</v>
       </c>
       <c r="P26">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="Q26">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="R26">
         <v>1.33</v>
@@ -5751,16 +5751,16 @@
         <v>3.4</v>
       </c>
       <c r="T26">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="U26">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="V26">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="W26">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="X26">
         <v>17</v>
@@ -5823,52 +5823,52 @@
         <v>7.2</v>
       </c>
       <c r="AR26">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AS26">
         <v>21</v>
       </c>
       <c r="AT26">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AU26">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AV26">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AW26">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AX26">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AY26">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AZ26">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BA26">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BB26">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BC26">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BD26">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BE26">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BF26">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BG26">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BH26" t="s">
         <v>255</v>
@@ -5900,10 +5900,10 @@
         <v>2.14</v>
       </c>
       <c r="I27">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="J27">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="K27">
         <v>4</v>
@@ -5924,25 +5924,25 @@
         <v>1.98</v>
       </c>
       <c r="Q27">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="R27">
         <v>1.38</v>
       </c>
       <c r="S27">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="T27">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="U27">
         <v>2.16</v>
       </c>
       <c r="V27">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="W27">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="X27">
         <v>970</v>
@@ -5960,7 +5960,7 @@
         <v>970</v>
       </c>
       <c r="AC27">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AD27">
         <v>970</v>
@@ -5969,7 +5969,7 @@
         <v>28</v>
       </c>
       <c r="AF27">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AG27">
         <v>970</v>
@@ -6002,55 +6002,55 @@
         <v>4</v>
       </c>
       <c r="AQ27">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="AR27">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="AS27">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AT27">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="AU27">
         <v>6.2</v>
       </c>
       <c r="AV27">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="AW27">
+        <v>4.1</v>
+      </c>
+      <c r="AX27">
         <v>4.2</v>
       </c>
-      <c r="AX27">
-        <v>4.3</v>
-      </c>
       <c r="AY27">
-        <v>4</v>
+        <v>10.5</v>
       </c>
       <c r="AZ27">
-        <v>4.1</v>
+        <v>12.5</v>
       </c>
       <c r="BA27">
         <v>4.5</v>
       </c>
       <c r="BB27">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BC27">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BD27">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BE27">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BF27">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BG27">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BH27" t="s">
         <v>255</v>
@@ -6076,16 +6076,16 @@
         <v>1.48</v>
       </c>
       <c r="G28">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="H28">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="I28">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="J28">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="K28">
         <v>5.2</v>
@@ -6106,13 +6106,13 @@
         <v>2.32</v>
       </c>
       <c r="Q28">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="R28">
         <v>1.52</v>
       </c>
       <c r="S28">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="T28">
         <v>1.85</v>
@@ -6124,19 +6124,19 @@
         <v>1.14</v>
       </c>
       <c r="W28">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="X28">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="Y28">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Z28">
         <v>1000</v>
       </c>
       <c r="AA28">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="AB28">
         <v>10.5</v>
@@ -6145,7 +6145,7 @@
         <v>11.5</v>
       </c>
       <c r="AD28">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AE28">
         <v>120</v>
@@ -6157,19 +6157,19 @@
         <v>10.5</v>
       </c>
       <c r="AH28">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AI28">
         <v>1000</v>
       </c>
       <c r="AJ28">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AK28">
         <v>15.5</v>
       </c>
       <c r="AL28">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AM28">
         <v>130</v>
@@ -6178,13 +6178,13 @@
         <v>6.6</v>
       </c>
       <c r="AO28">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AP28">
         <v>19.5</v>
       </c>
       <c r="AQ28">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AR28">
         <v>30</v>
@@ -6199,7 +6199,7 @@
         <v>10</v>
       </c>
       <c r="AV28">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AW28">
         <v>36</v>
@@ -6223,13 +6223,13 @@
         <v>12.5</v>
       </c>
       <c r="BD28">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BE28">
         <v>40</v>
       </c>
       <c r="BF28">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="BG28">
         <v>38</v>
@@ -6255,7 +6255,7 @@
         <v>216</v>
       </c>
       <c r="F29">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="G29">
         <v>2.32</v>
@@ -6267,13 +6267,13 @@
         <v>4</v>
       </c>
       <c r="J29">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K29">
         <v>3.95</v>
       </c>
       <c r="L29">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M29">
         <v>1.06</v>
@@ -6282,13 +6282,13 @@
         <v>3.7</v>
       </c>
       <c r="O29">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P29">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="Q29">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="R29">
         <v>1.36</v>
@@ -6306,7 +6306,7 @@
         <v>1.33</v>
       </c>
       <c r="W29">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="X29">
         <v>18.5</v>
@@ -6333,7 +6333,7 @@
         <v>55</v>
       </c>
       <c r="AF29">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AG29">
         <v>13.5</v>
@@ -6372,7 +6372,7 @@
         <v>19.5</v>
       </c>
       <c r="AS29">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AT29">
         <v>7.4</v>
@@ -6384,7 +6384,7 @@
         <v>11</v>
       </c>
       <c r="AW29">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AX29">
         <v>10.5</v>
@@ -6396,7 +6396,7 @@
         <v>12.5</v>
       </c>
       <c r="BA29">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BB29">
         <v>19.5</v>
@@ -6405,16 +6405,16 @@
         <v>16.5</v>
       </c>
       <c r="BD29">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BE29">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BF29">
         <v>11.5</v>
       </c>
       <c r="BG29">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BH29" t="s">
         <v>255</v>
@@ -6437,31 +6437,31 @@
         <v>217</v>
       </c>
       <c r="F30">
-        <v>2.1</v>
+        <v>2.36</v>
       </c>
       <c r="G30">
-        <v>3.15</v>
+        <v>2.56</v>
       </c>
       <c r="H30">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="I30">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="J30">
-        <v>2.32</v>
+        <v>3.1</v>
       </c>
       <c r="K30">
-        <v>950</v>
+        <v>3.7</v>
       </c>
       <c r="L30">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="M30">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="N30">
-        <v>2.32</v>
+        <v>3.05</v>
       </c>
       <c r="O30">
         <v>1.38</v>
@@ -6470,133 +6470,133 @@
         <v>1.84</v>
       </c>
       <c r="Q30">
-        <v>1.94</v>
+        <v>2.08</v>
       </c>
       <c r="R30">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="S30">
-        <v>3.25</v>
+        <v>3.85</v>
       </c>
       <c r="T30">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="U30">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="V30">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="W30">
-        <v>1.47</v>
+        <v>1.64</v>
       </c>
       <c r="X30">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y30">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Z30">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AA30">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB30">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC30">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AD30">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AE30">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AF30">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AG30">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH30">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AI30">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ30">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AK30">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL30">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM30">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN30">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AO30">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AP30">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AQ30">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AR30">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="AS30">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AT30">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AU30">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AV30">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AW30">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AX30">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AY30">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AZ30">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BA30">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BB30">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BC30">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BD30">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BE30">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BF30">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BG30">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BH30" t="s">
         <v>255</v>
@@ -6619,19 +6619,19 @@
         <v>218</v>
       </c>
       <c r="F31">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="G31">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="H31">
-        <v>2.64</v>
+        <v>2.54</v>
       </c>
       <c r="I31">
-        <v>2.66</v>
+        <v>2.58</v>
       </c>
       <c r="J31">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K31">
         <v>3.35</v>
@@ -6646,13 +6646,13 @@
         <v>3.35</v>
       </c>
       <c r="O31">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P31">
         <v>1.79</v>
       </c>
       <c r="Q31">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="R31">
         <v>1.29</v>
@@ -6667,25 +6667,25 @@
         <v>2.04</v>
       </c>
       <c r="V31">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="W31">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="X31">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Y31">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="Z31">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AA31">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AB31">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AC31">
         <v>7.2</v>
@@ -6694,22 +6694,22 @@
         <v>12</v>
       </c>
       <c r="AE31">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AF31">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AG31">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AH31">
         <v>18.5</v>
       </c>
       <c r="AI31">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AJ31">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AK31">
         <v>40</v>
@@ -6721,22 +6721,22 @@
         <v>120</v>
       </c>
       <c r="AN31">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AO31">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AP31">
         <v>10.5</v>
       </c>
       <c r="AQ31">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR31">
         <v>14.5</v>
       </c>
       <c r="AS31">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AT31">
         <v>10</v>
@@ -6748,37 +6748,37 @@
         <v>11</v>
       </c>
       <c r="AW31">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AX31">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AY31">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AZ31">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BA31">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BB31">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BC31">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BD31">
         <v>48</v>
       </c>
       <c r="BE31">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="BF31">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BG31">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="BH31" t="s">
         <v>255</v>
@@ -6801,22 +6801,22 @@
         <v>219</v>
       </c>
       <c r="F32">
-        <v>2.44</v>
+        <v>2.52</v>
       </c>
       <c r="G32">
         <v>2.66</v>
       </c>
       <c r="H32">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I32">
+        <v>3.4</v>
+      </c>
+      <c r="J32">
+        <v>3.25</v>
+      </c>
+      <c r="K32">
         <v>3.5</v>
-      </c>
-      <c r="J32">
-        <v>3.2</v>
-      </c>
-      <c r="K32">
-        <v>3.6</v>
       </c>
       <c r="L32">
         <v>1.43</v>
@@ -6849,7 +6849,7 @@
         <v>2.06</v>
       </c>
       <c r="V32">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W32">
         <v>1.6</v>
@@ -6858,7 +6858,7 @@
         <v>15</v>
       </c>
       <c r="Y32">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z32">
         <v>23</v>
@@ -6918,7 +6918,7 @@
         <v>18</v>
       </c>
       <c r="AS32">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AT32">
         <v>8.4</v>
@@ -6930,7 +6930,7 @@
         <v>11.5</v>
       </c>
       <c r="AW32">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AX32">
         <v>13.5</v>
@@ -6939,28 +6939,28 @@
         <v>10</v>
       </c>
       <c r="AZ32">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BA32">
         <v>6.6</v>
       </c>
       <c r="BB32">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BC32">
         <v>21</v>
       </c>
       <c r="BD32">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BE32">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BF32">
         <v>18.5</v>
       </c>
       <c r="BG32">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BH32" t="s">
         <v>255</v>
@@ -6983,22 +6983,22 @@
         <v>220</v>
       </c>
       <c r="F33">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="G33">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="H33">
         <v>2.52</v>
       </c>
       <c r="I33">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="J33">
         <v>3.8</v>
       </c>
       <c r="K33">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L33">
         <v>1.29</v>
@@ -7007,43 +7007,43 @@
         <v>1.05</v>
       </c>
       <c r="N33">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="O33">
         <v>1.26</v>
       </c>
       <c r="P33">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="Q33">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="R33">
         <v>1.48</v>
       </c>
       <c r="S33">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="T33">
+        <v>1.65</v>
+      </c>
+      <c r="U33">
+        <v>2.4</v>
+      </c>
+      <c r="V33">
         <v>1.63</v>
-      </c>
-      <c r="U33">
-        <v>2.46</v>
-      </c>
-      <c r="V33">
-        <v>1.62</v>
       </c>
       <c r="W33">
         <v>1.53</v>
       </c>
       <c r="X33">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y33">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z33">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="AA33">
         <v>38</v>
@@ -7058,7 +7058,7 @@
         <v>11.5</v>
       </c>
       <c r="AE33">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AF33">
         <v>22</v>
@@ -7067,16 +7067,16 @@
         <v>13</v>
       </c>
       <c r="AH33">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AI33">
         <v>34</v>
       </c>
       <c r="AJ33">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AK33">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AL33">
         <v>36</v>
@@ -7091,7 +7091,7 @@
         <v>17.5</v>
       </c>
       <c r="AP33">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AQ33">
         <v>11.5</v>
@@ -7100,22 +7100,22 @@
         <v>16.5</v>
       </c>
       <c r="AS33">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AT33">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AU33">
         <v>8</v>
       </c>
       <c r="AV33">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW33">
         <v>21</v>
       </c>
       <c r="AX33">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AY33">
         <v>11.5</v>
@@ -7124,22 +7124,22 @@
         <v>14</v>
       </c>
       <c r="BA33">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="BB33">
-        <v>11.5</v>
+        <v>34</v>
       </c>
       <c r="BC33">
         <v>25</v>
       </c>
       <c r="BD33">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="BE33">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="BF33">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BG33">
         <v>14.5</v>
@@ -7165,109 +7165,109 @@
         <v>221</v>
       </c>
       <c r="F34">
-        <v>1.02</v>
+        <v>1.18</v>
       </c>
       <c r="G34">
-        <v>110</v>
+        <v>1.29</v>
       </c>
       <c r="H34">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="I34">
-        <v>110</v>
+        <v>30</v>
       </c>
       <c r="J34">
-        <v>1.02</v>
+        <v>4.2</v>
       </c>
       <c r="K34">
-        <v>950</v>
+        <v>8.4</v>
       </c>
       <c r="L34">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="M34">
         <v>1.05</v>
       </c>
       <c r="N34">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O34">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="P34">
-        <v>1.24</v>
+        <v>2</v>
       </c>
       <c r="Q34">
-        <v>1.24</v>
+        <v>1.59</v>
       </c>
       <c r="R34">
-        <v>1.12</v>
+        <v>1.44</v>
       </c>
       <c r="S34">
-        <v>1.24</v>
+        <v>2.5</v>
       </c>
       <c r="T34">
-        <v>1.01</v>
+        <v>2.56</v>
       </c>
       <c r="U34">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="V34">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W34">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="X34">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Y34">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="Z34">
-        <v>1000</v>
+        <v>310</v>
       </c>
       <c r="AA34">
         <v>1000</v>
       </c>
       <c r="AB34">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AC34">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AD34">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AE34">
         <v>1000</v>
       </c>
       <c r="AF34">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AG34">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AH34">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AI34">
-        <v>1000</v>
+        <v>490</v>
       </c>
       <c r="AJ34">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AK34">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AL34">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM34">
-        <v>1000</v>
+        <v>490</v>
       </c>
       <c r="AN34">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="AO34">
         <v>1000</v>
@@ -7285,10 +7285,10 @@
         <v>1.03</v>
       </c>
       <c r="AT34">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU34">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV34">
         <v>1.03</v>
@@ -7297,10 +7297,10 @@
         <v>1.03</v>
       </c>
       <c r="AX34">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY34">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ34">
         <v>1.03</v>
@@ -7309,10 +7309,10 @@
         <v>1.03</v>
       </c>
       <c r="BB34">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC34">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD34">
         <v>1.03</v>
@@ -7321,7 +7321,7 @@
         <v>1.03</v>
       </c>
       <c r="BF34">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BG34">
         <v>1.01</v>
@@ -7347,10 +7347,10 @@
         <v>222</v>
       </c>
       <c r="F35">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="G35">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="H35">
         <v>5.6</v>
@@ -7362,7 +7362,7 @@
         <v>4.6</v>
       </c>
       <c r="K35">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L35">
         <v>1.25</v>
@@ -7371,7 +7371,7 @@
         <v>1.03</v>
       </c>
       <c r="N35">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="O35">
         <v>1.19</v>
@@ -7389,16 +7389,16 @@
         <v>2.42</v>
       </c>
       <c r="T35">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="U35">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="V35">
         <v>1.19</v>
       </c>
       <c r="W35">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="X35">
         <v>30</v>
@@ -7443,28 +7443,28 @@
         <v>15.5</v>
       </c>
       <c r="AL35">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AM35">
         <v>80</v>
       </c>
       <c r="AN35">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AO35">
         <v>60</v>
       </c>
       <c r="AP35">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AQ35">
         <v>22</v>
       </c>
       <c r="AR35">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AS35">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AT35">
         <v>10.5</v>
@@ -7476,7 +7476,7 @@
         <v>19.5</v>
       </c>
       <c r="AW35">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX35">
         <v>10.5</v>
@@ -7488,7 +7488,7 @@
         <v>16</v>
       </c>
       <c r="BA35">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BB35">
         <v>14</v>
@@ -7497,16 +7497,16 @@
         <v>13.5</v>
       </c>
       <c r="BD35">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE35">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BF35">
         <v>5.2</v>
       </c>
       <c r="BG35">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BH35" t="s">
         <v>255</v>
@@ -7529,28 +7529,28 @@
         <v>223</v>
       </c>
       <c r="F36">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="G36">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="H36">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="I36">
         <v>3.95</v>
       </c>
       <c r="J36">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="K36">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="L36">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="M36">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N36">
         <v>2.56</v>
@@ -7562,7 +7562,7 @@
         <v>1.5</v>
       </c>
       <c r="Q36">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="R36">
         <v>1.18</v>
@@ -7571,19 +7571,19 @@
         <v>5.3</v>
       </c>
       <c r="T36">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="U36">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="V36">
         <v>1.33</v>
       </c>
       <c r="W36">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="X36">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="Y36">
         <v>12</v>
@@ -7595,31 +7595,31 @@
         <v>95</v>
       </c>
       <c r="AB36">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC36">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD36">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AE36">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AF36">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AG36">
         <v>14.5</v>
       </c>
       <c r="AH36">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI36">
         <v>100</v>
       </c>
       <c r="AJ36">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AK36">
         <v>42</v>
@@ -7628,7 +7628,7 @@
         <v>75</v>
       </c>
       <c r="AM36">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AN36">
         <v>46</v>
@@ -7637,7 +7637,7 @@
         <v>100</v>
       </c>
       <c r="AP36">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AQ36">
         <v>7.8</v>
@@ -7649,10 +7649,10 @@
         <v>4.9</v>
       </c>
       <c r="AT36">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="AU36">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="AV36">
         <v>12.5</v>
@@ -7667,10 +7667,10 @@
         <v>9.6</v>
       </c>
       <c r="AZ36">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="BA36">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BB36">
         <v>4.7</v>
@@ -7688,7 +7688,7 @@
         <v>4.7</v>
       </c>
       <c r="BG36">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BH36" t="s">
         <v>255</v>
@@ -7711,10 +7711,10 @@
         <v>224</v>
       </c>
       <c r="F37">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="G37">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="H37">
         <v>5.2</v>
@@ -7729,13 +7729,13 @@
         <v>3.95</v>
       </c>
       <c r="L37">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M37">
         <v>1.08</v>
       </c>
       <c r="N37">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O37">
         <v>1.38</v>
@@ -7762,7 +7762,7 @@
         <v>1.18</v>
       </c>
       <c r="W37">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="X37">
         <v>14.5</v>
@@ -7893,31 +7893,31 @@
         <v>225</v>
       </c>
       <c r="F38">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="G38">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="H38">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="I38">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="J38">
         <v>3.4</v>
       </c>
       <c r="K38">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L38">
         <v>1.39</v>
       </c>
       <c r="M38">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N38">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="O38">
         <v>1.39</v>
@@ -7926,25 +7926,25 @@
         <v>1.78</v>
       </c>
       <c r="Q38">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R38">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S38">
         <v>3.9</v>
       </c>
       <c r="T38">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="U38">
         <v>1.94</v>
       </c>
       <c r="V38">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W38">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="X38">
         <v>970</v>
@@ -7959,7 +7959,7 @@
         <v>80</v>
       </c>
       <c r="AB38">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC38">
         <v>8.199999999999999</v>
@@ -7971,7 +7971,7 @@
         <v>55</v>
       </c>
       <c r="AF38">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AG38">
         <v>14</v>
@@ -7986,7 +7986,7 @@
         <v>40</v>
       </c>
       <c r="AK38">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AL38">
         <v>55</v>
@@ -8004,7 +8004,7 @@
         <v>9</v>
       </c>
       <c r="AQ38">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AR38">
         <v>17</v>
@@ -8075,58 +8075,58 @@
         <v>226</v>
       </c>
       <c r="F39">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="G39">
         <v>1.98</v>
       </c>
       <c r="H39">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="I39">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="J39">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="K39">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="L39">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="M39">
         <v>1.05</v>
       </c>
       <c r="N39">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="O39">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P39">
         <v>2.12</v>
       </c>
       <c r="Q39">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="R39">
         <v>1.46</v>
       </c>
       <c r="S39">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="T39">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="U39">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="V39">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="W39">
-        <v>1.92</v>
+        <v>2.06</v>
       </c>
       <c r="X39">
         <v>24</v>
@@ -8144,7 +8144,7 @@
         <v>970</v>
       </c>
       <c r="AC39">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="AD39">
         <v>21</v>
@@ -8153,13 +8153,13 @@
         <v>65</v>
       </c>
       <c r="AF39">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="AG39">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH39">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI39">
         <v>65</v>
@@ -8177,16 +8177,16 @@
         <v>120</v>
       </c>
       <c r="AN39">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AO39">
         <v>65</v>
       </c>
       <c r="AP39">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AQ39">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AR39">
         <v>1.01</v>
@@ -8195,37 +8195,37 @@
         <v>1.01</v>
       </c>
       <c r="AT39">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AU39">
         <v>7.4</v>
       </c>
       <c r="AV39">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AW39">
         <v>1.01</v>
       </c>
       <c r="AX39">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY39">
         <v>7.4</v>
       </c>
       <c r="AZ39">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA39">
         <v>1.01</v>
       </c>
       <c r="BB39">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BC39">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BD39">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE39">
         <v>1.01</v>
@@ -8260,19 +8260,19 @@
         <v>1.37</v>
       </c>
       <c r="G40">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="H40">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="I40">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J40">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="K40">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="L40">
         <v>1.16</v>
@@ -8293,22 +8293,22 @@
         <v>1.34</v>
       </c>
       <c r="R40">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="S40">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="T40">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="U40">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="V40">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="W40">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="X40">
         <v>60</v>
@@ -8323,19 +8323,19 @@
         <v>230</v>
       </c>
       <c r="AB40">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AC40">
         <v>17.5</v>
       </c>
       <c r="AD40">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AE40">
         <v>95</v>
       </c>
       <c r="AF40">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AG40">
         <v>13</v>
@@ -8359,7 +8359,7 @@
         <v>75</v>
       </c>
       <c r="AN40">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="AO40">
         <v>65</v>
@@ -8368,7 +8368,7 @@
         <v>28</v>
       </c>
       <c r="AQ40">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="AR40">
         <v>36</v>
@@ -8380,13 +8380,13 @@
         <v>15</v>
       </c>
       <c r="AU40">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AV40">
         <v>26</v>
       </c>
       <c r="AW40">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AX40">
         <v>11.5</v>
@@ -8398,7 +8398,7 @@
         <v>18.5</v>
       </c>
       <c r="BA40">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BB40">
         <v>12</v>
@@ -8407,16 +8407,16 @@
         <v>11.5</v>
       </c>
       <c r="BD40">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="BE40">
         <v>32</v>
       </c>
       <c r="BF40">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BG40">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BH40" t="s">
         <v>255</v>
@@ -8439,22 +8439,22 @@
         <v>228</v>
       </c>
       <c r="F41">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="G41">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="H41">
-        <v>2.98</v>
+        <v>3.15</v>
       </c>
       <c r="I41">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="J41">
         <v>3.75</v>
       </c>
       <c r="K41">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L41">
         <v>1.27</v>
@@ -8472,25 +8472,25 @@
         <v>2.28</v>
       </c>
       <c r="Q41">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="R41">
         <v>1.51</v>
       </c>
       <c r="S41">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="T41">
         <v>1.6</v>
       </c>
       <c r="U41">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="V41">
         <v>1.43</v>
       </c>
       <c r="W41">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="X41">
         <v>25</v>
@@ -8547,7 +8547,7 @@
         <v>28</v>
       </c>
       <c r="AP41">
-        <v>3.7</v>
+        <v>15</v>
       </c>
       <c r="AQ41">
         <v>11.5</v>
@@ -8562,25 +8562,25 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AU41">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="AV41">
         <v>10</v>
       </c>
       <c r="AW41">
-        <v>3.9</v>
+        <v>22</v>
       </c>
       <c r="AX41">
         <v>12.5</v>
       </c>
       <c r="AY41">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="AZ41">
         <v>11</v>
       </c>
       <c r="BA41">
-        <v>3.95</v>
+        <v>26</v>
       </c>
       <c r="BB41">
         <v>3.9</v>
@@ -8624,16 +8624,16 @@
         <v>1.81</v>
       </c>
       <c r="G42">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="H42">
         <v>4.7</v>
       </c>
       <c r="I42">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="J42">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K42">
         <v>3.95</v>
@@ -8672,7 +8672,7 @@
         <v>1.22</v>
       </c>
       <c r="W42">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="X42">
         <v>15.5</v>
@@ -8806,22 +8806,22 @@
         <v>3.05</v>
       </c>
       <c r="G43">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="H43">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="I43">
-        <v>2.9</v>
+        <v>2.68</v>
       </c>
       <c r="J43">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="K43">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L43">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="M43">
         <v>1.09</v>
@@ -8833,28 +8833,28 @@
         <v>1.42</v>
       </c>
       <c r="P43">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="Q43">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="R43">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="S43">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="T43">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="U43">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="V43">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="W43">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="X43">
         <v>13</v>
@@ -8863,16 +8863,16 @@
         <v>10.5</v>
       </c>
       <c r="Z43">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AA43">
         <v>46</v>
       </c>
       <c r="AB43">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC43">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD43">
         <v>14.5</v>
@@ -8893,7 +8893,7 @@
         <v>65</v>
       </c>
       <c r="AJ43">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AK43">
         <v>55</v>
@@ -8923,10 +8923,10 @@
         <v>1.01</v>
       </c>
       <c r="AT43">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AU43">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AV43">
         <v>8.800000000000001</v>
@@ -8941,7 +8941,7 @@
         <v>10.5</v>
       </c>
       <c r="AZ43">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA43">
         <v>1.01</v>
@@ -8985,7 +8985,7 @@
         <v>231</v>
       </c>
       <c r="F44">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="G44">
         <v>1.78</v>
@@ -8994,22 +8994,22 @@
         <v>5.2</v>
       </c>
       <c r="I44">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="J44">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K44">
         <v>4.1</v>
       </c>
       <c r="L44">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M44">
         <v>1.06</v>
       </c>
       <c r="N44">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="O44">
         <v>1.3</v>
@@ -9021,13 +9021,13 @@
         <v>1.87</v>
       </c>
       <c r="R44">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="S44">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="T44">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="U44">
         <v>2.06</v>
@@ -9039,31 +9039,31 @@
         <v>2.28</v>
       </c>
       <c r="X44">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Y44">
         <v>19.5</v>
       </c>
       <c r="Z44">
-        <v>46</v>
+        <v>95</v>
       </c>
       <c r="AA44">
         <v>160</v>
       </c>
       <c r="AB44">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC44">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD44">
         <v>22</v>
       </c>
       <c r="AE44">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AF44">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG44">
         <v>10</v>
@@ -9075,13 +9075,13 @@
         <v>80</v>
       </c>
       <c r="AJ44">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AK44">
         <v>19.5</v>
       </c>
       <c r="AL44">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="AM44">
         <v>130</v>
@@ -9093,19 +9093,19 @@
         <v>100</v>
       </c>
       <c r="AP44">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AQ44">
         <v>15.5</v>
       </c>
       <c r="AR44">
-        <v>6.6</v>
+        <v>24</v>
       </c>
       <c r="AS44">
-        <v>7.4</v>
+        <v>42</v>
       </c>
       <c r="AT44">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AU44">
         <v>8</v>
@@ -9114,19 +9114,19 @@
         <v>17.5</v>
       </c>
       <c r="AW44">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="AX44">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY44">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ44">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BA44">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="BB44">
         <v>15.5</v>
@@ -9135,16 +9135,16 @@
         <v>15.5</v>
       </c>
       <c r="BD44">
-        <v>6.4</v>
+        <v>23</v>
       </c>
       <c r="BE44">
-        <v>7.4</v>
+        <v>40</v>
       </c>
       <c r="BF44">
         <v>9.4</v>
       </c>
       <c r="BG44">
-        <v>7.2</v>
+        <v>36</v>
       </c>
       <c r="BH44" t="s">
         <v>255</v>
@@ -9176,7 +9176,7 @@
         <v>2.48</v>
       </c>
       <c r="I45">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="J45">
         <v>3.35</v>
@@ -9185,7 +9185,7 @@
         <v>3.6</v>
       </c>
       <c r="L45">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="M45">
         <v>1.08</v>
@@ -9203,7 +9203,7 @@
         <v>2.04</v>
       </c>
       <c r="R45">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="S45">
         <v>3.7</v>
@@ -9311,7 +9311,7 @@
         <v>34</v>
       </c>
       <c r="BB45">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="BC45">
         <v>30</v>
@@ -9349,13 +9349,13 @@
         <v>233</v>
       </c>
       <c r="F46">
-        <v>2.52</v>
+        <v>2.64</v>
       </c>
       <c r="G46">
         <v>2.74</v>
       </c>
       <c r="H46">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="I46">
         <v>3.1</v>
@@ -9364,10 +9364,10 @@
         <v>3.4</v>
       </c>
       <c r="K46">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="L46">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M46">
         <v>1.06</v>
@@ -9382,7 +9382,7 @@
         <v>1.98</v>
       </c>
       <c r="Q46">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="R46">
         <v>1.38</v>
@@ -9400,7 +9400,7 @@
         <v>1.48</v>
       </c>
       <c r="W46">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="X46">
         <v>19</v>
@@ -9534,10 +9534,10 @@
         <v>2.32</v>
       </c>
       <c r="G47">
-        <v>2.62</v>
+        <v>2.54</v>
       </c>
       <c r="H47">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="I47">
         <v>3.5</v>
@@ -9549,13 +9549,13 @@
         <v>3.8</v>
       </c>
       <c r="L47">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="M47">
         <v>1.07</v>
       </c>
       <c r="N47">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="O47">
         <v>1.33</v>
@@ -9570,7 +9570,7 @@
         <v>1.33</v>
       </c>
       <c r="S47">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="T47">
         <v>1.74</v>
@@ -9582,28 +9582,28 @@
         <v>1.4</v>
       </c>
       <c r="W47">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="X47">
         <v>17</v>
       </c>
       <c r="Y47">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Z47">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AA47">
         <v>70</v>
       </c>
       <c r="AB47">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AC47">
         <v>9.6</v>
       </c>
       <c r="AD47">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AE47">
         <v>46</v>
@@ -9618,7 +9618,7 @@
         <v>21</v>
       </c>
       <c r="AI47">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AJ47">
         <v>42</v>
@@ -9627,7 +9627,7 @@
         <v>34</v>
       </c>
       <c r="AL47">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AM47">
         <v>120</v>
@@ -9639,16 +9639,16 @@
         <v>44</v>
       </c>
       <c r="AP47">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AQ47">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR47">
         <v>16</v>
       </c>
       <c r="AS47">
-        <v>4.9</v>
+        <v>4</v>
       </c>
       <c r="AT47">
         <v>8.800000000000001</v>
@@ -9657,10 +9657,10 @@
         <v>6.8</v>
       </c>
       <c r="AV47">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AW47">
-        <v>4.7</v>
+        <v>3.95</v>
       </c>
       <c r="AX47">
         <v>11.5</v>
@@ -9672,25 +9672,25 @@
         <v>14.5</v>
       </c>
       <c r="BA47">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="BB47">
-        <v>4.7</v>
+        <v>3.9</v>
       </c>
       <c r="BC47">
         <v>19.5</v>
       </c>
       <c r="BD47">
-        <v>4.7</v>
+        <v>3.95</v>
       </c>
       <c r="BE47">
-        <v>5.1</v>
+        <v>4.1</v>
       </c>
       <c r="BF47">
         <v>15.5</v>
       </c>
       <c r="BG47">
-        <v>4.7</v>
+        <v>3.95</v>
       </c>
       <c r="BH47" t="s">
         <v>255</v>
@@ -9713,58 +9713,58 @@
         <v>235</v>
       </c>
       <c r="F48">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="G48">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="H48">
         <v>5.8</v>
       </c>
       <c r="I48">
-        <v>7</v>
+        <v>970</v>
       </c>
       <c r="J48">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="K48">
-        <v>5.4</v>
+        <v>950</v>
       </c>
       <c r="L48">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="M48">
         <v>1.03</v>
       </c>
       <c r="N48">
-        <v>5.4</v>
+        <v>2.12</v>
       </c>
       <c r="O48">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="P48">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="Q48">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="R48">
-        <v>1.61</v>
+        <v>1.35</v>
       </c>
       <c r="S48">
-        <v>2.3</v>
+        <v>1.92</v>
       </c>
       <c r="T48">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="U48">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="V48">
         <v>1.17</v>
       </c>
       <c r="W48">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="X48">
         <v>28</v>
@@ -9773,10 +9773,10 @@
         <v>30</v>
       </c>
       <c r="Z48">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AA48">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AB48">
         <v>12.5</v>
@@ -9812,25 +9812,25 @@
         <v>29</v>
       </c>
       <c r="AM48">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AN48">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AO48">
         <v>65</v>
       </c>
       <c r="AP48">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AQ48">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AR48">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="AS48">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT48">
         <v>10</v>
@@ -9842,7 +9842,7 @@
         <v>20</v>
       </c>
       <c r="AW48">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AX48">
         <v>10</v>
@@ -9854,7 +9854,7 @@
         <v>16</v>
       </c>
       <c r="BA48">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BB48">
         <v>12.5</v>
@@ -9863,16 +9863,16 @@
         <v>12.5</v>
       </c>
       <c r="BD48">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BE48">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BF48">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="BG48">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BH48" t="s">
         <v>255</v>
@@ -9898,16 +9898,16 @@
         <v>1.57</v>
       </c>
       <c r="G49">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="H49">
         <v>5.8</v>
       </c>
       <c r="I49">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="J49">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="K49">
         <v>5.2</v>
@@ -9925,28 +9925,28 @@
         <v>1.18</v>
       </c>
       <c r="P49">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="Q49">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="R49">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="S49">
-        <v>2.36</v>
+        <v>2.28</v>
       </c>
       <c r="T49">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="U49">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="V49">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="W49">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="X49">
         <v>30</v>
@@ -9955,10 +9955,10 @@
         <v>29</v>
       </c>
       <c r="Z49">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AA49">
-        <v>130</v>
+        <v>170</v>
       </c>
       <c r="AB49">
         <v>14</v>
@@ -9970,10 +9970,10 @@
         <v>24</v>
       </c>
       <c r="AE49">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AF49">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AG49">
         <v>12</v>
@@ -9985,7 +9985,7 @@
         <v>60</v>
       </c>
       <c r="AJ49">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AK49">
         <v>16.5</v>
@@ -10000,7 +10000,7 @@
         <v>6.8</v>
       </c>
       <c r="AO49">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AP49">
         <v>21</v>
@@ -10012,7 +10012,7 @@
         <v>36</v>
       </c>
       <c r="AS49">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AT49">
         <v>10</v>
@@ -10024,10 +10024,10 @@
         <v>18</v>
       </c>
       <c r="AW49">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AX49">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AY49">
         <v>8.800000000000001</v>
@@ -10048,13 +10048,13 @@
         <v>20</v>
       </c>
       <c r="BE49">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BF49">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="BG49">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BH49" t="s">
         <v>255</v>
@@ -10077,7 +10077,7 @@
         <v>237</v>
       </c>
       <c r="F50">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="G50">
         <v>1.55</v>
@@ -10089,13 +10089,13 @@
         <v>7</v>
       </c>
       <c r="J50">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="K50">
         <v>5.3</v>
       </c>
       <c r="L50">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="M50">
         <v>1.03</v>
@@ -10259,7 +10259,7 @@
         <v>238</v>
       </c>
       <c r="F51">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="G51">
         <v>2.06</v>
@@ -10277,7 +10277,7 @@
         <v>4.1</v>
       </c>
       <c r="L51">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="M51">
         <v>1.06</v>
@@ -10289,13 +10289,13 @@
         <v>1.26</v>
       </c>
       <c r="P51">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="Q51">
         <v>1.8</v>
       </c>
       <c r="R51">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S51">
         <v>2.96</v>
@@ -10322,7 +10322,7 @@
         <v>34</v>
       </c>
       <c r="AA51">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AB51">
         <v>11</v>
@@ -10352,7 +10352,7 @@
         <v>25</v>
       </c>
       <c r="AK51">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL51">
         <v>34</v>
@@ -10361,22 +10361,22 @@
         <v>100</v>
       </c>
       <c r="AN51">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AO51">
         <v>46</v>
       </c>
       <c r="AP51">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AQ51">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AR51">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AS51">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AT51">
         <v>9</v>
@@ -10385,10 +10385,10 @@
         <v>7.4</v>
       </c>
       <c r="AV51">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AW51">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AX51">
         <v>11</v>
@@ -10397,28 +10397,28 @@
         <v>9</v>
       </c>
       <c r="AZ51">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BA51">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BB51">
+        <v>6.4</v>
+      </c>
+      <c r="BC51">
         <v>6</v>
       </c>
-      <c r="BC51">
-        <v>5.9</v>
-      </c>
       <c r="BD51">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BE51">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BF51">
         <v>9.199999999999999</v>
       </c>
       <c r="BG51">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BH51" t="s">
         <v>255</v>
@@ -10444,7 +10444,7 @@
         <v>1.63</v>
       </c>
       <c r="G52">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="H52">
         <v>6</v>
@@ -10471,10 +10471,10 @@
         <v>1.32</v>
       </c>
       <c r="P52">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="Q52">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="R52">
         <v>1.37</v>
@@ -10492,7 +10492,7 @@
         <v>1.19</v>
       </c>
       <c r="W52">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="X52">
         <v>15.5</v>
@@ -10528,7 +10528,7 @@
         <v>23</v>
       </c>
       <c r="AI52">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AJ52">
         <v>15.5</v>
@@ -10549,13 +10549,13 @@
         <v>110</v>
       </c>
       <c r="AP52">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AQ52">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AR52">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AS52">
         <v>44</v>
@@ -10582,7 +10582,7 @@
         <v>21</v>
       </c>
       <c r="BA52">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="BB52">
         <v>14.5</v>
@@ -10632,7 +10632,7 @@
         <v>1.5</v>
       </c>
       <c r="I53">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="J53">
         <v>5.1</v>
@@ -10641,7 +10641,7 @@
         <v>5.2</v>
       </c>
       <c r="L53">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="M53">
         <v>1.04</v>
@@ -10653,16 +10653,16 @@
         <v>1.23</v>
       </c>
       <c r="P53">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="Q53">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="R53">
         <v>1.54</v>
       </c>
       <c r="S53">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="T53">
         <v>1.84</v>
@@ -10671,25 +10671,25 @@
         <v>2.16</v>
       </c>
       <c r="V53">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="W53">
         <v>1.16</v>
       </c>
       <c r="X53">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y53">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z53">
         <v>9.6</v>
       </c>
       <c r="AA53">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AB53">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AC53">
         <v>11</v>
@@ -10713,28 +10713,28 @@
         <v>29</v>
       </c>
       <c r="AJ53">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="AK53">
         <v>90</v>
       </c>
       <c r="AL53">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AM53">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AN53">
         <v>90</v>
       </c>
       <c r="AO53">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AP53">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ53">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR53">
         <v>9.199999999999999</v>
@@ -10743,13 +10743,13 @@
         <v>13</v>
       </c>
       <c r="AT53">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AU53">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AV53">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AW53">
         <v>13.5</v>
@@ -10761,13 +10761,13 @@
         <v>23</v>
       </c>
       <c r="AZ53">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BA53">
         <v>27</v>
       </c>
       <c r="BB53">
-        <v>110</v>
+        <v>46</v>
       </c>
       <c r="BC53">
         <v>75</v>
@@ -10805,16 +10805,16 @@
         <v>241</v>
       </c>
       <c r="F54">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="G54">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="H54">
+        <v>2.98</v>
+      </c>
+      <c r="I54">
         <v>3</v>
-      </c>
-      <c r="I54">
-        <v>3.1</v>
       </c>
       <c r="J54">
         <v>3.6</v>
@@ -10853,10 +10853,10 @@
         <v>2.2</v>
       </c>
       <c r="V54">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W54">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="X54">
         <v>14.5</v>
@@ -10919,7 +10919,7 @@
         <v>11.5</v>
       </c>
       <c r="AR54">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AS54">
         <v>44</v>
@@ -10955,7 +10955,7 @@
         <v>25</v>
       </c>
       <c r="BD54">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BE54">
         <v>38</v>
@@ -10987,7 +10987,7 @@
         <v>242</v>
       </c>
       <c r="F55">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="G55">
         <v>1.3</v>
@@ -10999,10 +10999,10 @@
         <v>13.5</v>
       </c>
       <c r="J55">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="K55">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="L55">
         <v>1.26</v>
@@ -11011,7 +11011,7 @@
         <v>1.03</v>
       </c>
       <c r="N55">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="O55">
         <v>1.17</v>
@@ -11026,10 +11026,10 @@
         <v>1.7</v>
       </c>
       <c r="S55">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="T55">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="U55">
         <v>1.94</v>
@@ -11041,7 +11041,7 @@
         <v>4.3</v>
       </c>
       <c r="X55">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Y55">
         <v>55</v>
@@ -11050,7 +11050,7 @@
         <v>130</v>
       </c>
       <c r="AA55">
-        <v>440</v>
+        <v>1000</v>
       </c>
       <c r="AB55">
         <v>11</v>
@@ -11059,7 +11059,7 @@
         <v>17.5</v>
       </c>
       <c r="AD55">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AE55">
         <v>190</v>
@@ -11071,7 +11071,7 @@
         <v>11</v>
       </c>
       <c r="AH55">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AI55">
         <v>140</v>
@@ -11092,19 +11092,19 @@
         <v>4.6</v>
       </c>
       <c r="AO55">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AP55">
-        <v>25</v>
+        <v>6.8</v>
       </c>
       <c r="AQ55">
+        <v>7.2</v>
+      </c>
+      <c r="AR55">
         <v>7.8</v>
       </c>
-      <c r="AR55">
-        <v>8.6</v>
-      </c>
       <c r="AS55">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AT55">
         <v>9.4</v>
@@ -11113,10 +11113,10 @@
         <v>11</v>
       </c>
       <c r="AV55">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AW55">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AX55">
         <v>7.8</v>
@@ -11128,7 +11128,7 @@
         <v>24</v>
       </c>
       <c r="BA55">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="BB55">
         <v>9.6</v>
@@ -11137,16 +11137,16 @@
         <v>12</v>
       </c>
       <c r="BD55">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="BE55">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="BF55">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="BG55">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="BH55" t="s">
         <v>255</v>
@@ -11169,10 +11169,10 @@
         <v>243</v>
       </c>
       <c r="F56">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="G56">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="H56">
         <v>3.5</v>
@@ -11181,28 +11181,28 @@
         <v>3.85</v>
       </c>
       <c r="J56">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="K56">
         <v>3.15</v>
       </c>
       <c r="L56">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="M56">
         <v>1.15</v>
       </c>
       <c r="N56">
-        <v>2.32</v>
+        <v>2.22</v>
       </c>
       <c r="O56">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="P56">
         <v>1.44</v>
       </c>
       <c r="Q56">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="R56">
         <v>1.14</v>
@@ -11214,13 +11214,13 @@
         <v>2.34</v>
       </c>
       <c r="U56">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="V56">
         <v>1.35</v>
       </c>
       <c r="W56">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="X56">
         <v>7.4</v>
@@ -11235,7 +11235,7 @@
         <v>110</v>
       </c>
       <c r="AB56">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AC56">
         <v>7.6</v>
@@ -11271,7 +11271,7 @@
         <v>310</v>
       </c>
       <c r="AN56">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AO56">
         <v>130</v>
@@ -11292,13 +11292,13 @@
         <v>5.8</v>
       </c>
       <c r="AU56">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV56">
         <v>15</v>
       </c>
       <c r="AW56">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX56">
         <v>11.5</v>
@@ -11307,28 +11307,28 @@
         <v>11</v>
       </c>
       <c r="AZ56">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BA56">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BB56">
         <v>32</v>
       </c>
       <c r="BC56">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BD56">
         <v>8.199999999999999</v>
       </c>
       <c r="BE56">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BF56">
         <v>36</v>
       </c>
       <c r="BG56">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BH56" t="s">
         <v>255</v>
@@ -11351,46 +11351,46 @@
         <v>244</v>
       </c>
       <c r="F57">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="G57">
-        <v>1.63</v>
+        <v>1.54</v>
       </c>
       <c r="H57">
-        <v>6.4</v>
+        <v>5.5</v>
       </c>
       <c r="I57">
-        <v>170</v>
+        <v>10.5</v>
       </c>
       <c r="J57">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="K57">
-        <v>9.4</v>
+        <v>5.1</v>
       </c>
       <c r="L57">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M57">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N57">
-        <v>1.89</v>
+        <v>1.01</v>
       </c>
       <c r="O57">
         <v>1.23</v>
       </c>
       <c r="P57">
-        <v>1.89</v>
+        <v>2.04</v>
       </c>
       <c r="Q57">
-        <v>1.64</v>
+        <v>1.76</v>
       </c>
       <c r="R57">
         <v>1.42</v>
       </c>
       <c r="S57">
-        <v>2.74</v>
+        <v>2.28</v>
       </c>
       <c r="T57">
         <v>1.01</v>
@@ -11399,67 +11399,67 @@
         <v>1.01</v>
       </c>
       <c r="V57">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="W57">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="X57">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Y57">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Z57">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AA57">
-        <v>1000</v>
+        <v>310</v>
       </c>
       <c r="AB57">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AC57">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AD57">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AE57">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AF57">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AG57">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH57">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AI57">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AJ57">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AK57">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AL57">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM57">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AN57">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AO57">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AP57">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ57">
         <v>1.03</v>
@@ -11471,13 +11471,13 @@
         <v>1.03</v>
       </c>
       <c r="AT57">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU57">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV57">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW57">
         <v>1.03</v>
@@ -11486,22 +11486,22 @@
         <v>1.03</v>
       </c>
       <c r="AY57">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ57">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA57">
         <v>1.03</v>
       </c>
       <c r="BB57">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC57">
         <v>1.03</v>
       </c>
       <c r="BD57">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE57">
         <v>1.03</v>
@@ -11715,13 +11715,13 @@
         <v>246</v>
       </c>
       <c r="F59">
-        <v>1.74</v>
+        <v>1.81</v>
       </c>
       <c r="G59">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="H59">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="I59">
         <v>6</v>
@@ -11730,7 +11730,7 @@
         <v>3.4</v>
       </c>
       <c r="K59">
-        <v>4.4</v>
+        <v>3.95</v>
       </c>
       <c r="L59">
         <v>1.41</v>
@@ -11757,16 +11757,16 @@
         <v>4.3</v>
       </c>
       <c r="T59">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="U59">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="V59">
         <v>1.2</v>
       </c>
       <c r="W59">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="X59">
         <v>13</v>
@@ -11781,10 +11781,10 @@
         <v>190</v>
       </c>
       <c r="AB59">
-        <v>970</v>
+        <v>7.2</v>
       </c>
       <c r="AC59">
-        <v>9.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AD59">
         <v>23</v>
@@ -11823,58 +11823,58 @@
         <v>160</v>
       </c>
       <c r="AP59">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="AQ59">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AR59">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="AS59">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="AT59">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="AU59">
         <v>4.2</v>
       </c>
       <c r="AV59">
+        <v>6.2</v>
+      </c>
+      <c r="AW59">
+        <v>3.2</v>
+      </c>
+      <c r="AX59">
+        <v>4.7</v>
+      </c>
+      <c r="AY59">
+        <v>9</v>
+      </c>
+      <c r="AZ59">
+        <v>3.55</v>
+      </c>
+      <c r="BA59">
+        <v>5.2</v>
+      </c>
+      <c r="BB59">
+        <v>6</v>
+      </c>
+      <c r="BC59">
+        <v>6.2</v>
+      </c>
+      <c r="BD59">
+        <v>3.9</v>
+      </c>
+      <c r="BE59">
+        <v>2.84</v>
+      </c>
+      <c r="BF59">
         <v>5.6</v>
       </c>
-      <c r="AW59">
-        <v>3.45</v>
-      </c>
-      <c r="AX59">
-        <v>4.3</v>
-      </c>
-      <c r="AY59">
-        <v>4.6</v>
-      </c>
-      <c r="AZ59">
-        <v>4.1</v>
-      </c>
-      <c r="BA59">
-        <v>4.8</v>
-      </c>
-      <c r="BB59">
-        <v>5.5</v>
-      </c>
-      <c r="BC59">
-        <v>5.6</v>
-      </c>
-      <c r="BD59">
-        <v>4.6</v>
-      </c>
-      <c r="BE59">
-        <v>3.05</v>
-      </c>
-      <c r="BF59">
-        <v>12</v>
-      </c>
       <c r="BG59">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="BH59" t="s">
         <v>255</v>
@@ -11897,19 +11897,19 @@
         <v>247</v>
       </c>
       <c r="F60">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="G60">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="H60">
         <v>6.4</v>
       </c>
       <c r="I60">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="J60">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K60">
         <v>3.9</v>
@@ -11948,7 +11948,7 @@
         <v>1.16</v>
       </c>
       <c r="W60">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="X60">
         <v>12</v>
@@ -11957,7 +11957,7 @@
         <v>970</v>
       </c>
       <c r="Z60">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="AA60">
         <v>290</v>
@@ -11993,7 +11993,7 @@
         <v>29</v>
       </c>
       <c r="AL60">
-        <v>710</v>
+        <v>65</v>
       </c>
       <c r="AM60">
         <v>250</v>
@@ -12008,22 +12008,22 @@
         <v>9.6</v>
       </c>
       <c r="AQ60">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AR60">
         <v>26</v>
       </c>
       <c r="AS60">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AT60">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AU60">
         <v>7.8</v>
       </c>
       <c r="AV60">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AW60">
         <v>40</v>
@@ -12038,7 +12038,7 @@
         <v>19.5</v>
       </c>
       <c r="BA60">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BB60">
         <v>14</v>
@@ -12047,7 +12047,7 @@
         <v>18</v>
       </c>
       <c r="BD60">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BE60">
         <v>90</v>
@@ -12079,13 +12079,13 @@
         <v>248</v>
       </c>
       <c r="F61">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="G61">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="H61">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="I61">
         <v>7</v>
@@ -12094,49 +12094,49 @@
         <v>3.15</v>
       </c>
       <c r="K61">
-        <v>6</v>
+        <v>3.9</v>
       </c>
       <c r="L61">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="M61">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N61">
-        <v>1.55</v>
+        <v>2.88</v>
       </c>
       <c r="O61">
-        <v>1.09</v>
+        <v>1.43</v>
       </c>
       <c r="P61">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="Q61">
+        <v>2.28</v>
+      </c>
+      <c r="R61">
+        <v>1.23</v>
+      </c>
+      <c r="S61">
+        <v>4.4</v>
+      </c>
+      <c r="T61">
+        <v>1.94</v>
+      </c>
+      <c r="U61">
+        <v>1.62</v>
+      </c>
+      <c r="V61">
+        <v>1.17</v>
+      </c>
+      <c r="W61">
         <v>2.18</v>
       </c>
-      <c r="R61">
-        <v>1.18</v>
-      </c>
-      <c r="S61">
-        <v>3.85</v>
-      </c>
-      <c r="T61">
-        <v>1.01</v>
-      </c>
-      <c r="U61">
-        <v>1.01</v>
-      </c>
-      <c r="V61">
-        <v>1.13</v>
-      </c>
-      <c r="W61">
-        <v>2.14</v>
-      </c>
       <c r="X61">
         <v>1000</v>
       </c>
       <c r="Y61">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Z61">
         <v>1000</v>
@@ -12145,40 +12145,40 @@
         <v>1000</v>
       </c>
       <c r="AB61">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC61">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD61">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AE61">
         <v>1000</v>
       </c>
       <c r="AF61">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="AG61">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AH61">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AI61">
         <v>1000</v>
       </c>
       <c r="AJ61">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AK61">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AL61">
         <v>1000</v>
       </c>
       <c r="AM61">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AN61">
         <v>1000</v>
@@ -12187,58 +12187,58 @@
         <v>1000</v>
       </c>
       <c r="AP61">
-        <v>1.03</v>
+        <v>2.7</v>
       </c>
       <c r="AQ61">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AR61">
-        <v>1.03</v>
+        <v>2.7</v>
       </c>
       <c r="AS61">
-        <v>1.03</v>
+        <v>2.7</v>
       </c>
       <c r="AT61">
-        <v>1.03</v>
+        <v>2.08</v>
       </c>
       <c r="AU61">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="AV61">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="AW61">
-        <v>1.03</v>
+        <v>2.7</v>
       </c>
       <c r="AX61">
-        <v>1.03</v>
+        <v>1.97</v>
       </c>
       <c r="AY61">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AZ61">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="BA61">
-        <v>1.03</v>
+        <v>2.7</v>
       </c>
       <c r="BB61">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="BC61">
-        <v>1.03</v>
+        <v>19</v>
       </c>
       <c r="BD61">
-        <v>1.03</v>
+        <v>2.7</v>
       </c>
       <c r="BE61">
-        <v>1.03</v>
+        <v>2.68</v>
       </c>
       <c r="BF61">
-        <v>1.01</v>
+        <v>2.7</v>
       </c>
       <c r="BG61">
-        <v>1.01</v>
+        <v>2.7</v>
       </c>
       <c r="BH61" t="s">
         <v>255</v>
@@ -12261,22 +12261,22 @@
         <v>249</v>
       </c>
       <c r="F62">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="G62">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="H62">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="I62">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="J62">
         <v>2.9</v>
       </c>
       <c r="K62">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L62">
         <v>1.47</v>
@@ -12285,7 +12285,7 @@
         <v>1.11</v>
       </c>
       <c r="N62">
-        <v>2.52</v>
+        <v>2.74</v>
       </c>
       <c r="O62">
         <v>1.48</v>
@@ -12294,13 +12294,13 @@
         <v>1.58</v>
       </c>
       <c r="Q62">
-        <v>2.28</v>
+        <v>2.42</v>
       </c>
       <c r="R62">
         <v>1.21</v>
       </c>
       <c r="S62">
-        <v>3.55</v>
+        <v>4.4</v>
       </c>
       <c r="T62">
         <v>2.1</v>
@@ -12309,10 +12309,10 @@
         <v>1.75</v>
       </c>
       <c r="V62">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="W62">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="X62">
         <v>11</v>
@@ -12354,7 +12354,7 @@
         <v>28</v>
       </c>
       <c r="AK62">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AL62">
         <v>65</v>
@@ -12369,46 +12369,46 @@
         <v>160</v>
       </c>
       <c r="AP62">
-        <v>3.55</v>
+        <v>7.4</v>
       </c>
       <c r="AQ62">
-        <v>3.95</v>
+        <v>10</v>
       </c>
       <c r="AR62">
         <v>4.7</v>
       </c>
       <c r="AS62">
+        <v>5.2</v>
+      </c>
+      <c r="AT62">
+        <v>5.4</v>
+      </c>
+      <c r="AU62">
+        <v>6</v>
+      </c>
+      <c r="AV62">
+        <v>16</v>
+      </c>
+      <c r="AW62">
         <v>5.1</v>
       </c>
-      <c r="AT62">
-        <v>3.15</v>
-      </c>
-      <c r="AU62">
-        <v>3.3</v>
-      </c>
-      <c r="AV62">
-        <v>4.3</v>
-      </c>
-      <c r="AW62">
-        <v>5</v>
-      </c>
       <c r="AX62">
-        <v>3.7</v>
+        <v>8.4</v>
       </c>
       <c r="AY62">
-        <v>3.7</v>
+        <v>8.4</v>
       </c>
       <c r="AZ62">
-        <v>4.4</v>
+        <v>18.5</v>
       </c>
       <c r="BA62">
         <v>5.1</v>
       </c>
       <c r="BB62">
-        <v>4.4</v>
+        <v>18</v>
       </c>
       <c r="BC62">
-        <v>4.5</v>
+        <v>19.5</v>
       </c>
       <c r="BD62">
         <v>4.9</v>
@@ -12417,10 +12417,10 @@
         <v>5.2</v>
       </c>
       <c r="BF62">
-        <v>4.4</v>
+        <v>16.5</v>
       </c>
       <c r="BG62">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BH62" t="s">
         <v>255</v>
@@ -12443,22 +12443,22 @@
         <v>250</v>
       </c>
       <c r="F63">
-        <v>2.02</v>
+        <v>2.14</v>
       </c>
       <c r="G63">
         <v>2.56</v>
       </c>
       <c r="H63">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="I63">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="J63">
         <v>2.66</v>
       </c>
       <c r="K63">
-        <v>5.6</v>
+        <v>3.3</v>
       </c>
       <c r="L63">
         <v>1.01</v>
@@ -12467,10 +12467,10 @@
         <v>1.01</v>
       </c>
       <c r="N63">
-        <v>1.37</v>
+        <v>1.49</v>
       </c>
       <c r="O63">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="P63">
         <v>1.37</v>
@@ -12485,13 +12485,13 @@
         <v>2.42</v>
       </c>
       <c r="T63">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="U63">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="V63">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="W63">
         <v>1.64</v>
@@ -12625,46 +12625,46 @@
         <v>251</v>
       </c>
       <c r="F64">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="G64">
-        <v>2.08</v>
+        <v>1.9</v>
       </c>
       <c r="H64">
-        <v>4.4</v>
+        <v>5.4</v>
       </c>
       <c r="I64">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="J64">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="K64">
-        <v>6.4</v>
+        <v>3.75</v>
       </c>
       <c r="L64">
         <v>1.01</v>
       </c>
       <c r="M64">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N64">
-        <v>1.42</v>
+        <v>2.48</v>
       </c>
       <c r="O64">
-        <v>1.02</v>
+        <v>1.46</v>
       </c>
       <c r="P64">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="Q64">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="R64">
         <v>1.17</v>
       </c>
       <c r="S64">
-        <v>2.3</v>
+        <v>4.8</v>
       </c>
       <c r="T64">
         <v>1.01</v>
@@ -12673,10 +12673,10 @@
         <v>1.01</v>
       </c>
       <c r="V64">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="W64">
-        <v>1.92</v>
+        <v>2.12</v>
       </c>
       <c r="X64">
         <v>1000</v>
@@ -12807,19 +12807,19 @@
         <v>252</v>
       </c>
       <c r="F65">
-        <v>1.27</v>
+        <v>1.04</v>
       </c>
       <c r="G65">
         <v>970</v>
       </c>
       <c r="H65">
-        <v>1.27</v>
+        <v>1.09</v>
       </c>
       <c r="I65">
         <v>970</v>
       </c>
       <c r="J65">
-        <v>1.09</v>
+        <v>1.92</v>
       </c>
       <c r="K65">
         <v>950</v>
@@ -12837,7 +12837,7 @@
         <v>1.15</v>
       </c>
       <c r="P65">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="Q65">
         <v>1.15</v>
@@ -12989,10 +12989,10 @@
         <v>253</v>
       </c>
       <c r="F66">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="G66">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="H66">
         <v>2.42</v>
@@ -13001,25 +13001,25 @@
         <v>2.62</v>
       </c>
       <c r="J66">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="K66">
         <v>3.05</v>
       </c>
       <c r="L66">
-        <v>1.68</v>
+        <v>1.58</v>
       </c>
       <c r="M66">
         <v>1.17</v>
       </c>
       <c r="N66">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="O66">
         <v>1.73</v>
       </c>
       <c r="P66">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="Q66">
         <v>3.2</v>
@@ -13070,7 +13070,7 @@
         <v>30</v>
       </c>
       <c r="AG66">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AH66">
         <v>38</v>
@@ -13091,7 +13091,7 @@
         <v>380</v>
       </c>
       <c r="AN66">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AO66">
         <v>70</v>
@@ -13106,7 +13106,7 @@
         <v>11.5</v>
       </c>
       <c r="AS66">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AT66">
         <v>7.2</v>
@@ -13118,7 +13118,7 @@
         <v>11.5</v>
       </c>
       <c r="AW66">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AX66">
         <v>21</v>
@@ -13136,19 +13136,19 @@
         <v>5.1</v>
       </c>
       <c r="BC66">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BD66">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BE66">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BF66">
         <v>5.2</v>
       </c>
       <c r="BG66">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BH66" t="s">
         <v>255</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-04.xlsx
@@ -805,7 +805,7 @@
     <t>Deportes Recoleta</t>
   </si>
   <si>
-    <t>2026-05-03 19:26:41</t>
+    <t>2026-05-03 21:42:42</t>
   </si>
 </sst>
 </file>
@@ -1365,16 +1365,16 @@
         <v>194</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>2.54</v>
       </c>
       <c r="G2">
         <v>5.8</v>
       </c>
       <c r="H2">
-        <v>1.88</v>
+        <v>2.08</v>
       </c>
       <c r="I2">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="J2">
         <v>2.86</v>
@@ -1386,13 +1386,13 @@
         <v>1.01</v>
       </c>
       <c r="M2">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="N2">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="O2">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="P2">
         <v>1.25</v>
@@ -1404,13 +1404,13 @@
         <v>1.18</v>
       </c>
       <c r="S2">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="T2">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="U2">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V2">
         <v>1.48</v>
@@ -1419,112 +1419,112 @@
         <v>1.35</v>
       </c>
       <c r="X2">
-        <v>90</v>
+        <v>970</v>
       </c>
       <c r="Y2">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="Z2">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AA2">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB2">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AC2">
         <v>42</v>
       </c>
       <c r="AD2">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AE2">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AF2">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AG2">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AH2">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AI2">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AJ2">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK2">
-        <v>1000</v>
+        <v>290</v>
       </c>
       <c r="AL2">
-        <v>1000</v>
+        <v>390</v>
       </c>
       <c r="AM2">
         <v>1000</v>
       </c>
       <c r="AN2">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AO2">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AP2">
-        <v>1.02</v>
+        <v>1.23</v>
       </c>
       <c r="AQ2">
-        <v>1.03</v>
+        <v>1.35</v>
       </c>
       <c r="AR2">
-        <v>1.03</v>
+        <v>1.36</v>
       </c>
       <c r="AS2">
-        <v>1.03</v>
+        <v>1.37</v>
       </c>
       <c r="AT2">
-        <v>1.03</v>
+        <v>1.36</v>
       </c>
       <c r="AU2">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="AV2">
-        <v>1.03</v>
+        <v>1.35</v>
       </c>
       <c r="AW2">
-        <v>1.03</v>
+        <v>1.37</v>
       </c>
       <c r="AX2">
-        <v>1.03</v>
+        <v>1.37</v>
       </c>
       <c r="AY2">
-        <v>1.03</v>
+        <v>1.36</v>
       </c>
       <c r="AZ2">
-        <v>1.03</v>
+        <v>1.36</v>
       </c>
       <c r="BA2">
-        <v>1.03</v>
+        <v>1.38</v>
       </c>
       <c r="BB2">
-        <v>1.03</v>
+        <v>1.38</v>
       </c>
       <c r="BC2">
-        <v>1.03</v>
+        <v>1.38</v>
       </c>
       <c r="BD2">
-        <v>1.03</v>
+        <v>1.38</v>
       </c>
       <c r="BE2">
-        <v>1.03</v>
+        <v>1.38</v>
       </c>
       <c r="BF2">
-        <v>1.03</v>
+        <v>1.55</v>
       </c>
       <c r="BG2">
-        <v>1.03</v>
+        <v>1.55</v>
       </c>
       <c r="BH2" t="s">
         <v>263</v>
@@ -1550,28 +1550,28 @@
         <v>1.95</v>
       </c>
       <c r="G3">
-        <v>3.85</v>
+        <v>4.5</v>
       </c>
       <c r="H3">
         <v>1.95</v>
       </c>
       <c r="I3">
-        <v>3.85</v>
+        <v>4.5</v>
       </c>
       <c r="J3">
         <v>2.9</v>
       </c>
       <c r="K3">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="L3">
         <v>1.01</v>
       </c>
       <c r="M3">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="N3">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="O3">
         <v>1.44</v>
@@ -1586,127 +1586,127 @@
         <v>1.21</v>
       </c>
       <c r="S3">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="T3">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="U3">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V3">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="W3">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="X3">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="Y3">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Z3">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB3">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AC3">
         <v>42</v>
       </c>
       <c r="AD3">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AE3">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF3">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG3">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AH3">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AI3">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK3">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL3">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM3">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN3">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AO3">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AP3">
-        <v>1.02</v>
+        <v>4.9</v>
       </c>
       <c r="AQ3">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="AR3">
-        <v>1.03</v>
+        <v>1.33</v>
       </c>
       <c r="AS3">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="AT3">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="AU3">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AV3">
-        <v>1.03</v>
+        <v>1.32</v>
       </c>
       <c r="AW3">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="AX3">
-        <v>1.03</v>
+        <v>1.33</v>
       </c>
       <c r="AY3">
-        <v>1.03</v>
+        <v>1.32</v>
       </c>
       <c r="AZ3">
-        <v>1.03</v>
+        <v>1.32</v>
       </c>
       <c r="BA3">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="BB3">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="BC3">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="BD3">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="BE3">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="BF3">
-        <v>1.03</v>
+        <v>1.55</v>
       </c>
       <c r="BG3">
-        <v>1.03</v>
+        <v>1.55</v>
       </c>
       <c r="BH3" t="s">
         <v>263</v>
@@ -1729,7 +1729,7 @@
         <v>196</v>
       </c>
       <c r="F4">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="G4">
         <v>4.2</v>
@@ -1744,7 +1744,7 @@
         <v>3</v>
       </c>
       <c r="K4">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L4">
         <v>1.46</v>
@@ -1762,16 +1762,16 @@
         <v>1.64</v>
       </c>
       <c r="Q4">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="R4">
         <v>1.24</v>
       </c>
       <c r="S4">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="T4">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="U4">
         <v>1.87</v>
@@ -1780,7 +1780,7 @@
         <v>1.65</v>
       </c>
       <c r="W4">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="X4">
         <v>12</v>
@@ -1792,7 +1792,7 @@
         <v>16</v>
       </c>
       <c r="AA4">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AB4">
         <v>13.5</v>
@@ -1828,67 +1828,67 @@
         <v>75</v>
       </c>
       <c r="AM4">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN4">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AO4">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AP4">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AQ4">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="AR4">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AS4">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="AT4">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AU4">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="AV4">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AW4">
+        <v>5.3</v>
+      </c>
+      <c r="AX4">
         <v>5.1</v>
       </c>
-      <c r="AX4">
-        <v>5</v>
-      </c>
       <c r="AY4">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AZ4">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BA4">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BB4">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BC4">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BD4">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BE4">
+        <v>6</v>
+      </c>
+      <c r="BF4">
         <v>5.9</v>
       </c>
-      <c r="BF4">
-        <v>5.6</v>
-      </c>
       <c r="BG4">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BH4" t="s">
         <v>263</v>
@@ -1911,7 +1911,7 @@
         <v>197</v>
       </c>
       <c r="F5">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="G5">
         <v>3.4</v>
@@ -1920,7 +1920,7 @@
         <v>2.7</v>
       </c>
       <c r="I5">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="J5">
         <v>2.78</v>
@@ -1929,13 +1929,13 @@
         <v>3.25</v>
       </c>
       <c r="L5">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="M5">
         <v>1.11</v>
       </c>
       <c r="N5">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="O5">
         <v>1.46</v>
@@ -1944,7 +1944,7 @@
         <v>1.54</v>
       </c>
       <c r="Q5">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="R5">
         <v>1.2</v>
@@ -1959,13 +1959,13 @@
         <v>1.82</v>
       </c>
       <c r="V5">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W5">
         <v>1.42</v>
       </c>
       <c r="X5">
-        <v>90</v>
+        <v>16.5</v>
       </c>
       <c r="Y5">
         <v>970</v>
@@ -2013,64 +2013,64 @@
         <v>1000</v>
       </c>
       <c r="AN5">
-        <v>60</v>
+        <v>600</v>
       </c>
       <c r="AO5">
-        <v>48</v>
+        <v>600</v>
       </c>
       <c r="AP5">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AQ5">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AR5">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AS5">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="AT5">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AU5">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="AV5">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="AW5">
+        <v>6.4</v>
+      </c>
+      <c r="AX5">
         <v>5.6</v>
       </c>
-      <c r="AX5">
-        <v>5.3</v>
-      </c>
       <c r="AY5">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AZ5">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BA5">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="BB5">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="BC5">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="BD5">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="BE5">
-        <v>6.2</v>
+        <v>4.2</v>
       </c>
       <c r="BF5">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="BG5">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="BH5" t="s">
         <v>263</v>
@@ -2093,64 +2093,64 @@
         <v>198</v>
       </c>
       <c r="F6">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="G6">
-        <v>1.74</v>
+        <v>1.58</v>
       </c>
       <c r="H6">
-        <v>5.5</v>
+        <v>7.6</v>
       </c>
       <c r="I6">
-        <v>8.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="J6">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="K6">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="L6">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="M6">
         <v>1.08</v>
       </c>
       <c r="N6">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="O6">
         <v>1.35</v>
       </c>
       <c r="P6">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="Q6">
-        <v>1.93</v>
+        <v>2.04</v>
       </c>
       <c r="R6">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S6">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="T6">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="U6">
-        <v>1.79</v>
+        <v>1.68</v>
       </c>
       <c r="V6">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="W6">
-        <v>2.34</v>
+        <v>2.74</v>
       </c>
       <c r="X6">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="Y6">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="Z6">
         <v>500</v>
@@ -2162,7 +2162,7 @@
         <v>13</v>
       </c>
       <c r="AC6">
-        <v>10.5</v>
+        <v>16.5</v>
       </c>
       <c r="AD6">
         <v>500</v>
@@ -2171,10 +2171,10 @@
         <v>700</v>
       </c>
       <c r="AF6">
-        <v>11</v>
+        <v>19.5</v>
       </c>
       <c r="AG6">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="AH6">
         <v>500</v>
@@ -2183,10 +2183,10 @@
         <v>700</v>
       </c>
       <c r="AJ6">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="AK6">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AL6">
         <v>500</v>
@@ -2195,7 +2195,7 @@
         <v>700</v>
       </c>
       <c r="AN6">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="AO6">
         <v>700</v>
@@ -2204,55 +2204,55 @@
         <v>5.6</v>
       </c>
       <c r="AQ6">
-        <v>5.1</v>
+        <v>7.2</v>
       </c>
       <c r="AR6">
-        <v>5.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS6">
-        <v>6</v>
+        <v>4.2</v>
       </c>
       <c r="AT6">
         <v>4.2</v>
       </c>
       <c r="AU6">
+        <v>4.9</v>
+      </c>
+      <c r="AV6">
+        <v>7.6</v>
+      </c>
+      <c r="AW6">
+        <v>5.4</v>
+      </c>
+      <c r="AX6">
+        <v>4.4</v>
+      </c>
+      <c r="AY6">
         <v>5.1</v>
       </c>
-      <c r="AV6">
-        <v>5</v>
-      </c>
-      <c r="AW6">
-        <v>5.9</v>
-      </c>
-      <c r="AX6">
-        <v>4.9</v>
-      </c>
-      <c r="AY6">
-        <v>7</v>
-      </c>
       <c r="AZ6">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="BA6">
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
       <c r="BB6">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="BC6">
         <v>4.8</v>
       </c>
       <c r="BD6">
-        <v>5.4</v>
+        <v>3.15</v>
       </c>
       <c r="BE6">
-        <v>6</v>
+        <v>3.25</v>
       </c>
       <c r="BF6">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="BG6">
-        <v>5.6</v>
+        <v>4.2</v>
       </c>
       <c r="BH6" t="s">
         <v>263</v>
@@ -2278,13 +2278,13 @@
         <v>3.2</v>
       </c>
       <c r="G7">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="H7">
         <v>2.34</v>
       </c>
       <c r="I7">
-        <v>2.86</v>
+        <v>2.76</v>
       </c>
       <c r="J7">
         <v>2.88</v>
@@ -2293,43 +2293,43 @@
         <v>3.85</v>
       </c>
       <c r="L7">
-        <v>1.45</v>
+        <v>1.51</v>
       </c>
       <c r="M7">
         <v>1.11</v>
       </c>
       <c r="N7">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="O7">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="P7">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="Q7">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="R7">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S7">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="T7">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="U7">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="V7">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="W7">
         <v>1.35</v>
       </c>
       <c r="X7">
-        <v>970</v>
+        <v>19.5</v>
       </c>
       <c r="Y7">
         <v>970</v>
@@ -2377,64 +2377,64 @@
         <v>500</v>
       </c>
       <c r="AN7">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO7">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP7">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="AQ7">
-        <v>3.45</v>
+        <v>6.6</v>
       </c>
       <c r="AR7">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="AS7">
-        <v>2.72</v>
+        <v>5.8</v>
       </c>
       <c r="AT7">
-        <v>3.8</v>
+        <v>3.05</v>
       </c>
       <c r="AU7">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="AV7">
-        <v>3.9</v>
+        <v>2.96</v>
       </c>
       <c r="AW7">
-        <v>2.7</v>
+        <v>5.7</v>
       </c>
       <c r="AX7">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="AY7">
-        <v>3.65</v>
+        <v>3.05</v>
       </c>
       <c r="AZ7">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="BA7">
-        <v>2.84</v>
+        <v>6</v>
       </c>
       <c r="BB7">
-        <v>2.74</v>
+        <v>6.2</v>
       </c>
       <c r="BC7">
-        <v>2.74</v>
+        <v>6</v>
       </c>
       <c r="BD7">
-        <v>2.76</v>
+        <v>6.2</v>
       </c>
       <c r="BE7">
-        <v>2.74</v>
+        <v>4.3</v>
       </c>
       <c r="BF7">
-        <v>2.76</v>
+        <v>6.2</v>
       </c>
       <c r="BG7">
-        <v>2.7</v>
+        <v>5.9</v>
       </c>
       <c r="BH7" t="s">
         <v>263</v>
@@ -2463,13 +2463,13 @@
         <v>1.7</v>
       </c>
       <c r="H8">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="I8">
         <v>8.4</v>
       </c>
       <c r="J8">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K8">
         <v>4.5</v>
@@ -2481,22 +2481,22 @@
         <v>1.07</v>
       </c>
       <c r="N8">
-        <v>2.7</v>
+        <v>3.15</v>
       </c>
       <c r="O8">
         <v>1.34</v>
       </c>
       <c r="P8">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
       <c r="Q8">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="R8">
         <v>1.32</v>
       </c>
       <c r="S8">
-        <v>2.72</v>
+        <v>3.25</v>
       </c>
       <c r="T8">
         <v>1.99</v>
@@ -2505,16 +2505,16 @@
         <v>1.83</v>
       </c>
       <c r="V8">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="W8">
         <v>2.42</v>
       </c>
       <c r="X8">
-        <v>90</v>
+        <v>16.5</v>
       </c>
       <c r="Y8">
-        <v>40</v>
+        <v>500</v>
       </c>
       <c r="Z8">
         <v>500</v>
@@ -2535,13 +2535,13 @@
         <v>700</v>
       </c>
       <c r="AF8">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AG8">
         <v>36</v>
       </c>
       <c r="AH8">
-        <v>500</v>
+        <v>70</v>
       </c>
       <c r="AI8">
         <v>700</v>
@@ -2550,7 +2550,7 @@
         <v>180</v>
       </c>
       <c r="AK8">
-        <v>65</v>
+        <v>22</v>
       </c>
       <c r="AL8">
         <v>500</v>
@@ -2559,7 +2559,7 @@
         <v>700</v>
       </c>
       <c r="AN8">
-        <v>27</v>
+        <v>12.5</v>
       </c>
       <c r="AO8">
         <v>700</v>
@@ -2568,13 +2568,13 @@
         <v>6.2</v>
       </c>
       <c r="AQ8">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="AR8">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AS8">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="AT8">
         <v>4.4</v>
@@ -2583,10 +2583,10 @@
         <v>5.6</v>
       </c>
       <c r="AV8">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="AW8">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="AX8">
         <v>5.1</v>
@@ -2595,28 +2595,28 @@
         <v>6.4</v>
       </c>
       <c r="AZ8">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BA8">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BB8">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="BC8">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BD8">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="BE8">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="BF8">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BG8">
-        <v>5.7</v>
+        <v>4.6</v>
       </c>
       <c r="BH8" t="s">
         <v>263</v>
@@ -2663,7 +2663,7 @@
         <v>1.1</v>
       </c>
       <c r="N9">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="O9">
         <v>1.43</v>
@@ -2738,7 +2738,7 @@
         <v>55</v>
       </c>
       <c r="AM9">
-        <v>190</v>
+        <v>500</v>
       </c>
       <c r="AN9">
         <v>26</v>
@@ -2824,7 +2824,7 @@
         <v>3.45</v>
       </c>
       <c r="G10">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="H10">
         <v>2.6</v>
@@ -2860,7 +2860,7 @@
         <v>1.16</v>
       </c>
       <c r="S10">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="T10">
         <v>2.16</v>
@@ -2884,7 +2884,7 @@
         <v>970</v>
       </c>
       <c r="AA10">
-        <v>50</v>
+        <v>220</v>
       </c>
       <c r="AB10">
         <v>9.4</v>
@@ -2893,40 +2893,40 @@
         <v>7.4</v>
       </c>
       <c r="AD10">
-        <v>970</v>
+        <v>36</v>
       </c>
       <c r="AE10">
-        <v>46</v>
+        <v>230</v>
       </c>
       <c r="AF10">
-        <v>22</v>
+        <v>500</v>
       </c>
       <c r="AG10">
         <v>970</v>
       </c>
       <c r="AH10">
-        <v>26</v>
+        <v>500</v>
       </c>
       <c r="AI10">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AJ10">
-        <v>75</v>
+        <v>900</v>
       </c>
       <c r="AK10">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AL10">
-        <v>90</v>
+        <v>540</v>
       </c>
       <c r="AM10">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="AN10">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AO10">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AP10">
         <v>6.8</v>
@@ -2938,7 +2938,7 @@
         <v>12</v>
       </c>
       <c r="AS10">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AT10">
         <v>7.8</v>
@@ -2962,22 +2962,22 @@
         <v>19.5</v>
       </c>
       <c r="BA10">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB10">
+        <v>23</v>
+      </c>
+      <c r="BC10">
         <v>8</v>
-      </c>
-      <c r="BB10">
-        <v>8.4</v>
-      </c>
-      <c r="BC10">
-        <v>7.8</v>
       </c>
       <c r="BD10">
         <v>8.199999999999999</v>
       </c>
       <c r="BE10">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF10">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BG10">
         <v>42</v>
@@ -3003,10 +3003,10 @@
         <v>203</v>
       </c>
       <c r="F11">
+        <v>1.75</v>
+      </c>
+      <c r="G11">
         <v>1.76</v>
-      </c>
-      <c r="G11">
-        <v>1.77</v>
       </c>
       <c r="H11">
         <v>5.2</v>
@@ -3030,31 +3030,31 @@
         <v>4.7</v>
       </c>
       <c r="O11">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P11">
         <v>2.28</v>
       </c>
       <c r="Q11">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="R11">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S11">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="T11">
         <v>1.76</v>
       </c>
       <c r="U11">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="V11">
         <v>1.23</v>
       </c>
       <c r="W11">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="X11">
         <v>19</v>
@@ -3066,10 +3066,10 @@
         <v>40</v>
       </c>
       <c r="AA11">
-        <v>190</v>
+        <v>700</v>
       </c>
       <c r="AB11">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AC11">
         <v>9.199999999999999</v>
@@ -3087,7 +3087,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AH11">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI11">
         <v>60</v>
@@ -3111,13 +3111,13 @@
         <v>65</v>
       </c>
       <c r="AP11">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AQ11">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AR11">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AS11">
         <v>100</v>
@@ -3126,7 +3126,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AU11">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV11">
         <v>18.5</v>
@@ -3156,7 +3156,7 @@
         <v>28</v>
       </c>
       <c r="BE11">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BF11">
         <v>8.4</v>
@@ -3185,22 +3185,22 @@
         <v>204</v>
       </c>
       <c r="F12">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="G12">
         <v>3.75</v>
       </c>
       <c r="H12">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="I12">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="J12">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K12">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="L12">
         <v>1.4</v>
@@ -3233,7 +3233,7 @@
         <v>1.77</v>
       </c>
       <c r="V12">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="W12">
         <v>1.37</v>
@@ -3272,13 +3272,13 @@
         <v>40</v>
       </c>
       <c r="AI12">
-        <v>290</v>
+        <v>500</v>
       </c>
       <c r="AJ12">
         <v>900</v>
       </c>
       <c r="AK12">
-        <v>230</v>
+        <v>500</v>
       </c>
       <c r="AL12">
         <v>370</v>
@@ -3287,10 +3287,10 @@
         <v>580</v>
       </c>
       <c r="AN12">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="AO12">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AP12">
         <v>8.800000000000001</v>
@@ -3326,13 +3326,13 @@
         <v>14.5</v>
       </c>
       <c r="BA12">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BB12">
         <v>6.4</v>
       </c>
       <c r="BC12">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BD12">
         <v>6.4</v>
@@ -3367,13 +3367,13 @@
         <v>205</v>
       </c>
       <c r="F13">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="G13">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="H13">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="I13">
         <v>1.88</v>
@@ -3391,13 +3391,13 @@
         <v>1.06</v>
       </c>
       <c r="N13">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="O13">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="P13">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="Q13">
         <v>1.89</v>
@@ -3409,28 +3409,28 @@
         <v>3.3</v>
       </c>
       <c r="T13">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="U13">
         <v>2</v>
       </c>
       <c r="V13">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="W13">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="X13">
         <v>970</v>
       </c>
       <c r="Y13">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="Z13">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="AA13">
-        <v>22</v>
+        <v>900</v>
       </c>
       <c r="AB13">
         <v>970</v>
@@ -3439,13 +3439,13 @@
         <v>9.4</v>
       </c>
       <c r="AD13">
+        <v>10.5</v>
+      </c>
+      <c r="AE13">
         <v>970</v>
       </c>
-      <c r="AE13">
-        <v>22</v>
-      </c>
       <c r="AF13">
-        <v>48</v>
+        <v>100</v>
       </c>
       <c r="AG13">
         <v>21</v>
@@ -3454,31 +3454,31 @@
         <v>60</v>
       </c>
       <c r="AI13">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="AJ13">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK13">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c r="AL13">
-        <v>85</v>
+        <v>190</v>
       </c>
       <c r="AM13">
-        <v>130</v>
+        <v>580</v>
       </c>
       <c r="AN13">
-        <v>95</v>
+        <v>300</v>
       </c>
       <c r="AO13">
-        <v>970</v>
+        <v>55</v>
       </c>
       <c r="AP13">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="AQ13">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AR13">
         <v>8.199999999999999</v>
@@ -3499,31 +3499,31 @@
         <v>14.5</v>
       </c>
       <c r="AX13">
-        <v>5.7</v>
+        <v>7.8</v>
       </c>
       <c r="AY13">
         <v>15.5</v>
       </c>
       <c r="AZ13">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="BA13">
-        <v>5.7</v>
+        <v>7.6</v>
       </c>
       <c r="BB13">
-        <v>6.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC13">
-        <v>6</v>
+        <v>8.4</v>
       </c>
       <c r="BD13">
-        <v>6</v>
+        <v>8.4</v>
       </c>
       <c r="BE13">
-        <v>6.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF13">
-        <v>6.2</v>
+        <v>8.6</v>
       </c>
       <c r="BG13">
         <v>9</v>
@@ -3552,10 +3552,10 @@
         <v>1.38</v>
       </c>
       <c r="G14">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="H14">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="I14">
         <v>990</v>
@@ -3600,7 +3600,7 @@
         <v>1.07</v>
       </c>
       <c r="W14">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="X14">
         <v>1000</v>
@@ -3630,7 +3630,7 @@
         <v>970</v>
       </c>
       <c r="AG14">
-        <v>29</v>
+        <v>970</v>
       </c>
       <c r="AH14">
         <v>1000</v>
@@ -3639,7 +3639,7 @@
         <v>1000</v>
       </c>
       <c r="AJ14">
-        <v>22</v>
+        <v>900</v>
       </c>
       <c r="AK14">
         <v>1000</v>
@@ -3651,64 +3651,64 @@
         <v>1000</v>
       </c>
       <c r="AN14">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO14">
         <v>1000</v>
       </c>
       <c r="AP14">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="AQ14">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="AR14">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="AS14">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="AT14">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="AU14">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="AV14">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="AW14">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="AX14">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="AY14">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="AZ14">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="BA14">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="BB14">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BC14">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="BD14">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="BE14">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="BF14">
-        <v>1.05</v>
+        <v>4.1</v>
       </c>
       <c r="BG14">
-        <v>1.05</v>
+        <v>1.55</v>
       </c>
       <c r="BH14" t="s">
         <v>263</v>
@@ -3913,10 +3913,10 @@
         <v>208</v>
       </c>
       <c r="F16">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="G16">
-        <v>600</v>
+        <v>5.4</v>
       </c>
       <c r="H16">
         <v>2.7</v>
@@ -3961,115 +3961,115 @@
         <v>1.11</v>
       </c>
       <c r="V16">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="W16">
         <v>1.55</v>
       </c>
       <c r="X16">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="Y16">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Z16">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA16">
         <v>900</v>
       </c>
       <c r="AB16">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AC16">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="AD16">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AE16">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF16">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG16">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH16">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AI16">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ16">
         <v>900</v>
       </c>
       <c r="AK16">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL16">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM16">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN16">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO16">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP16">
         <v>3.5</v>
       </c>
       <c r="AQ16">
-        <v>1.03</v>
+        <v>1.19</v>
       </c>
       <c r="AR16">
-        <v>1.03</v>
+        <v>1.19</v>
       </c>
       <c r="AS16">
-        <v>1.03</v>
+        <v>1.19</v>
       </c>
       <c r="AT16">
-        <v>1.03</v>
+        <v>1.19</v>
       </c>
       <c r="AU16">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="AV16">
-        <v>1.03</v>
+        <v>1.19</v>
       </c>
       <c r="AW16">
-        <v>1.03</v>
+        <v>1.19</v>
       </c>
       <c r="AX16">
-        <v>1.03</v>
+        <v>1.19</v>
       </c>
       <c r="AY16">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AZ16">
-        <v>1.03</v>
+        <v>1.19</v>
       </c>
       <c r="BA16">
-        <v>1.03</v>
+        <v>1.19</v>
       </c>
       <c r="BB16">
-        <v>1.03</v>
+        <v>1.19</v>
       </c>
       <c r="BC16">
-        <v>1.03</v>
+        <v>1.19</v>
       </c>
       <c r="BD16">
-        <v>1.03</v>
+        <v>1.19</v>
       </c>
       <c r="BE16">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="BF16">
-        <v>1.05</v>
+        <v>1.19</v>
       </c>
       <c r="BG16">
         <v>1.55</v>
@@ -4134,7 +4134,7 @@
         <v>1.12</v>
       </c>
       <c r="S17">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T17">
         <v>1.11</v>
@@ -4230,7 +4230,7 @@
         <v>1.03</v>
       </c>
       <c r="AY17">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AZ17">
         <v>1.03</v>
@@ -4283,16 +4283,16 @@
         <v>1.59</v>
       </c>
       <c r="H18">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="I18">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J18">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="K18">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L18">
         <v>1.39</v>
@@ -4301,16 +4301,16 @@
         <v>1.07</v>
       </c>
       <c r="N18">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="O18">
         <v>1.31</v>
       </c>
       <c r="P18">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="Q18">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="R18">
         <v>1.33</v>
@@ -4319,13 +4319,13 @@
         <v>3</v>
       </c>
       <c r="T18">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="U18">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="V18">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="W18">
         <v>2.68</v>
@@ -4340,7 +4340,7 @@
         <v>85</v>
       </c>
       <c r="AA18">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="AB18">
         <v>7.8</v>
@@ -4349,10 +4349,10 @@
         <v>10.5</v>
       </c>
       <c r="AD18">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AE18">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AF18">
         <v>9</v>
@@ -4376,67 +4376,67 @@
         <v>55</v>
       </c>
       <c r="AM18">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AN18">
         <v>9.6</v>
       </c>
       <c r="AO18">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="AP18">
+        <v>5.3</v>
+      </c>
+      <c r="AQ18">
+        <v>6</v>
+      </c>
+      <c r="AR18">
+        <v>7.2</v>
+      </c>
+      <c r="AS18">
+        <v>7.6</v>
+      </c>
+      <c r="AT18">
+        <v>4</v>
+      </c>
+      <c r="AU18">
+        <v>4.5</v>
+      </c>
+      <c r="AV18">
+        <v>18</v>
+      </c>
+      <c r="AW18">
+        <v>7.6</v>
+      </c>
+      <c r="AX18">
+        <v>4.3</v>
+      </c>
+      <c r="AY18">
+        <v>4.5</v>
+      </c>
+      <c r="AZ18">
+        <v>6.2</v>
+      </c>
+      <c r="BA18">
+        <v>7.6</v>
+      </c>
+      <c r="BB18">
         <v>5.1</v>
       </c>
-      <c r="AQ18">
-        <v>5.9</v>
-      </c>
-      <c r="AR18">
-        <v>7</v>
-      </c>
-      <c r="AS18">
-        <v>7.4</v>
-      </c>
-      <c r="AT18">
+      <c r="BC18">
         <v>5.6</v>
       </c>
-      <c r="AU18">
+      <c r="BD18">
+        <v>26</v>
+      </c>
+      <c r="BE18">
+        <v>7.6</v>
+      </c>
+      <c r="BF18">
         <v>4.4</v>
       </c>
-      <c r="AV18">
-        <v>6.4</v>
-      </c>
-      <c r="AW18">
-        <v>7.2</v>
-      </c>
-      <c r="AX18">
-        <v>4.2</v>
-      </c>
-      <c r="AY18">
-        <v>4.4</v>
-      </c>
-      <c r="AZ18">
-        <v>6</v>
-      </c>
-      <c r="BA18">
-        <v>7.2</v>
-      </c>
-      <c r="BB18">
-        <v>5</v>
-      </c>
-      <c r="BC18">
-        <v>5.4</v>
-      </c>
-      <c r="BD18">
-        <v>6.6</v>
-      </c>
-      <c r="BE18">
-        <v>7.2</v>
-      </c>
-      <c r="BF18">
-        <v>4.3</v>
-      </c>
       <c r="BG18">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BH18" t="s">
         <v>263</v>
@@ -4474,7 +4474,7 @@
         <v>4.1</v>
       </c>
       <c r="K19">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="L19">
         <v>1.24</v>
@@ -4489,7 +4489,7 @@
         <v>1.2</v>
       </c>
       <c r="P19">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="Q19">
         <v>1.53</v>
@@ -4504,7 +4504,7 @@
         <v>1.65</v>
       </c>
       <c r="U19">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="V19">
         <v>2.32</v>
@@ -4609,7 +4609,7 @@
         <v>4</v>
       </c>
       <c r="BD19">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BE19">
         <v>4.1</v>
@@ -4618,7 +4618,7 @@
         <v>7</v>
       </c>
       <c r="BG19">
-        <v>6.6</v>
+        <v>3.05</v>
       </c>
       <c r="BH19" t="s">
         <v>263</v>
@@ -4823,16 +4823,16 @@
         <v>213</v>
       </c>
       <c r="F21">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="G21">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="H21">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="I21">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="J21">
         <v>4.1</v>
@@ -4874,16 +4874,16 @@
         <v>1.13</v>
       </c>
       <c r="W21">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="X21">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="Y21">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="Z21">
-        <v>75</v>
+        <v>420</v>
       </c>
       <c r="AA21">
         <v>1000</v>
@@ -4895,13 +4895,13 @@
         <v>10.5</v>
       </c>
       <c r="AD21">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="AE21">
         <v>180</v>
       </c>
       <c r="AF21">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AG21">
         <v>11</v>
@@ -4910,7 +4910,7 @@
         <v>28</v>
       </c>
       <c r="AI21">
-        <v>160</v>
+        <v>470</v>
       </c>
       <c r="AJ21">
         <v>14.5</v>
@@ -4919,10 +4919,10 @@
         <v>18.5</v>
       </c>
       <c r="AL21">
-        <v>48</v>
+        <v>110</v>
       </c>
       <c r="AM21">
-        <v>220</v>
+        <v>580</v>
       </c>
       <c r="AN21">
         <v>10</v>
@@ -4934,7 +4934,7 @@
         <v>11.5</v>
       </c>
       <c r="AQ21">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="AR21">
         <v>25</v>
@@ -4952,10 +4952,10 @@
         <v>22</v>
       </c>
       <c r="AW21">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AX21">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AY21">
         <v>8.800000000000001</v>
@@ -4964,10 +4964,10 @@
         <v>15.5</v>
       </c>
       <c r="BA21">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BB21">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BC21">
         <v>15</v>
@@ -4976,13 +4976,13 @@
         <v>32</v>
       </c>
       <c r="BE21">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="BF21">
         <v>8.6</v>
       </c>
       <c r="BG21">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="BH21" t="s">
         <v>263</v>
@@ -5005,13 +5005,13 @@
         <v>214</v>
       </c>
       <c r="F22">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="G22">
         <v>2.2</v>
       </c>
       <c r="H22">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="I22">
         <v>4.3</v>
@@ -5035,7 +5035,7 @@
         <v>1.39</v>
       </c>
       <c r="P22">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="Q22">
         <v>2.12</v>
@@ -5050,7 +5050,7 @@
         <v>1.89</v>
       </c>
       <c r="U22">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="V22">
         <v>1.31</v>
@@ -5116,7 +5116,7 @@
         <v>10</v>
       </c>
       <c r="AQ22">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR22">
         <v>13</v>
@@ -5134,7 +5134,7 @@
         <v>14</v>
       </c>
       <c r="AW22">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AX22">
         <v>11</v>
@@ -5143,10 +5143,10 @@
         <v>9.4</v>
       </c>
       <c r="AZ22">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA22">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BB22">
         <v>11.5</v>
@@ -5161,7 +5161,7 @@
         <v>10</v>
       </c>
       <c r="BF22">
-        <v>15.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG22">
         <v>9.800000000000001</v>
@@ -5196,13 +5196,13 @@
         <v>1.73</v>
       </c>
       <c r="I23">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="J23">
         <v>3.7</v>
       </c>
       <c r="K23">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L23">
         <v>1.41</v>
@@ -5217,31 +5217,31 @@
         <v>1.34</v>
       </c>
       <c r="P23">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="Q23">
         <v>2</v>
       </c>
       <c r="R23">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S23">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="T23">
         <v>1.93</v>
       </c>
       <c r="U23">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="V23">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="W23">
         <v>1.2</v>
       </c>
       <c r="X23">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="Y23">
         <v>8.199999999999999</v>
@@ -5265,40 +5265,40 @@
         <v>21</v>
       </c>
       <c r="AF23">
-        <v>46</v>
+        <v>100</v>
       </c>
       <c r="AG23">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="AH23">
-        <v>60</v>
+        <v>22</v>
       </c>
       <c r="AI23">
-        <v>42</v>
+        <v>150</v>
       </c>
       <c r="AJ23">
-        <v>180</v>
+        <v>900</v>
       </c>
       <c r="AK23">
-        <v>90</v>
+        <v>400</v>
       </c>
       <c r="AL23">
-        <v>90</v>
+        <v>320</v>
       </c>
       <c r="AM23">
-        <v>160</v>
+        <v>580</v>
       </c>
       <c r="AN23">
-        <v>130</v>
+        <v>410</v>
       </c>
       <c r="AO23">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AP23">
         <v>11</v>
       </c>
       <c r="AQ23">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AR23">
         <v>8.6</v>
@@ -5340,7 +5340,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BE23">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BF23">
         <v>9</v>
@@ -5369,7 +5369,7 @@
         <v>216</v>
       </c>
       <c r="F24">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="G24">
         <v>1.94</v>
@@ -5384,7 +5384,7 @@
         <v>3.65</v>
       </c>
       <c r="K24">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L24">
         <v>1.43</v>
@@ -5399,7 +5399,7 @@
         <v>1.36</v>
       </c>
       <c r="P24">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="Q24">
         <v>2.16</v>
@@ -5581,10 +5581,10 @@
         <v>1.32</v>
       </c>
       <c r="P25">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="Q25">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="R25">
         <v>1.33</v>
@@ -5605,16 +5605,16 @@
         <v>1.34</v>
       </c>
       <c r="X25">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="Y25">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="Z25">
         <v>17.5</v>
       </c>
       <c r="AA25">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AB25">
         <v>16.5</v>
@@ -5623,13 +5623,13 @@
         <v>8.4</v>
       </c>
       <c r="AD25">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AE25">
         <v>30</v>
       </c>
       <c r="AF25">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AG25">
         <v>18.5</v>
@@ -5638,10 +5638,10 @@
         <v>18.5</v>
       </c>
       <c r="AI25">
-        <v>48</v>
+        <v>110</v>
       </c>
       <c r="AJ25">
-        <v>85</v>
+        <v>440</v>
       </c>
       <c r="AK25">
         <v>55</v>
@@ -5650,7 +5650,7 @@
         <v>65</v>
       </c>
       <c r="AM25">
-        <v>120</v>
+        <v>580</v>
       </c>
       <c r="AN25">
         <v>55</v>
@@ -5659,7 +5659,7 @@
         <v>23</v>
       </c>
       <c r="AP25">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AQ25">
         <v>8.199999999999999</v>
@@ -5668,7 +5668,7 @@
         <v>12</v>
       </c>
       <c r="AS25">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="AT25">
         <v>11</v>
@@ -5683,7 +5683,7 @@
         <v>20</v>
       </c>
       <c r="AX25">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AY25">
         <v>12.5</v>
@@ -5692,22 +5692,22 @@
         <v>15</v>
       </c>
       <c r="BA25">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="BB25">
-        <v>4.6</v>
+        <v>5.7</v>
       </c>
       <c r="BC25">
-        <v>4.5</v>
+        <v>5.9</v>
       </c>
       <c r="BD25">
-        <v>4.6</v>
+        <v>5.7</v>
       </c>
       <c r="BE25">
-        <v>4.6</v>
+        <v>5.8</v>
       </c>
       <c r="BF25">
-        <v>4.5</v>
+        <v>8</v>
       </c>
       <c r="BG25">
         <v>15.5</v>
@@ -5796,7 +5796,7 @@
         <v>34</v>
       </c>
       <c r="AA26">
-        <v>85</v>
+        <v>900</v>
       </c>
       <c r="AB26">
         <v>12.5</v>
@@ -5820,7 +5820,7 @@
         <v>21</v>
       </c>
       <c r="AI26">
-        <v>65</v>
+        <v>320</v>
       </c>
       <c r="AJ26">
         <v>34</v>
@@ -5832,7 +5832,7 @@
         <v>44</v>
       </c>
       <c r="AM26">
-        <v>110</v>
+        <v>580</v>
       </c>
       <c r="AN26">
         <v>19.5</v>
@@ -5850,7 +5850,7 @@
         <v>19.5</v>
       </c>
       <c r="AS26">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AT26">
         <v>7.4</v>
@@ -5862,7 +5862,7 @@
         <v>11</v>
       </c>
       <c r="AW26">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AX26">
         <v>10.5</v>
@@ -5874,7 +5874,7 @@
         <v>12.5</v>
       </c>
       <c r="BA26">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BB26">
         <v>19.5</v>
@@ -5883,16 +5883,16 @@
         <v>16.5</v>
       </c>
       <c r="BD26">
+        <v>20</v>
+      </c>
+      <c r="BE26">
         <v>4.3</v>
-      </c>
-      <c r="BE26">
-        <v>4.2</v>
       </c>
       <c r="BF26">
         <v>11.5</v>
       </c>
       <c r="BG26">
-        <v>4.2</v>
+        <v>10.5</v>
       </c>
       <c r="BH26" t="s">
         <v>263</v>
@@ -5933,7 +5933,7 @@
         <v>3.75</v>
       </c>
       <c r="L27">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="M27">
         <v>1.07</v>
@@ -6157,7 +6157,7 @@
         <v>500</v>
       </c>
       <c r="Z28">
-        <v>29</v>
+        <v>970</v>
       </c>
       <c r="AA28">
         <v>900</v>
@@ -6172,7 +6172,7 @@
         <v>19</v>
       </c>
       <c r="AE28">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AF28">
         <v>48</v>
@@ -6208,13 +6208,13 @@
         <v>11</v>
       </c>
       <c r="AQ28">
-        <v>5.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR28">
         <v>5.8</v>
       </c>
       <c r="AS28">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AT28">
         <v>7.6</v>
@@ -6226,10 +6226,10 @@
         <v>6.4</v>
       </c>
       <c r="AW28">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AX28">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AY28">
         <v>10.5</v>
@@ -6238,25 +6238,25 @@
         <v>12.5</v>
       </c>
       <c r="BA28">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BB28">
-        <v>5.5</v>
+        <v>4.3</v>
       </c>
       <c r="BC28">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BD28">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BE28">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BF28">
         <v>7.2</v>
       </c>
       <c r="BG28">
-        <v>5.3</v>
+        <v>4.4</v>
       </c>
       <c r="BH28" t="s">
         <v>263</v>
@@ -6285,7 +6285,7 @@
         <v>1.5</v>
       </c>
       <c r="H29">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="I29">
         <v>8.199999999999999</v>
@@ -6294,7 +6294,7 @@
         <v>4.9</v>
       </c>
       <c r="K29">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="L29">
         <v>1.25</v>
@@ -6339,7 +6339,7 @@
         <v>32</v>
       </c>
       <c r="Z29">
-        <v>1000</v>
+        <v>420</v>
       </c>
       <c r="AA29">
         <v>240</v>
@@ -6354,7 +6354,7 @@
         <v>32</v>
       </c>
       <c r="AE29">
-        <v>120</v>
+        <v>480</v>
       </c>
       <c r="AF29">
         <v>10</v>
@@ -6366,7 +6366,7 @@
         <v>23</v>
       </c>
       <c r="AI29">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AJ29">
         <v>13.5</v>
@@ -6378,7 +6378,7 @@
         <v>34</v>
       </c>
       <c r="AM29">
-        <v>130</v>
+        <v>390</v>
       </c>
       <c r="AN29">
         <v>6.2</v>
@@ -6438,7 +6438,7 @@
         <v>5.5</v>
       </c>
       <c r="BG29">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BH29" t="s">
         <v>263</v>
@@ -6467,13 +6467,13 @@
         <v>10</v>
       </c>
       <c r="H30">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="I30">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="J30">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K30">
         <v>4.5</v>
@@ -6494,7 +6494,7 @@
         <v>1.75</v>
       </c>
       <c r="Q30">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="R30">
         <v>1.35</v>
@@ -6509,7 +6509,7 @@
         <v>1.65</v>
       </c>
       <c r="V30">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="W30">
         <v>1.11</v>
@@ -6518,7 +6518,7 @@
         <v>18</v>
       </c>
       <c r="Y30">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Z30">
         <v>13</v>
@@ -6527,28 +6527,28 @@
         <v>21</v>
       </c>
       <c r="AB30">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="AC30">
         <v>12</v>
       </c>
       <c r="AD30">
-        <v>970</v>
+        <v>17.5</v>
       </c>
       <c r="AE30">
         <v>22</v>
       </c>
       <c r="AF30">
-        <v>90</v>
+        <v>420</v>
       </c>
       <c r="AG30">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="AH30">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="AI30">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="AJ30">
         <v>1000</v>
@@ -6566,7 +6566,7 @@
         <v>1000</v>
       </c>
       <c r="AO30">
-        <v>280</v>
+        <v>25</v>
       </c>
       <c r="AP30">
         <v>8.199999999999999</v>
@@ -6581,7 +6581,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AT30">
-        <v>5.8</v>
+        <v>10.5</v>
       </c>
       <c r="AU30">
         <v>7.6</v>
@@ -6590,34 +6590,34 @@
         <v>4.3</v>
       </c>
       <c r="AW30">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AX30">
         <v>6.8</v>
       </c>
       <c r="AY30">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AZ30">
-        <v>5.9</v>
+        <v>14.5</v>
       </c>
       <c r="BA30">
-        <v>6.8</v>
+        <v>20</v>
       </c>
       <c r="BB30">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BC30">
         <v>5.7</v>
       </c>
       <c r="BD30">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BE30">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="BF30">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BG30">
         <v>6.6</v>
@@ -6643,7 +6643,7 @@
         <v>223</v>
       </c>
       <c r="F31">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="G31">
         <v>2.52</v>
@@ -6655,13 +6655,13 @@
         <v>3.4</v>
       </c>
       <c r="J31">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K31">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L31">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="M31">
         <v>1.07</v>
@@ -6685,16 +6685,16 @@
         <v>3.55</v>
       </c>
       <c r="T31">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="U31">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="V31">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W31">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="X31">
         <v>14.5</v>
@@ -6772,7 +6772,7 @@
         <v>11</v>
       </c>
       <c r="AW31">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AX31">
         <v>13</v>
@@ -6793,7 +6793,7 @@
         <v>14.5</v>
       </c>
       <c r="BD31">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE31">
         <v>9</v>
@@ -6825,7 +6825,7 @@
         <v>224</v>
       </c>
       <c r="F32">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="G32">
         <v>2.64</v>
@@ -6840,10 +6840,10 @@
         <v>3.25</v>
       </c>
       <c r="K32">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="L32">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="M32">
         <v>1.08</v>
@@ -6873,7 +6873,7 @@
         <v>2.06</v>
       </c>
       <c r="V32">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W32">
         <v>1.6</v>
@@ -6885,10 +6885,10 @@
         <v>12</v>
       </c>
       <c r="Z32">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="AA32">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AB32">
         <v>10.5</v>
@@ -6900,7 +6900,7 @@
         <v>14.5</v>
       </c>
       <c r="AE32">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="AF32">
         <v>17</v>
@@ -6909,22 +6909,22 @@
         <v>12.5</v>
       </c>
       <c r="AH32">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="AI32">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AJ32">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="AK32">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="AL32">
-        <v>46</v>
+        <v>500</v>
       </c>
       <c r="AM32">
-        <v>130</v>
+        <v>580</v>
       </c>
       <c r="AN32">
         <v>32</v>
@@ -6942,7 +6942,7 @@
         <v>18</v>
       </c>
       <c r="AS32">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AT32">
         <v>8.4</v>
@@ -6963,7 +6963,7 @@
         <v>10</v>
       </c>
       <c r="AZ32">
-        <v>5.7</v>
+        <v>11.5</v>
       </c>
       <c r="BA32">
         <v>6.8</v>
@@ -6984,7 +6984,7 @@
         <v>18.5</v>
       </c>
       <c r="BG32">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BH32" t="s">
         <v>263</v>
@@ -7034,13 +7034,13 @@
         <v>3.35</v>
       </c>
       <c r="O33">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="P33">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="Q33">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="R33">
         <v>1.29</v>
@@ -7049,7 +7049,7 @@
         <v>4.2</v>
       </c>
       <c r="T33">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="U33">
         <v>2.04</v>
@@ -7085,7 +7085,7 @@
         <v>29</v>
       </c>
       <c r="AF33">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG33">
         <v>14</v>
@@ -7094,7 +7094,7 @@
         <v>18</v>
       </c>
       <c r="AI33">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AJ33">
         <v>55</v>
@@ -7106,10 +7106,10 @@
         <v>55</v>
       </c>
       <c r="AM33">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN33">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AO33">
         <v>27</v>
@@ -7148,22 +7148,22 @@
         <v>17</v>
       </c>
       <c r="BA33">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BB33">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BC33">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BD33">
         <v>48</v>
       </c>
       <c r="BE33">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="BF33">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BG33">
         <v>25</v>
@@ -7189,13 +7189,13 @@
         <v>226</v>
       </c>
       <c r="F34">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="G34">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="H34">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="I34">
         <v>2.6</v>
@@ -7204,7 +7204,7 @@
         <v>3.8</v>
       </c>
       <c r="K34">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L34">
         <v>1.28</v>
@@ -7213,46 +7213,46 @@
         <v>1.05</v>
       </c>
       <c r="N34">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O34">
         <v>1.24</v>
       </c>
       <c r="P34">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="Q34">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="R34">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="S34">
         <v>2.84</v>
       </c>
       <c r="T34">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="U34">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="V34">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="W34">
         <v>1.52</v>
       </c>
       <c r="X34">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="Y34">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z34">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AA34">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AB34">
         <v>14.5</v>
@@ -7267,7 +7267,7 @@
         <v>24</v>
       </c>
       <c r="AF34">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG34">
         <v>12.5</v>
@@ -7276,40 +7276,40 @@
         <v>15</v>
       </c>
       <c r="AI34">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AJ34">
         <v>44</v>
       </c>
       <c r="AK34">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AL34">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM34">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AN34">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AO34">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AP34">
         <v>18</v>
       </c>
       <c r="AQ34">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AR34">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AS34">
         <v>30</v>
       </c>
       <c r="AT34">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AU34">
         <v>8</v>
@@ -7321,7 +7321,7 @@
         <v>23</v>
       </c>
       <c r="AX34">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AY34">
         <v>11.5</v>
@@ -7333,19 +7333,19 @@
         <v>28</v>
       </c>
       <c r="BB34">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BC34">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BD34">
         <v>30</v>
       </c>
       <c r="BE34">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BF34">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BG34">
         <v>15</v>
@@ -7377,13 +7377,13 @@
         <v>1.27</v>
       </c>
       <c r="H35">
-        <v>7.8</v>
+        <v>20</v>
       </c>
       <c r="I35">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J35">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="K35">
         <v>7.8</v>
@@ -7395,34 +7395,34 @@
         <v>1.05</v>
       </c>
       <c r="N35">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="O35">
         <v>1.27</v>
       </c>
       <c r="P35">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="Q35">
         <v>1.78</v>
       </c>
       <c r="R35">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S35">
-        <v>2.58</v>
+        <v>3.05</v>
       </c>
       <c r="T35">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="U35">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="V35">
         <v>1.03</v>
       </c>
       <c r="W35">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="X35">
         <v>19.5</v>
@@ -7431,16 +7431,16 @@
         <v>100</v>
       </c>
       <c r="Z35">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="AA35">
         <v>1000</v>
       </c>
       <c r="AB35">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AC35">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AD35">
         <v>300</v>
@@ -7452,25 +7452,25 @@
         <v>6.8</v>
       </c>
       <c r="AG35">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH35">
         <v>160</v>
       </c>
       <c r="AI35">
-        <v>600</v>
+        <v>590</v>
       </c>
       <c r="AJ35">
         <v>8.800000000000001</v>
       </c>
       <c r="AK35">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AL35">
         <v>330</v>
       </c>
       <c r="AM35">
-        <v>620</v>
+        <v>610</v>
       </c>
       <c r="AN35">
         <v>5.7</v>
@@ -7479,58 +7479,58 @@
         <v>1000</v>
       </c>
       <c r="AP35">
-        <v>7.6</v>
+        <v>14.5</v>
       </c>
       <c r="AQ35">
-        <v>6.6</v>
+        <v>16</v>
       </c>
       <c r="AR35">
         <v>7.4</v>
       </c>
       <c r="AS35">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AT35">
-        <v>4.4</v>
+        <v>5.7</v>
       </c>
       <c r="AU35">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AV35">
         <v>7</v>
       </c>
       <c r="AW35">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AX35">
-        <v>3.85</v>
+        <v>5.2</v>
       </c>
       <c r="AY35">
-        <v>4.9</v>
+        <v>10</v>
       </c>
       <c r="AZ35">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BA35">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB35">
-        <v>4.9</v>
+        <v>6.8</v>
       </c>
       <c r="BC35">
-        <v>5.4</v>
+        <v>14</v>
       </c>
       <c r="BD35">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BE35">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BF35">
-        <v>3.25</v>
+        <v>4.5</v>
       </c>
       <c r="BG35">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BH35" t="s">
         <v>263</v>
@@ -7556,19 +7556,19 @@
         <v>1.82</v>
       </c>
       <c r="G36">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="H36">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I36">
         <v>5.5</v>
       </c>
       <c r="J36">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K36">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="L36">
         <v>1.44</v>
@@ -7613,10 +7613,10 @@
         <v>19</v>
       </c>
       <c r="Z36">
-        <v>46</v>
+        <v>120</v>
       </c>
       <c r="AA36">
-        <v>160</v>
+        <v>900</v>
       </c>
       <c r="AB36">
         <v>9.6</v>
@@ -7625,10 +7625,10 @@
         <v>10</v>
       </c>
       <c r="AD36">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="AE36">
-        <v>90</v>
+        <v>700</v>
       </c>
       <c r="AF36">
         <v>13.5</v>
@@ -7637,82 +7637,82 @@
         <v>12.5</v>
       </c>
       <c r="AH36">
+        <v>55</v>
+      </c>
+      <c r="AI36">
+        <v>700</v>
+      </c>
+      <c r="AJ36">
+        <v>90</v>
+      </c>
+      <c r="AK36">
         <v>60</v>
       </c>
-      <c r="AI36">
-        <v>95</v>
-      </c>
-      <c r="AJ36">
-        <v>26</v>
-      </c>
-      <c r="AK36">
-        <v>26</v>
-      </c>
       <c r="AL36">
-        <v>50</v>
+        <v>190</v>
       </c>
       <c r="AM36">
-        <v>160</v>
+        <v>580</v>
       </c>
       <c r="AN36">
         <v>18</v>
       </c>
       <c r="AO36">
-        <v>300</v>
+        <v>700</v>
       </c>
       <c r="AP36">
-        <v>9.4</v>
+        <v>6.2</v>
       </c>
       <c r="AQ36">
-        <v>3.6</v>
+        <v>8.4</v>
       </c>
       <c r="AR36">
         <v>4.2</v>
       </c>
       <c r="AS36">
+        <v>4.4</v>
+      </c>
+      <c r="AT36">
+        <v>4.4</v>
+      </c>
+      <c r="AU36">
+        <v>4.4</v>
+      </c>
+      <c r="AV36">
+        <v>4</v>
+      </c>
+      <c r="AW36">
+        <v>4.4</v>
+      </c>
+      <c r="AX36">
+        <v>5.6</v>
+      </c>
+      <c r="AY36">
+        <v>5.8</v>
+      </c>
+      <c r="AZ36">
         <v>4.2</v>
       </c>
-      <c r="AT36">
-        <v>3.2</v>
-      </c>
-      <c r="AU36">
-        <v>3.2</v>
-      </c>
-      <c r="AV36">
-        <v>3.75</v>
-      </c>
-      <c r="AW36">
-        <v>4.1</v>
-      </c>
-      <c r="AX36">
-        <v>3.5</v>
-      </c>
-      <c r="AY36">
-        <v>3.4</v>
-      </c>
-      <c r="AZ36">
-        <v>3.75</v>
-      </c>
       <c r="BA36">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BB36">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="BC36">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="BD36">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BE36">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BF36">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="BG36">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BH36" t="s">
         <v>263</v>
@@ -7735,7 +7735,7 @@
         <v>229</v>
       </c>
       <c r="F37">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="G37">
         <v>3.25</v>
@@ -7750,10 +7750,10 @@
         <v>3.35</v>
       </c>
       <c r="K37">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L37">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="M37">
         <v>1.08</v>
@@ -7917,7 +7917,7 @@
         <v>230</v>
       </c>
       <c r="F38">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="G38">
         <v>1.73</v>
@@ -7929,7 +7929,7 @@
         <v>5.8</v>
       </c>
       <c r="J38">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K38">
         <v>4.3</v>
@@ -7950,7 +7950,7 @@
         <v>2.06</v>
       </c>
       <c r="Q38">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="R38">
         <v>1.4</v>
@@ -7959,13 +7959,13 @@
         <v>3.2</v>
       </c>
       <c r="T38">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="U38">
         <v>2.04</v>
       </c>
       <c r="V38">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W38">
         <v>2.38</v>
@@ -8102,10 +8102,10 @@
         <v>3.05</v>
       </c>
       <c r="G39">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="H39">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="I39">
         <v>2.64</v>
@@ -8138,7 +8138,7 @@
         <v>1.23</v>
       </c>
       <c r="S39">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="T39">
         <v>1.96</v>
@@ -8177,7 +8177,7 @@
         <v>90</v>
       </c>
       <c r="AF39">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AG39">
         <v>15</v>
@@ -8216,7 +8216,7 @@
         <v>13</v>
       </c>
       <c r="AS39">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AT39">
         <v>8.800000000000001</v>
@@ -8228,7 +8228,7 @@
         <v>10</v>
       </c>
       <c r="AW39">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AX39">
         <v>18</v>
@@ -8255,7 +8255,7 @@
         <v>7.2</v>
       </c>
       <c r="BF39">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BG39">
         <v>6.2</v>
@@ -8284,7 +8284,7 @@
         <v>2.44</v>
       </c>
       <c r="G40">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="H40">
         <v>3</v>
@@ -8293,7 +8293,7 @@
         <v>3.1</v>
       </c>
       <c r="J40">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K40">
         <v>3.85</v>
@@ -8311,7 +8311,7 @@
         <v>1.24</v>
       </c>
       <c r="P40">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="Q40">
         <v>1.72</v>
@@ -8326,7 +8326,7 @@
         <v>1.61</v>
       </c>
       <c r="U40">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="V40">
         <v>1.47</v>
@@ -8371,7 +8371,7 @@
         <v>44</v>
       </c>
       <c r="AJ40">
-        <v>38</v>
+        <v>120</v>
       </c>
       <c r="AK40">
         <v>28</v>
@@ -8395,10 +8395,10 @@
         <v>13</v>
       </c>
       <c r="AR40">
-        <v>4.9</v>
+        <v>11.5</v>
       </c>
       <c r="AS40">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AT40">
         <v>10</v>
@@ -8410,7 +8410,7 @@
         <v>10</v>
       </c>
       <c r="AW40">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AX40">
         <v>16</v>
@@ -8428,10 +8428,10 @@
         <v>5.2</v>
       </c>
       <c r="BC40">
-        <v>4.9</v>
+        <v>11.5</v>
       </c>
       <c r="BD40">
-        <v>5.2</v>
+        <v>16</v>
       </c>
       <c r="BE40">
         <v>28</v>
@@ -8440,7 +8440,7 @@
         <v>11.5</v>
       </c>
       <c r="BG40">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BH40" t="s">
         <v>263</v>
@@ -8469,7 +8469,7 @@
         <v>1.59</v>
       </c>
       <c r="H41">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="I41">
         <v>6.4</v>
@@ -8481,13 +8481,13 @@
         <v>5</v>
       </c>
       <c r="L41">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="M41">
         <v>1.03</v>
       </c>
       <c r="N41">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="O41">
         <v>1.18</v>
@@ -8499,16 +8499,16 @@
         <v>1.55</v>
       </c>
       <c r="R41">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="S41">
         <v>2.4</v>
       </c>
       <c r="T41">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="U41">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="V41">
         <v>1.18</v>
@@ -8529,7 +8529,7 @@
         <v>150</v>
       </c>
       <c r="AB41">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AC41">
         <v>11.5</v>
@@ -8559,7 +8559,7 @@
         <v>15</v>
       </c>
       <c r="AL41">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AM41">
         <v>80</v>
@@ -8571,7 +8571,7 @@
         <v>60</v>
       </c>
       <c r="AP41">
-        <v>11.5</v>
+        <v>16</v>
       </c>
       <c r="AQ41">
         <v>25</v>
@@ -8592,10 +8592,10 @@
         <v>20</v>
       </c>
       <c r="AW41">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="AX41">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AY41">
         <v>9.199999999999999</v>
@@ -8645,10 +8645,10 @@
         <v>234</v>
       </c>
       <c r="F42">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="G42">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="H42">
         <v>4.1</v>
@@ -8657,10 +8657,10 @@
         <v>4.2</v>
       </c>
       <c r="J42">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K42">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L42">
         <v>1.3</v>
@@ -8675,7 +8675,7 @@
         <v>1.28</v>
       </c>
       <c r="P42">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="Q42">
         <v>1.89</v>
@@ -8696,7 +8696,7 @@
         <v>1.31</v>
       </c>
       <c r="W42">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="X42">
         <v>26</v>
@@ -8738,10 +8738,10 @@
         <v>38</v>
       </c>
       <c r="AK42">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="AL42">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AM42">
         <v>580</v>
@@ -8759,10 +8759,10 @@
         <v>9</v>
       </c>
       <c r="AR42">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AS42">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AT42">
         <v>7.2</v>
@@ -8786,25 +8786,25 @@
         <v>9</v>
       </c>
       <c r="BA42">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BB42">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BC42">
         <v>13.5</v>
       </c>
       <c r="BD42">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BE42">
+        <v>6.6</v>
+      </c>
+      <c r="BF42">
+        <v>4.6</v>
+      </c>
+      <c r="BG42">
         <v>6.4</v>
-      </c>
-      <c r="BF42">
-        <v>4.5</v>
-      </c>
-      <c r="BG42">
-        <v>6.2</v>
       </c>
       <c r="BH42" t="s">
         <v>263</v>
@@ -8833,7 +8833,7 @@
         <v>2.32</v>
       </c>
       <c r="H43">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="I43">
         <v>3.75</v>
@@ -8845,7 +8845,7 @@
         <v>3.6</v>
       </c>
       <c r="L43">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="M43">
         <v>1.09</v>
@@ -8869,7 +8869,7 @@
         <v>4.1</v>
       </c>
       <c r="T43">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="U43">
         <v>1.96</v>
@@ -8896,7 +8896,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AC43">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD43">
         <v>16</v>
@@ -8908,7 +8908,7 @@
         <v>17</v>
       </c>
       <c r="AG43">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AH43">
         <v>500</v>
@@ -8944,7 +8944,7 @@
         <v>17</v>
       </c>
       <c r="AS43">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AT43">
         <v>6.8</v>
@@ -8956,37 +8956,37 @@
         <v>10.5</v>
       </c>
       <c r="AW43">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AX43">
         <v>10.5</v>
       </c>
       <c r="AY43">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="AZ43">
         <v>14</v>
       </c>
       <c r="BA43">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BB43">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BC43">
         <v>20</v>
       </c>
       <c r="BD43">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BE43">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BF43">
         <v>17</v>
       </c>
       <c r="BG43">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BH43" t="s">
         <v>263</v>
@@ -9009,22 +9009,22 @@
         <v>236</v>
       </c>
       <c r="F44">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="G44">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="H44">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="I44">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="J44">
         <v>3.5</v>
       </c>
       <c r="K44">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L44">
         <v>1.45</v>
@@ -9057,25 +9057,25 @@
         <v>1.81</v>
       </c>
       <c r="V44">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="W44">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="X44">
         <v>14.5</v>
       </c>
       <c r="Y44">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="Z44">
         <v>55</v>
       </c>
       <c r="AA44">
-        <v>200</v>
+        <v>900</v>
       </c>
       <c r="AB44">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC44">
         <v>10</v>
@@ -9084,13 +9084,13 @@
         <v>28</v>
       </c>
       <c r="AE44">
-        <v>120</v>
+        <v>260</v>
       </c>
       <c r="AF44">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AG44">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH44">
         <v>27</v>
@@ -9102,16 +9102,16 @@
         <v>23</v>
       </c>
       <c r="AK44">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AL44">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AM44">
-        <v>190</v>
+        <v>580</v>
       </c>
       <c r="AN44">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AO44">
         <v>160</v>
@@ -9123,10 +9123,10 @@
         <v>14</v>
       </c>
       <c r="AR44">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="AS44">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="AT44">
         <v>6.2</v>
@@ -9138,7 +9138,7 @@
         <v>19</v>
       </c>
       <c r="AW44">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="AX44">
         <v>8.6</v>
@@ -9150,7 +9150,7 @@
         <v>19</v>
       </c>
       <c r="BA44">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="BB44">
         <v>16</v>
@@ -9162,13 +9162,13 @@
         <v>36</v>
       </c>
       <c r="BE44">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BF44">
         <v>10.5</v>
       </c>
       <c r="BG44">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BH44" t="s">
         <v>263</v>
@@ -9194,7 +9194,7 @@
         <v>2.4</v>
       </c>
       <c r="G45">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="H45">
         <v>3.95</v>
@@ -9293,7 +9293,7 @@
         <v>500</v>
       </c>
       <c r="AN45">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AO45">
         <v>110</v>
@@ -9302,13 +9302,13 @@
         <v>7</v>
       </c>
       <c r="AQ45">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR45">
         <v>20</v>
       </c>
       <c r="AS45">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AT45">
         <v>6.2</v>
@@ -9332,7 +9332,7 @@
         <v>19.5</v>
       </c>
       <c r="BA45">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BB45">
         <v>14.5</v>
@@ -9344,13 +9344,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BE45">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF45">
         <v>7.6</v>
       </c>
       <c r="BG45">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BH45" t="s">
         <v>263</v>
@@ -9376,7 +9376,7 @@
         <v>1.36</v>
       </c>
       <c r="G46">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="H46">
         <v>8.199999999999999</v>
@@ -9385,7 +9385,7 @@
         <v>9</v>
       </c>
       <c r="J46">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="K46">
         <v>6.8</v>
@@ -9400,19 +9400,19 @@
         <v>10</v>
       </c>
       <c r="O46">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="P46">
         <v>3.8</v>
       </c>
       <c r="Q46">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="R46">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="S46">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="T46">
         <v>1.61</v>
@@ -9424,7 +9424,7 @@
         <v>1.12</v>
       </c>
       <c r="W46">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="X46">
         <v>60</v>
@@ -9454,10 +9454,10 @@
         <v>13.5</v>
       </c>
       <c r="AG46">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH46">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI46">
         <v>75</v>
@@ -9481,7 +9481,7 @@
         <v>65</v>
       </c>
       <c r="AP46">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AQ46">
         <v>27</v>
@@ -9508,7 +9508,7 @@
         <v>11.5</v>
       </c>
       <c r="AY46">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AZ46">
         <v>18.5</v>
@@ -9517,7 +9517,7 @@
         <v>30</v>
       </c>
       <c r="BB46">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BC46">
         <v>11.5</v>
@@ -9606,7 +9606,7 @@
         <v>1.5</v>
       </c>
       <c r="W47">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="X47">
         <v>19</v>
@@ -9672,7 +9672,7 @@
         <v>10.5</v>
       </c>
       <c r="AS47">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AT47">
         <v>10</v>
@@ -9684,7 +9684,7 @@
         <v>7</v>
       </c>
       <c r="AW47">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AX47">
         <v>9</v>
@@ -9696,16 +9696,16 @@
         <v>8.4</v>
       </c>
       <c r="BA47">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BB47">
         <v>16</v>
       </c>
       <c r="BC47">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BD47">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BE47">
         <v>5</v>
@@ -9740,19 +9740,19 @@
         <v>2.34</v>
       </c>
       <c r="G48">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="H48">
         <v>3.1</v>
       </c>
       <c r="I48">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="J48">
         <v>3.3</v>
       </c>
       <c r="K48">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="L48">
         <v>1.4</v>
@@ -9794,7 +9794,7 @@
         <v>16.5</v>
       </c>
       <c r="Y48">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Z48">
         <v>26</v>
@@ -9854,7 +9854,7 @@
         <v>16</v>
       </c>
       <c r="AS48">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AT48">
         <v>8.800000000000001</v>
@@ -9866,7 +9866,7 @@
         <v>10</v>
       </c>
       <c r="AW48">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AX48">
         <v>11.5</v>
@@ -9878,10 +9878,10 @@
         <v>14.5</v>
       </c>
       <c r="BA48">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BB48">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BC48">
         <v>19.5</v>
@@ -9890,13 +9890,13 @@
         <v>29</v>
       </c>
       <c r="BE48">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BF48">
         <v>19.5</v>
       </c>
       <c r="BG48">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BH48" t="s">
         <v>263</v>
@@ -9925,7 +9925,7 @@
         <v>990</v>
       </c>
       <c r="H49">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="I49">
         <v>990</v>
@@ -10104,19 +10104,19 @@
         <v>1.45</v>
       </c>
       <c r="G50">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="H50">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="I50">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="J50">
         <v>4.9</v>
       </c>
       <c r="K50">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="L50">
         <v>1.24</v>
@@ -10125,13 +10125,13 @@
         <v>1.03</v>
       </c>
       <c r="N50">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="O50">
         <v>1.17</v>
       </c>
       <c r="P50">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="Q50">
         <v>1.52</v>
@@ -10152,7 +10152,7 @@
         <v>1.15</v>
       </c>
       <c r="W50">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="X50">
         <v>48</v>
@@ -10203,7 +10203,7 @@
         <v>320</v>
       </c>
       <c r="AN50">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AO50">
         <v>170</v>
@@ -10215,10 +10215,10 @@
         <v>13</v>
       </c>
       <c r="AR50">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AS50">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT50">
         <v>10</v>
@@ -10230,7 +10230,7 @@
         <v>12.5</v>
       </c>
       <c r="AW50">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AX50">
         <v>9.199999999999999</v>
@@ -10254,13 +10254,13 @@
         <v>14.5</v>
       </c>
       <c r="BE50">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF50">
         <v>4.8</v>
       </c>
       <c r="BG50">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BH50" t="s">
         <v>263</v>
@@ -10286,7 +10286,7 @@
         <v>1.57</v>
       </c>
       <c r="G51">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="H51">
         <v>5.8</v>
@@ -10295,10 +10295,10 @@
         <v>6.8</v>
       </c>
       <c r="J51">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="K51">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="L51">
         <v>1.25</v>
@@ -10307,40 +10307,40 @@
         <v>1.03</v>
       </c>
       <c r="N51">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="O51">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="P51">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="Q51">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="R51">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="S51">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="T51">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="U51">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="V51">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="W51">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="X51">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="Y51">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="Z51">
         <v>120</v>
@@ -10349,7 +10349,7 @@
         <v>700</v>
       </c>
       <c r="AB51">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AC51">
         <v>12</v>
@@ -10358,7 +10358,7 @@
         <v>24</v>
       </c>
       <c r="AE51">
-        <v>160</v>
+        <v>320</v>
       </c>
       <c r="AF51">
         <v>12</v>
@@ -10379,13 +10379,13 @@
         <v>15.5</v>
       </c>
       <c r="AL51">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="AM51">
         <v>580</v>
       </c>
       <c r="AN51">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AO51">
         <v>120</v>
@@ -10397,13 +10397,13 @@
         <v>22</v>
       </c>
       <c r="AR51">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AS51">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT51">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU51">
         <v>9.199999999999999</v>
@@ -10412,7 +10412,7 @@
         <v>18</v>
       </c>
       <c r="AW51">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AX51">
         <v>10</v>
@@ -10427,7 +10427,7 @@
         <v>44</v>
       </c>
       <c r="BB51">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BC51">
         <v>12</v>
@@ -10436,13 +10436,13 @@
         <v>20</v>
       </c>
       <c r="BE51">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF51">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="BG51">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BH51" t="s">
         <v>263</v>
@@ -10594,7 +10594,7 @@
         <v>9</v>
       </c>
       <c r="AW52">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX52">
         <v>11</v>
@@ -10603,7 +10603,7 @@
         <v>9</v>
       </c>
       <c r="AZ52">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BA52">
         <v>34</v>
@@ -10656,7 +10656,7 @@
         <v>6.8</v>
       </c>
       <c r="I53">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="J53">
         <v>4.9</v>
@@ -10668,7 +10668,7 @@
         <v>1.23</v>
       </c>
       <c r="M53">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="N53">
         <v>6</v>
@@ -10689,10 +10689,10 @@
         <v>2.26</v>
       </c>
       <c r="T53">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="U53">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="V53">
         <v>1.15</v>
@@ -10704,7 +10704,7 @@
         <v>29</v>
       </c>
       <c r="Y53">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="Z53">
         <v>150</v>
@@ -10740,19 +10740,19 @@
         <v>15</v>
       </c>
       <c r="AK53">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AL53">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AM53">
-        <v>320</v>
+        <v>80</v>
       </c>
       <c r="AN53">
         <v>5.7</v>
       </c>
       <c r="AO53">
-        <v>170</v>
+        <v>90</v>
       </c>
       <c r="AP53">
         <v>24</v>
@@ -10761,10 +10761,10 @@
         <v>25</v>
       </c>
       <c r="AR53">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AS53">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT53">
         <v>10.5</v>
@@ -10773,10 +10773,10 @@
         <v>10</v>
       </c>
       <c r="AV53">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="AW53">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AX53">
         <v>9.800000000000001</v>
@@ -10806,7 +10806,7 @@
         <v>4.8</v>
       </c>
       <c r="BG53">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BH53" t="s">
         <v>263</v>
@@ -10829,16 +10829,16 @@
         <v>246</v>
       </c>
       <c r="F54">
+        <v>1.63</v>
+      </c>
+      <c r="G54">
         <v>1.64</v>
-      </c>
-      <c r="G54">
-        <v>1.65</v>
       </c>
       <c r="H54">
         <v>6.2</v>
       </c>
       <c r="I54">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="J54">
         <v>4.3</v>
@@ -10880,7 +10880,7 @@
         <v>1.18</v>
       </c>
       <c r="W54">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="X54">
         <v>15.5</v>
@@ -10904,7 +10904,7 @@
         <v>24</v>
       </c>
       <c r="AE54">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AF54">
         <v>9</v>
@@ -10919,19 +10919,19 @@
         <v>90</v>
       </c>
       <c r="AJ54">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AK54">
         <v>17</v>
       </c>
       <c r="AL54">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM54">
         <v>140</v>
       </c>
       <c r="AN54">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AO54">
         <v>120</v>
@@ -10940,10 +10940,10 @@
         <v>14</v>
       </c>
       <c r="AQ54">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AR54">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AS54">
         <v>44</v>
@@ -10973,10 +10973,10 @@
         <v>80</v>
       </c>
       <c r="BB54">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BC54">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BD54">
         <v>34</v>
@@ -11098,7 +11098,7 @@
         <v>17.5</v>
       </c>
       <c r="AI55">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ55">
         <v>36</v>
@@ -11119,7 +11119,7 @@
         <v>32</v>
       </c>
       <c r="AP55">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AQ55">
         <v>11</v>
@@ -11170,7 +11170,7 @@
         <v>21</v>
       </c>
       <c r="BG55">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BH55" t="s">
         <v>263</v>
@@ -11217,22 +11217,22 @@
         <v>1.04</v>
       </c>
       <c r="N56">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="O56">
         <v>1.23</v>
       </c>
       <c r="P56">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="Q56">
         <v>1.68</v>
       </c>
       <c r="R56">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="S56">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="T56">
         <v>1.84</v>
@@ -11247,7 +11247,7 @@
         <v>1.15</v>
       </c>
       <c r="X56">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y56">
         <v>9.4</v>
@@ -11259,7 +11259,7 @@
         <v>13.5</v>
       </c>
       <c r="AB56">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AC56">
         <v>11</v>
@@ -11280,31 +11280,31 @@
         <v>22</v>
       </c>
       <c r="AI56">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AJ56">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AK56">
         <v>90</v>
       </c>
       <c r="AL56">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AM56">
         <v>100</v>
       </c>
       <c r="AN56">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AO56">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AP56">
         <v>21</v>
       </c>
       <c r="AQ56">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR56">
         <v>9.199999999999999</v>
@@ -11313,10 +11313,10 @@
         <v>13</v>
       </c>
       <c r="AT56">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AU56">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AV56">
         <v>9.199999999999999</v>
@@ -11331,10 +11331,10 @@
         <v>22</v>
       </c>
       <c r="AZ56">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA56">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BB56">
         <v>110</v>
@@ -11349,7 +11349,7 @@
         <v>90</v>
       </c>
       <c r="BF56">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="BG56">
         <v>6.2</v>
@@ -11387,10 +11387,10 @@
         <v>12.5</v>
       </c>
       <c r="J57">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="K57">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="L57">
         <v>1.26</v>
@@ -11405,22 +11405,22 @@
         <v>1.17</v>
       </c>
       <c r="P57">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="Q57">
         <v>1.52</v>
       </c>
       <c r="R57">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="S57">
         <v>2.28</v>
       </c>
       <c r="T57">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="U57">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="V57">
         <v>1.08</v>
@@ -11429,31 +11429,31 @@
         <v>4.2</v>
       </c>
       <c r="X57">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Y57">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="Z57">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AA57">
-        <v>450</v>
+        <v>470</v>
       </c>
       <c r="AB57">
         <v>11</v>
       </c>
       <c r="AC57">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AD57">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AE57">
         <v>190</v>
       </c>
       <c r="AF57">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AG57">
         <v>10.5</v>
@@ -11465,7 +11465,7 @@
         <v>140</v>
       </c>
       <c r="AJ57">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AK57">
         <v>13.5</v>
@@ -11477,34 +11477,34 @@
         <v>140</v>
       </c>
       <c r="AN57">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AO57">
         <v>170</v>
       </c>
       <c r="AP57">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AQ57">
         <v>34</v>
       </c>
       <c r="AR57">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="AS57">
-        <v>13.5</v>
+        <v>17</v>
       </c>
       <c r="AT57">
         <v>9.6</v>
       </c>
       <c r="AU57">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AV57">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AW57">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AX57">
         <v>8.4</v>
@@ -11516,7 +11516,7 @@
         <v>24</v>
       </c>
       <c r="BA57">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="BB57">
         <v>9.6</v>
@@ -11528,13 +11528,13 @@
         <v>27</v>
       </c>
       <c r="BE57">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BF57">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BG57">
-        <v>12.5</v>
+        <v>17</v>
       </c>
       <c r="BH57" t="s">
         <v>263</v>
@@ -11569,7 +11569,7 @@
         <v>3.85</v>
       </c>
       <c r="J58">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="K58">
         <v>3.1</v>
@@ -11581,10 +11581,10 @@
         <v>1.15</v>
       </c>
       <c r="N58">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="O58">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="P58">
         <v>1.44</v>
@@ -11602,7 +11602,7 @@
         <v>2.34</v>
       </c>
       <c r="U58">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="V58">
         <v>1.35</v>
@@ -11620,7 +11620,7 @@
         <v>25</v>
       </c>
       <c r="AA58">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AB58">
         <v>6.8</v>
@@ -11629,16 +11629,16 @@
         <v>7.6</v>
       </c>
       <c r="AD58">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AE58">
         <v>500</v>
       </c>
       <c r="AF58">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AG58">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH58">
         <v>30</v>
@@ -11665,7 +11665,7 @@
         <v>500</v>
       </c>
       <c r="AP58">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AQ58">
         <v>7.2</v>
@@ -11674,7 +11674,7 @@
         <v>20</v>
       </c>
       <c r="AS58">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AT58">
         <v>5.8</v>
@@ -11686,7 +11686,7 @@
         <v>15</v>
       </c>
       <c r="AW58">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AX58">
         <v>11.5</v>
@@ -11698,7 +11698,7 @@
         <v>24</v>
       </c>
       <c r="BA58">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BB58">
         <v>32</v>
@@ -11707,16 +11707,16 @@
         <v>34</v>
       </c>
       <c r="BD58">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BE58">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BF58">
         <v>36</v>
       </c>
       <c r="BG58">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BH58" t="s">
         <v>263</v>
@@ -11793,52 +11793,52 @@
         <v>2.88</v>
       </c>
       <c r="X59">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="Y59">
         <v>30</v>
       </c>
       <c r="Z59">
-        <v>85</v>
+        <v>270</v>
       </c>
       <c r="AA59">
         <v>310</v>
       </c>
       <c r="AB59">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="AC59">
         <v>11</v>
       </c>
       <c r="AD59">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="AE59">
-        <v>150</v>
+        <v>480</v>
       </c>
       <c r="AF59">
+        <v>9</v>
+      </c>
+      <c r="AG59">
         <v>10.5</v>
-      </c>
-      <c r="AG59">
-        <v>12</v>
       </c>
       <c r="AH59">
         <v>29</v>
       </c>
       <c r="AI59">
-        <v>130</v>
+        <v>460</v>
       </c>
       <c r="AJ59">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AK59">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AL59">
         <v>44</v>
       </c>
       <c r="AM59">
-        <v>160</v>
+        <v>380</v>
       </c>
       <c r="AN59">
         <v>7.4</v>
@@ -11847,58 +11847,58 @@
         <v>200</v>
       </c>
       <c r="AP59">
-        <v>4.7</v>
+        <v>7.2</v>
       </c>
       <c r="AQ59">
-        <v>5</v>
+        <v>7.6</v>
       </c>
       <c r="AR59">
-        <v>5.7</v>
+        <v>9</v>
       </c>
       <c r="AS59">
-        <v>6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT59">
-        <v>3.7</v>
+        <v>5.1</v>
       </c>
       <c r="AU59">
-        <v>3.9</v>
+        <v>6.2</v>
       </c>
       <c r="AV59">
+        <v>7.6</v>
+      </c>
+      <c r="AW59">
+        <v>9.4</v>
+      </c>
+      <c r="AX59">
+        <v>4.8</v>
+      </c>
+      <c r="AY59">
         <v>5.2</v>
       </c>
-      <c r="AW59">
-        <v>5.8</v>
-      </c>
-      <c r="AX59">
-        <v>3.85</v>
-      </c>
-      <c r="AY59">
-        <v>4</v>
-      </c>
       <c r="AZ59">
-        <v>5</v>
+        <v>7.6</v>
       </c>
       <c r="BA59">
-        <v>5.8</v>
+        <v>9.4</v>
       </c>
       <c r="BB59">
+        <v>6.4</v>
+      </c>
+      <c r="BC59">
+        <v>6.2</v>
+      </c>
+      <c r="BD59">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BE59">
+        <v>9.6</v>
+      </c>
+      <c r="BF59">
         <v>4.3</v>
       </c>
-      <c r="BC59">
-        <v>4.6</v>
-      </c>
-      <c r="BD59">
-        <v>5.3</v>
-      </c>
-      <c r="BE59">
-        <v>5.9</v>
-      </c>
-      <c r="BF59">
-        <v>3.35</v>
-      </c>
       <c r="BG59">
-        <v>5.9</v>
+        <v>9.6</v>
       </c>
       <c r="BH59" t="s">
         <v>263</v>
@@ -11924,7 +11924,7 @@
         <v>1.82</v>
       </c>
       <c r="G60">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="H60">
         <v>5.1</v>
@@ -11933,10 +11933,10 @@
         <v>5.7</v>
       </c>
       <c r="J60">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K60">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="L60">
         <v>1.41</v>
@@ -11972,7 +11972,7 @@
         <v>1.21</v>
       </c>
       <c r="W60">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="X60">
         <v>13</v>
@@ -12026,43 +12026,43 @@
         <v>20</v>
       </c>
       <c r="AO60">
-        <v>160</v>
+        <v>310</v>
       </c>
       <c r="AP60">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AQ60">
         <v>7.6</v>
       </c>
       <c r="AR60">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AS60">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AT60">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AU60">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AV60">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AW60">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AX60">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AY60">
         <v>9</v>
       </c>
       <c r="AZ60">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BA60">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB60">
         <v>17.5</v>
@@ -12074,13 +12074,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BE60">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BF60">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BG60">
-        <v>9.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="BH60" t="s">
         <v>263</v>
@@ -12127,7 +12127,7 @@
         <v>1.06</v>
       </c>
       <c r="N61">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="O61">
         <v>1.29</v>
@@ -12157,112 +12157,112 @@
         <v>1.73</v>
       </c>
       <c r="X61">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Y61">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="Z61">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AA61">
         <v>75</v>
       </c>
       <c r="AB61">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AC61">
         <v>8.6</v>
       </c>
       <c r="AD61">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AE61">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AF61">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AG61">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AH61">
         <v>17.5</v>
       </c>
       <c r="AI61">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ61">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AK61">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AL61">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AM61">
-        <v>100</v>
+        <v>260</v>
       </c>
       <c r="AN61">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AO61">
         <v>44</v>
       </c>
       <c r="AP61">
-        <v>4.3</v>
+        <v>6.6</v>
       </c>
       <c r="AQ61">
-        <v>4.2</v>
+        <v>6.4</v>
       </c>
       <c r="AR61">
-        <v>4.8</v>
+        <v>7.2</v>
       </c>
       <c r="AS61">
-        <v>5.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT61">
-        <v>3.9</v>
+        <v>5.8</v>
       </c>
       <c r="AU61">
-        <v>3.4</v>
+        <v>4.9</v>
       </c>
       <c r="AV61">
-        <v>4.2</v>
+        <v>6.4</v>
       </c>
       <c r="AW61">
-        <v>5.1</v>
+        <v>8</v>
       </c>
       <c r="AX61">
-        <v>4.2</v>
+        <v>6.4</v>
       </c>
       <c r="AY61">
-        <v>3.95</v>
+        <v>7</v>
       </c>
       <c r="AZ61">
-        <v>4.3</v>
+        <v>6.4</v>
       </c>
       <c r="BA61">
-        <v>5.1</v>
+        <v>8.4</v>
       </c>
       <c r="BB61">
-        <v>4.9</v>
+        <v>7.4</v>
       </c>
       <c r="BC61">
-        <v>4.7</v>
+        <v>7</v>
       </c>
       <c r="BD61">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BE61">
-        <v>5.4</v>
+        <v>9</v>
       </c>
       <c r="BF61">
-        <v>4.4</v>
+        <v>6.2</v>
       </c>
       <c r="BG61">
-        <v>5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH61" t="s">
         <v>263</v>
@@ -12285,7 +12285,7 @@
         <v>254</v>
       </c>
       <c r="F62">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="G62">
         <v>1.71</v>
@@ -12297,10 +12297,10 @@
         <v>7.4</v>
       </c>
       <c r="J62">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K62">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L62">
         <v>1.43</v>
@@ -12309,10 +12309,10 @@
         <v>1.1</v>
       </c>
       <c r="N62">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="O62">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="P62">
         <v>1.66</v>
@@ -12333,7 +12333,7 @@
         <v>1.72</v>
       </c>
       <c r="V62">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W62">
         <v>2.4</v>
@@ -12342,7 +12342,7 @@
         <v>11</v>
       </c>
       <c r="Y62">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Z62">
         <v>270</v>
@@ -12360,7 +12360,7 @@
         <v>34</v>
       </c>
       <c r="AE62">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AF62">
         <v>8.800000000000001</v>
@@ -12372,7 +12372,7 @@
         <v>48</v>
       </c>
       <c r="AI62">
-        <v>450</v>
+        <v>700</v>
       </c>
       <c r="AJ62">
         <v>17</v>
@@ -12384,13 +12384,13 @@
         <v>65</v>
       </c>
       <c r="AM62">
-        <v>580</v>
+        <v>700</v>
       </c>
       <c r="AN62">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AO62">
-        <v>280</v>
+        <v>700</v>
       </c>
       <c r="AP62">
         <v>9.6</v>
@@ -12417,13 +12417,13 @@
         <v>40</v>
       </c>
       <c r="AX62">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AY62">
         <v>9.4</v>
       </c>
       <c r="AZ62">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BA62">
         <v>44</v>
@@ -12441,7 +12441,7 @@
         <v>90</v>
       </c>
       <c r="BF62">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BG62">
         <v>48</v>
@@ -12470,34 +12470,34 @@
         <v>1.69</v>
       </c>
       <c r="G63">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="H63">
         <v>5.9</v>
       </c>
       <c r="I63">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="J63">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K63">
         <v>3.9</v>
       </c>
       <c r="L63">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="M63">
         <v>1.1</v>
       </c>
       <c r="N63">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="O63">
         <v>1.44</v>
       </c>
       <c r="P63">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="Q63">
         <v>2.3</v>
@@ -12512,13 +12512,13 @@
         <v>2.14</v>
       </c>
       <c r="U63">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="V63">
         <v>1.17</v>
       </c>
       <c r="W63">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="X63">
         <v>13</v>
@@ -12542,7 +12542,7 @@
         <v>30</v>
       </c>
       <c r="AE63">
-        <v>480</v>
+        <v>700</v>
       </c>
       <c r="AF63">
         <v>9.6</v>
@@ -12554,7 +12554,7 @@
         <v>32</v>
       </c>
       <c r="AI63">
-        <v>450</v>
+        <v>700</v>
       </c>
       <c r="AJ63">
         <v>23</v>
@@ -12566,13 +12566,13 @@
         <v>65</v>
       </c>
       <c r="AM63">
-        <v>580</v>
+        <v>700</v>
       </c>
       <c r="AN63">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AO63">
-        <v>230</v>
+        <v>700</v>
       </c>
       <c r="AP63">
         <v>7.8</v>
@@ -12596,7 +12596,7 @@
         <v>18</v>
       </c>
       <c r="AW63">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AX63">
         <v>8</v>
@@ -12608,7 +12608,7 @@
         <v>18.5</v>
       </c>
       <c r="BA63">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BB63">
         <v>13.5</v>
@@ -12620,7 +12620,7 @@
         <v>36</v>
       </c>
       <c r="BE63">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BF63">
         <v>12</v>
@@ -12658,7 +12658,7 @@
         <v>4.7</v>
       </c>
       <c r="I64">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="J64">
         <v>3.15</v>
@@ -12682,13 +12682,13 @@
         <v>1.58</v>
       </c>
       <c r="Q64">
-        <v>2.26</v>
+        <v>2.42</v>
       </c>
       <c r="R64">
         <v>1.21</v>
       </c>
       <c r="S64">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T64">
         <v>2.1</v>
@@ -12706,16 +12706,16 @@
         <v>9.800000000000001</v>
       </c>
       <c r="Y64">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z64">
         <v>44</v>
       </c>
       <c r="AA64">
-        <v>170</v>
+        <v>900</v>
       </c>
       <c r="AB64">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="AC64">
         <v>8</v>
@@ -12724,19 +12724,19 @@
         <v>25</v>
       </c>
       <c r="AE64">
-        <v>110</v>
+        <v>470</v>
       </c>
       <c r="AF64">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AG64">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH64">
         <v>28</v>
       </c>
       <c r="AI64">
-        <v>120</v>
+        <v>450</v>
       </c>
       <c r="AJ64">
         <v>28</v>
@@ -12745,10 +12745,10 @@
         <v>30</v>
       </c>
       <c r="AL64">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="AM64">
-        <v>220</v>
+        <v>580</v>
       </c>
       <c r="AN64">
         <v>26</v>
@@ -12757,58 +12757,58 @@
         <v>160</v>
       </c>
       <c r="AP64">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ64">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AR64">
-        <v>5.3</v>
+        <v>14.5</v>
       </c>
       <c r="AS64">
-        <v>5.8</v>
+        <v>7.8</v>
       </c>
       <c r="AT64">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="AU64">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AV64">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AW64">
-        <v>5.7</v>
+        <v>7.6</v>
       </c>
       <c r="AX64">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="AY64">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="AZ64">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BA64">
-        <v>5.7</v>
+        <v>7.6</v>
       </c>
       <c r="BB64">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BC64">
-        <v>19.5</v>
+        <v>13</v>
       </c>
       <c r="BD64">
-        <v>5.5</v>
+        <v>7.2</v>
       </c>
       <c r="BE64">
-        <v>5.9</v>
+        <v>8</v>
       </c>
       <c r="BF64">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BG64">
-        <v>5.8</v>
+        <v>7.8</v>
       </c>
       <c r="BH64" t="s">
         <v>263</v>
@@ -12984,7 +12984,7 @@
         <v>6</v>
       </c>
       <c r="BE65">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BF65">
         <v>7.8</v>
@@ -13127,7 +13127,7 @@
         <v>11.5</v>
       </c>
       <c r="AR66">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AS66">
         <v>7.6</v>
@@ -13142,7 +13142,7 @@
         <v>20</v>
       </c>
       <c r="AW66">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AX66">
         <v>7.2</v>
@@ -13163,10 +13163,10 @@
         <v>19</v>
       </c>
       <c r="BD66">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BE66">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF66">
         <v>15</v>
@@ -13201,7 +13201,7 @@
         <v>2.14</v>
       </c>
       <c r="H67">
-        <v>1.09</v>
+        <v>1.93</v>
       </c>
       <c r="I67">
         <v>970</v>
@@ -13219,7 +13219,7 @@
         <v>1.01</v>
       </c>
       <c r="N67">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="O67">
         <v>1.15</v>
@@ -13383,16 +13383,16 @@
         <v>1.73</v>
       </c>
       <c r="H68">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I68">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="J68">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K68">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="L68">
         <v>1.01</v>
@@ -13425,7 +13425,7 @@
         <v>1.01</v>
       </c>
       <c r="V68">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W68">
         <v>2.36</v>
@@ -13565,64 +13565,64 @@
         <v>3.95</v>
       </c>
       <c r="H69">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="I69">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="J69">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="K69">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="L69">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="M69">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="N69">
-        <v>2.16</v>
+        <v>2.38</v>
       </c>
       <c r="O69">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="P69">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="Q69">
-        <v>3.25</v>
+        <v>2.94</v>
       </c>
       <c r="R69">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="S69">
         <v>7.2</v>
       </c>
       <c r="T69">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="U69">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="V69">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="W69">
         <v>1.33</v>
       </c>
       <c r="X69">
-        <v>970</v>
+        <v>8</v>
       </c>
       <c r="Y69">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="Z69">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AA69">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AB69">
         <v>10.5</v>
@@ -13631,43 +13631,43 @@
         <v>7.6</v>
       </c>
       <c r="AD69">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="AE69">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AF69">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AG69">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AH69">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AI69">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AJ69">
         <v>120</v>
       </c>
       <c r="AK69">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AL69">
+        <v>130</v>
+      </c>
+      <c r="AM69">
+        <v>320</v>
+      </c>
+      <c r="AN69">
         <v>150</v>
       </c>
-      <c r="AM69">
-        <v>380</v>
-      </c>
-      <c r="AN69">
-        <v>160</v>
-      </c>
       <c r="AO69">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="AP69">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AQ69">
         <v>5.6</v>
@@ -13676,7 +13676,7 @@
         <v>11.5</v>
       </c>
       <c r="AS69">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="AT69">
         <v>7.2</v>
@@ -13685,10 +13685,10 @@
         <v>6.2</v>
       </c>
       <c r="AV69">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AW69">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="AX69">
         <v>21</v>
@@ -13697,28 +13697,28 @@
         <v>15.5</v>
       </c>
       <c r="AZ69">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="BA69">
-        <v>3.15</v>
+        <v>7</v>
       </c>
       <c r="BB69">
-        <v>3.15</v>
+        <v>7.2</v>
       </c>
       <c r="BC69">
-        <v>3.15</v>
+        <v>7</v>
       </c>
       <c r="BD69">
-        <v>3.2</v>
+        <v>7.2</v>
       </c>
       <c r="BE69">
-        <v>3.25</v>
+        <v>7.4</v>
       </c>
       <c r="BF69">
-        <v>3.2</v>
+        <v>7.2</v>
       </c>
       <c r="BG69">
-        <v>3.1</v>
+        <v>6.6</v>
       </c>
       <c r="BH69" t="s">
         <v>263</v>
@@ -13768,7 +13768,7 @@
         <v>2.62</v>
       </c>
       <c r="O70">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="P70">
         <v>1.58</v>
@@ -13813,7 +13813,7 @@
         <v>8.4</v>
       </c>
       <c r="AD70">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AE70">
         <v>95</v>
@@ -13831,7 +13831,7 @@
         <v>110</v>
       </c>
       <c r="AJ70">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AK70">
         <v>28</v>
@@ -13864,7 +13864,7 @@
         <v>3.6</v>
       </c>
       <c r="AU70">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AV70">
         <v>4.9</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-04.xlsx
@@ -805,7 +805,7 @@
     <t>Deportes Recoleta</t>
   </si>
   <si>
-    <t>2026-05-03 21:42:42</t>
+    <t>2026-05-03 23:55:10</t>
   </si>
 </sst>
 </file>
@@ -1374,7 +1374,7 @@
         <v>2.08</v>
       </c>
       <c r="I2">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="J2">
         <v>2.86</v>
@@ -1383,7 +1383,7 @@
         <v>7</v>
       </c>
       <c r="L2">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="M2">
         <v>1.1</v>
@@ -1392,10 +1392,10 @@
         <v>1.1</v>
       </c>
       <c r="O2">
-        <v>1.1</v>
+        <v>1.46</v>
       </c>
       <c r="P2">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="Q2">
         <v>1.8</v>
@@ -1413,7 +1413,7 @@
         <v>1.11</v>
       </c>
       <c r="V2">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W2">
         <v>1.35</v>
@@ -1473,52 +1473,52 @@
         <v>600</v>
       </c>
       <c r="AP2">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AQ2">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AR2">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AS2">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AT2">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AU2">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AV2">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AW2">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AX2">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AY2">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AZ2">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="BA2">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="BB2">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="BC2">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="BD2">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="BE2">
-        <v>1.38</v>
+        <v>130</v>
       </c>
       <c r="BF2">
         <v>1.55</v>
@@ -1550,25 +1550,25 @@
         <v>1.95</v>
       </c>
       <c r="G3">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="H3">
         <v>1.95</v>
       </c>
       <c r="I3">
-        <v>4.5</v>
+        <v>3.05</v>
       </c>
       <c r="J3">
         <v>2.9</v>
       </c>
       <c r="K3">
-        <v>5.3</v>
+        <v>7</v>
       </c>
       <c r="L3">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M3">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N3">
         <v>1.1</v>
@@ -1583,7 +1583,7 @@
         <v>1.75</v>
       </c>
       <c r="R3">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="S3">
         <v>1.05</v>
@@ -1595,10 +1595,10 @@
         <v>1.11</v>
       </c>
       <c r="V3">
-        <v>1.43</v>
+        <v>1.58</v>
       </c>
       <c r="W3">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="X3">
         <v>19</v>
@@ -1661,7 +1661,7 @@
         <v>5.6</v>
       </c>
       <c r="AR3">
-        <v>1.33</v>
+        <v>5.7</v>
       </c>
       <c r="AS3">
         <v>1.34</v>
@@ -1673,7 +1673,7 @@
         <v>4.4</v>
       </c>
       <c r="AV3">
-        <v>1.32</v>
+        <v>5.1</v>
       </c>
       <c r="AW3">
         <v>1.34</v>
@@ -1700,7 +1700,7 @@
         <v>1.34</v>
       </c>
       <c r="BE3">
-        <v>1.34</v>
+        <v>120</v>
       </c>
       <c r="BF3">
         <v>1.55</v>
@@ -1729,7 +1729,7 @@
         <v>196</v>
       </c>
       <c r="F4">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="G4">
         <v>4.2</v>
@@ -1738,7 +1738,7 @@
         <v>2.14</v>
       </c>
       <c r="I4">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="J4">
         <v>3</v>
@@ -1768,16 +1768,16 @@
         <v>1.24</v>
       </c>
       <c r="S4">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="T4">
         <v>1.87</v>
       </c>
       <c r="U4">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="V4">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="W4">
         <v>1.32</v>
@@ -1837,7 +1837,7 @@
         <v>28</v>
       </c>
       <c r="AP4">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="AQ4">
         <v>3.75</v>
@@ -1867,7 +1867,7 @@
         <v>4.7</v>
       </c>
       <c r="AZ4">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BA4">
         <v>5.8</v>
@@ -1959,7 +1959,7 @@
         <v>1.82</v>
       </c>
       <c r="V5">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W5">
         <v>1.42</v>
@@ -1986,31 +1986,31 @@
         <v>970</v>
       </c>
       <c r="AE5">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="AF5">
-        <v>38</v>
+        <v>500</v>
       </c>
       <c r="AG5">
         <v>970</v>
       </c>
       <c r="AH5">
-        <v>38</v>
+        <v>950</v>
       </c>
       <c r="AI5">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AJ5">
         <v>900</v>
       </c>
       <c r="AK5">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AL5">
-        <v>170</v>
+        <v>500</v>
       </c>
       <c r="AM5">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN5">
         <v>600</v>
@@ -2019,58 +2019,58 @@
         <v>600</v>
       </c>
       <c r="AP5">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AQ5">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AR5">
-        <v>5.4</v>
+        <v>6.8</v>
       </c>
       <c r="AS5">
-        <v>6.6</v>
+        <v>5</v>
       </c>
       <c r="AT5">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AU5">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="AV5">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="AW5">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AX5">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AY5">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AZ5">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BA5">
         <v>6.8</v>
       </c>
       <c r="BB5">
+        <v>8</v>
+      </c>
+      <c r="BC5">
+        <v>9</v>
+      </c>
+      <c r="BD5">
+        <v>7.6</v>
+      </c>
+      <c r="BE5">
         <v>7</v>
       </c>
-      <c r="BC5">
-        <v>6.8</v>
-      </c>
-      <c r="BD5">
-        <v>7</v>
-      </c>
-      <c r="BE5">
-        <v>4.2</v>
-      </c>
       <c r="BF5">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BG5">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BH5" t="s">
         <v>263</v>
@@ -2093,19 +2093,19 @@
         <v>198</v>
       </c>
       <c r="F6">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="G6">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="H6">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="I6">
         <v>12</v>
       </c>
       <c r="J6">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K6">
         <v>4.6</v>
@@ -2117,13 +2117,13 @@
         <v>1.08</v>
       </c>
       <c r="N6">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O6">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P6">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="Q6">
         <v>2.04</v>
@@ -2132,7 +2132,7 @@
         <v>1.3</v>
       </c>
       <c r="S6">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="T6">
         <v>2.18</v>
@@ -2141,7 +2141,7 @@
         <v>1.68</v>
       </c>
       <c r="V6">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="W6">
         <v>2.74</v>
@@ -2162,7 +2162,7 @@
         <v>13</v>
       </c>
       <c r="AC6">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="AD6">
         <v>500</v>
@@ -2192,7 +2192,7 @@
         <v>500</v>
       </c>
       <c r="AM6">
-        <v>700</v>
+        <v>580</v>
       </c>
       <c r="AN6">
         <v>29</v>
@@ -2201,13 +2201,13 @@
         <v>700</v>
       </c>
       <c r="AP6">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AQ6">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AR6">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AS6">
         <v>4.2</v>
@@ -2216,13 +2216,13 @@
         <v>4.2</v>
       </c>
       <c r="AU6">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AV6">
         <v>7.6</v>
       </c>
       <c r="AW6">
-        <v>5.4</v>
+        <v>4.2</v>
       </c>
       <c r="AX6">
         <v>4.4</v>
@@ -2231,22 +2231,22 @@
         <v>5.1</v>
       </c>
       <c r="AZ6">
-        <v>4.7</v>
+        <v>7.4</v>
       </c>
       <c r="BA6">
-        <v>5.3</v>
+        <v>4.2</v>
       </c>
       <c r="BB6">
+        <v>6</v>
+      </c>
+      <c r="BC6">
+        <v>6.6</v>
+      </c>
+      <c r="BD6">
+        <v>5.1</v>
+      </c>
+      <c r="BE6">
         <v>4.5</v>
-      </c>
-      <c r="BC6">
-        <v>4.8</v>
-      </c>
-      <c r="BD6">
-        <v>3.15</v>
-      </c>
-      <c r="BE6">
-        <v>3.25</v>
       </c>
       <c r="BF6">
         <v>5</v>
@@ -2469,7 +2469,7 @@
         <v>8.4</v>
       </c>
       <c r="J8">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K8">
         <v>4.5</v>
@@ -2601,10 +2601,10 @@
         <v>6.4</v>
       </c>
       <c r="BB8">
-        <v>5.3</v>
+        <v>7</v>
       </c>
       <c r="BC8">
-        <v>5.3</v>
+        <v>8.4</v>
       </c>
       <c r="BD8">
         <v>5.9</v>
@@ -2642,10 +2642,10 @@
         <v>1.93</v>
       </c>
       <c r="G9">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="H9">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="I9">
         <v>5.2</v>
@@ -2663,7 +2663,7 @@
         <v>1.1</v>
       </c>
       <c r="N9">
-        <v>2.62</v>
+        <v>2.76</v>
       </c>
       <c r="O9">
         <v>1.43</v>
@@ -2672,13 +2672,13 @@
         <v>1.59</v>
       </c>
       <c r="Q9">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="R9">
         <v>1.22</v>
       </c>
       <c r="S9">
-        <v>3.45</v>
+        <v>4.4</v>
       </c>
       <c r="T9">
         <v>1.98</v>
@@ -2687,10 +2687,10 @@
         <v>1.78</v>
       </c>
       <c r="V9">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W9">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="X9">
         <v>11</v>
@@ -2717,13 +2717,13 @@
         <v>190</v>
       </c>
       <c r="AF9">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG9">
         <v>12</v>
       </c>
       <c r="AH9">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AI9">
         <v>230</v>
@@ -2738,67 +2738,67 @@
         <v>55</v>
       </c>
       <c r="AM9">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN9">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AO9">
-        <v>130</v>
+        <v>600</v>
       </c>
       <c r="AP9">
-        <v>4.2</v>
+        <v>7.8</v>
       </c>
       <c r="AQ9">
-        <v>4.5</v>
+        <v>10</v>
       </c>
       <c r="AR9">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AS9">
+        <v>6.8</v>
+      </c>
+      <c r="AT9">
+        <v>5.8</v>
+      </c>
+      <c r="AU9">
+        <v>6.2</v>
+      </c>
+      <c r="AV9">
+        <v>15</v>
+      </c>
+      <c r="AW9">
+        <v>6.6</v>
+      </c>
+      <c r="AX9">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY9">
+        <v>8.6</v>
+      </c>
+      <c r="AZ9">
+        <v>17</v>
+      </c>
+      <c r="BA9">
+        <v>6.8</v>
+      </c>
+      <c r="BB9">
+        <v>20</v>
+      </c>
+      <c r="BC9">
+        <v>20</v>
+      </c>
+      <c r="BD9">
         <v>6.4</v>
       </c>
-      <c r="AT9">
-        <v>3.6</v>
-      </c>
-      <c r="AU9">
-        <v>3.7</v>
-      </c>
-      <c r="AV9">
-        <v>5.2</v>
-      </c>
-      <c r="AW9">
-        <v>6.2</v>
-      </c>
-      <c r="AX9">
-        <v>4.5</v>
-      </c>
-      <c r="AY9">
-        <v>4.3</v>
-      </c>
-      <c r="AZ9">
-        <v>5.4</v>
-      </c>
-      <c r="BA9">
-        <v>6.2</v>
-      </c>
-      <c r="BB9">
-        <v>5.4</v>
-      </c>
-      <c r="BC9">
-        <v>5.4</v>
-      </c>
-      <c r="BD9">
-        <v>6</v>
-      </c>
       <c r="BE9">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BF9">
-        <v>5.4</v>
+        <v>18</v>
       </c>
       <c r="BG9">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BH9" t="s">
         <v>263</v>
@@ -2827,13 +2827,13 @@
         <v>3.65</v>
       </c>
       <c r="H10">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="I10">
         <v>2.78</v>
       </c>
       <c r="J10">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="K10">
         <v>3.05</v>
@@ -2845,7 +2845,7 @@
         <v>1.14</v>
       </c>
       <c r="N10">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="O10">
         <v>1.58</v>
@@ -2866,7 +2866,7 @@
         <v>2.16</v>
       </c>
       <c r="U10">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="V10">
         <v>1.56</v>
@@ -2923,10 +2923,10 @@
         <v>500</v>
       </c>
       <c r="AN10">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO10">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP10">
         <v>6.8</v>
@@ -2938,7 +2938,7 @@
         <v>12</v>
       </c>
       <c r="AS10">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="AT10">
         <v>7.8</v>
@@ -2956,7 +2956,7 @@
         <v>16</v>
       </c>
       <c r="AY10">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AZ10">
         <v>19.5</v>
@@ -3003,16 +3003,16 @@
         <v>203</v>
       </c>
       <c r="F11">
+        <v>1.74</v>
+      </c>
+      <c r="G11">
         <v>1.75</v>
       </c>
-      <c r="G11">
-        <v>1.76</v>
-      </c>
       <c r="H11">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="I11">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="J11">
         <v>4.1</v>
@@ -3051,13 +3051,13 @@
         <v>2.24</v>
       </c>
       <c r="V11">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="W11">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="X11">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Y11">
         <v>21</v>
@@ -3066,7 +3066,7 @@
         <v>40</v>
       </c>
       <c r="AA11">
-        <v>700</v>
+        <v>130</v>
       </c>
       <c r="AB11">
         <v>10.5</v>
@@ -3087,7 +3087,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AH11">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AI11">
         <v>60</v>
@@ -3108,28 +3108,28 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AO11">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AP11">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AQ11">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AR11">
         <v>36</v>
       </c>
       <c r="AS11">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AT11">
         <v>9.800000000000001</v>
       </c>
       <c r="AU11">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AV11">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AW11">
         <v>50</v>
@@ -3147,13 +3147,13 @@
         <v>55</v>
       </c>
       <c r="BB11">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BC11">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BD11">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BE11">
         <v>70</v>
@@ -3188,22 +3188,22 @@
         <v>3.55</v>
       </c>
       <c r="G12">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="H12">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="I12">
         <v>2.4</v>
       </c>
       <c r="J12">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K12">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L12">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="M12">
         <v>1.09</v>
@@ -3218,13 +3218,13 @@
         <v>1.68</v>
       </c>
       <c r="Q12">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R12">
         <v>1.25</v>
       </c>
       <c r="S12">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="T12">
         <v>1.78</v>
@@ -3236,10 +3236,10 @@
         <v>1.71</v>
       </c>
       <c r="W12">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="X12">
-        <v>13.5</v>
+        <v>19.5</v>
       </c>
       <c r="Y12">
         <v>9.6</v>
@@ -3254,10 +3254,10 @@
         <v>11.5</v>
       </c>
       <c r="AC12">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD12">
-        <v>13.5</v>
+        <v>21</v>
       </c>
       <c r="AE12">
         <v>65</v>
@@ -3266,10 +3266,10 @@
         <v>60</v>
       </c>
       <c r="AG12">
-        <v>27</v>
+        <v>970</v>
       </c>
       <c r="AH12">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="AI12">
         <v>500</v>
@@ -3287,13 +3287,13 @@
         <v>580</v>
       </c>
       <c r="AN12">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO12">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP12">
-        <v>8.800000000000001</v>
+        <v>5.8</v>
       </c>
       <c r="AQ12">
         <v>4.9</v>
@@ -3311,13 +3311,13 @@
         <v>6</v>
       </c>
       <c r="AV12">
-        <v>8.800000000000001</v>
+        <v>6.4</v>
       </c>
       <c r="AW12">
-        <v>19</v>
+        <v>7.6</v>
       </c>
       <c r="AX12">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="AY12">
         <v>8.4</v>
@@ -3326,25 +3326,25 @@
         <v>14.5</v>
       </c>
       <c r="BA12">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BB12">
+        <v>8.6</v>
+      </c>
+      <c r="BC12">
         <v>6.4</v>
       </c>
-      <c r="BC12">
-        <v>6.2</v>
-      </c>
       <c r="BD12">
-        <v>6.4</v>
+        <v>8.6</v>
       </c>
       <c r="BE12">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BF12">
-        <v>6.4</v>
+        <v>8.6</v>
       </c>
       <c r="BG12">
-        <v>5.6</v>
+        <v>7.2</v>
       </c>
       <c r="BH12" t="s">
         <v>263</v>
@@ -3370,13 +3370,13 @@
         <v>4.7</v>
       </c>
       <c r="G13">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="H13">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="I13">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="J13">
         <v>3.8</v>
@@ -3394,7 +3394,7 @@
         <v>3.85</v>
       </c>
       <c r="O13">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P13">
         <v>1.95</v>
@@ -3415,10 +3415,10 @@
         <v>2</v>
       </c>
       <c r="V13">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="W13">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="X13">
         <v>970</v>
@@ -3436,7 +3436,7 @@
         <v>970</v>
       </c>
       <c r="AC13">
-        <v>9.4</v>
+        <v>14</v>
       </c>
       <c r="AD13">
         <v>10.5</v>
@@ -3445,31 +3445,31 @@
         <v>970</v>
       </c>
       <c r="AF13">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="AG13">
-        <v>21</v>
+        <v>500</v>
       </c>
       <c r="AH13">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AI13">
-        <v>95</v>
+        <v>500</v>
       </c>
       <c r="AJ13">
         <v>900</v>
       </c>
       <c r="AK13">
-        <v>170</v>
+        <v>700</v>
       </c>
       <c r="AL13">
-        <v>190</v>
+        <v>700</v>
       </c>
       <c r="AM13">
         <v>580</v>
       </c>
       <c r="AN13">
-        <v>300</v>
+        <v>700</v>
       </c>
       <c r="AO13">
         <v>55</v>
@@ -3564,7 +3564,7 @@
         <v>2.48</v>
       </c>
       <c r="K14">
-        <v>950</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L14">
         <v>1.01</v>
@@ -3600,7 +3600,7 @@
         <v>1.07</v>
       </c>
       <c r="W14">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="X14">
         <v>1000</v>
@@ -3651,58 +3651,58 @@
         <v>1000</v>
       </c>
       <c r="AN14">
-        <v>55</v>
+        <v>600</v>
       </c>
       <c r="AO14">
         <v>1000</v>
       </c>
       <c r="AP14">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AQ14">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AR14">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AS14">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AT14">
         <v>3.25</v>
       </c>
       <c r="AU14">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AV14">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AW14">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AX14">
+        <v>1.39</v>
+      </c>
+      <c r="AY14">
         <v>1.38</v>
       </c>
-      <c r="AY14">
-        <v>1.37</v>
-      </c>
       <c r="AZ14">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="BA14">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="BB14">
         <v>6.4</v>
       </c>
       <c r="BC14">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="BD14">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="BE14">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="BF14">
         <v>4.1</v>
@@ -3839,58 +3839,58 @@
         <v>1000</v>
       </c>
       <c r="AP15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE15">
         <v>1.01</v>
       </c>
       <c r="BF15">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="BG15">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="BH15" t="s">
         <v>263</v>
@@ -3916,7 +3916,7 @@
         <v>1.62</v>
       </c>
       <c r="G16">
-        <v>5.4</v>
+        <v>4</v>
       </c>
       <c r="H16">
         <v>2.7</v>
@@ -3961,16 +3961,16 @@
         <v>1.11</v>
       </c>
       <c r="V16">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="W16">
         <v>1.55</v>
       </c>
       <c r="X16">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="Y16">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="Z16">
         <v>500</v>
@@ -3979,13 +3979,13 @@
         <v>900</v>
       </c>
       <c r="AB16">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AC16">
-        <v>95</v>
+        <v>950</v>
       </c>
       <c r="AD16">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AE16">
         <v>500</v>
@@ -3997,7 +3997,7 @@
         <v>970</v>
       </c>
       <c r="AH16">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AI16">
         <v>500</v>
@@ -4015,7 +4015,7 @@
         <v>500</v>
       </c>
       <c r="AN16">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO16">
         <v>500</v>
@@ -4128,7 +4128,7 @@
         <v>1.24</v>
       </c>
       <c r="Q17">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="R17">
         <v>1.12</v>
@@ -4203,58 +4203,58 @@
         <v>1000</v>
       </c>
       <c r="AP17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY17">
         <v>10</v>
       </c>
       <c r="AZ17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE17">
         <v>1.01</v>
       </c>
       <c r="BF17">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="BG17">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="BH17" t="s">
         <v>263</v>
@@ -4280,7 +4280,7 @@
         <v>1.5</v>
       </c>
       <c r="G18">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="H18">
         <v>7.4</v>
@@ -4307,7 +4307,7 @@
         <v>1.31</v>
       </c>
       <c r="P18">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="Q18">
         <v>1.85</v>
@@ -4316,19 +4316,19 @@
         <v>1.33</v>
       </c>
       <c r="S18">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="T18">
         <v>2.06</v>
       </c>
       <c r="U18">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="V18">
         <v>1.13</v>
       </c>
       <c r="W18">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="X18">
         <v>15.5</v>
@@ -4385,28 +4385,28 @@
         <v>250</v>
       </c>
       <c r="AP18">
-        <v>5.3</v>
+        <v>12.5</v>
       </c>
       <c r="AQ18">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="AR18">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AS18">
         <v>7.6</v>
       </c>
       <c r="AT18">
-        <v>4</v>
+        <v>6.4</v>
       </c>
       <c r="AU18">
-        <v>4.5</v>
+        <v>8.4</v>
       </c>
       <c r="AV18">
-        <v>18</v>
+        <v>6.6</v>
       </c>
       <c r="AW18">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AX18">
         <v>4.3</v>
@@ -4415,25 +4415,25 @@
         <v>4.5</v>
       </c>
       <c r="AZ18">
-        <v>6.2</v>
+        <v>21</v>
       </c>
       <c r="BA18">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BB18">
-        <v>5.1</v>
+        <v>11.5</v>
       </c>
       <c r="BC18">
-        <v>5.6</v>
+        <v>14.5</v>
       </c>
       <c r="BD18">
-        <v>26</v>
+        <v>6.8</v>
       </c>
       <c r="BE18">
         <v>7.6</v>
       </c>
       <c r="BF18">
-        <v>4.4</v>
+        <v>7.8</v>
       </c>
       <c r="BG18">
         <v>7.8</v>
@@ -4471,7 +4471,7 @@
         <v>1.75</v>
       </c>
       <c r="J19">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K19">
         <v>4.5</v>
@@ -4489,16 +4489,16 @@
         <v>1.2</v>
       </c>
       <c r="P19">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="Q19">
         <v>1.53</v>
       </c>
       <c r="R19">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="S19">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="T19">
         <v>1.65</v>
@@ -4516,10 +4516,10 @@
         <v>29</v>
       </c>
       <c r="Y19">
+        <v>14</v>
+      </c>
+      <c r="Z19">
         <v>14.5</v>
-      </c>
-      <c r="Z19">
-        <v>15</v>
       </c>
       <c r="AA19">
         <v>22</v>
@@ -4528,10 +4528,10 @@
         <v>29</v>
       </c>
       <c r="AC19">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AD19">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AE19">
         <v>20</v>
@@ -4555,7 +4555,7 @@
         <v>320</v>
       </c>
       <c r="AL19">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="AM19">
         <v>580</v>
@@ -4567,7 +4567,7 @@
         <v>9</v>
       </c>
       <c r="AP19">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="AQ19">
         <v>6.4</v>
@@ -4579,7 +4579,7 @@
         <v>9</v>
       </c>
       <c r="AT19">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="AU19">
         <v>5.8</v>
@@ -4591,34 +4591,34 @@
         <v>8.4</v>
       </c>
       <c r="AX19">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="AY19">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="AZ19">
-        <v>3.85</v>
+        <v>4.6</v>
       </c>
       <c r="BA19">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="BB19">
-        <v>4.3</v>
+        <v>5.3</v>
       </c>
       <c r="BC19">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="BD19">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="BE19">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="BF19">
         <v>7</v>
       </c>
       <c r="BG19">
-        <v>3.05</v>
+        <v>3.55</v>
       </c>
       <c r="BH19" t="s">
         <v>263</v>
@@ -4644,10 +4644,10 @@
         <v>2.56</v>
       </c>
       <c r="G20">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="H20">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="I20">
         <v>2.82</v>
@@ -4692,7 +4692,7 @@
         <v>1.54</v>
       </c>
       <c r="W20">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="X20">
         <v>22</v>
@@ -4743,7 +4743,7 @@
         <v>580</v>
       </c>
       <c r="AN20">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AO20">
         <v>17.5</v>
@@ -4782,7 +4782,7 @@
         <v>11.5</v>
       </c>
       <c r="BA20">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BB20">
         <v>32</v>
@@ -4794,7 +4794,7 @@
         <v>7.4</v>
       </c>
       <c r="BE20">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF20">
         <v>14</v>
@@ -4934,37 +4934,37 @@
         <v>11.5</v>
       </c>
       <c r="AQ21">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="AR21">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AS21">
         <v>8.4</v>
       </c>
       <c r="AT21">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AU21">
         <v>8.4</v>
       </c>
       <c r="AV21">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AW21">
         <v>9.4</v>
       </c>
       <c r="AX21">
-        <v>4.8</v>
+        <v>6.4</v>
       </c>
       <c r="AY21">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ21">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA21">
-        <v>9.4</v>
+        <v>29</v>
       </c>
       <c r="BB21">
         <v>12</v>
@@ -5011,13 +5011,13 @@
         <v>2.2</v>
       </c>
       <c r="H22">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="I22">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="J22">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K22">
         <v>3.6</v>
@@ -5053,7 +5053,7 @@
         <v>1.98</v>
       </c>
       <c r="V22">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W22">
         <v>1.83</v>
@@ -5113,19 +5113,19 @@
         <v>500</v>
       </c>
       <c r="AP22">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AQ22">
         <v>11.5</v>
       </c>
       <c r="AR22">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AS22">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AT22">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AU22">
         <v>6.6</v>
@@ -5134,7 +5134,7 @@
         <v>14</v>
       </c>
       <c r="AW22">
-        <v>10.5</v>
+        <v>24</v>
       </c>
       <c r="AX22">
         <v>11</v>
@@ -5146,10 +5146,10 @@
         <v>17</v>
       </c>
       <c r="BA22">
-        <v>9.6</v>
+        <v>29</v>
       </c>
       <c r="BB22">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BC22">
         <v>21</v>
@@ -5161,10 +5161,10 @@
         <v>10</v>
       </c>
       <c r="BF22">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BG22">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BH22" t="s">
         <v>263</v>
@@ -5187,25 +5187,25 @@
         <v>215</v>
       </c>
       <c r="F23">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="G23">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="H23">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="I23">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="J23">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="K23">
         <v>3.95</v>
       </c>
       <c r="L23">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="M23">
         <v>1.07</v>
@@ -5217,7 +5217,7 @@
         <v>1.34</v>
       </c>
       <c r="P23">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="Q23">
         <v>2</v>
@@ -5226,19 +5226,19 @@
         <v>1.32</v>
       </c>
       <c r="S23">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="T23">
         <v>1.93</v>
       </c>
       <c r="U23">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="V23">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="W23">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="X23">
         <v>15.5</v>
@@ -5250,7 +5250,7 @@
         <v>10.5</v>
       </c>
       <c r="AA23">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AB23">
         <v>18.5</v>
@@ -5289,7 +5289,7 @@
         <v>580</v>
       </c>
       <c r="AN23">
-        <v>410</v>
+        <v>700</v>
       </c>
       <c r="AO23">
         <v>13</v>
@@ -5334,13 +5334,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BC23">
-        <v>8.800000000000001</v>
+        <v>28</v>
       </c>
       <c r="BD23">
-        <v>8.800000000000001</v>
+        <v>28</v>
       </c>
       <c r="BE23">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BF23">
         <v>9</v>
@@ -5384,7 +5384,7 @@
         <v>3.65</v>
       </c>
       <c r="K24">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="L24">
         <v>1.43</v>
@@ -5480,13 +5480,13 @@
         <v>11.5</v>
       </c>
       <c r="AQ24">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AR24">
         <v>14.5</v>
       </c>
       <c r="AS24">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AT24">
         <v>7.2</v>
@@ -5507,13 +5507,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ24">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BA24">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BB24">
-        <v>15.5</v>
+        <v>19</v>
       </c>
       <c r="BC24">
         <v>18.5</v>
@@ -5522,7 +5522,7 @@
         <v>28</v>
       </c>
       <c r="BE24">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BF24">
         <v>10.5</v>
@@ -5581,13 +5581,13 @@
         <v>1.32</v>
       </c>
       <c r="P25">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="Q25">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="R25">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S25">
         <v>3.4</v>
@@ -5596,13 +5596,13 @@
         <v>1.77</v>
       </c>
       <c r="U25">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="V25">
         <v>1.71</v>
       </c>
       <c r="W25">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="X25">
         <v>14.5</v>
@@ -5611,7 +5611,7 @@
         <v>10.5</v>
       </c>
       <c r="Z25">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="AA25">
         <v>32</v>
@@ -5626,13 +5626,13 @@
         <v>12</v>
       </c>
       <c r="AE25">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AF25">
         <v>27</v>
       </c>
       <c r="AG25">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AH25">
         <v>18.5</v>
@@ -5647,22 +5647,22 @@
         <v>55</v>
       </c>
       <c r="AL25">
-        <v>65</v>
+        <v>250</v>
       </c>
       <c r="AM25">
         <v>580</v>
       </c>
       <c r="AN25">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="AO25">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="AP25">
         <v>11.5</v>
       </c>
       <c r="AQ25">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AR25">
         <v>12</v>
@@ -5671,7 +5671,7 @@
         <v>13</v>
       </c>
       <c r="AT25">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AU25">
         <v>6.8</v>
@@ -5692,19 +5692,19 @@
         <v>15</v>
       </c>
       <c r="BA25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BB25">
-        <v>5.7</v>
+        <v>7.2</v>
       </c>
       <c r="BC25">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="BD25">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="BE25">
-        <v>5.8</v>
+        <v>7.4</v>
       </c>
       <c r="BF25">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>3.95</v>
       </c>
       <c r="L26">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="M26">
         <v>1.06</v>
@@ -5933,7 +5933,7 @@
         <v>3.75</v>
       </c>
       <c r="L27">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="M27">
         <v>1.07</v>
@@ -6241,7 +6241,7 @@
         <v>7.2</v>
       </c>
       <c r="BB28">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="BC28">
         <v>7.2</v>
@@ -6256,7 +6256,7 @@
         <v>7.2</v>
       </c>
       <c r="BG28">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BH28" t="s">
         <v>263</v>
@@ -6288,7 +6288,7 @@
         <v>7.4</v>
       </c>
       <c r="I29">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="J29">
         <v>4.9</v>
@@ -6318,7 +6318,7 @@
         <v>1.55</v>
       </c>
       <c r="S29">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="T29">
         <v>1.87</v>
@@ -6414,7 +6414,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AY29">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ29">
         <v>19.5</v>
@@ -6494,7 +6494,7 @@
         <v>1.75</v>
       </c>
       <c r="Q30">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="R30">
         <v>1.35</v>
@@ -6509,7 +6509,7 @@
         <v>1.65</v>
       </c>
       <c r="V30">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="W30">
         <v>1.11</v>
@@ -6608,13 +6608,13 @@
         <v>4.3</v>
       </c>
       <c r="BC30">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="BD30">
         <v>4.4</v>
       </c>
       <c r="BE30">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BF30">
         <v>4.3</v>
@@ -6658,10 +6658,10 @@
         <v>3.5</v>
       </c>
       <c r="K31">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L31">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="M31">
         <v>1.07</v>
@@ -6673,7 +6673,7 @@
         <v>1.34</v>
       </c>
       <c r="P31">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="Q31">
         <v>1.96</v>
@@ -6691,10 +6691,10 @@
         <v>2.06</v>
       </c>
       <c r="V31">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W31">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="X31">
         <v>14.5</v>
@@ -6796,7 +6796,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BE31">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF31">
         <v>19.5</v>
@@ -6825,22 +6825,22 @@
         <v>224</v>
       </c>
       <c r="F32">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="G32">
         <v>2.64</v>
       </c>
       <c r="H32">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="I32">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="J32">
         <v>3.25</v>
       </c>
       <c r="K32">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L32">
         <v>1.43</v>
@@ -6879,7 +6879,7 @@
         <v>1.6</v>
       </c>
       <c r="X32">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="Y32">
         <v>12</v>
@@ -6900,7 +6900,7 @@
         <v>14.5</v>
       </c>
       <c r="AE32">
-        <v>95</v>
+        <v>500</v>
       </c>
       <c r="AF32">
         <v>17</v>
@@ -6909,13 +6909,13 @@
         <v>12.5</v>
       </c>
       <c r="AH32">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="AI32">
         <v>500</v>
       </c>
       <c r="AJ32">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AK32">
         <v>75</v>
@@ -6942,7 +6942,7 @@
         <v>18</v>
       </c>
       <c r="AS32">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AT32">
         <v>8.4</v>
@@ -6954,7 +6954,7 @@
         <v>11.5</v>
       </c>
       <c r="AW32">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AX32">
         <v>13.5</v>
@@ -6966,25 +6966,25 @@
         <v>11.5</v>
       </c>
       <c r="BA32">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BB32">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BC32">
         <v>21</v>
       </c>
       <c r="BD32">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BE32">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF32">
         <v>18.5</v>
       </c>
       <c r="BG32">
-        <v>6.8</v>
+        <v>28</v>
       </c>
       <c r="BH32" t="s">
         <v>263</v>
@@ -7007,10 +7007,10 @@
         <v>225</v>
       </c>
       <c r="F33">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="G33">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="H33">
         <v>2.56</v>
@@ -7025,7 +7025,7 @@
         <v>3.3</v>
       </c>
       <c r="L33">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="M33">
         <v>1.09</v>
@@ -7058,10 +7058,10 @@
         <v>1.63</v>
       </c>
       <c r="W33">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="X33">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Y33">
         <v>9.4</v>
@@ -7148,10 +7148,10 @@
         <v>17</v>
       </c>
       <c r="BA33">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BB33">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BC33">
         <v>36</v>
@@ -7160,7 +7160,7 @@
         <v>48</v>
       </c>
       <c r="BE33">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="BF33">
         <v>40</v>
@@ -7189,13 +7189,13 @@
         <v>226</v>
       </c>
       <c r="F34">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="G34">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="H34">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="I34">
         <v>2.6</v>
@@ -7213,31 +7213,31 @@
         <v>1.05</v>
       </c>
       <c r="N34">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="O34">
         <v>1.24</v>
       </c>
       <c r="P34">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="Q34">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="R34">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="S34">
         <v>2.84</v>
       </c>
       <c r="T34">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="U34">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="V34">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="W34">
         <v>1.52</v>
@@ -7255,7 +7255,7 @@
         <v>36</v>
       </c>
       <c r="AB34">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AC34">
         <v>8.6</v>
@@ -7279,7 +7279,7 @@
         <v>32</v>
       </c>
       <c r="AJ34">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AK34">
         <v>30</v>
@@ -7291,28 +7291,28 @@
         <v>55</v>
       </c>
       <c r="AN34">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AO34">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AP34">
         <v>18</v>
       </c>
       <c r="AQ34">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AR34">
         <v>16.5</v>
       </c>
       <c r="AS34">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AT34">
         <v>13</v>
       </c>
       <c r="AU34">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV34">
         <v>10.5</v>
@@ -7330,7 +7330,7 @@
         <v>14</v>
       </c>
       <c r="BA34">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BB34">
         <v>34</v>
@@ -7339,7 +7339,7 @@
         <v>26</v>
       </c>
       <c r="BD34">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BE34">
         <v>46</v>
@@ -7348,7 +7348,7 @@
         <v>18.5</v>
       </c>
       <c r="BG34">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BH34" t="s">
         <v>263</v>
@@ -7377,19 +7377,19 @@
         <v>1.27</v>
       </c>
       <c r="H35">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="I35">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J35">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="K35">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="L35">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="M35">
         <v>1.05</v>
@@ -7404,10 +7404,10 @@
         <v>1.96</v>
       </c>
       <c r="Q35">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="R35">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="S35">
         <v>3.05</v>
@@ -7419,31 +7419,31 @@
         <v>1.44</v>
       </c>
       <c r="V35">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W35">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="X35">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Y35">
-        <v>100</v>
+        <v>950</v>
       </c>
       <c r="Z35">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="AA35">
         <v>1000</v>
       </c>
       <c r="AB35">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AC35">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AD35">
-        <v>300</v>
+        <v>950</v>
       </c>
       <c r="AE35">
         <v>1000</v>
@@ -7455,10 +7455,10 @@
         <v>13.5</v>
       </c>
       <c r="AH35">
-        <v>160</v>
+        <v>950</v>
       </c>
       <c r="AI35">
-        <v>590</v>
+        <v>560</v>
       </c>
       <c r="AJ35">
         <v>8.800000000000001</v>
@@ -7470,7 +7470,7 @@
         <v>330</v>
       </c>
       <c r="AM35">
-        <v>610</v>
+        <v>590</v>
       </c>
       <c r="AN35">
         <v>5.7</v>
@@ -7482,13 +7482,13 @@
         <v>14.5</v>
       </c>
       <c r="AQ35">
-        <v>16</v>
+        <v>7.6</v>
       </c>
       <c r="AR35">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AS35">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT35">
         <v>5.7</v>
@@ -7497,22 +7497,22 @@
         <v>13</v>
       </c>
       <c r="AV35">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AW35">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX35">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AY35">
         <v>10</v>
       </c>
       <c r="AZ35">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BA35">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BB35">
         <v>6.8</v>
@@ -7521,16 +7521,16 @@
         <v>14</v>
       </c>
       <c r="BD35">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BE35">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BF35">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BG35">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH35" t="s">
         <v>263</v>
@@ -7556,7 +7556,7 @@
         <v>1.82</v>
       </c>
       <c r="G36">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="H36">
         <v>4.8</v>
@@ -7568,7 +7568,7 @@
         <v>3.55</v>
       </c>
       <c r="K36">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="L36">
         <v>1.44</v>
@@ -7625,7 +7625,7 @@
         <v>10</v>
       </c>
       <c r="AD36">
-        <v>46</v>
+        <v>950</v>
       </c>
       <c r="AE36">
         <v>700</v>
@@ -7744,43 +7744,43 @@
         <v>2.48</v>
       </c>
       <c r="I37">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="J37">
         <v>3.35</v>
       </c>
       <c r="K37">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L37">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="M37">
         <v>1.08</v>
       </c>
       <c r="N37">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O37">
         <v>1.35</v>
       </c>
       <c r="P37">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="Q37">
         <v>2.04</v>
       </c>
       <c r="R37">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="S37">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="T37">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="U37">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V37">
         <v>1.62</v>
@@ -7789,7 +7789,7 @@
         <v>1.44</v>
       </c>
       <c r="X37">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y37">
         <v>10.5</v>
@@ -7888,7 +7888,7 @@
         <v>38</v>
       </c>
       <c r="BE37">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF37">
         <v>26</v>
@@ -7917,10 +7917,10 @@
         <v>230</v>
       </c>
       <c r="F38">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="G38">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="H38">
         <v>5.5</v>
@@ -7941,7 +7941,7 @@
         <v>1.06</v>
       </c>
       <c r="N38">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="O38">
         <v>1.3</v>
@@ -7950,13 +7950,13 @@
         <v>2.06</v>
       </c>
       <c r="Q38">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="R38">
         <v>1.4</v>
       </c>
       <c r="S38">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="T38">
         <v>1.88</v>
@@ -7965,7 +7965,7 @@
         <v>2.04</v>
       </c>
       <c r="V38">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W38">
         <v>2.38</v>
@@ -7989,7 +7989,7 @@
         <v>9.4</v>
       </c>
       <c r="AD38">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AE38">
         <v>160</v>
@@ -8004,7 +8004,7 @@
         <v>21</v>
       </c>
       <c r="AI38">
-        <v>160</v>
+        <v>320</v>
       </c>
       <c r="AJ38">
         <v>17</v>
@@ -8022,7 +8022,7 @@
         <v>10</v>
       </c>
       <c r="AO38">
-        <v>95</v>
+        <v>160</v>
       </c>
       <c r="AP38">
         <v>14.5</v>
@@ -8073,7 +8073,7 @@
         <v>40</v>
       </c>
       <c r="BF38">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG38">
         <v>36</v>
@@ -8138,7 +8138,7 @@
         <v>1.23</v>
       </c>
       <c r="S39">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="T39">
         <v>1.96</v>
@@ -8201,7 +8201,7 @@
         <v>580</v>
       </c>
       <c r="AN39">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="AO39">
         <v>70</v>
@@ -8284,7 +8284,7 @@
         <v>2.44</v>
       </c>
       <c r="G40">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="H40">
         <v>3</v>
@@ -8466,10 +8466,10 @@
         <v>1.56</v>
       </c>
       <c r="G41">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="H41">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="I41">
         <v>6.4</v>
@@ -8499,7 +8499,7 @@
         <v>1.55</v>
       </c>
       <c r="R41">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="S41">
         <v>2.4</v>
@@ -8514,7 +8514,7 @@
         <v>1.18</v>
       </c>
       <c r="W41">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="X41">
         <v>29</v>
@@ -8580,7 +8580,7 @@
         <v>23</v>
       </c>
       <c r="AS41">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AT41">
         <v>11</v>
@@ -8622,7 +8622,7 @@
         <v>5.6</v>
       </c>
       <c r="BG41">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BH41" t="s">
         <v>263</v>
@@ -8648,7 +8648,7 @@
         <v>1.85</v>
       </c>
       <c r="G42">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="H42">
         <v>4.1</v>
@@ -8696,7 +8696,7 @@
         <v>1.31</v>
       </c>
       <c r="W42">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="X42">
         <v>26</v>
@@ -8759,7 +8759,7 @@
         <v>9</v>
       </c>
       <c r="AR42">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="AS42">
         <v>6.6</v>
@@ -8830,7 +8830,7 @@
         <v>2.24</v>
       </c>
       <c r="G43">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="H43">
         <v>3.5</v>
@@ -8845,7 +8845,7 @@
         <v>3.6</v>
       </c>
       <c r="L43">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="M43">
         <v>1.09</v>
@@ -8968,16 +8968,16 @@
         <v>14</v>
       </c>
       <c r="BA43">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BB43">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BC43">
         <v>20</v>
       </c>
       <c r="BD43">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BE43">
         <v>6.8</v>
@@ -9021,13 +9021,13 @@
         <v>6.8</v>
       </c>
       <c r="J44">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K44">
         <v>3.95</v>
       </c>
       <c r="L44">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="M44">
         <v>1.08</v>
@@ -9057,7 +9057,7 @@
         <v>1.81</v>
       </c>
       <c r="V44">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W44">
         <v>2.24</v>
@@ -9123,7 +9123,7 @@
         <v>14</v>
       </c>
       <c r="AR44">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AS44">
         <v>5.6</v>
@@ -9200,13 +9200,13 @@
         <v>3.95</v>
       </c>
       <c r="I45">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="J45">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="K45">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="L45">
         <v>1.51</v>
@@ -9257,7 +9257,7 @@
         <v>900</v>
       </c>
       <c r="AB45">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AC45">
         <v>7</v>
@@ -9308,7 +9308,7 @@
         <v>20</v>
       </c>
       <c r="AS45">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AT45">
         <v>6.2</v>
@@ -9332,7 +9332,7 @@
         <v>19.5</v>
       </c>
       <c r="BA45">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BB45">
         <v>14.5</v>
@@ -9341,16 +9341,16 @@
         <v>16</v>
       </c>
       <c r="BD45">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BE45">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BF45">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BG45">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH45" t="s">
         <v>263</v>
@@ -9379,7 +9379,7 @@
         <v>1.38</v>
       </c>
       <c r="H46">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="I46">
         <v>9</v>
@@ -9388,7 +9388,7 @@
         <v>6.4</v>
       </c>
       <c r="K46">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="L46">
         <v>1.16</v>
@@ -9406,25 +9406,25 @@
         <v>3.8</v>
       </c>
       <c r="Q46">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="R46">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="S46">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="T46">
         <v>1.61</v>
       </c>
       <c r="U46">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="V46">
         <v>1.12</v>
       </c>
       <c r="W46">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="X46">
         <v>60</v>
@@ -9454,7 +9454,7 @@
         <v>13.5</v>
       </c>
       <c r="AG46">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH46">
         <v>24</v>
@@ -9466,7 +9466,7 @@
         <v>15</v>
       </c>
       <c r="AK46">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AL46">
         <v>27</v>
@@ -9493,7 +9493,7 @@
         <v>65</v>
       </c>
       <c r="AT46">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AU46">
         <v>15</v>
@@ -9520,7 +9520,7 @@
         <v>12</v>
       </c>
       <c r="BC46">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BD46">
         <v>17</v>
@@ -9737,10 +9737,10 @@
         <v>240</v>
       </c>
       <c r="F48">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="G48">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="H48">
         <v>3.1</v>
@@ -9749,10 +9749,10 @@
         <v>3.4</v>
       </c>
       <c r="J48">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="K48">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L48">
         <v>1.4</v>
@@ -9803,25 +9803,25 @@
         <v>60</v>
       </c>
       <c r="AB48">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC48">
         <v>8.199999999999999</v>
       </c>
       <c r="AD48">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AE48">
         <v>46</v>
       </c>
       <c r="AF48">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AG48">
         <v>14</v>
       </c>
       <c r="AH48">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI48">
         <v>55</v>
@@ -9839,7 +9839,7 @@
         <v>120</v>
       </c>
       <c r="AN48">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AO48">
         <v>44</v>
@@ -9854,7 +9854,7 @@
         <v>16</v>
       </c>
       <c r="AS48">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="AT48">
         <v>8.800000000000001</v>
@@ -9866,7 +9866,7 @@
         <v>10</v>
       </c>
       <c r="AW48">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="AX48">
         <v>11.5</v>
@@ -9878,10 +9878,10 @@
         <v>14.5</v>
       </c>
       <c r="BA48">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BB48">
-        <v>5.2</v>
+        <v>24</v>
       </c>
       <c r="BC48">
         <v>19.5</v>
@@ -9890,13 +9890,13 @@
         <v>29</v>
       </c>
       <c r="BE48">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BF48">
         <v>19.5</v>
       </c>
       <c r="BG48">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BH48" t="s">
         <v>263</v>
@@ -9958,7 +9958,7 @@
         <v>1.16</v>
       </c>
       <c r="S49">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="T49">
         <v>1.11</v>
@@ -10027,58 +10027,58 @@
         <v>1000</v>
       </c>
       <c r="AP49">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ49">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR49">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS49">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT49">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU49">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV49">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW49">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX49">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY49">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ49">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA49">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB49">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC49">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD49">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE49">
         <v>1.01</v>
       </c>
       <c r="BF49">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="BG49">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="BH49" t="s">
         <v>263</v>
@@ -10104,16 +10104,16 @@
         <v>1.45</v>
       </c>
       <c r="G50">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="H50">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="I50">
         <v>7.6</v>
       </c>
       <c r="J50">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="K50">
         <v>5.8</v>
@@ -10131,7 +10131,7 @@
         <v>1.17</v>
       </c>
       <c r="P50">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="Q50">
         <v>1.52</v>
@@ -10301,7 +10301,7 @@
         <v>5.3</v>
       </c>
       <c r="L51">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="M51">
         <v>1.03</v>
@@ -10331,7 +10331,7 @@
         <v>2.26</v>
       </c>
       <c r="V51">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="W51">
         <v>2.6</v>
@@ -10412,7 +10412,7 @@
         <v>18</v>
       </c>
       <c r="AW51">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="AX51">
         <v>10</v>
@@ -10501,7 +10501,7 @@
         <v>1.79</v>
       </c>
       <c r="R52">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="S52">
         <v>2.96</v>
@@ -10656,7 +10656,7 @@
         <v>6.8</v>
       </c>
       <c r="I53">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="J53">
         <v>4.9</v>
@@ -10668,28 +10668,28 @@
         <v>1.23</v>
       </c>
       <c r="M53">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="N53">
         <v>6</v>
       </c>
       <c r="O53">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="P53">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="Q53">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="R53">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="S53">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="T53">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="U53">
         <v>2.3</v>
@@ -10716,7 +10716,7 @@
         <v>12.5</v>
       </c>
       <c r="AC53">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AD53">
         <v>29</v>
@@ -10749,7 +10749,7 @@
         <v>80</v>
       </c>
       <c r="AN53">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="AO53">
         <v>90</v>
@@ -10758,28 +10758,28 @@
         <v>24</v>
       </c>
       <c r="AQ53">
-        <v>25</v>
+        <v>14.5</v>
       </c>
       <c r="AR53">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AS53">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AT53">
         <v>10.5</v>
       </c>
       <c r="AU53">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AV53">
         <v>13</v>
       </c>
       <c r="AW53">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AX53">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AY53">
         <v>9.199999999999999</v>
@@ -10788,7 +10788,7 @@
         <v>16.5</v>
       </c>
       <c r="BA53">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="BB53">
         <v>12.5</v>
@@ -10803,10 +10803,10 @@
         <v>36</v>
       </c>
       <c r="BF53">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BG53">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="BH53" t="s">
         <v>263</v>
@@ -10835,7 +10835,7 @@
         <v>1.64</v>
       </c>
       <c r="H54">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="I54">
         <v>6.6</v>
@@ -10859,22 +10859,22 @@
         <v>1.33</v>
       </c>
       <c r="P54">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="Q54">
         <v>1.96</v>
       </c>
       <c r="R54">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="S54">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="T54">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U54">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="V54">
         <v>1.18</v>
@@ -10907,7 +10907,7 @@
         <v>95</v>
       </c>
       <c r="AF54">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG54">
         <v>9.4</v>
@@ -10940,7 +10940,7 @@
         <v>14</v>
       </c>
       <c r="AQ54">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AR54">
         <v>44</v>
@@ -10958,10 +10958,10 @@
         <v>22</v>
       </c>
       <c r="AW54">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AX54">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY54">
         <v>9.199999999999999</v>
@@ -10970,7 +10970,7 @@
         <v>21</v>
       </c>
       <c r="BA54">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="BB54">
         <v>14</v>
@@ -10982,13 +10982,13 @@
         <v>34</v>
       </c>
       <c r="BE54">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="BF54">
         <v>9.199999999999999</v>
       </c>
       <c r="BG54">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="BH54" t="s">
         <v>263</v>
@@ -11011,7 +11011,7 @@
         <v>247</v>
       </c>
       <c r="F55">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="G55">
         <v>2.54</v>
@@ -11035,13 +11035,13 @@
         <v>1.07</v>
       </c>
       <c r="N55">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="O55">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="P55">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="Q55">
         <v>2.02</v>
@@ -11050,7 +11050,7 @@
         <v>1.36</v>
       </c>
       <c r="S55">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="T55">
         <v>1.8</v>
@@ -11152,7 +11152,7 @@
         <v>16</v>
       </c>
       <c r="BA55">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BB55">
         <v>32</v>
@@ -11167,7 +11167,7 @@
         <v>50</v>
       </c>
       <c r="BF55">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BG55">
         <v>29</v>
@@ -11229,19 +11229,19 @@
         <v>1.68</v>
       </c>
       <c r="R56">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="S56">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="T56">
         <v>1.84</v>
       </c>
       <c r="U56">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V56">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="W56">
         <v>1.15</v>
@@ -11268,7 +11268,7 @@
         <v>9.6</v>
       </c>
       <c r="AE56">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AF56">
         <v>65</v>
@@ -11277,25 +11277,25 @@
         <v>26</v>
       </c>
       <c r="AH56">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI56">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AJ56">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="AK56">
         <v>90</v>
       </c>
       <c r="AL56">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AM56">
         <v>100</v>
       </c>
       <c r="AN56">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AO56">
         <v>6.4</v>
@@ -11325,31 +11325,31 @@
         <v>13.5</v>
       </c>
       <c r="AX56">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AY56">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AZ56">
         <v>20</v>
       </c>
       <c r="BA56">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BB56">
         <v>110</v>
       </c>
       <c r="BC56">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="BD56">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="BE56">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="BF56">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="BG56">
         <v>6.2</v>
@@ -11381,7 +11381,7 @@
         <v>1.31</v>
       </c>
       <c r="H57">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I57">
         <v>12.5</v>
@@ -11399,28 +11399,28 @@
         <v>1.03</v>
       </c>
       <c r="N57">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="O57">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="P57">
-        <v>2.72</v>
+        <v>2.84</v>
       </c>
       <c r="Q57">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="R57">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="S57">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="T57">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="U57">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="V57">
         <v>1.08</v>
@@ -11429,7 +11429,7 @@
         <v>4.2</v>
       </c>
       <c r="X57">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="Y57">
         <v>46</v>
@@ -11444,7 +11444,7 @@
         <v>11</v>
       </c>
       <c r="AC57">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AD57">
         <v>48</v>
@@ -11453,7 +11453,7 @@
         <v>190</v>
       </c>
       <c r="AF57">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AG57">
         <v>10.5</v>
@@ -11465,13 +11465,13 @@
         <v>140</v>
       </c>
       <c r="AJ57">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AK57">
         <v>13.5</v>
       </c>
       <c r="AL57">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AM57">
         <v>140</v>
@@ -11480,7 +11480,7 @@
         <v>4.3</v>
       </c>
       <c r="AO57">
-        <v>170</v>
+        <v>200</v>
       </c>
       <c r="AP57">
         <v>34</v>
@@ -11489,10 +11489,10 @@
         <v>34</v>
       </c>
       <c r="AR57">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AS57">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AT57">
         <v>9.6</v>
@@ -11504,7 +11504,7 @@
         <v>28</v>
       </c>
       <c r="AW57">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AX57">
         <v>8.4</v>
@@ -11513,7 +11513,7 @@
         <v>9.6</v>
       </c>
       <c r="AZ57">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BA57">
         <v>16.5</v>
@@ -11534,7 +11534,7 @@
         <v>3.9</v>
       </c>
       <c r="BG57">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="BH57" t="s">
         <v>263</v>
@@ -11572,7 +11572,7 @@
         <v>2.96</v>
       </c>
       <c r="K58">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="L58">
         <v>1.6</v>
@@ -11581,16 +11581,16 @@
         <v>1.15</v>
       </c>
       <c r="N58">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="O58">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="P58">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="Q58">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="R58">
         <v>1.14</v>
@@ -11599,10 +11599,10 @@
         <v>6.8</v>
       </c>
       <c r="T58">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="U58">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="V58">
         <v>1.35</v>
@@ -11611,13 +11611,13 @@
         <v>1.63</v>
       </c>
       <c r="X58">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="Y58">
         <v>9.199999999999999</v>
       </c>
       <c r="Z58">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA58">
         <v>500</v>
@@ -11632,7 +11632,7 @@
         <v>18</v>
       </c>
       <c r="AE58">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="AF58">
         <v>14</v>
@@ -11668,16 +11668,16 @@
         <v>6.4</v>
       </c>
       <c r="AQ58">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AR58">
         <v>20</v>
       </c>
       <c r="AS58">
-        <v>10.5</v>
+        <v>34</v>
       </c>
       <c r="AT58">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AU58">
         <v>6.4</v>
@@ -11686,19 +11686,19 @@
         <v>15</v>
       </c>
       <c r="AW58">
-        <v>10.5</v>
+        <v>32</v>
       </c>
       <c r="AX58">
         <v>11.5</v>
       </c>
       <c r="AY58">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AZ58">
         <v>24</v>
       </c>
       <c r="BA58">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="BB58">
         <v>32</v>
@@ -11707,16 +11707,16 @@
         <v>34</v>
       </c>
       <c r="BD58">
-        <v>10.5</v>
+        <v>36</v>
       </c>
       <c r="BE58">
-        <v>11.5</v>
+        <v>110</v>
       </c>
       <c r="BF58">
         <v>36</v>
       </c>
       <c r="BG58">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="BH58" t="s">
         <v>263</v>
@@ -11745,16 +11745,16 @@
         <v>1.53</v>
       </c>
       <c r="H59">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="I59">
         <v>9</v>
       </c>
       <c r="J59">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="K59">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L59">
         <v>1.35</v>
@@ -11763,7 +11763,7 @@
         <v>1.05</v>
       </c>
       <c r="N59">
-        <v>1.1</v>
+        <v>4.1</v>
       </c>
       <c r="O59">
         <v>1.26</v>
@@ -11772,13 +11772,13 @@
         <v>2.08</v>
       </c>
       <c r="Q59">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="R59">
         <v>1.42</v>
       </c>
       <c r="S59">
-        <v>2.72</v>
+        <v>3</v>
       </c>
       <c r="T59">
         <v>1.97</v>
@@ -11847,7 +11847,7 @@
         <v>200</v>
       </c>
       <c r="AP59">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="AQ59">
         <v>7.6</v>
@@ -11865,7 +11865,7 @@
         <v>6.2</v>
       </c>
       <c r="AV59">
-        <v>7.6</v>
+        <v>14.5</v>
       </c>
       <c r="AW59">
         <v>9.4</v>
@@ -11886,10 +11886,10 @@
         <v>6.4</v>
       </c>
       <c r="BC59">
-        <v>6.2</v>
+        <v>12</v>
       </c>
       <c r="BD59">
-        <v>8.199999999999999</v>
+        <v>19.5</v>
       </c>
       <c r="BE59">
         <v>9.6</v>
@@ -11924,7 +11924,7 @@
         <v>1.82</v>
       </c>
       <c r="G60">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="H60">
         <v>5.1</v>
@@ -11936,13 +11936,13 @@
         <v>3.45</v>
       </c>
       <c r="K60">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L60">
         <v>1.41</v>
       </c>
       <c r="M60">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N60">
         <v>3</v>
@@ -11954,7 +11954,7 @@
         <v>1.78</v>
       </c>
       <c r="Q60">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="R60">
         <v>1.25</v>
@@ -11963,7 +11963,7 @@
         <v>4.3</v>
       </c>
       <c r="T60">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="U60">
         <v>1.71</v>
@@ -11972,10 +11972,10 @@
         <v>1.21</v>
       </c>
       <c r="W60">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="X60">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="Y60">
         <v>970</v>
@@ -12023,46 +12023,46 @@
         <v>580</v>
       </c>
       <c r="AN60">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AO60">
         <v>310</v>
       </c>
       <c r="AP60">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AQ60">
         <v>7.6</v>
       </c>
       <c r="AR60">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AS60">
+        <v>3.55</v>
+      </c>
+      <c r="AT60">
+        <v>6.2</v>
+      </c>
+      <c r="AU60">
         <v>5</v>
       </c>
-      <c r="AT60">
-        <v>4.3</v>
-      </c>
-      <c r="AU60">
-        <v>4.6</v>
-      </c>
       <c r="AV60">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW60">
-        <v>9.6</v>
+        <v>7.4</v>
       </c>
       <c r="AX60">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="AY60">
-        <v>9</v>
+        <v>6.2</v>
       </c>
       <c r="AZ60">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BA60">
-        <v>9.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="BB60">
         <v>17.5</v>
@@ -12071,16 +12071,16 @@
         <v>11.5</v>
       </c>
       <c r="BD60">
-        <v>8.800000000000001</v>
+        <v>7</v>
       </c>
       <c r="BE60">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BF60">
-        <v>7</v>
+        <v>14.5</v>
       </c>
       <c r="BG60">
-        <v>7.8</v>
+        <v>4.6</v>
       </c>
       <c r="BH60" t="s">
         <v>263</v>
@@ -12127,7 +12127,7 @@
         <v>1.06</v>
       </c>
       <c r="N61">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="O61">
         <v>1.29</v>
@@ -12142,7 +12142,7 @@
         <v>1.38</v>
       </c>
       <c r="S61">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="T61">
         <v>1.71</v>
@@ -12220,7 +12220,7 @@
         <v>7.2</v>
       </c>
       <c r="AS61">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AT61">
         <v>5.8</v>
@@ -12232,7 +12232,7 @@
         <v>6.4</v>
       </c>
       <c r="AW61">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="AX61">
         <v>6.4</v>
@@ -12241,19 +12241,19 @@
         <v>7</v>
       </c>
       <c r="AZ61">
-        <v>6.4</v>
+        <v>14.5</v>
       </c>
       <c r="BA61">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BB61">
         <v>7.4</v>
       </c>
       <c r="BC61">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="BD61">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="BE61">
         <v>9</v>
@@ -12297,10 +12297,10 @@
         <v>7.4</v>
       </c>
       <c r="J62">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="K62">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L62">
         <v>1.43</v>
@@ -12387,7 +12387,7 @@
         <v>700</v>
       </c>
       <c r="AN62">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AO62">
         <v>700</v>
@@ -12396,10 +12396,10 @@
         <v>9.6</v>
       </c>
       <c r="AQ62">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AR62">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AS62">
         <v>95</v>
@@ -12408,10 +12408,10 @@
         <v>5.8</v>
       </c>
       <c r="AU62">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AV62">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AW62">
         <v>40</v>
@@ -12432,7 +12432,7 @@
         <v>14</v>
       </c>
       <c r="BC62">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="BD62">
         <v>29</v>
@@ -12441,7 +12441,7 @@
         <v>90</v>
       </c>
       <c r="BF62">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="BG62">
         <v>48</v>
@@ -12473,7 +12473,7 @@
         <v>1.81</v>
       </c>
       <c r="H63">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="I63">
         <v>6.8</v>
@@ -12509,7 +12509,7 @@
         <v>4.4</v>
       </c>
       <c r="T63">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="U63">
         <v>1.73</v>
@@ -12533,7 +12533,7 @@
         <v>900</v>
       </c>
       <c r="AB63">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AC63">
         <v>9.800000000000001</v>
@@ -12545,7 +12545,7 @@
         <v>700</v>
       </c>
       <c r="AF63">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AG63">
         <v>12.5</v>
@@ -12584,10 +12584,10 @@
         <v>34</v>
       </c>
       <c r="AS63">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="AT63">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AU63">
         <v>6.2</v>
@@ -12596,7 +12596,7 @@
         <v>18</v>
       </c>
       <c r="AW63">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="AX63">
         <v>8</v>
@@ -12608,7 +12608,7 @@
         <v>18.5</v>
       </c>
       <c r="BA63">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="BB63">
         <v>13.5</v>
@@ -12620,13 +12620,13 @@
         <v>36</v>
       </c>
       <c r="BE63">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BF63">
         <v>12</v>
       </c>
       <c r="BG63">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BH63" t="s">
         <v>263</v>
@@ -12649,7 +12649,7 @@
         <v>256</v>
       </c>
       <c r="F64">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="G64">
         <v>2.08</v>
@@ -12658,13 +12658,13 @@
         <v>4.7</v>
       </c>
       <c r="I64">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="J64">
         <v>3.15</v>
       </c>
       <c r="K64">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L64">
         <v>1.47</v>
@@ -12673,7 +12673,7 @@
         <v>1.11</v>
       </c>
       <c r="N64">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="O64">
         <v>1.48</v>
@@ -12682,13 +12682,13 @@
         <v>1.58</v>
       </c>
       <c r="Q64">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="R64">
         <v>1.21</v>
       </c>
       <c r="S64">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="T64">
         <v>2.1</v>
@@ -12697,7 +12697,7 @@
         <v>1.75</v>
       </c>
       <c r="V64">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="W64">
         <v>1.92</v>
@@ -12721,13 +12721,13 @@
         <v>8</v>
       </c>
       <c r="AD64">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AE64">
         <v>470</v>
       </c>
       <c r="AF64">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AG64">
         <v>11.5</v>
@@ -12745,7 +12745,7 @@
         <v>30</v>
       </c>
       <c r="AL64">
-        <v>150</v>
+        <v>370</v>
       </c>
       <c r="AM64">
         <v>580</v>
@@ -12778,7 +12778,7 @@
         <v>18</v>
       </c>
       <c r="AW64">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AX64">
         <v>9.4</v>
@@ -12790,7 +12790,7 @@
         <v>20</v>
       </c>
       <c r="BA64">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BB64">
         <v>20</v>
@@ -12799,16 +12799,16 @@
         <v>13</v>
       </c>
       <c r="BD64">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BE64">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF64">
         <v>19</v>
       </c>
       <c r="BG64">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BH64" t="s">
         <v>263</v>
@@ -12858,13 +12858,13 @@
         <v>2.42</v>
       </c>
       <c r="O65">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="P65">
         <v>1.47</v>
       </c>
       <c r="Q65">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="R65">
         <v>1.17</v>
@@ -12873,7 +12873,7 @@
         <v>5.5</v>
       </c>
       <c r="T65">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="U65">
         <v>1.7</v>
@@ -12897,7 +12897,7 @@
         <v>900</v>
       </c>
       <c r="AB65">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC65">
         <v>8.199999999999999</v>
@@ -12960,7 +12960,7 @@
         <v>13.5</v>
       </c>
       <c r="AW65">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AX65">
         <v>10</v>
@@ -12981,16 +12981,16 @@
         <v>16</v>
       </c>
       <c r="BD65">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BE65">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BF65">
         <v>7.8</v>
       </c>
       <c r="BG65">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BH65" t="s">
         <v>263</v>
@@ -13013,7 +13013,7 @@
         <v>258</v>
       </c>
       <c r="F66">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="G66">
         <v>1.9</v>
@@ -13022,7 +13022,7 @@
         <v>5.9</v>
       </c>
       <c r="I66">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="J66">
         <v>3.15</v>
@@ -13040,7 +13040,7 @@
         <v>2.44</v>
       </c>
       <c r="O66">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="P66">
         <v>1.49</v>
@@ -13052,7 +13052,7 @@
         <v>1.17</v>
       </c>
       <c r="S66">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="T66">
         <v>2.36</v>
@@ -13067,10 +13067,10 @@
         <v>2.12</v>
       </c>
       <c r="X66">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="Y66">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Z66">
         <v>55</v>
@@ -13079,7 +13079,7 @@
         <v>900</v>
       </c>
       <c r="AB66">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AC66">
         <v>9.4</v>
@@ -13127,10 +13127,10 @@
         <v>11.5</v>
       </c>
       <c r="AR66">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AS66">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AT66">
         <v>4.9</v>
@@ -13142,7 +13142,7 @@
         <v>20</v>
       </c>
       <c r="AW66">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AX66">
         <v>7.2</v>
@@ -13154,7 +13154,7 @@
         <v>17</v>
       </c>
       <c r="BA66">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BB66">
         <v>15</v>
@@ -13163,16 +13163,16 @@
         <v>19</v>
       </c>
       <c r="BD66">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BE66">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF66">
         <v>15</v>
       </c>
       <c r="BG66">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BH66" t="s">
         <v>263</v>
@@ -13195,19 +13195,19 @@
         <v>259</v>
       </c>
       <c r="F67">
-        <v>1.04</v>
+        <v>1.5</v>
       </c>
       <c r="G67">
         <v>2.14</v>
       </c>
       <c r="H67">
-        <v>1.93</v>
+        <v>1.09</v>
       </c>
       <c r="I67">
-        <v>970</v>
+        <v>990</v>
       </c>
       <c r="J67">
-        <v>1.92</v>
+        <v>1.1</v>
       </c>
       <c r="K67">
         <v>950</v>
@@ -13216,16 +13216,16 @@
         <v>1.01</v>
       </c>
       <c r="M67">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N67">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="O67">
         <v>1.15</v>
       </c>
       <c r="P67">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Q67">
         <v>1.15</v>
@@ -13237,13 +13237,13 @@
         <v>1.15</v>
       </c>
       <c r="T67">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U67">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V67">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="W67">
         <v>1.88</v>
@@ -13401,7 +13401,7 @@
         <v>1.01</v>
       </c>
       <c r="N68">
-        <v>1.54</v>
+        <v>2.38</v>
       </c>
       <c r="O68">
         <v>1.41</v>
@@ -13413,16 +13413,16 @@
         <v>2.02</v>
       </c>
       <c r="R68">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="S68">
-        <v>2.02</v>
+        <v>2.96</v>
       </c>
       <c r="T68">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U68">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V68">
         <v>1.03</v>
@@ -13568,37 +13568,37 @@
         <v>2.42</v>
       </c>
       <c r="I69">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="J69">
-        <v>2.98</v>
+        <v>2.92</v>
       </c>
       <c r="K69">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="L69">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="M69">
         <v>1.14</v>
       </c>
       <c r="N69">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="O69">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="P69">
         <v>1.43</v>
       </c>
       <c r="Q69">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="R69">
         <v>1.14</v>
       </c>
       <c r="S69">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="T69">
         <v>2.28</v>
@@ -13607,16 +13607,16 @@
         <v>1.64</v>
       </c>
       <c r="V69">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="W69">
         <v>1.33</v>
       </c>
       <c r="X69">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="Y69">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="Z69">
         <v>14</v>
@@ -13628,22 +13628,22 @@
         <v>10.5</v>
       </c>
       <c r="AC69">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD69">
         <v>13.5</v>
       </c>
       <c r="AE69">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AF69">
         <v>26</v>
       </c>
       <c r="AG69">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AH69">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AI69">
         <v>95</v>
@@ -13658,28 +13658,28 @@
         <v>130</v>
       </c>
       <c r="AM69">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="AN69">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AO69">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AP69">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AQ69">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AR69">
         <v>11.5</v>
       </c>
       <c r="AS69">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AT69">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AU69">
         <v>6.2</v>
@@ -13688,7 +13688,7 @@
         <v>11</v>
       </c>
       <c r="AW69">
-        <v>6.4</v>
+        <v>32</v>
       </c>
       <c r="AX69">
         <v>21</v>
@@ -13697,28 +13697,28 @@
         <v>15.5</v>
       </c>
       <c r="AZ69">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BA69">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB69">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="BC69">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD69">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="BE69">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF69">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="BG69">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BH69" t="s">
         <v>263</v>
@@ -13741,16 +13741,16 @@
         <v>262</v>
       </c>
       <c r="F70">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="G70">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="H70">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="I70">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="J70">
         <v>2.98</v>
@@ -13759,40 +13759,40 @@
         <v>3.65</v>
       </c>
       <c r="L70">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="M70">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="N70">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="O70">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="P70">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="Q70">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="R70">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S70">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="T70">
-        <v>1.93</v>
+        <v>2.02</v>
       </c>
       <c r="U70">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="V70">
         <v>1.22</v>
       </c>
       <c r="W70">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="X70">
         <v>970</v>
@@ -13807,10 +13807,10 @@
         <v>1000</v>
       </c>
       <c r="AB70">
-        <v>8.199999999999999</v>
+        <v>970</v>
       </c>
       <c r="AC70">
-        <v>8.4</v>
+        <v>970</v>
       </c>
       <c r="AD70">
         <v>21</v>
@@ -13849,58 +13849,58 @@
         <v>150</v>
       </c>
       <c r="AP70">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AQ70">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AR70">
+        <v>6</v>
+      </c>
+      <c r="AS70">
+        <v>2.5</v>
+      </c>
+      <c r="AT70">
+        <v>3.7</v>
+      </c>
+      <c r="AU70">
+        <v>3.95</v>
+      </c>
+      <c r="AV70">
+        <v>5.3</v>
+      </c>
+      <c r="AW70">
+        <v>6.4</v>
+      </c>
+      <c r="AX70">
+        <v>4.4</v>
+      </c>
+      <c r="AY70">
+        <v>4.3</v>
+      </c>
+      <c r="AZ70">
+        <v>5.5</v>
+      </c>
+      <c r="BA70">
+        <v>6.6</v>
+      </c>
+      <c r="BB70">
+        <v>5.5</v>
+      </c>
+      <c r="BC70">
         <v>5.6</v>
       </c>
-      <c r="AS70">
+      <c r="BD70">
         <v>6.2</v>
       </c>
-      <c r="AT70">
-        <v>3.6</v>
-      </c>
-      <c r="AU70">
-        <v>3.9</v>
-      </c>
-      <c r="AV70">
-        <v>4.9</v>
-      </c>
-      <c r="AW70">
-        <v>6</v>
-      </c>
-      <c r="AX70">
-        <v>4.2</v>
-      </c>
-      <c r="AY70">
-        <v>4.1</v>
-      </c>
-      <c r="AZ70">
-        <v>5.2</v>
-      </c>
-      <c r="BA70">
-        <v>6</v>
-      </c>
-      <c r="BB70">
-        <v>5.1</v>
-      </c>
-      <c r="BC70">
-        <v>5.2</v>
-      </c>
-      <c r="BD70">
-        <v>5.8</v>
-      </c>
       <c r="BE70">
-        <v>6.2</v>
+        <v>2.5</v>
       </c>
       <c r="BF70">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BG70">
-        <v>6.2</v>
+        <v>2.5</v>
       </c>
       <c r="BH70" t="s">
         <v>263</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-04.xlsx
@@ -805,7 +805,7 @@
     <t>Deportes Recoleta</t>
   </si>
   <si>
-    <t>2026-05-04 04:18:46</t>
+    <t>2026-05-04 06:32:04</t>
   </si>
 </sst>
 </file>
@@ -1365,166 +1365,166 @@
         <v>194</v>
       </c>
       <c r="F2">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="G2">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="H2">
-        <v>2.32</v>
+        <v>1000</v>
       </c>
       <c r="I2">
-        <v>2.48</v>
+        <v>1000</v>
       </c>
       <c r="J2">
-        <v>2.96</v>
+        <v>1000</v>
       </c>
       <c r="K2">
-        <v>3.15</v>
+        <v>1000</v>
       </c>
       <c r="L2">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="M2">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="P2">
-        <v>1.51</v>
+        <v>1.1</v>
       </c>
       <c r="Q2">
-        <v>2.8</v>
+        <v>6.4</v>
       </c>
       <c r="R2">
-        <v>1.2</v>
+        <v>1.01</v>
       </c>
       <c r="S2">
-        <v>5.8</v>
+        <v>50</v>
       </c>
       <c r="T2">
-        <v>1.11</v>
+        <v>1.41</v>
       </c>
       <c r="U2">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="V2">
-        <v>1.67</v>
+        <v>1.01</v>
       </c>
       <c r="W2">
-        <v>1.32</v>
+        <v>500</v>
       </c>
       <c r="X2">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="Y2">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="Z2">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AA2">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="AB2">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AC2">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AD2">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AE2">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AF2">
-        <v>500</v>
+        <v>1.09</v>
       </c>
       <c r="AG2">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AH2">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AI2">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AJ2">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="AK2">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AL2">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AM2">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AN2">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="AO2">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="AP2">
-        <v>5.8</v>
+        <v>1000</v>
       </c>
       <c r="AQ2">
-        <v>1.93</v>
+        <v>1000</v>
       </c>
       <c r="AR2">
-        <v>1.79</v>
+        <v>1000</v>
       </c>
       <c r="AS2">
-        <v>1.95</v>
+        <v>1000</v>
       </c>
       <c r="AT2">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="AU2">
-        <v>1.61</v>
+        <v>12</v>
       </c>
       <c r="AV2">
-        <v>9.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="AW2">
-        <v>1.94</v>
+        <v>12</v>
       </c>
       <c r="AX2">
-        <v>1.9</v>
+        <v>1.01</v>
       </c>
       <c r="AY2">
-        <v>1.88</v>
+        <v>7.4</v>
       </c>
       <c r="AZ2">
-        <v>1.92</v>
+        <v>10</v>
       </c>
       <c r="BA2">
-        <v>1.98</v>
+        <v>7.8</v>
       </c>
       <c r="BB2">
-        <v>1.98</v>
+        <v>7.4</v>
       </c>
       <c r="BC2">
-        <v>1.98</v>
+        <v>12</v>
       </c>
       <c r="BD2">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BE2">
-        <v>130</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF2">
-        <v>2</v>
+        <v>3.65</v>
       </c>
       <c r="BG2">
-        <v>1.99</v>
+        <v>7.8</v>
       </c>
       <c r="BH2" t="s">
         <v>263</v>
@@ -1547,166 +1547,166 @@
         <v>195</v>
       </c>
       <c r="F3">
-        <v>2.66</v>
+        <v>110</v>
       </c>
       <c r="G3">
-        <v>2.88</v>
+        <v>1000</v>
       </c>
       <c r="H3">
-        <v>3</v>
+        <v>1.05</v>
       </c>
       <c r="I3">
-        <v>3.15</v>
+        <v>1.11</v>
       </c>
       <c r="J3">
-        <v>3.1</v>
+        <v>8.6</v>
       </c>
       <c r="K3">
-        <v>3.3</v>
+        <v>680</v>
       </c>
       <c r="L3">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="M3">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="N3">
-        <v>3.2</v>
+        <v>1.14</v>
       </c>
       <c r="O3">
-        <v>1.41</v>
+        <v>4.7</v>
       </c>
       <c r="P3">
-        <v>1.74</v>
+        <v>1.01</v>
       </c>
       <c r="Q3">
-        <v>2.28</v>
+        <v>34</v>
       </c>
       <c r="R3">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="S3">
+        <v>110</v>
+      </c>
+      <c r="T3">
+        <v>1.71</v>
+      </c>
+      <c r="U3">
+        <v>1.01</v>
+      </c>
+      <c r="V3">
         <v>4.3</v>
       </c>
-      <c r="T3">
-        <v>1.88</v>
-      </c>
-      <c r="U3">
-        <v>1.92</v>
-      </c>
-      <c r="V3">
-        <v>1.47</v>
-      </c>
       <c r="W3">
-        <v>1.53</v>
+        <v>1.01</v>
       </c>
       <c r="X3">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="Y3">
-        <v>11.5</v>
+        <v>1.18</v>
       </c>
       <c r="Z3">
-        <v>21</v>
+        <v>810</v>
       </c>
       <c r="AA3">
-        <v>230</v>
+        <v>1000</v>
       </c>
       <c r="AB3">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AC3">
-        <v>7.8</v>
+        <v>790</v>
       </c>
       <c r="AD3">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AE3">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AF3">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AG3">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AH3">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AI3">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AJ3">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AK3">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AL3">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AM3">
-        <v>580</v>
+        <v>1000</v>
       </c>
       <c r="AN3">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="AO3">
         <v>1000</v>
       </c>
       <c r="AP3">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AQ3">
-        <v>9.199999999999999</v>
+        <v>1.02</v>
       </c>
       <c r="AR3">
-        <v>12.5</v>
+        <v>5.3</v>
       </c>
       <c r="AS3">
-        <v>14</v>
+        <v>5.4</v>
       </c>
       <c r="AT3">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AU3">
         <v>6.4</v>
       </c>
       <c r="AV3">
-        <v>11.5</v>
+        <v>5.4</v>
       </c>
       <c r="AW3">
-        <v>16</v>
+        <v>5.4</v>
       </c>
       <c r="AX3">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AY3">
-        <v>10</v>
+        <v>6.6</v>
       </c>
       <c r="AZ3">
-        <v>16.5</v>
+        <v>5.4</v>
       </c>
       <c r="BA3">
-        <v>11.5</v>
+        <v>5.4</v>
       </c>
       <c r="BB3">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="BC3">
-        <v>28</v>
+        <v>5.4</v>
       </c>
       <c r="BD3">
-        <v>22</v>
+        <v>5.4</v>
       </c>
       <c r="BE3">
-        <v>120</v>
+        <v>5.4</v>
       </c>
       <c r="BF3">
-        <v>8.6</v>
+        <v>5.4</v>
       </c>
       <c r="BG3">
-        <v>8.6</v>
+        <v>6.6</v>
       </c>
       <c r="BH3" t="s">
         <v>263</v>
@@ -1729,166 +1729,166 @@
         <v>196</v>
       </c>
       <c r="F4">
+        <v>3.4</v>
+      </c>
+      <c r="G4">
+        <v>3.95</v>
+      </c>
+      <c r="H4">
+        <v>2.2</v>
+      </c>
+      <c r="I4">
+        <v>2.4</v>
+      </c>
+      <c r="J4">
         <v>3.2</v>
       </c>
-      <c r="G4">
-        <v>4.2</v>
-      </c>
-      <c r="H4">
-        <v>2.14</v>
-      </c>
-      <c r="I4">
-        <v>2.5</v>
-      </c>
-      <c r="J4">
-        <v>3</v>
-      </c>
       <c r="K4">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L4">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="M4">
         <v>1.09</v>
       </c>
       <c r="N4">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="O4">
         <v>1.42</v>
       </c>
       <c r="P4">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="Q4">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="R4">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S4">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="T4">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
       <c r="U4">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="V4">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="W4">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="X4">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Y4">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z4">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AA4">
         <v>34</v>
       </c>
       <c r="AB4">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AC4">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD4">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE4">
+        <v>30</v>
+      </c>
+      <c r="AF4">
+        <v>27</v>
+      </c>
+      <c r="AG4">
+        <v>16.5</v>
+      </c>
+      <c r="AH4">
+        <v>21</v>
+      </c>
+      <c r="AI4">
+        <v>75</v>
+      </c>
+      <c r="AJ4">
+        <v>170</v>
+      </c>
+      <c r="AK4">
+        <v>70</v>
+      </c>
+      <c r="AL4">
+        <v>110</v>
+      </c>
+      <c r="AM4">
+        <v>890</v>
+      </c>
+      <c r="AN4">
+        <v>600</v>
+      </c>
+      <c r="AO4">
+        <v>27</v>
+      </c>
+      <c r="AP4">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AQ4">
+        <v>7</v>
+      </c>
+      <c r="AR4">
+        <v>11.5</v>
+      </c>
+      <c r="AS4">
+        <v>23</v>
+      </c>
+      <c r="AT4">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU4">
+        <v>6.4</v>
+      </c>
+      <c r="AV4">
+        <v>9.6</v>
+      </c>
+      <c r="AW4">
+        <v>22</v>
+      </c>
+      <c r="AX4">
+        <v>21</v>
+      </c>
+      <c r="AY4">
+        <v>13</v>
+      </c>
+      <c r="AZ4">
+        <v>17</v>
+      </c>
+      <c r="BA4">
         <v>32</v>
       </c>
-      <c r="AF4">
-        <v>28</v>
-      </c>
-      <c r="AG4">
-        <v>17</v>
-      </c>
-      <c r="AH4">
-        <v>22</v>
-      </c>
-      <c r="AI4">
-        <v>55</v>
-      </c>
-      <c r="AJ4">
-        <v>900</v>
-      </c>
-      <c r="AK4">
-        <v>60</v>
-      </c>
-      <c r="AL4">
-        <v>75</v>
-      </c>
-      <c r="AM4">
-        <v>580</v>
-      </c>
-      <c r="AN4">
-        <v>70</v>
-      </c>
-      <c r="AO4">
-        <v>28</v>
-      </c>
-      <c r="AP4">
-        <v>4.9</v>
-      </c>
-      <c r="AQ4">
-        <v>3.9</v>
-      </c>
-      <c r="AR4">
-        <v>4.7</v>
-      </c>
-      <c r="AS4">
-        <v>5.8</v>
-      </c>
-      <c r="AT4">
-        <v>4.6</v>
-      </c>
-      <c r="AU4">
-        <v>3.8</v>
-      </c>
-      <c r="AV4">
-        <v>4.5</v>
-      </c>
-      <c r="AW4">
-        <v>5.7</v>
-      </c>
-      <c r="AX4">
-        <v>5.6</v>
-      </c>
-      <c r="AY4">
-        <v>4.9</v>
-      </c>
-      <c r="AZ4">
-        <v>5.9</v>
-      </c>
-      <c r="BA4">
-        <v>6.2</v>
-      </c>
       <c r="BB4">
-        <v>6.4</v>
+        <v>40</v>
       </c>
       <c r="BC4">
-        <v>6.2</v>
+        <v>32</v>
       </c>
       <c r="BD4">
-        <v>6.4</v>
+        <v>30</v>
       </c>
       <c r="BE4">
-        <v>6.6</v>
+        <v>110</v>
       </c>
       <c r="BF4">
-        <v>6.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG4">
-        <v>5.6</v>
+        <v>21</v>
       </c>
       <c r="BH4" t="s">
         <v>263</v>
@@ -1911,97 +1911,97 @@
         <v>197</v>
       </c>
       <c r="F5">
-        <v>2.86</v>
+        <v>3.25</v>
       </c>
       <c r="G5">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="H5">
+        <v>2.4</v>
+      </c>
+      <c r="I5">
         <v>2.68</v>
       </c>
-      <c r="I5">
-        <v>3.2</v>
-      </c>
       <c r="J5">
-        <v>2.78</v>
+        <v>2.96</v>
       </c>
       <c r="K5">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="L5">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="M5">
         <v>1.11</v>
       </c>
       <c r="N5">
-        <v>2.58</v>
+        <v>2.8</v>
       </c>
       <c r="O5">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="P5">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="Q5">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="R5">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S5">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="T5">
-        <v>1.94</v>
+        <v>2.04</v>
       </c>
       <c r="U5">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="V5">
-        <v>1.47</v>
+        <v>1.6</v>
       </c>
       <c r="W5">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="X5">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="Y5">
-        <v>970</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z5">
-        <v>970</v>
+        <v>32</v>
       </c>
       <c r="AA5">
         <v>900</v>
       </c>
       <c r="AB5">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="AC5">
         <v>12</v>
       </c>
       <c r="AD5">
-        <v>970</v>
+        <v>26</v>
       </c>
       <c r="AE5">
         <v>500</v>
       </c>
       <c r="AF5">
-        <v>500</v>
+        <v>38</v>
       </c>
       <c r="AG5">
-        <v>970</v>
+        <v>23</v>
       </c>
       <c r="AH5">
-        <v>950</v>
+        <v>60</v>
       </c>
       <c r="AI5">
         <v>500</v>
       </c>
       <c r="AJ5">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK5">
         <v>500</v>
@@ -2010,7 +2010,7 @@
         <v>500</v>
       </c>
       <c r="AM5">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN5">
         <v>600</v>
@@ -2019,58 +2019,58 @@
         <v>600</v>
       </c>
       <c r="AP5">
-        <v>4.3</v>
+        <v>7.6</v>
       </c>
       <c r="AQ5">
-        <v>4.4</v>
+        <v>6.8</v>
       </c>
       <c r="AR5">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AS5">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AT5">
-        <v>4.5</v>
+        <v>6.2</v>
       </c>
       <c r="AU5">
-        <v>4</v>
+        <v>5.9</v>
       </c>
       <c r="AV5">
-        <v>5.5</v>
+        <v>7.2</v>
       </c>
       <c r="AW5">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="AX5">
-        <v>5.4</v>
+        <v>8.4</v>
       </c>
       <c r="AY5">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AZ5">
-        <v>5.9</v>
+        <v>17</v>
       </c>
       <c r="BA5">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BB5">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BC5">
-        <v>9</v>
+        <v>15.5</v>
       </c>
       <c r="BD5">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BE5">
+        <v>8.4</v>
+      </c>
+      <c r="BF5">
+        <v>8</v>
+      </c>
+      <c r="BG5">
         <v>7</v>
-      </c>
-      <c r="BF5">
-        <v>7.2</v>
-      </c>
-      <c r="BG5">
-        <v>6.2</v>
       </c>
       <c r="BH5" t="s">
         <v>263</v>
@@ -2093,28 +2093,28 @@
         <v>198</v>
       </c>
       <c r="F6">
-        <v>1.43</v>
+        <v>1.6</v>
       </c>
       <c r="G6">
-        <v>1.52</v>
+        <v>1.67</v>
       </c>
       <c r="H6">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="I6">
-        <v>11</v>
+        <v>8.4</v>
       </c>
       <c r="J6">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="K6">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="L6">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="M6">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N6">
         <v>3.55</v>
@@ -2123,34 +2123,34 @@
         <v>1.32</v>
       </c>
       <c r="P6">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="Q6">
-        <v>1.8</v>
+        <v>1.97</v>
       </c>
       <c r="R6">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="S6">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="T6">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="U6">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="V6">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="W6">
-        <v>2.88</v>
+        <v>2.48</v>
       </c>
       <c r="X6">
-        <v>970</v>
+        <v>19</v>
       </c>
       <c r="Y6">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="Z6">
         <v>500</v>
@@ -2162,7 +2162,7 @@
         <v>13</v>
       </c>
       <c r="AC6">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="AD6">
         <v>950</v>
@@ -2171,10 +2171,10 @@
         <v>700</v>
       </c>
       <c r="AF6">
-        <v>19.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG6">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="AH6">
         <v>950</v>
@@ -2183,10 +2183,10 @@
         <v>700</v>
       </c>
       <c r="AJ6">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="AK6">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="AL6">
         <v>500</v>
@@ -2195,64 +2195,64 @@
         <v>580</v>
       </c>
       <c r="AN6">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="AO6">
         <v>700</v>
       </c>
       <c r="AP6">
-        <v>6</v>
+        <v>8.6</v>
       </c>
       <c r="AQ6">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AR6">
-        <v>6.8</v>
+        <v>14.5</v>
       </c>
       <c r="AS6">
-        <v>4.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT6">
-        <v>4.3</v>
+        <v>6.6</v>
       </c>
       <c r="AU6">
-        <v>5.2</v>
+        <v>8</v>
       </c>
       <c r="AV6">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AW6">
-        <v>4.2</v>
+        <v>8.4</v>
       </c>
       <c r="AX6">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="AY6">
-        <v>5.2</v>
+        <v>8.4</v>
       </c>
       <c r="AZ6">
+        <v>13</v>
+      </c>
+      <c r="BA6">
+        <v>8.4</v>
+      </c>
+      <c r="BB6">
+        <v>11</v>
+      </c>
+      <c r="BC6">
+        <v>10.5</v>
+      </c>
+      <c r="BD6">
         <v>7.4</v>
       </c>
-      <c r="BA6">
-        <v>4.2</v>
-      </c>
-      <c r="BB6">
-        <v>6</v>
-      </c>
-      <c r="BC6">
-        <v>6.2</v>
-      </c>
-      <c r="BD6">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BE6">
-        <v>3.2</v>
+        <v>8.6</v>
       </c>
       <c r="BF6">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BG6">
-        <v>4.2</v>
+        <v>6.4</v>
       </c>
       <c r="BH6" t="s">
         <v>263</v>
@@ -2278,61 +2278,61 @@
         <v>3.15</v>
       </c>
       <c r="G7">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="H7">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="I7">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="J7">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="K7">
         <v>3.55</v>
       </c>
       <c r="L7">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="M7">
         <v>1.12</v>
       </c>
       <c r="N7">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="O7">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="P7">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="Q7">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="R7">
         <v>1.21</v>
       </c>
       <c r="S7">
-        <v>3.7</v>
+        <v>5</v>
       </c>
       <c r="T7">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="U7">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="V7">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="W7">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="X7">
-        <v>19.5</v>
+        <v>90</v>
       </c>
       <c r="Y7">
-        <v>150</v>
+        <v>16</v>
       </c>
       <c r="Z7">
         <v>970</v>
@@ -2341,7 +2341,7 @@
         <v>900</v>
       </c>
       <c r="AB7">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AC7">
         <v>42</v>
@@ -2374,7 +2374,7 @@
         <v>500</v>
       </c>
       <c r="AM7">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN7">
         <v>600</v>
@@ -2383,55 +2383,55 @@
         <v>600</v>
       </c>
       <c r="AP7">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AQ7">
-        <v>6.6</v>
+        <v>4.6</v>
       </c>
       <c r="AR7">
-        <v>3.15</v>
+        <v>6.8</v>
       </c>
       <c r="AS7">
-        <v>3.1</v>
+        <v>15</v>
       </c>
       <c r="AT7">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AU7">
         <v>4</v>
       </c>
       <c r="AV7">
-        <v>3.6</v>
+        <v>5.5</v>
       </c>
       <c r="AW7">
-        <v>4.3</v>
+        <v>5.9</v>
       </c>
       <c r="AX7">
-        <v>3.3</v>
+        <v>6</v>
       </c>
       <c r="AY7">
-        <v>3.8</v>
+        <v>6.8</v>
       </c>
       <c r="AZ7">
-        <v>3.45</v>
+        <v>5.8</v>
       </c>
       <c r="BA7">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BB7">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BC7">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BD7">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BE7">
-        <v>4.8</v>
+        <v>6.4</v>
       </c>
       <c r="BF7">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BG7">
         <v>6.2</v>
@@ -2457,61 +2457,61 @@
         <v>200</v>
       </c>
       <c r="F8">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="G8">
         <v>1.7</v>
       </c>
       <c r="H8">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="I8">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="J8">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="K8">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="L8">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="M8">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N8">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="O8">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="P8">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="Q8">
-        <v>1.9</v>
+        <v>2.04</v>
       </c>
       <c r="R8">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S8">
-        <v>3.25</v>
+        <v>3.9</v>
       </c>
       <c r="T8">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="U8">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="V8">
         <v>1.15</v>
       </c>
       <c r="W8">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="X8">
-        <v>16.5</v>
+        <v>90</v>
       </c>
       <c r="Y8">
         <v>950</v>
@@ -2523,10 +2523,10 @@
         <v>700</v>
       </c>
       <c r="AB8">
-        <v>8.4</v>
+        <v>13</v>
       </c>
       <c r="AC8">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AD8">
         <v>75</v>
@@ -2541,7 +2541,7 @@
         <v>36</v>
       </c>
       <c r="AH8">
-        <v>70</v>
+        <v>950</v>
       </c>
       <c r="AI8">
         <v>700</v>
@@ -2550,7 +2550,7 @@
         <v>180</v>
       </c>
       <c r="AK8">
-        <v>22</v>
+        <v>500</v>
       </c>
       <c r="AL8">
         <v>500</v>
@@ -2559,7 +2559,7 @@
         <v>700</v>
       </c>
       <c r="AN8">
-        <v>12.5</v>
+        <v>29</v>
       </c>
       <c r="AO8">
         <v>700</v>
@@ -2568,55 +2568,55 @@
         <v>6.2</v>
       </c>
       <c r="AQ8">
-        <v>5.9</v>
+        <v>9</v>
       </c>
       <c r="AR8">
-        <v>6.2</v>
+        <v>9</v>
       </c>
       <c r="AS8">
-        <v>6.8</v>
+        <v>10</v>
       </c>
       <c r="AT8">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AU8">
         <v>5.6</v>
       </c>
       <c r="AV8">
-        <v>5.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW8">
-        <v>6.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX8">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AY8">
         <v>6.4</v>
       </c>
       <c r="AZ8">
-        <v>5.6</v>
+        <v>11</v>
       </c>
       <c r="BA8">
-        <v>6.6</v>
+        <v>9.6</v>
       </c>
       <c r="BB8">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BC8">
         <v>8.4</v>
       </c>
       <c r="BD8">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="BE8">
-        <v>6.8</v>
+        <v>10</v>
       </c>
       <c r="BF8">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="BG8">
-        <v>3.7</v>
+        <v>5.3</v>
       </c>
       <c r="BH8" t="s">
         <v>263</v>
@@ -2639,7 +2639,7 @@
         <v>201</v>
       </c>
       <c r="F9">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="G9">
         <v>2.1</v>
@@ -2651,10 +2651,10 @@
         <v>5</v>
       </c>
       <c r="J9">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K9">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L9">
         <v>1.51</v>
@@ -2663,10 +2663,10 @@
         <v>1.1</v>
       </c>
       <c r="N9">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="O9">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="P9">
         <v>1.64</v>
@@ -2824,10 +2824,10 @@
         <v>3.45</v>
       </c>
       <c r="G10">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="H10">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="I10">
         <v>2.76</v>
@@ -2836,7 +2836,7 @@
         <v>2.86</v>
       </c>
       <c r="K10">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="L10">
         <v>1.65</v>
@@ -2845,13 +2845,13 @@
         <v>1.15</v>
       </c>
       <c r="N10">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="O10">
         <v>1.59</v>
       </c>
       <c r="P10">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="Q10">
         <v>2.9</v>
@@ -2872,10 +2872,10 @@
         <v>1.56</v>
       </c>
       <c r="W10">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="X10">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y10">
         <v>8</v>
@@ -2884,7 +2884,7 @@
         <v>500</v>
       </c>
       <c r="AA10">
-        <v>900</v>
+        <v>220</v>
       </c>
       <c r="AB10">
         <v>9.6</v>
@@ -2908,13 +2908,13 @@
         <v>85</v>
       </c>
       <c r="AI10">
-        <v>500</v>
+        <v>460</v>
       </c>
       <c r="AJ10">
         <v>500</v>
       </c>
       <c r="AK10">
-        <v>500</v>
+        <v>130</v>
       </c>
       <c r="AL10">
         <v>540</v>
@@ -2926,7 +2926,7 @@
         <v>600</v>
       </c>
       <c r="AO10">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP10">
         <v>6.8</v>
@@ -2950,10 +2950,10 @@
         <v>11</v>
       </c>
       <c r="AW10">
-        <v>18.5</v>
+        <v>25</v>
       </c>
       <c r="AX10">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="AY10">
         <v>9.199999999999999</v>
@@ -2962,25 +2962,25 @@
         <v>15</v>
       </c>
       <c r="BA10">
-        <v>12.5</v>
+        <v>28</v>
       </c>
       <c r="BB10">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="BC10">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="BD10">
+        <v>29</v>
+      </c>
+      <c r="BE10">
+        <v>11</v>
+      </c>
+      <c r="BF10">
         <v>10</v>
       </c>
-      <c r="BE10">
-        <v>10.5</v>
-      </c>
-      <c r="BF10">
+      <c r="BG10">
         <v>9.6</v>
-      </c>
-      <c r="BG10">
-        <v>9.4</v>
       </c>
       <c r="BH10" t="s">
         <v>263</v>
@@ -3003,16 +3003,16 @@
         <v>203</v>
       </c>
       <c r="F11">
+        <v>1.76</v>
+      </c>
+      <c r="G11">
         <v>1.77</v>
       </c>
-      <c r="G11">
-        <v>1.78</v>
-      </c>
       <c r="H11">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="I11">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="J11">
         <v>4.1</v>
@@ -3021,46 +3021,46 @@
         <v>4.2</v>
       </c>
       <c r="L11">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="M11">
         <v>1.05</v>
       </c>
       <c r="N11">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="O11">
         <v>1.25</v>
       </c>
       <c r="P11">
+        <v>2.32</v>
+      </c>
+      <c r="Q11">
+        <v>1.75</v>
+      </c>
+      <c r="R11">
+        <v>1.52</v>
+      </c>
+      <c r="S11">
+        <v>2.88</v>
+      </c>
+      <c r="T11">
+        <v>1.75</v>
+      </c>
+      <c r="U11">
         <v>2.28</v>
       </c>
-      <c r="Q11">
-        <v>1.77</v>
-      </c>
-      <c r="R11">
-        <v>1.51</v>
-      </c>
-      <c r="S11">
-        <v>2.92</v>
-      </c>
-      <c r="T11">
-        <v>1.76</v>
-      </c>
-      <c r="U11">
-        <v>2.26</v>
-      </c>
       <c r="V11">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="W11">
         <v>2.28</v>
       </c>
       <c r="X11">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="Y11">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="Z11">
         <v>40</v>
@@ -3075,10 +3075,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD11">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AE11">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF11">
         <v>11.5</v>
@@ -3087,34 +3087,34 @@
         <v>9.6</v>
       </c>
       <c r="AH11">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AI11">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ11">
         <v>18</v>
       </c>
       <c r="AK11">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AL11">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AM11">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AN11">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AO11">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AP11">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AQ11">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AR11">
         <v>36</v>
@@ -3123,13 +3123,13 @@
         <v>110</v>
       </c>
       <c r="AT11">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AU11">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AV11">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AW11">
         <v>50</v>
@@ -3150,16 +3150,16 @@
         <v>17.5</v>
       </c>
       <c r="BC11">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BD11">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BE11">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="BF11">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG11">
         <v>55</v>
@@ -3191,19 +3191,19 @@
         <v>3.65</v>
       </c>
       <c r="H12">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="I12">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="J12">
         <v>3.3</v>
       </c>
       <c r="K12">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L12">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="M12">
         <v>1.09</v>
@@ -3212,64 +3212,64 @@
         <v>3.25</v>
       </c>
       <c r="O12">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P12">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="Q12">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="R12">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S12">
         <v>4.3</v>
       </c>
       <c r="T12">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="U12">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="V12">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="W12">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="X12">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="Y12">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Z12">
-        <v>970</v>
+        <v>32</v>
       </c>
       <c r="AA12">
-        <v>900</v>
+        <v>130</v>
       </c>
       <c r="AB12">
-        <v>11.5</v>
+        <v>19</v>
       </c>
       <c r="AC12">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AD12">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AE12">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AF12">
         <v>500</v>
       </c>
       <c r="AG12">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AH12">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AI12">
         <v>500</v>
@@ -3293,22 +3293,22 @@
         <v>600</v>
       </c>
       <c r="AP12">
+        <v>7</v>
+      </c>
+      <c r="AQ12">
+        <v>7.8</v>
+      </c>
+      <c r="AR12">
+        <v>7.8</v>
+      </c>
+      <c r="AS12">
+        <v>15.5</v>
+      </c>
+      <c r="AT12">
+        <v>7</v>
+      </c>
+      <c r="AU12">
         <v>6.2</v>
-      </c>
-      <c r="AQ12">
-        <v>5.3</v>
-      </c>
-      <c r="AR12">
-        <v>11</v>
-      </c>
-      <c r="AS12">
-        <v>10</v>
-      </c>
-      <c r="AT12">
-        <v>9.6</v>
-      </c>
-      <c r="AU12">
-        <v>6</v>
       </c>
       <c r="AV12">
         <v>9.6</v>
@@ -3317,34 +3317,34 @@
         <v>13</v>
       </c>
       <c r="AX12">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="AY12">
         <v>8.4</v>
       </c>
       <c r="AZ12">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="BA12">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BB12">
         <v>11.5</v>
       </c>
       <c r="BC12">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BD12">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="BE12">
-        <v>4.2</v>
+        <v>6.2</v>
       </c>
       <c r="BF12">
         <v>9.4</v>
       </c>
       <c r="BG12">
-        <v>5.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH12" t="s">
         <v>263</v>
@@ -3367,25 +3367,25 @@
         <v>205</v>
       </c>
       <c r="F13">
-        <v>4.5</v>
+        <v>3.95</v>
       </c>
       <c r="G13">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="H13">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="I13">
-        <v>1.85</v>
+        <v>1.99</v>
       </c>
       <c r="J13">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="K13">
         <v>4.2</v>
       </c>
       <c r="L13">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="M13">
         <v>1.06</v>
@@ -3394,16 +3394,16 @@
         <v>4</v>
       </c>
       <c r="O13">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P13">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="Q13">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="R13">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="S13">
         <v>3.45</v>
@@ -3412,49 +3412,49 @@
         <v>1.8</v>
       </c>
       <c r="U13">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="V13">
-        <v>2.16</v>
+        <v>2</v>
       </c>
       <c r="W13">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="X13">
+        <v>30</v>
+      </c>
+      <c r="Y13">
+        <v>15.5</v>
+      </c>
+      <c r="Z13">
+        <v>13</v>
+      </c>
+      <c r="AA13">
+        <v>38</v>
+      </c>
+      <c r="AB13">
         <v>26</v>
       </c>
-      <c r="Y13">
-        <v>10.5</v>
-      </c>
-      <c r="Z13">
-        <v>11</v>
-      </c>
-      <c r="AA13">
-        <v>34</v>
-      </c>
-      <c r="AB13">
-        <v>32</v>
-      </c>
       <c r="AC13">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD13">
         <v>10</v>
       </c>
       <c r="AE13">
-        <v>65</v>
+        <v>22</v>
       </c>
       <c r="AF13">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="AG13">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="AH13">
         <v>60</v>
       </c>
       <c r="AI13">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AJ13">
         <v>900</v>
@@ -3472,22 +3472,22 @@
         <v>700</v>
       </c>
       <c r="AO13">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="AP13">
-        <v>6.6</v>
+        <v>13.5</v>
       </c>
       <c r="AQ13">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR13">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AS13">
-        <v>7.8</v>
+        <v>18.5</v>
       </c>
       <c r="AT13">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="AU13">
         <v>7.4</v>
@@ -3496,37 +3496,37 @@
         <v>8.4</v>
       </c>
       <c r="AW13">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="AX13">
-        <v>16.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY13">
-        <v>8.4</v>
+        <v>12</v>
       </c>
       <c r="AZ13">
-        <v>9.4</v>
+        <v>12.5</v>
       </c>
       <c r="BA13">
-        <v>14.5</v>
+        <v>26</v>
       </c>
       <c r="BB13">
+        <v>10</v>
+      </c>
+      <c r="BC13">
+        <v>40</v>
+      </c>
+      <c r="BD13">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BE13">
+        <v>10.5</v>
+      </c>
+      <c r="BF13">
         <v>9.6</v>
       </c>
-      <c r="BC13">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BD13">
-        <v>46</v>
-      </c>
-      <c r="BE13">
-        <v>9.6</v>
-      </c>
-      <c r="BF13">
-        <v>9.199999999999999</v>
-      </c>
       <c r="BG13">
-        <v>5.6</v>
+        <v>12.5</v>
       </c>
       <c r="BH13" t="s">
         <v>263</v>
@@ -3552,7 +3552,7 @@
         <v>1.46</v>
       </c>
       <c r="G14">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="H14">
         <v>9.199999999999999</v>
@@ -3564,7 +3564,7 @@
         <v>4</v>
       </c>
       <c r="K14">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L14">
         <v>1.55</v>
@@ -3576,7 +3576,7 @@
         <v>2.78</v>
       </c>
       <c r="O14">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="P14">
         <v>1.58</v>
@@ -3591,16 +3591,16 @@
         <v>5.2</v>
       </c>
       <c r="T14">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="U14">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="V14">
         <v>1.1</v>
       </c>
       <c r="W14">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="X14">
         <v>10</v>
@@ -3615,7 +3615,7 @@
         <v>1000</v>
       </c>
       <c r="AB14">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AC14">
         <v>11</v>
@@ -3663,34 +3663,34 @@
         <v>9.6</v>
       </c>
       <c r="AR14">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS14">
         <v>10</v>
       </c>
       <c r="AT14">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="AU14">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="AV14">
-        <v>20</v>
+        <v>8.6</v>
       </c>
       <c r="AW14">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AX14">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AY14">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AZ14">
-        <v>8.4</v>
+        <v>25</v>
       </c>
       <c r="BA14">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BB14">
         <v>6.4</v>
@@ -3699,13 +3699,13 @@
         <v>18.5</v>
       </c>
       <c r="BD14">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="BE14">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF14">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BG14">
         <v>10</v>
@@ -3731,52 +3731,52 @@
         <v>207</v>
       </c>
       <c r="F15">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="G15">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="H15">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="I15">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="J15">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="K15">
         <v>2.74</v>
       </c>
       <c r="L15">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="M15">
         <v>1.19</v>
       </c>
       <c r="N15">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="O15">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="P15">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="Q15">
         <v>3.3</v>
       </c>
       <c r="R15">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="S15">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="T15">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="U15">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="V15">
         <v>1.38</v>
@@ -3785,19 +3785,19 @@
         <v>1.47</v>
       </c>
       <c r="X15">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="Y15">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="Z15">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AA15">
         <v>170</v>
       </c>
       <c r="AB15">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AC15">
         <v>7.4</v>
@@ -3806,7 +3806,7 @@
         <v>17.5</v>
       </c>
       <c r="AE15">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="AF15">
         <v>17.5</v>
@@ -3815,10 +3815,10 @@
         <v>15.5</v>
       </c>
       <c r="AH15">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AI15">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="AJ15">
         <v>60</v>
@@ -3839,58 +3839,58 @@
         <v>600</v>
       </c>
       <c r="AP15">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AQ15">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AR15">
         <v>16.5</v>
       </c>
       <c r="AS15">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="AT15">
         <v>6.2</v>
       </c>
       <c r="AU15">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AV15">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AW15">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="AX15">
         <v>14</v>
       </c>
       <c r="AY15">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AZ15">
-        <v>6.6</v>
+        <v>21</v>
       </c>
       <c r="BA15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BB15">
+        <v>6.8</v>
+      </c>
+      <c r="BC15">
+        <v>7.6</v>
+      </c>
+      <c r="BD15">
+        <v>7</v>
+      </c>
+      <c r="BE15">
         <v>7.4</v>
       </c>
-      <c r="BC15">
-        <v>7.4</v>
-      </c>
-      <c r="BD15">
-        <v>7.8</v>
-      </c>
-      <c r="BE15">
-        <v>8.4</v>
-      </c>
       <c r="BF15">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="BG15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BH15" t="s">
         <v>263</v>
@@ -3913,52 +3913,52 @@
         <v>208</v>
       </c>
       <c r="F16">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="G16">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="H16">
         <v>5.6</v>
       </c>
       <c r="I16">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="J16">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K16">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L16">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="M16">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="N16">
-        <v>2.32</v>
+        <v>2.24</v>
       </c>
       <c r="O16">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="P16">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="Q16">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="R16">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="S16">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="T16">
-        <v>2.48</v>
+        <v>2.56</v>
       </c>
       <c r="U16">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="V16">
         <v>1.17</v>
@@ -3967,7 +3967,7 @@
         <v>2.06</v>
       </c>
       <c r="X16">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="Y16">
         <v>14</v>
@@ -3979,7 +3979,7 @@
         <v>900</v>
       </c>
       <c r="AB16">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="AC16">
         <v>8.4</v>
@@ -3994,7 +3994,7 @@
         <v>10.5</v>
       </c>
       <c r="AG16">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AH16">
         <v>85</v>
@@ -4006,73 +4006,73 @@
         <v>25</v>
       </c>
       <c r="AK16">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="AL16">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="AM16">
-        <v>500</v>
+        <v>510</v>
       </c>
       <c r="AN16">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="AO16">
         <v>600</v>
       </c>
       <c r="AP16">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="AQ16">
         <v>10.5</v>
       </c>
       <c r="AR16">
-        <v>6.8</v>
+        <v>18.5</v>
       </c>
       <c r="AS16">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AT16">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="AU16">
         <v>6.6</v>
       </c>
       <c r="AV16">
-        <v>6.2</v>
+        <v>12.5</v>
       </c>
       <c r="AW16">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AX16">
         <v>8</v>
       </c>
       <c r="AY16">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ16">
         <v>14.5</v>
       </c>
       <c r="BA16">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BB16">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BC16">
-        <v>7.2</v>
+        <v>22</v>
       </c>
       <c r="BD16">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BE16">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BF16">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BG16">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BH16" t="s">
         <v>263</v>
@@ -4095,58 +4095,58 @@
         <v>209</v>
       </c>
       <c r="F17">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="G17">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="H17">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="I17">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="J17">
         <v>3.95</v>
       </c>
       <c r="K17">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="L17">
+        <v>1.56</v>
+      </c>
+      <c r="M17">
+        <v>1.11</v>
+      </c>
+      <c r="N17">
+        <v>2.74</v>
+      </c>
+      <c r="O17">
+        <v>1.54</v>
+      </c>
+      <c r="P17">
         <v>1.59</v>
       </c>
-      <c r="M17">
-        <v>1.12</v>
-      </c>
-      <c r="N17">
-        <v>2.58</v>
-      </c>
-      <c r="O17">
-        <v>1.57</v>
-      </c>
-      <c r="P17">
-        <v>1.52</v>
-      </c>
       <c r="Q17">
-        <v>2.72</v>
+        <v>2.52</v>
       </c>
       <c r="R17">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="S17">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="T17">
-        <v>2.62</v>
+        <v>2.42</v>
       </c>
       <c r="U17">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="V17">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="W17">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X17">
         <v>970</v>
@@ -4155,10 +4155,10 @@
         <v>28</v>
       </c>
       <c r="Z17">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AA17">
-        <v>500</v>
+        <v>180</v>
       </c>
       <c r="AB17">
         <v>950</v>
@@ -4167,13 +4167,13 @@
         <v>42</v>
       </c>
       <c r="AD17">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AE17">
         <v>500</v>
       </c>
       <c r="AF17">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AG17">
         <v>950</v>
@@ -4203,28 +4203,28 @@
         <v>29</v>
       </c>
       <c r="AP17">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AQ17">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AR17">
         <v>3.9</v>
       </c>
       <c r="AS17">
-        <v>3.25</v>
+        <v>5.1</v>
       </c>
       <c r="AT17">
         <v>4.2</v>
       </c>
       <c r="AU17">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AV17">
-        <v>2.82</v>
+        <v>8.6</v>
       </c>
       <c r="AW17">
-        <v>2.58</v>
+        <v>5.2</v>
       </c>
       <c r="AX17">
         <v>4.2</v>
@@ -4233,10 +4233,10 @@
         <v>10</v>
       </c>
       <c r="AZ17">
-        <v>2.68</v>
+        <v>5.8</v>
       </c>
       <c r="BA17">
-        <v>2.78</v>
+        <v>3.6</v>
       </c>
       <c r="BB17">
         <v>4.2</v>
@@ -4248,13 +4248,13 @@
         <v>4.2</v>
       </c>
       <c r="BE17">
-        <v>1.9</v>
+        <v>2.46</v>
       </c>
       <c r="BF17">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="BG17">
-        <v>3.25</v>
+        <v>4.5</v>
       </c>
       <c r="BH17" t="s">
         <v>263</v>
@@ -4277,136 +4277,136 @@
         <v>210</v>
       </c>
       <c r="F18">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="G18">
-        <v>1.56</v>
+        <v>1.66</v>
       </c>
       <c r="H18">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="I18">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="J18">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="K18">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="L18">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="M18">
         <v>1.07</v>
       </c>
       <c r="N18">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="O18">
+        <v>1.34</v>
+      </c>
+      <c r="P18">
+        <v>1.89</v>
+      </c>
+      <c r="Q18">
+        <v>2.02</v>
+      </c>
+      <c r="R18">
         <v>1.33</v>
       </c>
-      <c r="P18">
-        <v>1.92</v>
-      </c>
-      <c r="Q18">
-        <v>1.98</v>
-      </c>
-      <c r="R18">
-        <v>1.36</v>
-      </c>
       <c r="S18">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="T18">
-        <v>2.06</v>
+        <v>1.96</v>
       </c>
       <c r="U18">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="V18">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="W18">
-        <v>2.7</v>
+        <v>2.48</v>
       </c>
       <c r="X18">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Y18">
         <v>24</v>
       </c>
       <c r="Z18">
-        <v>170</v>
+        <v>500</v>
       </c>
       <c r="AA18">
-        <v>330</v>
+        <v>700</v>
       </c>
       <c r="AB18">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AC18">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AD18">
-        <v>32</v>
+        <v>85</v>
       </c>
       <c r="AE18">
-        <v>170</v>
+        <v>700</v>
       </c>
       <c r="AF18">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AG18">
         <v>10.5</v>
       </c>
       <c r="AH18">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AI18">
-        <v>150</v>
+        <v>700</v>
       </c>
       <c r="AJ18">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AK18">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AL18">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AM18">
-        <v>200</v>
+        <v>700</v>
       </c>
       <c r="AN18">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AO18">
-        <v>240</v>
+        <v>700</v>
       </c>
       <c r="AP18">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AQ18">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AR18">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS18">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT18">
         <v>6.4</v>
       </c>
       <c r="AU18">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AV18">
-        <v>13.5</v>
+        <v>19</v>
       </c>
       <c r="AW18">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AX18">
         <v>7.2</v>
@@ -4418,10 +4418,10 @@
         <v>21</v>
       </c>
       <c r="BA18">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BB18">
-        <v>6.2</v>
+        <v>13</v>
       </c>
       <c r="BC18">
         <v>14.5</v>
@@ -4430,13 +4430,13 @@
         <v>34</v>
       </c>
       <c r="BE18">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BF18">
-        <v>5</v>
+        <v>7.8</v>
       </c>
       <c r="BG18">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH18" t="s">
         <v>263</v>
@@ -4459,13 +4459,13 @@
         <v>211</v>
       </c>
       <c r="F19">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="G19">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="H19">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="I19">
         <v>1.77</v>
@@ -4498,7 +4498,7 @@
         <v>1.57</v>
       </c>
       <c r="S19">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="T19">
         <v>1.67</v>
@@ -4510,7 +4510,7 @@
         <v>2.28</v>
       </c>
       <c r="W19">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="X19">
         <v>48</v>
@@ -4525,7 +4525,7 @@
         <v>900</v>
       </c>
       <c r="AB19">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AC19">
         <v>10</v>
@@ -4540,7 +4540,7 @@
         <v>140</v>
       </c>
       <c r="AG19">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="AH19">
         <v>25</v>
@@ -4549,7 +4549,7 @@
         <v>75</v>
       </c>
       <c r="AJ19">
-        <v>130</v>
+        <v>700</v>
       </c>
       <c r="AK19">
         <v>320</v>
@@ -4558,13 +4558,13 @@
         <v>150</v>
       </c>
       <c r="AM19">
-        <v>320</v>
+        <v>200</v>
       </c>
       <c r="AN19">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="AO19">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AP19">
         <v>11.5</v>
@@ -4603,19 +4603,19 @@
         <v>13</v>
       </c>
       <c r="BB19">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BC19">
         <v>12</v>
       </c>
       <c r="BD19">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BE19">
         <v>50</v>
       </c>
       <c r="BF19">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BG19">
         <v>6.6</v>
@@ -4641,16 +4641,16 @@
         <v>212</v>
       </c>
       <c r="F20">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="G20">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="H20">
         <v>2.56</v>
       </c>
       <c r="I20">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="J20">
         <v>3.75</v>
@@ -4674,10 +4674,10 @@
         <v>2.32</v>
       </c>
       <c r="Q20">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="R20">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="S20">
         <v>2.78</v>
@@ -4689,7 +4689,7 @@
         <v>2.44</v>
       </c>
       <c r="V20">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="W20">
         <v>1.53</v>
@@ -4698,13 +4698,13 @@
         <v>22</v>
       </c>
       <c r="Y20">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Z20">
         <v>21</v>
       </c>
       <c r="AA20">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="AB20">
         <v>15.5</v>
@@ -4743,7 +4743,7 @@
         <v>580</v>
       </c>
       <c r="AN20">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AO20">
         <v>17.5</v>
@@ -4794,7 +4794,7 @@
         <v>13.5</v>
       </c>
       <c r="BE20">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BF20">
         <v>14</v>
@@ -4823,22 +4823,22 @@
         <v>213</v>
       </c>
       <c r="F21">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="G21">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="H21">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="I21">
         <v>8.6</v>
       </c>
       <c r="J21">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="K21">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L21">
         <v>1.42</v>
@@ -4847,10 +4847,10 @@
         <v>1.07</v>
       </c>
       <c r="N21">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="O21">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="P21">
         <v>1.92</v>
@@ -4859,7 +4859,7 @@
         <v>2.04</v>
       </c>
       <c r="R21">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="S21">
         <v>3.75</v>
@@ -4868,22 +4868,22 @@
         <v>2.14</v>
       </c>
       <c r="U21">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="V21">
         <v>1.13</v>
       </c>
       <c r="W21">
-        <v>2.74</v>
+        <v>2.82</v>
       </c>
       <c r="X21">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Y21">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="Z21">
-        <v>420</v>
+        <v>75</v>
       </c>
       <c r="AA21">
         <v>350</v>
@@ -4895,7 +4895,7 @@
         <v>10.5</v>
       </c>
       <c r="AD21">
-        <v>950</v>
+        <v>32</v>
       </c>
       <c r="AE21">
         <v>170</v>
@@ -4907,10 +4907,10 @@
         <v>10.5</v>
       </c>
       <c r="AH21">
-        <v>950</v>
+        <v>50</v>
       </c>
       <c r="AI21">
-        <v>470</v>
+        <v>140</v>
       </c>
       <c r="AJ21">
         <v>14.5</v>
@@ -4919,25 +4919,25 @@
         <v>18</v>
       </c>
       <c r="AL21">
-        <v>250</v>
+        <v>110</v>
       </c>
       <c r="AM21">
         <v>580</v>
       </c>
       <c r="AN21">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AO21">
         <v>280</v>
       </c>
       <c r="AP21">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AQ21">
         <v>16.5</v>
       </c>
       <c r="AR21">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AS21">
         <v>11</v>
@@ -4946,7 +4946,7 @@
         <v>6.4</v>
       </c>
       <c r="AU21">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV21">
         <v>14</v>
@@ -4961,10 +4961,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ21">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BA21">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="BB21">
         <v>12</v>
@@ -4976,7 +4976,7 @@
         <v>34</v>
       </c>
       <c r="BE21">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BF21">
         <v>8.4</v>
@@ -5005,22 +5005,22 @@
         <v>214</v>
       </c>
       <c r="F22">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="G22">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="H22">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="I22">
         <v>3.95</v>
       </c>
       <c r="J22">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="K22">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="L22">
         <v>1.47</v>
@@ -5035,19 +5035,19 @@
         <v>1.4</v>
       </c>
       <c r="P22">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="Q22">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="R22">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="S22">
         <v>4.2</v>
       </c>
       <c r="T22">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="U22">
         <v>1.98</v>
@@ -5056,7 +5056,7 @@
         <v>1.33</v>
       </c>
       <c r="W22">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="X22">
         <v>12</v>
@@ -5065,7 +5065,7 @@
         <v>13</v>
       </c>
       <c r="Z22">
-        <v>95</v>
+        <v>48</v>
       </c>
       <c r="AA22">
         <v>900</v>
@@ -5077,10 +5077,10 @@
         <v>7.8</v>
       </c>
       <c r="AD22">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AE22">
-        <v>130</v>
+        <v>95</v>
       </c>
       <c r="AF22">
         <v>13</v>
@@ -5092,25 +5092,25 @@
         <v>19.5</v>
       </c>
       <c r="AI22">
-        <v>500</v>
+        <v>70</v>
       </c>
       <c r="AJ22">
         <v>500</v>
       </c>
       <c r="AK22">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AL22">
-        <v>500</v>
+        <v>46</v>
       </c>
       <c r="AM22">
         <v>580</v>
       </c>
       <c r="AN22">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="AO22">
-        <v>600</v>
+        <v>70</v>
       </c>
       <c r="AP22">
         <v>10</v>
@@ -5122,7 +5122,7 @@
         <v>24</v>
       </c>
       <c r="AS22">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="AT22">
         <v>7.4</v>
@@ -5134,7 +5134,7 @@
         <v>14</v>
       </c>
       <c r="AW22">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="AX22">
         <v>11</v>
@@ -5146,10 +5146,10 @@
         <v>17</v>
       </c>
       <c r="BA22">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BB22">
-        <v>13</v>
+        <v>17.5</v>
       </c>
       <c r="BC22">
         <v>21</v>
@@ -5158,13 +5158,13 @@
         <v>36</v>
       </c>
       <c r="BE22">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BF22">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BG22">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BH22" t="s">
         <v>263</v>
@@ -5187,13 +5187,13 @@
         <v>215</v>
       </c>
       <c r="F23">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="G23">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="H23">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="I23">
         <v>1.76</v>
@@ -5211,22 +5211,22 @@
         <v>1.07</v>
       </c>
       <c r="N23">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="O23">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="P23">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="Q23">
         <v>2.08</v>
       </c>
       <c r="R23">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="S23">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="T23">
         <v>1.99</v>
@@ -5241,7 +5241,7 @@
         <v>1.2</v>
       </c>
       <c r="X23">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="Y23">
         <v>8.199999999999999</v>
@@ -5253,22 +5253,22 @@
         <v>18</v>
       </c>
       <c r="AB23">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AC23">
         <v>9</v>
       </c>
       <c r="AD23">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AE23">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AF23">
         <v>100</v>
       </c>
       <c r="AG23">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="AH23">
         <v>22</v>
@@ -5280,7 +5280,7 @@
         <v>900</v>
       </c>
       <c r="AK23">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="AL23">
         <v>320</v>
@@ -5322,7 +5322,7 @@
         <v>36</v>
       </c>
       <c r="AY23">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AZ23">
         <v>19.5</v>
@@ -5331,19 +5331,19 @@
         <v>32</v>
       </c>
       <c r="BB23">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BC23">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="BD23">
         <v>38</v>
       </c>
       <c r="BE23">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="BF23">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BG23">
         <v>10.5</v>
@@ -5369,7 +5369,7 @@
         <v>216</v>
       </c>
       <c r="F24">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="G24">
         <v>1.93</v>
@@ -5384,7 +5384,7 @@
         <v>3.7</v>
       </c>
       <c r="K24">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L24">
         <v>1.43</v>
@@ -5393,7 +5393,7 @@
         <v>1.07</v>
       </c>
       <c r="N24">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="O24">
         <v>1.36</v>
@@ -5402,7 +5402,7 @@
         <v>1.89</v>
       </c>
       <c r="Q24">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="R24">
         <v>1.33</v>
@@ -5411,46 +5411,46 @@
         <v>3.85</v>
       </c>
       <c r="T24">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="U24">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="V24">
         <v>1.26</v>
       </c>
       <c r="W24">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="X24">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Y24">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Z24">
         <v>36</v>
       </c>
       <c r="AA24">
-        <v>130</v>
+        <v>900</v>
       </c>
       <c r="AB24">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC24">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD24">
         <v>22</v>
       </c>
       <c r="AE24">
-        <v>320</v>
+        <v>120</v>
       </c>
       <c r="AF24">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AG24">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH24">
         <v>23</v>
@@ -5474,22 +5474,22 @@
         <v>17</v>
       </c>
       <c r="AO24">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AP24">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AQ24">
         <v>13</v>
       </c>
       <c r="AR24">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AS24">
         <v>70</v>
       </c>
       <c r="AT24">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AU24">
         <v>7.4</v>
@@ -5504,10 +5504,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AY24">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ24">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BA24">
         <v>50</v>
@@ -5519,13 +5519,13 @@
         <v>18.5</v>
       </c>
       <c r="BD24">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="BE24">
         <v>85</v>
       </c>
       <c r="BF24">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BG24">
         <v>55</v>
@@ -5551,22 +5551,22 @@
         <v>217</v>
       </c>
       <c r="F25">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="G25">
         <v>3.7</v>
       </c>
       <c r="H25">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="I25">
         <v>2.32</v>
       </c>
       <c r="J25">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K25">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="L25">
         <v>1.42</v>
@@ -5584,7 +5584,7 @@
         <v>1.92</v>
       </c>
       <c r="Q25">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="R25">
         <v>1.35</v>
@@ -5593,10 +5593,10 @@
         <v>3.6</v>
       </c>
       <c r="T25">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="U25">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="V25">
         <v>1.76</v>
@@ -5614,10 +5614,10 @@
         <v>15</v>
       </c>
       <c r="AA25">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="AB25">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AC25">
         <v>8.4</v>
@@ -5626,10 +5626,10 @@
         <v>11.5</v>
       </c>
       <c r="AE25">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AF25">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="AG25">
         <v>16</v>
@@ -5641,40 +5641,40 @@
         <v>110</v>
       </c>
       <c r="AJ25">
-        <v>440</v>
+        <v>160</v>
       </c>
       <c r="AK25">
         <v>55</v>
       </c>
       <c r="AL25">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="AM25">
         <v>580</v>
       </c>
       <c r="AN25">
-        <v>75</v>
+        <v>600</v>
       </c>
       <c r="AO25">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AP25">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AQ25">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AR25">
         <v>12</v>
       </c>
       <c r="AS25">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AT25">
         <v>11.5</v>
       </c>
       <c r="AU25">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AV25">
         <v>9.4</v>
@@ -5683,34 +5683,34 @@
         <v>20</v>
       </c>
       <c r="AX25">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AY25">
         <v>13</v>
       </c>
       <c r="AZ25">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA25">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="BB25">
-        <v>7.8</v>
+        <v>23</v>
       </c>
       <c r="BC25">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BD25">
-        <v>7.8</v>
+        <v>24</v>
       </c>
       <c r="BE25">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BF25">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="BG25">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BH25" t="s">
         <v>263</v>
@@ -5733,22 +5733,22 @@
         <v>218</v>
       </c>
       <c r="F26">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="G26">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="H26">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="I26">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="J26">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="K26">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="L26">
         <v>1.46</v>
@@ -5775,16 +5775,16 @@
         <v>3.85</v>
       </c>
       <c r="T26">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="U26">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V26">
         <v>1.37</v>
       </c>
       <c r="W26">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="X26">
         <v>13</v>
@@ -5793,64 +5793,64 @@
         <v>13.5</v>
       </c>
       <c r="Z26">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AA26">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB26">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AC26">
         <v>7.8</v>
       </c>
       <c r="AD26">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="AE26">
-        <v>190</v>
+        <v>85</v>
       </c>
       <c r="AF26">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AG26">
         <v>11</v>
       </c>
       <c r="AH26">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI26">
         <v>320</v>
       </c>
       <c r="AJ26">
-        <v>85</v>
+        <v>34</v>
       </c>
       <c r="AK26">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AL26">
         <v>150</v>
       </c>
       <c r="AM26">
-        <v>580</v>
+        <v>500</v>
       </c>
       <c r="AN26">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AO26">
-        <v>600</v>
+        <v>140</v>
       </c>
       <c r="AP26">
         <v>7.4</v>
       </c>
       <c r="AQ26">
-        <v>7.6</v>
+        <v>11</v>
       </c>
       <c r="AR26">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="AS26">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="AT26">
         <v>8</v>
@@ -5877,22 +5877,22 @@
         <v>19.5</v>
       </c>
       <c r="BB26">
-        <v>10.5</v>
+        <v>19</v>
       </c>
       <c r="BC26">
-        <v>11.5</v>
+        <v>16.5</v>
       </c>
       <c r="BD26">
         <v>20</v>
       </c>
       <c r="BE26">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BF26">
         <v>17.5</v>
       </c>
       <c r="BG26">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BH26" t="s">
         <v>263</v>
@@ -5915,22 +5915,22 @@
         <v>219</v>
       </c>
       <c r="F27">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="G27">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="H27">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="I27">
         <v>2.98</v>
       </c>
       <c r="J27">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K27">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="L27">
         <v>1.42</v>
@@ -5939,112 +5939,112 @@
         <v>1.07</v>
       </c>
       <c r="N27">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="O27">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P27">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="Q27">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="R27">
         <v>1.36</v>
       </c>
       <c r="S27">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="T27">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="U27">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="V27">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W27">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="X27">
-        <v>17.5</v>
+        <v>14</v>
       </c>
       <c r="Y27">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="Z27">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="AA27">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AB27">
+        <v>11</v>
+      </c>
+      <c r="AC27">
+        <v>8</v>
+      </c>
+      <c r="AD27">
         <v>13</v>
       </c>
-      <c r="AC27">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD27">
-        <v>15.5</v>
-      </c>
       <c r="AE27">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="AF27">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="AG27">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH27">
-        <v>19.5</v>
+        <v>24</v>
       </c>
       <c r="AI27">
-        <v>48</v>
+        <v>80</v>
       </c>
       <c r="AJ27">
+        <v>130</v>
+      </c>
+      <c r="AK27">
+        <v>75</v>
+      </c>
+      <c r="AL27">
+        <v>100</v>
+      </c>
+      <c r="AM27">
+        <v>580</v>
+      </c>
+      <c r="AN27">
+        <v>42</v>
+      </c>
+      <c r="AO27">
         <v>46</v>
       </c>
-      <c r="AK27">
-        <v>34</v>
-      </c>
-      <c r="AL27">
-        <v>46</v>
-      </c>
-      <c r="AM27">
-        <v>95</v>
-      </c>
-      <c r="AN27">
-        <v>25</v>
-      </c>
-      <c r="AO27">
-        <v>600</v>
-      </c>
       <c r="AP27">
-        <v>6.6</v>
+        <v>12</v>
       </c>
       <c r="AQ27">
+        <v>10</v>
+      </c>
+      <c r="AR27">
+        <v>11</v>
+      </c>
+      <c r="AS27">
+        <v>20</v>
+      </c>
+      <c r="AT27">
+        <v>9.6</v>
+      </c>
+      <c r="AU27">
         <v>7</v>
       </c>
-      <c r="AR27">
-        <v>7.8</v>
-      </c>
-      <c r="AS27">
-        <v>5.4</v>
-      </c>
-      <c r="AT27">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AU27">
-        <v>6.2</v>
-      </c>
       <c r="AV27">
-        <v>5.1</v>
+        <v>11.5</v>
       </c>
       <c r="AW27">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AX27">
         <v>15.5</v>
@@ -6053,28 +6053,28 @@
         <v>10.5</v>
       </c>
       <c r="AZ27">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="BA27">
         <v>20</v>
       </c>
       <c r="BB27">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BC27">
         <v>13.5</v>
       </c>
       <c r="BD27">
-        <v>4.9</v>
+        <v>18.5</v>
       </c>
       <c r="BE27">
-        <v>5.1</v>
+        <v>12</v>
       </c>
       <c r="BF27">
-        <v>5.2</v>
+        <v>9</v>
       </c>
       <c r="BG27">
-        <v>17.5</v>
+        <v>9.4</v>
       </c>
       <c r="BH27" t="s">
         <v>263</v>
@@ -6100,7 +6100,7 @@
         <v>3.3</v>
       </c>
       <c r="G28">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="H28">
         <v>2.2</v>
@@ -6121,7 +6121,7 @@
         <v>1.06</v>
       </c>
       <c r="N28">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="O28">
         <v>1.3</v>
@@ -6130,13 +6130,13 @@
         <v>2.02</v>
       </c>
       <c r="Q28">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="R28">
         <v>1.39</v>
       </c>
       <c r="S28">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="T28">
         <v>1.75</v>
@@ -6145,52 +6145,52 @@
         <v>2.18</v>
       </c>
       <c r="V28">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="W28">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="X28">
-        <v>970</v>
+        <v>90</v>
       </c>
       <c r="Y28">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="Z28">
-        <v>970</v>
+        <v>29</v>
       </c>
       <c r="AA28">
-        <v>900</v>
+        <v>90</v>
       </c>
       <c r="AB28">
-        <v>500</v>
+        <v>24</v>
       </c>
       <c r="AC28">
-        <v>10.5</v>
+        <v>8.6</v>
       </c>
       <c r="AD28">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="AE28">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AF28">
         <v>48</v>
       </c>
       <c r="AG28">
-        <v>970</v>
+        <v>29</v>
       </c>
       <c r="AH28">
         <v>36</v>
       </c>
       <c r="AI28">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="AJ28">
         <v>500</v>
       </c>
       <c r="AK28">
-        <v>500</v>
+        <v>110</v>
       </c>
       <c r="AL28">
         <v>500</v>
@@ -6208,55 +6208,55 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AQ28">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AR28">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="AS28">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AT28">
         <v>7.6</v>
       </c>
       <c r="AU28">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV28">
         <v>6.4</v>
       </c>
       <c r="AW28">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AX28">
         <v>11.5</v>
       </c>
       <c r="AY28">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ28">
         <v>10.5</v>
       </c>
       <c r="BA28">
-        <v>8.6</v>
+        <v>18</v>
       </c>
       <c r="BB28">
         <v>20</v>
       </c>
       <c r="BC28">
-        <v>25</v>
+        <v>13.5</v>
       </c>
       <c r="BD28">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="BE28">
         <v>5.3</v>
       </c>
       <c r="BF28">
-        <v>23</v>
+        <v>7.2</v>
       </c>
       <c r="BG28">
-        <v>4.4</v>
+        <v>7.2</v>
       </c>
       <c r="BH28" t="s">
         <v>263</v>
@@ -6279,22 +6279,22 @@
         <v>221</v>
       </c>
       <c r="F29">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="G29">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="H29">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="I29">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="J29">
         <v>4.8</v>
       </c>
       <c r="K29">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="L29">
         <v>1.32</v>
@@ -6312,13 +6312,13 @@
         <v>2.42</v>
       </c>
       <c r="Q29">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="R29">
         <v>1.55</v>
       </c>
       <c r="S29">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="T29">
         <v>1.85</v>
@@ -6330,7 +6330,7 @@
         <v>1.15</v>
       </c>
       <c r="W29">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="X29">
         <v>23</v>
@@ -6339,7 +6339,7 @@
         <v>28</v>
       </c>
       <c r="Z29">
-        <v>65</v>
+        <v>160</v>
       </c>
       <c r="AA29">
         <v>240</v>
@@ -6357,22 +6357,22 @@
         <v>480</v>
       </c>
       <c r="AF29">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG29">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH29">
         <v>23</v>
       </c>
       <c r="AI29">
-        <v>210</v>
+        <v>390</v>
       </c>
       <c r="AJ29">
         <v>13.5</v>
       </c>
       <c r="AK29">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AL29">
         <v>34</v>
@@ -6387,7 +6387,7 @@
         <v>120</v>
       </c>
       <c r="AP29">
-        <v>19.5</v>
+        <v>16.5</v>
       </c>
       <c r="AQ29">
         <v>23</v>
@@ -6417,10 +6417,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ29">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BA29">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="BB29">
         <v>11.5</v>
@@ -6432,13 +6432,13 @@
         <v>26</v>
       </c>
       <c r="BE29">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="BF29">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BG29">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="BH29" t="s">
         <v>263</v>
@@ -6470,7 +6470,7 @@
         <v>1.52</v>
       </c>
       <c r="I30">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="J30">
         <v>4.3</v>
@@ -6503,13 +6503,13 @@
         <v>3.6</v>
       </c>
       <c r="T30">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="U30">
         <v>1.81</v>
       </c>
       <c r="V30">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="W30">
         <v>1.13</v>
@@ -6530,7 +6530,7 @@
         <v>950</v>
       </c>
       <c r="AC30">
-        <v>15</v>
+        <v>10.5</v>
       </c>
       <c r="AD30">
         <v>17.5</v>
@@ -6566,7 +6566,7 @@
         <v>230</v>
       </c>
       <c r="AO30">
-        <v>25</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AP30">
         <v>8.199999999999999</v>
@@ -6578,7 +6578,7 @@
         <v>7.4</v>
       </c>
       <c r="AS30">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AT30">
         <v>17.5</v>
@@ -6587,10 +6587,10 @@
         <v>5.9</v>
       </c>
       <c r="AV30">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AW30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX30">
         <v>23</v>
@@ -6605,22 +6605,22 @@
         <v>19.5</v>
       </c>
       <c r="BB30">
+        <v>12.5</v>
+      </c>
+      <c r="BC30">
         <v>8.6</v>
       </c>
-      <c r="BC30">
-        <v>5</v>
-      </c>
       <c r="BD30">
-        <v>4.2</v>
+        <v>8.6</v>
       </c>
       <c r="BE30">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF30">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="BG30">
-        <v>5.6</v>
+        <v>7.6</v>
       </c>
       <c r="BH30" t="s">
         <v>263</v>
@@ -6643,28 +6643,28 @@
         <v>223</v>
       </c>
       <c r="F31">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="G31">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="H31">
         <v>3.15</v>
       </c>
       <c r="I31">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="J31">
         <v>3.45</v>
       </c>
       <c r="K31">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L31">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="M31">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N31">
         <v>3.55</v>
@@ -6673,13 +6673,13 @@
         <v>1.36</v>
       </c>
       <c r="P31">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="Q31">
         <v>2.12</v>
       </c>
       <c r="R31">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S31">
         <v>3.9</v>
@@ -6688,13 +6688,13 @@
         <v>1.8</v>
       </c>
       <c r="U31">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="V31">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="W31">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="X31">
         <v>14</v>
@@ -6706,22 +6706,22 @@
         <v>23</v>
       </c>
       <c r="AA31">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB31">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AC31">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AD31">
         <v>14</v>
       </c>
       <c r="AE31">
-        <v>190</v>
+        <v>95</v>
       </c>
       <c r="AF31">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AG31">
         <v>11.5</v>
@@ -6730,16 +6730,16 @@
         <v>18.5</v>
       </c>
       <c r="AI31">
-        <v>290</v>
+        <v>120</v>
       </c>
       <c r="AJ31">
         <v>80</v>
       </c>
       <c r="AK31">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AL31">
-        <v>190</v>
+        <v>100</v>
       </c>
       <c r="AM31">
         <v>580</v>
@@ -6763,46 +6763,46 @@
         <v>42</v>
       </c>
       <c r="AT31">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AU31">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AV31">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AW31">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="AX31">
         <v>13</v>
       </c>
       <c r="AY31">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AZ31">
+        <v>15.5</v>
+      </c>
+      <c r="BA31">
+        <v>23</v>
+      </c>
+      <c r="BB31">
         <v>15</v>
       </c>
-      <c r="BA31">
-        <v>38</v>
-      </c>
-      <c r="BB31">
-        <v>14.5</v>
-      </c>
       <c r="BC31">
-        <v>14.5</v>
+        <v>22</v>
       </c>
       <c r="BD31">
+        <v>25</v>
+      </c>
+      <c r="BE31">
+        <v>29</v>
+      </c>
+      <c r="BF31">
         <v>20</v>
       </c>
-      <c r="BE31">
-        <v>12.5</v>
-      </c>
-      <c r="BF31">
-        <v>19.5</v>
-      </c>
       <c r="BG31">
-        <v>10.5</v>
+        <v>19</v>
       </c>
       <c r="BH31" t="s">
         <v>263</v>
@@ -6825,16 +6825,16 @@
         <v>224</v>
       </c>
       <c r="F32">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="G32">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="H32">
         <v>3.1</v>
       </c>
       <c r="I32">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="J32">
         <v>3.35</v>
@@ -6867,10 +6867,10 @@
         <v>3.95</v>
       </c>
       <c r="T32">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="U32">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="V32">
         <v>1.45</v>
@@ -6933,25 +6933,25 @@
         <v>600</v>
       </c>
       <c r="AP32">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AQ32">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AR32">
         <v>18</v>
       </c>
       <c r="AS32">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AT32">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AU32">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AV32">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW32">
         <v>15</v>
@@ -6960,13 +6960,13 @@
         <v>13.5</v>
       </c>
       <c r="AY32">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ32">
         <v>15.5</v>
       </c>
       <c r="BA32">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB32">
         <v>14</v>
@@ -6984,7 +6984,7 @@
         <v>18.5</v>
       </c>
       <c r="BG32">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BH32" t="s">
         <v>263</v>
@@ -7007,10 +7007,10 @@
         <v>225</v>
       </c>
       <c r="F33">
+        <v>3.15</v>
+      </c>
+      <c r="G33">
         <v>3.2</v>
-      </c>
-      <c r="G33">
-        <v>3.25</v>
       </c>
       <c r="H33">
         <v>2.58</v>
@@ -7025,52 +7025,52 @@
         <v>3.35</v>
       </c>
       <c r="L33">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="M33">
         <v>1.09</v>
       </c>
       <c r="N33">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O33">
         <v>1.41</v>
       </c>
       <c r="P33">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="Q33">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="R33">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S33">
         <v>4.2</v>
       </c>
       <c r="T33">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="U33">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="V33">
         <v>1.62</v>
       </c>
       <c r="W33">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="X33">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Y33">
         <v>9.4</v>
       </c>
       <c r="Z33">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AA33">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AB33">
         <v>11</v>
@@ -7082,19 +7082,19 @@
         <v>12</v>
       </c>
       <c r="AE33">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AF33">
         <v>21</v>
       </c>
       <c r="AG33">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH33">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI33">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AJ33">
         <v>55</v>
@@ -7112,7 +7112,7 @@
         <v>46</v>
       </c>
       <c r="AO33">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AP33">
         <v>10.5</v>
@@ -7130,7 +7130,7 @@
         <v>10.5</v>
       </c>
       <c r="AU33">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV33">
         <v>11</v>
@@ -7145,7 +7145,7 @@
         <v>13</v>
       </c>
       <c r="AZ33">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA33">
         <v>40</v>
@@ -7157,7 +7157,7 @@
         <v>36</v>
       </c>
       <c r="BD33">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BE33">
         <v>90</v>
@@ -7166,7 +7166,7 @@
         <v>40</v>
       </c>
       <c r="BG33">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BH33" t="s">
         <v>263</v>
@@ -7189,16 +7189,16 @@
         <v>226</v>
       </c>
       <c r="F34">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="G34">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="H34">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="I34">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="J34">
         <v>3.75</v>
@@ -7210,7 +7210,7 @@
         <v>1.35</v>
       </c>
       <c r="M34">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N34">
         <v>4.7</v>
@@ -7219,31 +7219,31 @@
         <v>1.25</v>
       </c>
       <c r="P34">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="Q34">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="R34">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="S34">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="T34">
         <v>1.69</v>
       </c>
       <c r="U34">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="V34">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="W34">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="X34">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="Y34">
         <v>12.5</v>
@@ -7252,7 +7252,7 @@
         <v>18</v>
       </c>
       <c r="AA34">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AB34">
         <v>14</v>
@@ -7270,7 +7270,7 @@
         <v>21</v>
       </c>
       <c r="AG34">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH34">
         <v>15</v>
@@ -7282,10 +7282,10 @@
         <v>42</v>
       </c>
       <c r="AK34">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AL34">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM34">
         <v>65</v>
@@ -7294,13 +7294,13 @@
         <v>21</v>
       </c>
       <c r="AO34">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AP34">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AQ34">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AR34">
         <v>16.5</v>
@@ -7312,16 +7312,16 @@
         <v>13</v>
       </c>
       <c r="AU34">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV34">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW34">
         <v>23</v>
       </c>
       <c r="AX34">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AY34">
         <v>12</v>
@@ -7330,16 +7330,16 @@
         <v>14</v>
       </c>
       <c r="BA34">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BB34">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BC34">
         <v>27</v>
       </c>
       <c r="BD34">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BE34">
         <v>55</v>
@@ -7377,16 +7377,16 @@
         <v>1.29</v>
       </c>
       <c r="H35">
-        <v>12</v>
+        <v>15.5</v>
       </c>
       <c r="I35">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J35">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="K35">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="L35">
         <v>1.38</v>
@@ -7413,22 +7413,22 @@
         <v>3.2</v>
       </c>
       <c r="T35">
-        <v>2.66</v>
+        <v>2.58</v>
       </c>
       <c r="U35">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="V35">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W35">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="X35">
         <v>18.5</v>
       </c>
       <c r="Y35">
-        <v>110</v>
+        <v>950</v>
       </c>
       <c r="Z35">
         <v>240</v>
@@ -7440,13 +7440,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AC35">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AD35">
-        <v>950</v>
+        <v>300</v>
       </c>
       <c r="AE35">
-        <v>1000</v>
+        <v>590</v>
       </c>
       <c r="AF35">
         <v>6.8</v>
@@ -7473,34 +7473,34 @@
         <v>460</v>
       </c>
       <c r="AN35">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AO35">
         <v>1000</v>
       </c>
       <c r="AP35">
-        <v>7.6</v>
+        <v>14.5</v>
       </c>
       <c r="AQ35">
         <v>16</v>
       </c>
       <c r="AR35">
+        <v>8</v>
+      </c>
+      <c r="AS35">
+        <v>8.4</v>
+      </c>
+      <c r="AT35">
+        <v>4.1</v>
+      </c>
+      <c r="AU35">
+        <v>12</v>
+      </c>
+      <c r="AV35">
+        <v>7.6</v>
+      </c>
+      <c r="AW35">
         <v>8.199999999999999</v>
-      </c>
-      <c r="AS35">
-        <v>8.6</v>
-      </c>
-      <c r="AT35">
-        <v>4.2</v>
-      </c>
-      <c r="AU35">
-        <v>7</v>
-      </c>
-      <c r="AV35">
-        <v>7.8</v>
-      </c>
-      <c r="AW35">
-        <v>8.6</v>
       </c>
       <c r="AX35">
         <v>5.6</v>
@@ -7512,7 +7512,7 @@
         <v>20</v>
       </c>
       <c r="BA35">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB35">
         <v>7.4</v>
@@ -7521,16 +7521,16 @@
         <v>14</v>
       </c>
       <c r="BD35">
-        <v>7.6</v>
+        <v>26</v>
       </c>
       <c r="BE35">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF35">
         <v>4.9</v>
       </c>
       <c r="BG35">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BH35" t="s">
         <v>263</v>
@@ -7556,13 +7556,13 @@
         <v>2.04</v>
       </c>
       <c r="G36">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="H36">
         <v>4.2</v>
       </c>
       <c r="I36">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="J36">
         <v>3.45</v>
@@ -7595,7 +7595,7 @@
         <v>4</v>
       </c>
       <c r="T36">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="U36">
         <v>1.96</v>
@@ -7604,13 +7604,13 @@
         <v>1.29</v>
       </c>
       <c r="W36">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="X36">
-        <v>90</v>
+        <v>22</v>
       </c>
       <c r="Y36">
-        <v>970</v>
+        <v>32</v>
       </c>
       <c r="Z36">
         <v>120</v>
@@ -7619,13 +7619,13 @@
         <v>900</v>
       </c>
       <c r="AB36">
-        <v>950</v>
+        <v>27</v>
       </c>
       <c r="AC36">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="AD36">
-        <v>970</v>
+        <v>46</v>
       </c>
       <c r="AE36">
         <v>700</v>
@@ -7634,13 +7634,13 @@
         <v>970</v>
       </c>
       <c r="AG36">
-        <v>970</v>
+        <v>36</v>
       </c>
       <c r="AH36">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="AI36">
-        <v>700</v>
+        <v>370</v>
       </c>
       <c r="AJ36">
         <v>900</v>
@@ -7658,22 +7658,22 @@
         <v>85</v>
       </c>
       <c r="AO36">
-        <v>600</v>
+        <v>480</v>
       </c>
       <c r="AP36">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AQ36">
         <v>8.4</v>
       </c>
       <c r="AR36">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AS36">
-        <v>2.78</v>
+        <v>4.2</v>
       </c>
       <c r="AT36">
-        <v>5.2</v>
+        <v>7.2</v>
       </c>
       <c r="AU36">
         <v>7</v>
@@ -7682,22 +7682,22 @@
         <v>10.5</v>
       </c>
       <c r="AW36">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="AX36">
-        <v>6.6</v>
+        <v>10</v>
       </c>
       <c r="AY36">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AZ36">
         <v>11.5</v>
       </c>
       <c r="BA36">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BB36">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BC36">
         <v>19.5</v>
@@ -7706,13 +7706,13 @@
         <v>21</v>
       </c>
       <c r="BE36">
-        <v>3.45</v>
+        <v>4.3</v>
       </c>
       <c r="BF36">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG36">
-        <v>5.7</v>
+        <v>4.2</v>
       </c>
       <c r="BH36" t="s">
         <v>263</v>
@@ -7735,22 +7735,22 @@
         <v>229</v>
       </c>
       <c r="F37">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="G37">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="H37">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="I37">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="J37">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K37">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L37">
         <v>1.46</v>
@@ -7765,19 +7765,19 @@
         <v>1.36</v>
       </c>
       <c r="P37">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="Q37">
         <v>2.12</v>
       </c>
       <c r="R37">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="S37">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="T37">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="U37">
         <v>2.12</v>
@@ -7786,10 +7786,10 @@
         <v>1.62</v>
       </c>
       <c r="W37">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="X37">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Y37">
         <v>10.5</v>
@@ -7804,7 +7804,7 @@
         <v>11.5</v>
       </c>
       <c r="AC37">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD37">
         <v>12</v>
@@ -7837,10 +7837,10 @@
         <v>100</v>
       </c>
       <c r="AN37">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AO37">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AP37">
         <v>11.5</v>
@@ -7870,10 +7870,10 @@
         <v>18.5</v>
       </c>
       <c r="AY37">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AZ37">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BA37">
         <v>38</v>
@@ -7888,7 +7888,7 @@
         <v>44</v>
       </c>
       <c r="BE37">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="BF37">
         <v>30</v>
@@ -7917,19 +7917,19 @@
         <v>230</v>
       </c>
       <c r="F38">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="G38">
         <v>1.73</v>
       </c>
       <c r="H38">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="I38">
         <v>5.7</v>
       </c>
       <c r="J38">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K38">
         <v>4.3</v>
@@ -7947,10 +7947,10 @@
         <v>1.29</v>
       </c>
       <c r="P38">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q38">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="R38">
         <v>1.41</v>
@@ -7968,13 +7968,13 @@
         <v>1.21</v>
       </c>
       <c r="W38">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="X38">
         <v>17</v>
       </c>
       <c r="Y38">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="Z38">
         <v>46</v>
@@ -8037,7 +8037,7 @@
         <v>50</v>
       </c>
       <c r="AT38">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU38">
         <v>8.4</v>
@@ -8046,7 +8046,7 @@
         <v>19.5</v>
       </c>
       <c r="AW38">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AX38">
         <v>9.199999999999999</v>
@@ -8070,10 +8070,10 @@
         <v>30</v>
       </c>
       <c r="BE38">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BF38">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BG38">
         <v>48</v>
@@ -8105,19 +8105,19 @@
         <v>3.3</v>
       </c>
       <c r="H39">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="I39">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="J39">
         <v>3.3</v>
       </c>
       <c r="K39">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L39">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="M39">
         <v>1.1</v>
@@ -8129,25 +8129,25 @@
         <v>1.44</v>
       </c>
       <c r="P39">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="Q39">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="R39">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S39">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="T39">
         <v>1.98</v>
       </c>
       <c r="U39">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="V39">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="W39">
         <v>1.44</v>
@@ -8177,10 +8177,10 @@
         <v>90</v>
       </c>
       <c r="AF39">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="AG39">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH39">
         <v>21</v>
@@ -8189,7 +8189,7 @@
         <v>150</v>
       </c>
       <c r="AJ39">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK39">
         <v>140</v>
@@ -8201,16 +8201,16 @@
         <v>580</v>
       </c>
       <c r="AN39">
-        <v>500</v>
+        <v>90</v>
       </c>
       <c r="AO39">
         <v>34</v>
       </c>
       <c r="AP39">
-        <v>9.199999999999999</v>
+        <v>5.6</v>
       </c>
       <c r="AQ39">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AR39">
         <v>13</v>
@@ -8219,7 +8219,7 @@
         <v>16</v>
       </c>
       <c r="AT39">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU39">
         <v>6.4</v>
@@ -8240,25 +8240,25 @@
         <v>17.5</v>
       </c>
       <c r="BA39">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BB39">
         <v>23</v>
       </c>
       <c r="BC39">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BD39">
+        <v>9.4</v>
+      </c>
+      <c r="BE39">
+        <v>10</v>
+      </c>
+      <c r="BF39">
         <v>9</v>
       </c>
-      <c r="BD39">
-        <v>9</v>
-      </c>
-      <c r="BE39">
-        <v>9.6</v>
-      </c>
-      <c r="BF39">
-        <v>10</v>
-      </c>
       <c r="BG39">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BH39" t="s">
         <v>263</v>
@@ -8284,13 +8284,13 @@
         <v>2.48</v>
       </c>
       <c r="G40">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="H40">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="I40">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="J40">
         <v>3.75</v>
@@ -8299,7 +8299,7 @@
         <v>3.85</v>
       </c>
       <c r="L40">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="M40">
         <v>1.05</v>
@@ -8311,22 +8311,22 @@
         <v>1.23</v>
       </c>
       <c r="P40">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="Q40">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="R40">
         <v>1.54</v>
       </c>
       <c r="S40">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="T40">
         <v>1.61</v>
       </c>
       <c r="U40">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="V40">
         <v>1.5</v>
@@ -8335,7 +8335,7 @@
         <v>1.64</v>
       </c>
       <c r="X40">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y40">
         <v>15</v>
@@ -8344,7 +8344,7 @@
         <v>22</v>
       </c>
       <c r="AA40">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AB40">
         <v>14</v>
@@ -8356,13 +8356,13 @@
         <v>13.5</v>
       </c>
       <c r="AE40">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AF40">
         <v>18.5</v>
       </c>
       <c r="AG40">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH40">
         <v>15.5</v>
@@ -8374,19 +8374,19 @@
         <v>120</v>
       </c>
       <c r="AK40">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AL40">
         <v>80</v>
       </c>
       <c r="AM40">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AN40">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AO40">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="AP40">
         <v>17.5</v>
@@ -8413,7 +8413,7 @@
         <v>14.5</v>
       </c>
       <c r="AX40">
-        <v>9.6</v>
+        <v>16.5</v>
       </c>
       <c r="AY40">
         <v>10</v>
@@ -8466,13 +8466,13 @@
         <v>1.58</v>
       </c>
       <c r="G41">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="H41">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="I41">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="J41">
         <v>4.7</v>
@@ -8493,10 +8493,10 @@
         <v>1.18</v>
       </c>
       <c r="P41">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="Q41">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="R41">
         <v>1.66</v>
@@ -8508,13 +8508,13 @@
         <v>1.67</v>
       </c>
       <c r="U41">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="V41">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="W41">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="X41">
         <v>29</v>
@@ -8538,7 +8538,7 @@
         <v>23</v>
       </c>
       <c r="AE41">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AF41">
         <v>11.5</v>
@@ -8574,10 +8574,10 @@
         <v>24</v>
       </c>
       <c r="AQ41">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AR41">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AS41">
         <v>29</v>
@@ -8604,7 +8604,7 @@
         <v>16.5</v>
       </c>
       <c r="BA41">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="BB41">
         <v>14</v>
@@ -8645,13 +8645,13 @@
         <v>234</v>
       </c>
       <c r="F42">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="G42">
         <v>1.95</v>
       </c>
       <c r="H42">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="I42">
         <v>4.2</v>
@@ -8687,10 +8687,10 @@
         <v>3.25</v>
       </c>
       <c r="T42">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="U42">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V42">
         <v>1.31</v>
@@ -8699,58 +8699,58 @@
         <v>2.04</v>
       </c>
       <c r="X42">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="Y42">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="Z42">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="AA42">
         <v>900</v>
       </c>
       <c r="AB42">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AC42">
         <v>12</v>
       </c>
       <c r="AD42">
-        <v>500</v>
+        <v>32</v>
       </c>
       <c r="AE42">
-        <v>500</v>
+        <v>320</v>
       </c>
       <c r="AF42">
         <v>13.5</v>
       </c>
       <c r="AG42">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH42">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="AI42">
         <v>500</v>
       </c>
       <c r="AJ42">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AK42">
         <v>34</v>
       </c>
       <c r="AL42">
-        <v>500</v>
+        <v>80</v>
       </c>
       <c r="AM42">
         <v>580</v>
       </c>
       <c r="AN42">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="AO42">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="AP42">
         <v>8.4</v>
@@ -8762,7 +8762,7 @@
         <v>16</v>
       </c>
       <c r="AS42">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT42">
         <v>5.8</v>
@@ -8774,7 +8774,7 @@
         <v>10.5</v>
       </c>
       <c r="AW42">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AX42">
         <v>9.800000000000001</v>
@@ -8786,7 +8786,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BA42">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB42">
         <v>10.5</v>
@@ -8804,7 +8804,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BG42">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BH42" t="s">
         <v>263</v>
@@ -8827,166 +8827,166 @@
         <v>235</v>
       </c>
       <c r="F43">
-        <v>2.26</v>
+        <v>2.1</v>
       </c>
       <c r="G43">
-        <v>2.34</v>
+        <v>2.14</v>
       </c>
       <c r="H43">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="I43">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="J43">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="K43">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="L43">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="M43">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N43">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="O43">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="P43">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="Q43">
         <v>2.18</v>
       </c>
       <c r="R43">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S43">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="T43">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="U43">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="V43">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="W43">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="X43">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Y43">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Z43">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="AA43">
         <v>900</v>
       </c>
       <c r="AB43">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AC43">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD43">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AE43">
-        <v>500</v>
+        <v>120</v>
       </c>
       <c r="AF43">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="AG43">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH43">
-        <v>500</v>
+        <v>38</v>
       </c>
       <c r="AI43">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="AJ43">
-        <v>900</v>
+        <v>29</v>
       </c>
       <c r="AK43">
         <v>65</v>
       </c>
       <c r="AL43">
-        <v>500</v>
+        <v>110</v>
       </c>
       <c r="AM43">
         <v>580</v>
       </c>
       <c r="AN43">
-        <v>600</v>
+        <v>22</v>
       </c>
       <c r="AO43">
-        <v>600</v>
+        <v>210</v>
       </c>
       <c r="AP43">
+        <v>10</v>
+      </c>
+      <c r="AQ43">
+        <v>10.5</v>
+      </c>
+      <c r="AR43">
+        <v>11.5</v>
+      </c>
+      <c r="AS43">
         <v>9.800000000000001</v>
       </c>
-      <c r="AQ43">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AR43">
-        <v>21</v>
-      </c>
-      <c r="AS43">
-        <v>27</v>
-      </c>
       <c r="AT43">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AU43">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AV43">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AW43">
-        <v>8.6</v>
+        <v>23</v>
       </c>
       <c r="AX43">
         <v>10.5</v>
       </c>
       <c r="AY43">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ43">
-        <v>9.6</v>
+        <v>17.5</v>
       </c>
       <c r="BA43">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="BB43">
-        <v>23</v>
+        <v>12.5</v>
       </c>
       <c r="BC43">
         <v>12.5</v>
       </c>
       <c r="BD43">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BE43">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BF43">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BG43">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BH43" t="s">
         <v>263</v>
@@ -9024,7 +9024,7 @@
         <v>3.6</v>
       </c>
       <c r="K44">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="L44">
         <v>1.5</v>
@@ -9042,7 +9042,7 @@
         <v>1.76</v>
       </c>
       <c r="Q44">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="R44">
         <v>1.28</v>
@@ -9138,7 +9138,7 @@
         <v>20</v>
       </c>
       <c r="AW44">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX44">
         <v>8.6</v>
@@ -9150,7 +9150,7 @@
         <v>19</v>
       </c>
       <c r="BA44">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BB44">
         <v>16</v>
@@ -9191,19 +9191,19 @@
         <v>237</v>
       </c>
       <c r="F45">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="G45">
         <v>2.54</v>
       </c>
       <c r="H45">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="I45">
         <v>4.2</v>
       </c>
       <c r="J45">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="K45">
         <v>2.96</v>
@@ -9239,10 +9239,10 @@
         <v>1.76</v>
       </c>
       <c r="V45">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="W45">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="X45">
         <v>8.4</v>
@@ -9251,7 +9251,7 @@
         <v>11.5</v>
       </c>
       <c r="Z45">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AA45">
         <v>900</v>
@@ -9269,7 +9269,7 @@
         <v>70</v>
       </c>
       <c r="AF45">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AG45">
         <v>13</v>
@@ -9278,10 +9278,10 @@
         <v>23</v>
       </c>
       <c r="AI45">
-        <v>460</v>
+        <v>210</v>
       </c>
       <c r="AJ45">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="AK45">
         <v>36</v>
@@ -9308,7 +9308,7 @@
         <v>20</v>
       </c>
       <c r="AS45">
-        <v>24</v>
+        <v>10.5</v>
       </c>
       <c r="AT45">
         <v>6.2</v>
@@ -9344,13 +9344,13 @@
         <v>32</v>
       </c>
       <c r="BE45">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF45">
-        <v>11.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG45">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BH45" t="s">
         <v>263</v>
@@ -9382,7 +9382,7 @@
         <v>8</v>
       </c>
       <c r="I46">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="J46">
         <v>6.4</v>
@@ -9397,10 +9397,10 @@
         <v>1.01</v>
       </c>
       <c r="N46">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="O46">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="P46">
         <v>3.8</v>
@@ -9415,13 +9415,13 @@
         <v>1.86</v>
       </c>
       <c r="T46">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="U46">
         <v>2.52</v>
       </c>
       <c r="V46">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="W46">
         <v>3.6</v>
@@ -9436,7 +9436,7 @@
         <v>85</v>
       </c>
       <c r="AA46">
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="AB46">
         <v>17.5</v>
@@ -9463,16 +9463,16 @@
         <v>65</v>
       </c>
       <c r="AJ46">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AK46">
         <v>13</v>
       </c>
       <c r="AL46">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AM46">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AN46">
         <v>3.5</v>
@@ -9484,13 +9484,13 @@
         <v>44</v>
       </c>
       <c r="AQ46">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AR46">
+        <v>75</v>
+      </c>
+      <c r="AS46">
         <v>65</v>
-      </c>
-      <c r="AS46">
-        <v>100</v>
       </c>
       <c r="AT46">
         <v>16</v>
@@ -9499,10 +9499,10 @@
         <v>14.5</v>
       </c>
       <c r="AV46">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AW46">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="AX46">
         <v>11.5</v>
@@ -9514,10 +9514,10 @@
         <v>18.5</v>
       </c>
       <c r="BA46">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="BB46">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BC46">
         <v>12</v>
@@ -9526,13 +9526,13 @@
         <v>21</v>
       </c>
       <c r="BE46">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="BF46">
         <v>3.35</v>
       </c>
       <c r="BG46">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="BH46" t="s">
         <v>263</v>
@@ -9555,28 +9555,28 @@
         <v>239</v>
       </c>
       <c r="F47">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="G47">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="H47">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="I47">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="J47">
         <v>3.4</v>
       </c>
       <c r="K47">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L47">
         <v>1.4</v>
       </c>
       <c r="M47">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N47">
         <v>4.1</v>
@@ -9591,7 +9591,7 @@
         <v>1.92</v>
       </c>
       <c r="R47">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S47">
         <v>3.3</v>
@@ -9600,7 +9600,7 @@
         <v>1.71</v>
       </c>
       <c r="U47">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="V47">
         <v>1.51</v>
@@ -9615,7 +9615,7 @@
         <v>12.5</v>
       </c>
       <c r="Z47">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AA47">
         <v>46</v>
@@ -9624,16 +9624,16 @@
         <v>12</v>
       </c>
       <c r="AC47">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD47">
         <v>13</v>
       </c>
       <c r="AE47">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AF47">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AG47">
         <v>12.5</v>
@@ -9645,7 +9645,7 @@
         <v>42</v>
       </c>
       <c r="AJ47">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AK47">
         <v>29</v>
@@ -9654,34 +9654,34 @@
         <v>40</v>
       </c>
       <c r="AM47">
-        <v>85</v>
+        <v>130</v>
       </c>
       <c r="AN47">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO47">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AP47">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AQ47">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR47">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AS47">
         <v>38</v>
       </c>
       <c r="AT47">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AU47">
         <v>7.2</v>
       </c>
       <c r="AV47">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AW47">
         <v>27</v>
@@ -9699,19 +9699,19 @@
         <v>34</v>
       </c>
       <c r="BB47">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="BC47">
         <v>25</v>
       </c>
       <c r="BD47">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BE47">
         <v>65</v>
       </c>
       <c r="BF47">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BG47">
         <v>22</v>
@@ -9737,19 +9737,19 @@
         <v>240</v>
       </c>
       <c r="F48">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="G48">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="H48">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="I48">
+        <v>3.25</v>
+      </c>
+      <c r="J48">
         <v>3.35</v>
-      </c>
-      <c r="J48">
-        <v>3.5</v>
       </c>
       <c r="K48">
         <v>3.65</v>
@@ -9761,7 +9761,7 @@
         <v>1.08</v>
       </c>
       <c r="N48">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="O48">
         <v>1.35</v>
@@ -9779,28 +9779,28 @@
         <v>3.75</v>
       </c>
       <c r="T48">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="U48">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="V48">
         <v>1.44</v>
       </c>
       <c r="W48">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="X48">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Y48">
         <v>12.5</v>
       </c>
       <c r="Z48">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="AA48">
-        <v>130</v>
+        <v>55</v>
       </c>
       <c r="AB48">
         <v>10.5</v>
@@ -9812,7 +9812,7 @@
         <v>14</v>
       </c>
       <c r="AE48">
-        <v>100</v>
+        <v>38</v>
       </c>
       <c r="AF48">
         <v>18.5</v>
@@ -9827,7 +9827,7 @@
         <v>55</v>
       </c>
       <c r="AJ48">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AK48">
         <v>34</v>
@@ -9842,7 +9842,7 @@
         <v>28</v>
       </c>
       <c r="AO48">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AP48">
         <v>10</v>
@@ -9851,10 +9851,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AR48">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AS48">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AT48">
         <v>8.199999999999999</v>
@@ -9878,25 +9878,25 @@
         <v>15.5</v>
       </c>
       <c r="BA48">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="BB48">
         <v>24</v>
       </c>
       <c r="BC48">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="BD48">
         <v>29</v>
       </c>
       <c r="BE48">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF48">
-        <v>20</v>
+        <v>7.2</v>
       </c>
       <c r="BG48">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BH48" t="s">
         <v>263</v>
@@ -9919,22 +9919,22 @@
         <v>241</v>
       </c>
       <c r="F49">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="G49">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="H49">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="I49">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J49">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K49">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L49">
         <v>1.4</v>
@@ -9949,7 +9949,7 @@
         <v>1.31</v>
       </c>
       <c r="P49">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="Q49">
         <v>1.94</v>
@@ -9961,22 +9961,22 @@
         <v>3.35</v>
       </c>
       <c r="T49">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="U49">
         <v>1.76</v>
       </c>
       <c r="V49">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="W49">
-        <v>2.66</v>
+        <v>2.56</v>
       </c>
       <c r="X49">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="Y49">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="Z49">
         <v>420</v>
@@ -10009,7 +10009,7 @@
         <v>700</v>
       </c>
       <c r="AJ49">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AK49">
         <v>18.5</v>
@@ -10021,7 +10021,7 @@
         <v>580</v>
       </c>
       <c r="AN49">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AO49">
         <v>700</v>
@@ -10030,16 +10030,16 @@
         <v>7</v>
       </c>
       <c r="AQ49">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AR49">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AS49">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AT49">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AU49">
         <v>8.4</v>
@@ -10048,7 +10048,7 @@
         <v>21</v>
       </c>
       <c r="AW49">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AX49">
         <v>7</v>
@@ -10060,25 +10060,25 @@
         <v>20</v>
       </c>
       <c r="BA49">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BB49">
         <v>10.5</v>
       </c>
       <c r="BC49">
-        <v>5.4</v>
+        <v>14</v>
       </c>
       <c r="BD49">
-        <v>6.6</v>
+        <v>17.5</v>
       </c>
       <c r="BE49">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BF49">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BG49">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BH49" t="s">
         <v>263</v>
@@ -10101,22 +10101,22 @@
         <v>242</v>
       </c>
       <c r="F50">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="G50">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="H50">
         <v>6.4</v>
       </c>
       <c r="I50">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J50">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="K50">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="L50">
         <v>1.29</v>
@@ -10125,19 +10125,19 @@
         <v>1.03</v>
       </c>
       <c r="N50">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="O50">
         <v>1.18</v>
       </c>
       <c r="P50">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="Q50">
         <v>1.56</v>
       </c>
       <c r="R50">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="S50">
         <v>2.44</v>
@@ -10152,7 +10152,7 @@
         <v>1.16</v>
       </c>
       <c r="W50">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="X50">
         <v>48</v>
@@ -10161,7 +10161,7 @@
         <v>75</v>
       </c>
       <c r="Z50">
-        <v>150</v>
+        <v>420</v>
       </c>
       <c r="AA50">
         <v>190</v>
@@ -10173,7 +10173,7 @@
         <v>13</v>
       </c>
       <c r="AD50">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="AE50">
         <v>480</v>
@@ -10212,13 +10212,13 @@
         <v>14</v>
       </c>
       <c r="AQ50">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AR50">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AS50">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AT50">
         <v>10</v>
@@ -10230,7 +10230,7 @@
         <v>12.5</v>
       </c>
       <c r="AW50">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AX50">
         <v>9.199999999999999</v>
@@ -10242,7 +10242,7 @@
         <v>17.5</v>
       </c>
       <c r="BA50">
-        <v>23</v>
+        <v>9.4</v>
       </c>
       <c r="BB50">
         <v>12</v>
@@ -10254,13 +10254,13 @@
         <v>14.5</v>
       </c>
       <c r="BE50">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BF50">
         <v>4.8</v>
       </c>
       <c r="BG50">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BH50" t="s">
         <v>263</v>
@@ -10286,7 +10286,7 @@
         <v>1.56</v>
       </c>
       <c r="G51">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="H51">
         <v>6</v>
@@ -10307,22 +10307,22 @@
         <v>1.03</v>
       </c>
       <c r="N51">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="O51">
         <v>1.18</v>
       </c>
       <c r="P51">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="Q51">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="R51">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="S51">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="T51">
         <v>1.65</v>
@@ -10331,10 +10331,10 @@
         <v>2.28</v>
       </c>
       <c r="V51">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W51">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="X51">
         <v>48</v>
@@ -10412,7 +10412,7 @@
         <v>18</v>
       </c>
       <c r="AW51">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AX51">
         <v>10</v>
@@ -10436,7 +10436,7 @@
         <v>19.5</v>
       </c>
       <c r="BE51">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BF51">
         <v>5.3</v>
@@ -10474,10 +10474,10 @@
         <v>3.9</v>
       </c>
       <c r="I52">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="J52">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K52">
         <v>3.95</v>
@@ -10489,10 +10489,10 @@
         <v>1.05</v>
       </c>
       <c r="N52">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="O52">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P52">
         <v>2.24</v>
@@ -10510,16 +10510,16 @@
         <v>1.68</v>
       </c>
       <c r="U52">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="V52">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W52">
         <v>1.94</v>
       </c>
       <c r="X52">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Y52">
         <v>18</v>
@@ -10531,7 +10531,7 @@
         <v>75</v>
       </c>
       <c r="AB52">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC52">
         <v>9.4</v>
@@ -10573,7 +10573,7 @@
         <v>38</v>
       </c>
       <c r="AP52">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AQ52">
         <v>15</v>
@@ -10582,7 +10582,7 @@
         <v>14.5</v>
       </c>
       <c r="AS52">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AT52">
         <v>9.6</v>
@@ -10594,7 +10594,7 @@
         <v>14</v>
       </c>
       <c r="AW52">
-        <v>9.199999999999999</v>
+        <v>19.5</v>
       </c>
       <c r="AX52">
         <v>12</v>
@@ -10606,7 +10606,7 @@
         <v>13.5</v>
       </c>
       <c r="BA52">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="BB52">
         <v>20</v>
@@ -10624,7 +10624,7 @@
         <v>10</v>
       </c>
       <c r="BG52">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH52" t="s">
         <v>263</v>
@@ -10647,7 +10647,7 @@
         <v>245</v>
       </c>
       <c r="F53">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="G53">
         <v>1.51</v>
@@ -10656,7 +10656,7 @@
         <v>6.8</v>
       </c>
       <c r="I53">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="J53">
         <v>5.1</v>
@@ -10677,31 +10677,31 @@
         <v>1.17</v>
       </c>
       <c r="P53">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="Q53">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="R53">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="S53">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="T53">
         <v>1.7</v>
       </c>
       <c r="U53">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="V53">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="W53">
         <v>2.96</v>
       </c>
       <c r="X53">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Y53">
         <v>34</v>
@@ -10710,7 +10710,7 @@
         <v>65</v>
       </c>
       <c r="AA53">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AB53">
         <v>12.5</v>
@@ -10719,19 +10719,19 @@
         <v>12</v>
       </c>
       <c r="AD53">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AE53">
         <v>80</v>
       </c>
       <c r="AF53">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG53">
         <v>10</v>
       </c>
       <c r="AH53">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AI53">
         <v>65</v>
@@ -10740,16 +10740,16 @@
         <v>14.5</v>
       </c>
       <c r="AK53">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AL53">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AM53">
         <v>75</v>
       </c>
       <c r="AN53">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="AO53">
         <v>75</v>
@@ -10758,55 +10758,55 @@
         <v>25</v>
       </c>
       <c r="AQ53">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AR53">
         <v>50</v>
       </c>
       <c r="AS53">
-        <v>14.5</v>
+        <v>19.5</v>
       </c>
       <c r="AT53">
         <v>11</v>
       </c>
       <c r="AU53">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AV53">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AW53">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AX53">
         <v>10</v>
       </c>
       <c r="AY53">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ53">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BA53">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BB53">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BC53">
         <v>13</v>
       </c>
       <c r="BD53">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BE53">
+        <v>38</v>
+      </c>
+      <c r="BF53">
+        <v>4.8</v>
+      </c>
+      <c r="BG53">
         <v>60</v>
-      </c>
-      <c r="BF53">
-        <v>5</v>
-      </c>
-      <c r="BG53">
-        <v>70</v>
       </c>
       <c r="BH53" t="s">
         <v>263</v>
@@ -10829,19 +10829,19 @@
         <v>246</v>
       </c>
       <c r="F54">
+        <v>1.62</v>
+      </c>
+      <c r="G54">
         <v>1.63</v>
       </c>
-      <c r="G54">
-        <v>1.64</v>
-      </c>
       <c r="H54">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="I54">
         <v>6.6</v>
       </c>
       <c r="J54">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K54">
         <v>4.4</v>
@@ -10850,52 +10850,52 @@
         <v>1.41</v>
       </c>
       <c r="M54">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N54">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="O54">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P54">
         <v>2.02</v>
       </c>
       <c r="Q54">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="R54">
         <v>1.38</v>
       </c>
       <c r="S54">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="T54">
         <v>2.02</v>
       </c>
       <c r="U54">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="V54">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W54">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="X54">
         <v>15.5</v>
       </c>
       <c r="Y54">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Z54">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AA54">
         <v>190</v>
       </c>
       <c r="AB54">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AC54">
         <v>9.199999999999999</v>
@@ -10907,10 +10907,10 @@
         <v>95</v>
       </c>
       <c r="AF54">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AG54">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH54">
         <v>23</v>
@@ -10919,19 +10919,19 @@
         <v>90</v>
       </c>
       <c r="AJ54">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AK54">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AL54">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AM54">
         <v>130</v>
       </c>
       <c r="AN54">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AO54">
         <v>120</v>
@@ -10940,16 +10940,16 @@
         <v>14</v>
       </c>
       <c r="AQ54">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AR54">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AS54">
         <v>44</v>
       </c>
       <c r="AT54">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AU54">
         <v>8.800000000000001</v>
@@ -10958,13 +10958,13 @@
         <v>22</v>
       </c>
       <c r="AW54">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="AX54">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY54">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ54">
         <v>21</v>
@@ -10976,19 +10976,19 @@
         <v>14</v>
       </c>
       <c r="BC54">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BD54">
         <v>34</v>
       </c>
       <c r="BE54">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="BF54">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BG54">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="BH54" t="s">
         <v>263</v>
@@ -11011,16 +11011,16 @@
         <v>247</v>
       </c>
       <c r="F55">
+        <v>2.58</v>
+      </c>
+      <c r="G55">
         <v>2.62</v>
-      </c>
-      <c r="G55">
-        <v>2.64</v>
       </c>
       <c r="H55">
         <v>2.98</v>
       </c>
       <c r="I55">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="J55">
         <v>3.5</v>
@@ -11029,19 +11029,19 @@
         <v>3.55</v>
       </c>
       <c r="L55">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="M55">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N55">
         <v>3.75</v>
       </c>
       <c r="O55">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="P55">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="Q55">
         <v>2.04</v>
@@ -11059,7 +11059,7 @@
         <v>2.2</v>
       </c>
       <c r="V55">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W55">
         <v>1.61</v>
@@ -11068,13 +11068,13 @@
         <v>14</v>
       </c>
       <c r="Y55">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Z55">
         <v>19</v>
       </c>
       <c r="AA55">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AB55">
         <v>10.5</v>
@@ -11083,7 +11083,7 @@
         <v>7.6</v>
       </c>
       <c r="AD55">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE55">
         <v>34</v>
@@ -11098,7 +11098,7 @@
         <v>17</v>
       </c>
       <c r="AI55">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ55">
         <v>38</v>
@@ -11110,7 +11110,7 @@
         <v>42</v>
       </c>
       <c r="AM55">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AN55">
         <v>24</v>
@@ -11128,7 +11128,7 @@
         <v>18</v>
       </c>
       <c r="AS55">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AT55">
         <v>9.800000000000001</v>
@@ -11146,13 +11146,13 @@
         <v>15.5</v>
       </c>
       <c r="AY55">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ55">
         <v>16</v>
       </c>
       <c r="BA55">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BB55">
         <v>34</v>
@@ -11193,22 +11193,22 @@
         <v>248</v>
       </c>
       <c r="F56">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="G56">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="H56">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="I56">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="J56">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="K56">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="L56">
         <v>1.33</v>
@@ -11217,7 +11217,7 @@
         <v>1.04</v>
       </c>
       <c r="N56">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="O56">
         <v>1.22</v>
@@ -11229,22 +11229,22 @@
         <v>1.68</v>
       </c>
       <c r="R56">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="S56">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="T56">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="U56">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="V56">
-        <v>2.84</v>
+        <v>2.92</v>
       </c>
       <c r="W56">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="X56">
         <v>22</v>
@@ -11259,10 +11259,10 @@
         <v>14</v>
       </c>
       <c r="AB56">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AC56">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AD56">
         <v>9.6</v>
@@ -11274,28 +11274,28 @@
         <v>65</v>
       </c>
       <c r="AG56">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AH56">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AI56">
         <v>28</v>
       </c>
       <c r="AJ56">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="AK56">
         <v>85</v>
       </c>
       <c r="AL56">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AM56">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AN56">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="AO56">
         <v>6.6</v>
@@ -11304,19 +11304,19 @@
         <v>21</v>
       </c>
       <c r="AQ56">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AR56">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AS56">
         <v>13.5</v>
       </c>
       <c r="AT56">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AU56">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AV56">
         <v>9.4</v>
@@ -11328,16 +11328,16 @@
         <v>55</v>
       </c>
       <c r="AY56">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AZ56">
         <v>19</v>
       </c>
       <c r="BA56">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BB56">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="BC56">
         <v>75</v>
@@ -11349,7 +11349,7 @@
         <v>85</v>
       </c>
       <c r="BF56">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="BG56">
         <v>6.2</v>
@@ -11378,10 +11378,10 @@
         <v>1.29</v>
       </c>
       <c r="G57">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="H57">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="I57">
         <v>13</v>
@@ -11393,49 +11393,49 @@
         <v>6.8</v>
       </c>
       <c r="L57">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="M57">
         <v>1.03</v>
       </c>
       <c r="N57">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="O57">
         <v>1.16</v>
       </c>
       <c r="P57">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="Q57">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="R57">
         <v>1.74</v>
       </c>
       <c r="S57">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="T57">
         <v>1.96</v>
       </c>
       <c r="U57">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="V57">
         <v>1.08</v>
       </c>
       <c r="W57">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="X57">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Y57">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="Z57">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AA57">
         <v>490</v>
@@ -11447,7 +11447,7 @@
         <v>15</v>
       </c>
       <c r="AD57">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AE57">
         <v>180</v>
@@ -11462,7 +11462,7 @@
         <v>29</v>
       </c>
       <c r="AI57">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AJ57">
         <v>11</v>
@@ -11480,19 +11480,19 @@
         <v>4.1</v>
       </c>
       <c r="AO57">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="AP57">
         <v>32</v>
       </c>
       <c r="AQ57">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AR57">
-        <v>17.5</v>
+        <v>75</v>
       </c>
       <c r="AS57">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AT57">
         <v>10</v>
@@ -11504,7 +11504,7 @@
         <v>36</v>
       </c>
       <c r="AW57">
-        <v>17.5</v>
+        <v>42</v>
       </c>
       <c r="AX57">
         <v>8.4</v>
@@ -11516,10 +11516,10 @@
         <v>24</v>
       </c>
       <c r="BA57">
-        <v>18</v>
+        <v>100</v>
       </c>
       <c r="BB57">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BC57">
         <v>12</v>
@@ -11528,13 +11528,13 @@
         <v>28</v>
       </c>
       <c r="BE57">
-        <v>29</v>
+        <v>80</v>
       </c>
       <c r="BF57">
         <v>3.75</v>
       </c>
       <c r="BG57">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BH57" t="s">
         <v>263</v>
@@ -11563,19 +11563,19 @@
         <v>2.54</v>
       </c>
       <c r="H58">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="I58">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="J58">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="K58">
         <v>3.15</v>
       </c>
       <c r="L58">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="M58">
         <v>1.15</v>
@@ -11587,10 +11587,10 @@
         <v>1.67</v>
       </c>
       <c r="P58">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="Q58">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="R58">
         <v>1.15</v>
@@ -11599,10 +11599,10 @@
         <v>7.2</v>
       </c>
       <c r="T58">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="U58">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="V58">
         <v>1.37</v>
@@ -11611,7 +11611,7 @@
         <v>1.64</v>
       </c>
       <c r="X58">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="Y58">
         <v>9.199999999999999</v>
@@ -11662,7 +11662,7 @@
         <v>50</v>
       </c>
       <c r="AO58">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AP58">
         <v>6.8</v>
@@ -11674,7 +11674,7 @@
         <v>20</v>
       </c>
       <c r="AS58">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AT58">
         <v>6.2</v>
@@ -11686,7 +11686,7 @@
         <v>15</v>
       </c>
       <c r="AW58">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="AX58">
         <v>11.5</v>
@@ -11695,7 +11695,7 @@
         <v>12</v>
       </c>
       <c r="AZ58">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BA58">
         <v>70</v>
@@ -11707,7 +11707,7 @@
         <v>34</v>
       </c>
       <c r="BD58">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="BE58">
         <v>110</v>
@@ -11716,7 +11716,7 @@
         <v>36</v>
       </c>
       <c r="BG58">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="BH58" t="s">
         <v>263</v>
@@ -11739,16 +11739,16 @@
         <v>251</v>
       </c>
       <c r="F59">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="G59">
         <v>1.53</v>
       </c>
       <c r="H59">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="I59">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="J59">
         <v>4.4</v>
@@ -11766,34 +11766,34 @@
         <v>4.3</v>
       </c>
       <c r="O59">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P59">
         <v>2.12</v>
       </c>
       <c r="Q59">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="R59">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S59">
         <v>3.05</v>
       </c>
       <c r="T59">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="U59">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="V59">
         <v>1.13</v>
       </c>
       <c r="W59">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="X59">
-        <v>26</v>
+        <v>18.5</v>
       </c>
       <c r="Y59">
         <v>65</v>
@@ -11811,28 +11811,28 @@
         <v>11</v>
       </c>
       <c r="AD59">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AE59">
         <v>480</v>
       </c>
       <c r="AF59">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="AG59">
         <v>10.5</v>
       </c>
       <c r="AH59">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AI59">
         <v>460</v>
       </c>
       <c r="AJ59">
-        <v>180</v>
+        <v>13.5</v>
       </c>
       <c r="AK59">
-        <v>32</v>
+        <v>16.5</v>
       </c>
       <c r="AL59">
         <v>44</v>
@@ -11844,43 +11844,43 @@
         <v>7.6</v>
       </c>
       <c r="AO59">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="AP59">
-        <v>5.4</v>
+        <v>8</v>
       </c>
       <c r="AQ59">
         <v>11.5</v>
       </c>
       <c r="AR59">
-        <v>6.4</v>
+        <v>11</v>
       </c>
       <c r="AS59">
-        <v>6.4</v>
+        <v>11.5</v>
       </c>
       <c r="AT59">
-        <v>5.1</v>
+        <v>7.4</v>
       </c>
       <c r="AU59">
-        <v>6.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV59">
-        <v>5.4</v>
+        <v>8.6</v>
       </c>
       <c r="AW59">
-        <v>5.8</v>
+        <v>11</v>
       </c>
       <c r="AX59">
-        <v>4.7</v>
+        <v>7.8</v>
       </c>
       <c r="AY59">
-        <v>4.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ59">
-        <v>5.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BA59">
-        <v>5.8</v>
+        <v>11</v>
       </c>
       <c r="BB59">
         <v>6.4</v>
@@ -11892,13 +11892,13 @@
         <v>27</v>
       </c>
       <c r="BE59">
-        <v>5.9</v>
+        <v>11</v>
       </c>
       <c r="BF59">
-        <v>3.7</v>
+        <v>4.7</v>
       </c>
       <c r="BG59">
-        <v>5.9</v>
+        <v>11.5</v>
       </c>
       <c r="BH59" t="s">
         <v>263</v>
@@ -11921,34 +11921,34 @@
         <v>252</v>
       </c>
       <c r="F60">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="G60">
         <v>1.88</v>
       </c>
       <c r="H60">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="I60">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="J60">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K60">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L60">
         <v>1.48</v>
       </c>
       <c r="M60">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N60">
         <v>3.4</v>
       </c>
       <c r="O60">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P60">
         <v>1.8</v>
@@ -11963,10 +11963,10 @@
         <v>4.1</v>
       </c>
       <c r="T60">
-        <v>1.9</v>
+        <v>1.99</v>
       </c>
       <c r="U60">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="V60">
         <v>1.22</v>
@@ -11999,7 +11999,7 @@
         <v>700</v>
       </c>
       <c r="AF60">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="AG60">
         <v>10.5</v>
@@ -12023,64 +12023,64 @@
         <v>580</v>
       </c>
       <c r="AN60">
-        <v>22</v>
+        <v>85</v>
       </c>
       <c r="AO60">
         <v>700</v>
       </c>
       <c r="AP60">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="AQ60">
         <v>7.6</v>
       </c>
       <c r="AR60">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="AS60">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="AT60">
         <v>6.4</v>
       </c>
       <c r="AU60">
-        <v>4.6</v>
+        <v>7.2</v>
       </c>
       <c r="AV60">
-        <v>7</v>
+        <v>11.5</v>
       </c>
       <c r="AW60">
-        <v>4.3</v>
+        <v>12</v>
       </c>
       <c r="AX60">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="AY60">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AZ60">
-        <v>7</v>
+        <v>18.5</v>
       </c>
       <c r="BA60">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="BB60">
         <v>9</v>
       </c>
       <c r="BC60">
-        <v>7</v>
+        <v>11.5</v>
       </c>
       <c r="BD60">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="BE60">
-        <v>9.800000000000001</v>
+        <v>3.55</v>
       </c>
       <c r="BF60">
         <v>12</v>
       </c>
       <c r="BG60">
-        <v>9.6</v>
+        <v>12.5</v>
       </c>
       <c r="BH60" t="s">
         <v>263</v>
@@ -12106,10 +12106,10 @@
         <v>2.14</v>
       </c>
       <c r="G61">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="H61">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="I61">
         <v>3.8</v>
@@ -12121,40 +12121,40 @@
         <v>3.85</v>
       </c>
       <c r="L61">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="M61">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N61">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="O61">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P61">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="Q61">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="R61">
         <v>1.37</v>
       </c>
       <c r="S61">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="T61">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="U61">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="V61">
         <v>1.37</v>
       </c>
       <c r="W61">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="X61">
         <v>15.5</v>
@@ -12166,7 +12166,7 @@
         <v>26</v>
       </c>
       <c r="AA61">
-        <v>160</v>
+        <v>280</v>
       </c>
       <c r="AB61">
         <v>10.5</v>
@@ -12193,7 +12193,7 @@
         <v>120</v>
       </c>
       <c r="AJ61">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AK61">
         <v>24</v>
@@ -12208,61 +12208,61 @@
         <v>17</v>
       </c>
       <c r="AO61">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AP61">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AQ61">
         <v>7</v>
       </c>
       <c r="AR61">
-        <v>8.6</v>
+        <v>19.5</v>
       </c>
       <c r="AS61">
         <v>10.5</v>
       </c>
       <c r="AT61">
-        <v>5.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU61">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AV61">
-        <v>7.4</v>
+        <v>13.5</v>
       </c>
       <c r="AW61">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="AX61">
         <v>7.2</v>
       </c>
       <c r="AY61">
-        <v>7</v>
+        <v>8.6</v>
       </c>
       <c r="AZ61">
-        <v>7.6</v>
+        <v>14.5</v>
       </c>
       <c r="BA61">
-        <v>10.5</v>
+        <v>38</v>
       </c>
       <c r="BB61">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="BC61">
         <v>20</v>
       </c>
       <c r="BD61">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="BE61">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BF61">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BG61">
-        <v>9.800000000000001</v>
+        <v>30</v>
       </c>
       <c r="BH61" t="s">
         <v>263</v>
@@ -12288,13 +12288,13 @@
         <v>1.69</v>
       </c>
       <c r="G62">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="H62">
         <v>6.2</v>
       </c>
       <c r="I62">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="J62">
         <v>3.85</v>
@@ -12309,7 +12309,7 @@
         <v>1.09</v>
       </c>
       <c r="N62">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="O62">
         <v>1.42</v>
@@ -12318,7 +12318,7 @@
         <v>1.76</v>
       </c>
       <c r="Q62">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="R62">
         <v>1.28</v>
@@ -12330,13 +12330,13 @@
         <v>2.1</v>
       </c>
       <c r="U62">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="V62">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W62">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="X62">
         <v>12.5</v>
@@ -12375,7 +12375,7 @@
         <v>450</v>
       </c>
       <c r="AJ62">
-        <v>20</v>
+        <v>180</v>
       </c>
       <c r="AK62">
         <v>65</v>
@@ -12399,10 +12399,10 @@
         <v>13.5</v>
       </c>
       <c r="AR62">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AS62">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AT62">
         <v>6.4</v>
@@ -12411,10 +12411,10 @@
         <v>7.4</v>
       </c>
       <c r="AV62">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AW62">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="AX62">
         <v>8</v>
@@ -12435,7 +12435,7 @@
         <v>17</v>
       </c>
       <c r="BD62">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BE62">
         <v>70</v>
@@ -12467,67 +12467,67 @@
         <v>255</v>
       </c>
       <c r="F63">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="G63">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="H63">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="I63">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="J63">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="K63">
         <v>3.7</v>
       </c>
       <c r="L63">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="M63">
         <v>1.1</v>
       </c>
       <c r="N63">
-        <v>2.98</v>
+        <v>2.88</v>
       </c>
       <c r="O63">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="P63">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="Q63">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="R63">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="S63">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="T63">
-        <v>2.16</v>
+        <v>2.06</v>
       </c>
       <c r="U63">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="V63">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="W63">
-        <v>2.24</v>
+        <v>2.08</v>
       </c>
       <c r="X63">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="Y63">
-        <v>19.5</v>
+        <v>15</v>
       </c>
       <c r="Z63">
-        <v>120</v>
+        <v>220</v>
       </c>
       <c r="AA63">
         <v>900</v>
@@ -12536,97 +12536,97 @@
         <v>6.6</v>
       </c>
       <c r="AC63">
-        <v>10</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD63">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="AE63">
         <v>700</v>
       </c>
       <c r="AF63">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AG63">
         <v>10</v>
       </c>
       <c r="AH63">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="AI63">
         <v>700</v>
       </c>
       <c r="AJ63">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="AK63">
-        <v>27</v>
+        <v>70</v>
       </c>
       <c r="AL63">
-        <v>65</v>
+        <v>160</v>
       </c>
       <c r="AM63">
         <v>700</v>
       </c>
       <c r="AN63">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AO63">
         <v>700</v>
       </c>
       <c r="AP63">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ63">
+        <v>12</v>
+      </c>
+      <c r="AR63">
+        <v>32</v>
+      </c>
+      <c r="AS63">
+        <v>11</v>
+      </c>
+      <c r="AT63">
+        <v>6</v>
+      </c>
+      <c r="AU63">
+        <v>7</v>
+      </c>
+      <c r="AV63">
+        <v>18.5</v>
+      </c>
+      <c r="AW63">
+        <v>13</v>
+      </c>
+      <c r="AX63">
+        <v>8.4</v>
+      </c>
+      <c r="AY63">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ63">
+        <v>21</v>
+      </c>
+      <c r="BA63">
         <v>11.5</v>
       </c>
-      <c r="AR63">
-        <v>34</v>
-      </c>
-      <c r="AS63">
-        <v>7.6</v>
-      </c>
-      <c r="AT63">
-        <v>5.7</v>
-      </c>
-      <c r="AU63">
-        <v>7.4</v>
-      </c>
-      <c r="AV63">
-        <v>18</v>
-      </c>
-      <c r="AW63">
-        <v>7.6</v>
-      </c>
-      <c r="AX63">
-        <v>7.8</v>
-      </c>
-      <c r="AY63">
-        <v>8.6</v>
-      </c>
-      <c r="AZ63">
+      <c r="BB63">
         <v>18.5</v>
       </c>
-      <c r="BA63">
-        <v>7.4</v>
-      </c>
-      <c r="BB63">
-        <v>13.5</v>
-      </c>
       <c r="BC63">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="BD63">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="BE63">
-        <v>7.6</v>
+        <v>14</v>
       </c>
       <c r="BF63">
-        <v>12</v>
+        <v>16.5</v>
       </c>
       <c r="BG63">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="BH63" t="s">
         <v>263</v>
@@ -12679,22 +12679,22 @@
         <v>1.49</v>
       </c>
       <c r="P64">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="Q64">
         <v>2.52</v>
       </c>
       <c r="R64">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S64">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="T64">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="U64">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="V64">
         <v>1.25</v>
@@ -12718,7 +12718,7 @@
         <v>6.8</v>
       </c>
       <c r="AC64">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD64">
         <v>42</v>
@@ -12733,7 +12733,7 @@
         <v>11</v>
       </c>
       <c r="AH64">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AI64">
         <v>450</v>
@@ -12766,7 +12766,7 @@
         <v>14.5</v>
       </c>
       <c r="AS64">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AT64">
         <v>6</v>
@@ -12778,7 +12778,7 @@
         <v>18</v>
       </c>
       <c r="AW64">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AX64">
         <v>9.4</v>
@@ -12790,7 +12790,7 @@
         <v>20</v>
       </c>
       <c r="BA64">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BB64">
         <v>20</v>
@@ -12799,16 +12799,16 @@
         <v>13</v>
       </c>
       <c r="BD64">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE64">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF64">
         <v>19</v>
       </c>
       <c r="BG64">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BH64" t="s">
         <v>263</v>
@@ -12831,16 +12831,16 @@
         <v>257</v>
       </c>
       <c r="F65">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="G65">
         <v>2.46</v>
       </c>
       <c r="H65">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="I65">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="J65">
         <v>2.98</v>
@@ -12891,7 +12891,7 @@
         <v>10.5</v>
       </c>
       <c r="Z65">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AA65">
         <v>900</v>
@@ -12942,7 +12942,7 @@
         <v>4.7</v>
       </c>
       <c r="AQ65">
-        <v>5.4</v>
+        <v>8.6</v>
       </c>
       <c r="AR65">
         <v>10.5</v>
@@ -12951,16 +12951,16 @@
         <v>10</v>
       </c>
       <c r="AT65">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AU65">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AV65">
-        <v>7.2</v>
+        <v>14.5</v>
       </c>
       <c r="AW65">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX65">
         <v>6.2</v>
@@ -12969,7 +12969,7 @@
         <v>10.5</v>
       </c>
       <c r="AZ65">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BA65">
         <v>10</v>
@@ -12978,16 +12978,16 @@
         <v>14.5</v>
       </c>
       <c r="BC65">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="BD65">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE65">
         <v>10.5</v>
       </c>
       <c r="BF65">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG65">
         <v>10</v>
@@ -13046,7 +13046,7 @@
         <v>1.49</v>
       </c>
       <c r="Q66">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="R66">
         <v>1.17</v>
@@ -13198,19 +13198,19 @@
         <v>1.89</v>
       </c>
       <c r="G67">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="H67">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="I67">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="J67">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="K67">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="L67">
         <v>1.01</v>
@@ -13219,22 +13219,22 @@
         <v>1.02</v>
       </c>
       <c r="N67">
-        <v>5.5</v>
+        <v>2.56</v>
       </c>
       <c r="O67">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="P67">
-        <v>2.68</v>
+        <v>1.61</v>
       </c>
       <c r="Q67">
         <v>1.52</v>
       </c>
       <c r="R67">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="S67">
-        <v>2.18</v>
+        <v>1.52</v>
       </c>
       <c r="T67">
         <v>1.11</v>
@@ -13246,7 +13246,7 @@
         <v>1.33</v>
       </c>
       <c r="W67">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="X67">
         <v>1000</v>
@@ -13377,10 +13377,10 @@
         <v>260</v>
       </c>
       <c r="F68">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="G68">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="H68">
         <v>7.4</v>
@@ -13410,7 +13410,7 @@
         <v>1.69</v>
       </c>
       <c r="Q68">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="R68">
         <v>1.25</v>
@@ -13419,16 +13419,16 @@
         <v>4.3</v>
       </c>
       <c r="T68">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="U68">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="V68">
         <v>1.11</v>
       </c>
       <c r="W68">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="X68">
         <v>970</v>
@@ -13437,7 +13437,7 @@
         <v>950</v>
       </c>
       <c r="Z68">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AA68">
         <v>1000</v>
@@ -13446,7 +13446,7 @@
         <v>7.4</v>
       </c>
       <c r="AC68">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="AD68">
         <v>950</v>
@@ -13458,7 +13458,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AG68">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="AH68">
         <v>950</v>
@@ -13485,10 +13485,10 @@
         <v>1000</v>
       </c>
       <c r="AP68">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AQ68">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="AR68">
         <v>4.2</v>
@@ -13497,7 +13497,7 @@
         <v>4.3</v>
       </c>
       <c r="AT68">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AU68">
         <v>7.2</v>
@@ -13524,7 +13524,7 @@
         <v>10</v>
       </c>
       <c r="BC68">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="BD68">
         <v>4.1</v>
@@ -13533,7 +13533,7 @@
         <v>4.3</v>
       </c>
       <c r="BF68">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG68">
         <v>4.3</v>
@@ -13595,7 +13595,7 @@
         <v>3.1</v>
       </c>
       <c r="R69">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="S69">
         <v>6.8</v>
@@ -13744,7 +13744,7 @@
         <v>1.91</v>
       </c>
       <c r="G70">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="H70">
         <v>4.5</v>
@@ -13762,7 +13762,7 @@
         <v>1.52</v>
       </c>
       <c r="M70">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N70">
         <v>3.1</v>
@@ -13771,7 +13771,7 @@
         <v>1.45</v>
       </c>
       <c r="P70">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="Q70">
         <v>2.3</v>
@@ -13780,7 +13780,7 @@
         <v>1.26</v>
       </c>
       <c r="S70">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="T70">
         <v>1.89</v>
@@ -13792,7 +13792,7 @@
         <v>1.26</v>
       </c>
       <c r="W70">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="X70">
         <v>970</v>
@@ -13801,7 +13801,7 @@
         <v>970</v>
       </c>
       <c r="Z70">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AA70">
         <v>140</v>
@@ -13831,10 +13831,10 @@
         <v>95</v>
       </c>
       <c r="AJ70">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK70">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AL70">
         <v>55</v>
@@ -13843,7 +13843,7 @@
         <v>1000</v>
       </c>
       <c r="AN70">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO70">
         <v>120</v>
@@ -13852,55 +13852,55 @@
         <v>8.4</v>
       </c>
       <c r="AQ70">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AR70">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AS70">
-        <v>3.5</v>
+        <v>2.76</v>
       </c>
       <c r="AT70">
         <v>6.4</v>
       </c>
       <c r="AU70">
+        <v>4.1</v>
+      </c>
+      <c r="AV70">
+        <v>5.1</v>
+      </c>
+      <c r="AW70">
+        <v>2.72</v>
+      </c>
+      <c r="AX70">
         <v>4.3</v>
-      </c>
-      <c r="AV70">
-        <v>5</v>
-      </c>
-      <c r="AW70">
-        <v>3.45</v>
-      </c>
-      <c r="AX70">
-        <v>4.1</v>
       </c>
       <c r="AY70">
         <v>7.8</v>
       </c>
       <c r="AZ70">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BA70">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="BB70">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BC70">
         <v>5.3</v>
       </c>
       <c r="BD70">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BE70">
-        <v>3.55</v>
+        <v>2.76</v>
       </c>
       <c r="BF70">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BG70">
-        <v>3.5</v>
+        <v>2.74</v>
       </c>
       <c r="BH70" t="s">
         <v>263</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH18"/>
+  <dimension ref="A1:BH13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -733,7 +733,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Italian Serie A</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -743,36 +743,36 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Union Magdalena</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Barranquilla</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -787,147 +787,147 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BG2" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-04 17:51:34</t>
+          <t>2026-05-04 20:01:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>English Premier League</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -937,191 +937,191 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Man City</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.36</v>
+        <v>2.2</v>
       </c>
       <c r="G3" t="n">
-        <v>1.37</v>
+        <v>2.22</v>
       </c>
       <c r="H3" t="n">
-        <v>25</v>
+        <v>7.4</v>
       </c>
       <c r="I3" t="n">
-        <v>27</v>
+        <v>7.8</v>
       </c>
       <c r="J3" t="n">
-        <v>4.4</v>
+        <v>2.38</v>
       </c>
       <c r="K3" t="n">
-        <v>4.5</v>
+        <v>2.42</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V3" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="W3" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="X3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>80</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>80</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>28</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>180</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>48</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>140</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>150</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP3" t="n">
         <v>3.2</v>
       </c>
-      <c r="X3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>390</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>1000</v>
-      </c>
       <c r="AQ3" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AS3" t="n">
-        <v>1000</v>
+        <v>310</v>
       </c>
       <c r="AT3" t="n">
-        <v>1000</v>
+        <v>3.65</v>
       </c>
       <c r="AU3" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AV3" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AW3" t="n">
-        <v>1000</v>
+        <v>440</v>
       </c>
       <c r="AX3" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AY3" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="BA3" t="n">
-        <v>1000</v>
+        <v>420</v>
       </c>
       <c r="BB3" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BC3" t="n">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.59</v>
+        <v>360</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.3</v>
+        <v>510</v>
       </c>
       <c r="BF3" t="n">
-        <v>9.199999999999999</v>
+        <v>85</v>
       </c>
       <c r="BG3" t="n">
-        <v>27</v>
+        <v>290</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-04 17:51:34</t>
+          <t>2026-05-04 20:01:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Spanish La Liga</t>
+          <t>Chilean Primera B</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1131,36 +1131,36 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Union San Felipe</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.16</v>
+        <v>1.06</v>
       </c>
       <c r="H4" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="I4" t="n">
-        <v>130</v>
+        <v>270</v>
       </c>
       <c r="J4" t="n">
-        <v>8.199999999999999</v>
+        <v>23</v>
       </c>
       <c r="K4" t="n">
-        <v>8.4</v>
+        <v>27</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1169,34 +1169,34 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="Q4" t="n">
-        <v>23</v>
+        <v>1.28</v>
       </c>
       <c r="R4" t="n">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="S4" t="n">
-        <v>130</v>
+        <v>2.34</v>
       </c>
       <c r="T4" t="n">
-        <v>6.6</v>
+        <v>2.46</v>
       </c>
       <c r="U4" t="n">
-        <v>1.14</v>
+        <v>1.61</v>
       </c>
       <c r="V4" t="n">
         <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="X4" t="n">
         <v>1000</v>
@@ -1211,43 +1211,43 @@
         <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.39</v>
+        <v>1000</v>
       </c>
       <c r="AC4" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AD4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>280</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM4" t="n">
         <v>220</v>
       </c>
-      <c r="AE4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>140</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>180</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>980</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1000</v>
-      </c>
       <c r="AN4" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="AO4" t="n">
         <v>1000</v>
@@ -1265,57 +1265,57 @@
         <v>1000</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.37</v>
+        <v>14.5</v>
       </c>
       <c r="AU4" t="n">
-        <v>8.800000000000001</v>
+        <v>14.5</v>
       </c>
       <c r="AV4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>26</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>100</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>32</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>120</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BG4" t="n">
         <v>110</v>
       </c>
-      <c r="AW4" t="n">
-        <v>140</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>46</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>270</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>110</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>80</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>270</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>110</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>110</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>75</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>50</v>
-      </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-04 17:51:34</t>
+          <t>2026-05-04 20:01:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Portuguese Primeira Liga</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1325,191 +1325,191 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>19:15:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Sporting Lisbon</t>
+          <t>Velez Sarsfield</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Guimaraes</t>
+          <t>Newells</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="G5" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="H5" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="I5" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="J5" t="n">
-        <v>150</v>
+        <v>2.72</v>
       </c>
       <c r="K5" t="n">
-        <v>1000</v>
+        <v>2.76</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="T5" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="U5" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="V5" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="W5" t="n">
-        <v>500</v>
+        <v>1.89</v>
       </c>
       <c r="X5" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="Y5" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Z5" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA5" t="n">
-        <v>1000</v>
+        <v>410</v>
       </c>
       <c r="AB5" t="n">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="AC5" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AE5" t="n">
-        <v>1000</v>
+        <v>430</v>
       </c>
       <c r="AF5" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AG5" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AH5" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AI5" t="n">
         <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AK5" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AL5" t="n">
-        <v>1000</v>
+        <v>280</v>
       </c>
       <c r="AM5" t="n">
         <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.01</v>
+        <v>95</v>
       </c>
       <c r="AO5" t="n">
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AR5" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AS5" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AT5" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="AU5" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AV5" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AW5" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AX5" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AY5" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BA5" t="n">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="BB5" t="n">
-        <v>100</v>
+        <v>28</v>
       </c>
       <c r="BC5" t="n">
-        <v>100</v>
+        <v>48</v>
       </c>
       <c r="BD5" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="BE5" t="n">
-        <v>100</v>
+        <v>17</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.01</v>
+        <v>50</v>
       </c>
       <c r="BG5" t="n">
-        <v>100</v>
+        <v>310</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-04 17:51:34</t>
+          <t>2026-05-04 20:01:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1519,36 +1519,36 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>19:30:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Gimnasia Mendoza</t>
+          <t>Penarol</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Defensa y Justicia</t>
+          <t>Defensor Sporting</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.45</v>
+        <v>1.3</v>
       </c>
       <c r="G6" t="n">
-        <v>3.55</v>
+        <v>1.31</v>
       </c>
       <c r="H6" t="n">
-        <v>3.25</v>
+        <v>14.5</v>
       </c>
       <c r="I6" t="n">
-        <v>3.4</v>
+        <v>16.5</v>
       </c>
       <c r="J6" t="n">
-        <v>2.4</v>
+        <v>5.8</v>
       </c>
       <c r="K6" t="n">
-        <v>2.46</v>
+        <v>6.2</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1557,34 +1557,34 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="P6" t="n">
-        <v>3.65</v>
+        <v>2.28</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.36</v>
+        <v>1.74</v>
       </c>
       <c r="R6" t="n">
-        <v>1.57</v>
+        <v>1.39</v>
       </c>
       <c r="S6" t="n">
-        <v>2.66</v>
+        <v>3.5</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="V6" t="n">
-        <v>1.41</v>
+        <v>1.06</v>
       </c>
       <c r="W6" t="n">
-        <v>1.39</v>
+        <v>4.2</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
@@ -1599,111 +1599,111 @@
         <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.95</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD6" t="n">
-        <v>5.7</v>
+        <v>28</v>
       </c>
       <c r="AE6" t="n">
-        <v>20</v>
+        <v>150</v>
       </c>
       <c r="AF6" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="AG6" t="n">
-        <v>5.7</v>
+        <v>7.8</v>
       </c>
       <c r="AH6" t="n">
-        <v>8.199999999999999</v>
+        <v>23</v>
       </c>
       <c r="AI6" t="n">
-        <v>27</v>
+        <v>110</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AK6" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AL6" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="AM6" t="n">
-        <v>85</v>
+        <v>200</v>
       </c>
       <c r="AN6" t="n">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="AO6" t="n">
-        <v>50</v>
+        <v>280</v>
       </c>
       <c r="AP6" t="n">
-        <v>18</v>
+        <v>13.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>18</v>
+        <v>13.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>18</v>
+        <v>13.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>18</v>
+        <v>13.5</v>
       </c>
       <c r="AT6" t="n">
-        <v>18</v>
+        <v>6.6</v>
       </c>
       <c r="AU6" t="n">
-        <v>3.7</v>
+        <v>8.4</v>
       </c>
       <c r="AV6" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="AW6" t="n">
-        <v>16.5</v>
+        <v>110</v>
       </c>
       <c r="AX6" t="n">
-        <v>18</v>
+        <v>5.6</v>
       </c>
       <c r="AY6" t="n">
-        <v>5.3</v>
+        <v>7.2</v>
       </c>
       <c r="AZ6" t="n">
-        <v>7.4</v>
+        <v>19</v>
       </c>
       <c r="BA6" t="n">
-        <v>24</v>
+        <v>75</v>
       </c>
       <c r="BB6" t="n">
-        <v>18</v>
+        <v>9.4</v>
       </c>
       <c r="BC6" t="n">
-        <v>18.5</v>
+        <v>13</v>
       </c>
       <c r="BD6" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="BE6" t="n">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="BF6" t="n">
-        <v>36</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG6" t="n">
-        <v>32</v>
+        <v>150</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-04 17:51:34</t>
+          <t>2026-05-04 20:01:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>Brazilian Serie C</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1713,191 +1713,191 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Union Magdalena</t>
+          <t>Ypiranga RS</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Barranquilla</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.86</v>
+        <v>2.14</v>
       </c>
       <c r="G7" t="n">
-        <v>1.88</v>
+        <v>2.24</v>
       </c>
       <c r="H7" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="I7" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="J7" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="K7" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="L7" t="n">
-        <v>1.4</v>
+        <v>1.61</v>
       </c>
       <c r="M7" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="N7" t="n">
-        <v>3.95</v>
+        <v>2.78</v>
       </c>
       <c r="O7" t="n">
-        <v>1.32</v>
+        <v>1.53</v>
       </c>
       <c r="P7" t="n">
-        <v>2</v>
+        <v>1.61</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.98</v>
+        <v>2.62</v>
       </c>
       <c r="R7" t="n">
-        <v>1.39</v>
+        <v>1.22</v>
       </c>
       <c r="S7" t="n">
-        <v>3.5</v>
+        <v>5.4</v>
       </c>
       <c r="T7" t="n">
-        <v>1.81</v>
+        <v>2.1</v>
       </c>
       <c r="U7" t="n">
-        <v>2.1</v>
+        <v>1.78</v>
       </c>
       <c r="V7" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="W7" t="n">
-        <v>2.12</v>
+        <v>1.8</v>
       </c>
       <c r="X7" t="n">
-        <v>15.5</v>
+        <v>8.6</v>
       </c>
       <c r="Y7" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="Z7" t="n">
         <v>36</v>
       </c>
       <c r="AA7" t="n">
-        <v>110</v>
+        <v>900</v>
       </c>
       <c r="AB7" t="n">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="AC7" t="n">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>60</v>
+        <v>470</v>
       </c>
       <c r="AF7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG7" t="n">
         <v>11.5</v>
       </c>
-      <c r="AG7" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="AH7" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="AI7" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AJ7" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="AK7" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="AL7" t="n">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="AM7" t="n">
         <v>580</v>
       </c>
       <c r="AN7" t="n">
-        <v>13.5</v>
+        <v>30</v>
       </c>
       <c r="AO7" t="n">
-        <v>65</v>
+        <v>700</v>
       </c>
       <c r="AP7" t="n">
-        <v>13.5</v>
+        <v>8</v>
       </c>
       <c r="AQ7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>26</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>29</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>16</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>46</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA7" t="n">
         <v>14.5</v>
       </c>
-      <c r="AR7" t="n">
-        <v>29</v>
-      </c>
-      <c r="AS7" t="n">
+      <c r="BB7" t="n">
+        <v>21</v>
+      </c>
+      <c r="BC7" t="n">
         <v>25</v>
       </c>
-      <c r="AT7" t="n">
-        <v>8</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>48</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>18</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>48</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>20</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>18.5</v>
-      </c>
       <c r="BD7" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="BE7" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="BF7" t="n">
-        <v>12</v>
+        <v>19.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>50</v>
+        <v>14.5</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-04 17:51:34</t>
+          <t>2026-05-04 20:01:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Brazilian Serie C</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1907,191 +1907,191 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Barra FC</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.99</v>
+        <v>2.66</v>
       </c>
       <c r="G8" t="n">
-        <v>2.02</v>
+        <v>2.74</v>
       </c>
       <c r="H8" t="n">
-        <v>4.8</v>
+        <v>3.25</v>
       </c>
       <c r="I8" t="n">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="J8" t="n">
-        <v>3.35</v>
+        <v>2.96</v>
       </c>
       <c r="K8" t="n">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="L8" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="M8" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="N8" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="O8" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="P8" t="n">
-        <v>1.63</v>
+        <v>1.51</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.52</v>
+        <v>2.82</v>
       </c>
       <c r="R8" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="S8" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="T8" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="U8" t="n">
-        <v>1.82</v>
+        <v>1.76</v>
       </c>
       <c r="V8" t="n">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="W8" t="n">
-        <v>1.98</v>
+        <v>1.57</v>
       </c>
       <c r="X8" t="n">
-        <v>9.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y8" t="n">
-        <v>14</v>
+        <v>9.4</v>
       </c>
       <c r="Z8" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="AA8" t="n">
-        <v>130</v>
+        <v>70</v>
       </c>
       <c r="AB8" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC8" t="n">
         <v>7</v>
       </c>
-      <c r="AC8" t="n">
-        <v>7.6</v>
-      </c>
       <c r="AD8" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AE8" t="n">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="AF8" t="n">
-        <v>10.5</v>
+        <v>16</v>
       </c>
       <c r="AG8" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="AH8" t="n">
         <v>25</v>
       </c>
       <c r="AI8" t="n">
-        <v>110</v>
+        <v>260</v>
       </c>
       <c r="AJ8" t="n">
-        <v>24</v>
+        <v>85</v>
       </c>
       <c r="AK8" t="n">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="AL8" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>500</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>50</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>80</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>18</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>50</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>44</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>23</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>70</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>38</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>32</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>38</v>
+      </c>
+      <c r="BE8" t="n">
         <v>55</v>
       </c>
-      <c r="AM8" t="n">
-        <v>190</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>22</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>120</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>29</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>60</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>70</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>22</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>50</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>21</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>22</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>34</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>28</v>
-      </c>
       <c r="BF8" t="n">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="BG8" t="n">
-        <v>15.5</v>
+        <v>38</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-04 17:51:34</t>
+          <t>2026-05-04 20:01:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Chilean Primera B</t>
+          <t>Brazilian Serie C</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,191 +2101,191 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Floresta EC</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Union San Felipe</t>
+          <t>Maranhao</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="H9" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="I9" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="J9" t="n">
-        <v>3.55</v>
+        <v>3.05</v>
       </c>
       <c r="K9" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="L9" t="n">
-        <v>1.4</v>
+        <v>1.64</v>
       </c>
       <c r="M9" t="n">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="N9" t="n">
-        <v>3.9</v>
+        <v>2.46</v>
       </c>
       <c r="O9" t="n">
-        <v>1.3</v>
+        <v>1.63</v>
       </c>
       <c r="P9" t="n">
-        <v>2</v>
+        <v>1.47</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.96</v>
+        <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>1.39</v>
+        <v>1.17</v>
       </c>
       <c r="S9" t="n">
-        <v>3.4</v>
+        <v>6.4</v>
       </c>
       <c r="T9" t="n">
-        <v>1.82</v>
+        <v>2.34</v>
       </c>
       <c r="U9" t="n">
-        <v>2.08</v>
+        <v>1.64</v>
       </c>
       <c r="V9" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="W9" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="X9" t="n">
-        <v>16</v>
+        <v>7.8</v>
       </c>
       <c r="Y9" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="Z9" t="n">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="AA9" t="n">
-        <v>270</v>
+        <v>900</v>
       </c>
       <c r="AB9" t="n">
-        <v>9</v>
+        <v>6.2</v>
       </c>
       <c r="AC9" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD9" t="n">
-        <v>18.5</v>
+        <v>24</v>
       </c>
       <c r="AE9" t="n">
-        <v>65</v>
+        <v>700</v>
       </c>
       <c r="AF9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AG9" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>18.5</v>
+        <v>30</v>
       </c>
       <c r="AI9" t="n">
-        <v>150</v>
+        <v>700</v>
       </c>
       <c r="AJ9" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AK9" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="AL9" t="n">
-        <v>44</v>
+        <v>170</v>
       </c>
       <c r="AM9" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="AN9" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="AO9" t="n">
-        <v>100</v>
+        <v>700</v>
       </c>
       <c r="AP9" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="AQ9" t="n">
-        <v>14</v>
+        <v>10.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="AS9" t="n">
-        <v>20</v>
+        <v>10.5</v>
       </c>
       <c r="AT9" t="n">
-        <v>8</v>
+        <v>5.3</v>
       </c>
       <c r="AU9" t="n">
         <v>7</v>
       </c>
       <c r="AV9" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AW9" t="n">
-        <v>18</v>
+        <v>10.5</v>
       </c>
       <c r="AX9" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY9" t="n">
         <v>10.5</v>
       </c>
-      <c r="AY9" t="n">
-        <v>9.4</v>
-      </c>
       <c r="AZ9" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="BA9" t="n">
-        <v>38</v>
+        <v>11.5</v>
       </c>
       <c r="BB9" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="BC9" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="BD9" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="BE9" t="n">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="BF9" t="n">
-        <v>11.5</v>
+        <v>19</v>
       </c>
       <c r="BG9" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-04 17:51:34</t>
+          <t>2026-05-04 20:01:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Bolivian Liga de Futbol Profesional</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2295,191 +2295,191 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>19:15:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Velez Sarsfield</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Newells</t>
+          <t>Blooming Santa Cruz</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.79</v>
+        <v>1.86</v>
       </c>
       <c r="G10" t="n">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="H10" t="n">
-        <v>5.6</v>
+        <v>3.9</v>
       </c>
       <c r="I10" t="n">
-        <v>5.9</v>
+        <v>4.2</v>
       </c>
       <c r="J10" t="n">
-        <v>3.65</v>
+        <v>4.4</v>
       </c>
       <c r="K10" t="n">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="L10" t="n">
-        <v>1.48</v>
+        <v>1.26</v>
       </c>
       <c r="M10" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="N10" t="n">
-        <v>3.2</v>
+        <v>6.6</v>
       </c>
       <c r="O10" t="n">
-        <v>1.42</v>
+        <v>1.15</v>
       </c>
       <c r="P10" t="n">
-        <v>1.75</v>
+        <v>2.94</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.26</v>
+        <v>1.49</v>
       </c>
       <c r="R10" t="n">
-        <v>1.28</v>
+        <v>1.76</v>
       </c>
       <c r="S10" t="n">
-        <v>4.4</v>
+        <v>2.2</v>
       </c>
       <c r="T10" t="n">
-        <v>2.08</v>
+        <v>1.5</v>
       </c>
       <c r="U10" t="n">
-        <v>1.85</v>
+        <v>2.72</v>
       </c>
       <c r="V10" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="W10" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="X10" t="n">
-        <v>11.5</v>
+        <v>32</v>
       </c>
       <c r="Y10" t="n">
-        <v>16.5</v>
+        <v>27</v>
       </c>
       <c r="Z10" t="n">
         <v>44</v>
       </c>
       <c r="AA10" t="n">
-        <v>900</v>
+        <v>120</v>
       </c>
       <c r="AB10" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>24</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN10" t="n">
         <v>7.2</v>
       </c>
-      <c r="AC10" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD10" t="n">
+      <c r="AO10" t="n">
+        <v>26</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>26</v>
+      </c>
+      <c r="AQ10" t="n">
         <v>23</v>
       </c>
-      <c r="AE10" t="n">
-        <v>95</v>
-      </c>
-      <c r="AF10" t="n">
+      <c r="AR10" t="n">
+        <v>34</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>14</v>
+      </c>
+      <c r="AU10" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="AG10" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>19</v>
-      </c>
-      <c r="AK10" t="n">
+      <c r="AV10" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>34</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>34</v>
+      </c>
+      <c r="BB10" t="n">
         <v>22</v>
       </c>
-      <c r="AL10" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>160</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>15</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>140</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ10" t="n">
+      <c r="BC10" t="n">
         <v>14.5</v>
       </c>
-      <c r="AR10" t="n">
-        <v>38</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>44</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV10" t="n">
+      <c r="BD10" t="n">
         <v>20</v>
       </c>
-      <c r="AW10" t="n">
-        <v>55</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ10" t="n">
+      <c r="BE10" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BG10" t="n">
         <v>21</v>
       </c>
-      <c r="BA10" t="n">
-        <v>60</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>17</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>19</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>40</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>90</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>13</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>70</v>
-      </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-04 17:51:34</t>
+          <t>2026-05-04 20:01:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2489,126 +2489,126 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Penarol</t>
+          <t>Quindio</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Defensor Sporting</t>
+          <t>Tigres FC Zipaquira</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.81</v>
+        <v>1.66</v>
       </c>
       <c r="G11" t="n">
-        <v>1.84</v>
+        <v>1.71</v>
       </c>
       <c r="H11" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="I11" t="n">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
       <c r="J11" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="K11" t="n">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="L11" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="M11" t="n">
         <v>1.1</v>
       </c>
       <c r="N11" t="n">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="O11" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="P11" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="R11" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="S11" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="T11" t="n">
-        <v>2.1</v>
+        <v>2.26</v>
       </c>
       <c r="U11" t="n">
-        <v>1.81</v>
+        <v>1.66</v>
       </c>
       <c r="V11" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="W11" t="n">
-        <v>2.18</v>
+        <v>2.4</v>
       </c>
       <c r="X11" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Y11" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="Z11" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="AA11" t="n">
-        <v>160</v>
+        <v>260</v>
       </c>
       <c r="AB11" t="n">
         <v>6.6</v>
       </c>
       <c r="AC11" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD11" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="AE11" t="n">
-        <v>95</v>
+        <v>150</v>
       </c>
       <c r="AF11" t="n">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="AG11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AH11" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="AI11" t="n">
-        <v>110</v>
+        <v>170</v>
       </c>
       <c r="AJ11" t="n">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="AK11" t="n">
         <v>23</v>
       </c>
       <c r="AL11" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AM11" t="n">
-        <v>180</v>
+        <v>250</v>
       </c>
       <c r="AN11" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AO11" t="n">
-        <v>140</v>
+        <v>280</v>
       </c>
       <c r="AP11" t="n">
         <v>9.6</v>
@@ -2617,63 +2617,63 @@
         <v>14.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>32</v>
+        <v>10.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="AT11" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="AU11" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AV11" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AW11" t="n">
-        <v>44</v>
+        <v>10.5</v>
       </c>
       <c r="AX11" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="AY11" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ11" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="BA11" t="n">
-        <v>60</v>
+        <v>10.5</v>
       </c>
       <c r="BB11" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BC11" t="n">
         <v>20</v>
       </c>
       <c r="BD11" t="n">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="BE11" t="n">
-        <v>70</v>
+        <v>11</v>
       </c>
       <c r="BF11" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BG11" t="n">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-04 17:51:34</t>
+          <t>2026-05-04 20:01:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2683,191 +2683,191 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Ypiranga RS</t>
+          <t>Estudiantes Rio Cuarto</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Instituto</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.06</v>
+        <v>3.85</v>
       </c>
       <c r="G12" t="n">
-        <v>2.16</v>
+        <v>4.1</v>
       </c>
       <c r="H12" t="n">
-        <v>4.2</v>
+        <v>2.36</v>
       </c>
       <c r="I12" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="J12" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="K12" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="L12" t="n">
-        <v>1.55</v>
+        <v>1.69</v>
       </c>
       <c r="M12" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="N12" t="n">
-        <v>2.84</v>
+        <v>2.52</v>
       </c>
       <c r="O12" t="n">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="P12" t="n">
-        <v>1.59</v>
+        <v>1.49</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.52</v>
+        <v>2.98</v>
       </c>
       <c r="R12" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="S12" t="n">
-        <v>5.1</v>
+        <v>6.6</v>
       </c>
       <c r="T12" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="U12" t="n">
-        <v>1.82</v>
+        <v>1.71</v>
       </c>
       <c r="V12" t="n">
-        <v>1.27</v>
+        <v>1.71</v>
       </c>
       <c r="W12" t="n">
-        <v>1.86</v>
+        <v>1.33</v>
       </c>
       <c r="X12" t="n">
-        <v>9.6</v>
+        <v>7.8</v>
       </c>
       <c r="Y12" t="n">
-        <v>18</v>
+        <v>6.8</v>
       </c>
       <c r="Z12" t="n">
-        <v>100</v>
+        <v>12.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>900</v>
+        <v>36</v>
       </c>
       <c r="AB12" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>38</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>29</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>160</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>80</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>120</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>250</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>150</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>40</v>
+      </c>
+      <c r="AP12" t="n">
         <v>7.2</v>
       </c>
-      <c r="AC12" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>30</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>470</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG12" t="n">
+      <c r="AQ12" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AR12" t="n">
         <v>11</v>
       </c>
-      <c r="AH12" t="n">
-        <v>60</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>140</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>65</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>500</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>36</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>700</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>15</v>
-      </c>
       <c r="AS12" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="AT12" t="n">
-        <v>6.2</v>
+        <v>9</v>
       </c>
       <c r="AU12" t="n">
         <v>6.6</v>
       </c>
       <c r="AV12" t="n">
-        <v>16</v>
+        <v>11.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="AX12" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="AY12" t="n">
-        <v>9.800000000000001</v>
+        <v>16.5</v>
       </c>
       <c r="AZ12" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="BA12" t="n">
-        <v>12.5</v>
+        <v>38</v>
       </c>
       <c r="BB12" t="n">
-        <v>11</v>
+        <v>60</v>
       </c>
       <c r="BC12" t="n">
-        <v>18.5</v>
+        <v>60</v>
       </c>
       <c r="BD12" t="n">
-        <v>28</v>
+        <v>85</v>
       </c>
       <c r="BE12" t="n">
-        <v>13.5</v>
+        <v>90</v>
       </c>
       <c r="BF12" t="n">
-        <v>9.199999999999999</v>
+        <v>95</v>
       </c>
       <c r="BG12" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-04 17:51:34</t>
+          <t>2026-05-04 20:01:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Chilean Primera B</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2877,1154 +2877,184 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Barra FC</t>
+          <t>Deportes Recoleta</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.2</v>
+        <v>1.96</v>
       </c>
       <c r="G13" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="H13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I13" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N13" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Q13" t="n">
         <v>2.3</v>
       </c>
-      <c r="H13" t="n">
-        <v>4</v>
-      </c>
-      <c r="I13" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J13" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="N13" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="P13" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>2.78</v>
-      </c>
       <c r="R13" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="S13" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="T13" t="n">
-        <v>2.22</v>
+        <v>2.06</v>
       </c>
       <c r="U13" t="n">
-        <v>1.68</v>
+        <v>1.81</v>
       </c>
       <c r="V13" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="W13" t="n">
-        <v>1.76</v>
+        <v>1.94</v>
       </c>
       <c r="X13" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>44</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>260</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AC13" t="n">
         <v>8</v>
       </c>
-      <c r="Y13" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>27</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>110</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>7.4</v>
-      </c>
       <c r="AD13" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AE13" t="n">
-        <v>80</v>
+        <v>130</v>
       </c>
       <c r="AF13" t="n">
         <v>12</v>
       </c>
       <c r="AG13" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH13" t="n">
         <v>28</v>
       </c>
       <c r="AI13" t="n">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="AJ13" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="AK13" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL13" t="n">
         <v>70</v>
       </c>
       <c r="AM13" t="n">
-        <v>240</v>
+        <v>170</v>
       </c>
       <c r="AN13" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AO13" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AP13" t="n">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="AQ13" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AR13" t="n">
-        <v>23</v>
+        <v>7.8</v>
       </c>
       <c r="AS13" t="n">
-        <v>28</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT13" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AU13" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV13" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>38</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX13" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AY13" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AZ13" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="BA13" t="n">
-        <v>15.5</v>
+        <v>9</v>
       </c>
       <c r="BB13" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="BC13" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="BD13" t="n">
-        <v>32</v>
+        <v>8.4</v>
       </c>
       <c r="BE13" t="n">
-        <v>16.5</v>
+        <v>9.4</v>
       </c>
       <c r="BF13" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="BG13" t="n">
-        <v>13.5</v>
+        <v>30</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-05-04 17:51:34</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Brazilian Serie C</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>20:00:00</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Floresta EC</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Maranhao</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="G14" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="H14" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="I14" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="J14" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="K14" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="N14" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="O14" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="S14" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="X14" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>40</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>900</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>25</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>700</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>30</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>700</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>26</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>170</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>600</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>700</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>23</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>10</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>20</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>11</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>9</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>10</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>13</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>11</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>8</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>10</v>
-      </c>
-      <c r="BH14" t="inlineStr">
-        <is>
-          <t>2026-05-04 17:51:34</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>21:00:00</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Universitario de Vinto</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Blooming Santa Cruz</t>
-        </is>
-      </c>
-      <c r="F15" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="G15" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="H15" t="n">
-        <v>4</v>
-      </c>
-      <c r="I15" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J15" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N15" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="U15" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W15" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="X15" t="n">
-        <v>29</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>27</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>38</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>85</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>15</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>18</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>40</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>40</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>24</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>24</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>60</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>25</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>22</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>22</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>30</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>34</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>34</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>20</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>15</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>20</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>42</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>21</v>
-      </c>
-      <c r="BH15" t="inlineStr">
-        <is>
-          <t>2026-05-04 17:51:34</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Colombian Primera B</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>21:00:00</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Quindio</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Tigres FC Zipaquira</t>
-        </is>
-      </c>
-      <c r="F16" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="G16" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="H16" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="I16" t="n">
-        <v>9</v>
-      </c>
-      <c r="J16" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="K16" t="n">
-        <v>4</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N16" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="P16" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="S16" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="W16" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="X16" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>20</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>70</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>340</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>34</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>200</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>36</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>200</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>16</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>300</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>14</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>390</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>16</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>11</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>7</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>11</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>12</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BH16" t="inlineStr">
-        <is>
-          <t>2026-05-04 17:51:34</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Argentinian Primera Division</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>21:30:00</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Estudiantes Rio Cuarto</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Instituto</t>
-        </is>
-      </c>
-      <c r="F17" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="G17" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H17" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="I17" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="J17" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="K17" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="N17" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="O17" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="P17" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="S17" t="n">
-        <v>7</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="X17" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>34</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>38</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>26</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>30</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>100</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>80</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>120</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>260</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>130</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>42</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>7</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>6</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>11</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>29</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>9</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>32</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>22</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>17</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>25</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>46</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>48</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>65</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>40</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>50</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>40</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>24</v>
-      </c>
-      <c r="BH17" t="inlineStr">
-        <is>
-          <t>2026-05-04 17:51:34</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Chilean Primera B</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>21:30:00</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>San Marcos</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Deportes Recoleta</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="G18" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="H18" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="I18" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="J18" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="K18" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N18" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S18" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="X18" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>16</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>38</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>130</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>970</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>80</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>26</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>27</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>170</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>24</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>120</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>20</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BH18" t="inlineStr">
-        <is>
-          <t>2026-05-04 17:51:34</t>
+          <t>2026-05-04 20:01:00</t>
         </is>
       </c>
     </row>
